--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="227">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260302--01</t>
-  </si>
-  <si>
-    <t>20260302--02</t>
-  </si>
-  <si>
-    <t>20260302--03</t>
-  </si>
-  <si>
     <t>20260303--01</t>
   </si>
   <si>
@@ -145,85 +136,88 @@
     <t>20260308--05</t>
   </si>
   <si>
-    <t>02:18</t>
+    <t>20260309--01</t>
+  </si>
+  <si>
+    <t>20260309--02</t>
+  </si>
+  <si>
+    <t>20260309--03</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>02:03</t>
+  </si>
+  <si>
+    <t>04:25</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:32</t>
   </si>
   <si>
     <t>06:05</t>
   </si>
   <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>02:03</t>
-  </si>
-  <si>
-    <t>04:25</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>04:12</t>
-  </si>
-  <si>
-    <t>02:33</t>
+    <t>04:48</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>04:19</t>
-  </si>
-  <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>00:58</t>
+    <t>00:59</t>
   </si>
   <si>
     <t>04:31</t>
@@ -232,460 +226,457 @@
     <t>02:54</t>
   </si>
   <si>
-    <t>01:11</t>
-  </si>
-  <si>
-    <t>01:43</t>
-  </si>
-  <si>
-    <t>00:56:00</t>
-  </si>
-  <si>
-    <t>02:32:25</t>
-  </si>
-  <si>
-    <t>04:09:49</t>
-  </si>
-  <si>
-    <t>01:53:23</t>
-  </si>
-  <si>
-    <t>03:30:42</t>
-  </si>
-  <si>
-    <t>01:14:18</t>
-  </si>
-  <si>
-    <t>02:51:31</t>
-  </si>
-  <si>
-    <t>04:29:11</t>
-  </si>
-  <si>
-    <t>00:35:11</t>
-  </si>
-  <si>
-    <t>02:12:17</t>
-  </si>
-  <si>
-    <t>03:49:54</t>
-  </si>
-  <si>
-    <t>23:56:01</t>
-  </si>
-  <si>
-    <t>01:33:00</t>
-  </si>
-  <si>
-    <t>03:10:34</t>
-  </si>
-  <si>
-    <t>04:48:34</t>
-  </si>
-  <si>
-    <t>23:16:50</t>
-  </si>
-  <si>
-    <t>00:53:39</t>
-  </si>
-  <si>
-    <t>02:31:10</t>
-  </si>
-  <si>
-    <t>04:09:05</t>
-  </si>
-  <si>
-    <t>22:37:37</t>
-  </si>
-  <si>
-    <t>00:14:16</t>
-  </si>
-  <si>
-    <t>01:51:43</t>
-  </si>
-  <si>
-    <t>03:29:32</t>
-  </si>
-  <si>
-    <t>21:58:23</t>
-  </si>
-  <si>
-    <t>23:34:49</t>
-  </si>
-  <si>
-    <t>00:59:25</t>
-  </si>
-  <si>
-    <t>02:34:45</t>
-  </si>
-  <si>
-    <t>04:12:06</t>
-  </si>
-  <si>
-    <t>01:55:45</t>
-  </si>
-  <si>
-    <t>03:32:58</t>
-  </si>
-  <si>
-    <t>01:16:43</t>
-  </si>
-  <si>
-    <t>02:53:47</t>
-  </si>
-  <si>
-    <t>04:31:38</t>
-  </si>
-  <si>
-    <t>00:37:40</t>
-  </si>
-  <si>
-    <t>02:14:33</t>
-  </si>
-  <si>
-    <t>03:52:17</t>
-  </si>
-  <si>
-    <t>23:58:37</t>
-  </si>
-  <si>
-    <t>01:35:16</t>
-  </si>
-  <si>
-    <t>03:12:54</t>
-  </si>
-  <si>
-    <t>04:52:06</t>
-  </si>
-  <si>
-    <t>23:19:34</t>
-  </si>
-  <si>
-    <t>00:55:56</t>
-  </si>
-  <si>
-    <t>02:33:29</t>
-  </si>
-  <si>
-    <t>04:12:08</t>
-  </si>
-  <si>
-    <t>22:40:34</t>
-  </si>
-  <si>
-    <t>00:16:34</t>
-  </si>
-  <si>
-    <t>01:54:00</t>
-  </si>
-  <si>
-    <t>03:32:21</t>
-  </si>
-  <si>
-    <t>22:01:43</t>
-  </si>
-  <si>
-    <t>23:37:09</t>
-  </si>
-  <si>
-    <t>01:00:34</t>
-  </si>
-  <si>
-    <t>02:37:47</t>
-  </si>
-  <si>
-    <t>04:15:17</t>
-  </si>
-  <si>
-    <t>01:58:42</t>
+    <t>01:12</t>
+  </si>
+  <si>
+    <t>01:44</t>
+  </si>
+  <si>
+    <t>00:11</t>
+  </si>
+  <si>
+    <t>01:53:22</t>
+  </si>
+  <si>
+    <t>03:30:41</t>
+  </si>
+  <si>
+    <t>01:14:17</t>
+  </si>
+  <si>
+    <t>02:51:30</t>
+  </si>
+  <si>
+    <t>04:29:10</t>
+  </si>
+  <si>
+    <t>00:35:08</t>
+  </si>
+  <si>
+    <t>02:12:15</t>
+  </si>
+  <si>
+    <t>03:49:52</t>
+  </si>
+  <si>
+    <t>23:55:58</t>
+  </si>
+  <si>
+    <t>01:32:56</t>
+  </si>
+  <si>
+    <t>03:10:30</t>
+  </si>
+  <si>
+    <t>04:48:31</t>
+  </si>
+  <si>
+    <t>23:16:45</t>
+  </si>
+  <si>
+    <t>00:53:35</t>
+  </si>
+  <si>
+    <t>02:31:05</t>
+  </si>
+  <si>
+    <t>04:08:59</t>
+  </si>
+  <si>
+    <t>22:37:31</t>
+  </si>
+  <si>
+    <t>00:14:09</t>
+  </si>
+  <si>
+    <t>01:51:36</t>
+  </si>
+  <si>
+    <t>03:29:26</t>
+  </si>
+  <si>
+    <t>21:58:15</t>
+  </si>
+  <si>
+    <t>23:34:41</t>
+  </si>
+  <si>
+    <t>01:12:04</t>
+  </si>
+  <si>
+    <t>02:49:49</t>
+  </si>
+  <si>
+    <t>22:55:10</t>
+  </si>
+  <si>
+    <t>01:55:44</t>
+  </si>
+  <si>
+    <t>03:32:57</t>
+  </si>
+  <si>
+    <t>01:16:42</t>
+  </si>
+  <si>
+    <t>02:53:46</t>
+  </si>
+  <si>
+    <t>04:31:36</t>
+  </si>
+  <si>
+    <t>00:37:38</t>
+  </si>
+  <si>
+    <t>02:14:31</t>
+  </si>
+  <si>
+    <t>03:52:15</t>
+  </si>
+  <si>
+    <t>23:58:33</t>
+  </si>
+  <si>
+    <t>01:35:13</t>
+  </si>
+  <si>
+    <t>03:12:51</t>
+  </si>
+  <si>
+    <t>04:52:03</t>
+  </si>
+  <si>
+    <t>23:19:29</t>
+  </si>
+  <si>
+    <t>00:55:51</t>
+  </si>
+  <si>
+    <t>02:33:24</t>
+  </si>
+  <si>
+    <t>04:12:03</t>
+  </si>
+  <si>
+    <t>22:40:28</t>
+  </si>
+  <si>
+    <t>00:16:27</t>
+  </si>
+  <si>
+    <t>01:53:54</t>
+  </si>
+  <si>
+    <t>03:32:14</t>
+  </si>
+  <si>
+    <t>22:01:35</t>
+  </si>
+  <si>
+    <t>23:37:01</t>
+  </si>
+  <si>
+    <t>01:14:20</t>
+  </si>
+  <si>
+    <t>02:52:28</t>
+  </si>
+  <si>
+    <t>22:57:32</t>
+  </si>
+  <si>
+    <t>01:58:41</t>
   </si>
   <si>
     <t>03:36:10</t>
   </si>
   <si>
-    <t>01:19:33</t>
-  </si>
-  <si>
-    <t>02:57:00</t>
-  </si>
-  <si>
-    <t>04:34:26</t>
-  </si>
-  <si>
-    <t>00:40:20</t>
-  </si>
-  <si>
-    <t>02:17:45</t>
+    <t>01:19:31</t>
+  </si>
+  <si>
+    <t>02:56:58</t>
+  </si>
+  <si>
+    <t>04:34:25</t>
+  </si>
+  <si>
+    <t>00:40:18</t>
+  </si>
+  <si>
+    <t>02:17:43</t>
+  </si>
+  <si>
+    <t>03:55:11</t>
+  </si>
+  <si>
+    <t>00:01:02</t>
+  </si>
+  <si>
+    <t>01:38:24</t>
+  </si>
+  <si>
+    <t>03:15:52</t>
+  </si>
+  <si>
+    <t>04:53:04</t>
+  </si>
+  <si>
+    <t>23:21:41</t>
+  </si>
+  <si>
+    <t>00:59:01</t>
+  </si>
+  <si>
+    <t>02:36:30</t>
+  </si>
+  <si>
+    <t>04:13:45</t>
+  </si>
+  <si>
+    <t>22:42:18</t>
+  </si>
+  <si>
+    <t>00:19:34</t>
+  </si>
+  <si>
+    <t>01:57:02</t>
+  </si>
+  <si>
+    <t>03:34:21</t>
+  </si>
+  <si>
+    <t>22:02:51</t>
+  </si>
+  <si>
+    <t>23:40:03</t>
+  </si>
+  <si>
+    <t>01:17:31</t>
+  </si>
+  <si>
+    <t>02:54:52</t>
+  </si>
+  <si>
+    <t>23:00:28</t>
+  </si>
+  <si>
+    <t>02:01:38</t>
+  </si>
+  <si>
+    <t>03:39:23</t>
+  </si>
+  <si>
+    <t>01:22:22</t>
+  </si>
+  <si>
+    <t>03:00:12</t>
+  </si>
+  <si>
+    <t>04:37:14</t>
+  </si>
+  <si>
+    <t>00:42:59</t>
+  </si>
+  <si>
+    <t>02:20:56</t>
+  </si>
+  <si>
+    <t>03:58:07</t>
+  </si>
+  <si>
+    <t>00:03:30</t>
+  </si>
+  <si>
+    <t>01:41:35</t>
+  </si>
+  <si>
+    <t>03:18:54</t>
+  </si>
+  <si>
+    <t>04:54:06</t>
+  </si>
+  <si>
+    <t>23:23:54</t>
+  </si>
+  <si>
+    <t>01:02:10</t>
+  </si>
+  <si>
+    <t>02:39:35</t>
+  </si>
+  <si>
+    <t>04:15:27</t>
+  </si>
+  <si>
+    <t>22:44:08</t>
+  </si>
+  <si>
+    <t>00:22:40</t>
+  </si>
+  <si>
+    <t>02:00:11</t>
+  </si>
+  <si>
+    <t>03:36:27</t>
+  </si>
+  <si>
+    <t>22:04:07</t>
+  </si>
+  <si>
+    <t>23:43:06</t>
+  </si>
+  <si>
+    <t>01:20:42</t>
+  </si>
+  <si>
+    <t>02:57:16</t>
+  </si>
+  <si>
+    <t>23:03:26</t>
+  </si>
+  <si>
+    <t>02:04:01</t>
+  </si>
+  <si>
+    <t>03:41:39</t>
+  </si>
+  <si>
+    <t>01:24:48</t>
+  </si>
+  <si>
+    <t>03:02:27</t>
+  </si>
+  <si>
+    <t>04:39:40</t>
+  </si>
+  <si>
+    <t>00:45:29</t>
+  </si>
+  <si>
+    <t>02:23:12</t>
+  </si>
+  <si>
+    <t>04:00:30</t>
+  </si>
+  <si>
+    <t>00:06:07</t>
+  </si>
+  <si>
+    <t>01:43:52</t>
+  </si>
+  <si>
+    <t>03:21:14</t>
+  </si>
+  <si>
+    <t>04:57:37</t>
+  </si>
+  <si>
+    <t>23:26:39</t>
+  </si>
+  <si>
+    <t>01:04:27</t>
+  </si>
+  <si>
+    <t>02:41:54</t>
+  </si>
+  <si>
+    <t>04:18:29</t>
+  </si>
+  <si>
+    <t>22:47:06</t>
+  </si>
+  <si>
+    <t>00:24:59</t>
+  </si>
+  <si>
+    <t>02:02:28</t>
+  </si>
+  <si>
+    <t>03:39:14</t>
+  </si>
+  <si>
+    <t>22:07:28</t>
+  </si>
+  <si>
+    <t>23:45:26</t>
+  </si>
+  <si>
+    <t>01:22:58</t>
+  </si>
+  <si>
+    <t>02:59:53</t>
+  </si>
+  <si>
+    <t>23:05:48</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>02:03:13</t>
+  </si>
+  <si>
+    <t>03:36:43</t>
+  </si>
+  <si>
+    <t>02:59:13</t>
+  </si>
+  <si>
+    <t>04:32:43</t>
+  </si>
+  <si>
+    <t>02:21:43</t>
   </si>
   <si>
     <t>03:55:13</t>
   </si>
   <si>
-    <t>00:01:05</t>
-  </si>
-  <si>
-    <t>01:38:27</t>
-  </si>
-  <si>
-    <t>03:15:56</t>
-  </si>
-  <si>
-    <t>04:53:08</t>
-  </si>
-  <si>
-    <t>23:21:46</t>
-  </si>
-  <si>
-    <t>00:59:06</t>
-  </si>
-  <si>
-    <t>02:36:34</t>
-  </si>
-  <si>
-    <t>04:13:50</t>
-  </si>
-  <si>
-    <t>22:42:24</t>
-  </si>
-  <si>
-    <t>00:19:40</t>
-  </si>
-  <si>
-    <t>01:57:09</t>
-  </si>
-  <si>
-    <t>03:34:27</t>
-  </si>
-  <si>
-    <t>22:02:59</t>
-  </si>
-  <si>
-    <t>23:40:11</t>
-  </si>
-  <si>
-    <t>01:01:43</t>
-  </si>
-  <si>
-    <t>02:40:50</t>
-  </si>
-  <si>
-    <t>04:18:29</t>
-  </si>
-  <si>
-    <t>02:01:39</t>
-  </si>
-  <si>
-    <t>03:39:23</t>
-  </si>
-  <si>
-    <t>01:22:23</t>
-  </si>
-  <si>
-    <t>03:00:13</t>
-  </si>
-  <si>
-    <t>04:37:16</t>
-  </si>
-  <si>
-    <t>00:43:01</t>
-  </si>
-  <si>
-    <t>02:20:58</t>
-  </si>
-  <si>
-    <t>03:58:09</t>
-  </si>
-  <si>
-    <t>00:03:34</t>
-  </si>
-  <si>
-    <t>01:41:39</t>
-  </si>
-  <si>
-    <t>03:18:57</t>
-  </si>
-  <si>
-    <t>04:54:09</t>
-  </si>
-  <si>
-    <t>23:23:59</t>
-  </si>
-  <si>
-    <t>01:02:15</t>
-  </si>
-  <si>
-    <t>02:39:40</t>
-  </si>
-  <si>
-    <t>04:15:31</t>
-  </si>
-  <si>
-    <t>22:44:15</t>
-  </si>
-  <si>
-    <t>00:22:47</t>
-  </si>
-  <si>
-    <t>02:00:18</t>
-  </si>
-  <si>
-    <t>03:36:33</t>
-  </si>
-  <si>
-    <t>22:04:16</t>
-  </si>
-  <si>
-    <t>23:43:14</t>
-  </si>
-  <si>
-    <t>01:05:10</t>
-  </si>
-  <si>
-    <t>02:43:11</t>
-  </si>
-  <si>
-    <t>04:20:46</t>
-  </si>
-  <si>
-    <t>02:04:02</t>
-  </si>
-  <si>
-    <t>03:41:39</t>
-  </si>
-  <si>
-    <t>01:24:49</t>
-  </si>
-  <si>
-    <t>03:02:29</t>
-  </si>
-  <si>
-    <t>04:39:42</t>
-  </si>
-  <si>
-    <t>00:45:32</t>
-  </si>
-  <si>
-    <t>02:23:14</t>
-  </si>
-  <si>
-    <t>04:00:32</t>
-  </si>
-  <si>
-    <t>00:06:10</t>
-  </si>
-  <si>
-    <t>01:43:55</t>
-  </si>
-  <si>
-    <t>03:21:18</t>
-  </si>
-  <si>
-    <t>04:57:41</t>
-  </si>
-  <si>
-    <t>23:26:44</t>
-  </si>
-  <si>
-    <t>01:04:32</t>
-  </si>
-  <si>
-    <t>02:41:59</t>
-  </si>
-  <si>
-    <t>04:18:34</t>
-  </si>
-  <si>
-    <t>22:47:13</t>
-  </si>
-  <si>
-    <t>00:25:05</t>
-  </si>
-  <si>
-    <t>02:02:35</t>
-  </si>
-  <si>
-    <t>03:39:21</t>
-  </si>
-  <si>
-    <t>22:07:36</t>
-  </si>
-  <si>
-    <t>23:45:34</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>02:40:40</t>
-  </si>
-  <si>
-    <t>04:14:10</t>
-  </si>
-  <si>
-    <t>02:03:13</t>
-  </si>
-  <si>
-    <t>03:36:43</t>
-  </si>
-  <si>
-    <t>02:59:15</t>
-  </si>
-  <si>
-    <t>04:32:45</t>
-  </si>
-  <si>
-    <t>02:21:45</t>
-  </si>
-  <si>
-    <t>03:55:15</t>
-  </si>
-  <si>
-    <t>03:17:46</t>
-  </si>
-  <si>
-    <t>04:51:16</t>
-  </si>
-  <si>
-    <t>02:40:18</t>
-  </si>
-  <si>
-    <t>04:13:48</t>
-  </si>
-  <si>
-    <t>03:36:23</t>
+    <t>03:17:42</t>
+  </si>
+  <si>
+    <t>04:51:12</t>
+  </si>
+  <si>
+    <t>02:40:13</t>
+  </si>
+  <si>
+    <t>04:13:43</t>
+  </si>
+  <si>
+    <t>03:36:16</t>
+  </si>
+  <si>
+    <t>02:58:54</t>
   </si>
   <si>
     <t>B</t>
@@ -697,13 +688,13 @@
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -752,7 +743,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,85 +827,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1427,7 +1418,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
@@ -1436,46 +1427,46 @@
         <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="L2" s="4">
-        <v>-41.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="O2" s="6">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="P2" s="7">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="9">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1483,7 +1474,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
@@ -1492,46 +1483,46 @@
         <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L3" s="4">
-        <v>-29.9</v>
+        <v>-21.1</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="10">
+      <c r="O3" s="6">
+        <v>59</v>
+      </c>
+      <c r="P3" s="7">
         <v>80</v>
       </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="Q3" s="10">
+        <v>3</v>
+      </c>
+      <c r="R3" s="11">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1539,54 +1530,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="L4" s="4">
-        <v>-15.3</v>
+        <v>-39</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O4" s="11">
-        <v>42</v>
-      </c>
-      <c r="P4" s="10">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
+        <v>224</v>
+      </c>
+      <c r="O4" s="12">
+        <v>39</v>
+      </c>
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>39</v>
+      </c>
+      <c r="R4" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1595,55 +1586,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L5" s="4">
-        <v>-34.8</v>
+        <v>-26.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O5" s="11">
-        <v>88</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>71</v>
+        <v>225</v>
+      </c>
+      <c r="O5" s="12">
+        <v>48</v>
+      </c>
+      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>48</v>
       </c>
       <c r="R5" s="13">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1651,55 +1642,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.1</v>
+        <v>-11.7</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O6" s="11">
-        <v>63</v>
-      </c>
-      <c r="P6" s="8">
+      <c r="O6" s="12">
+        <v>38</v>
+      </c>
+      <c r="P6" s="13">
         <v>0</v>
       </c>
       <c r="Q6" s="14">
-        <v>52</v>
-      </c>
-      <c r="R6" s="14">
-        <v>48</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1707,55 +1698,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>-39</v>
+        <v>-42.1</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O7" s="9">
-        <v>1</v>
-      </c>
-      <c r="P7" s="8">
+      <c r="O7" s="12">
+        <v>9</v>
+      </c>
+      <c r="P7" s="13">
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1763,54 +1754,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L8" s="4">
-        <v>-26.5</v>
+        <v>-31.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
+        <v>224</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1819,54 +1810,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L9" s="4">
-        <v>-11.7</v>
+        <v>-17.5</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O9" s="11">
-        <v>60</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>60</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="O9" s="16">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1875,54 +1866,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.1</v>
+        <v>-44.1</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O10" s="6">
-        <v>29</v>
-      </c>
-      <c r="P10" s="15">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="O10" s="16">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1934,51 +1925,51 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="L11" s="4">
-        <v>-31.6</v>
+        <v>-36.2</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O11" s="9">
-        <v>10</v>
-      </c>
-      <c r="P11" s="16">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
+      <c r="O11" s="16">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1987,54 +1978,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L12" s="4">
-        <v>-17.4</v>
+        <v>-23.1</v>
       </c>
       <c r="M12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
+      <c r="O12" s="16">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2043,54 +2034,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="L13" s="4">
-        <v>-44.1</v>
+        <v>-8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O13" s="9">
-        <v>4</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
+        <v>226</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2099,54 +2090,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-36.2</v>
+        <v>-44.7</v>
       </c>
       <c r="M14" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O14" s="9">
-        <v>2</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
+      <c r="O14" s="12">
+        <v>23</v>
+      </c>
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>23</v>
+      </c>
+      <c r="R14" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2155,54 +2146,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4">
-        <v>-23</v>
+        <v>-39.8</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O15" s="6">
-        <v>10</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
+        <v>224</v>
+      </c>
+      <c r="O15" s="12">
+        <v>38</v>
+      </c>
+      <c r="P15" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>35</v>
+      </c>
+      <c r="R15" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2211,54 +2202,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L16" s="4">
-        <v>-8</v>
+        <v>-28.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O16" s="9">
-        <v>5</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
+        <v>224</v>
+      </c>
+      <c r="O16" s="12">
+        <v>43</v>
+      </c>
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>43</v>
+      </c>
+      <c r="R16" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2267,55 +2258,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="L17" s="4">
-        <v>-44.7</v>
+        <v>-13.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O17" s="11">
-        <v>81</v>
-      </c>
-      <c r="P17" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7">
-        <v>60</v>
+        <v>226</v>
+      </c>
+      <c r="O17" s="12">
+        <v>35</v>
+      </c>
+      <c r="P17" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>35</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2323,55 +2314,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L18" s="4">
-        <v>-39.8</v>
+        <v>-43.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O18" s="11">
-        <v>75</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>0</v>
-      </c>
-      <c r="R18" s="12">
-        <v>70</v>
+        <v>226</v>
+      </c>
+      <c r="O18" s="6">
+        <v>80</v>
+      </c>
+      <c r="P18" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="19">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2379,55 +2370,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-42.4</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="L19" s="4">
-        <v>-28.3</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O19" s="11">
-        <v>75</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="14">
-        <v>50</v>
+      <c r="O19" s="6">
+        <v>72</v>
+      </c>
+      <c r="P19" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="20">
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2435,55 +2426,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="L20" s="4">
-        <v>-13.9</v>
+        <v>-33.2</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O20" s="11">
-        <v>63</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="17">
-        <v>5</v>
+        <v>224</v>
+      </c>
+      <c r="O20" s="6">
+        <v>69</v>
+      </c>
+      <c r="P20" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2491,55 +2482,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>93</v>
+        <v>219</v>
       </c>
       <c r="L21" s="4">
-        <v>-43.8</v>
+        <v>-19.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O21" s="11">
-        <v>92</v>
-      </c>
-      <c r="P21" s="18">
-        <v>35</v>
-      </c>
-      <c r="Q21" s="14">
-        <v>51</v>
-      </c>
-      <c r="R21" s="19">
-        <v>21</v>
+        <v>225</v>
+      </c>
+      <c r="O21" s="6">
+        <v>50</v>
+      </c>
+      <c r="P21" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>0</v>
+      </c>
+      <c r="R21" s="21">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2547,55 +2538,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4">
-        <v>-42.4</v>
+        <v>-41.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O22" s="11">
-        <v>98</v>
-      </c>
-      <c r="P22" s="15">
-        <v>25</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>62</v>
-      </c>
-      <c r="R22" s="20">
-        <v>65</v>
+        <v>226</v>
+      </c>
+      <c r="O22" s="12">
+        <v>40</v>
+      </c>
+      <c r="P22" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>40</v>
+      </c>
+      <c r="R22" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2603,55 +2594,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23" s="4">
-        <v>-33.2</v>
+        <v>-43.6</v>
       </c>
       <c r="M23" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O23" s="11">
-        <v>93</v>
-      </c>
-      <c r="P23" s="19">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="14">
-        <v>49</v>
-      </c>
-      <c r="R23" s="14">
-        <v>48</v>
+      <c r="O23" s="12">
+        <v>24</v>
+      </c>
+      <c r="P23" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>24</v>
+      </c>
+      <c r="R23" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2659,55 +2650,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>200</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>223</v>
+        <v>95</v>
       </c>
       <c r="L24" s="4">
-        <v>-19.6</v>
+        <v>-37.3</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="O24" s="11">
-        <v>84</v>
-      </c>
-      <c r="P24" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q24" s="18">
-        <v>33</v>
-      </c>
-      <c r="R24" s="19">
-        <v>19</v>
+        <v>224</v>
+      </c>
+      <c r="O24" s="16">
+        <v>8</v>
+      </c>
+      <c r="P24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>8</v>
+      </c>
+      <c r="R24" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2715,7 +2706,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>64</v>
@@ -2724,46 +2715,46 @@
         <v>65</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="L25" s="4">
-        <v>-41.5</v>
+        <v>-25</v>
       </c>
       <c r="M25" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="O25" s="11">
-        <v>90</v>
-      </c>
-      <c r="P25" s="21">
-        <v>16</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>59</v>
-      </c>
-      <c r="R25" s="21">
-        <v>15</v>
+      <c r="O25" s="16">
+        <v>4</v>
+      </c>
+      <c r="P25" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>4</v>
+      </c>
+      <c r="R25" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2771,55 +2762,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L26" s="4">
-        <v>-43.6</v>
+        <v>-43.5</v>
       </c>
       <c r="M26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O26" s="11">
-        <v>94</v>
-      </c>
-      <c r="P26" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>62</v>
-      </c>
-      <c r="R26" s="21">
-        <v>16</v>
+      <c r="O26" s="16">
+        <v>0</v>
+      </c>
+      <c r="P26" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="238">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260303--01</t>
-  </si>
-  <si>
-    <t>20260303--02</t>
-  </si>
-  <si>
     <t>20260304--01</t>
   </si>
   <si>
@@ -145,102 +139,114 @@
     <t>20260309--03</t>
   </si>
   <si>
+    <t>20260310--01</t>
+  </si>
+  <si>
+    <t>20260310--02</t>
+  </si>
+  <si>
+    <t>20260310--03</t>
+  </si>
+  <si>
+    <t>20260310--04</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>05:38</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>04:25</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>02:32</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
     <t>05:54</t>
   </si>
   <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>02:03</t>
-  </si>
-  <si>
-    <t>04:25</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:32</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>04:48</t>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:14</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:40</t>
-  </si>
-  <si>
     <t>00:59</t>
   </si>
   <si>
     <t>04:31</t>
   </si>
   <si>
-    <t>02:54</t>
+    <t>02:55</t>
   </si>
   <si>
     <t>01:12</t>
   </si>
   <si>
-    <t>01:44</t>
+    <t>01:43</t>
   </si>
   <si>
     <t>00:11</t>
   </si>
   <si>
-    <t>01:53:22</t>
-  </si>
-  <si>
-    <t>03:30:41</t>
-  </si>
-  <si>
     <t>01:14:17</t>
   </si>
   <si>
@@ -250,7 +256,7 @@
     <t>04:29:10</t>
   </si>
   <si>
-    <t>00:35:08</t>
+    <t>00:35:09</t>
   </si>
   <si>
     <t>02:12:15</t>
@@ -259,61 +265,67 @@
     <t>03:49:52</t>
   </si>
   <si>
-    <t>23:55:58</t>
-  </si>
-  <si>
-    <t>01:32:56</t>
-  </si>
-  <si>
-    <t>03:10:30</t>
-  </si>
-  <si>
-    <t>04:48:31</t>
-  </si>
-  <si>
-    <t>23:16:45</t>
-  </si>
-  <si>
-    <t>00:53:35</t>
-  </si>
-  <si>
-    <t>02:31:05</t>
-  </si>
-  <si>
-    <t>04:08:59</t>
-  </si>
-  <si>
-    <t>22:37:31</t>
-  </si>
-  <si>
-    <t>00:14:09</t>
-  </si>
-  <si>
-    <t>01:51:36</t>
-  </si>
-  <si>
-    <t>03:29:26</t>
-  </si>
-  <si>
-    <t>21:58:15</t>
-  </si>
-  <si>
-    <t>23:34:41</t>
-  </si>
-  <si>
-    <t>01:12:04</t>
-  </si>
-  <si>
-    <t>02:49:49</t>
-  </si>
-  <si>
-    <t>22:55:10</t>
-  </si>
-  <si>
-    <t>01:55:44</t>
-  </si>
-  <si>
-    <t>03:32:57</t>
+    <t>23:55:59</t>
+  </si>
+  <si>
+    <t>01:32:57</t>
+  </si>
+  <si>
+    <t>03:10:31</t>
+  </si>
+  <si>
+    <t>04:48:32</t>
+  </si>
+  <si>
+    <t>23:16:47</t>
+  </si>
+  <si>
+    <t>00:53:36</t>
+  </si>
+  <si>
+    <t>02:31:07</t>
+  </si>
+  <si>
+    <t>04:09:01</t>
+  </si>
+  <si>
+    <t>22:37:33</t>
+  </si>
+  <si>
+    <t>00:14:12</t>
+  </si>
+  <si>
+    <t>01:51:39</t>
+  </si>
+  <si>
+    <t>03:29:28</t>
+  </si>
+  <si>
+    <t>21:58:19</t>
+  </si>
+  <si>
+    <t>23:34:45</t>
+  </si>
+  <si>
+    <t>01:12:08</t>
+  </si>
+  <si>
+    <t>02:49:53</t>
+  </si>
+  <si>
+    <t>22:55:15</t>
+  </si>
+  <si>
+    <t>00:32:33</t>
+  </si>
+  <si>
+    <t>02:10:14</t>
+  </si>
+  <si>
+    <t>22:15:42</t>
+  </si>
+  <si>
+    <t>23:52:54</t>
   </si>
   <si>
     <t>01:16:42</t>
@@ -334,349 +346,370 @@
     <t>03:52:15</t>
   </si>
   <si>
-    <t>23:58:33</t>
-  </si>
-  <si>
-    <t>01:35:13</t>
-  </si>
-  <si>
-    <t>03:12:51</t>
+    <t>23:58:34</t>
+  </si>
+  <si>
+    <t>01:35:14</t>
+  </si>
+  <si>
+    <t>03:12:52</t>
   </si>
   <si>
     <t>04:52:03</t>
   </si>
   <si>
-    <t>23:19:29</t>
-  </si>
-  <si>
-    <t>00:55:51</t>
-  </si>
-  <si>
-    <t>02:33:24</t>
-  </si>
-  <si>
-    <t>04:12:03</t>
-  </si>
-  <si>
-    <t>22:40:28</t>
-  </si>
-  <si>
-    <t>00:16:27</t>
-  </si>
-  <si>
-    <t>01:53:54</t>
-  </si>
-  <si>
-    <t>03:32:14</t>
-  </si>
-  <si>
-    <t>22:01:35</t>
-  </si>
-  <si>
-    <t>23:37:01</t>
-  </si>
-  <si>
-    <t>01:14:20</t>
-  </si>
-  <si>
-    <t>02:52:28</t>
-  </si>
-  <si>
-    <t>22:57:32</t>
-  </si>
-  <si>
-    <t>01:58:41</t>
-  </si>
-  <si>
-    <t>03:36:10</t>
-  </si>
-  <si>
-    <t>01:19:31</t>
-  </si>
-  <si>
-    <t>02:56:58</t>
+    <t>23:19:31</t>
+  </si>
+  <si>
+    <t>00:55:53</t>
+  </si>
+  <si>
+    <t>02:33:26</t>
+  </si>
+  <si>
+    <t>04:12:04</t>
+  </si>
+  <si>
+    <t>22:40:30</t>
+  </si>
+  <si>
+    <t>00:16:30</t>
+  </si>
+  <si>
+    <t>01:53:56</t>
+  </si>
+  <si>
+    <t>03:32:16</t>
+  </si>
+  <si>
+    <t>22:01:39</t>
+  </si>
+  <si>
+    <t>23:37:04</t>
+  </si>
+  <si>
+    <t>01:14:24</t>
+  </si>
+  <si>
+    <t>02:52:31</t>
+  </si>
+  <si>
+    <t>22:57:37</t>
+  </si>
+  <si>
+    <t>00:34:49</t>
+  </si>
+  <si>
+    <t>02:12:46</t>
+  </si>
+  <si>
+    <t>22:18:07</t>
+  </si>
+  <si>
+    <t>23:55:10</t>
+  </si>
+  <si>
+    <t>01:19:32</t>
+  </si>
+  <si>
+    <t>02:56:59</t>
   </si>
   <si>
     <t>04:34:25</t>
   </si>
   <si>
-    <t>00:40:18</t>
-  </si>
-  <si>
-    <t>02:17:43</t>
+    <t>00:40:19</t>
+  </si>
+  <si>
+    <t>02:17:44</t>
   </si>
   <si>
     <t>03:55:11</t>
   </si>
   <si>
-    <t>00:01:02</t>
-  </si>
-  <si>
-    <t>01:38:24</t>
-  </si>
-  <si>
-    <t>03:15:52</t>
-  </si>
-  <si>
-    <t>04:53:04</t>
-  </si>
-  <si>
-    <t>23:21:41</t>
-  </si>
-  <si>
-    <t>00:59:01</t>
-  </si>
-  <si>
-    <t>02:36:30</t>
+    <t>00:01:03</t>
+  </si>
+  <si>
+    <t>01:38:25</t>
+  </si>
+  <si>
+    <t>03:15:53</t>
+  </si>
+  <si>
+    <t>04:53:05</t>
+  </si>
+  <si>
+    <t>23:21:43</t>
+  </si>
+  <si>
+    <t>00:59:02</t>
+  </si>
+  <si>
+    <t>02:36:31</t>
+  </si>
+  <si>
+    <t>04:13:46</t>
+  </si>
+  <si>
+    <t>22:42:20</t>
+  </si>
+  <si>
+    <t>00:19:36</t>
+  </si>
+  <si>
+    <t>01:57:05</t>
+  </si>
+  <si>
+    <t>03:34:23</t>
+  </si>
+  <si>
+    <t>22:02:54</t>
+  </si>
+  <si>
+    <t>23:40:06</t>
+  </si>
+  <si>
+    <t>01:17:35</t>
+  </si>
+  <si>
+    <t>02:54:55</t>
+  </si>
+  <si>
+    <t>23:00:33</t>
+  </si>
+  <si>
+    <t>00:38:01</t>
+  </si>
+  <si>
+    <t>02:15:23</t>
+  </si>
+  <si>
+    <t>22:20:57</t>
+  </si>
+  <si>
+    <t>23:58:22</t>
+  </si>
+  <si>
+    <t>01:22:22</t>
+  </si>
+  <si>
+    <t>03:00:12</t>
+  </si>
+  <si>
+    <t>04:37:14</t>
+  </si>
+  <si>
+    <t>00:43:00</t>
+  </si>
+  <si>
+    <t>02:20:56</t>
+  </si>
+  <si>
+    <t>03:58:08</t>
+  </si>
+  <si>
+    <t>00:03:31</t>
+  </si>
+  <si>
+    <t>01:41:36</t>
+  </si>
+  <si>
+    <t>03:18:55</t>
+  </si>
+  <si>
+    <t>04:54:07</t>
+  </si>
+  <si>
+    <t>23:23:56</t>
+  </si>
+  <si>
+    <t>01:02:12</t>
+  </si>
+  <si>
+    <t>02:39:37</t>
+  </si>
+  <si>
+    <t>04:15:28</t>
+  </si>
+  <si>
+    <t>22:44:11</t>
+  </si>
+  <si>
+    <t>00:22:43</t>
+  </si>
+  <si>
+    <t>02:00:14</t>
+  </si>
+  <si>
+    <t>03:36:30</t>
+  </si>
+  <si>
+    <t>22:04:11</t>
+  </si>
+  <si>
+    <t>23:43:09</t>
+  </si>
+  <si>
+    <t>01:20:45</t>
+  </si>
+  <si>
+    <t>02:57:19</t>
+  </si>
+  <si>
+    <t>23:03:31</t>
+  </si>
+  <si>
+    <t>00:41:12</t>
+  </si>
+  <si>
+    <t>02:18:00</t>
+  </si>
+  <si>
+    <t>22:23:47</t>
+  </si>
+  <si>
+    <t>00:01:35</t>
+  </si>
+  <si>
+    <t>01:24:48</t>
+  </si>
+  <si>
+    <t>03:02:28</t>
+  </si>
+  <si>
+    <t>04:39:40</t>
+  </si>
+  <si>
+    <t>00:45:30</t>
+  </si>
+  <si>
+    <t>02:23:12</t>
+  </si>
+  <si>
+    <t>04:00:30</t>
+  </si>
+  <si>
+    <t>00:06:08</t>
+  </si>
+  <si>
+    <t>01:43:53</t>
+  </si>
+  <si>
+    <t>03:21:15</t>
+  </si>
+  <si>
+    <t>04:57:38</t>
+  </si>
+  <si>
+    <t>23:26:41</t>
+  </si>
+  <si>
+    <t>01:04:29</t>
+  </si>
+  <si>
+    <t>02:41:56</t>
+  </si>
+  <si>
+    <t>04:18:31</t>
+  </si>
+  <si>
+    <t>22:47:09</t>
+  </si>
+  <si>
+    <t>00:25:01</t>
+  </si>
+  <si>
+    <t>02:02:31</t>
+  </si>
+  <si>
+    <t>03:39:17</t>
+  </si>
+  <si>
+    <t>22:07:31</t>
+  </si>
+  <si>
+    <t>23:45:29</t>
+  </si>
+  <si>
+    <t>01:23:02</t>
+  </si>
+  <si>
+    <t>02:59:57</t>
+  </si>
+  <si>
+    <t>23:05:53</t>
+  </si>
+  <si>
+    <t>00:43:28</t>
+  </si>
+  <si>
+    <t>02:20:32</t>
+  </si>
+  <si>
+    <t>22:26:13</t>
+  </si>
+  <si>
+    <t>00:03:50</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>13°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>3°</t>
+  </si>
+  <si>
+    <t>02:59:13</t>
+  </si>
+  <si>
+    <t>04:32:43</t>
+  </si>
+  <si>
+    <t>02:21:43</t>
+  </si>
+  <si>
+    <t>03:55:13</t>
+  </si>
+  <si>
+    <t>03:17:43</t>
+  </si>
+  <si>
+    <t>04:51:13</t>
+  </si>
+  <si>
+    <t>02:40:15</t>
   </si>
   <si>
     <t>04:13:45</t>
   </si>
   <si>
-    <t>22:42:18</t>
-  </si>
-  <si>
-    <t>00:19:34</t>
-  </si>
-  <si>
-    <t>01:57:02</t>
-  </si>
-  <si>
-    <t>03:34:21</t>
-  </si>
-  <si>
-    <t>22:02:51</t>
-  </si>
-  <si>
-    <t>23:40:03</t>
-  </si>
-  <si>
-    <t>01:17:31</t>
-  </si>
-  <si>
-    <t>02:54:52</t>
-  </si>
-  <si>
-    <t>23:00:28</t>
-  </si>
-  <si>
-    <t>02:01:38</t>
-  </si>
-  <si>
-    <t>03:39:23</t>
-  </si>
-  <si>
-    <t>01:22:22</t>
-  </si>
-  <si>
-    <t>03:00:12</t>
-  </si>
-  <si>
-    <t>04:37:14</t>
-  </si>
-  <si>
-    <t>00:42:59</t>
-  </si>
-  <si>
-    <t>02:20:56</t>
-  </si>
-  <si>
-    <t>03:58:07</t>
-  </si>
-  <si>
-    <t>00:03:30</t>
-  </si>
-  <si>
-    <t>01:41:35</t>
-  </si>
-  <si>
-    <t>03:18:54</t>
-  </si>
-  <si>
-    <t>04:54:06</t>
-  </si>
-  <si>
-    <t>23:23:54</t>
-  </si>
-  <si>
-    <t>01:02:10</t>
-  </si>
-  <si>
-    <t>02:39:35</t>
-  </si>
-  <si>
-    <t>04:15:27</t>
-  </si>
-  <si>
-    <t>22:44:08</t>
-  </si>
-  <si>
-    <t>00:22:40</t>
-  </si>
-  <si>
-    <t>02:00:11</t>
-  </si>
-  <si>
-    <t>03:36:27</t>
-  </si>
-  <si>
-    <t>22:04:07</t>
-  </si>
-  <si>
-    <t>23:43:06</t>
-  </si>
-  <si>
-    <t>01:20:42</t>
-  </si>
-  <si>
-    <t>02:57:16</t>
-  </si>
-  <si>
-    <t>23:03:26</t>
-  </si>
-  <si>
-    <t>02:04:01</t>
-  </si>
-  <si>
-    <t>03:41:39</t>
-  </si>
-  <si>
-    <t>01:24:48</t>
-  </si>
-  <si>
-    <t>03:02:27</t>
-  </si>
-  <si>
-    <t>04:39:40</t>
-  </si>
-  <si>
-    <t>00:45:29</t>
-  </si>
-  <si>
-    <t>02:23:12</t>
-  </si>
-  <si>
-    <t>04:00:30</t>
-  </si>
-  <si>
-    <t>00:06:07</t>
-  </si>
-  <si>
-    <t>01:43:52</t>
-  </si>
-  <si>
-    <t>03:21:14</t>
-  </si>
-  <si>
-    <t>04:57:37</t>
-  </si>
-  <si>
-    <t>23:26:39</t>
-  </si>
-  <si>
-    <t>01:04:27</t>
-  </si>
-  <si>
-    <t>02:41:54</t>
-  </si>
-  <si>
-    <t>04:18:29</t>
-  </si>
-  <si>
-    <t>22:47:06</t>
-  </si>
-  <si>
-    <t>00:24:59</t>
-  </si>
-  <si>
-    <t>02:02:28</t>
-  </si>
-  <si>
-    <t>03:39:14</t>
-  </si>
-  <si>
-    <t>22:07:28</t>
-  </si>
-  <si>
-    <t>23:45:26</t>
-  </si>
-  <si>
-    <t>01:22:58</t>
-  </si>
-  <si>
-    <t>02:59:53</t>
-  </si>
-  <si>
-    <t>23:05:48</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>02:03:13</t>
-  </si>
-  <si>
-    <t>03:36:43</t>
-  </si>
-  <si>
-    <t>02:59:13</t>
-  </si>
-  <si>
-    <t>04:32:43</t>
-  </si>
-  <si>
-    <t>02:21:43</t>
-  </si>
-  <si>
-    <t>03:55:13</t>
-  </si>
-  <si>
-    <t>03:17:42</t>
-  </si>
-  <si>
-    <t>04:51:12</t>
-  </si>
-  <si>
-    <t>02:40:13</t>
-  </si>
-  <si>
-    <t>04:13:43</t>
-  </si>
-  <si>
-    <t>03:36:16</t>
-  </si>
-  <si>
-    <t>02:58:54</t>
+    <t>03:36:19</t>
+  </si>
+  <si>
+    <t>02:58:57</t>
   </si>
   <si>
     <t>B</t>
@@ -728,7 +761,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -755,6 +788,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -767,73 +848,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,7 +895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -931,12 +952,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1340,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1418,43 +1433,43 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="L2" s="4">
-        <v>-34.8</v>
+        <v>-39</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="O2" s="6">
         <v>59</v>
@@ -1463,10 +1478,10 @@
         <v>80</v>
       </c>
       <c r="Q2" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1474,55 +1489,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.1</v>
+        <v>-26.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="O3" s="6">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="P3" s="7">
         <v>80</v>
       </c>
-      <c r="Q3" s="10">
-        <v>3</v>
-      </c>
-      <c r="R3" s="11">
-        <v>24</v>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1530,55 +1545,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="L4" s="4">
-        <v>-39</v>
+        <v>-11.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O4" s="12">
-        <v>39</v>
-      </c>
-      <c r="P4" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>39</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
+        <v>236</v>
+      </c>
+      <c r="O4" s="6">
+        <v>84</v>
+      </c>
+      <c r="P4" s="7">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>13</v>
+      </c>
+      <c r="R4" s="12">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1586,54 +1601,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="L5" s="4">
-        <v>-26.5</v>
+        <v>-42.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" s="12">
-        <v>48</v>
-      </c>
-      <c r="P5" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>48</v>
-      </c>
-      <c r="R5" s="13">
+        <v>235</v>
+      </c>
+      <c r="O5" s="13">
+        <v>7</v>
+      </c>
+      <c r="P5" s="14">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1642,54 +1657,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="L6" s="4">
-        <v>-11.7</v>
+        <v>-31.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O6" s="12">
-        <v>38</v>
-      </c>
-      <c r="P6" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>38</v>
-      </c>
-      <c r="R6" s="13">
+        <v>235</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1698,54 +1713,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="L7" s="4">
-        <v>-42.1</v>
+        <v>-17.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O7" s="12">
-        <v>9</v>
-      </c>
-      <c r="P7" s="13">
+        <v>236</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
       <c r="Q7" s="8">
-        <v>9</v>
-      </c>
-      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1754,54 +1769,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="L8" s="4">
-        <v>-31.6</v>
+        <v>-44.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O8" s="16">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
+        <v>235</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1810,54 +1825,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="L9" s="4">
-        <v>-17.5</v>
+        <v>-36.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" s="16">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
+        <v>235</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1866,54 +1881,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="L10" s="4">
-        <v>-44.1</v>
+        <v>-23.1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O10" s="16">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
+        <v>236</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1922,54 +1937,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="L11" s="4">
-        <v>-36.2</v>
+        <v>-8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O11" s="16">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
+        <v>237</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1978,55 +1993,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>215</v>
+        <v>87</v>
       </c>
       <c r="L12" s="4">
-        <v>-23.1</v>
+        <v>-44.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="16">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
+        <v>235</v>
+      </c>
+      <c r="O12" s="13">
+        <v>3</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2034,55 +2049,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-39.8</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="O13" s="15">
+        <v>22</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
         <v>11</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-8</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O13" s="16">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2090,55 +2105,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="L14" s="4">
-        <v>-44.7</v>
+        <v>-28.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O14" s="12">
-        <v>23</v>
-      </c>
-      <c r="P14" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>23</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
+        <v>235</v>
+      </c>
+      <c r="O14" s="15">
+        <v>25</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2146,54 +2161,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="L15" s="4">
-        <v>-39.8</v>
+        <v>-13.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O15" s="12">
-        <v>38</v>
-      </c>
-      <c r="P15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>35</v>
-      </c>
-      <c r="R15" s="13">
+        <v>237</v>
+      </c>
+      <c r="O15" s="13">
+        <v>4</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2202,54 +2217,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>217</v>
+        <v>91</v>
       </c>
       <c r="L16" s="4">
-        <v>-28.3</v>
+        <v>-43.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O16" s="12">
-        <v>43</v>
-      </c>
-      <c r="P16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>43</v>
-      </c>
-      <c r="R16" s="13">
+        <v>237</v>
+      </c>
+      <c r="O16" s="15">
+        <v>39</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>5</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2258,54 +2273,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="L17" s="4">
-        <v>-13.9</v>
+        <v>-42.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O17" s="12">
-        <v>35</v>
-      </c>
-      <c r="P17" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>35</v>
-      </c>
-      <c r="R17" s="13">
+        <v>235</v>
+      </c>
+      <c r="O17" s="13">
+        <v>17</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>3</v>
+      </c>
+      <c r="R17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2314,55 +2329,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L18" s="4">
-        <v>-43.8</v>
+        <v>-33.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O18" s="6">
-        <v>80</v>
-      </c>
-      <c r="P18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="19">
-        <v>59</v>
+        <v>235</v>
+      </c>
+      <c r="O18" s="13">
+        <v>16</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>12</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2370,55 +2385,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
+        <v>15</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="O19" s="15">
         <v>29</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-42.4</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O19" s="6">
-        <v>72</v>
-      </c>
-      <c r="P19" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="20">
-        <v>66</v>
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>29</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2426,55 +2441,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L20" s="4">
-        <v>-33.2</v>
+        <v>-41.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="O20" s="6">
-        <v>69</v>
-      </c>
-      <c r="P20" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="15">
-        <v>51</v>
+        <v>75</v>
+      </c>
+      <c r="P20" s="17">
+        <v>55</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2482,55 +2497,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="L21" s="4">
-        <v>-19.6</v>
+        <v>-43.6</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="O21" s="6">
-        <v>50</v>
-      </c>
-      <c r="P21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="21">
-        <v>29</v>
+        <v>80</v>
+      </c>
+      <c r="P21" s="17">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2538,55 +2553,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L22" s="4">
-        <v>-41.5</v>
+        <v>-37.3</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O22" s="12">
-        <v>40</v>
-      </c>
-      <c r="P22" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="14">
-        <v>40</v>
-      </c>
-      <c r="R22" s="10">
-        <v>6</v>
+        <v>235</v>
+      </c>
+      <c r="O22" s="6">
+        <v>79</v>
+      </c>
+      <c r="P22" s="18">
+        <v>59</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2594,55 +2609,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="L23" s="4">
-        <v>-43.6</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O23" s="12">
-        <v>24</v>
-      </c>
-      <c r="P23" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="11">
-        <v>24</v>
-      </c>
-      <c r="R23" s="10">
-        <v>3</v>
+        <v>235</v>
+      </c>
+      <c r="O23" s="6">
+        <v>74</v>
+      </c>
+      <c r="P23" s="18">
+        <v>59</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2650,55 +2665,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L24" s="4">
-        <v>-37.3</v>
+        <v>-43.5</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O24" s="16">
-        <v>8</v>
-      </c>
-      <c r="P24" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>8</v>
-      </c>
-      <c r="R24" s="13">
-        <v>0</v>
+        <v>235</v>
+      </c>
+      <c r="O24" s="15">
+        <v>39</v>
+      </c>
+      <c r="P24" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>20</v>
+      </c>
+      <c r="R24" s="11">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2706,55 +2721,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="L25" s="4">
-        <v>-25</v>
+        <v>-40.4</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O25" s="16">
-        <v>4</v>
-      </c>
-      <c r="P25" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>4</v>
-      </c>
-      <c r="R25" s="13">
-        <v>0</v>
+        <v>235</v>
+      </c>
+      <c r="O25" s="15">
+        <v>34</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>11</v>
+      </c>
+      <c r="R25" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2762,114 +2777,226 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-30.2</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="O26" s="6">
+        <v>52</v>
+      </c>
+      <c r="P26" s="14">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>22</v>
+      </c>
+      <c r="R26" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-43.5</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O26" s="16">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0</v>
+      <c r="B27" s="2">
+        <v>23</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-41.8</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="O27" s="15">
+        <v>20</v>
+      </c>
+      <c r="P27" s="14">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>20</v>
+      </c>
+      <c r="R27" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="2">
+        <v>33</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="4">
+        <v>-42.3</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="O28" s="13">
+        <v>10</v>
+      </c>
+      <c r="P28" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>10</v>
+      </c>
+      <c r="R28" s="16">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A28">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B28">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C28">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D28">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E28">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F28">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G28">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H28">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I28">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K28">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L28">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2888,12 +3015,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M28">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N28">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2910,22 +3037,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O28">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P28">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q28">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R28">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260304--01</t>
-  </si>
-  <si>
-    <t>20260304--02</t>
-  </si>
-  <si>
-    <t>20260304--03</t>
-  </si>
-  <si>
     <t>20260305--01</t>
   </si>
   <si>
@@ -151,513 +142,510 @@
     <t>20260310--04</t>
   </si>
   <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:26</t>
-  </si>
-  <si>
-    <t>05:38</t>
-  </si>
-  <si>
-    <t>05:22</t>
+    <t>20260311--01</t>
+  </si>
+  <si>
+    <t>20260311--02</t>
+  </si>
+  <si>
+    <t>20260311--03</t>
+  </si>
+  <si>
+    <t>05:21</t>
   </si>
   <si>
     <t>06:25</t>
   </si>
   <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
     <t>05:53</t>
   </si>
   <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>02:04</t>
-  </si>
-  <si>
-    <t>04:25</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>02:32</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:23</t>
+    <t>06:24</t>
   </si>
   <si>
     <t>05:14</t>
   </si>
   <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:59</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>02:55</t>
-  </si>
-  <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>01:43</t>
-  </si>
-  <si>
-    <t>00:11</t>
-  </si>
-  <si>
-    <t>01:14:17</t>
-  </si>
-  <si>
-    <t>02:51:30</t>
-  </si>
-  <si>
-    <t>04:29:10</t>
-  </si>
-  <si>
-    <t>00:35:09</t>
-  </si>
-  <si>
-    <t>02:12:15</t>
-  </si>
-  <si>
-    <t>03:49:52</t>
-  </si>
-  <si>
-    <t>23:55:59</t>
-  </si>
-  <si>
-    <t>01:32:57</t>
-  </si>
-  <si>
-    <t>03:10:31</t>
-  </si>
-  <si>
-    <t>04:48:32</t>
-  </si>
-  <si>
-    <t>23:16:47</t>
-  </si>
-  <si>
-    <t>00:53:36</t>
-  </si>
-  <si>
-    <t>02:31:07</t>
-  </si>
-  <si>
-    <t>04:09:01</t>
-  </si>
-  <si>
-    <t>22:37:33</t>
-  </si>
-  <si>
-    <t>00:14:12</t>
-  </si>
-  <si>
-    <t>01:51:39</t>
-  </si>
-  <si>
-    <t>03:29:28</t>
-  </si>
-  <si>
-    <t>21:58:19</t>
-  </si>
-  <si>
-    <t>23:34:45</t>
-  </si>
-  <si>
-    <t>01:12:08</t>
-  </si>
-  <si>
-    <t>02:49:53</t>
-  </si>
-  <si>
-    <t>22:55:15</t>
-  </si>
-  <si>
-    <t>00:32:33</t>
-  </si>
-  <si>
-    <t>02:10:14</t>
-  </si>
-  <si>
-    <t>22:15:42</t>
-  </si>
-  <si>
-    <t>23:52:54</t>
-  </si>
-  <si>
-    <t>01:16:42</t>
-  </si>
-  <si>
-    <t>02:53:46</t>
-  </si>
-  <si>
-    <t>04:31:36</t>
-  </si>
-  <si>
-    <t>00:37:38</t>
-  </si>
-  <si>
-    <t>02:14:31</t>
-  </si>
-  <si>
-    <t>03:52:15</t>
-  </si>
-  <si>
-    <t>23:58:34</t>
-  </si>
-  <si>
-    <t>01:35:14</t>
-  </si>
-  <si>
-    <t>03:12:52</t>
-  </si>
-  <si>
-    <t>04:52:03</t>
-  </si>
-  <si>
-    <t>23:19:31</t>
-  </si>
-  <si>
-    <t>00:55:53</t>
-  </si>
-  <si>
-    <t>02:33:26</t>
-  </si>
-  <si>
-    <t>04:12:04</t>
-  </si>
-  <si>
-    <t>22:40:30</t>
-  </si>
-  <si>
-    <t>00:16:30</t>
-  </si>
-  <si>
-    <t>01:53:56</t>
-  </si>
-  <si>
-    <t>03:32:16</t>
-  </si>
-  <si>
-    <t>22:01:39</t>
-  </si>
-  <si>
-    <t>23:37:04</t>
-  </si>
-  <si>
-    <t>01:14:24</t>
-  </si>
-  <si>
-    <t>02:52:31</t>
-  </si>
-  <si>
-    <t>22:57:37</t>
-  </si>
-  <si>
-    <t>00:34:49</t>
-  </si>
-  <si>
-    <t>02:12:46</t>
-  </si>
-  <si>
-    <t>22:18:07</t>
-  </si>
-  <si>
-    <t>23:55:10</t>
-  </si>
-  <si>
-    <t>01:19:32</t>
-  </si>
-  <si>
-    <t>02:56:59</t>
-  </si>
-  <si>
-    <t>04:34:25</t>
-  </si>
-  <si>
-    <t>00:40:19</t>
-  </si>
-  <si>
-    <t>02:17:44</t>
-  </si>
-  <si>
-    <t>03:55:11</t>
-  </si>
-  <si>
-    <t>00:01:03</t>
-  </si>
-  <si>
-    <t>01:38:25</t>
-  </si>
-  <si>
-    <t>03:15:53</t>
-  </si>
-  <si>
-    <t>04:53:05</t>
-  </si>
-  <si>
-    <t>23:21:43</t>
-  </si>
-  <si>
-    <t>00:59:02</t>
-  </si>
-  <si>
-    <t>02:36:31</t>
-  </si>
-  <si>
-    <t>04:13:46</t>
-  </si>
-  <si>
-    <t>22:42:20</t>
-  </si>
-  <si>
-    <t>00:19:36</t>
-  </si>
-  <si>
-    <t>01:57:05</t>
-  </si>
-  <si>
-    <t>03:34:23</t>
-  </si>
-  <si>
-    <t>22:02:54</t>
-  </si>
-  <si>
-    <t>23:40:06</t>
-  </si>
-  <si>
-    <t>01:17:35</t>
-  </si>
-  <si>
-    <t>02:54:55</t>
-  </si>
-  <si>
-    <t>23:00:33</t>
-  </si>
-  <si>
-    <t>00:38:01</t>
-  </si>
-  <si>
-    <t>02:15:23</t>
-  </si>
-  <si>
-    <t>22:20:57</t>
-  </si>
-  <si>
-    <t>23:58:22</t>
-  </si>
-  <si>
-    <t>01:22:22</t>
-  </si>
-  <si>
-    <t>03:00:12</t>
-  </si>
-  <si>
-    <t>04:37:14</t>
-  </si>
-  <si>
-    <t>00:43:00</t>
-  </si>
-  <si>
-    <t>02:20:56</t>
-  </si>
-  <si>
-    <t>03:58:08</t>
-  </si>
-  <si>
-    <t>00:03:31</t>
-  </si>
-  <si>
-    <t>01:41:36</t>
-  </si>
-  <si>
-    <t>03:18:55</t>
-  </si>
-  <si>
-    <t>04:54:07</t>
-  </si>
-  <si>
-    <t>23:23:56</t>
-  </si>
-  <si>
-    <t>01:02:12</t>
-  </si>
-  <si>
-    <t>02:39:37</t>
-  </si>
-  <si>
-    <t>04:15:28</t>
-  </si>
-  <si>
-    <t>22:44:11</t>
-  </si>
-  <si>
-    <t>00:22:43</t>
-  </si>
-  <si>
-    <t>02:00:14</t>
-  </si>
-  <si>
-    <t>03:36:30</t>
-  </si>
-  <si>
-    <t>22:04:11</t>
-  </si>
-  <si>
-    <t>23:43:09</t>
-  </si>
-  <si>
-    <t>01:20:45</t>
-  </si>
-  <si>
-    <t>02:57:19</t>
-  </si>
-  <si>
-    <t>23:03:31</t>
-  </si>
-  <si>
-    <t>00:41:12</t>
-  </si>
-  <si>
-    <t>02:18:00</t>
-  </si>
-  <si>
-    <t>22:23:47</t>
-  </si>
-  <si>
-    <t>00:01:35</t>
-  </si>
-  <si>
-    <t>01:24:48</t>
-  </si>
-  <si>
-    <t>03:02:28</t>
-  </si>
-  <si>
-    <t>04:39:40</t>
-  </si>
-  <si>
-    <t>00:45:30</t>
-  </si>
-  <si>
-    <t>02:23:12</t>
-  </si>
-  <si>
-    <t>04:00:30</t>
-  </si>
-  <si>
-    <t>00:06:08</t>
-  </si>
-  <si>
-    <t>01:43:53</t>
-  </si>
-  <si>
-    <t>03:21:15</t>
-  </si>
-  <si>
-    <t>04:57:38</t>
-  </si>
-  <si>
-    <t>23:26:41</t>
-  </si>
-  <si>
-    <t>01:04:29</t>
-  </si>
-  <si>
-    <t>02:41:56</t>
-  </si>
-  <si>
-    <t>04:18:31</t>
-  </si>
-  <si>
-    <t>22:47:09</t>
-  </si>
-  <si>
-    <t>00:25:01</t>
-  </si>
-  <si>
-    <t>02:02:31</t>
-  </si>
-  <si>
-    <t>03:39:17</t>
-  </si>
-  <si>
-    <t>22:07:31</t>
-  </si>
-  <si>
-    <t>23:45:29</t>
-  </si>
-  <si>
-    <t>01:23:02</t>
-  </si>
-  <si>
-    <t>02:59:57</t>
-  </si>
-  <si>
-    <t>23:05:53</t>
-  </si>
-  <si>
-    <t>00:43:28</t>
-  </si>
-  <si>
-    <t>02:20:32</t>
-  </si>
-  <si>
-    <t>22:26:13</t>
-  </si>
-  <si>
-    <t>00:03:50</t>
+    <t>02:54</t>
+  </si>
+  <si>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>01:44</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>00:35:08</t>
+  </si>
+  <si>
+    <t>02:12:14</t>
+  </si>
+  <si>
+    <t>03:49:51</t>
+  </si>
+  <si>
+    <t>23:55:56</t>
+  </si>
+  <si>
+    <t>01:32:54</t>
+  </si>
+  <si>
+    <t>03:10:28</t>
+  </si>
+  <si>
+    <t>04:48:28</t>
+  </si>
+  <si>
+    <t>23:16:41</t>
+  </si>
+  <si>
+    <t>00:53:30</t>
+  </si>
+  <si>
+    <t>02:31:00</t>
+  </si>
+  <si>
+    <t>04:08:54</t>
+  </si>
+  <si>
+    <t>22:37:24</t>
+  </si>
+  <si>
+    <t>00:14:02</t>
+  </si>
+  <si>
+    <t>01:51:29</t>
+  </si>
+  <si>
+    <t>03:29:18</t>
+  </si>
+  <si>
+    <t>21:58:05</t>
+  </si>
+  <si>
+    <t>23:34:30</t>
+  </si>
+  <si>
+    <t>01:11:53</t>
+  </si>
+  <si>
+    <t>02:49:37</t>
+  </si>
+  <si>
+    <t>22:54:55</t>
+  </si>
+  <si>
+    <t>00:32:12</t>
+  </si>
+  <si>
+    <t>02:09:53</t>
+  </si>
+  <si>
+    <t>22:15:16</t>
+  </si>
+  <si>
+    <t>23:52:27</t>
+  </si>
+  <si>
+    <t>01:30:05</t>
+  </si>
+  <si>
+    <t>21:35:34</t>
+  </si>
+  <si>
+    <t>23:12:38</t>
+  </si>
+  <si>
+    <t>00:37:37</t>
+  </si>
+  <si>
+    <t>02:14:30</t>
+  </si>
+  <si>
+    <t>03:52:14</t>
+  </si>
+  <si>
+    <t>23:58:31</t>
+  </si>
+  <si>
+    <t>01:35:10</t>
+  </si>
+  <si>
+    <t>03:12:48</t>
+  </si>
+  <si>
+    <t>04:51:59</t>
+  </si>
+  <si>
+    <t>23:19:25</t>
+  </si>
+  <si>
+    <t>00:55:47</t>
+  </si>
+  <si>
+    <t>02:33:19</t>
+  </si>
+  <si>
+    <t>04:11:57</t>
+  </si>
+  <si>
+    <t>22:40:21</t>
+  </si>
+  <si>
+    <t>00:16:20</t>
+  </si>
+  <si>
+    <t>01:53:46</t>
+  </si>
+  <si>
+    <t>03:32:06</t>
+  </si>
+  <si>
+    <t>22:01:25</t>
+  </si>
+  <si>
+    <t>23:36:50</t>
+  </si>
+  <si>
+    <t>01:14:09</t>
+  </si>
+  <si>
+    <t>02:52:16</t>
+  </si>
+  <si>
+    <t>22:57:17</t>
+  </si>
+  <si>
+    <t>00:34:28</t>
+  </si>
+  <si>
+    <t>02:12:25</t>
+  </si>
+  <si>
+    <t>22:17:41</t>
+  </si>
+  <si>
+    <t>23:54:43</t>
+  </si>
+  <si>
+    <t>01:32:32</t>
+  </si>
+  <si>
+    <t>21:38:03</t>
+  </si>
+  <si>
+    <t>23:14:54</t>
+  </si>
+  <si>
+    <t>00:40:17</t>
+  </si>
+  <si>
+    <t>02:17:42</t>
+  </si>
+  <si>
+    <t>03:55:10</t>
+  </si>
+  <si>
+    <t>00:00:59</t>
+  </si>
+  <si>
+    <t>01:38:21</t>
+  </si>
+  <si>
+    <t>03:15:50</t>
+  </si>
+  <si>
+    <t>04:53:01</t>
+  </si>
+  <si>
+    <t>23:21:37</t>
+  </si>
+  <si>
+    <t>00:58:56</t>
+  </si>
+  <si>
+    <t>02:36:25</t>
+  </si>
+  <si>
+    <t>04:13:39</t>
+  </si>
+  <si>
+    <t>22:42:11</t>
+  </si>
+  <si>
+    <t>00:19:26</t>
+  </si>
+  <si>
+    <t>01:56:55</t>
+  </si>
+  <si>
+    <t>03:34:12</t>
+  </si>
+  <si>
+    <t>22:02:40</t>
+  </si>
+  <si>
+    <t>23:39:52</t>
+  </si>
+  <si>
+    <t>01:17:20</t>
+  </si>
+  <si>
+    <t>02:54:40</t>
+  </si>
+  <si>
+    <t>23:00:13</t>
+  </si>
+  <si>
+    <t>00:37:40</t>
+  </si>
+  <si>
+    <t>02:15:02</t>
+  </si>
+  <si>
+    <t>22:20:30</t>
+  </si>
+  <si>
+    <t>23:57:55</t>
+  </si>
+  <si>
+    <t>01:35:20</t>
+  </si>
+  <si>
+    <t>21:40:43</t>
+  </si>
+  <si>
+    <t>23:18:06</t>
+  </si>
+  <si>
+    <t>00:42:58</t>
+  </si>
+  <si>
+    <t>02:20:55</t>
+  </si>
+  <si>
+    <t>03:58:06</t>
+  </si>
+  <si>
+    <t>00:03:28</t>
+  </si>
+  <si>
+    <t>01:41:33</t>
+  </si>
+  <si>
+    <t>03:18:51</t>
+  </si>
+  <si>
+    <t>04:54:04</t>
+  </si>
+  <si>
+    <t>23:23:49</t>
+  </si>
+  <si>
+    <t>01:02:05</t>
+  </si>
+  <si>
+    <t>02:39:30</t>
+  </si>
+  <si>
+    <t>04:15:22</t>
+  </si>
+  <si>
+    <t>22:44:01</t>
+  </si>
+  <si>
+    <t>00:22:33</t>
+  </si>
+  <si>
+    <t>02:00:03</t>
+  </si>
+  <si>
+    <t>03:36:19</t>
+  </si>
+  <si>
+    <t>22:03:55</t>
+  </si>
+  <si>
+    <t>23:42:54</t>
+  </si>
+  <si>
+    <t>01:20:30</t>
+  </si>
+  <si>
+    <t>02:57:04</t>
+  </si>
+  <si>
+    <t>23:03:10</t>
+  </si>
+  <si>
+    <t>00:40:52</t>
+  </si>
+  <si>
+    <t>02:17:39</t>
+  </si>
+  <si>
+    <t>22:23:20</t>
+  </si>
+  <si>
+    <t>00:01:07</t>
+  </si>
+  <si>
+    <t>01:38:07</t>
+  </si>
+  <si>
+    <t>21:43:24</t>
+  </si>
+  <si>
+    <t>23:21:18</t>
+  </si>
+  <si>
+    <t>00:45:28</t>
+  </si>
+  <si>
+    <t>02:23:11</t>
+  </si>
+  <si>
+    <t>04:00:29</t>
+  </si>
+  <si>
+    <t>00:06:04</t>
+  </si>
+  <si>
+    <t>01:43:49</t>
+  </si>
+  <si>
+    <t>03:21:12</t>
+  </si>
+  <si>
+    <t>04:57:35</t>
+  </si>
+  <si>
+    <t>23:26:34</t>
+  </si>
+  <si>
+    <t>01:04:23</t>
+  </si>
+  <si>
+    <t>02:41:49</t>
+  </si>
+  <si>
+    <t>04:18:24</t>
+  </si>
+  <si>
+    <t>22:46:59</t>
+  </si>
+  <si>
+    <t>00:24:51</t>
+  </si>
+  <si>
+    <t>02:02:20</t>
+  </si>
+  <si>
+    <t>03:39:07</t>
+  </si>
+  <si>
+    <t>22:07:17</t>
+  </si>
+  <si>
+    <t>23:45:14</t>
+  </si>
+  <si>
+    <t>01:22:47</t>
+  </si>
+  <si>
+    <t>02:59:42</t>
+  </si>
+  <si>
+    <t>23:05:33</t>
+  </si>
+  <si>
+    <t>00:43:07</t>
+  </si>
+  <si>
+    <t>02:20:11</t>
+  </si>
+  <si>
+    <t>22:25:46</t>
+  </si>
+  <si>
+    <t>00:03:23</t>
+  </si>
+  <si>
+    <t>01:40:33</t>
+  </si>
+  <si>
+    <t>21:45:54</t>
+  </si>
+  <si>
+    <t>23:23:34</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>6°</t>
   </si>
   <si>
@@ -682,34 +670,28 @@
     <t>3°</t>
   </si>
   <si>
-    <t>02:59:13</t>
-  </si>
-  <si>
-    <t>04:32:43</t>
-  </si>
-  <si>
-    <t>02:21:43</t>
-  </si>
-  <si>
-    <t>03:55:13</t>
-  </si>
-  <si>
-    <t>03:17:43</t>
-  </si>
-  <si>
-    <t>04:51:13</t>
-  </si>
-  <si>
-    <t>02:40:15</t>
-  </si>
-  <si>
-    <t>04:13:45</t>
-  </si>
-  <si>
-    <t>03:36:19</t>
-  </si>
-  <si>
-    <t>02:58:57</t>
+    <t>02:21:42</t>
+  </si>
+  <si>
+    <t>03:55:12</t>
+  </si>
+  <si>
+    <t>03:17:40</t>
+  </si>
+  <si>
+    <t>04:51:09</t>
+  </si>
+  <si>
+    <t>02:40:08</t>
+  </si>
+  <si>
+    <t>04:13:38</t>
+  </si>
+  <si>
+    <t>03:36:09</t>
+  </si>
+  <si>
+    <t>02:58:42</t>
   </si>
   <si>
     <t>B</t>
@@ -761,7 +743,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -776,13 +758,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +782,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,13 +794,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -830,31 +866,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,6 +970,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1433,55 +1469,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L2" s="4">
-        <v>-39</v>
+        <v>-42.1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O2" s="6">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="P2" s="7">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>44</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1489,55 +1525,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="L3" s="4">
-        <v>-26.5</v>
+        <v>-31.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="O3" s="6">
-        <v>51</v>
-      </c>
-      <c r="P3" s="7">
-        <v>80</v>
+        <v>21</v>
+      </c>
+      <c r="P3" s="9">
+        <v>45</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>68</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1545,55 +1581,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L4" s="4">
-        <v>-11.7</v>
+        <v>-17.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="O4" s="6">
-        <v>84</v>
-      </c>
-      <c r="P4" s="7">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>13</v>
-      </c>
-      <c r="R4" s="12">
-        <v>30</v>
+        <v>230</v>
+      </c>
+      <c r="O4" s="10">
+        <v>2</v>
+      </c>
+      <c r="P4" s="9">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1601,49 +1637,49 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L5" s="4">
-        <v>-42.1</v>
+        <v>-44.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O5" s="13">
-        <v>7</v>
-      </c>
-      <c r="P5" s="14">
-        <v>7</v>
+        <v>229</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
@@ -1663,39 +1699,39 @@
         <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.6</v>
+        <v>-36.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O6" s="13">
+        <v>229</v>
+      </c>
+      <c r="O6" s="10">
         <v>0</v>
       </c>
       <c r="P6" s="8">
@@ -1713,45 +1749,45 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L7" s="4">
-        <v>-17.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="O7" s="13">
+        <v>230</v>
+      </c>
+      <c r="O7" s="10">
         <v>0</v>
       </c>
       <c r="P7" s="8">
@@ -1769,45 +1805,45 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="L8" s="4">
-        <v>-44.1</v>
+        <v>-8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O8" s="13">
+        <v>231</v>
+      </c>
+      <c r="O8" s="10">
         <v>0</v>
       </c>
       <c r="P8" s="8">
@@ -1825,46 +1861,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L9" s="4">
-        <v>-36.2</v>
+        <v>-44.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0</v>
+        <v>229</v>
+      </c>
+      <c r="O9" s="10">
+        <v>2</v>
       </c>
       <c r="P9" s="8">
         <v>0</v>
@@ -1873,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1881,46 +1917,46 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-39.8</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L10" s="4">
-        <v>-23.1</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
+        <v>229</v>
+      </c>
+      <c r="O10" s="10">
+        <v>2</v>
       </c>
       <c r="P10" s="8">
         <v>0</v>
@@ -1929,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1937,46 +1973,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L11" s="4">
-        <v>-8</v>
+        <v>-28.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
+        <v>229</v>
+      </c>
+      <c r="O11" s="10">
+        <v>2</v>
       </c>
       <c r="P11" s="8">
         <v>0</v>
@@ -1985,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1993,46 +2029,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="L12" s="4">
-        <v>-44.7</v>
+        <v>-13.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O12" s="13">
-        <v>3</v>
+        <v>231</v>
+      </c>
+      <c r="O12" s="10">
+        <v>16</v>
       </c>
       <c r="P12" s="8">
         <v>0</v>
@@ -2040,8 +2076,8 @@
       <c r="Q12" s="8">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
-        <v>2</v>
+      <c r="R12" s="11">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2049,55 +2085,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L13" s="4">
-        <v>-39.8</v>
+        <v>-43.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O13" s="15">
-        <v>22</v>
+        <v>231</v>
+      </c>
+      <c r="O13" s="12">
+        <v>75</v>
       </c>
       <c r="P13" s="8">
         <v>0</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="16">
-        <v>11</v>
+      <c r="Q13" s="13">
+        <v>40</v>
+      </c>
+      <c r="R13" s="14">
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2105,55 +2141,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="L14" s="4">
-        <v>-28.3</v>
+        <v>-42.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O14" s="15">
-        <v>25</v>
+        <v>229</v>
+      </c>
+      <c r="O14" s="12">
+        <v>95</v>
       </c>
       <c r="P14" s="8">
         <v>0</v>
       </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <v>3</v>
+      <c r="Q14" s="9">
+        <v>43</v>
+      </c>
+      <c r="R14" s="15">
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2161,55 +2197,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-33.2</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="L15" s="4">
-        <v>-13.9</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O15" s="13">
-        <v>4</v>
+      <c r="O15" s="12">
+        <v>100</v>
       </c>
       <c r="P15" s="8">
         <v>0</v>
       </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
-        <v>0</v>
+      <c r="Q15" s="16">
+        <v>86</v>
+      </c>
+      <c r="R15" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2217,55 +2253,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="L16" s="4">
-        <v>-43.8</v>
+        <v>-19.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O16" s="15">
-        <v>39</v>
+        <v>230</v>
+      </c>
+      <c r="O16" s="12">
+        <v>100</v>
       </c>
       <c r="P16" s="8">
         <v>0</v>
       </c>
-      <c r="Q16" s="14">
-        <v>5</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+      <c r="Q16" s="18">
+        <v>75</v>
+      </c>
+      <c r="R16" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2273,52 +2309,52 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L17" s="4">
-        <v>-42.4</v>
+        <v>-41.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O17" s="13">
-        <v>17</v>
+        <v>231</v>
+      </c>
+      <c r="O17" s="6">
+        <v>25</v>
       </c>
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="14">
-        <v>3</v>
+      <c r="Q17" s="19">
+        <v>25</v>
       </c>
       <c r="R17" s="8">
         <v>0</v>
@@ -2329,52 +2365,52 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L18" s="4">
-        <v>-33.2</v>
+        <v>-43.7</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O18" s="13">
-        <v>16</v>
+        <v>229</v>
+      </c>
+      <c r="O18" s="6">
+        <v>28</v>
       </c>
       <c r="P18" s="8">
         <v>0</v>
       </c>
-      <c r="Q18" s="16">
-        <v>12</v>
+      <c r="Q18" s="19">
+        <v>27</v>
       </c>
       <c r="R18" s="8">
         <v>0</v>
@@ -2385,52 +2421,52 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>230</v>
+        <v>91</v>
       </c>
       <c r="L19" s="4">
-        <v>-19.6</v>
+        <v>-37.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="O19" s="15">
-        <v>29</v>
+        <v>229</v>
+      </c>
+      <c r="O19" s="6">
+        <v>25</v>
       </c>
       <c r="P19" s="8">
         <v>0</v>
       </c>
-      <c r="Q19" s="12">
-        <v>29</v>
+      <c r="Q19" s="20">
+        <v>20</v>
       </c>
       <c r="R19" s="8">
         <v>0</v>
@@ -2441,52 +2477,52 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="L20" s="4">
-        <v>-41.5</v>
+        <v>-25.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="O20" s="6">
-        <v>75</v>
-      </c>
-      <c r="P20" s="17">
-        <v>55</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="21">
+        <v>10</v>
       </c>
       <c r="R20" s="8">
         <v>0</v>
@@ -2497,55 +2533,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-43.5</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="O21" s="12">
+        <v>90</v>
+      </c>
+      <c r="P21" s="14">
         <v>70</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-43.6</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O21" s="6">
-        <v>80</v>
-      </c>
-      <c r="P21" s="17">
-        <v>55</v>
-      </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2553,55 +2589,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L22" s="4">
-        <v>-37.3</v>
+        <v>-40.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O22" s="6">
+        <v>229</v>
+      </c>
+      <c r="O22" s="12">
+        <v>96</v>
+      </c>
+      <c r="P22" s="22">
         <v>79</v>
       </c>
-      <c r="P22" s="18">
-        <v>59</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>0</v>
+      <c r="Q22" s="23">
+        <v>3</v>
       </c>
       <c r="R22" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2609,55 +2645,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>231</v>
+        <v>95</v>
       </c>
       <c r="L23" s="4">
-        <v>-25</v>
+        <v>-30.2</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O23" s="6">
+        <v>229</v>
+      </c>
+      <c r="O23" s="12">
+        <v>82</v>
+      </c>
+      <c r="P23" s="18">
         <v>74</v>
       </c>
-      <c r="P23" s="18">
-        <v>59</v>
-      </c>
       <c r="Q23" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2665,55 +2701,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L24" s="4">
-        <v>-43.5</v>
+        <v>-41.8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O24" s="15">
-        <v>39</v>
-      </c>
-      <c r="P24" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="19">
-        <v>20</v>
-      </c>
-      <c r="R24" s="11">
-        <v>13</v>
+        <v>229</v>
+      </c>
+      <c r="O24" s="10">
+        <v>4</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2721,55 +2757,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L25" s="4">
-        <v>-40.4</v>
+        <v>-42.3</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O25" s="15">
-        <v>34</v>
+        <v>229</v>
+      </c>
+      <c r="O25" s="10">
+        <v>4</v>
       </c>
       <c r="P25" s="8">
         <v>0</v>
       </c>
-      <c r="Q25" s="16">
-        <v>11</v>
-      </c>
-      <c r="R25" s="19">
-        <v>21</v>
+      <c r="Q25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2777,55 +2813,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L26" s="4">
-        <v>-30.2</v>
+        <v>-34.6</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O26" s="6">
-        <v>52</v>
-      </c>
-      <c r="P26" s="14">
+        <v>229</v>
+      </c>
+      <c r="O26" s="10">
         <v>4</v>
       </c>
-      <c r="Q26" s="19">
-        <v>22</v>
-      </c>
-      <c r="R26" s="11">
-        <v>17</v>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2833,55 +2869,55 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L27" s="4">
-        <v>-41.8</v>
+        <v>-38.8</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O27" s="15">
-        <v>20</v>
-      </c>
-      <c r="P27" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="19">
-        <v>20</v>
-      </c>
-      <c r="R27" s="11">
-        <v>16</v>
+        <v>229</v>
+      </c>
+      <c r="O27" s="12">
+        <v>82</v>
+      </c>
+      <c r="P27" s="7">
+        <v>49</v>
+      </c>
+      <c r="Q27" s="24">
+        <v>65</v>
+      </c>
+      <c r="R27" s="22">
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2889,55 +2925,55 @@
         <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L28" s="4">
-        <v>-42.3</v>
+        <v>-42.8</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O28" s="13">
-        <v>10</v>
-      </c>
-      <c r="P28" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q28" s="16">
-        <v>10</v>
-      </c>
-      <c r="R28" s="16">
-        <v>10</v>
+        <v>229</v>
+      </c>
+      <c r="O28" s="12">
+        <v>91</v>
+      </c>
+      <c r="P28" s="25">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="24">
+        <v>65</v>
+      </c>
+      <c r="R28" s="18">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="220">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260305--01</t>
-  </si>
-  <si>
-    <t>20260305--02</t>
-  </si>
-  <si>
-    <t>20260305--03</t>
-  </si>
-  <si>
     <t>20260306--01</t>
   </si>
   <si>
@@ -91,9 +82,6 @@
     <t>20260306--04</t>
   </si>
   <si>
-    <t>20260306--05</t>
-  </si>
-  <si>
     <t>20260307--01</t>
   </si>
   <si>
@@ -151,85 +139,94 @@
     <t>20260311--03</t>
   </si>
   <si>
+    <t>20260312--01</t>
+  </si>
+  <si>
+    <t>20260312--02</t>
+  </si>
+  <si>
+    <t>20260312--03</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>02:04</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
     <t>05:21</t>
   </si>
   <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:25</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:35</t>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:56</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:54</t>
-  </si>
-  <si>
-    <t>01:11</t>
+    <t>01:12</t>
   </si>
   <si>
     <t>01:44</t>
@@ -238,343 +235,316 @@
     <t>00:10</t>
   </si>
   <si>
-    <t>00:35:08</t>
-  </si>
-  <si>
-    <t>02:12:14</t>
-  </si>
-  <si>
-    <t>03:49:51</t>
-  </si>
-  <si>
-    <t>23:55:56</t>
-  </si>
-  <si>
-    <t>01:32:54</t>
+    <t>01:32:55</t>
   </si>
   <si>
     <t>03:10:28</t>
   </si>
   <si>
-    <t>04:48:28</t>
-  </si>
-  <si>
-    <t>23:16:41</t>
-  </si>
-  <si>
-    <t>00:53:30</t>
-  </si>
-  <si>
-    <t>02:31:00</t>
-  </si>
-  <si>
-    <t>04:08:54</t>
-  </si>
-  <si>
-    <t>22:37:24</t>
-  </si>
-  <si>
-    <t>00:14:02</t>
-  </si>
-  <si>
-    <t>01:51:29</t>
-  </si>
-  <si>
-    <t>03:29:18</t>
-  </si>
-  <si>
-    <t>21:58:05</t>
-  </si>
-  <si>
-    <t>23:34:30</t>
-  </si>
-  <si>
-    <t>01:11:53</t>
-  </si>
-  <si>
-    <t>02:49:37</t>
-  </si>
-  <si>
-    <t>22:54:55</t>
-  </si>
-  <si>
-    <t>00:32:12</t>
-  </si>
-  <si>
-    <t>02:09:53</t>
-  </si>
-  <si>
-    <t>22:15:16</t>
-  </si>
-  <si>
-    <t>23:52:27</t>
-  </si>
-  <si>
-    <t>01:30:05</t>
-  </si>
-  <si>
-    <t>21:35:34</t>
-  </si>
-  <si>
-    <t>23:12:38</t>
-  </si>
-  <si>
-    <t>00:37:37</t>
-  </si>
-  <si>
-    <t>02:14:30</t>
-  </si>
-  <si>
-    <t>03:52:14</t>
-  </si>
-  <si>
-    <t>23:58:31</t>
-  </si>
-  <si>
-    <t>01:35:10</t>
-  </si>
-  <si>
-    <t>03:12:48</t>
-  </si>
-  <si>
-    <t>04:51:59</t>
-  </si>
-  <si>
-    <t>23:19:25</t>
-  </si>
-  <si>
-    <t>00:55:47</t>
-  </si>
-  <si>
-    <t>02:33:19</t>
-  </si>
-  <si>
-    <t>04:11:57</t>
-  </si>
-  <si>
-    <t>22:40:21</t>
-  </si>
-  <si>
-    <t>00:16:20</t>
-  </si>
-  <si>
-    <t>01:53:46</t>
-  </si>
-  <si>
-    <t>03:32:06</t>
-  </si>
-  <si>
-    <t>22:01:25</t>
-  </si>
-  <si>
-    <t>23:36:50</t>
-  </si>
-  <si>
-    <t>01:14:09</t>
-  </si>
-  <si>
-    <t>02:52:16</t>
-  </si>
-  <si>
-    <t>22:57:17</t>
-  </si>
-  <si>
-    <t>00:34:28</t>
-  </si>
-  <si>
-    <t>02:12:25</t>
-  </si>
-  <si>
-    <t>22:17:41</t>
-  </si>
-  <si>
-    <t>23:54:43</t>
-  </si>
-  <si>
-    <t>01:32:32</t>
-  </si>
-  <si>
-    <t>21:38:03</t>
-  </si>
-  <si>
-    <t>23:14:54</t>
-  </si>
-  <si>
-    <t>00:40:17</t>
-  </si>
-  <si>
-    <t>02:17:42</t>
-  </si>
-  <si>
-    <t>03:55:10</t>
-  </si>
-  <si>
-    <t>00:00:59</t>
-  </si>
-  <si>
-    <t>01:38:21</t>
+    <t>04:48:29</t>
+  </si>
+  <si>
+    <t>23:16:43</t>
+  </si>
+  <si>
+    <t>00:53:32</t>
+  </si>
+  <si>
+    <t>02:31:03</t>
+  </si>
+  <si>
+    <t>04:08:57</t>
+  </si>
+  <si>
+    <t>22:37:28</t>
+  </si>
+  <si>
+    <t>00:14:06</t>
+  </si>
+  <si>
+    <t>01:51:33</t>
+  </si>
+  <si>
+    <t>03:29:22</t>
+  </si>
+  <si>
+    <t>21:58:11</t>
+  </si>
+  <si>
+    <t>23:34:37</t>
+  </si>
+  <si>
+    <t>01:12:00</t>
+  </si>
+  <si>
+    <t>02:49:45</t>
+  </si>
+  <si>
+    <t>22:55:05</t>
+  </si>
+  <si>
+    <t>00:32:23</t>
+  </si>
+  <si>
+    <t>02:10:04</t>
+  </si>
+  <si>
+    <t>22:15:31</t>
+  </si>
+  <si>
+    <t>23:52:43</t>
+  </si>
+  <si>
+    <t>01:30:21</t>
+  </si>
+  <si>
+    <t>21:35:54</t>
+  </si>
+  <si>
+    <t>23:12:59</t>
+  </si>
+  <si>
+    <t>00:50:34</t>
+  </si>
+  <si>
+    <t>20:56:14</t>
+  </si>
+  <si>
+    <t>22:33:11</t>
+  </si>
+  <si>
+    <t>01:35:11</t>
+  </si>
+  <si>
+    <t>03:12:49</t>
+  </si>
+  <si>
+    <t>04:52:00</t>
+  </si>
+  <si>
+    <t>23:19:27</t>
+  </si>
+  <si>
+    <t>00:55:49</t>
+  </si>
+  <si>
+    <t>02:33:21</t>
+  </si>
+  <si>
+    <t>04:12:00</t>
+  </si>
+  <si>
+    <t>22:40:25</t>
+  </si>
+  <si>
+    <t>00:16:24</t>
+  </si>
+  <si>
+    <t>01:53:50</t>
+  </si>
+  <si>
+    <t>03:32:10</t>
+  </si>
+  <si>
+    <t>22:01:32</t>
+  </si>
+  <si>
+    <t>23:36:57</t>
+  </si>
+  <si>
+    <t>01:14:16</t>
+  </si>
+  <si>
+    <t>02:52:23</t>
+  </si>
+  <si>
+    <t>22:57:27</t>
+  </si>
+  <si>
+    <t>00:34:39</t>
+  </si>
+  <si>
+    <t>02:12:36</t>
+  </si>
+  <si>
+    <t>22:17:56</t>
+  </si>
+  <si>
+    <t>23:54:58</t>
+  </si>
+  <si>
+    <t>01:32:48</t>
+  </si>
+  <si>
+    <t>21:38:23</t>
+  </si>
+  <si>
+    <t>23:15:14</t>
+  </si>
+  <si>
+    <t>00:52:57</t>
+  </si>
+  <si>
+    <t>20:58:50</t>
+  </si>
+  <si>
+    <t>22:35:27</t>
+  </si>
+  <si>
+    <t>01:38:22</t>
   </si>
   <si>
     <t>03:15:50</t>
   </si>
   <si>
-    <t>04:53:01</t>
-  </si>
-  <si>
-    <t>23:21:37</t>
-  </si>
-  <si>
-    <t>00:58:56</t>
-  </si>
-  <si>
-    <t>02:36:25</t>
-  </si>
-  <si>
-    <t>04:13:39</t>
-  </si>
-  <si>
-    <t>22:42:11</t>
-  </si>
-  <si>
-    <t>00:19:26</t>
-  </si>
-  <si>
-    <t>01:56:55</t>
-  </si>
-  <si>
-    <t>03:34:12</t>
-  </si>
-  <si>
-    <t>22:02:40</t>
-  </si>
-  <si>
-    <t>23:39:52</t>
-  </si>
-  <si>
-    <t>01:17:20</t>
-  </si>
-  <si>
-    <t>02:54:40</t>
-  </si>
-  <si>
-    <t>23:00:13</t>
-  </si>
-  <si>
-    <t>00:37:40</t>
-  </si>
-  <si>
-    <t>02:15:02</t>
-  </si>
-  <si>
-    <t>22:20:30</t>
-  </si>
-  <si>
-    <t>23:57:55</t>
-  </si>
-  <si>
-    <t>01:35:20</t>
-  </si>
-  <si>
-    <t>21:40:43</t>
-  </si>
-  <si>
-    <t>23:18:06</t>
-  </si>
-  <si>
-    <t>00:42:58</t>
-  </si>
-  <si>
-    <t>02:20:55</t>
-  </si>
-  <si>
-    <t>03:58:06</t>
-  </si>
-  <si>
-    <t>00:03:28</t>
+    <t>04:53:02</t>
+  </si>
+  <si>
+    <t>23:21:39</t>
+  </si>
+  <si>
+    <t>00:58:58</t>
+  </si>
+  <si>
+    <t>02:36:27</t>
+  </si>
+  <si>
+    <t>04:13:42</t>
+  </si>
+  <si>
+    <t>22:42:14</t>
+  </si>
+  <si>
+    <t>00:19:30</t>
+  </si>
+  <si>
+    <t>01:56:59</t>
+  </si>
+  <si>
+    <t>03:34:17</t>
+  </si>
+  <si>
+    <t>22:02:47</t>
+  </si>
+  <si>
+    <t>23:39:59</t>
+  </si>
+  <si>
+    <t>01:17:27</t>
+  </si>
+  <si>
+    <t>02:54:47</t>
+  </si>
+  <si>
+    <t>23:00:24</t>
+  </si>
+  <si>
+    <t>00:37:50</t>
+  </si>
+  <si>
+    <t>02:15:13</t>
+  </si>
+  <si>
+    <t>22:20:45</t>
+  </si>
+  <si>
+    <t>23:58:10</t>
+  </si>
+  <si>
+    <t>01:35:35</t>
+  </si>
+  <si>
+    <t>21:41:03</t>
+  </si>
+  <si>
+    <t>23:18:26</t>
+  </si>
+  <si>
+    <t>00:55:52</t>
+  </si>
+  <si>
+    <t>21:01:18</t>
+  </si>
+  <si>
+    <t>22:38:38</t>
   </si>
   <si>
     <t>01:41:33</t>
   </si>
   <si>
-    <t>03:18:51</t>
+    <t>03:18:52</t>
   </si>
   <si>
     <t>04:54:04</t>
   </si>
   <si>
-    <t>23:23:49</t>
-  </si>
-  <si>
-    <t>01:02:05</t>
-  </si>
-  <si>
-    <t>02:39:30</t>
-  </si>
-  <si>
-    <t>04:15:22</t>
-  </si>
-  <si>
-    <t>22:44:01</t>
-  </si>
-  <si>
-    <t>00:22:33</t>
-  </si>
-  <si>
-    <t>02:00:03</t>
-  </si>
-  <si>
-    <t>03:36:19</t>
-  </si>
-  <si>
-    <t>22:03:55</t>
-  </si>
-  <si>
-    <t>23:42:54</t>
-  </si>
-  <si>
-    <t>01:20:30</t>
-  </si>
-  <si>
-    <t>02:57:04</t>
-  </si>
-  <si>
-    <t>23:03:10</t>
-  </si>
-  <si>
-    <t>00:40:52</t>
-  </si>
-  <si>
-    <t>02:17:39</t>
-  </si>
-  <si>
-    <t>22:23:20</t>
-  </si>
-  <si>
-    <t>00:01:07</t>
-  </si>
-  <si>
-    <t>01:38:07</t>
-  </si>
-  <si>
-    <t>21:43:24</t>
-  </si>
-  <si>
-    <t>23:21:18</t>
-  </si>
-  <si>
-    <t>00:45:28</t>
-  </si>
-  <si>
-    <t>02:23:11</t>
-  </si>
-  <si>
-    <t>04:00:29</t>
-  </si>
-  <si>
-    <t>00:06:04</t>
-  </si>
-  <si>
-    <t>01:43:49</t>
+    <t>23:23:51</t>
+  </si>
+  <si>
+    <t>01:02:07</t>
+  </si>
+  <si>
+    <t>02:39:32</t>
+  </si>
+  <si>
+    <t>04:15:24</t>
+  </si>
+  <si>
+    <t>22:44:05</t>
+  </si>
+  <si>
+    <t>00:22:37</t>
+  </si>
+  <si>
+    <t>02:00:07</t>
+  </si>
+  <si>
+    <t>03:36:23</t>
+  </si>
+  <si>
+    <t>22:04:02</t>
+  </si>
+  <si>
+    <t>23:43:01</t>
+  </si>
+  <si>
+    <t>01:20:37</t>
+  </si>
+  <si>
+    <t>02:57:11</t>
+  </si>
+  <si>
+    <t>23:03:21</t>
+  </si>
+  <si>
+    <t>00:41:02</t>
+  </si>
+  <si>
+    <t>02:17:50</t>
+  </si>
+  <si>
+    <t>22:23:35</t>
+  </si>
+  <si>
+    <t>00:01:23</t>
+  </si>
+  <si>
+    <t>21:43:44</t>
+  </si>
+  <si>
+    <t>23:21:38</t>
+  </si>
+  <si>
+    <t>00:58:47</t>
+  </si>
+  <si>
+    <t>21:03:46</t>
+  </si>
+  <si>
+    <t>22:41:49</t>
+  </si>
+  <si>
+    <t>01:43:50</t>
   </si>
   <si>
     <t>03:21:12</t>
@@ -583,75 +553,75 @@
     <t>04:57:35</t>
   </si>
   <si>
-    <t>23:26:34</t>
-  </si>
-  <si>
-    <t>01:04:23</t>
-  </si>
-  <si>
-    <t>02:41:49</t>
-  </si>
-  <si>
-    <t>04:18:24</t>
-  </si>
-  <si>
-    <t>22:46:59</t>
-  </si>
-  <si>
-    <t>00:24:51</t>
-  </si>
-  <si>
-    <t>02:02:20</t>
-  </si>
-  <si>
-    <t>03:39:07</t>
-  </si>
-  <si>
-    <t>22:07:17</t>
-  </si>
-  <si>
-    <t>23:45:14</t>
-  </si>
-  <si>
-    <t>01:22:47</t>
-  </si>
-  <si>
-    <t>02:59:42</t>
-  </si>
-  <si>
-    <t>23:05:33</t>
-  </si>
-  <si>
-    <t>00:43:07</t>
-  </si>
-  <si>
-    <t>02:20:11</t>
-  </si>
-  <si>
-    <t>22:25:46</t>
-  </si>
-  <si>
-    <t>00:03:23</t>
-  </si>
-  <si>
-    <t>01:40:33</t>
-  </si>
-  <si>
-    <t>21:45:54</t>
-  </si>
-  <si>
-    <t>23:23:34</t>
+    <t>23:26:36</t>
+  </si>
+  <si>
+    <t>01:04:25</t>
+  </si>
+  <si>
+    <t>02:41:51</t>
+  </si>
+  <si>
+    <t>04:18:26</t>
+  </si>
+  <si>
+    <t>22:47:03</t>
+  </si>
+  <si>
+    <t>00:24:55</t>
+  </si>
+  <si>
+    <t>02:02:25</t>
+  </si>
+  <si>
+    <t>03:39:11</t>
+  </si>
+  <si>
+    <t>22:07:24</t>
+  </si>
+  <si>
+    <t>23:45:21</t>
+  </si>
+  <si>
+    <t>01:22:54</t>
+  </si>
+  <si>
+    <t>02:59:49</t>
+  </si>
+  <si>
+    <t>23:05:43</t>
+  </si>
+  <si>
+    <t>00:43:18</t>
+  </si>
+  <si>
+    <t>02:20:22</t>
+  </si>
+  <si>
+    <t>22:26:01</t>
+  </si>
+  <si>
+    <t>00:03:38</t>
+  </si>
+  <si>
+    <t>01:40:48</t>
+  </si>
+  <si>
+    <t>21:46:14</t>
+  </si>
+  <si>
+    <t>23:23:54</t>
+  </si>
+  <si>
+    <t>01:01:09</t>
+  </si>
+  <si>
+    <t>21:06:22</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
     <t>17°</t>
   </si>
   <si>
@@ -670,28 +640,22 @@
     <t>3°</t>
   </si>
   <si>
-    <t>02:21:42</t>
-  </si>
-  <si>
-    <t>03:55:12</t>
-  </si>
-  <si>
     <t>03:17:40</t>
   </si>
   <si>
-    <t>04:51:09</t>
-  </si>
-  <si>
-    <t>02:40:08</t>
-  </si>
-  <si>
-    <t>04:13:38</t>
-  </si>
-  <si>
-    <t>03:36:09</t>
-  </si>
-  <si>
-    <t>02:58:42</t>
+    <t>04:51:10</t>
+  </si>
+  <si>
+    <t>02:40:10</t>
+  </si>
+  <si>
+    <t>04:13:40</t>
+  </si>
+  <si>
+    <t>03:36:13</t>
+  </si>
+  <si>
+    <t>02:58:49</t>
   </si>
   <si>
     <t>B</t>
@@ -743,7 +707,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -758,13 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,13 +734,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,37 +770,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -842,37 +806,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -913,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -976,18 +916,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1391,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1469,54 +1397,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L2" s="4">
-        <v>-42.1</v>
+        <v>-36.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>52</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1525,54 +1453,54 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L3" s="4">
-        <v>-31.6</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="O3" s="6">
-        <v>21</v>
-      </c>
-      <c r="P3" s="9">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1581,55 +1509,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-8</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="L4" s="4">
-        <v>-17.5</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O4" s="10">
-        <v>2</v>
-      </c>
-      <c r="P4" s="9">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>1</v>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1637,55 +1565,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" s="4">
-        <v>-44.1</v>
+        <v>-44.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O5" s="6">
+        <v>2</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1693,55 +1621,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L6" s="4">
-        <v>-36.2</v>
+        <v>-39.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
+        <v>217</v>
+      </c>
+      <c r="O6" s="6">
+        <v>3</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
       <c r="R6" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1749,55 +1677,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.1</v>
+        <v>-28.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
+        <v>217</v>
+      </c>
+      <c r="O7" s="6">
+        <v>5</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1805,55 +1733,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="L8" s="4">
-        <v>-8</v>
+        <v>-13.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="O8" s="9">
+        <v>33</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1861,55 +1789,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L9" s="4">
-        <v>-44.7</v>
+        <v>-43.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O9" s="10">
+        <v>219</v>
+      </c>
+      <c r="O9" s="6">
+        <v>11</v>
+      </c>
+      <c r="P9" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="7">
         <v>2</v>
       </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
       <c r="R9" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1917,55 +1845,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L10" s="4">
-        <v>-39.8</v>
+        <v>-42.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O10" s="10">
-        <v>2</v>
+        <v>217</v>
+      </c>
+      <c r="O10" s="9">
+        <v>19</v>
       </c>
       <c r="P10" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="11">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1973,55 +1901,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-33.2</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-28.3</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O11" s="10">
-        <v>2</v>
+        <v>217</v>
+      </c>
+      <c r="O11" s="9">
+        <v>35</v>
       </c>
       <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0</v>
-      </c>
-      <c r="R11" s="8">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>14</v>
+      </c>
+      <c r="R11" s="10">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2029,55 +1957,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-13.9</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="N12" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O12" s="10">
-        <v>16</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>16</v>
+        <v>218</v>
+      </c>
+      <c r="O12" s="13">
+        <v>75</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>1</v>
+      </c>
+      <c r="R12" s="14">
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2085,55 +2013,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L13" s="4">
-        <v>-43.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O13" s="12">
-        <v>75</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>40</v>
-      </c>
-      <c r="R13" s="14">
-        <v>72</v>
+        <v>219</v>
+      </c>
+      <c r="O13" s="13">
+        <v>63</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>3</v>
+      </c>
+      <c r="R13" s="15">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2141,55 +2069,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-42.4</v>
+        <v>-43.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O14" s="12">
-        <v>95</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>43</v>
-      </c>
-      <c r="R14" s="15">
-        <v>95</v>
+        <v>217</v>
+      </c>
+      <c r="O14" s="13">
+        <v>57</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>3</v>
+      </c>
+      <c r="R14" s="16">
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2197,55 +2125,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4">
-        <v>-33.2</v>
+        <v>-37.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O15" s="12">
-        <v>100</v>
-      </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>86</v>
-      </c>
-      <c r="R15" s="17">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O15" s="13">
+        <v>56</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>39</v>
+      </c>
+      <c r="R15" s="18">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2253,55 +2181,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="L16" s="4">
-        <v>-19.6</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O16" s="12">
-        <v>100</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>75</v>
-      </c>
-      <c r="R16" s="17">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O16" s="9">
+        <v>45</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="19">
+        <v>26</v>
+      </c>
+      <c r="R16" s="18">
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2309,54 +2237,54 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L17" s="4">
-        <v>-41.5</v>
+        <v>-43.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="O17" s="6">
-        <v>25</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="19">
-        <v>25</v>
-      </c>
-      <c r="R17" s="8">
+        <v>8</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>8</v>
+      </c>
+      <c r="R17" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2365,54 +2293,54 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L18" s="4">
-        <v>-43.7</v>
+        <v>-40.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="O18" s="6">
-        <v>28</v>
-      </c>
-      <c r="P18" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>27</v>
-      </c>
-      <c r="R18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2421,54 +2349,54 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-37.3</v>
+        <v>-30.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="O19" s="6">
-        <v>25</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>20</v>
-      </c>
-      <c r="R19" s="8">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2477,55 +2405,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-41.8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-25.1</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O20" s="6">
-        <v>17</v>
-      </c>
-      <c r="P20" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="21">
-        <v>10</v>
+      <c r="O20" s="9">
+        <v>19</v>
+      </c>
+      <c r="P20" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
       </c>
       <c r="R20" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2533,55 +2461,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L21" s="4">
-        <v>-43.5</v>
+        <v>-42.3</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O21" s="12">
-        <v>90</v>
-      </c>
-      <c r="P21" s="14">
-        <v>70</v>
-      </c>
-      <c r="Q21" s="8">
+        <v>217</v>
+      </c>
+      <c r="O21" s="6">
+        <v>18</v>
+      </c>
+      <c r="P21" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="7">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2589,55 +2517,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4">
-        <v>-40.4</v>
+        <v>-34.6</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O22" s="12">
-        <v>96</v>
-      </c>
-      <c r="P22" s="22">
-        <v>79</v>
-      </c>
-      <c r="Q22" s="23">
-        <v>3</v>
-      </c>
-      <c r="R22" s="8">
+        <v>217</v>
+      </c>
+      <c r="O22" s="9">
+        <v>21</v>
+      </c>
+      <c r="P22" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="7">
         <v>2</v>
+      </c>
+      <c r="R22" s="11">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2648,52 +2576,52 @@
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23" s="4">
-        <v>-30.2</v>
+        <v>-38.9</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O23" s="12">
-        <v>82</v>
-      </c>
-      <c r="P23" s="18">
-        <v>74</v>
+        <v>217</v>
+      </c>
+      <c r="O23" s="9">
+        <v>27</v>
+      </c>
+      <c r="P23" s="12">
+        <v>15</v>
       </c>
       <c r="Q23" s="8">
-        <v>2</v>
-      </c>
-      <c r="R23" s="8">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R23" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2701,54 +2629,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L24" s="4">
-        <v>-41.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O24" s="10">
-        <v>4</v>
-      </c>
-      <c r="P24" s="8">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O24" s="9">
+        <v>28</v>
+      </c>
+      <c r="P24" s="19">
+        <v>23</v>
       </c>
       <c r="Q24" s="8">
-        <v>0</v>
-      </c>
-      <c r="R24" s="8">
+        <v>3</v>
+      </c>
+      <c r="R24" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2757,55 +2685,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L25" s="4">
-        <v>-42.3</v>
+        <v>-38.2</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O25" s="10">
-        <v>4</v>
-      </c>
-      <c r="P25" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>0</v>
-      </c>
-      <c r="R25" s="8">
+        <v>217</v>
+      </c>
+      <c r="O25" s="9">
+        <v>27</v>
+      </c>
+      <c r="P25" s="19">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="7">
         <v>1</v>
+      </c>
+      <c r="R25" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2813,7 +2741,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>68</v>
@@ -2822,46 +2750,46 @@
         <v>69</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L26" s="4">
-        <v>-34.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O26" s="10">
-        <v>4</v>
-      </c>
-      <c r="P26" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="8">
-        <v>0</v>
-      </c>
-      <c r="R26" s="8">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="O26" s="13">
+        <v>56</v>
+      </c>
+      <c r="P26" s="19">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>35</v>
+      </c>
+      <c r="R26" s="20">
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2869,170 +2797,114 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L27" s="4">
-        <v>-38.8</v>
+        <v>-41.8</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O27" s="12">
-        <v>82</v>
-      </c>
-      <c r="P27" s="7">
+        <v>217</v>
+      </c>
+      <c r="O27" s="13">
+        <v>68</v>
+      </c>
+      <c r="P27" s="10">
+        <v>35</v>
+      </c>
+      <c r="Q27" s="20">
+        <v>32</v>
+      </c>
+      <c r="R27" s="21">
         <v>49</v>
-      </c>
-      <c r="Q27" s="24">
-        <v>65</v>
-      </c>
-      <c r="R27" s="22">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="2">
-        <v>32</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L28" s="4">
-        <v>-42.8</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O28" s="12">
-        <v>91</v>
-      </c>
-      <c r="P28" s="25">
-        <v>56</v>
-      </c>
-      <c r="Q28" s="24">
-        <v>65</v>
-      </c>
-      <c r="R28" s="18">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A28">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B28">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C28">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D28">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E28">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F28">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G28">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H28">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I28">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J28">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K28">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L28">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -3051,12 +2923,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M28">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N28">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3073,22 +2945,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O28">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P28">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q28">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R28">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="223">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260306--01</t>
-  </si>
-  <si>
-    <t>20260306--02</t>
-  </si>
-  <si>
-    <t>20260306--03</t>
-  </si>
-  <si>
-    <t>20260306--04</t>
-  </si>
-  <si>
     <t>20260307--01</t>
   </si>
   <si>
@@ -148,13 +136,88 @@
     <t>20260312--03</t>
   </si>
   <si>
+    <t>20260313--01</t>
+  </si>
+  <si>
+    <t>20260313--02</t>
+  </si>
+  <si>
+    <t>20260313--03</t>
+  </si>
+  <si>
+    <t>20260313--04</t>
+  </si>
+  <si>
+    <t>20260313--05</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:31</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
     <t>06:22</t>
   </si>
   <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>02:04</t>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>01:54</t>
   </si>
   <si>
     <t>04:24</t>
@@ -163,90 +226,18 @@
     <t>06:18</t>
   </si>
   <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:56</t>
+    <t>06:10</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>01:44</t>
+    <t>01:43</t>
   </si>
   <si>
     <t>00:10</t>
   </si>
   <si>
-    <t>01:32:55</t>
-  </si>
-  <si>
-    <t>03:10:28</t>
-  </si>
-  <si>
-    <t>04:48:29</t>
-  </si>
-  <si>
-    <t>23:16:43</t>
-  </si>
-  <si>
     <t>00:53:32</t>
   </si>
   <si>
@@ -259,70 +250,73 @@
     <t>22:37:28</t>
   </si>
   <si>
-    <t>00:14:06</t>
-  </si>
-  <si>
-    <t>01:51:33</t>
-  </si>
-  <si>
-    <t>03:29:22</t>
-  </si>
-  <si>
-    <t>21:58:11</t>
-  </si>
-  <si>
-    <t>23:34:37</t>
-  </si>
-  <si>
-    <t>01:12:00</t>
-  </si>
-  <si>
-    <t>02:49:45</t>
-  </si>
-  <si>
-    <t>22:55:05</t>
-  </si>
-  <si>
-    <t>00:32:23</t>
-  </si>
-  <si>
-    <t>02:10:04</t>
-  </si>
-  <si>
-    <t>22:15:31</t>
-  </si>
-  <si>
-    <t>23:52:43</t>
-  </si>
-  <si>
-    <t>01:30:21</t>
-  </si>
-  <si>
-    <t>21:35:54</t>
-  </si>
-  <si>
-    <t>23:12:59</t>
-  </si>
-  <si>
-    <t>00:50:34</t>
-  </si>
-  <si>
-    <t>20:56:14</t>
-  </si>
-  <si>
-    <t>22:33:11</t>
-  </si>
-  <si>
-    <t>01:35:11</t>
-  </si>
-  <si>
-    <t>03:12:49</t>
-  </si>
-  <si>
-    <t>04:52:00</t>
-  </si>
-  <si>
-    <t>23:19:27</t>
+    <t>00:14:07</t>
+  </si>
+  <si>
+    <t>01:51:34</t>
+  </si>
+  <si>
+    <t>03:29:23</t>
+  </si>
+  <si>
+    <t>21:58:13</t>
+  </si>
+  <si>
+    <t>23:34:39</t>
+  </si>
+  <si>
+    <t>01:12:02</t>
+  </si>
+  <si>
+    <t>02:49:47</t>
+  </si>
+  <si>
+    <t>22:55:08</t>
+  </si>
+  <si>
+    <t>00:32:26</t>
+  </si>
+  <si>
+    <t>02:10:08</t>
+  </si>
+  <si>
+    <t>22:15:35</t>
+  </si>
+  <si>
+    <t>23:52:47</t>
+  </si>
+  <si>
+    <t>01:30:26</t>
+  </si>
+  <si>
+    <t>21:36:00</t>
+  </si>
+  <si>
+    <t>23:13:05</t>
+  </si>
+  <si>
+    <t>00:50:41</t>
+  </si>
+  <si>
+    <t>20:56:23</t>
+  </si>
+  <si>
+    <t>22:33:20</t>
+  </si>
+  <si>
+    <t>00:10:52</t>
+  </si>
+  <si>
+    <t>01:48:51</t>
+  </si>
+  <si>
+    <t>20:16:44</t>
+  </si>
+  <si>
+    <t>21:53:32</t>
+  </si>
+  <si>
+    <t>23:31:01</t>
   </si>
   <si>
     <t>00:55:49</t>
@@ -334,73 +328,76 @@
     <t>04:12:00</t>
   </si>
   <si>
-    <t>22:40:25</t>
-  </si>
-  <si>
-    <t>00:16:24</t>
-  </si>
-  <si>
-    <t>01:53:50</t>
-  </si>
-  <si>
-    <t>03:32:10</t>
-  </si>
-  <si>
-    <t>22:01:32</t>
-  </si>
-  <si>
-    <t>23:36:57</t>
-  </si>
-  <si>
-    <t>01:14:16</t>
-  </si>
-  <si>
-    <t>02:52:23</t>
-  </si>
-  <si>
-    <t>22:57:27</t>
-  </si>
-  <si>
-    <t>00:34:39</t>
-  </si>
-  <si>
-    <t>02:12:36</t>
-  </si>
-  <si>
-    <t>22:17:56</t>
-  </si>
-  <si>
-    <t>23:54:58</t>
-  </si>
-  <si>
-    <t>01:32:48</t>
-  </si>
-  <si>
-    <t>21:38:23</t>
-  </si>
-  <si>
-    <t>23:15:14</t>
-  </si>
-  <si>
-    <t>00:52:57</t>
-  </si>
-  <si>
-    <t>20:58:50</t>
-  </si>
-  <si>
-    <t>22:35:27</t>
-  </si>
-  <si>
-    <t>01:38:22</t>
-  </si>
-  <si>
-    <t>03:15:50</t>
-  </si>
-  <si>
-    <t>04:53:02</t>
-  </si>
-  <si>
-    <t>23:21:39</t>
+    <t>22:40:26</t>
+  </si>
+  <si>
+    <t>00:16:25</t>
+  </si>
+  <si>
+    <t>01:53:51</t>
+  </si>
+  <si>
+    <t>03:32:11</t>
+  </si>
+  <si>
+    <t>22:01:33</t>
+  </si>
+  <si>
+    <t>23:36:58</t>
+  </si>
+  <si>
+    <t>01:14:18</t>
+  </si>
+  <si>
+    <t>02:52:25</t>
+  </si>
+  <si>
+    <t>22:57:30</t>
+  </si>
+  <si>
+    <t>00:34:42</t>
+  </si>
+  <si>
+    <t>02:12:39</t>
+  </si>
+  <si>
+    <t>22:18:00</t>
+  </si>
+  <si>
+    <t>23:55:03</t>
+  </si>
+  <si>
+    <t>01:32:52</t>
+  </si>
+  <si>
+    <t>21:38:29</t>
+  </si>
+  <si>
+    <t>23:15:21</t>
+  </si>
+  <si>
+    <t>00:53:04</t>
+  </si>
+  <si>
+    <t>20:58:58</t>
+  </si>
+  <si>
+    <t>22:35:36</t>
+  </si>
+  <si>
+    <t>00:13:13</t>
+  </si>
+  <si>
+    <t>01:52:26</t>
+  </si>
+  <si>
+    <t>20:19:28</t>
+  </si>
+  <si>
+    <t>21:55:49</t>
+  </si>
+  <si>
+    <t>23:33:20</t>
   </si>
   <si>
     <t>00:58:58</t>
@@ -412,79 +409,82 @@
     <t>04:13:42</t>
   </si>
   <si>
-    <t>22:42:14</t>
-  </si>
-  <si>
-    <t>00:19:30</t>
-  </si>
-  <si>
-    <t>01:56:59</t>
+    <t>22:42:15</t>
+  </si>
+  <si>
+    <t>00:19:31</t>
+  </si>
+  <si>
+    <t>01:57:00</t>
   </si>
   <si>
     <t>03:34:17</t>
   </si>
   <si>
-    <t>22:02:47</t>
-  </si>
-  <si>
-    <t>23:39:59</t>
-  </si>
-  <si>
-    <t>01:17:27</t>
-  </si>
-  <si>
-    <t>02:54:47</t>
-  </si>
-  <si>
-    <t>23:00:24</t>
-  </si>
-  <si>
-    <t>00:37:50</t>
-  </si>
-  <si>
-    <t>02:15:13</t>
-  </si>
-  <si>
-    <t>22:20:45</t>
-  </si>
-  <si>
-    <t>23:58:10</t>
-  </si>
-  <si>
-    <t>01:35:35</t>
-  </si>
-  <si>
-    <t>21:41:03</t>
-  </si>
-  <si>
-    <t>23:18:26</t>
-  </si>
-  <si>
-    <t>00:55:52</t>
-  </si>
-  <si>
-    <t>21:01:18</t>
-  </si>
-  <si>
-    <t>22:38:38</t>
-  </si>
-  <si>
-    <t>01:41:33</t>
-  </si>
-  <si>
-    <t>03:18:52</t>
-  </si>
-  <si>
-    <t>04:54:04</t>
-  </si>
-  <si>
-    <t>23:23:51</t>
-  </si>
-  <si>
-    <t>01:02:07</t>
-  </si>
-  <si>
-    <t>02:39:32</t>
+    <t>22:02:48</t>
+  </si>
+  <si>
+    <t>23:40:00</t>
+  </si>
+  <si>
+    <t>01:17:29</t>
+  </si>
+  <si>
+    <t>02:54:49</t>
+  </si>
+  <si>
+    <t>23:00:27</t>
+  </si>
+  <si>
+    <t>00:37:53</t>
+  </si>
+  <si>
+    <t>02:15:16</t>
+  </si>
+  <si>
+    <t>22:20:50</t>
+  </si>
+  <si>
+    <t>23:58:15</t>
+  </si>
+  <si>
+    <t>01:35:39</t>
+  </si>
+  <si>
+    <t>21:41:09</t>
+  </si>
+  <si>
+    <t>23:18:33</t>
+  </si>
+  <si>
+    <t>00:55:58</t>
+  </si>
+  <si>
+    <t>21:01:26</t>
+  </si>
+  <si>
+    <t>22:38:47</t>
+  </si>
+  <si>
+    <t>00:16:13</t>
+  </si>
+  <si>
+    <t>01:53:24</t>
+  </si>
+  <si>
+    <t>20:21:40</t>
+  </si>
+  <si>
+    <t>21:58:58</t>
+  </si>
+  <si>
+    <t>23:36:25</t>
+  </si>
+  <si>
+    <t>01:02:08</t>
+  </si>
+  <si>
+    <t>02:39:33</t>
   </si>
   <si>
     <t>04:15:24</t>
@@ -493,67 +493,73 @@
     <t>22:44:05</t>
   </si>
   <si>
-    <t>00:22:37</t>
-  </si>
-  <si>
-    <t>02:00:07</t>
-  </si>
-  <si>
-    <t>03:36:23</t>
-  </si>
-  <si>
-    <t>22:04:02</t>
-  </si>
-  <si>
-    <t>23:43:01</t>
-  </si>
-  <si>
-    <t>01:20:37</t>
-  </si>
-  <si>
-    <t>02:57:11</t>
-  </si>
-  <si>
-    <t>23:03:21</t>
-  </si>
-  <si>
-    <t>00:41:02</t>
-  </si>
-  <si>
-    <t>02:17:50</t>
-  </si>
-  <si>
-    <t>22:23:35</t>
-  </si>
-  <si>
-    <t>00:01:23</t>
-  </si>
-  <si>
-    <t>21:43:44</t>
-  </si>
-  <si>
-    <t>23:21:38</t>
-  </si>
-  <si>
-    <t>00:58:47</t>
-  </si>
-  <si>
-    <t>21:03:46</t>
-  </si>
-  <si>
-    <t>22:41:49</t>
-  </si>
-  <si>
-    <t>01:43:50</t>
-  </si>
-  <si>
-    <t>03:21:12</t>
-  </si>
-  <si>
-    <t>04:57:35</t>
-  </si>
-  <si>
-    <t>23:26:36</t>
+    <t>00:22:38</t>
+  </si>
+  <si>
+    <t>02:00:08</t>
+  </si>
+  <si>
+    <t>03:36:24</t>
+  </si>
+  <si>
+    <t>22:04:04</t>
+  </si>
+  <si>
+    <t>23:43:03</t>
+  </si>
+  <si>
+    <t>01:20:39</t>
+  </si>
+  <si>
+    <t>02:57:13</t>
+  </si>
+  <si>
+    <t>23:03:24</t>
+  </si>
+  <si>
+    <t>00:41:05</t>
+  </si>
+  <si>
+    <t>02:17:53</t>
+  </si>
+  <si>
+    <t>22:23:40</t>
+  </si>
+  <si>
+    <t>00:01:27</t>
+  </si>
+  <si>
+    <t>01:38:27</t>
+  </si>
+  <si>
+    <t>21:43:51</t>
+  </si>
+  <si>
+    <t>23:21:45</t>
+  </si>
+  <si>
+    <t>00:58:53</t>
+  </si>
+  <si>
+    <t>21:03:55</t>
+  </si>
+  <si>
+    <t>22:41:58</t>
+  </si>
+  <si>
+    <t>00:19:14</t>
+  </si>
+  <si>
+    <t>01:54:20</t>
+  </si>
+  <si>
+    <t>20:23:52</t>
+  </si>
+  <si>
+    <t>22:02:07</t>
+  </si>
+  <si>
+    <t>23:39:30</t>
   </si>
   <si>
     <t>01:04:25</t>
@@ -562,72 +568,84 @@
     <t>02:41:51</t>
   </si>
   <si>
-    <t>04:18:26</t>
+    <t>04:18:27</t>
   </si>
   <si>
     <t>22:47:03</t>
   </si>
   <si>
-    <t>00:24:55</t>
-  </si>
-  <si>
-    <t>02:02:25</t>
-  </si>
-  <si>
-    <t>03:39:11</t>
-  </si>
-  <si>
-    <t>22:07:24</t>
-  </si>
-  <si>
-    <t>23:45:21</t>
-  </si>
-  <si>
-    <t>01:22:54</t>
-  </si>
-  <si>
-    <t>02:59:49</t>
-  </si>
-  <si>
-    <t>23:05:43</t>
-  </si>
-  <si>
-    <t>00:43:18</t>
-  </si>
-  <si>
-    <t>02:20:22</t>
-  </si>
-  <si>
-    <t>22:26:01</t>
-  </si>
-  <si>
-    <t>00:03:38</t>
-  </si>
-  <si>
-    <t>01:40:48</t>
-  </si>
-  <si>
-    <t>21:46:14</t>
-  </si>
-  <si>
-    <t>23:23:54</t>
-  </si>
-  <si>
-    <t>01:01:09</t>
-  </si>
-  <si>
-    <t>21:06:22</t>
+    <t>00:24:56</t>
+  </si>
+  <si>
+    <t>02:02:26</t>
+  </si>
+  <si>
+    <t>03:39:12</t>
+  </si>
+  <si>
+    <t>22:07:25</t>
+  </si>
+  <si>
+    <t>23:45:23</t>
+  </si>
+  <si>
+    <t>01:22:56</t>
+  </si>
+  <si>
+    <t>02:59:51</t>
+  </si>
+  <si>
+    <t>23:05:46</t>
+  </si>
+  <si>
+    <t>00:43:21</t>
+  </si>
+  <si>
+    <t>02:20:25</t>
+  </si>
+  <si>
+    <t>22:26:05</t>
+  </si>
+  <si>
+    <t>00:03:43</t>
+  </si>
+  <si>
+    <t>01:40:53</t>
+  </si>
+  <si>
+    <t>21:46:20</t>
+  </si>
+  <si>
+    <t>23:24:01</t>
+  </si>
+  <si>
+    <t>01:01:16</t>
+  </si>
+  <si>
+    <t>21:06:31</t>
+  </si>
+  <si>
+    <t>22:44:14</t>
+  </si>
+  <si>
+    <t>00:21:34</t>
+  </si>
+  <si>
+    <t>01:57:55</t>
+  </si>
+  <si>
+    <t>20:26:37</t>
+  </si>
+  <si>
+    <t>22:04:24</t>
+  </si>
+  <si>
+    <t>23:41:48</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
     <t>7°</t>
   </si>
   <si>
@@ -640,22 +658,16 @@
     <t>3°</t>
   </si>
   <si>
-    <t>03:17:40</t>
-  </si>
-  <si>
-    <t>04:51:10</t>
-  </si>
-  <si>
     <t>02:40:10</t>
   </si>
   <si>
-    <t>04:13:40</t>
-  </si>
-  <si>
-    <t>03:36:13</t>
-  </si>
-  <si>
-    <t>02:58:49</t>
+    <t>04:13:41</t>
+  </si>
+  <si>
+    <t>03:36:14</t>
+  </si>
+  <si>
+    <t>02:58:51</t>
   </si>
   <si>
     <t>B</t>
@@ -664,16 +676,13 @@
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -707,7 +716,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -740,13 +749,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,60 +840,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -916,6 +943,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1319,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1397,46 +1433,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L2" s="4">
-        <v>-36.2</v>
+        <v>-39.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1444,8 +1480,8 @@
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1453,43 +1489,43 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.1</v>
+        <v>-28.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
@@ -1500,8 +1536,8 @@
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="R3" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1509,43 +1545,43 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="L4" s="4">
-        <v>-8</v>
+        <v>-13.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -1556,8 +1592,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="R4" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1565,46 +1601,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L5" s="4">
-        <v>-44.7</v>
+        <v>-43.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O5" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1612,8 +1648,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>2</v>
+      <c r="R5" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1621,55 +1657,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L6" s="4">
-        <v>-39.8</v>
+        <v>-42.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O6" s="6">
+        <v>220</v>
+      </c>
+      <c r="O6" s="9">
+        <v>60</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
         <v>3</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>3</v>
+      <c r="R6" s="10">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1677,46 +1713,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="L7" s="4">
-        <v>-28.3</v>
+        <v>-33.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O7" s="6">
-        <v>5</v>
+        <v>220</v>
+      </c>
+      <c r="O7" s="9">
+        <v>67</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1724,8 +1760,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
-        <v>5</v>
+      <c r="R7" s="11">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1733,55 +1769,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="L8" s="4">
-        <v>-13.9</v>
+        <v>-19.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O8" s="9">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>33</v>
+      <c r="Q8" s="12">
+        <v>28</v>
+      </c>
+      <c r="R8" s="13">
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1789,55 +1825,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L9" s="4">
-        <v>-43.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" s="6">
-        <v>11</v>
-      </c>
-      <c r="P9" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>2</v>
-      </c>
-      <c r="R9" s="8">
-        <v>7</v>
+        <v>221</v>
+      </c>
+      <c r="O9" s="9">
+        <v>67</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>58</v>
+      </c>
+      <c r="R9" s="14">
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1845,55 +1881,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L10" s="4">
-        <v>-42.4</v>
+        <v>-43.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O10" s="9">
-        <v>19</v>
-      </c>
-      <c r="P10" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>7</v>
-      </c>
-      <c r="R10" s="11">
-        <v>11</v>
+        <v>85</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>72</v>
+      </c>
+      <c r="R10" s="14">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1901,55 +1937,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" s="4">
-        <v>-33.2</v>
+        <v>-37.3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O11" s="9">
-        <v>35</v>
-      </c>
-      <c r="P11" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>14</v>
-      </c>
-      <c r="R11" s="10">
-        <v>35</v>
+        <v>56</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>37</v>
+      </c>
+      <c r="R11" s="17">
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1957,55 +1993,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L12" s="4">
-        <v>-19.6</v>
+        <v>-25</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O12" s="13">
-        <v>75</v>
+        <v>220</v>
+      </c>
+      <c r="O12" s="9">
+        <v>95</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
       </c>
-      <c r="Q12" s="7">
-        <v>1</v>
-      </c>
-      <c r="R12" s="14">
-        <v>75</v>
+      <c r="Q12" s="18">
+        <v>80</v>
+      </c>
+      <c r="R12" s="19">
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2013,55 +2049,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L13" s="4">
-        <v>-41.5</v>
+        <v>-43.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" s="13">
-        <v>63</v>
+        <v>220</v>
+      </c>
+      <c r="O13" s="6">
+        <v>5</v>
       </c>
       <c r="P13" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="8">
-        <v>3</v>
-      </c>
-      <c r="R13" s="15">
-        <v>61</v>
+        <v>4</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2069,55 +2105,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L14" s="4">
-        <v>-43.7</v>
+        <v>-40.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O14" s="13">
-        <v>57</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
+        <v>220</v>
+      </c>
+      <c r="O14" s="20">
+        <v>25</v>
+      </c>
+      <c r="P14" s="8">
         <v>3</v>
       </c>
-      <c r="R14" s="16">
-        <v>56</v>
+      <c r="Q14" s="21">
+        <v>25</v>
+      </c>
+      <c r="R14" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2125,55 +2161,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L15" s="4">
-        <v>-37.3</v>
+        <v>-30.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O15" s="13">
-        <v>56</v>
+        <v>220</v>
+      </c>
+      <c r="O15" s="20">
+        <v>39</v>
       </c>
       <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="22">
         <v>39</v>
       </c>
-      <c r="R15" s="18">
-        <v>43</v>
+      <c r="R15" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2181,55 +2217,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>213</v>
+        <v>88</v>
       </c>
       <c r="L16" s="4">
-        <v>-25</v>
+        <v>-41.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" s="9">
-        <v>45</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>26</v>
-      </c>
-      <c r="R16" s="18">
-        <v>43</v>
+        <v>220</v>
+      </c>
+      <c r="O16" s="20">
+        <v>20</v>
+      </c>
+      <c r="P16" s="23">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>1</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2237,52 +2273,52 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L17" s="4">
-        <v>-43.5</v>
+        <v>-42.3</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O17" s="6">
-        <v>8</v>
-      </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="P17" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
       </c>
       <c r="R17" s="7">
         <v>0</v>
@@ -2293,46 +2329,46 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L18" s="4">
-        <v>-40.4</v>
+        <v>-34.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="7">
         <v>0</v>
@@ -2352,52 +2388,52 @@
         <v>20</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L19" s="4">
-        <v>-30.2</v>
+        <v>-38.9</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="O19" s="9">
+        <v>68</v>
+      </c>
+      <c r="P19" s="12">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>68</v>
+      </c>
+      <c r="R19" s="16">
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2405,55 +2441,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L20" s="4">
-        <v>-41.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O20" s="9">
-        <v>19</v>
-      </c>
-      <c r="P20" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="P20" s="23">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>64</v>
+      </c>
+      <c r="R20" s="12">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2461,55 +2497,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L21" s="4">
-        <v>-42.3</v>
+        <v>-38.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O21" s="6">
-        <v>18</v>
-      </c>
-      <c r="P21" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
-        <v>5</v>
+        <v>220</v>
+      </c>
+      <c r="O21" s="9">
+        <v>54</v>
+      </c>
+      <c r="P21" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>54</v>
+      </c>
+      <c r="R21" s="21">
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2517,55 +2553,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L22" s="4">
-        <v>-34.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O22" s="9">
-        <v>21</v>
-      </c>
-      <c r="P22" s="8">
-        <v>4</v>
+        <v>220</v>
+      </c>
+      <c r="O22" s="20">
+        <v>19</v>
+      </c>
+      <c r="P22" s="7">
+        <v>2</v>
       </c>
       <c r="Q22" s="7">
-        <v>2</v>
-      </c>
-      <c r="R22" s="11">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="R22" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2573,52 +2609,52 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L23" s="4">
-        <v>-38.9</v>
+        <v>-41.8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O23" s="9">
+        <v>220</v>
+      </c>
+      <c r="O23" s="20">
         <v>27</v>
       </c>
-      <c r="P23" s="12">
-        <v>15</v>
+      <c r="P23" s="8">
+        <v>6</v>
       </c>
       <c r="Q23" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R23" s="7">
         <v>0</v>
@@ -2629,55 +2665,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L24" s="4">
-        <v>-42.8</v>
+        <v>-40.6</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O24" s="9">
-        <v>28</v>
-      </c>
-      <c r="P24" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>3</v>
-      </c>
-      <c r="R24" s="7">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="P24" s="24">
+        <v>17</v>
+      </c>
+      <c r="Q24" s="12">
+        <v>29</v>
+      </c>
+      <c r="R24" s="24">
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2685,55 +2721,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L25" s="4">
-        <v>-38.2</v>
+        <v>-31.8</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O25" s="9">
-        <v>27</v>
-      </c>
-      <c r="P25" s="19">
-        <v>25</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>1</v>
-      </c>
-      <c r="R25" s="7">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="P25" s="12">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>35</v>
+      </c>
+      <c r="R25" s="24">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2741,55 +2777,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" s="4">
-        <v>-34.8</v>
+        <v>-29.9</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O26" s="13">
-        <v>56</v>
-      </c>
-      <c r="P26" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>35</v>
-      </c>
-      <c r="R26" s="20">
-        <v>31</v>
+        <v>220</v>
+      </c>
+      <c r="O26" s="20">
+        <v>40</v>
+      </c>
+      <c r="P26" s="22">
+        <v>40</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2797,114 +2833,170 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-39.5</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O27" s="20">
+        <v>38</v>
+      </c>
+      <c r="P27" s="22">
+        <v>38</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-41.8</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O27" s="13">
-        <v>68</v>
-      </c>
-      <c r="P27" s="10">
-        <v>35</v>
-      </c>
-      <c r="Q27" s="20">
-        <v>32</v>
-      </c>
-      <c r="R27" s="21">
-        <v>49</v>
+      <c r="B28" s="2">
+        <v>28</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L28" s="4">
+        <v>-41.7</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O28" s="20">
+        <v>17</v>
+      </c>
+      <c r="P28" s="24">
+        <v>17</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>0</v>
+      </c>
+      <c r="R28" s="24">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A28">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B28">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C28">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D28">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E28">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F28">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G28">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H28">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I28">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K28">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L28">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2923,12 +3015,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M28">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N28">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2945,22 +3037,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O28">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P28">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q28">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R28">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="220">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260307--01</t>
-  </si>
-  <si>
-    <t>20260307--02</t>
-  </si>
-  <si>
-    <t>20260307--03</t>
-  </si>
-  <si>
-    <t>20260307--04</t>
-  </si>
-  <si>
     <t>20260308--01</t>
   </si>
   <si>
@@ -151,523 +139,526 @@
     <t>20260313--05</t>
   </si>
   <si>
-    <t>06:19</t>
+    <t>20260314--01</t>
+  </si>
+  <si>
+    <t>20260314--02</t>
+  </si>
+  <si>
+    <t>20260314--03</t>
+  </si>
+  <si>
+    <t>20260314--04</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:29</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>01:56</t>
+  </si>
+  <si>
+    <t>04:23</t>
+  </si>
+  <si>
+    <t>06:18</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>03:23</t>
+  </si>
+  <si>
+    <t>03:36</t>
   </si>
   <si>
     <t>06:12</t>
   </si>
   <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>03:39</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:31</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:57</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>01:54</t>
-  </si>
-  <si>
-    <t>04:24</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>06:10</t>
+    <t>06:16</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:43</t>
-  </si>
-  <si>
     <t>00:10</t>
   </si>
   <si>
-    <t>00:53:32</t>
-  </si>
-  <si>
-    <t>02:31:03</t>
-  </si>
-  <si>
-    <t>04:08:57</t>
-  </si>
-  <si>
-    <t>22:37:28</t>
-  </si>
-  <si>
-    <t>00:14:07</t>
-  </si>
-  <si>
-    <t>01:51:34</t>
-  </si>
-  <si>
-    <t>03:29:23</t>
-  </si>
-  <si>
-    <t>21:58:13</t>
-  </si>
-  <si>
-    <t>23:34:39</t>
-  </si>
-  <si>
-    <t>01:12:02</t>
-  </si>
-  <si>
-    <t>02:49:47</t>
-  </si>
-  <si>
-    <t>22:55:08</t>
-  </si>
-  <si>
-    <t>00:32:26</t>
-  </si>
-  <si>
-    <t>02:10:08</t>
-  </si>
-  <si>
-    <t>22:15:35</t>
-  </si>
-  <si>
-    <t>23:52:47</t>
-  </si>
-  <si>
-    <t>01:30:26</t>
-  </si>
-  <si>
-    <t>21:36:00</t>
-  </si>
-  <si>
-    <t>23:13:05</t>
-  </si>
-  <si>
-    <t>00:50:41</t>
-  </si>
-  <si>
-    <t>20:56:23</t>
-  </si>
-  <si>
-    <t>22:33:20</t>
-  </si>
-  <si>
-    <t>00:10:52</t>
-  </si>
-  <si>
-    <t>01:48:51</t>
-  </si>
-  <si>
-    <t>20:16:44</t>
-  </si>
-  <si>
-    <t>21:53:32</t>
-  </si>
-  <si>
-    <t>23:31:01</t>
-  </si>
-  <si>
-    <t>00:55:49</t>
-  </si>
-  <si>
-    <t>02:33:21</t>
-  </si>
-  <si>
-    <t>04:12:00</t>
-  </si>
-  <si>
-    <t>22:40:26</t>
-  </si>
-  <si>
-    <t>00:16:25</t>
-  </si>
-  <si>
-    <t>01:53:51</t>
-  </si>
-  <si>
-    <t>03:32:11</t>
-  </si>
-  <si>
-    <t>22:01:33</t>
-  </si>
-  <si>
-    <t>23:36:58</t>
-  </si>
-  <si>
-    <t>01:14:18</t>
-  </si>
-  <si>
-    <t>02:52:25</t>
-  </si>
-  <si>
-    <t>22:57:30</t>
-  </si>
-  <si>
-    <t>00:34:42</t>
-  </si>
-  <si>
-    <t>02:12:39</t>
-  </si>
-  <si>
-    <t>22:18:00</t>
-  </si>
-  <si>
-    <t>23:55:03</t>
-  </si>
-  <si>
-    <t>01:32:52</t>
-  </si>
-  <si>
-    <t>21:38:29</t>
-  </si>
-  <si>
-    <t>23:15:21</t>
-  </si>
-  <si>
-    <t>00:53:04</t>
-  </si>
-  <si>
-    <t>20:58:58</t>
-  </si>
-  <si>
-    <t>22:35:36</t>
-  </si>
-  <si>
-    <t>00:13:13</t>
-  </si>
-  <si>
-    <t>01:52:26</t>
-  </si>
-  <si>
-    <t>20:19:28</t>
-  </si>
-  <si>
-    <t>21:55:49</t>
-  </si>
-  <si>
-    <t>23:33:20</t>
-  </si>
-  <si>
-    <t>00:58:58</t>
-  </si>
-  <si>
-    <t>02:36:27</t>
-  </si>
-  <si>
-    <t>04:13:42</t>
-  </si>
-  <si>
-    <t>22:42:15</t>
-  </si>
-  <si>
-    <t>00:19:31</t>
-  </si>
-  <si>
-    <t>01:57:00</t>
+    <t>00:14:06</t>
+  </si>
+  <si>
+    <t>01:51:33</t>
+  </si>
+  <si>
+    <t>03:29:22</t>
+  </si>
+  <si>
+    <t>21:58:11</t>
+  </si>
+  <si>
+    <t>23:34:37</t>
+  </si>
+  <si>
+    <t>01:11:59</t>
+  </si>
+  <si>
+    <t>02:49:44</t>
+  </si>
+  <si>
+    <t>22:55:04</t>
+  </si>
+  <si>
+    <t>00:32:21</t>
+  </si>
+  <si>
+    <t>02:10:02</t>
+  </si>
+  <si>
+    <t>22:15:27</t>
+  </si>
+  <si>
+    <t>23:52:39</t>
+  </si>
+  <si>
+    <t>01:30:17</t>
+  </si>
+  <si>
+    <t>21:35:48</t>
+  </si>
+  <si>
+    <t>23:12:52</t>
+  </si>
+  <si>
+    <t>00:50:27</t>
+  </si>
+  <si>
+    <t>20:56:05</t>
+  </si>
+  <si>
+    <t>22:33:02</t>
+  </si>
+  <si>
+    <t>00:10:34</t>
+  </si>
+  <si>
+    <t>01:48:32</t>
+  </si>
+  <si>
+    <t>20:16:20</t>
+  </si>
+  <si>
+    <t>21:53:08</t>
+  </si>
+  <si>
+    <t>23:30:36</t>
+  </si>
+  <si>
+    <t>01:08:28</t>
+  </si>
+  <si>
+    <t>19:36:34</t>
+  </si>
+  <si>
+    <t>21:13:09</t>
+  </si>
+  <si>
+    <t>22:50:34</t>
+  </si>
+  <si>
+    <t>00:16:24</t>
+  </si>
+  <si>
+    <t>01:53:50</t>
+  </si>
+  <si>
+    <t>03:32:10</t>
+  </si>
+  <si>
+    <t>22:01:32</t>
+  </si>
+  <si>
+    <t>23:36:56</t>
+  </si>
+  <si>
+    <t>01:14:16</t>
+  </si>
+  <si>
+    <t>02:52:22</t>
+  </si>
+  <si>
+    <t>22:57:25</t>
+  </si>
+  <si>
+    <t>00:34:37</t>
+  </si>
+  <si>
+    <t>02:12:34</t>
+  </si>
+  <si>
+    <t>22:17:52</t>
+  </si>
+  <si>
+    <t>23:54:54</t>
+  </si>
+  <si>
+    <t>01:32:44</t>
+  </si>
+  <si>
+    <t>21:38:17</t>
+  </si>
+  <si>
+    <t>23:15:08</t>
+  </si>
+  <si>
+    <t>00:52:51</t>
+  </si>
+  <si>
+    <t>20:58:41</t>
+  </si>
+  <si>
+    <t>22:35:18</t>
+  </si>
+  <si>
+    <t>00:12:54</t>
+  </si>
+  <si>
+    <t>01:52:06</t>
+  </si>
+  <si>
+    <t>20:19:05</t>
+  </si>
+  <si>
+    <t>21:55:24</t>
+  </si>
+  <si>
+    <t>23:32:55</t>
+  </si>
+  <si>
+    <t>01:11:31</t>
+  </si>
+  <si>
+    <t>19:39:32</t>
+  </si>
+  <si>
+    <t>21:15:27</t>
+  </si>
+  <si>
+    <t>22:52:51</t>
+  </si>
+  <si>
+    <t>00:19:30</t>
+  </si>
+  <si>
+    <t>01:56:59</t>
   </si>
   <si>
     <t>03:34:17</t>
   </si>
   <si>
-    <t>22:02:48</t>
-  </si>
-  <si>
-    <t>23:40:00</t>
-  </si>
-  <si>
-    <t>01:17:29</t>
-  </si>
-  <si>
-    <t>02:54:49</t>
-  </si>
-  <si>
-    <t>23:00:27</t>
-  </si>
-  <si>
-    <t>00:37:53</t>
-  </si>
-  <si>
-    <t>02:15:16</t>
-  </si>
-  <si>
-    <t>22:20:50</t>
-  </si>
-  <si>
-    <t>23:58:15</t>
-  </si>
-  <si>
-    <t>01:35:39</t>
-  </si>
-  <si>
-    <t>21:41:09</t>
-  </si>
-  <si>
-    <t>23:18:33</t>
-  </si>
-  <si>
-    <t>00:55:58</t>
-  </si>
-  <si>
-    <t>21:01:26</t>
-  </si>
-  <si>
-    <t>22:38:47</t>
-  </si>
-  <si>
-    <t>00:16:13</t>
-  </si>
-  <si>
-    <t>01:53:24</t>
-  </si>
-  <si>
-    <t>20:21:40</t>
-  </si>
-  <si>
-    <t>21:58:58</t>
-  </si>
-  <si>
-    <t>23:36:25</t>
-  </si>
-  <si>
-    <t>01:02:08</t>
-  </si>
-  <si>
-    <t>02:39:33</t>
-  </si>
-  <si>
-    <t>04:15:24</t>
-  </si>
-  <si>
-    <t>22:44:05</t>
-  </si>
-  <si>
-    <t>00:22:38</t>
-  </si>
-  <si>
-    <t>02:00:08</t>
-  </si>
-  <si>
-    <t>03:36:24</t>
-  </si>
-  <si>
-    <t>22:04:04</t>
-  </si>
-  <si>
-    <t>23:43:03</t>
-  </si>
-  <si>
-    <t>01:20:39</t>
-  </si>
-  <si>
-    <t>02:57:13</t>
-  </si>
-  <si>
-    <t>23:03:24</t>
-  </si>
-  <si>
-    <t>00:41:05</t>
-  </si>
-  <si>
-    <t>02:17:53</t>
-  </si>
-  <si>
-    <t>22:23:40</t>
-  </si>
-  <si>
-    <t>00:01:27</t>
-  </si>
-  <si>
-    <t>01:38:27</t>
-  </si>
-  <si>
-    <t>21:43:51</t>
-  </si>
-  <si>
-    <t>23:21:45</t>
-  </si>
-  <si>
-    <t>00:58:53</t>
-  </si>
-  <si>
-    <t>21:03:55</t>
-  </si>
-  <si>
-    <t>22:41:58</t>
-  </si>
-  <si>
-    <t>00:19:14</t>
-  </si>
-  <si>
-    <t>01:54:20</t>
-  </si>
-  <si>
-    <t>20:23:52</t>
-  </si>
-  <si>
-    <t>22:02:07</t>
-  </si>
-  <si>
-    <t>23:39:30</t>
-  </si>
-  <si>
-    <t>01:04:25</t>
-  </si>
-  <si>
-    <t>02:41:51</t>
-  </si>
-  <si>
-    <t>04:18:27</t>
-  </si>
-  <si>
-    <t>22:47:03</t>
-  </si>
-  <si>
-    <t>00:24:56</t>
-  </si>
-  <si>
-    <t>02:02:26</t>
-  </si>
-  <si>
-    <t>03:39:12</t>
-  </si>
-  <si>
-    <t>22:07:25</t>
-  </si>
-  <si>
-    <t>23:45:23</t>
-  </si>
-  <si>
-    <t>01:22:56</t>
-  </si>
-  <si>
-    <t>02:59:51</t>
-  </si>
-  <si>
-    <t>23:05:46</t>
-  </si>
-  <si>
-    <t>00:43:21</t>
-  </si>
-  <si>
-    <t>02:20:25</t>
-  </si>
-  <si>
-    <t>22:26:05</t>
-  </si>
-  <si>
-    <t>00:03:43</t>
-  </si>
-  <si>
-    <t>01:40:53</t>
-  </si>
-  <si>
-    <t>21:46:20</t>
-  </si>
-  <si>
-    <t>23:24:01</t>
-  </si>
-  <si>
-    <t>01:01:16</t>
-  </si>
-  <si>
-    <t>21:06:31</t>
-  </si>
-  <si>
-    <t>22:44:14</t>
-  </si>
-  <si>
-    <t>00:21:34</t>
-  </si>
-  <si>
-    <t>01:57:55</t>
-  </si>
-  <si>
-    <t>20:26:37</t>
-  </si>
-  <si>
-    <t>22:04:24</t>
-  </si>
-  <si>
-    <t>23:41:48</t>
+    <t>22:02:46</t>
+  </si>
+  <si>
+    <t>23:39:58</t>
+  </si>
+  <si>
+    <t>01:17:26</t>
+  </si>
+  <si>
+    <t>02:54:46</t>
+  </si>
+  <si>
+    <t>23:00:22</t>
+  </si>
+  <si>
+    <t>00:37:48</t>
+  </si>
+  <si>
+    <t>02:15:11</t>
+  </si>
+  <si>
+    <t>22:20:41</t>
+  </si>
+  <si>
+    <t>23:58:06</t>
+  </si>
+  <si>
+    <t>01:35:31</t>
+  </si>
+  <si>
+    <t>21:40:57</t>
+  </si>
+  <si>
+    <t>23:18:20</t>
+  </si>
+  <si>
+    <t>00:55:45</t>
+  </si>
+  <si>
+    <t>21:01:08</t>
+  </si>
+  <si>
+    <t>22:38:28</t>
+  </si>
+  <si>
+    <t>00:15:55</t>
+  </si>
+  <si>
+    <t>01:53:04</t>
+  </si>
+  <si>
+    <t>20:21:16</t>
+  </si>
+  <si>
+    <t>21:58:33</t>
+  </si>
+  <si>
+    <t>23:35:59</t>
+  </si>
+  <si>
+    <t>01:13:12</t>
+  </si>
+  <si>
+    <t>19:41:19</t>
+  </si>
+  <si>
+    <t>21:18:33</t>
+  </si>
+  <si>
+    <t>22:55:59</t>
+  </si>
+  <si>
+    <t>00:22:37</t>
+  </si>
+  <si>
+    <t>02:00:07</t>
+  </si>
+  <si>
+    <t>03:36:23</t>
+  </si>
+  <si>
+    <t>22:04:01</t>
+  </si>
+  <si>
+    <t>23:43:01</t>
+  </si>
+  <si>
+    <t>01:20:37</t>
+  </si>
+  <si>
+    <t>02:57:10</t>
+  </si>
+  <si>
+    <t>23:03:19</t>
+  </si>
+  <si>
+    <t>00:41:00</t>
+  </si>
+  <si>
+    <t>02:17:48</t>
+  </si>
+  <si>
+    <t>22:23:31</t>
+  </si>
+  <si>
+    <t>00:01:19</t>
+  </si>
+  <si>
+    <t>01:38:18</t>
+  </si>
+  <si>
+    <t>21:43:38</t>
+  </si>
+  <si>
+    <t>23:21:32</t>
+  </si>
+  <si>
+    <t>00:58:40</t>
+  </si>
+  <si>
+    <t>21:03:37</t>
+  </si>
+  <si>
+    <t>22:41:39</t>
+  </si>
+  <si>
+    <t>00:18:55</t>
+  </si>
+  <si>
+    <t>01:54:02</t>
+  </si>
+  <si>
+    <t>20:23:28</t>
+  </si>
+  <si>
+    <t>22:01:42</t>
+  </si>
+  <si>
+    <t>23:39:04</t>
+  </si>
+  <si>
+    <t>01:14:54</t>
+  </si>
+  <si>
+    <t>19:43:08</t>
+  </si>
+  <si>
+    <t>21:21:39</t>
+  </si>
+  <si>
+    <t>22:59:07</t>
+  </si>
+  <si>
+    <t>00:24:55</t>
+  </si>
+  <si>
+    <t>02:02:25</t>
+  </si>
+  <si>
+    <t>03:39:11</t>
+  </si>
+  <si>
+    <t>22:07:23</t>
+  </si>
+  <si>
+    <t>23:45:21</t>
+  </si>
+  <si>
+    <t>01:22:53</t>
+  </si>
+  <si>
+    <t>02:59:48</t>
+  </si>
+  <si>
+    <t>23:05:41</t>
+  </si>
+  <si>
+    <t>00:43:16</t>
+  </si>
+  <si>
+    <t>02:20:19</t>
+  </si>
+  <si>
+    <t>22:25:57</t>
+  </si>
+  <si>
+    <t>00:03:34</t>
+  </si>
+  <si>
+    <t>01:40:44</t>
+  </si>
+  <si>
+    <t>21:46:07</t>
+  </si>
+  <si>
+    <t>23:23:47</t>
+  </si>
+  <si>
+    <t>01:01:03</t>
+  </si>
+  <si>
+    <t>21:06:13</t>
+  </si>
+  <si>
+    <t>22:43:55</t>
+  </si>
+  <si>
+    <t>00:21:16</t>
+  </si>
+  <si>
+    <t>01:57:36</t>
+  </si>
+  <si>
+    <t>20:26:13</t>
+  </si>
+  <si>
+    <t>22:03:59</t>
+  </si>
+  <si>
+    <t>23:41:23</t>
+  </si>
+  <si>
+    <t>01:17:56</t>
+  </si>
+  <si>
+    <t>19:46:07</t>
+  </si>
+  <si>
+    <t>21:23:57</t>
+  </si>
+  <si>
+    <t>23:01:24</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>13°</t>
-  </si>
-  <si>
     <t>11°</t>
   </si>
   <si>
     <t>3°</t>
   </si>
   <si>
-    <t>02:40:10</t>
-  </si>
-  <si>
-    <t>04:13:41</t>
-  </si>
-  <si>
-    <t>03:36:14</t>
-  </si>
-  <si>
-    <t>02:58:51</t>
+    <t>-1°</t>
+  </si>
+  <si>
+    <t>03:36:13</t>
+  </si>
+  <si>
+    <t>02:58:48</t>
+  </si>
+  <si>
+    <t>19:36:22</t>
   </si>
   <si>
     <t>B</t>
@@ -679,10 +670,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -716,7 +707,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -731,7 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,7 +734,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,7 +770,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,79 +848,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,7 +895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,6 +967,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1433,7 +1460,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>45</v>
@@ -1442,46 +1469,46 @@
         <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L2" s="4">
-        <v>-39.8</v>
+        <v>-42.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" s="8">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1489,7 +1516,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>46</v>
@@ -1498,46 +1525,46 @@
         <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="L3" s="4">
-        <v>-28.3</v>
+        <v>-33.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O3" s="9">
+        <v>10</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="R3" s="10">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1545,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>47</v>
@@ -1554,46 +1581,46 @@
         <v>72</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L4" s="4">
-        <v>-13.9</v>
+        <v>-19.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O4" s="6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>6</v>
+      <c r="Q4" s="11">
+        <v>3</v>
+      </c>
+      <c r="R4" s="12">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1601,7 +1628,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>48</v>
@@ -1610,46 +1637,46 @@
         <v>71</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" s="4">
-        <v>-43.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O5" s="6">
-        <v>7</v>
+        <v>219</v>
+      </c>
+      <c r="O5" s="13">
+        <v>99</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>6</v>
+      <c r="Q5" s="14">
+        <v>74</v>
+      </c>
+      <c r="R5" s="15">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1657,7 +1684,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>49</v>
@@ -1666,46 +1693,46 @@
         <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L6" s="4">
-        <v>-42.4</v>
+        <v>-43.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O6" s="9">
-        <v>60</v>
+        <v>217</v>
+      </c>
+      <c r="O6" s="13">
+        <v>96</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
-        <v>3</v>
-      </c>
-      <c r="R6" s="10">
-        <v>60</v>
+      <c r="Q6" s="12">
+        <v>93</v>
+      </c>
+      <c r="R6" s="12">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1713,7 +1740,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>50</v>
@@ -1722,46 +1749,46 @@
         <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>-33.2</v>
+        <v>-37.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O7" s="9">
-        <v>67</v>
+        <v>217</v>
+      </c>
+      <c r="O7" s="13">
+        <v>91</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>64</v>
+      <c r="Q7" s="15">
+        <v>81</v>
+      </c>
+      <c r="R7" s="16">
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1769,55 +1796,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L8" s="4">
-        <v>-19.6</v>
+        <v>-25</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O8" s="9">
-        <v>94</v>
+        <v>217</v>
+      </c>
+      <c r="O8" s="13">
+        <v>100</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="12">
-        <v>28</v>
-      </c>
-      <c r="R8" s="13">
+      <c r="Q8" s="17">
         <v>91</v>
+      </c>
+      <c r="R8" s="18">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1825,7 +1852,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>52</v>
@@ -1834,46 +1861,46 @@
         <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L9" s="4">
-        <v>-41.5</v>
+        <v>-43.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O9" s="9">
-        <v>67</v>
+        <v>217</v>
+      </c>
+      <c r="O9" s="13">
+        <v>61</v>
       </c>
       <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>58</v>
-      </c>
-      <c r="R9" s="14">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>61</v>
+      </c>
+      <c r="R9" s="20">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1881,7 +1908,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
@@ -1890,46 +1917,46 @@
         <v>71</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L10" s="4">
-        <v>-43.6</v>
+        <v>-40.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O10" s="9">
-        <v>85</v>
+        <v>217</v>
+      </c>
+      <c r="O10" s="13">
+        <v>54</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="15">
-        <v>72</v>
-      </c>
-      <c r="R10" s="14">
-        <v>56</v>
+      <c r="Q10" s="8">
+        <v>54</v>
+      </c>
+      <c r="R10" s="21">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1937,7 +1964,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>54</v>
@@ -1946,46 +1973,46 @@
         <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L11" s="4">
-        <v>-37.3</v>
+        <v>-30.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O11" s="9">
-        <v>56</v>
+        <v>217</v>
+      </c>
+      <c r="O11" s="6">
+        <v>41</v>
       </c>
       <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="22">
         <v>37</v>
       </c>
-      <c r="R11" s="17">
-        <v>48</v>
+      <c r="R11" s="23">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1993,7 +2020,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>55</v>
@@ -2002,46 +2029,46 @@
         <v>71</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-41.8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="L12" s="4">
-        <v>-25</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O12" s="9">
-        <v>95</v>
+      <c r="O12" s="6">
+        <v>47</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
       </c>
-      <c r="Q12" s="18">
-        <v>80</v>
-      </c>
-      <c r="R12" s="19">
-        <v>93</v>
+      <c r="Q12" s="24">
+        <v>23</v>
+      </c>
+      <c r="R12" s="24">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2049,7 +2076,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>56</v>
@@ -2058,46 +2085,46 @@
         <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L13" s="4">
-        <v>-43.5</v>
+        <v>-42.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O13" s="6">
-        <v>5</v>
-      </c>
-      <c r="P13" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>4</v>
-      </c>
-      <c r="R13" s="7">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O13" s="13">
+        <v>66</v>
+      </c>
+      <c r="P13" s="25">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="26">
+        <v>66</v>
+      </c>
+      <c r="R13" s="22">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2105,7 +2132,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>57</v>
@@ -2114,46 +2141,46 @@
         <v>71</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L14" s="4">
-        <v>-40.4</v>
+        <v>-34.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O14" s="20">
-        <v>25</v>
-      </c>
-      <c r="P14" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>25</v>
-      </c>
-      <c r="R14" s="7">
-        <v>2</v>
+        <v>217</v>
+      </c>
+      <c r="O14" s="13">
+        <v>72</v>
+      </c>
+      <c r="P14" s="25">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>68</v>
+      </c>
+      <c r="R14" s="28">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2170,46 +2197,46 @@
         <v>71</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4">
-        <v>-30.2</v>
+        <v>-38.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O15" s="20">
-        <v>39</v>
+        <v>217</v>
+      </c>
+      <c r="O15" s="9">
+        <v>5</v>
       </c>
       <c r="P15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="7">
         <v>2</v>
       </c>
-      <c r="Q15" s="22">
-        <v>39</v>
-      </c>
-      <c r="R15" s="8">
-        <v>5</v>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2217,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>59</v>
@@ -2226,43 +2253,43 @@
         <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L16" s="4">
-        <v>-41.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O16" s="20">
-        <v>20</v>
-      </c>
-      <c r="P16" s="23">
-        <v>12</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="O16" s="9">
+        <v>8</v>
+      </c>
+      <c r="P16" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>5</v>
       </c>
       <c r="R16" s="7">
         <v>0</v>
@@ -2273,7 +2300,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>60</v>
@@ -2282,43 +2309,43 @@
         <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L17" s="4">
-        <v>-42.3</v>
+        <v>-38.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O17" s="6">
-        <v>6</v>
-      </c>
-      <c r="P17" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="P17" s="28">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>27</v>
       </c>
       <c r="R17" s="7">
         <v>0</v>
@@ -2329,7 +2356,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>61</v>
@@ -2338,46 +2365,46 @@
         <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L18" s="4">
-        <v>-34.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O18" s="6">
-        <v>1</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="P18" s="25">
+        <v>17</v>
       </c>
       <c r="Q18" s="7">
         <v>0</v>
       </c>
-      <c r="R18" s="7">
-        <v>0</v>
+      <c r="R18" s="20">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2385,55 +2412,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L19" s="4">
-        <v>-38.9</v>
+        <v>-41.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O19" s="9">
-        <v>68</v>
-      </c>
-      <c r="P19" s="12">
-        <v>30</v>
-      </c>
-      <c r="Q19" s="15">
-        <v>68</v>
-      </c>
-      <c r="R19" s="16">
-        <v>36</v>
+        <v>217</v>
+      </c>
+      <c r="O19" s="6">
+        <v>39</v>
+      </c>
+      <c r="P19" s="25">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25">
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2441,55 +2468,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L20" s="4">
-        <v>-42.8</v>
+        <v>-40.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O20" s="9">
+        <v>217</v>
+      </c>
+      <c r="O20" s="13">
         <v>64</v>
       </c>
-      <c r="P20" s="23">
-        <v>12</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>64</v>
-      </c>
-      <c r="R20" s="12">
-        <v>28</v>
+      <c r="P20" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="10">
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2497,7 +2524,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>63</v>
@@ -2506,46 +2533,46 @@
         <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L21" s="4">
-        <v>-38.1</v>
+        <v>-31.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O21" s="9">
-        <v>54</v>
-      </c>
-      <c r="P21" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="14">
-        <v>54</v>
+        <v>219</v>
+      </c>
+      <c r="O21" s="13">
+        <v>62</v>
+      </c>
+      <c r="P21" s="20">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>1</v>
       </c>
       <c r="R21" s="21">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2553,7 +2580,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>64</v>
@@ -2562,43 +2589,43 @@
         <v>71</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4">
-        <v>-34.8</v>
+        <v>-29.9</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O22" s="20">
-        <v>19</v>
+        <v>217</v>
+      </c>
+      <c r="O22" s="9">
+        <v>18</v>
       </c>
       <c r="P22" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="7">
         <v>0</v>
@@ -2609,7 +2636,7 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>65</v>
@@ -2618,43 +2645,43 @@
         <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23" s="4">
-        <v>-41.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O23" s="20">
-        <v>27</v>
-      </c>
-      <c r="P23" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>7</v>
+        <v>217</v>
+      </c>
+      <c r="O23" s="6">
+        <v>32</v>
+      </c>
+      <c r="P23" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0</v>
       </c>
       <c r="R23" s="7">
         <v>0</v>
@@ -2665,7 +2692,7 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>66</v>
@@ -2674,46 +2701,46 @@
         <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L24" s="4">
-        <v>-40.6</v>
+        <v>-41.8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O24" s="9">
-        <v>54</v>
-      </c>
-      <c r="P24" s="24">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="12">
-        <v>29</v>
-      </c>
-      <c r="R24" s="24">
-        <v>13</v>
+        <v>217</v>
+      </c>
+      <c r="O24" s="6">
+        <v>21</v>
+      </c>
+      <c r="P24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>0</v>
+      </c>
+      <c r="R24" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2721,7 +2748,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>67</v>
@@ -2730,46 +2757,46 @@
         <v>71</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L25" s="4">
-        <v>-31.8</v>
+        <v>-35.8</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O25" s="9">
-        <v>55</v>
-      </c>
-      <c r="P25" s="12">
+        <v>219</v>
+      </c>
+      <c r="O25" s="6">
         <v>30</v>
       </c>
-      <c r="Q25" s="16">
-        <v>35</v>
-      </c>
-      <c r="R25" s="24">
-        <v>14</v>
+      <c r="P25" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>0</v>
+      </c>
+      <c r="R25" s="28">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2777,7 +2804,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>68</v>
@@ -2786,46 +2813,46 @@
         <v>71</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="L26" s="4">
-        <v>-29.9</v>
+        <v>-24.2</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O26" s="20">
-        <v>40</v>
-      </c>
-      <c r="P26" s="22">
-        <v>40</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="O26" s="13">
+        <v>58</v>
+      </c>
+      <c r="P26" s="25">
+        <v>17</v>
+      </c>
+      <c r="Q26" s="21">
+        <v>41</v>
+      </c>
+      <c r="R26" s="19">
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2833,7 +2860,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>69</v>
@@ -2842,46 +2869,46 @@
         <v>71</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L27" s="4">
-        <v>-39.5</v>
+        <v>-35.9</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O27" s="20">
-        <v>38</v>
-      </c>
-      <c r="P27" s="22">
-        <v>38</v>
-      </c>
-      <c r="Q27" s="7">
-        <v>0</v>
-      </c>
-      <c r="R27" s="8">
-        <v>5</v>
+        <v>217</v>
+      </c>
+      <c r="O27" s="13">
+        <v>66</v>
+      </c>
+      <c r="P27" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>49</v>
+      </c>
+      <c r="R27" s="28">
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2889,7 +2916,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>70</v>
@@ -2898,46 +2925,46 @@
         <v>71</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L28" s="4">
-        <v>-41.7</v>
+        <v>-41.4</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O28" s="20">
-        <v>17</v>
-      </c>
-      <c r="P28" s="24">
-        <v>17</v>
-      </c>
-      <c r="Q28" s="7">
-        <v>0</v>
-      </c>
-      <c r="R28" s="24">
-        <v>17</v>
+        <v>217</v>
+      </c>
+      <c r="O28" s="13">
+        <v>50</v>
+      </c>
+      <c r="P28" s="20">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="22">
+        <v>33</v>
+      </c>
+      <c r="R28" s="23">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="215">
   <si>
     <t>Datum</t>
   </si>
@@ -70,21 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260308--01</t>
-  </si>
-  <si>
-    <t>20260308--02</t>
-  </si>
-  <si>
-    <t>20260308--03</t>
-  </si>
-  <si>
-    <t>20260308--04</t>
-  </si>
-  <si>
-    <t>20260308--05</t>
-  </si>
-  <si>
     <t>20260309--01</t>
   </si>
   <si>
@@ -151,526 +136,526 @@
     <t>20260314--04</t>
   </si>
   <si>
-    <t>06:13</t>
+    <t>20260315--01</t>
+  </si>
+  <si>
+    <t>20260315--02</t>
+  </si>
+  <si>
+    <t>20260315--03</t>
+  </si>
+  <si>
+    <t>20260315--04</t>
+  </si>
+  <si>
+    <t>20260315--05</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>01:57</t>
+  </si>
+  <si>
+    <t>04:22</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:29</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>01:56</t>
-  </si>
-  <si>
-    <t>04:23</t>
-  </si>
-  <si>
-    <t>06:18</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>06:10</t>
   </si>
   <si>
     <t>03:23</t>
   </si>
   <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>06:12</t>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>06:11</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>02:18</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>00:14:06</t>
-  </si>
-  <si>
-    <t>01:51:33</t>
-  </si>
-  <si>
-    <t>03:29:22</t>
-  </si>
-  <si>
-    <t>21:58:11</t>
-  </si>
-  <si>
-    <t>23:34:37</t>
-  </si>
-  <si>
     <t>01:11:59</t>
   </si>
   <si>
     <t>02:49:44</t>
   </si>
   <si>
-    <t>22:55:04</t>
-  </si>
-  <si>
-    <t>00:32:21</t>
-  </si>
-  <si>
-    <t>02:10:02</t>
-  </si>
-  <si>
-    <t>22:15:27</t>
-  </si>
-  <si>
-    <t>23:52:39</t>
-  </si>
-  <si>
-    <t>01:30:17</t>
-  </si>
-  <si>
-    <t>21:35:48</t>
-  </si>
-  <si>
-    <t>23:12:52</t>
-  </si>
-  <si>
-    <t>00:50:27</t>
-  </si>
-  <si>
-    <t>20:56:05</t>
-  </si>
-  <si>
-    <t>22:33:02</t>
-  </si>
-  <si>
-    <t>00:10:34</t>
-  </si>
-  <si>
-    <t>01:48:32</t>
-  </si>
-  <si>
-    <t>20:16:20</t>
-  </si>
-  <si>
-    <t>21:53:08</t>
-  </si>
-  <si>
-    <t>23:30:36</t>
-  </si>
-  <si>
-    <t>01:08:28</t>
-  </si>
-  <si>
-    <t>19:36:34</t>
-  </si>
-  <si>
-    <t>21:13:09</t>
-  </si>
-  <si>
-    <t>22:50:34</t>
-  </si>
-  <si>
-    <t>00:16:24</t>
-  </si>
-  <si>
-    <t>01:53:50</t>
-  </si>
-  <si>
-    <t>03:32:10</t>
-  </si>
-  <si>
-    <t>22:01:32</t>
-  </si>
-  <si>
-    <t>23:36:56</t>
-  </si>
-  <si>
-    <t>01:14:16</t>
+    <t>22:55:02</t>
+  </si>
+  <si>
+    <t>00:32:20</t>
+  </si>
+  <si>
+    <t>02:10:01</t>
+  </si>
+  <si>
+    <t>22:15:24</t>
+  </si>
+  <si>
+    <t>23:52:36</t>
+  </si>
+  <si>
+    <t>01:30:14</t>
+  </si>
+  <si>
+    <t>21:35:42</t>
+  </si>
+  <si>
+    <t>23:12:47</t>
+  </si>
+  <si>
+    <t>00:50:22</t>
+  </si>
+  <si>
+    <t>20:55:57</t>
+  </si>
+  <si>
+    <t>22:32:53</t>
+  </si>
+  <si>
+    <t>00:10:25</t>
+  </si>
+  <si>
+    <t>01:48:23</t>
+  </si>
+  <si>
+    <t>20:16:08</t>
+  </si>
+  <si>
+    <t>21:52:55</t>
+  </si>
+  <si>
+    <t>23:30:23</t>
+  </si>
+  <si>
+    <t>01:08:15</t>
+  </si>
+  <si>
+    <t>19:36:17</t>
+  </si>
+  <si>
+    <t>21:12:53</t>
+  </si>
+  <si>
+    <t>22:50:17</t>
+  </si>
+  <si>
+    <t>00:28:03</t>
+  </si>
+  <si>
+    <t>18:56:24</t>
+  </si>
+  <si>
+    <t>20:32:46</t>
+  </si>
+  <si>
+    <t>22:10:06</t>
+  </si>
+  <si>
+    <t>23:47:48</t>
+  </si>
+  <si>
+    <t>01:14:15</t>
   </si>
   <si>
     <t>02:52:22</t>
   </si>
   <si>
-    <t>22:57:25</t>
-  </si>
-  <si>
-    <t>00:34:37</t>
-  </si>
-  <si>
-    <t>02:12:34</t>
-  </si>
-  <si>
-    <t>22:17:52</t>
-  </si>
-  <si>
-    <t>23:54:54</t>
-  </si>
-  <si>
-    <t>01:32:44</t>
-  </si>
-  <si>
-    <t>21:38:17</t>
-  </si>
-  <si>
-    <t>23:15:08</t>
-  </si>
-  <si>
-    <t>00:52:51</t>
-  </si>
-  <si>
-    <t>20:58:41</t>
-  </si>
-  <si>
-    <t>22:35:18</t>
-  </si>
-  <si>
-    <t>00:12:54</t>
-  </si>
-  <si>
-    <t>01:52:06</t>
-  </si>
-  <si>
-    <t>20:19:05</t>
-  </si>
-  <si>
-    <t>21:55:24</t>
-  </si>
-  <si>
-    <t>23:32:55</t>
-  </si>
-  <si>
-    <t>01:11:31</t>
-  </si>
-  <si>
-    <t>19:39:32</t>
-  </si>
-  <si>
-    <t>21:15:27</t>
-  </si>
-  <si>
-    <t>22:52:51</t>
-  </si>
-  <si>
-    <t>00:19:30</t>
-  </si>
-  <si>
-    <t>01:56:59</t>
-  </si>
-  <si>
-    <t>03:34:17</t>
-  </si>
-  <si>
-    <t>22:02:46</t>
-  </si>
-  <si>
-    <t>23:39:58</t>
-  </si>
-  <si>
-    <t>01:17:26</t>
+    <t>22:57:24</t>
+  </si>
+  <si>
+    <t>00:34:35</t>
+  </si>
+  <si>
+    <t>02:12:32</t>
+  </si>
+  <si>
+    <t>22:17:49</t>
+  </si>
+  <si>
+    <t>23:54:51</t>
+  </si>
+  <si>
+    <t>01:32:40</t>
+  </si>
+  <si>
+    <t>21:38:12</t>
+  </si>
+  <si>
+    <t>23:15:02</t>
+  </si>
+  <si>
+    <t>00:52:45</t>
+  </si>
+  <si>
+    <t>20:58:32</t>
+  </si>
+  <si>
+    <t>22:35:09</t>
+  </si>
+  <si>
+    <t>00:12:45</t>
+  </si>
+  <si>
+    <t>01:51:57</t>
+  </si>
+  <si>
+    <t>20:18:53</t>
+  </si>
+  <si>
+    <t>21:55:12</t>
+  </si>
+  <si>
+    <t>23:32:42</t>
+  </si>
+  <si>
+    <t>01:11:18</t>
+  </si>
+  <si>
+    <t>19:39:16</t>
+  </si>
+  <si>
+    <t>21:15:11</t>
+  </si>
+  <si>
+    <t>22:52:34</t>
+  </si>
+  <si>
+    <t>00:30:51</t>
+  </si>
+  <si>
+    <t>18:59:49</t>
+  </si>
+  <si>
+    <t>20:35:06</t>
+  </si>
+  <si>
+    <t>22:12:22</t>
+  </si>
+  <si>
+    <t>23:50:25</t>
+  </si>
+  <si>
+    <t>01:17:25</t>
   </si>
   <si>
     <t>02:54:46</t>
   </si>
   <si>
-    <t>23:00:22</t>
-  </si>
-  <si>
-    <t>00:37:48</t>
-  </si>
-  <si>
-    <t>02:15:11</t>
-  </si>
-  <si>
-    <t>22:20:41</t>
-  </si>
-  <si>
-    <t>23:58:06</t>
-  </si>
-  <si>
-    <t>01:35:31</t>
-  </si>
-  <si>
-    <t>21:40:57</t>
-  </si>
-  <si>
-    <t>23:18:20</t>
-  </si>
-  <si>
-    <t>00:55:45</t>
-  </si>
-  <si>
-    <t>21:01:08</t>
-  </si>
-  <si>
-    <t>22:38:28</t>
-  </si>
-  <si>
-    <t>00:15:55</t>
-  </si>
-  <si>
-    <t>01:53:04</t>
-  </si>
-  <si>
-    <t>20:21:16</t>
-  </si>
-  <si>
-    <t>21:58:33</t>
-  </si>
-  <si>
-    <t>23:35:59</t>
-  </si>
-  <si>
-    <t>01:13:12</t>
-  </si>
-  <si>
-    <t>19:41:19</t>
-  </si>
-  <si>
-    <t>21:18:33</t>
-  </si>
-  <si>
-    <t>22:55:59</t>
-  </si>
-  <si>
-    <t>00:22:37</t>
-  </si>
-  <si>
-    <t>02:00:07</t>
-  </si>
-  <si>
-    <t>03:36:23</t>
-  </si>
-  <si>
-    <t>22:04:01</t>
-  </si>
-  <si>
-    <t>23:43:01</t>
-  </si>
-  <si>
-    <t>01:20:37</t>
+    <t>23:00:20</t>
+  </si>
+  <si>
+    <t>00:37:47</t>
+  </si>
+  <si>
+    <t>02:15:09</t>
+  </si>
+  <si>
+    <t>22:20:38</t>
+  </si>
+  <si>
+    <t>23:58:03</t>
+  </si>
+  <si>
+    <t>01:35:27</t>
+  </si>
+  <si>
+    <t>21:40:51</t>
+  </si>
+  <si>
+    <t>23:18:14</t>
+  </si>
+  <si>
+    <t>00:55:39</t>
+  </si>
+  <si>
+    <t>21:01:00</t>
+  </si>
+  <si>
+    <t>22:38:20</t>
+  </si>
+  <si>
+    <t>00:15:46</t>
+  </si>
+  <si>
+    <t>01:52:55</t>
+  </si>
+  <si>
+    <t>20:21:04</t>
+  </si>
+  <si>
+    <t>21:58:20</t>
+  </si>
+  <si>
+    <t>23:35:47</t>
+  </si>
+  <si>
+    <t>01:12:59</t>
+  </si>
+  <si>
+    <t>19:41:03</t>
+  </si>
+  <si>
+    <t>21:18:16</t>
+  </si>
+  <si>
+    <t>22:55:42</t>
+  </si>
+  <si>
+    <t>00:32:58</t>
+  </si>
+  <si>
+    <t>19:00:58</t>
+  </si>
+  <si>
+    <t>20:38:07</t>
+  </si>
+  <si>
+    <t>22:15:32</t>
+  </si>
+  <si>
+    <t>23:52:50</t>
+  </si>
+  <si>
+    <t>01:20:36</t>
   </si>
   <si>
     <t>02:57:10</t>
   </si>
   <si>
-    <t>23:03:19</t>
-  </si>
-  <si>
-    <t>00:41:00</t>
-  </si>
-  <si>
-    <t>02:17:48</t>
-  </si>
-  <si>
-    <t>22:23:31</t>
-  </si>
-  <si>
-    <t>00:01:19</t>
-  </si>
-  <si>
-    <t>01:38:18</t>
-  </si>
-  <si>
-    <t>21:43:38</t>
-  </si>
-  <si>
-    <t>23:21:32</t>
-  </si>
-  <si>
-    <t>00:58:40</t>
-  </si>
-  <si>
-    <t>21:03:37</t>
-  </si>
-  <si>
-    <t>22:41:39</t>
-  </si>
-  <si>
-    <t>00:18:55</t>
-  </si>
-  <si>
-    <t>01:54:02</t>
-  </si>
-  <si>
-    <t>20:23:28</t>
-  </si>
-  <si>
-    <t>22:01:42</t>
-  </si>
-  <si>
-    <t>23:39:04</t>
-  </si>
-  <si>
-    <t>01:14:54</t>
-  </si>
-  <si>
-    <t>19:43:08</t>
-  </si>
-  <si>
-    <t>21:21:39</t>
-  </si>
-  <si>
-    <t>22:59:07</t>
-  </si>
-  <si>
-    <t>00:24:55</t>
-  </si>
-  <si>
-    <t>02:02:25</t>
-  </si>
-  <si>
-    <t>03:39:11</t>
-  </si>
-  <si>
-    <t>22:07:23</t>
-  </si>
-  <si>
-    <t>23:45:21</t>
-  </si>
-  <si>
-    <t>01:22:53</t>
+    <t>23:03:17</t>
+  </si>
+  <si>
+    <t>00:40:59</t>
+  </si>
+  <si>
+    <t>02:17:46</t>
+  </si>
+  <si>
+    <t>22:23:28</t>
+  </si>
+  <si>
+    <t>00:01:15</t>
+  </si>
+  <si>
+    <t>01:38:14</t>
+  </si>
+  <si>
+    <t>21:43:32</t>
+  </si>
+  <si>
+    <t>23:21:26</t>
+  </si>
+  <si>
+    <t>00:58:34</t>
+  </si>
+  <si>
+    <t>21:03:28</t>
+  </si>
+  <si>
+    <t>22:41:30</t>
+  </si>
+  <si>
+    <t>00:18:46</t>
+  </si>
+  <si>
+    <t>01:53:54</t>
+  </si>
+  <si>
+    <t>20:23:15</t>
+  </si>
+  <si>
+    <t>22:01:29</t>
+  </si>
+  <si>
+    <t>23:38:52</t>
+  </si>
+  <si>
+    <t>01:14:41</t>
+  </si>
+  <si>
+    <t>19:42:51</t>
+  </si>
+  <si>
+    <t>21:21:22</t>
+  </si>
+  <si>
+    <t>22:58:50</t>
+  </si>
+  <si>
+    <t>00:35:05</t>
+  </si>
+  <si>
+    <t>19:02:07</t>
+  </si>
+  <si>
+    <t>20:41:08</t>
+  </si>
+  <si>
+    <t>22:18:42</t>
+  </si>
+  <si>
+    <t>23:55:15</t>
+  </si>
+  <si>
+    <t>01:22:52</t>
   </si>
   <si>
     <t>02:59:48</t>
   </si>
   <si>
-    <t>23:05:41</t>
-  </si>
-  <si>
-    <t>00:43:16</t>
-  </si>
-  <si>
-    <t>02:20:19</t>
-  </si>
-  <si>
-    <t>22:25:57</t>
-  </si>
-  <si>
-    <t>00:03:34</t>
-  </si>
-  <si>
-    <t>01:40:44</t>
-  </si>
-  <si>
-    <t>21:46:07</t>
-  </si>
-  <si>
-    <t>23:23:47</t>
-  </si>
-  <si>
-    <t>01:01:03</t>
-  </si>
-  <si>
-    <t>21:06:13</t>
-  </si>
-  <si>
-    <t>22:43:55</t>
-  </si>
-  <si>
-    <t>00:21:16</t>
-  </si>
-  <si>
-    <t>01:57:36</t>
-  </si>
-  <si>
-    <t>20:26:13</t>
-  </si>
-  <si>
-    <t>22:03:59</t>
-  </si>
-  <si>
-    <t>23:41:23</t>
-  </si>
-  <si>
-    <t>01:17:56</t>
-  </si>
-  <si>
-    <t>19:46:07</t>
-  </si>
-  <si>
-    <t>21:23:57</t>
-  </si>
-  <si>
-    <t>23:01:24</t>
+    <t>23:05:40</t>
+  </si>
+  <si>
+    <t>00:43:15</t>
+  </si>
+  <si>
+    <t>02:20:18</t>
+  </si>
+  <si>
+    <t>22:25:54</t>
+  </si>
+  <si>
+    <t>00:03:31</t>
+  </si>
+  <si>
+    <t>01:40:41</t>
+  </si>
+  <si>
+    <t>21:46:02</t>
+  </si>
+  <si>
+    <t>23:23:42</t>
+  </si>
+  <si>
+    <t>01:00:57</t>
+  </si>
+  <si>
+    <t>21:06:04</t>
+  </si>
+  <si>
+    <t>22:43:47</t>
+  </si>
+  <si>
+    <t>00:21:07</t>
+  </si>
+  <si>
+    <t>01:57:27</t>
+  </si>
+  <si>
+    <t>20:26:00</t>
+  </si>
+  <si>
+    <t>22:03:46</t>
+  </si>
+  <si>
+    <t>23:41:10</t>
+  </si>
+  <si>
+    <t>01:17:43</t>
+  </si>
+  <si>
+    <t>19:45:50</t>
+  </si>
+  <si>
+    <t>21:23:40</t>
+  </si>
+  <si>
+    <t>23:01:07</t>
+  </si>
+  <si>
+    <t>00:37:52</t>
+  </si>
+  <si>
+    <t>19:05:33</t>
+  </si>
+  <si>
+    <t>20:43:29</t>
+  </si>
+  <si>
+    <t>22:20:59</t>
+  </si>
+  <si>
+    <t>23:57:52</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>11°</t>
-  </si>
-  <si>
     <t>3°</t>
   </si>
   <si>
     <t>-1°</t>
   </si>
   <si>
-    <t>03:36:13</t>
+    <t>6°</t>
   </si>
   <si>
     <t>02:58:48</t>
   </si>
   <si>
-    <t>19:36:22</t>
+    <t>19:36:06</t>
+  </si>
+  <si>
+    <t>18:58:29</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -707,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,7 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,43 +719,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,13 +737,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,7 +779,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -824,37 +827,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -976,9 +955,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1460,55 +1436,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4">
-        <v>-42.4</v>
+        <v>-37.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O2" s="6">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="7">
-        <v>2</v>
-      </c>
-      <c r="R2" s="8">
-        <v>53</v>
+      <c r="Q2" s="8">
+        <v>88</v>
+      </c>
+      <c r="R2" s="9">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1516,55 +1492,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="L3" s="4">
-        <v>-33.2</v>
+        <v>-25.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O3" s="9">
-        <v>10</v>
+        <v>213</v>
+      </c>
+      <c r="O3" s="6">
+        <v>54</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>2</v>
-      </c>
-      <c r="R3" s="10">
-        <v>51</v>
+      <c r="Q3" s="10">
+        <v>85</v>
+      </c>
+      <c r="R3" s="11">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1572,55 +1548,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-43.5</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="L4" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="N4" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="O4" s="6">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>3</v>
-      </c>
-      <c r="R4" s="12">
-        <v>96</v>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>14</v>
+      </c>
+      <c r="R4" s="13">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1628,55 +1604,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-41.5</v>
+        <v>-40.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O5" s="13">
-        <v>99</v>
+        <v>213</v>
+      </c>
+      <c r="O5" s="6">
+        <v>91</v>
       </c>
       <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>74</v>
-      </c>
-      <c r="R5" s="15">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>91</v>
+      </c>
+      <c r="R5" s="14">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1684,55 +1660,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-43.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O6" s="13">
+        <v>213</v>
+      </c>
+      <c r="O6" s="6">
+        <v>99</v>
+      </c>
+      <c r="P6" s="15">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="16">
         <v>96</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>93</v>
-      </c>
-      <c r="R6" s="12">
-        <v>96</v>
+      <c r="R6" s="17">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1740,55 +1716,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.3</v>
+        <v>-41.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O7" s="13">
-        <v>91</v>
+        <v>213</v>
+      </c>
+      <c r="O7" s="6">
+        <v>56</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="15">
-        <v>81</v>
-      </c>
-      <c r="R7" s="16">
-        <v>86</v>
+      <c r="Q7" s="18">
+        <v>22</v>
+      </c>
+      <c r="R7" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1796,55 +1772,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-42.3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L8" s="4">
-        <v>-25</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O8" s="13">
-        <v>100</v>
+      <c r="O8" s="6">
+        <v>59</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="17">
-        <v>91</v>
-      </c>
-      <c r="R8" s="18">
-        <v>100</v>
+      <c r="Q8" s="19">
+        <v>24</v>
+      </c>
+      <c r="R8" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1852,55 +1828,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-34.6</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O9" s="20">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-43.5</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O9" s="13">
-        <v>61</v>
-      </c>
       <c r="P9" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="19">
-        <v>61</v>
-      </c>
-      <c r="R9" s="20">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>7</v>
+      </c>
+      <c r="R9" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1908,55 +1884,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-40.4</v>
+        <v>-38.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O10" s="13">
-        <v>54</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>54</v>
-      </c>
-      <c r="R10" s="21">
-        <v>38</v>
+        <v>213</v>
+      </c>
+      <c r="O10" s="6">
+        <v>100</v>
+      </c>
+      <c r="P10" s="22">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>96</v>
+      </c>
+      <c r="R10" s="23">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1964,55 +1940,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-42.8</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O11" s="6">
+        <v>100</v>
+      </c>
+      <c r="P11" s="14">
         <v>54</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-30.2</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O11" s="6">
-        <v>41</v>
-      </c>
-      <c r="P11" s="7">
-        <v>1</v>
-      </c>
       <c r="Q11" s="22">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="R11" s="23">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2020,55 +1996,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L12" s="4">
-        <v>-41.8</v>
+        <v>-38.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O12" s="6">
-        <v>47</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="24">
-        <v>23</v>
-      </c>
-      <c r="R12" s="24">
-        <v>25</v>
+        <v>100</v>
+      </c>
+      <c r="P12" s="14">
+        <v>53</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>100</v>
+      </c>
+      <c r="R12" s="23">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2076,55 +2052,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-42.3</v>
+        <v>-34.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O13" s="13">
-        <v>66</v>
-      </c>
-      <c r="P13" s="25">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="26">
-        <v>66</v>
-      </c>
-      <c r="R13" s="22">
-        <v>35</v>
+        <v>213</v>
+      </c>
+      <c r="O13" s="6">
+        <v>57</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="14">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2132,55 +2108,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-34.6</v>
+        <v>-41.8</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O14" s="13">
-        <v>72</v>
-      </c>
-      <c r="P14" s="25">
-        <v>14</v>
-      </c>
-      <c r="Q14" s="27">
-        <v>68</v>
-      </c>
-      <c r="R14" s="28">
-        <v>30</v>
+        <v>213</v>
+      </c>
+      <c r="O14" s="6">
+        <v>67</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2188,55 +2164,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L15" s="4">
-        <v>-38.9</v>
+        <v>-40.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O15" s="9">
-        <v>5</v>
+        <v>213</v>
+      </c>
+      <c r="O15" s="6">
+        <v>65</v>
       </c>
       <c r="P15" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="7">
-        <v>2</v>
-      </c>
-      <c r="R15" s="7">
         <v>0</v>
+      </c>
+      <c r="R15" s="17">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2244,55 +2220,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-42.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" s="9">
-        <v>8</v>
-      </c>
-      <c r="P16" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>5</v>
-      </c>
-      <c r="R16" s="7">
+        <v>214</v>
+      </c>
+      <c r="O16" s="6">
+        <v>51</v>
+      </c>
+      <c r="P16" s="7">
         <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="24">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2300,55 +2276,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L17" s="4">
-        <v>-38.2</v>
+        <v>-29.8</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O17" s="6">
-        <v>28</v>
-      </c>
-      <c r="P17" s="28">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>27</v>
-      </c>
-      <c r="R17" s="7">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="P17" s="21">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>1</v>
+      </c>
+      <c r="R17" s="25">
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2356,55 +2332,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L18" s="4">
-        <v>-34.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O18" s="6">
-        <v>27</v>
-      </c>
-      <c r="P18" s="25">
-        <v>17</v>
+        <v>79</v>
+      </c>
+      <c r="P18" s="26">
+        <v>10</v>
       </c>
       <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="20">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="R18" s="25">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2412,55 +2388,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L19" s="4">
         <v>-41.8</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O19" s="6">
-        <v>39</v>
-      </c>
-      <c r="P19" s="25">
-        <v>16</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
-      </c>
-      <c r="R19" s="25">
-        <v>17</v>
+        <v>78</v>
+      </c>
+      <c r="P19" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>45</v>
+      </c>
+      <c r="R19" s="15">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2468,55 +2444,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L20" s="4">
-        <v>-40.6</v>
+        <v>-35.8</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O20" s="13">
-        <v>64</v>
-      </c>
-      <c r="P20" s="25">
-        <v>15</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="10">
-        <v>51</v>
+        <v>214</v>
+      </c>
+      <c r="O20" s="6">
+        <v>80</v>
+      </c>
+      <c r="P20" s="12">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>75</v>
+      </c>
+      <c r="R20" s="14">
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2524,55 +2500,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="L21" s="4">
-        <v>-31.8</v>
+        <v>-24.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O21" s="13">
-        <v>62</v>
-      </c>
-      <c r="P21" s="20">
-        <v>9</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>1</v>
-      </c>
-      <c r="R21" s="21">
-        <v>42</v>
+        <v>214</v>
+      </c>
+      <c r="O21" s="6">
+        <v>99</v>
+      </c>
+      <c r="P21" s="9">
+        <v>78</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>99</v>
+      </c>
+      <c r="R21" s="23">
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2580,55 +2556,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-29.9</v>
+        <v>-35.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O22" s="9">
-        <v>18</v>
-      </c>
-      <c r="P22" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="7">
-        <v>0</v>
+        <v>213</v>
+      </c>
+      <c r="O22" s="6">
+        <v>89</v>
+      </c>
+      <c r="P22" s="14">
+        <v>54</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>89</v>
+      </c>
+      <c r="R22" s="8">
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2639,52 +2615,52 @@
         <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L23" s="4">
-        <v>-39.4</v>
+        <v>-41.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O23" s="6">
-        <v>32</v>
-      </c>
-      <c r="P23" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="P23" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>79</v>
+      </c>
+      <c r="R23" s="22">
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2692,55 +2668,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L24" s="4">
-        <v>-41.8</v>
+        <v>-38.8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O24" s="6">
-        <v>21</v>
-      </c>
-      <c r="P24" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="11">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="P24" s="19">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>50</v>
+      </c>
+      <c r="R24" s="19">
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2748,55 +2724,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>208</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="L25" s="4">
-        <v>-35.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O25" s="6">
-        <v>30</v>
-      </c>
-      <c r="P25" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="28">
-        <v>30</v>
+        <v>95</v>
+      </c>
+      <c r="P25" s="13">
+        <v>49</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>83</v>
+      </c>
+      <c r="R25" s="21">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2804,55 +2780,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>214</v>
+        <v>94</v>
       </c>
       <c r="L26" s="4">
-        <v>-24.2</v>
+        <v>-31.3</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O26" s="13">
-        <v>58</v>
-      </c>
-      <c r="P26" s="25">
-        <v>17</v>
-      </c>
-      <c r="Q26" s="21">
-        <v>41</v>
-      </c>
-      <c r="R26" s="19">
-        <v>58</v>
+        <v>213</v>
+      </c>
+      <c r="O26" s="6">
+        <v>91</v>
+      </c>
+      <c r="P26" s="11">
+        <v>63</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>81</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2860,55 +2836,55 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L27" s="4">
+        <v>-39.7</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O27" s="6">
+        <v>89</v>
+      </c>
+      <c r="P27" s="9">
+        <v>80</v>
+      </c>
+      <c r="Q27" s="27">
         <v>71</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-35.9</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O27" s="13">
-        <v>66</v>
-      </c>
-      <c r="P27" s="11">
-        <v>7</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>49</v>
-      </c>
-      <c r="R27" s="28">
-        <v>32</v>
+      <c r="R27" s="12">
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2916,55 +2892,55 @@
         <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L28" s="4">
-        <v>-41.4</v>
+        <v>-40.5</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O28" s="13">
-        <v>50</v>
-      </c>
-      <c r="P28" s="20">
-        <v>9</v>
-      </c>
-      <c r="Q28" s="22">
-        <v>33</v>
-      </c>
-      <c r="R28" s="23">
-        <v>22</v>
+        <v>213</v>
+      </c>
+      <c r="O28" s="6">
+        <v>89</v>
+      </c>
+      <c r="P28" s="9">
+        <v>80</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>63</v>
+      </c>
+      <c r="R28" s="18">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260309--01</t>
-  </si>
-  <si>
-    <t>20260309--02</t>
-  </si>
-  <si>
-    <t>20260309--03</t>
-  </si>
-  <si>
     <t>20260310--01</t>
   </si>
   <si>
@@ -151,36 +142,39 @@
     <t>20260315--05</t>
   </si>
   <si>
+    <t>20260316--01</t>
+  </si>
+  <si>
+    <t>20260316--02</t>
+  </si>
+  <si>
+    <t>20260316--03</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
     <t>06:21</t>
   </si>
   <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
     <t>06:01</t>
   </si>
   <si>
@@ -223,18 +217,18 @@
     <t>04:50</t>
   </si>
   <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:11:59</t>
-  </si>
-  <si>
-    <t>02:49:44</t>
-  </si>
-  <si>
-    <t>22:55:02</t>
-  </si>
-  <si>
     <t>00:32:20</t>
   </si>
   <si>
@@ -307,13 +301,13 @@
     <t>23:47:48</t>
   </si>
   <si>
-    <t>01:14:15</t>
-  </si>
-  <si>
-    <t>02:52:22</t>
-  </si>
-  <si>
-    <t>22:57:24</t>
+    <t>19:52:35</t>
+  </si>
+  <si>
+    <t>21:29:49</t>
+  </si>
+  <si>
+    <t>23:07:28</t>
   </si>
   <si>
     <t>00:34:35</t>
@@ -388,13 +382,13 @@
     <t>23:50:25</t>
   </si>
   <si>
-    <t>01:17:25</t>
-  </si>
-  <si>
-    <t>02:54:46</t>
-  </si>
-  <si>
-    <t>23:00:20</t>
+    <t>19:54:57</t>
+  </si>
+  <si>
+    <t>21:32:05</t>
+  </si>
+  <si>
+    <t>23:09:59</t>
   </si>
   <si>
     <t>00:37:47</t>
@@ -469,13 +463,13 @@
     <t>23:52:50</t>
   </si>
   <si>
-    <t>01:20:36</t>
-  </si>
-  <si>
-    <t>02:57:10</t>
-  </si>
-  <si>
-    <t>23:03:17</t>
+    <t>19:57:53</t>
+  </si>
+  <si>
+    <t>21:35:17</t>
+  </si>
+  <si>
+    <t>23:12:37</t>
   </si>
   <si>
     <t>00:40:59</t>
@@ -550,13 +544,13 @@
     <t>23:55:15</t>
   </si>
   <si>
-    <t>01:22:52</t>
-  </si>
-  <si>
-    <t>02:59:48</t>
-  </si>
-  <si>
-    <t>23:05:40</t>
+    <t>20:00:49</t>
+  </si>
+  <si>
+    <t>21:38:28</t>
+  </si>
+  <si>
+    <t>23:15:15</t>
   </si>
   <si>
     <t>00:43:15</t>
@@ -631,25 +625,31 @@
     <t>23:57:52</t>
   </si>
   <si>
+    <t>20:03:11</t>
+  </si>
+  <si>
+    <t>21:40:44</t>
+  </si>
+  <si>
+    <t>23:17:46</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>3°</t>
-  </si>
-  <si>
     <t>-1°</t>
   </si>
   <si>
     <t>6°</t>
   </si>
   <si>
-    <t>02:58:48</t>
-  </si>
-  <si>
     <t>19:36:06</t>
   </si>
   <si>
     <t>18:58:29</t>
+  </si>
+  <si>
+    <t>19:54:05</t>
   </si>
   <si>
     <t>B</t>
@@ -692,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,7 +719,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +779,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,7 +797,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,85 +815,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -949,12 +937,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1436,37 +1418,37 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-37.3</v>
+        <v>-40.4</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>212</v>
@@ -1475,16 +1457,16 @@
         <v>213</v>
       </c>
       <c r="O2" s="6">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="8">
-        <v>88</v>
-      </c>
-      <c r="R2" s="9">
-        <v>81</v>
+        <v>72</v>
+      </c>
+      <c r="R2" s="8">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1492,37 +1474,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>206</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.1</v>
+        <v>-30.2</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>212</v>
@@ -1531,16 +1513,16 @@
         <v>213</v>
       </c>
       <c r="O3" s="6">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>85</v>
-      </c>
-      <c r="R3" s="11">
-        <v>64</v>
+        <v>1</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>100</v>
+      </c>
+      <c r="R3" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1548,37 +1530,37 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-43.5</v>
+        <v>-41.8</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>212</v>
@@ -1586,17 +1568,17 @@
       <c r="N4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O4" s="6">
-        <v>50</v>
+      <c r="O4" s="10">
+        <v>10</v>
       </c>
       <c r="P4" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>14</v>
-      </c>
-      <c r="R4" s="13">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>5</v>
+      </c>
+      <c r="R4" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1607,34 +1589,34 @@
         <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-40.4</v>
+        <v>-42.3</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>212</v>
@@ -1642,17 +1624,17 @@
       <c r="N5" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O5" s="6">
-        <v>91</v>
+      <c r="O5" s="10">
+        <v>6</v>
       </c>
       <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>91</v>
-      </c>
-      <c r="R5" s="14">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1660,37 +1642,37 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L6" s="4">
-        <v>-30.2</v>
+        <v>-34.6</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>212</v>
@@ -1698,17 +1680,17 @@
       <c r="N6" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O6" s="6">
-        <v>99</v>
-      </c>
-      <c r="P6" s="15">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>96</v>
-      </c>
-      <c r="R6" s="17">
-        <v>61</v>
+      <c r="O6" s="12">
+        <v>45</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>15</v>
+      </c>
+      <c r="R6" s="14">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1716,37 +1698,37 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L7" s="4">
-        <v>-41.8</v>
+        <v>-38.8</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>212</v>
@@ -1755,16 +1737,16 @@
         <v>213</v>
       </c>
       <c r="O7" s="6">
-        <v>56</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>22</v>
-      </c>
-      <c r="R7" s="14">
-        <v>55</v>
+        <v>99</v>
+      </c>
+      <c r="P7" s="15">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>87</v>
+      </c>
+      <c r="R7" s="9">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1775,34 +1757,34 @@
         <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-42.3</v>
+        <v>-42.8</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>212</v>
@@ -1811,16 +1793,16 @@
         <v>213</v>
       </c>
       <c r="O8" s="6">
-        <v>59</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>24</v>
-      </c>
-      <c r="R8" s="14">
-        <v>55</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="8">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>100</v>
+      </c>
+      <c r="R8" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1828,37 +1810,37 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L9" s="4">
-        <v>-34.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>212</v>
@@ -1866,17 +1848,17 @@
       <c r="N9" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O9" s="20">
-        <v>25</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>7</v>
-      </c>
-      <c r="R9" s="19">
-        <v>25</v>
+      <c r="O9" s="6">
+        <v>100</v>
+      </c>
+      <c r="P9" s="17">
+        <v>78</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>100</v>
+      </c>
+      <c r="R9" s="18">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1884,37 +1866,37 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" s="4">
-        <v>-38.8</v>
+        <v>-34.8</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>212</v>
@@ -1922,17 +1904,17 @@
       <c r="N10" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O10" s="6">
-        <v>100</v>
-      </c>
-      <c r="P10" s="22">
-        <v>73</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>96</v>
-      </c>
-      <c r="R10" s="23">
-        <v>100</v>
+      <c r="O10" s="10">
+        <v>2</v>
+      </c>
+      <c r="P10" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1943,34 +1925,34 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L11" s="4">
-        <v>-42.8</v>
+        <v>-41.8</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>212</v>
@@ -1978,17 +1960,17 @@
       <c r="N11" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O11" s="6">
-        <v>100</v>
-      </c>
-      <c r="P11" s="14">
-        <v>54</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>75</v>
-      </c>
-      <c r="R11" s="23">
-        <v>100</v>
+      <c r="O11" s="10">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1996,37 +1978,37 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-38.2</v>
+        <v>-40.6</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>212</v>
@@ -2034,17 +2016,17 @@
       <c r="N12" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O12" s="6">
-        <v>100</v>
-      </c>
-      <c r="P12" s="14">
-        <v>53</v>
-      </c>
-      <c r="Q12" s="23">
-        <v>100</v>
-      </c>
-      <c r="R12" s="23">
-        <v>100</v>
+      <c r="O12" s="10">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2052,46 +2034,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L13" s="4">
-        <v>-34.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O13" s="6">
-        <v>57</v>
+        <v>214</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
@@ -2099,8 +2081,8 @@
       <c r="Q13" s="7">
         <v>0</v>
       </c>
-      <c r="R13" s="14">
-        <v>57</v>
+      <c r="R13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2108,37 +2090,37 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L14" s="4">
-        <v>-41.8</v>
+        <v>-29.8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>212</v>
@@ -2147,16 +2129,16 @@
         <v>213</v>
       </c>
       <c r="O14" s="6">
-        <v>67</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="P14" s="15">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="19">
+        <v>42</v>
+      </c>
+      <c r="R14" s="13">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2164,37 +2146,37 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L15" s="4">
-        <v>-40.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>212</v>
@@ -2203,16 +2185,16 @@
         <v>213</v>
       </c>
       <c r="O15" s="6">
-        <v>65</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>59</v>
+        <v>96</v>
+      </c>
+      <c r="P15" s="13">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>63</v>
+      </c>
+      <c r="R15" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2220,55 +2202,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>-31.8</v>
+        <v>-41.8</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O16" s="6">
-        <v>51</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="24">
-        <v>39</v>
+        <v>99</v>
+      </c>
+      <c r="P16" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>86</v>
+      </c>
+      <c r="R16" s="20">
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2276,55 +2258,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17" s="4">
-        <v>-29.8</v>
+        <v>-35.8</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O17" s="6">
-        <v>70</v>
-      </c>
-      <c r="P17" s="21">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>1</v>
-      </c>
-      <c r="R17" s="25">
-        <v>35</v>
+        <v>100</v>
+      </c>
+      <c r="P17" s="14">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>98</v>
+      </c>
+      <c r="R17" s="20">
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2332,55 +2314,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="L18" s="4">
-        <v>-39.4</v>
+        <v>-24.1</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O18" s="6">
-        <v>79</v>
-      </c>
-      <c r="P18" s="26">
-        <v>10</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>1</v>
-      </c>
-      <c r="R18" s="25">
-        <v>35</v>
+        <v>98</v>
+      </c>
+      <c r="P18" s="20">
+        <v>63</v>
+      </c>
+      <c r="Q18" s="21">
+        <v>57</v>
+      </c>
+      <c r="R18" s="20">
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2388,37 +2370,37 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L19" s="4">
-        <v>-41.8</v>
+        <v>-35.8</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>212</v>
@@ -2427,16 +2409,16 @@
         <v>213</v>
       </c>
       <c r="O19" s="6">
-        <v>78</v>
-      </c>
-      <c r="P19" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="15">
-        <v>45</v>
-      </c>
-      <c r="R19" s="15">
-        <v>44</v>
+        <v>100</v>
+      </c>
+      <c r="P19" s="8">
+        <v>69</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>73</v>
+      </c>
+      <c r="R19" s="16">
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2444,55 +2426,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L20" s="4">
-        <v>-35.8</v>
+        <v>-41.4</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O20" s="6">
-        <v>80</v>
-      </c>
-      <c r="P20" s="12">
-        <v>14</v>
+        <v>92</v>
+      </c>
+      <c r="P20" s="20">
+        <v>63</v>
       </c>
       <c r="Q20" s="22">
-        <v>75</v>
-      </c>
-      <c r="R20" s="14">
-        <v>53</v>
+        <v>73</v>
+      </c>
+      <c r="R20" s="8">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2500,55 +2482,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="L21" s="4">
-        <v>-24.1</v>
+        <v>-38.8</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O21" s="6">
-        <v>99</v>
-      </c>
-      <c r="P21" s="9">
-        <v>78</v>
-      </c>
-      <c r="Q21" s="23">
-        <v>99</v>
+        <v>77</v>
+      </c>
+      <c r="P21" s="23">
+        <v>51</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>70</v>
       </c>
       <c r="R21" s="23">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2556,55 +2538,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="L22" s="4">
-        <v>-35.8</v>
+        <v>-18.1</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O22" s="6">
-        <v>89</v>
-      </c>
-      <c r="P22" s="14">
-        <v>54</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>89</v>
-      </c>
-      <c r="R22" s="8">
-        <v>89</v>
+        <v>97</v>
+      </c>
+      <c r="P22" s="22">
+        <v>77</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>87</v>
+      </c>
+      <c r="R22" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2612,37 +2594,37 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L23" s="4">
-        <v>-41.4</v>
+        <v>-31.3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>212</v>
@@ -2651,16 +2633,16 @@
         <v>213</v>
       </c>
       <c r="O23" s="6">
-        <v>79</v>
-      </c>
-      <c r="P23" s="15">
-        <v>45</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>79</v>
-      </c>
-      <c r="R23" s="22">
-        <v>77</v>
+        <v>90</v>
+      </c>
+      <c r="P23" s="21">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>83</v>
+      </c>
+      <c r="R23" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2668,37 +2650,37 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L24" s="4">
-        <v>-38.8</v>
+        <v>-39.7</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>212</v>
@@ -2707,16 +2689,16 @@
         <v>213</v>
       </c>
       <c r="O24" s="6">
-        <v>50</v>
-      </c>
-      <c r="P24" s="19">
-        <v>23</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>50</v>
-      </c>
-      <c r="R24" s="19">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="P24" s="24">
+        <v>36</v>
+      </c>
+      <c r="Q24" s="22">
+        <v>76</v>
+      </c>
+      <c r="R24" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2724,55 +2706,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="L25" s="4">
-        <v>-18.1</v>
+        <v>-40.5</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>212</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O25" s="6">
-        <v>95</v>
-      </c>
-      <c r="P25" s="13">
-        <v>49</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>83</v>
-      </c>
-      <c r="R25" s="21">
-        <v>3</v>
+        <v>68</v>
+      </c>
+      <c r="P25" s="24">
+        <v>35</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>68</v>
+      </c>
+      <c r="R25" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2780,37 +2762,37 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="L26" s="4">
-        <v>-31.3</v>
+        <v>-25.8</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>212</v>
@@ -2819,16 +2801,16 @@
         <v>213</v>
       </c>
       <c r="O26" s="6">
-        <v>91</v>
-      </c>
-      <c r="P26" s="11">
+        <v>73</v>
+      </c>
+      <c r="P26" s="13">
+        <v>16</v>
+      </c>
+      <c r="Q26" s="20">
         <v>63</v>
       </c>
-      <c r="Q26" s="9">
-        <v>81</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
+      <c r="R26" s="22">
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2836,37 +2818,37 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L27" s="4">
-        <v>-39.7</v>
+        <v>-36.6</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>212</v>
@@ -2875,16 +2857,16 @@
         <v>213</v>
       </c>
       <c r="O27" s="6">
-        <v>89</v>
-      </c>
-      <c r="P27" s="9">
-        <v>80</v>
-      </c>
-      <c r="Q27" s="27">
-        <v>71</v>
-      </c>
-      <c r="R27" s="12">
-        <v>17</v>
+        <v>96</v>
+      </c>
+      <c r="P27" s="14">
+        <v>45</v>
+      </c>
+      <c r="Q27" s="18">
+        <v>60</v>
+      </c>
+      <c r="R27" s="25">
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2892,37 +2874,37 @@
         <v>44</v>
       </c>
       <c r="B28" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L28" s="4">
-        <v>-40.5</v>
+        <v>-40.8</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>212</v>
@@ -2931,16 +2913,16 @@
         <v>213</v>
       </c>
       <c r="O28" s="6">
-        <v>89</v>
-      </c>
-      <c r="P28" s="9">
-        <v>80</v>
-      </c>
-      <c r="Q28" s="11">
+        <v>98</v>
+      </c>
+      <c r="P28" s="19">
+        <v>40</v>
+      </c>
+      <c r="Q28" s="20">
         <v>63</v>
       </c>
-      <c r="R28" s="18">
-        <v>18</v>
+      <c r="R28" s="14">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="214">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260310--01</t>
-  </si>
-  <si>
-    <t>20260310--02</t>
-  </si>
-  <si>
-    <t>20260310--03</t>
-  </si>
-  <si>
-    <t>20260310--04</t>
-  </si>
-  <si>
     <t>20260311--01</t>
   </si>
   <si>
@@ -151,21 +139,24 @@
     <t>20260316--03</t>
   </si>
   <si>
+    <t>20260317--01</t>
+  </si>
+  <si>
+    <t>20260317--02</t>
+  </si>
+  <si>
+    <t>20260317--03</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
     <t>05:49</t>
   </si>
   <si>
@@ -178,22 +169,22 @@
     <t>06:01</t>
   </si>
   <si>
-    <t>01:57</t>
-  </si>
-  <si>
-    <t>04:22</t>
+    <t>01:56</t>
+  </si>
+  <si>
+    <t>04:23</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>06:10</t>
+    <t>06:09</t>
   </si>
   <si>
     <t>03:23</t>
   </si>
   <si>
-    <t>03:35</t>
+    <t>03:36</t>
   </si>
   <si>
     <t>06:11</t>
@@ -202,22 +193,22 @@
     <t>06:16</t>
   </si>
   <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>02:18</t>
-  </si>
-  <si>
-    <t>06:02</t>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>06:03</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>05:52</t>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>05:51</t>
   </si>
   <si>
     <t>06:23</t>
@@ -226,412 +217,406 @@
     <t>05:16</t>
   </si>
   <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:32:20</t>
-  </si>
-  <si>
-    <t>02:10:01</t>
-  </si>
-  <si>
-    <t>22:15:24</t>
-  </si>
-  <si>
-    <t>23:52:36</t>
-  </si>
-  <si>
-    <t>01:30:14</t>
-  </si>
-  <si>
-    <t>21:35:42</t>
-  </si>
-  <si>
-    <t>23:12:47</t>
-  </si>
-  <si>
-    <t>00:50:22</t>
-  </si>
-  <si>
-    <t>20:55:57</t>
-  </si>
-  <si>
-    <t>22:32:53</t>
-  </si>
-  <si>
-    <t>00:10:25</t>
-  </si>
-  <si>
-    <t>01:48:23</t>
-  </si>
-  <si>
-    <t>20:16:08</t>
-  </si>
-  <si>
-    <t>21:52:55</t>
-  </si>
-  <si>
-    <t>23:30:23</t>
-  </si>
-  <si>
-    <t>01:08:15</t>
-  </si>
-  <si>
-    <t>19:36:17</t>
-  </si>
-  <si>
-    <t>21:12:53</t>
-  </si>
-  <si>
-    <t>22:50:17</t>
-  </si>
-  <si>
-    <t>00:28:03</t>
-  </si>
-  <si>
-    <t>18:56:24</t>
-  </si>
-  <si>
-    <t>20:32:46</t>
-  </si>
-  <si>
-    <t>22:10:06</t>
-  </si>
-  <si>
-    <t>23:47:48</t>
-  </si>
-  <si>
-    <t>19:52:35</t>
-  </si>
-  <si>
-    <t>21:29:49</t>
-  </si>
-  <si>
-    <t>23:07:28</t>
-  </si>
-  <si>
-    <t>00:34:35</t>
-  </si>
-  <si>
-    <t>02:12:32</t>
-  </si>
-  <si>
-    <t>22:17:49</t>
-  </si>
-  <si>
-    <t>23:54:51</t>
-  </si>
-  <si>
-    <t>01:32:40</t>
-  </si>
-  <si>
-    <t>21:38:12</t>
-  </si>
-  <si>
-    <t>23:15:02</t>
-  </si>
-  <si>
-    <t>00:52:45</t>
-  </si>
-  <si>
-    <t>20:58:32</t>
-  </si>
-  <si>
-    <t>22:35:09</t>
-  </si>
-  <si>
-    <t>00:12:45</t>
-  </si>
-  <si>
-    <t>01:51:57</t>
-  </si>
-  <si>
-    <t>20:18:53</t>
-  </si>
-  <si>
-    <t>21:55:12</t>
-  </si>
-  <si>
-    <t>23:32:42</t>
-  </si>
-  <si>
-    <t>01:11:18</t>
-  </si>
-  <si>
-    <t>19:39:16</t>
-  </si>
-  <si>
-    <t>21:15:11</t>
-  </si>
-  <si>
-    <t>22:52:34</t>
-  </si>
-  <si>
-    <t>00:30:51</t>
-  </si>
-  <si>
-    <t>18:59:49</t>
-  </si>
-  <si>
-    <t>20:35:06</t>
-  </si>
-  <si>
-    <t>22:12:22</t>
-  </si>
-  <si>
-    <t>23:50:25</t>
-  </si>
-  <si>
-    <t>19:54:57</t>
-  </si>
-  <si>
-    <t>21:32:05</t>
-  </si>
-  <si>
-    <t>23:09:59</t>
-  </si>
-  <si>
-    <t>00:37:47</t>
-  </si>
-  <si>
-    <t>02:15:09</t>
-  </si>
-  <si>
-    <t>22:20:38</t>
-  </si>
-  <si>
-    <t>23:58:03</t>
-  </si>
-  <si>
-    <t>01:35:27</t>
-  </si>
-  <si>
-    <t>21:40:51</t>
-  </si>
-  <si>
-    <t>23:18:14</t>
-  </si>
-  <si>
-    <t>00:55:39</t>
-  </si>
-  <si>
-    <t>21:01:00</t>
-  </si>
-  <si>
-    <t>22:38:20</t>
-  </si>
-  <si>
-    <t>00:15:46</t>
-  </si>
-  <si>
-    <t>01:52:55</t>
-  </si>
-  <si>
-    <t>20:21:04</t>
-  </si>
-  <si>
-    <t>21:58:20</t>
-  </si>
-  <si>
-    <t>23:35:47</t>
-  </si>
-  <si>
-    <t>01:12:59</t>
-  </si>
-  <si>
-    <t>19:41:03</t>
-  </si>
-  <si>
-    <t>21:18:16</t>
-  </si>
-  <si>
-    <t>22:55:42</t>
-  </si>
-  <si>
-    <t>00:32:58</t>
-  </si>
-  <si>
-    <t>19:00:58</t>
-  </si>
-  <si>
-    <t>20:38:07</t>
-  </si>
-  <si>
-    <t>22:15:32</t>
-  </si>
-  <si>
-    <t>23:52:50</t>
-  </si>
-  <si>
-    <t>19:57:53</t>
-  </si>
-  <si>
-    <t>21:35:17</t>
-  </si>
-  <si>
-    <t>23:12:37</t>
-  </si>
-  <si>
-    <t>00:40:59</t>
-  </si>
-  <si>
-    <t>02:17:46</t>
-  </si>
-  <si>
-    <t>22:23:28</t>
-  </si>
-  <si>
-    <t>00:01:15</t>
-  </si>
-  <si>
-    <t>01:38:14</t>
-  </si>
-  <si>
-    <t>21:43:32</t>
-  </si>
-  <si>
-    <t>23:21:26</t>
-  </si>
-  <si>
-    <t>00:58:34</t>
-  </si>
-  <si>
-    <t>21:03:28</t>
-  </si>
-  <si>
-    <t>22:41:30</t>
-  </si>
-  <si>
-    <t>00:18:46</t>
-  </si>
-  <si>
-    <t>01:53:54</t>
-  </si>
-  <si>
-    <t>20:23:15</t>
-  </si>
-  <si>
-    <t>22:01:29</t>
-  </si>
-  <si>
-    <t>23:38:52</t>
-  </si>
-  <si>
-    <t>01:14:41</t>
-  </si>
-  <si>
-    <t>19:42:51</t>
-  </si>
-  <si>
-    <t>21:21:22</t>
-  </si>
-  <si>
-    <t>22:58:50</t>
-  </si>
-  <si>
-    <t>00:35:05</t>
-  </si>
-  <si>
-    <t>19:02:07</t>
-  </si>
-  <si>
-    <t>20:41:08</t>
-  </si>
-  <si>
-    <t>22:18:42</t>
-  </si>
-  <si>
-    <t>23:55:15</t>
-  </si>
-  <si>
-    <t>20:00:49</t>
-  </si>
-  <si>
-    <t>21:38:28</t>
-  </si>
-  <si>
-    <t>23:15:15</t>
-  </si>
-  <si>
-    <t>00:43:15</t>
-  </si>
-  <si>
-    <t>02:20:18</t>
-  </si>
-  <si>
-    <t>22:25:54</t>
-  </si>
-  <si>
-    <t>00:03:31</t>
-  </si>
-  <si>
-    <t>01:40:41</t>
-  </si>
-  <si>
-    <t>21:46:02</t>
-  </si>
-  <si>
-    <t>23:23:42</t>
-  </si>
-  <si>
-    <t>01:00:57</t>
-  </si>
-  <si>
-    <t>21:06:04</t>
-  </si>
-  <si>
-    <t>22:43:47</t>
-  </si>
-  <si>
-    <t>00:21:07</t>
-  </si>
-  <si>
-    <t>01:57:27</t>
-  </si>
-  <si>
-    <t>20:26:00</t>
-  </si>
-  <si>
-    <t>22:03:46</t>
-  </si>
-  <si>
-    <t>23:41:10</t>
-  </si>
-  <si>
-    <t>01:17:43</t>
-  </si>
-  <si>
-    <t>19:45:50</t>
-  </si>
-  <si>
-    <t>21:23:40</t>
-  </si>
-  <si>
-    <t>23:01:07</t>
-  </si>
-  <si>
-    <t>00:37:52</t>
-  </si>
-  <si>
-    <t>19:05:33</t>
-  </si>
-  <si>
-    <t>20:43:29</t>
-  </si>
-  <si>
-    <t>22:20:59</t>
-  </si>
-  <si>
-    <t>23:57:52</t>
-  </si>
-  <si>
-    <t>20:03:11</t>
-  </si>
-  <si>
-    <t>21:40:44</t>
-  </si>
-  <si>
-    <t>23:17:46</t>
+    <t>01:13</t>
+  </si>
+  <si>
+    <t>01:30:16</t>
+  </si>
+  <si>
+    <t>21:35:47</t>
+  </si>
+  <si>
+    <t>23:12:51</t>
+  </si>
+  <si>
+    <t>00:50:26</t>
+  </si>
+  <si>
+    <t>20:56:04</t>
+  </si>
+  <si>
+    <t>22:33:01</t>
+  </si>
+  <si>
+    <t>00:10:32</t>
+  </si>
+  <si>
+    <t>01:48:31</t>
+  </si>
+  <si>
+    <t>20:16:19</t>
+  </si>
+  <si>
+    <t>21:53:06</t>
+  </si>
+  <si>
+    <t>23:30:34</t>
+  </si>
+  <si>
+    <t>01:08:26</t>
+  </si>
+  <si>
+    <t>19:36:31</t>
+  </si>
+  <si>
+    <t>21:13:07</t>
+  </si>
+  <si>
+    <t>22:50:31</t>
+  </si>
+  <si>
+    <t>00:28:18</t>
+  </si>
+  <si>
+    <t>18:56:42</t>
+  </si>
+  <si>
+    <t>20:33:05</t>
+  </si>
+  <si>
+    <t>22:10:25</t>
+  </si>
+  <si>
+    <t>23:48:07</t>
+  </si>
+  <si>
+    <t>19:52:59</t>
+  </si>
+  <si>
+    <t>21:30:13</t>
+  </si>
+  <si>
+    <t>23:07:52</t>
+  </si>
+  <si>
+    <t>19:12:50</t>
+  </si>
+  <si>
+    <t>20:49:58</t>
+  </si>
+  <si>
+    <t>22:27:34</t>
+  </si>
+  <si>
+    <t>01:32:43</t>
+  </si>
+  <si>
+    <t>21:38:16</t>
+  </si>
+  <si>
+    <t>23:15:07</t>
+  </si>
+  <si>
+    <t>00:52:50</t>
+  </si>
+  <si>
+    <t>20:58:39</t>
+  </si>
+  <si>
+    <t>22:35:17</t>
+  </si>
+  <si>
+    <t>00:12:53</t>
+  </si>
+  <si>
+    <t>01:52:05</t>
+  </si>
+  <si>
+    <t>20:19:03</t>
+  </si>
+  <si>
+    <t>21:55:23</t>
+  </si>
+  <si>
+    <t>23:32:53</t>
+  </si>
+  <si>
+    <t>01:11:29</t>
+  </si>
+  <si>
+    <t>19:39:29</t>
+  </si>
+  <si>
+    <t>21:15:25</t>
+  </si>
+  <si>
+    <t>22:52:49</t>
+  </si>
+  <si>
+    <t>00:31:06</t>
+  </si>
+  <si>
+    <t>19:00:06</t>
+  </si>
+  <si>
+    <t>20:35:24</t>
+  </si>
+  <si>
+    <t>22:12:41</t>
+  </si>
+  <si>
+    <t>23:50:45</t>
+  </si>
+  <si>
+    <t>19:55:21</t>
+  </si>
+  <si>
+    <t>21:32:29</t>
+  </si>
+  <si>
+    <t>23:10:23</t>
+  </si>
+  <si>
+    <t>19:15:15</t>
+  </si>
+  <si>
+    <t>20:52:14</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>01:35:30</t>
+  </si>
+  <si>
+    <t>21:40:56</t>
+  </si>
+  <si>
+    <t>23:18:19</t>
+  </si>
+  <si>
+    <t>00:55:44</t>
+  </si>
+  <si>
+    <t>21:01:07</t>
+  </si>
+  <si>
+    <t>22:38:27</t>
+  </si>
+  <si>
+    <t>00:15:53</t>
+  </si>
+  <si>
+    <t>01:53:03</t>
+  </si>
+  <si>
+    <t>20:21:14</t>
+  </si>
+  <si>
+    <t>21:58:31</t>
+  </si>
+  <si>
+    <t>23:35:58</t>
+  </si>
+  <si>
+    <t>01:13:11</t>
+  </si>
+  <si>
+    <t>19:41:17</t>
+  </si>
+  <si>
+    <t>21:18:31</t>
+  </si>
+  <si>
+    <t>22:55:57</t>
+  </si>
+  <si>
+    <t>00:33:13</t>
+  </si>
+  <si>
+    <t>19:01:16</t>
+  </si>
+  <si>
+    <t>20:38:26</t>
+  </si>
+  <si>
+    <t>22:15:51</t>
+  </si>
+  <si>
+    <t>23:53:10</t>
+  </si>
+  <si>
+    <t>19:58:17</t>
+  </si>
+  <si>
+    <t>21:35:41</t>
+  </si>
+  <si>
+    <t>23:13:01</t>
+  </si>
+  <si>
+    <t>19:18:03</t>
+  </si>
+  <si>
+    <t>20:55:26</t>
+  </si>
+  <si>
+    <t>22:32:48</t>
+  </si>
+  <si>
+    <t>01:38:17</t>
+  </si>
+  <si>
+    <t>21:43:37</t>
+  </si>
+  <si>
+    <t>23:21:31</t>
+  </si>
+  <si>
+    <t>00:58:39</t>
+  </si>
+  <si>
+    <t>21:03:35</t>
+  </si>
+  <si>
+    <t>22:41:38</t>
+  </si>
+  <si>
+    <t>00:18:54</t>
+  </si>
+  <si>
+    <t>01:54:01</t>
+  </si>
+  <si>
+    <t>20:23:26</t>
+  </si>
+  <si>
+    <t>22:01:40</t>
+  </si>
+  <si>
+    <t>23:39:02</t>
+  </si>
+  <si>
+    <t>01:14:52</t>
+  </si>
+  <si>
+    <t>19:43:05</t>
+  </si>
+  <si>
+    <t>21:21:36</t>
+  </si>
+  <si>
+    <t>22:59:05</t>
+  </si>
+  <si>
+    <t>00:35:19</t>
+  </si>
+  <si>
+    <t>19:02:27</t>
+  </si>
+  <si>
+    <t>20:41:27</t>
+  </si>
+  <si>
+    <t>22:19:01</t>
+  </si>
+  <si>
+    <t>23:55:34</t>
+  </si>
+  <si>
+    <t>20:01:12</t>
+  </si>
+  <si>
+    <t>21:38:52</t>
+  </si>
+  <si>
+    <t>23:15:39</t>
+  </si>
+  <si>
+    <t>19:20:52</t>
+  </si>
+  <si>
+    <t>20:58:38</t>
+  </si>
+  <si>
+    <t>22:35:36</t>
+  </si>
+  <si>
+    <t>01:40:43</t>
+  </si>
+  <si>
+    <t>21:46:07</t>
+  </si>
+  <si>
+    <t>23:23:46</t>
+  </si>
+  <si>
+    <t>01:01:02</t>
+  </si>
+  <si>
+    <t>21:06:11</t>
+  </si>
+  <si>
+    <t>22:43:54</t>
+  </si>
+  <si>
+    <t>00:21:14</t>
+  </si>
+  <si>
+    <t>01:57:34</t>
+  </si>
+  <si>
+    <t>20:26:11</t>
+  </si>
+  <si>
+    <t>22:03:57</t>
+  </si>
+  <si>
+    <t>23:41:21</t>
+  </si>
+  <si>
+    <t>01:17:54</t>
+  </si>
+  <si>
+    <t>19:46:04</t>
+  </si>
+  <si>
+    <t>21:23:55</t>
+  </si>
+  <si>
+    <t>23:01:22</t>
+  </si>
+  <si>
+    <t>00:38:06</t>
+  </si>
+  <si>
+    <t>19:05:51</t>
+  </si>
+  <si>
+    <t>20:43:47</t>
+  </si>
+  <si>
+    <t>22:21:18</t>
+  </si>
+  <si>
+    <t>23:58:11</t>
+  </si>
+  <si>
+    <t>20:03:35</t>
+  </si>
+  <si>
+    <t>21:41:08</t>
+  </si>
+  <si>
+    <t>23:18:10</t>
+  </si>
+  <si>
+    <t>19:23:18</t>
+  </si>
+  <si>
+    <t>21:00:53</t>
+  </si>
+  <si>
+    <t>22:38:02</t>
   </si>
   <si>
     <t>0°</t>
@@ -643,22 +628,34 @@
     <t>6°</t>
   </si>
   <si>
-    <t>19:36:06</t>
-  </si>
-  <si>
-    <t>18:58:29</t>
-  </si>
-  <si>
-    <t>19:54:05</t>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>19:36:20</t>
+  </si>
+  <si>
+    <t>18:58:46</t>
+  </si>
+  <si>
+    <t>19:54:28</t>
+  </si>
+  <si>
+    <t>19:16:28</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -692,7 +689,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -707,13 +704,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,12 +776,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -749,7 +788,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -761,7 +800,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,55 +812,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -937,6 +946,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1340,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1418,55 +1433,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-40.4</v>
+        <v>-34.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O2" s="6">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1477,52 +1492,52 @@
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L3" s="4">
-        <v>-30.2</v>
+        <v>-38.9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O3" s="6">
-        <v>84</v>
-      </c>
-      <c r="P3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>100</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
+        <v>211</v>
+      </c>
+      <c r="O3" s="9">
+        <v>88</v>
+      </c>
+      <c r="P3" s="10">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>77</v>
+      </c>
+      <c r="R3" s="12">
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1530,55 +1545,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-41.8</v>
+        <v>-42.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O4" s="10">
-        <v>10</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>5</v>
-      </c>
-      <c r="R4" s="11">
-        <v>3</v>
+        <v>211</v>
+      </c>
+      <c r="O4" s="9">
+        <v>99</v>
+      </c>
+      <c r="P4" s="13">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>95</v>
+      </c>
+      <c r="R4" s="15">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1586,55 +1601,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-42.3</v>
+        <v>-38.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O5" s="10">
-        <v>6</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>3</v>
+        <v>211</v>
+      </c>
+      <c r="O5" s="9">
+        <v>100</v>
+      </c>
+      <c r="P5" s="16">
+        <v>70</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>100</v>
+      </c>
+      <c r="R5" s="15">
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1642,55 +1657,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L6" s="4">
-        <v>-34.6</v>
+        <v>-34.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O6" s="12">
-        <v>45</v>
+        <v>211</v>
+      </c>
+      <c r="O6" s="6">
+        <v>3</v>
       </c>
       <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
-        <v>15</v>
-      </c>
-      <c r="R6" s="14">
-        <v>45</v>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1698,55 +1713,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>76</v>
       </c>
       <c r="L7" s="4">
-        <v>-38.8</v>
+        <v>-41.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O7" s="6">
-        <v>99</v>
-      </c>
-      <c r="P7" s="15">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>87</v>
-      </c>
-      <c r="R7" s="9">
-        <v>98</v>
+        <v>8</v>
+      </c>
+      <c r="P7" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1754,55 +1769,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-42.8</v>
+        <v>-40.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="8">
-        <v>68</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>100</v>
-      </c>
-      <c r="R8" s="9">
-        <v>100</v>
+        <v>211</v>
+      </c>
+      <c r="O8" s="19">
+        <v>14</v>
+      </c>
+      <c r="P8" s="18">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1810,55 +1825,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L9" s="4">
-        <v>-38.2</v>
+        <v>-31.8</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="O9" s="6">
-        <v>100</v>
-      </c>
-      <c r="P9" s="17">
-        <v>78</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>100</v>
-      </c>
-      <c r="R9" s="18">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="P9" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1866,55 +1881,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>79</v>
       </c>
       <c r="L10" s="4">
-        <v>-34.8</v>
+        <v>-29.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O10" s="10">
-        <v>2</v>
+        <v>211</v>
+      </c>
+      <c r="O10" s="9">
+        <v>96</v>
       </c>
       <c r="P10" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="7">
-        <v>2</v>
+      <c r="Q10" s="10">
+        <v>22</v>
+      </c>
+      <c r="R10" s="15">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1922,55 +1937,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L11" s="4">
-        <v>-41.8</v>
+        <v>-39.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="O11" s="9">
+        <v>100</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
       </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
+      <c r="Q11" s="20">
+        <v>40</v>
+      </c>
+      <c r="R11" s="11">
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1978,55 +1993,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-40.6</v>
+        <v>-41.8</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O12" s="10">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="O12" s="9">
+        <v>100</v>
+      </c>
+      <c r="P12" s="8">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="21">
+        <v>43</v>
+      </c>
+      <c r="R12" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2034,55 +2049,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L13" s="4">
-        <v>-31.8</v>
+        <v>-35.8</v>
       </c>
       <c r="M13" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
-        <v>0</v>
+      <c r="O13" s="9">
+        <v>100</v>
+      </c>
+      <c r="P13" s="18">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>41</v>
+      </c>
+      <c r="R13" s="13">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2090,55 +2105,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="L14" s="4">
-        <v>-29.8</v>
+        <v>-24.2</v>
       </c>
       <c r="M14" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O14" s="6">
-        <v>82</v>
-      </c>
-      <c r="P14" s="15">
-        <v>9</v>
-      </c>
-      <c r="Q14" s="19">
-        <v>42</v>
-      </c>
-      <c r="R14" s="13">
-        <v>14</v>
+      <c r="O14" s="9">
+        <v>100</v>
+      </c>
+      <c r="P14" s="22">
+        <v>64</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>72</v>
+      </c>
+      <c r="R14" s="15">
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2146,55 +2161,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L15" s="4">
-        <v>-39.4</v>
+        <v>-35.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O15" s="6">
-        <v>96</v>
-      </c>
-      <c r="P15" s="13">
-        <v>14</v>
-      </c>
-      <c r="Q15" s="20">
-        <v>63</v>
-      </c>
-      <c r="R15" s="11">
-        <v>5</v>
+        <v>211</v>
+      </c>
+      <c r="O15" s="9">
+        <v>100</v>
+      </c>
+      <c r="P15" s="23">
+        <v>86</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>72</v>
+      </c>
+      <c r="R15" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2202,55 +2217,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>-41.8</v>
+        <v>-41.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O16" s="6">
-        <v>99</v>
-      </c>
-      <c r="P16" s="11">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>86</v>
-      </c>
-      <c r="R16" s="20">
-        <v>67</v>
+        <v>211</v>
+      </c>
+      <c r="O16" s="9">
+        <v>100</v>
+      </c>
+      <c r="P16" s="12">
+        <v>79</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>75</v>
+      </c>
+      <c r="R16" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2258,55 +2273,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L17" s="4">
-        <v>-35.8</v>
+        <v>-38.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O17" s="6">
+        <v>211</v>
+      </c>
+      <c r="O17" s="9">
         <v>100</v>
       </c>
-      <c r="P17" s="14">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>98</v>
-      </c>
-      <c r="R17" s="20">
-        <v>67</v>
+      <c r="P17" s="11">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>72</v>
+      </c>
+      <c r="R17" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2314,55 +2329,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-18.2</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="L18" s="4">
-        <v>-24.1</v>
-      </c>
-      <c r="M18" s="3" t="s">
+      <c r="N18" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O18" s="6">
-        <v>98</v>
-      </c>
-      <c r="P18" s="20">
-        <v>63</v>
-      </c>
-      <c r="Q18" s="21">
-        <v>57</v>
-      </c>
-      <c r="R18" s="20">
-        <v>65</v>
+      <c r="O18" s="9">
+        <v>100</v>
+      </c>
+      <c r="P18" s="15">
+        <v>89</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>81</v>
+      </c>
+      <c r="R18" s="11">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2370,55 +2385,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>88</v>
       </c>
       <c r="L19" s="4">
-        <v>-35.8</v>
+        <v>-31.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O19" s="6">
+        <v>211</v>
+      </c>
+      <c r="O19" s="9">
         <v>100</v>
       </c>
-      <c r="P19" s="8">
-        <v>69</v>
-      </c>
-      <c r="Q19" s="22">
-        <v>73</v>
-      </c>
-      <c r="R19" s="16">
-        <v>86</v>
+      <c r="P19" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>89</v>
+      </c>
+      <c r="R19" s="24">
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2426,55 +2441,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L20" s="4">
-        <v>-41.4</v>
+        <v>-39.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O20" s="6">
-        <v>92</v>
-      </c>
-      <c r="P20" s="20">
-        <v>63</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>73</v>
-      </c>
-      <c r="R20" s="8">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="O20" s="9">
+        <v>100</v>
+      </c>
+      <c r="P20" s="15">
+        <v>88</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>87</v>
+      </c>
+      <c r="R20" s="20">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2482,55 +2497,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L21" s="4">
-        <v>-38.8</v>
+        <v>-40.5</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O21" s="6">
-        <v>77</v>
+        <v>211</v>
+      </c>
+      <c r="O21" s="9">
+        <v>100</v>
       </c>
       <c r="P21" s="23">
-        <v>51</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>70</v>
-      </c>
-      <c r="R21" s="23">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>75</v>
+      </c>
+      <c r="R21" s="13">
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2538,55 +2553,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L22" s="4">
-        <v>-18.1</v>
+        <v>-25.9</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O22" s="6">
-        <v>97</v>
-      </c>
-      <c r="P22" s="22">
-        <v>77</v>
-      </c>
-      <c r="Q22" s="16">
-        <v>87</v>
+        <v>211</v>
+      </c>
+      <c r="O22" s="9">
+        <v>83</v>
+      </c>
+      <c r="P22" s="16">
+        <v>70</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>31</v>
       </c>
       <c r="R22" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2594,55 +2609,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>92</v>
       </c>
       <c r="L23" s="4">
-        <v>-31.3</v>
+        <v>-36.7</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O23" s="6">
-        <v>90</v>
-      </c>
-      <c r="P23" s="21">
-        <v>56</v>
-      </c>
-      <c r="Q23" s="16">
-        <v>83</v>
+        <v>211</v>
+      </c>
+      <c r="O23" s="9">
+        <v>76</v>
+      </c>
+      <c r="P23" s="20">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>21</v>
       </c>
       <c r="R23" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2650,52 +2665,52 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>93</v>
       </c>
       <c r="L24" s="4">
-        <v>-39.7</v>
+        <v>-40.8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O24" s="6">
-        <v>76</v>
-      </c>
-      <c r="P24" s="24">
-        <v>36</v>
-      </c>
-      <c r="Q24" s="22">
-        <v>76</v>
+        <v>211</v>
+      </c>
+      <c r="O24" s="9">
+        <v>62</v>
+      </c>
+      <c r="P24" s="21">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="26">
+        <v>12</v>
       </c>
       <c r="R24" s="7">
         <v>0</v>
@@ -2706,10 +2721,10 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>70</v>
@@ -2718,43 +2733,43 @@
         <v>94</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>94</v>
+        <v>208</v>
       </c>
       <c r="L25" s="4">
-        <v>-40.5</v>
+        <v>-20.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O25" s="6">
-        <v>68</v>
-      </c>
-      <c r="P25" s="24">
-        <v>35</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>68</v>
-      </c>
-      <c r="R25" s="7">
-        <v>2</v>
+      <c r="O25" s="9">
+        <v>53</v>
+      </c>
+      <c r="P25" s="21">
+        <v>46</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>18</v>
+      </c>
+      <c r="R25" s="18">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2762,55 +2777,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>95</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-32.5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L26" s="4">
-        <v>-25.8</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O26" s="6">
-        <v>73</v>
-      </c>
-      <c r="P26" s="13">
-        <v>16</v>
-      </c>
-      <c r="Q26" s="20">
-        <v>63</v>
-      </c>
-      <c r="R26" s="22">
-        <v>73</v>
+      <c r="O26" s="19">
+        <v>38</v>
+      </c>
+      <c r="P26" s="27">
+        <v>35</v>
+      </c>
+      <c r="Q26" s="26">
+        <v>10</v>
+      </c>
+      <c r="R26" s="26">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2818,170 +2833,114 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>96</v>
       </c>
       <c r="L27" s="4">
-        <v>-36.6</v>
+        <v>-39.7</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O27" s="6">
-        <v>96</v>
-      </c>
-      <c r="P27" s="14">
-        <v>45</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>60</v>
-      </c>
-      <c r="R27" s="25">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="2">
-        <v>20</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L28" s="4">
-        <v>-40.8</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O28" s="6">
-        <v>98</v>
-      </c>
-      <c r="P28" s="19">
-        <v>40</v>
-      </c>
-      <c r="Q28" s="20">
-        <v>63</v>
-      </c>
-      <c r="R28" s="14">
-        <v>43</v>
+        <v>211</v>
+      </c>
+      <c r="O27" s="19">
+        <v>25</v>
+      </c>
+      <c r="P27" s="8">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>1</v>
+      </c>
+      <c r="R27" s="26">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A28">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B28">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C28">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D28">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E28">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F28">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G28">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H28">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I28">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J28">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K28">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L28">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -3000,12 +2959,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M28">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N28">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3022,22 +2981,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O28">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P28">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q28">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R28">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="218">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260311--01</t>
-  </si>
-  <si>
-    <t>20260311--02</t>
-  </si>
-  <si>
-    <t>20260311--03</t>
-  </si>
-  <si>
     <t>20260312--01</t>
   </si>
   <si>
@@ -148,475 +139,484 @@
     <t>20260317--03</t>
   </si>
   <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:21</t>
+    <t>20260318--01</t>
+  </si>
+  <si>
+    <t>20260318--02</t>
+  </si>
+  <si>
+    <t>20260318--03</t>
+  </si>
+  <si>
+    <t>05:49</t>
+  </si>
+  <si>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>01:55</t>
+  </si>
+  <si>
+    <t>04:23</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>03:22</t>
+  </si>
+  <si>
+    <t>03:36</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>02:22</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:36</t>
   </si>
   <si>
     <t>06:24</t>
   </si>
   <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>01:56</t>
-  </si>
-  <si>
-    <t>04:23</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>03:36</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:13</t>
-  </si>
-  <si>
-    <t>02:21</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>04:49</t>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
   </si>
   <si>
     <t>05:51</t>
   </si>
   <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:13</t>
-  </si>
-  <si>
-    <t>01:30:16</t>
-  </si>
-  <si>
-    <t>21:35:47</t>
-  </si>
-  <si>
-    <t>23:12:51</t>
-  </si>
-  <si>
-    <t>00:50:26</t>
-  </si>
-  <si>
-    <t>20:56:04</t>
-  </si>
-  <si>
-    <t>22:33:01</t>
-  </si>
-  <si>
-    <t>00:10:32</t>
-  </si>
-  <si>
-    <t>01:48:31</t>
-  </si>
-  <si>
-    <t>20:16:19</t>
-  </si>
-  <si>
-    <t>21:53:06</t>
-  </si>
-  <si>
-    <t>23:30:34</t>
-  </si>
-  <si>
-    <t>01:08:26</t>
-  </si>
-  <si>
-    <t>19:36:31</t>
-  </si>
-  <si>
-    <t>21:13:07</t>
-  </si>
-  <si>
-    <t>22:50:31</t>
-  </si>
-  <si>
-    <t>00:28:18</t>
-  </si>
-  <si>
-    <t>18:56:42</t>
-  </si>
-  <si>
-    <t>20:33:05</t>
-  </si>
-  <si>
-    <t>22:10:25</t>
-  </si>
-  <si>
-    <t>23:48:07</t>
-  </si>
-  <si>
-    <t>19:52:59</t>
-  </si>
-  <si>
-    <t>21:30:13</t>
-  </si>
-  <si>
-    <t>23:07:52</t>
-  </si>
-  <si>
-    <t>19:12:50</t>
-  </si>
-  <si>
-    <t>20:49:58</t>
-  </si>
-  <si>
-    <t>22:27:34</t>
-  </si>
-  <si>
-    <t>01:32:43</t>
-  </si>
-  <si>
-    <t>21:38:16</t>
-  </si>
-  <si>
-    <t>23:15:07</t>
-  </si>
-  <si>
-    <t>00:52:50</t>
-  </si>
-  <si>
-    <t>20:58:39</t>
-  </si>
-  <si>
-    <t>22:35:17</t>
-  </si>
-  <si>
-    <t>00:12:53</t>
-  </si>
-  <si>
-    <t>01:52:05</t>
-  </si>
-  <si>
-    <t>20:19:03</t>
-  </si>
-  <si>
-    <t>21:55:23</t>
-  </si>
-  <si>
-    <t>23:32:53</t>
-  </si>
-  <si>
-    <t>01:11:29</t>
-  </si>
-  <si>
-    <t>19:39:29</t>
-  </si>
-  <si>
-    <t>21:15:25</t>
-  </si>
-  <si>
-    <t>22:52:49</t>
-  </si>
-  <si>
-    <t>00:31:06</t>
-  </si>
-  <si>
-    <t>19:00:06</t>
-  </si>
-  <si>
-    <t>20:35:24</t>
-  </si>
-  <si>
-    <t>22:12:41</t>
-  </si>
-  <si>
-    <t>23:50:45</t>
-  </si>
-  <si>
-    <t>19:55:21</t>
-  </si>
-  <si>
-    <t>21:32:29</t>
-  </si>
-  <si>
-    <t>23:10:23</t>
-  </si>
-  <si>
-    <t>19:15:15</t>
-  </si>
-  <si>
-    <t>20:52:14</t>
-  </si>
-  <si>
-    <t>22:30:00</t>
-  </si>
-  <si>
-    <t>01:35:30</t>
-  </si>
-  <si>
-    <t>21:40:56</t>
-  </si>
-  <si>
-    <t>23:18:19</t>
-  </si>
-  <si>
-    <t>00:55:44</t>
-  </si>
-  <si>
-    <t>21:01:07</t>
-  </si>
-  <si>
-    <t>22:38:27</t>
-  </si>
-  <si>
-    <t>00:15:53</t>
-  </si>
-  <si>
-    <t>01:53:03</t>
-  </si>
-  <si>
-    <t>20:21:14</t>
-  </si>
-  <si>
-    <t>21:58:31</t>
-  </si>
-  <si>
-    <t>23:35:58</t>
-  </si>
-  <si>
-    <t>01:13:11</t>
-  </si>
-  <si>
-    <t>19:41:17</t>
-  </si>
-  <si>
-    <t>21:18:31</t>
-  </si>
-  <si>
-    <t>22:55:57</t>
-  </si>
-  <si>
-    <t>00:33:13</t>
-  </si>
-  <si>
-    <t>19:01:16</t>
-  </si>
-  <si>
-    <t>20:38:26</t>
-  </si>
-  <si>
-    <t>22:15:51</t>
-  </si>
-  <si>
-    <t>23:53:10</t>
-  </si>
-  <si>
-    <t>19:58:17</t>
-  </si>
-  <si>
-    <t>21:35:41</t>
-  </si>
-  <si>
-    <t>23:13:01</t>
-  </si>
-  <si>
-    <t>19:18:03</t>
-  </si>
-  <si>
-    <t>20:55:26</t>
-  </si>
-  <si>
-    <t>22:32:48</t>
-  </si>
-  <si>
-    <t>01:38:17</t>
-  </si>
-  <si>
-    <t>21:43:37</t>
-  </si>
-  <si>
-    <t>23:21:31</t>
-  </si>
-  <si>
-    <t>00:58:39</t>
-  </si>
-  <si>
-    <t>21:03:35</t>
-  </si>
-  <si>
-    <t>22:41:38</t>
-  </si>
-  <si>
-    <t>00:18:54</t>
-  </si>
-  <si>
-    <t>01:54:01</t>
-  </si>
-  <si>
-    <t>20:23:26</t>
-  </si>
-  <si>
-    <t>22:01:40</t>
-  </si>
-  <si>
-    <t>23:39:02</t>
-  </si>
-  <si>
-    <t>01:14:52</t>
-  </si>
-  <si>
-    <t>19:43:05</t>
-  </si>
-  <si>
-    <t>21:21:36</t>
-  </si>
-  <si>
-    <t>22:59:05</t>
-  </si>
-  <si>
-    <t>00:35:19</t>
-  </si>
-  <si>
-    <t>19:02:27</t>
-  </si>
-  <si>
-    <t>20:41:27</t>
-  </si>
-  <si>
-    <t>22:19:01</t>
-  </si>
-  <si>
-    <t>23:55:34</t>
-  </si>
-  <si>
-    <t>20:01:12</t>
-  </si>
-  <si>
-    <t>21:38:52</t>
-  </si>
-  <si>
-    <t>23:15:39</t>
-  </si>
-  <si>
-    <t>19:20:52</t>
-  </si>
-  <si>
-    <t>20:58:38</t>
-  </si>
-  <si>
-    <t>22:35:36</t>
-  </si>
-  <si>
-    <t>01:40:43</t>
-  </si>
-  <si>
-    <t>21:46:07</t>
-  </si>
-  <si>
-    <t>23:23:46</t>
-  </si>
-  <si>
-    <t>01:01:02</t>
-  </si>
-  <si>
-    <t>21:06:11</t>
-  </si>
-  <si>
-    <t>22:43:54</t>
-  </si>
-  <si>
-    <t>00:21:14</t>
-  </si>
-  <si>
-    <t>01:57:34</t>
-  </si>
-  <si>
-    <t>20:26:11</t>
-  </si>
-  <si>
-    <t>22:03:57</t>
-  </si>
-  <si>
-    <t>23:41:21</t>
-  </si>
-  <si>
-    <t>01:17:54</t>
-  </si>
-  <si>
-    <t>19:46:04</t>
-  </si>
-  <si>
-    <t>21:23:55</t>
-  </si>
-  <si>
-    <t>23:01:22</t>
-  </si>
-  <si>
-    <t>00:38:06</t>
-  </si>
-  <si>
-    <t>19:05:51</t>
-  </si>
-  <si>
-    <t>20:43:47</t>
-  </si>
-  <si>
-    <t>22:21:18</t>
-  </si>
-  <si>
-    <t>23:58:11</t>
-  </si>
-  <si>
-    <t>20:03:35</t>
-  </si>
-  <si>
-    <t>21:41:08</t>
-  </si>
-  <si>
-    <t>23:18:10</t>
-  </si>
-  <si>
-    <t>19:23:18</t>
-  </si>
-  <si>
-    <t>21:00:53</t>
-  </si>
-  <si>
-    <t>22:38:02</t>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>03:06</t>
+  </si>
+  <si>
+    <t>00:50:30</t>
+  </si>
+  <si>
+    <t>20:56:10</t>
+  </si>
+  <si>
+    <t>22:33:07</t>
+  </si>
+  <si>
+    <t>00:10:39</t>
+  </si>
+  <si>
+    <t>01:48:37</t>
+  </si>
+  <si>
+    <t>20:16:28</t>
+  </si>
+  <si>
+    <t>21:53:15</t>
+  </si>
+  <si>
+    <t>23:30:44</t>
+  </si>
+  <si>
+    <t>01:08:36</t>
+  </si>
+  <si>
+    <t>19:36:44</t>
+  </si>
+  <si>
+    <t>21:13:20</t>
+  </si>
+  <si>
+    <t>22:50:45</t>
+  </si>
+  <si>
+    <t>00:28:32</t>
+  </si>
+  <si>
+    <t>18:57:00</t>
+  </si>
+  <si>
+    <t>20:33:23</t>
+  </si>
+  <si>
+    <t>22:10:43</t>
+  </si>
+  <si>
+    <t>23:48:26</t>
+  </si>
+  <si>
+    <t>19:53:22</t>
+  </si>
+  <si>
+    <t>21:30:38</t>
+  </si>
+  <si>
+    <t>23:08:17</t>
+  </si>
+  <si>
+    <t>19:13:19</t>
+  </si>
+  <si>
+    <t>20:50:29</t>
+  </si>
+  <si>
+    <t>22:28:05</t>
+  </si>
+  <si>
+    <t>18:33:14</t>
+  </si>
+  <si>
+    <t>20:10:16</t>
+  </si>
+  <si>
+    <t>21:47:49</t>
+  </si>
+  <si>
+    <t>00:52:53</t>
+  </si>
+  <si>
+    <t>20:58:45</t>
+  </si>
+  <si>
+    <t>22:35:23</t>
+  </si>
+  <si>
+    <t>00:12:59</t>
+  </si>
+  <si>
+    <t>01:52:12</t>
+  </si>
+  <si>
+    <t>20:19:12</t>
+  </si>
+  <si>
+    <t>21:55:32</t>
+  </si>
+  <si>
+    <t>23:33:02</t>
+  </si>
+  <si>
+    <t>01:11:39</t>
+  </si>
+  <si>
+    <t>19:39:42</t>
+  </si>
+  <si>
+    <t>21:15:38</t>
+  </si>
+  <si>
+    <t>22:53:02</t>
+  </si>
+  <si>
+    <t>00:31:20</t>
+  </si>
+  <si>
+    <t>19:00:23</t>
+  </si>
+  <si>
+    <t>20:35:42</t>
+  </si>
+  <si>
+    <t>22:12:59</t>
+  </si>
+  <si>
+    <t>23:51:04</t>
+  </si>
+  <si>
+    <t>19:55:44</t>
+  </si>
+  <si>
+    <t>21:32:53</t>
+  </si>
+  <si>
+    <t>23:10:48</t>
+  </si>
+  <si>
+    <t>19:15:45</t>
+  </si>
+  <si>
+    <t>20:52:44</t>
+  </si>
+  <si>
+    <t>22:30:31</t>
+  </si>
+  <si>
+    <t>18:35:45</t>
+  </si>
+  <si>
+    <t>20:12:32</t>
+  </si>
+  <si>
+    <t>21:50:12</t>
+  </si>
+  <si>
+    <t>00:55:48</t>
+  </si>
+  <si>
+    <t>21:01:13</t>
+  </si>
+  <si>
+    <t>22:38:33</t>
+  </si>
+  <si>
+    <t>00:15:59</t>
+  </si>
+  <si>
+    <t>01:53:09</t>
+  </si>
+  <si>
+    <t>20:21:23</t>
+  </si>
+  <si>
+    <t>21:58:40</t>
+  </si>
+  <si>
+    <t>23:36:07</t>
+  </si>
+  <si>
+    <t>01:13:20</t>
+  </si>
+  <si>
+    <t>19:41:30</t>
+  </si>
+  <si>
+    <t>21:18:44</t>
+  </si>
+  <si>
+    <t>22:56:10</t>
+  </si>
+  <si>
+    <t>00:33:26</t>
+  </si>
+  <si>
+    <t>19:01:34</t>
+  </si>
+  <si>
+    <t>20:38:44</t>
+  </si>
+  <si>
+    <t>22:16:09</t>
+  </si>
+  <si>
+    <t>23:53:28</t>
+  </si>
+  <si>
+    <t>19:58:40</t>
+  </si>
+  <si>
+    <t>21:36:05</t>
+  </si>
+  <si>
+    <t>23:13:26</t>
+  </si>
+  <si>
+    <t>19:18:33</t>
+  </si>
+  <si>
+    <t>20:55:56</t>
+  </si>
+  <si>
+    <t>22:33:19</t>
+  </si>
+  <si>
+    <t>18:38:22</t>
+  </si>
+  <si>
+    <t>20:15:43</t>
+  </si>
+  <si>
+    <t>21:53:07</t>
+  </si>
+  <si>
+    <t>00:58:42</t>
+  </si>
+  <si>
+    <t>21:03:41</t>
+  </si>
+  <si>
+    <t>22:41:44</t>
+  </si>
+  <si>
+    <t>00:19:00</t>
+  </si>
+  <si>
+    <t>01:54:07</t>
+  </si>
+  <si>
+    <t>20:23:35</t>
+  </si>
+  <si>
+    <t>22:01:49</t>
+  </si>
+  <si>
+    <t>23:39:12</t>
+  </si>
+  <si>
+    <t>01:15:01</t>
+  </si>
+  <si>
+    <t>19:43:18</t>
+  </si>
+  <si>
+    <t>21:21:49</t>
+  </si>
+  <si>
+    <t>22:59:18</t>
+  </si>
+  <si>
+    <t>00:35:33</t>
+  </si>
+  <si>
+    <t>19:02:45</t>
+  </si>
+  <si>
+    <t>20:41:45</t>
+  </si>
+  <si>
+    <t>22:19:20</t>
+  </si>
+  <si>
+    <t>23:55:52</t>
+  </si>
+  <si>
+    <t>20:01:36</t>
+  </si>
+  <si>
+    <t>21:39:16</t>
+  </si>
+  <si>
+    <t>23:16:03</t>
+  </si>
+  <si>
+    <t>19:21:21</t>
+  </si>
+  <si>
+    <t>20:59:08</t>
+  </si>
+  <si>
+    <t>22:36:06</t>
+  </si>
+  <si>
+    <t>18:41:01</t>
+  </si>
+  <si>
+    <t>20:18:55</t>
+  </si>
+  <si>
+    <t>21:56:03</t>
+  </si>
+  <si>
+    <t>01:01:05</t>
+  </si>
+  <si>
+    <t>21:06:17</t>
+  </si>
+  <si>
+    <t>22:44:00</t>
+  </si>
+  <si>
+    <t>00:21:20</t>
+  </si>
+  <si>
+    <t>01:57:40</t>
+  </si>
+  <si>
+    <t>20:26:19</t>
+  </si>
+  <si>
+    <t>22:04:06</t>
+  </si>
+  <si>
+    <t>23:41:30</t>
+  </si>
+  <si>
+    <t>01:18:03</t>
+  </si>
+  <si>
+    <t>19:46:17</t>
+  </si>
+  <si>
+    <t>21:24:08</t>
+  </si>
+  <si>
+    <t>23:01:35</t>
+  </si>
+  <si>
+    <t>00:38:20</t>
+  </si>
+  <si>
+    <t>19:06:09</t>
+  </si>
+  <si>
+    <t>20:44:05</t>
+  </si>
+  <si>
+    <t>22:21:36</t>
+  </si>
+  <si>
+    <t>23:58:30</t>
+  </si>
+  <si>
+    <t>20:03:59</t>
+  </si>
+  <si>
+    <t>21:41:32</t>
+  </si>
+  <si>
+    <t>23:18:34</t>
+  </si>
+  <si>
+    <t>19:23:47</t>
+  </si>
+  <si>
+    <t>21:01:23</t>
+  </si>
+  <si>
+    <t>22:38:32</t>
+  </si>
+  <si>
+    <t>18:43:32</t>
+  </si>
+  <si>
+    <t>20:21:10</t>
+  </si>
+  <si>
+    <t>21:58:25</t>
   </si>
   <si>
     <t>0°</t>
@@ -628,19 +628,31 @@
     <t>6°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>19:36:20</t>
-  </si>
-  <si>
-    <t>18:58:46</t>
-  </si>
-  <si>
-    <t>19:54:28</t>
-  </si>
-  <si>
-    <t>19:16:28</t>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>19:36:32</t>
+  </si>
+  <si>
+    <t>18:59:03</t>
+  </si>
+  <si>
+    <t>19:54:51</t>
+  </si>
+  <si>
+    <t>19:16:56</t>
+  </si>
+  <si>
+    <t>18:38:51</t>
+  </si>
+  <si>
+    <t>20:12:19</t>
   </si>
   <si>
     <t>B</t>
@@ -689,7 +701,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,6 +711,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -716,13 +752,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,25 +824,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,73 +836,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,7 +889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,6 +970,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1433,13 +1454,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>71</v>
@@ -1463,25 +1484,25 @@
         <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-34.6</v>
+        <v>-38.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>82</v>
+      </c>
+      <c r="R2" s="9">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1489,13 +1510,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>72</v>
@@ -1519,25 +1540,25 @@
         <v>72</v>
       </c>
       <c r="L3" s="4">
-        <v>-38.9</v>
+        <v>-34.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="9">
-        <v>88</v>
-      </c>
-      <c r="P3" s="10">
-        <v>21</v>
+        <v>215</v>
+      </c>
+      <c r="O3" s="10">
+        <v>2</v>
+      </c>
+      <c r="P3" s="11">
+        <v>0</v>
       </c>
       <c r="Q3" s="11">
-        <v>77</v>
-      </c>
-      <c r="R3" s="12">
-        <v>79</v>
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1551,7 +1572,7 @@
         <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>73</v>
@@ -1575,25 +1596,25 @@
         <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-42.8</v>
+        <v>-41.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O4" s="9">
-        <v>99</v>
-      </c>
-      <c r="P4" s="13">
-        <v>56</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>95</v>
-      </c>
-      <c r="R4" s="15">
-        <v>90</v>
+        <v>215</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
+      </c>
+      <c r="P4" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1601,13 +1622,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>74</v>
@@ -1631,25 +1652,25 @@
         <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-38.2</v>
+        <v>-40.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O5" s="9">
-        <v>100</v>
-      </c>
-      <c r="P5" s="16">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="17">
-        <v>100</v>
-      </c>
-      <c r="R5" s="15">
-        <v>91</v>
+        <v>215</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1657,13 +1678,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>75</v>
@@ -1687,25 +1708,25 @@
         <v>75</v>
       </c>
       <c r="L6" s="4">
-        <v>-34.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O6" s="6">
+        <v>216</v>
+      </c>
+      <c r="O6" s="10">
         <v>3</v>
       </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7">
+      <c r="P6" s="11">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
+      <c r="Q6" s="11">
         <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1713,13 +1734,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>76</v>
@@ -1743,25 +1764,25 @@
         <v>76</v>
       </c>
       <c r="L7" s="4">
-        <v>-41.8</v>
+        <v>-29.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O7" s="6">
-        <v>8</v>
-      </c>
-      <c r="P7" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="7">
+        <v>100</v>
+      </c>
+      <c r="P7" s="11">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>0</v>
+      <c r="Q7" s="13">
+        <v>55</v>
+      </c>
+      <c r="R7" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1769,13 +1790,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>77</v>
@@ -1799,25 +1820,25 @@
         <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-40.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O8" s="19">
-        <v>14</v>
-      </c>
-      <c r="P8" s="18">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="7">
+        <v>215</v>
+      </c>
+      <c r="O8" s="6">
+        <v>95</v>
+      </c>
+      <c r="P8" s="11">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
-        <v>2</v>
+      <c r="Q8" s="15">
+        <v>49</v>
+      </c>
+      <c r="R8" s="16">
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1825,13 +1846,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>78</v>
@@ -1855,25 +1876,25 @@
         <v>78</v>
       </c>
       <c r="L9" s="4">
-        <v>-31.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O9" s="6">
+        <v>95</v>
+      </c>
+      <c r="P9" s="17">
         <v>8</v>
       </c>
-      <c r="P9" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7">
-        <v>2</v>
+      <c r="Q9" s="18">
+        <v>76</v>
+      </c>
+      <c r="R9" s="18">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1881,13 +1902,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>79</v>
@@ -1911,25 +1932,25 @@
         <v>79</v>
       </c>
       <c r="L10" s="4">
-        <v>-29.9</v>
+        <v>-35.8</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O10" s="9">
-        <v>96</v>
-      </c>
-      <c r="P10" s="7">
+        <v>216</v>
+      </c>
+      <c r="O10" s="6">
+        <v>100</v>
+      </c>
+      <c r="P10" s="11">
         <v>0</v>
       </c>
-      <c r="Q10" s="10">
-        <v>22</v>
-      </c>
-      <c r="R10" s="15">
-        <v>90</v>
+      <c r="Q10" s="19">
+        <v>86</v>
+      </c>
+      <c r="R10" s="13">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1937,13 +1958,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>80</v>
@@ -1961,31 +1982,31 @@
         <v>184</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="L11" s="4">
-        <v>-39.4</v>
+        <v>-24.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O11" s="9">
-        <v>100</v>
-      </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>40</v>
-      </c>
-      <c r="R11" s="11">
-        <v>73</v>
+        <v>216</v>
+      </c>
+      <c r="O11" s="6">
+        <v>97</v>
+      </c>
+      <c r="P11" s="20">
+        <v>66</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>83</v>
+      </c>
+      <c r="R11" s="21">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1993,13 +2014,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>81</v>
@@ -2023,25 +2044,25 @@
         <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-41.8</v>
+        <v>-35.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O12" s="9">
-        <v>100</v>
-      </c>
-      <c r="P12" s="8">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>43</v>
-      </c>
-      <c r="R12" s="17">
-        <v>100</v>
+        <v>215</v>
+      </c>
+      <c r="O12" s="6">
+        <v>90</v>
+      </c>
+      <c r="P12" s="20">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>8</v>
+      </c>
+      <c r="R12" s="13">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2049,13 +2070,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>82</v>
@@ -2079,25 +2100,25 @@
         <v>82</v>
       </c>
       <c r="L13" s="4">
-        <v>-35.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O13" s="9">
-        <v>100</v>
-      </c>
-      <c r="P13" s="18">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="20">
-        <v>41</v>
-      </c>
-      <c r="R13" s="13">
-        <v>57</v>
+        <v>215</v>
+      </c>
+      <c r="O13" s="6">
+        <v>99</v>
+      </c>
+      <c r="P13" s="20">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>3</v>
+      </c>
+      <c r="R13" s="16">
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2105,13 +2126,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>83</v>
@@ -2129,31 +2150,31 @@
         <v>187</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="L14" s="4">
-        <v>-24.2</v>
+        <v>-38.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O14" s="9">
+        <v>215</v>
+      </c>
+      <c r="O14" s="6">
         <v>100</v>
       </c>
-      <c r="P14" s="22">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>72</v>
-      </c>
-      <c r="R14" s="15">
-        <v>90</v>
+      <c r="P14" s="13">
+        <v>57</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>36</v>
+      </c>
+      <c r="R14" s="23">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2161,13 +2182,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>84</v>
@@ -2185,31 +2206,31 @@
         <v>188</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L15" s="4">
-        <v>-35.9</v>
+        <v>-18.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O15" s="9">
+        <v>216</v>
+      </c>
+      <c r="O15" s="6">
         <v>100</v>
       </c>
-      <c r="P15" s="23">
-        <v>86</v>
+      <c r="P15" s="16">
+        <v>93</v>
       </c>
       <c r="Q15" s="16">
-        <v>72</v>
-      </c>
-      <c r="R15" s="17">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="R15" s="24">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2217,13 +2238,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>85</v>
@@ -2247,25 +2268,25 @@
         <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>-41.4</v>
+        <v>-31.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O16" s="9">
-        <v>100</v>
-      </c>
-      <c r="P16" s="12">
-        <v>79</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>75</v>
-      </c>
-      <c r="R16" s="17">
-        <v>100</v>
+        <v>215</v>
+      </c>
+      <c r="O16" s="6">
+        <v>99</v>
+      </c>
+      <c r="P16" s="19">
+        <v>85</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>97</v>
+      </c>
+      <c r="R16" s="12">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2273,13 +2294,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>86</v>
@@ -2303,25 +2324,25 @@
         <v>86</v>
       </c>
       <c r="L17" s="4">
-        <v>-38.7</v>
+        <v>-39.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O17" s="9">
+        <v>215</v>
+      </c>
+      <c r="O17" s="6">
         <v>100</v>
       </c>
-      <c r="P17" s="11">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>72</v>
-      </c>
-      <c r="R17" s="17">
-        <v>100</v>
+      <c r="P17" s="19">
+        <v>83</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>92</v>
+      </c>
+      <c r="R17" s="22">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2329,13 +2350,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>87</v>
@@ -2353,31 +2374,31 @@
         <v>191</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>206</v>
+        <v>87</v>
       </c>
       <c r="L18" s="4">
-        <v>-18.2</v>
+        <v>-40.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O18" s="9">
+        <v>215</v>
+      </c>
+      <c r="O18" s="6">
         <v>100</v>
       </c>
-      <c r="P18" s="15">
-        <v>89</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>81</v>
-      </c>
-      <c r="R18" s="11">
-        <v>73</v>
+      <c r="P18" s="21">
+        <v>70</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>78</v>
+      </c>
+      <c r="R18" s="20">
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2385,13 +2406,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>88</v>
@@ -2409,31 +2430,31 @@
         <v>192</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-25.9</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" s="6">
         <v>88</v>
       </c>
-      <c r="L19" s="4">
-        <v>-31.3</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O19" s="9">
-        <v>100</v>
-      </c>
-      <c r="P19" s="15">
-        <v>90</v>
-      </c>
-      <c r="Q19" s="15">
-        <v>89</v>
-      </c>
-      <c r="R19" s="24">
-        <v>59</v>
+      <c r="P19" s="20">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>73</v>
+      </c>
+      <c r="R19" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2441,13 +2462,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>89</v>
@@ -2471,25 +2492,25 @@
         <v>89</v>
       </c>
       <c r="L20" s="4">
-        <v>-39.7</v>
+        <v>-36.7</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O20" s="9">
-        <v>100</v>
+        <v>215</v>
+      </c>
+      <c r="O20" s="6">
+        <v>90</v>
       </c>
       <c r="P20" s="15">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="Q20" s="23">
-        <v>87</v>
-      </c>
-      <c r="R20" s="20">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2497,13 +2518,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>90</v>
@@ -2527,25 +2548,25 @@
         <v>90</v>
       </c>
       <c r="L21" s="4">
-        <v>-40.5</v>
+        <v>-40.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O21" s="9">
-        <v>100</v>
-      </c>
-      <c r="P21" s="23">
-        <v>86</v>
-      </c>
-      <c r="Q21" s="11">
-        <v>75</v>
-      </c>
-      <c r="R21" s="13">
-        <v>55</v>
+        <v>215</v>
+      </c>
+      <c r="O21" s="6">
+        <v>82</v>
+      </c>
+      <c r="P21" s="13">
+        <v>57</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>12</v>
+      </c>
+      <c r="R21" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2553,10 +2574,10 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -2577,30 +2598,30 @@
         <v>195</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="L22" s="4">
-        <v>-25.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O22" s="9">
-        <v>83</v>
-      </c>
-      <c r="P22" s="16">
-        <v>70</v>
-      </c>
-      <c r="Q22" s="25">
-        <v>31</v>
-      </c>
-      <c r="R22" s="7">
+        <v>217</v>
+      </c>
+      <c r="O22" s="26">
+        <v>28</v>
+      </c>
+      <c r="P22" s="27">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>0</v>
+      </c>
+      <c r="R22" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2612,10 +2633,10 @@
         <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>92</v>
@@ -2639,24 +2660,24 @@
         <v>92</v>
       </c>
       <c r="L23" s="4">
-        <v>-36.7</v>
+        <v>-32.6</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O23" s="9">
-        <v>76</v>
-      </c>
-      <c r="P23" s="20">
-        <v>42</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>21</v>
-      </c>
-      <c r="R23" s="7">
+        <v>215</v>
+      </c>
+      <c r="O23" s="26">
+        <v>18</v>
+      </c>
+      <c r="P23" s="28">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0</v>
+      </c>
+      <c r="R23" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2665,13 +2686,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>93</v>
@@ -2695,24 +2716,24 @@
         <v>93</v>
       </c>
       <c r="L24" s="4">
-        <v>-40.8</v>
+        <v>-39.7</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O24" s="9">
-        <v>62</v>
-      </c>
-      <c r="P24" s="21">
-        <v>46</v>
-      </c>
-      <c r="Q24" s="26">
-        <v>12</v>
-      </c>
-      <c r="R24" s="7">
+        <v>215</v>
+      </c>
+      <c r="O24" s="10">
+        <v>8</v>
+      </c>
+      <c r="P24" s="12">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>0</v>
+      </c>
+      <c r="R24" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2721,10 +2742,10 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>70</v>
@@ -2745,31 +2766,31 @@
         <v>198</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L25" s="4">
-        <v>-20.1</v>
+        <v>-14</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O25" s="9">
-        <v>53</v>
-      </c>
-      <c r="P25" s="21">
-        <v>46</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>18</v>
-      </c>
-      <c r="R25" s="18">
-        <v>5</v>
+        <v>217</v>
+      </c>
+      <c r="O25" s="10">
+        <v>3</v>
+      </c>
+      <c r="P25" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>0</v>
+      </c>
+      <c r="R25" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2780,10 +2801,10 @@
         <v>32</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>95</v>
@@ -2801,31 +2822,31 @@
         <v>199</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="L26" s="4">
-        <v>-32.5</v>
+        <v>-27.6</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O26" s="19">
-        <v>38</v>
-      </c>
-      <c r="P26" s="27">
-        <v>35</v>
-      </c>
-      <c r="Q26" s="26">
-        <v>10</v>
-      </c>
-      <c r="R26" s="26">
-        <v>10</v>
+        <v>215</v>
+      </c>
+      <c r="O26" s="10">
+        <v>1</v>
+      </c>
+      <c r="P26" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>0</v>
+      </c>
+      <c r="R26" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2833,13 +2854,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>96</v>
@@ -2863,25 +2884,25 @@
         <v>96</v>
       </c>
       <c r="L27" s="4">
-        <v>-39.7</v>
+        <v>-37.3</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O27" s="19">
-        <v>25</v>
-      </c>
-      <c r="P27" s="8">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="7">
+        <v>215</v>
+      </c>
+      <c r="O27" s="10">
         <v>1</v>
       </c>
-      <c r="R27" s="26">
-        <v>8</v>
+      <c r="P27" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>0</v>
+      </c>
+      <c r="R27" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260312--01</t>
-  </si>
-  <si>
-    <t>20260312--02</t>
-  </si>
-  <si>
-    <t>20260312--03</t>
-  </si>
-  <si>
     <t>20260313--01</t>
   </si>
   <si>
@@ -148,13 +139,16 @@
     <t>20260318--03</t>
   </si>
   <si>
-    <t>05:49</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:21</t>
+    <t>20260319--01</t>
+  </si>
+  <si>
+    <t>20260319--02</t>
+  </si>
+  <si>
+    <t>20260319--03</t>
+  </si>
+  <si>
+    <t>20260319--04</t>
   </si>
   <si>
     <t>06:01</t>
@@ -163,16 +157,16 @@
     <t>01:55</t>
   </si>
   <si>
-    <t>04:23</t>
+    <t>04:22</t>
   </si>
   <si>
     <t>06:17</t>
   </si>
   <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>03:22</t>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>03:21</t>
   </si>
   <si>
     <t>03:36</t>
@@ -181,22 +175,25 @@
     <t>06:11</t>
   </si>
   <si>
-    <t>06:16</t>
+    <t>06:15</t>
   </si>
   <si>
     <t>04:13</t>
   </si>
   <si>
-    <t>02:22</t>
+    <t>02:21</t>
   </si>
   <si>
     <t>06:03</t>
   </si>
   <si>
+    <t>06:20</t>
+  </si>
+  <si>
     <t>04:48</t>
   </si>
   <si>
-    <t>05:52</t>
+    <t>05:51</t>
   </si>
   <si>
     <t>06:23</t>
@@ -205,37 +202,40 @@
     <t>05:15</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>06:24</t>
+    <t>05:37</t>
   </si>
   <si>
     <t>05:35</t>
   </si>
   <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:51</t>
+    <t>05:17</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>02:16</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:11</t>
-  </si>
-  <si>
-    <t>03:06</t>
-  </si>
-  <si>
-    <t>00:50:30</t>
-  </si>
-  <si>
-    <t>20:56:10</t>
-  </si>
-  <si>
-    <t>22:33:07</t>
+    <t>01:12</t>
+  </si>
+  <si>
+    <t>03:07</t>
+  </si>
+  <si>
+    <t>01:46</t>
   </si>
   <si>
     <t>00:10:39</t>
@@ -247,7 +247,7 @@
     <t>20:16:28</t>
   </si>
   <si>
-    <t>21:53:15</t>
+    <t>21:53:16</t>
   </si>
   <si>
     <t>23:30:44</t>
@@ -256,64 +256,67 @@
     <t>01:08:36</t>
   </si>
   <si>
-    <t>19:36:44</t>
-  </si>
-  <si>
-    <t>21:13:20</t>
-  </si>
-  <si>
-    <t>22:50:45</t>
-  </si>
-  <si>
-    <t>00:28:32</t>
-  </si>
-  <si>
-    <t>18:57:00</t>
-  </si>
-  <si>
-    <t>20:33:23</t>
-  </si>
-  <si>
-    <t>22:10:43</t>
-  </si>
-  <si>
-    <t>23:48:26</t>
-  </si>
-  <si>
-    <t>19:53:22</t>
-  </si>
-  <si>
-    <t>21:30:38</t>
-  </si>
-  <si>
-    <t>23:08:17</t>
-  </si>
-  <si>
-    <t>19:13:19</t>
-  </si>
-  <si>
-    <t>20:50:29</t>
-  </si>
-  <si>
-    <t>22:28:05</t>
-  </si>
-  <si>
-    <t>18:33:14</t>
-  </si>
-  <si>
-    <t>20:10:16</t>
-  </si>
-  <si>
-    <t>21:47:49</t>
-  </si>
-  <si>
-    <t>00:52:53</t>
-  </si>
-  <si>
-    <t>20:58:45</t>
-  </si>
-  <si>
-    <t>22:35:23</t>
+    <t>19:36:45</t>
+  </si>
+  <si>
+    <t>21:13:21</t>
+  </si>
+  <si>
+    <t>22:50:46</t>
+  </si>
+  <si>
+    <t>00:28:33</t>
+  </si>
+  <si>
+    <t>18:57:01</t>
+  </si>
+  <si>
+    <t>20:33:24</t>
+  </si>
+  <si>
+    <t>22:10:45</t>
+  </si>
+  <si>
+    <t>23:48:28</t>
+  </si>
+  <si>
+    <t>19:53:25</t>
+  </si>
+  <si>
+    <t>21:30:40</t>
+  </si>
+  <si>
+    <t>23:08:20</t>
+  </si>
+  <si>
+    <t>19:13:23</t>
+  </si>
+  <si>
+    <t>20:50:32</t>
+  </si>
+  <si>
+    <t>22:28:08</t>
+  </si>
+  <si>
+    <t>18:33:19</t>
+  </si>
+  <si>
+    <t>20:10:21</t>
+  </si>
+  <si>
+    <t>21:47:54</t>
+  </si>
+  <si>
+    <t>17:53:13</t>
+  </si>
+  <si>
+    <t>19:30:07</t>
+  </si>
+  <si>
+    <t>21:07:37</t>
+  </si>
+  <si>
+    <t>22:45:32</t>
   </si>
   <si>
     <t>00:12:59</t>
@@ -322,79 +325,82 @@
     <t>01:52:12</t>
   </si>
   <si>
-    <t>20:19:12</t>
+    <t>20:19:13</t>
   </si>
   <si>
     <t>21:55:32</t>
   </si>
   <si>
-    <t>23:33:02</t>
-  </si>
-  <si>
-    <t>01:11:39</t>
-  </si>
-  <si>
-    <t>19:39:42</t>
-  </si>
-  <si>
-    <t>21:15:38</t>
-  </si>
-  <si>
-    <t>22:53:02</t>
-  </si>
-  <si>
-    <t>00:31:20</t>
-  </si>
-  <si>
-    <t>19:00:23</t>
-  </si>
-  <si>
-    <t>20:35:42</t>
-  </si>
-  <si>
-    <t>22:12:59</t>
-  </si>
-  <si>
-    <t>23:51:04</t>
-  </si>
-  <si>
-    <t>19:55:44</t>
-  </si>
-  <si>
-    <t>21:32:53</t>
-  </si>
-  <si>
-    <t>23:10:48</t>
-  </si>
-  <si>
-    <t>19:15:45</t>
-  </si>
-  <si>
-    <t>20:52:44</t>
-  </si>
-  <si>
-    <t>22:30:31</t>
-  </si>
-  <si>
-    <t>18:35:45</t>
-  </si>
-  <si>
-    <t>20:12:32</t>
-  </si>
-  <si>
-    <t>21:50:12</t>
-  </si>
-  <si>
-    <t>00:55:48</t>
-  </si>
-  <si>
-    <t>21:01:13</t>
-  </si>
-  <si>
-    <t>22:38:33</t>
-  </si>
-  <si>
-    <t>00:15:59</t>
+    <t>23:33:03</t>
+  </si>
+  <si>
+    <t>01:11:40</t>
+  </si>
+  <si>
+    <t>19:39:43</t>
+  </si>
+  <si>
+    <t>21:15:39</t>
+  </si>
+  <si>
+    <t>22:53:04</t>
+  </si>
+  <si>
+    <t>00:31:21</t>
+  </si>
+  <si>
+    <t>19:00:25</t>
+  </si>
+  <si>
+    <t>20:35:44</t>
+  </si>
+  <si>
+    <t>22:13:01</t>
+  </si>
+  <si>
+    <t>23:51:06</t>
+  </si>
+  <si>
+    <t>19:55:47</t>
+  </si>
+  <si>
+    <t>21:32:56</t>
+  </si>
+  <si>
+    <t>23:10:51</t>
+  </si>
+  <si>
+    <t>19:15:48</t>
+  </si>
+  <si>
+    <t>20:52:48</t>
+  </si>
+  <si>
+    <t>22:30:35</t>
+  </si>
+  <si>
+    <t>18:35:49</t>
+  </si>
+  <si>
+    <t>20:12:37</t>
+  </si>
+  <si>
+    <t>21:50:17</t>
+  </si>
+  <si>
+    <t>17:55:50</t>
+  </si>
+  <si>
+    <t>19:32:23</t>
+  </si>
+  <si>
+    <t>21:09:57</t>
+  </si>
+  <si>
+    <t>22:48:58</t>
+  </si>
+  <si>
+    <t>00:16:00</t>
   </si>
   <si>
     <t>01:53:09</t>
@@ -403,73 +409,76 @@
     <t>20:21:23</t>
   </si>
   <si>
-    <t>21:58:40</t>
+    <t>21:58:41</t>
   </si>
   <si>
     <t>23:36:07</t>
   </si>
   <si>
-    <t>01:13:20</t>
-  </si>
-  <si>
-    <t>19:41:30</t>
-  </si>
-  <si>
-    <t>21:18:44</t>
-  </si>
-  <si>
-    <t>22:56:10</t>
-  </si>
-  <si>
-    <t>00:33:26</t>
-  </si>
-  <si>
-    <t>19:01:34</t>
-  </si>
-  <si>
-    <t>20:38:44</t>
-  </si>
-  <si>
-    <t>22:16:09</t>
-  </si>
-  <si>
-    <t>23:53:28</t>
-  </si>
-  <si>
-    <t>19:58:40</t>
-  </si>
-  <si>
-    <t>21:36:05</t>
-  </si>
-  <si>
-    <t>23:13:26</t>
-  </si>
-  <si>
-    <t>19:18:33</t>
-  </si>
-  <si>
-    <t>20:55:56</t>
-  </si>
-  <si>
-    <t>22:33:19</t>
-  </si>
-  <si>
-    <t>18:38:22</t>
-  </si>
-  <si>
-    <t>20:15:43</t>
-  </si>
-  <si>
-    <t>21:53:07</t>
-  </si>
-  <si>
-    <t>00:58:42</t>
-  </si>
-  <si>
-    <t>21:03:41</t>
-  </si>
-  <si>
-    <t>22:41:44</t>
+    <t>01:13:21</t>
+  </si>
+  <si>
+    <t>19:41:31</t>
+  </si>
+  <si>
+    <t>21:18:45</t>
+  </si>
+  <si>
+    <t>22:56:11</t>
+  </si>
+  <si>
+    <t>00:33:28</t>
+  </si>
+  <si>
+    <t>19:01:35</t>
+  </si>
+  <si>
+    <t>20:38:45</t>
+  </si>
+  <si>
+    <t>22:16:11</t>
+  </si>
+  <si>
+    <t>23:53:30</t>
+  </si>
+  <si>
+    <t>19:58:43</t>
+  </si>
+  <si>
+    <t>21:36:07</t>
+  </si>
+  <si>
+    <t>23:13:28</t>
+  </si>
+  <si>
+    <t>19:18:36</t>
+  </si>
+  <si>
+    <t>20:56:00</t>
+  </si>
+  <si>
+    <t>22:33:23</t>
+  </si>
+  <si>
+    <t>18:38:27</t>
+  </si>
+  <si>
+    <t>20:15:48</t>
+  </si>
+  <si>
+    <t>21:53:12</t>
+  </si>
+  <si>
+    <t>17:58:15</t>
+  </si>
+  <si>
+    <t>19:35:33</t>
+  </si>
+  <si>
+    <t>21:12:58</t>
+  </si>
+  <si>
+    <t>22:50:06</t>
   </si>
   <si>
     <t>00:19:00</t>
@@ -490,133 +499,148 @@
     <t>01:15:01</t>
   </si>
   <si>
-    <t>19:43:18</t>
-  </si>
-  <si>
-    <t>21:21:49</t>
-  </si>
-  <si>
-    <t>22:59:18</t>
-  </si>
-  <si>
-    <t>00:35:33</t>
-  </si>
-  <si>
-    <t>19:02:45</t>
-  </si>
-  <si>
-    <t>20:41:45</t>
-  </si>
-  <si>
-    <t>22:19:20</t>
-  </si>
-  <si>
-    <t>23:55:52</t>
-  </si>
-  <si>
-    <t>20:01:36</t>
-  </si>
-  <si>
-    <t>21:39:16</t>
-  </si>
-  <si>
-    <t>23:16:03</t>
-  </si>
-  <si>
-    <t>19:21:21</t>
-  </si>
-  <si>
-    <t>20:59:08</t>
-  </si>
-  <si>
-    <t>22:36:06</t>
-  </si>
-  <si>
-    <t>18:41:01</t>
-  </si>
-  <si>
-    <t>20:18:55</t>
-  </si>
-  <si>
-    <t>21:56:03</t>
-  </si>
-  <si>
-    <t>01:01:05</t>
-  </si>
-  <si>
-    <t>21:06:17</t>
-  </si>
-  <si>
-    <t>22:44:00</t>
+    <t>19:43:19</t>
+  </si>
+  <si>
+    <t>21:21:50</t>
+  </si>
+  <si>
+    <t>22:59:19</t>
+  </si>
+  <si>
+    <t>00:35:34</t>
+  </si>
+  <si>
+    <t>19:02:46</t>
+  </si>
+  <si>
+    <t>20:41:47</t>
+  </si>
+  <si>
+    <t>22:19:21</t>
+  </si>
+  <si>
+    <t>23:55:54</t>
+  </si>
+  <si>
+    <t>20:01:38</t>
+  </si>
+  <si>
+    <t>21:39:19</t>
+  </si>
+  <si>
+    <t>23:16:06</t>
+  </si>
+  <si>
+    <t>19:21:25</t>
+  </si>
+  <si>
+    <t>20:59:11</t>
+  </si>
+  <si>
+    <t>22:36:10</t>
+  </si>
+  <si>
+    <t>18:41:06</t>
+  </si>
+  <si>
+    <t>20:18:59</t>
+  </si>
+  <si>
+    <t>21:56:07</t>
+  </si>
+  <si>
+    <t>18:00:40</t>
+  </si>
+  <si>
+    <t>19:38:43</t>
+  </si>
+  <si>
+    <t>21:15:59</t>
+  </si>
+  <si>
+    <t>22:51:14</t>
   </si>
   <si>
     <t>00:21:20</t>
   </si>
   <si>
-    <t>01:57:40</t>
-  </si>
-  <si>
-    <t>20:26:19</t>
+    <t>01:57:41</t>
+  </si>
+  <si>
+    <t>20:26:20</t>
   </si>
   <si>
     <t>22:04:06</t>
   </si>
   <si>
-    <t>23:41:30</t>
-  </si>
-  <si>
-    <t>01:18:03</t>
-  </si>
-  <si>
-    <t>19:46:17</t>
-  </si>
-  <si>
-    <t>21:24:08</t>
-  </si>
-  <si>
-    <t>23:01:35</t>
-  </si>
-  <si>
-    <t>00:38:20</t>
-  </si>
-  <si>
-    <t>19:06:09</t>
-  </si>
-  <si>
-    <t>20:44:05</t>
-  </si>
-  <si>
-    <t>22:21:36</t>
-  </si>
-  <si>
-    <t>23:58:30</t>
-  </si>
-  <si>
-    <t>20:03:59</t>
-  </si>
-  <si>
-    <t>21:41:32</t>
-  </si>
-  <si>
-    <t>23:18:34</t>
-  </si>
-  <si>
-    <t>19:23:47</t>
-  </si>
-  <si>
-    <t>21:01:23</t>
-  </si>
-  <si>
-    <t>22:38:32</t>
-  </si>
-  <si>
-    <t>18:43:32</t>
-  </si>
-  <si>
-    <t>20:21:10</t>
-  </si>
-  <si>
-    <t>21:58:25</t>
+    <t>23:41:31</t>
+  </si>
+  <si>
+    <t>01:18:04</t>
+  </si>
+  <si>
+    <t>19:46:18</t>
+  </si>
+  <si>
+    <t>21:24:09</t>
+  </si>
+  <si>
+    <t>23:01:36</t>
+  </si>
+  <si>
+    <t>00:38:21</t>
+  </si>
+  <si>
+    <t>19:06:11</t>
+  </si>
+  <si>
+    <t>20:44:07</t>
+  </si>
+  <si>
+    <t>22:21:37</t>
+  </si>
+  <si>
+    <t>23:58:31</t>
+  </si>
+  <si>
+    <t>20:04:01</t>
+  </si>
+  <si>
+    <t>21:41:34</t>
+  </si>
+  <si>
+    <t>23:18:36</t>
+  </si>
+  <si>
+    <t>19:23:51</t>
+  </si>
+  <si>
+    <t>21:01:27</t>
+  </si>
+  <si>
+    <t>22:38:36</t>
+  </si>
+  <si>
+    <t>18:43:37</t>
+  </si>
+  <si>
+    <t>20:21:15</t>
+  </si>
+  <si>
+    <t>21:58:30</t>
+  </si>
+  <si>
+    <t>18:03:18</t>
+  </si>
+  <si>
+    <t>19:40:59</t>
+  </si>
+  <si>
+    <t>21:18:19</t>
+  </si>
+  <si>
+    <t>22:54:40</t>
   </si>
   <si>
     <t>0°</t>
@@ -637,28 +661,46 @@
     <t>9°</t>
   </si>
   <si>
-    <t>19:36:32</t>
-  </si>
-  <si>
-    <t>18:59:03</t>
-  </si>
-  <si>
-    <t>19:54:51</t>
-  </si>
-  <si>
-    <t>19:16:56</t>
-  </si>
-  <si>
-    <t>18:38:51</t>
-  </si>
-  <si>
-    <t>20:12:19</t>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>19:36:33</t>
+  </si>
+  <si>
+    <t>18:59:05</t>
+  </si>
+  <si>
+    <t>19:54:53</t>
+  </si>
+  <si>
+    <t>19:17:00</t>
+  </si>
+  <si>
+    <t>18:38:56</t>
+  </si>
+  <si>
+    <t>20:12:23</t>
+  </si>
+  <si>
+    <t>18:00:42</t>
+  </si>
+  <si>
+    <t>19:34:09</t>
+  </si>
+  <si>
+    <t>21:07:35</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>3</t>
@@ -701,7 +743,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -711,30 +753,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,7 +776,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,7 +818,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,73 +860,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -970,9 +1006,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1376,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1454,55 +1487,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.2</v>
+        <v>-40.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="O2" s="6">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="P2" s="7">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>82</v>
-      </c>
-      <c r="R2" s="9">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1510,55 +1543,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L3" s="4">
-        <v>-34.8</v>
+        <v>-31.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O3" s="10">
-        <v>2</v>
-      </c>
-      <c r="P3" s="11">
+        <v>230</v>
+      </c>
+      <c r="O3" s="6">
+        <v>12</v>
+      </c>
+      <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>2</v>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1566,55 +1599,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L4" s="4">
-        <v>-41.8</v>
+        <v>-29.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O4" s="10">
+        <v>229</v>
+      </c>
+      <c r="O4" s="9">
+        <v>45</v>
+      </c>
+      <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="P4" s="11">
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="11">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
-        <v>0</v>
+      <c r="R4" s="10">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1622,55 +1655,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L5" s="4">
-        <v>-40.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>0</v>
+        <v>229</v>
+      </c>
+      <c r="O5" s="11">
+        <v>82</v>
+      </c>
+      <c r="P5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>13</v>
+      </c>
+      <c r="R5" s="13">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1678,55 +1711,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L6" s="4">
-        <v>-31.8</v>
+        <v>-41.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O6" s="10">
-        <v>3</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12">
-        <v>3</v>
+        <v>229</v>
+      </c>
+      <c r="O6" s="11">
+        <v>100</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>69</v>
+      </c>
+      <c r="R6" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1734,55 +1767,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L7" s="4">
-        <v>-29.9</v>
+        <v>-35.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>55</v>
-      </c>
-      <c r="R7" s="14">
-        <v>100</v>
+        <v>230</v>
+      </c>
+      <c r="O7" s="11">
+        <v>96</v>
+      </c>
+      <c r="P7" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>85</v>
+      </c>
+      <c r="R7" s="17">
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1790,55 +1823,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="L8" s="4">
-        <v>-39.4</v>
+        <v>-24.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O8" s="6">
-        <v>95</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>49</v>
-      </c>
-      <c r="R8" s="16">
-        <v>94</v>
+        <v>230</v>
+      </c>
+      <c r="O8" s="11">
+        <v>97</v>
+      </c>
+      <c r="P8" s="18">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>36</v>
+      </c>
+      <c r="R8" s="17">
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1846,55 +1879,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-35.9</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="O9" s="11">
+        <v>92</v>
+      </c>
+      <c r="P9" s="16">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>7</v>
+      </c>
+      <c r="R9" s="14">
         <v>68</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-41.7</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O9" s="6">
-        <v>95</v>
-      </c>
-      <c r="P9" s="17">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>76</v>
-      </c>
-      <c r="R9" s="18">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1902,55 +1935,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10" s="4">
-        <v>-35.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O10" s="6">
+        <v>229</v>
+      </c>
+      <c r="O10" s="11">
         <v>100</v>
       </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>86</v>
-      </c>
-      <c r="R10" s="13">
-        <v>56</v>
+      <c r="P10" s="15">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>29</v>
+      </c>
+      <c r="R10" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1958,55 +1991,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="L11" s="4">
-        <v>-24.2</v>
+        <v>-38.7</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O11" s="6">
-        <v>97</v>
-      </c>
-      <c r="P11" s="20">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>83</v>
-      </c>
-      <c r="R11" s="21">
-        <v>72</v>
+        <v>229</v>
+      </c>
+      <c r="O11" s="11">
+        <v>100</v>
+      </c>
+      <c r="P11" s="15">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>65</v>
+      </c>
+      <c r="R11" s="15">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2014,55 +2047,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>81</v>
+        <v>218</v>
       </c>
       <c r="L12" s="4">
-        <v>-35.9</v>
+        <v>-18.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O12" s="6">
-        <v>90</v>
-      </c>
-      <c r="P12" s="20">
-        <v>65</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>8</v>
-      </c>
-      <c r="R12" s="13">
-        <v>55</v>
+        <v>230</v>
+      </c>
+      <c r="O12" s="11">
+        <v>98</v>
+      </c>
+      <c r="P12" s="22">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>94</v>
+      </c>
+      <c r="R12" s="10">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2070,55 +2103,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L13" s="4">
-        <v>-41.5</v>
+        <v>-31.3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O13" s="6">
-        <v>99</v>
-      </c>
-      <c r="P13" s="20">
-        <v>64</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>3</v>
-      </c>
-      <c r="R13" s="16">
-        <v>95</v>
+        <v>229</v>
+      </c>
+      <c r="O13" s="11">
+        <v>100</v>
+      </c>
+      <c r="P13" s="17">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>98</v>
+      </c>
+      <c r="R13" s="23">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2126,55 +2159,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L14" s="4">
-        <v>-38.7</v>
+        <v>-39.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O14" s="6">
-        <v>100</v>
+        <v>229</v>
+      </c>
+      <c r="O14" s="11">
+        <v>99</v>
       </c>
       <c r="P14" s="13">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="22">
-        <v>36</v>
-      </c>
-      <c r="R14" s="23">
-        <v>20</v>
+        <v>97</v>
+      </c>
+      <c r="R14" s="24">
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2182,55 +2215,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="L15" s="4">
-        <v>-18.2</v>
+        <v>-40.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O15" s="6">
+        <v>229</v>
+      </c>
+      <c r="O15" s="11">
         <v>100</v>
       </c>
-      <c r="P15" s="16">
-        <v>93</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>96</v>
-      </c>
-      <c r="R15" s="24">
-        <v>31</v>
+      <c r="P15" s="21">
+        <v>66</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>95</v>
+      </c>
+      <c r="R15" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2238,55 +2271,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="L16" s="4">
-        <v>-31.3</v>
+        <v>-26</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O16" s="6">
-        <v>99</v>
-      </c>
-      <c r="P16" s="19">
-        <v>85</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>97</v>
-      </c>
-      <c r="R16" s="12">
-        <v>6</v>
+        <v>229</v>
+      </c>
+      <c r="O16" s="11">
+        <v>75</v>
+      </c>
+      <c r="P16" s="25">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>74</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2294,55 +2327,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L17" s="4">
-        <v>-39.7</v>
+        <v>-36.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O17" s="6">
-        <v>100</v>
-      </c>
-      <c r="P17" s="19">
-        <v>83</v>
-      </c>
-      <c r="Q17" s="25">
-        <v>92</v>
-      </c>
-      <c r="R17" s="22">
-        <v>34</v>
+        <v>229</v>
+      </c>
+      <c r="O17" s="11">
+        <v>66</v>
+      </c>
+      <c r="P17" s="24">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="21">
+        <v>66</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2350,55 +2383,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L18" s="4">
-        <v>-40.5</v>
+        <v>-40.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O18" s="6">
-        <v>100</v>
-      </c>
-      <c r="P18" s="21">
-        <v>70</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>78</v>
-      </c>
-      <c r="R18" s="20">
+        <v>229</v>
+      </c>
+      <c r="O18" s="11">
+        <v>86</v>
+      </c>
+      <c r="P18" s="24">
+        <v>55</v>
+      </c>
+      <c r="Q18" s="21">
         <v>67</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2406,55 +2439,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L19" s="4">
-        <v>-25.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O19" s="6">
-        <v>88</v>
-      </c>
-      <c r="P19" s="20">
-        <v>66</v>
-      </c>
-      <c r="Q19" s="18">
-        <v>73</v>
-      </c>
-      <c r="R19" s="11">
+        <v>231</v>
+      </c>
+      <c r="O19" s="9">
+        <v>42</v>
+      </c>
+      <c r="P19" s="23">
+        <v>39</v>
+      </c>
+      <c r="Q19" s="7">
         <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2465,52 +2498,52 @@
         <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L20" s="4">
-        <v>-36.7</v>
+        <v>-32.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O20" s="6">
-        <v>90</v>
-      </c>
-      <c r="P20" s="15">
-        <v>49</v>
-      </c>
-      <c r="Q20" s="23">
-        <v>20</v>
-      </c>
-      <c r="R20" s="11">
+        <v>229</v>
+      </c>
+      <c r="O20" s="9">
+        <v>37</v>
+      </c>
+      <c r="P20" s="20">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="7">
         <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2518,55 +2551,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L21" s="4">
-        <v>-40.8</v>
+        <v>-39.7</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="O21" s="6">
-        <v>82</v>
-      </c>
-      <c r="P21" s="13">
-        <v>57</v>
-      </c>
-      <c r="Q21" s="17">
+        <v>18</v>
+      </c>
+      <c r="P21" s="26">
         <v>12</v>
       </c>
-      <c r="R21" s="11">
+      <c r="Q21" s="7">
         <v>0</v>
+      </c>
+      <c r="R21" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2574,54 +2607,54 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="L22" s="4">
-        <v>-20.2</v>
+        <v>-14</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O22" s="26">
-        <v>28</v>
-      </c>
-      <c r="P22" s="27">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="11">
+        <v>231</v>
+      </c>
+      <c r="O22" s="6">
+        <v>7</v>
+      </c>
+      <c r="P22" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="7">
         <v>0</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2633,51 +2666,51 @@
         <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>92</v>
+        <v>222</v>
       </c>
       <c r="L23" s="4">
-        <v>-32.6</v>
+        <v>-27.6</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O23" s="26">
-        <v>18</v>
-      </c>
-      <c r="P23" s="28">
-        <v>17</v>
-      </c>
-      <c r="Q23" s="11">
+        <v>229</v>
+      </c>
+      <c r="O23" s="6">
+        <v>3</v>
+      </c>
+      <c r="P23" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="7">
         <v>0</v>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2686,54 +2719,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L24" s="4">
-        <v>-39.7</v>
+        <v>-37.3</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O24" s="10">
-        <v>8</v>
-      </c>
-      <c r="P24" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q24" s="11">
+        <v>229</v>
+      </c>
+      <c r="O24" s="6">
+        <v>1</v>
+      </c>
+      <c r="P24" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="7">
         <v>0</v>
       </c>
-      <c r="R24" s="11">
+      <c r="R24" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2742,54 +2775,54 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="L25" s="4">
-        <v>-14</v>
+        <v>-7.6</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="10">
-        <v>3</v>
-      </c>
-      <c r="P25" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="11">
+        <v>231</v>
+      </c>
+      <c r="O25" s="9">
+        <v>24</v>
+      </c>
+      <c r="P25" s="27">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="7">
         <v>0</v>
       </c>
-      <c r="R25" s="11">
+      <c r="R25" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2798,54 +2831,54 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="L26" s="4">
-        <v>-27.6</v>
+        <v>-22</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O26" s="10">
-        <v>1</v>
-      </c>
-      <c r="P26" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="11">
+        <v>231</v>
+      </c>
+      <c r="O26" s="6">
+        <v>10</v>
+      </c>
+      <c r="P26" s="26">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="7">
         <v>0</v>
       </c>
-      <c r="R26" s="11">
+      <c r="R26" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2854,114 +2887,170 @@
         <v>43</v>
       </c>
       <c r="B27" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>96</v>
+        <v>225</v>
       </c>
       <c r="L27" s="4">
-        <v>-37.3</v>
+        <v>-33.5</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O27" s="10">
+        <v>229</v>
+      </c>
+      <c r="O27" s="6">
+        <v>3</v>
+      </c>
+      <c r="P27" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="7">
         <v>1</v>
       </c>
-      <c r="P27" s="11">
+      <c r="R27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="2">
+        <v>11</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L28" s="4">
+        <v>-39.4</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="O28" s="6">
+        <v>3</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="7">
         <v>1</v>
       </c>
-      <c r="Q27" s="11">
-        <v>0</v>
-      </c>
-      <c r="R27" s="11">
+      <c r="R28" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A28">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B28">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C28">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D28">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E28">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F28">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G28">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H28">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I28">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K28">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L28">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2980,12 +3069,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M28">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N28">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3002,22 +3091,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O28">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P28">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q28">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R28">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="219">
   <si>
     <t>Datum</t>
   </si>
@@ -70,21 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260313--01</t>
-  </si>
-  <si>
-    <t>20260313--02</t>
-  </si>
-  <si>
-    <t>20260313--03</t>
-  </si>
-  <si>
-    <t>20260313--04</t>
-  </si>
-  <si>
-    <t>20260313--05</t>
-  </si>
-  <si>
     <t>20260314--01</t>
   </si>
   <si>
@@ -151,25 +136,19 @@
     <t>20260319--04</t>
   </si>
   <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>01:55</t>
-  </si>
-  <si>
-    <t>04:22</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>20260320--01</t>
+  </si>
+  <si>
+    <t>20260320--02</t>
+  </si>
+  <si>
+    <t>20260320--03</t>
   </si>
   <si>
     <t>03:21</t>
   </si>
   <si>
-    <t>03:36</t>
+    <t>03:35</t>
   </si>
   <si>
     <t>06:11</t>
@@ -178,13 +157,13 @@
     <t>06:15</t>
   </si>
   <si>
-    <t>04:13</t>
+    <t>04:12</t>
   </si>
   <si>
     <t>02:21</t>
   </si>
   <si>
-    <t>06:03</t>
+    <t>06:02</t>
   </si>
   <si>
     <t>06:20</t>
@@ -193,226 +172,199 @@
     <t>04:48</t>
   </si>
   <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
     <t>05:51</t>
   </si>
   <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
     <t>04:50</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>02:16</t>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:33</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>03:07</t>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>03:06</t>
   </si>
   <si>
     <t>01:46</t>
   </si>
   <si>
-    <t>00:10:39</t>
-  </si>
-  <si>
-    <t>01:48:37</t>
-  </si>
-  <si>
-    <t>20:16:28</t>
-  </si>
-  <si>
-    <t>21:53:16</t>
-  </si>
-  <si>
-    <t>23:30:44</t>
-  </si>
-  <si>
-    <t>01:08:36</t>
-  </si>
-  <si>
-    <t>19:36:45</t>
-  </si>
-  <si>
-    <t>21:13:21</t>
-  </si>
-  <si>
-    <t>22:50:46</t>
-  </si>
-  <si>
-    <t>00:28:33</t>
-  </si>
-  <si>
-    <t>18:57:01</t>
-  </si>
-  <si>
-    <t>20:33:24</t>
-  </si>
-  <si>
-    <t>22:10:45</t>
-  </si>
-  <si>
-    <t>23:48:28</t>
-  </si>
-  <si>
-    <t>19:53:25</t>
-  </si>
-  <si>
-    <t>21:30:40</t>
-  </si>
-  <si>
-    <t>23:08:20</t>
-  </si>
-  <si>
-    <t>19:13:23</t>
-  </si>
-  <si>
-    <t>20:50:32</t>
-  </si>
-  <si>
-    <t>22:28:08</t>
-  </si>
-  <si>
-    <t>18:33:19</t>
-  </si>
-  <si>
-    <t>20:10:21</t>
-  </si>
-  <si>
-    <t>21:47:54</t>
-  </si>
-  <si>
-    <t>17:53:13</t>
-  </si>
-  <si>
-    <t>19:30:07</t>
-  </si>
-  <si>
-    <t>21:07:37</t>
-  </si>
-  <si>
-    <t>22:45:32</t>
-  </si>
-  <si>
-    <t>00:12:59</t>
-  </si>
-  <si>
-    <t>01:52:12</t>
-  </si>
-  <si>
-    <t>20:19:13</t>
-  </si>
-  <si>
-    <t>21:55:32</t>
-  </si>
-  <si>
-    <t>23:33:03</t>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>01:08:37</t>
+  </si>
+  <si>
+    <t>19:36:46</t>
+  </si>
+  <si>
+    <t>21:13:22</t>
+  </si>
+  <si>
+    <t>22:50:47</t>
+  </si>
+  <si>
+    <t>00:28:34</t>
+  </si>
+  <si>
+    <t>18:57:02</t>
+  </si>
+  <si>
+    <t>20:33:25</t>
+  </si>
+  <si>
+    <t>22:10:46</t>
+  </si>
+  <si>
+    <t>23:48:29</t>
+  </si>
+  <si>
+    <t>19:53:26</t>
+  </si>
+  <si>
+    <t>21:30:42</t>
+  </si>
+  <si>
+    <t>23:08:21</t>
+  </si>
+  <si>
+    <t>19:13:25</t>
+  </si>
+  <si>
+    <t>20:50:34</t>
+  </si>
+  <si>
+    <t>22:28:10</t>
+  </si>
+  <si>
+    <t>18:33:21</t>
+  </si>
+  <si>
+    <t>20:10:24</t>
+  </si>
+  <si>
+    <t>21:47:57</t>
+  </si>
+  <si>
+    <t>17:53:16</t>
+  </si>
+  <si>
+    <t>19:30:10</t>
+  </si>
+  <si>
+    <t>21:07:40</t>
+  </si>
+  <si>
+    <t>22:45:36</t>
+  </si>
+  <si>
+    <t>18:49:54</t>
+  </si>
+  <si>
+    <t>20:27:20</t>
+  </si>
+  <si>
+    <t>22:05:09</t>
   </si>
   <si>
     <t>01:11:40</t>
   </si>
   <si>
-    <t>19:39:43</t>
-  </si>
-  <si>
-    <t>21:15:39</t>
+    <t>19:39:44</t>
+  </si>
+  <si>
+    <t>21:15:40</t>
   </si>
   <si>
     <t>22:53:04</t>
   </si>
   <si>
-    <t>00:31:21</t>
-  </si>
-  <si>
-    <t>19:00:25</t>
-  </si>
-  <si>
-    <t>20:35:44</t>
-  </si>
-  <si>
-    <t>22:13:01</t>
-  </si>
-  <si>
-    <t>23:51:06</t>
-  </si>
-  <si>
-    <t>19:55:47</t>
-  </si>
-  <si>
-    <t>21:32:56</t>
-  </si>
-  <si>
-    <t>23:10:51</t>
-  </si>
-  <si>
-    <t>19:15:48</t>
-  </si>
-  <si>
-    <t>20:52:48</t>
-  </si>
-  <si>
-    <t>22:30:35</t>
-  </si>
-  <si>
-    <t>18:35:49</t>
-  </si>
-  <si>
-    <t>20:12:37</t>
-  </si>
-  <si>
-    <t>21:50:17</t>
-  </si>
-  <si>
-    <t>17:55:50</t>
-  </si>
-  <si>
-    <t>19:32:23</t>
-  </si>
-  <si>
-    <t>21:09:57</t>
-  </si>
-  <si>
-    <t>22:48:58</t>
-  </si>
-  <si>
-    <t>00:16:00</t>
-  </si>
-  <si>
-    <t>01:53:09</t>
-  </si>
-  <si>
-    <t>20:21:23</t>
-  </si>
-  <si>
-    <t>21:58:41</t>
-  </si>
-  <si>
-    <t>23:36:07</t>
+    <t>00:31:22</t>
+  </si>
+  <si>
+    <t>19:00:26</t>
+  </si>
+  <si>
+    <t>20:35:45</t>
+  </si>
+  <si>
+    <t>22:13:02</t>
+  </si>
+  <si>
+    <t>23:51:07</t>
+  </si>
+  <si>
+    <t>19:55:48</t>
+  </si>
+  <si>
+    <t>21:32:57</t>
+  </si>
+  <si>
+    <t>23:10:52</t>
+  </si>
+  <si>
+    <t>19:15:50</t>
+  </si>
+  <si>
+    <t>20:52:50</t>
+  </si>
+  <si>
+    <t>22:30:36</t>
+  </si>
+  <si>
+    <t>18:35:52</t>
+  </si>
+  <si>
+    <t>20:12:39</t>
+  </si>
+  <si>
+    <t>21:50:19</t>
+  </si>
+  <si>
+    <t>17:55:53</t>
+  </si>
+  <si>
+    <t>19:32:26</t>
+  </si>
+  <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
+    <t>22:49:02</t>
+  </si>
+  <si>
+    <t>18:52:11</t>
+  </si>
+  <si>
+    <t>20:29:38</t>
+  </si>
+  <si>
+    <t>22:08:09</t>
   </si>
   <si>
     <t>01:13:21</t>
@@ -424,76 +376,70 @@
     <t>21:18:45</t>
   </si>
   <si>
-    <t>22:56:11</t>
+    <t>22:56:12</t>
   </si>
   <si>
     <t>00:33:28</t>
   </si>
   <si>
-    <t>19:01:35</t>
-  </si>
-  <si>
-    <t>20:38:45</t>
-  </si>
-  <si>
-    <t>22:16:11</t>
-  </si>
-  <si>
-    <t>23:53:30</t>
-  </si>
-  <si>
-    <t>19:58:43</t>
-  </si>
-  <si>
-    <t>21:36:07</t>
-  </si>
-  <si>
-    <t>23:13:28</t>
-  </si>
-  <si>
-    <t>19:18:36</t>
-  </si>
-  <si>
-    <t>20:56:00</t>
-  </si>
-  <si>
-    <t>22:33:23</t>
-  </si>
-  <si>
-    <t>18:38:27</t>
-  </si>
-  <si>
-    <t>20:15:48</t>
-  </si>
-  <si>
-    <t>21:53:12</t>
-  </si>
-  <si>
-    <t>17:58:15</t>
-  </si>
-  <si>
-    <t>19:35:33</t>
-  </si>
-  <si>
-    <t>21:12:58</t>
-  </si>
-  <si>
-    <t>22:50:06</t>
-  </si>
-  <si>
-    <t>00:19:00</t>
-  </si>
-  <si>
-    <t>01:54:07</t>
-  </si>
-  <si>
-    <t>20:23:35</t>
-  </si>
-  <si>
-    <t>22:01:49</t>
-  </si>
-  <si>
-    <t>23:39:12</t>
+    <t>19:01:36</t>
+  </si>
+  <si>
+    <t>20:38:46</t>
+  </si>
+  <si>
+    <t>22:16:12</t>
+  </si>
+  <si>
+    <t>23:53:31</t>
+  </si>
+  <si>
+    <t>19:58:44</t>
+  </si>
+  <si>
+    <t>21:36:09</t>
+  </si>
+  <si>
+    <t>23:13:30</t>
+  </si>
+  <si>
+    <t>19:18:38</t>
+  </si>
+  <si>
+    <t>20:56:01</t>
+  </si>
+  <si>
+    <t>22:33:24</t>
+  </si>
+  <si>
+    <t>18:38:29</t>
+  </si>
+  <si>
+    <t>20:15:50</t>
+  </si>
+  <si>
+    <t>21:53:14</t>
+  </si>
+  <si>
+    <t>17:58:18</t>
+  </si>
+  <si>
+    <t>19:35:36</t>
+  </si>
+  <si>
+    <t>21:13:01</t>
+  </si>
+  <si>
+    <t>22:50:10</t>
+  </si>
+  <si>
+    <t>18:55:18</t>
+  </si>
+  <si>
+    <t>20:32:43</t>
+  </si>
+  <si>
+    <t>22:09:56</t>
   </si>
   <si>
     <t>01:15:01</t>
@@ -502,7 +448,7 @@
     <t>19:43:19</t>
   </si>
   <si>
-    <t>21:21:50</t>
+    <t>21:21:51</t>
   </si>
   <si>
     <t>22:59:19</t>
@@ -511,70 +457,64 @@
     <t>00:35:34</t>
   </si>
   <si>
-    <t>19:02:46</t>
+    <t>19:02:47</t>
   </si>
   <si>
     <t>20:41:47</t>
   </si>
   <si>
-    <t>22:19:21</t>
-  </si>
-  <si>
-    <t>23:55:54</t>
-  </si>
-  <si>
-    <t>20:01:38</t>
-  </si>
-  <si>
-    <t>21:39:19</t>
-  </si>
-  <si>
-    <t>23:16:06</t>
-  </si>
-  <si>
-    <t>19:21:25</t>
-  </si>
-  <si>
-    <t>20:59:11</t>
-  </si>
-  <si>
-    <t>22:36:10</t>
-  </si>
-  <si>
-    <t>18:41:06</t>
-  </si>
-  <si>
-    <t>20:18:59</t>
-  </si>
-  <si>
-    <t>21:56:07</t>
-  </si>
-  <si>
-    <t>18:00:40</t>
-  </si>
-  <si>
-    <t>19:38:43</t>
-  </si>
-  <si>
-    <t>21:15:59</t>
-  </si>
-  <si>
-    <t>22:51:14</t>
-  </si>
-  <si>
-    <t>00:21:20</t>
-  </si>
-  <si>
-    <t>01:57:41</t>
-  </si>
-  <si>
-    <t>20:26:20</t>
-  </si>
-  <si>
-    <t>22:04:06</t>
-  </si>
-  <si>
-    <t>23:41:31</t>
+    <t>22:19:22</t>
+  </si>
+  <si>
+    <t>23:55:55</t>
+  </si>
+  <si>
+    <t>20:01:40</t>
+  </si>
+  <si>
+    <t>21:39:20</t>
+  </si>
+  <si>
+    <t>23:16:07</t>
+  </si>
+  <si>
+    <t>19:21:27</t>
+  </si>
+  <si>
+    <t>20:59:13</t>
+  </si>
+  <si>
+    <t>22:36:12</t>
+  </si>
+  <si>
+    <t>18:41:08</t>
+  </si>
+  <si>
+    <t>20:19:02</t>
+  </si>
+  <si>
+    <t>21:56:10</t>
+  </si>
+  <si>
+    <t>18:00:43</t>
+  </si>
+  <si>
+    <t>19:38:46</t>
+  </si>
+  <si>
+    <t>21:16:02</t>
+  </si>
+  <si>
+    <t>22:51:17</t>
+  </si>
+  <si>
+    <t>18:58:26</t>
+  </si>
+  <si>
+    <t>20:35:49</t>
+  </si>
+  <si>
+    <t>22:11:42</t>
   </si>
   <si>
     <t>01:18:04</t>
@@ -586,7 +526,7 @@
     <t>21:24:09</t>
   </si>
   <si>
-    <t>23:01:36</t>
+    <t>23:01:37</t>
   </si>
   <si>
     <t>00:38:21</t>
@@ -595,52 +535,61 @@
     <t>19:06:11</t>
   </si>
   <si>
-    <t>20:44:07</t>
-  </si>
-  <si>
-    <t>22:21:37</t>
-  </si>
-  <si>
-    <t>23:58:31</t>
-  </si>
-  <si>
-    <t>20:04:01</t>
-  </si>
-  <si>
-    <t>21:41:34</t>
-  </si>
-  <si>
-    <t>23:18:36</t>
-  </si>
-  <si>
-    <t>19:23:51</t>
-  </si>
-  <si>
-    <t>21:01:27</t>
-  </si>
-  <si>
-    <t>22:38:36</t>
-  </si>
-  <si>
-    <t>18:43:37</t>
-  </si>
-  <si>
-    <t>20:21:15</t>
-  </si>
-  <si>
-    <t>21:58:30</t>
-  </si>
-  <si>
-    <t>18:03:18</t>
-  </si>
-  <si>
-    <t>19:40:59</t>
-  </si>
-  <si>
-    <t>21:18:19</t>
-  </si>
-  <si>
-    <t>22:54:40</t>
+    <t>20:44:08</t>
+  </si>
+  <si>
+    <t>22:21:38</t>
+  </si>
+  <si>
+    <t>23:58:32</t>
+  </si>
+  <si>
+    <t>20:04:02</t>
+  </si>
+  <si>
+    <t>21:41:35</t>
+  </si>
+  <si>
+    <t>23:18:37</t>
+  </si>
+  <si>
+    <t>19:23:53</t>
+  </si>
+  <si>
+    <t>21:01:28</t>
+  </si>
+  <si>
+    <t>22:38:37</t>
+  </si>
+  <si>
+    <t>18:43:39</t>
+  </si>
+  <si>
+    <t>20:21:17</t>
+  </si>
+  <si>
+    <t>21:58:32</t>
+  </si>
+  <si>
+    <t>18:03:21</t>
+  </si>
+  <si>
+    <t>19:41:02</t>
+  </si>
+  <si>
+    <t>21:18:22</t>
+  </si>
+  <si>
+    <t>22:54:43</t>
+  </si>
+  <si>
+    <t>19:00:43</t>
+  </si>
+  <si>
+    <t>20:38:07</t>
+  </si>
+  <si>
+    <t>22:14:41</t>
   </si>
   <si>
     <t>0°</t>
@@ -667,31 +616,43 @@
     <t>23°</t>
   </si>
   <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
     <t>19:36:33</t>
   </si>
   <si>
     <t>18:59:05</t>
   </si>
   <si>
-    <t>19:54:53</t>
-  </si>
-  <si>
-    <t>19:17:00</t>
-  </si>
-  <si>
-    <t>18:38:56</t>
-  </si>
-  <si>
-    <t>20:12:23</t>
-  </si>
-  <si>
-    <t>18:00:42</t>
-  </si>
-  <si>
-    <t>19:34:09</t>
-  </si>
-  <si>
-    <t>21:07:35</t>
+    <t>19:54:54</t>
+  </si>
+  <si>
+    <t>19:17:01</t>
+  </si>
+  <si>
+    <t>18:38:58</t>
+  </si>
+  <si>
+    <t>20:12:25</t>
+  </si>
+  <si>
+    <t>18:00:45</t>
+  </si>
+  <si>
+    <t>19:34:12</t>
+  </si>
+  <si>
+    <t>21:07:38</t>
+  </si>
+  <si>
+    <t>18:55:50</t>
+  </si>
+  <si>
+    <t>20:29:16</t>
   </si>
   <si>
     <t>B</t>
@@ -703,10 +664,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -743,7 +704,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -753,36 +714,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,13 +731,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,19 +773,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -842,49 +851,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1006,6 +973,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1409,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1487,55 +1457,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L2" s="4">
-        <v>-40.6</v>
+        <v>-35.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>85</v>
+      </c>
+      <c r="R2" s="9">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1543,55 +1513,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="L3" s="4">
-        <v>-31.8</v>
+        <v>-24.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="O3" s="6">
-        <v>12</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="P3" s="10">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>85</v>
+      </c>
+      <c r="R3" s="9">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1599,55 +1569,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L4" s="4">
-        <v>-29.9</v>
+        <v>-35.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O4" s="9">
-        <v>45</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="10">
-        <v>45</v>
+        <v>217</v>
+      </c>
+      <c r="O4" s="6">
+        <v>99</v>
+      </c>
+      <c r="P4" s="9">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>79</v>
+      </c>
+      <c r="R4" s="8">
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1658,52 +1628,52 @@
         <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.4</v>
+        <v>-41.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O5" s="11">
-        <v>82</v>
-      </c>
-      <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>13</v>
-      </c>
-      <c r="R5" s="13">
-        <v>82</v>
+        <v>217</v>
+      </c>
+      <c r="O5" s="6">
+        <v>99</v>
+      </c>
+      <c r="P5" s="8">
+        <v>86</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>54</v>
+      </c>
+      <c r="R5" s="12">
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1711,54 +1681,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="L6" s="4">
-        <v>-41.7</v>
+        <v>-38.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O6" s="11">
+        <v>217</v>
+      </c>
+      <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>69</v>
-      </c>
-      <c r="R6" s="15">
+      <c r="P6" s="12">
+        <v>96</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>77</v>
+      </c>
+      <c r="R6" s="14">
         <v>100</v>
       </c>
     </row>
@@ -1767,55 +1737,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="L7" s="4">
-        <v>-35.8</v>
+        <v>-18.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O7" s="11">
-        <v>96</v>
-      </c>
-      <c r="P7" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>85</v>
-      </c>
-      <c r="R7" s="17">
-        <v>90</v>
+        <v>216</v>
+      </c>
+      <c r="O7" s="6">
+        <v>100</v>
+      </c>
+      <c r="P7" s="15">
+        <v>59</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>100</v>
+      </c>
+      <c r="R7" s="10">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1823,55 +1793,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-31.3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="4">
-        <v>-24.2</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O8" s="11">
-        <v>97</v>
-      </c>
-      <c r="P8" s="18">
-        <v>76</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>36</v>
-      </c>
-      <c r="R8" s="17">
-        <v>90</v>
+      <c r="O8" s="6">
+        <v>99</v>
+      </c>
+      <c r="P8" s="15">
+        <v>61</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>94</v>
+      </c>
+      <c r="R8" s="8">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1879,55 +1849,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L9" s="4">
-        <v>-35.9</v>
+        <v>-39.7</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O9" s="11">
-        <v>92</v>
-      </c>
-      <c r="P9" s="16">
+        <v>217</v>
+      </c>
+      <c r="O9" s="6">
+        <v>98</v>
+      </c>
+      <c r="P9" s="8">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="8">
         <v>87</v>
       </c>
-      <c r="Q9" s="8">
-        <v>7</v>
-      </c>
-      <c r="R9" s="14">
-        <v>68</v>
+      <c r="R9" s="9">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1935,55 +1905,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-40.5</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O10" s="6">
+        <v>98</v>
+      </c>
+      <c r="P10" s="9">
         <v>82</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-41.5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O10" s="11">
-        <v>100</v>
-      </c>
-      <c r="P10" s="15">
-        <v>98</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>29</v>
-      </c>
-      <c r="R10" s="15">
-        <v>100</v>
+      <c r="Q10" s="9">
+        <v>79</v>
+      </c>
+      <c r="R10" s="9">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1991,55 +1961,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="L11" s="4">
-        <v>-38.7</v>
+        <v>-26</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O11" s="11">
-        <v>100</v>
-      </c>
-      <c r="P11" s="15">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>65</v>
-      </c>
-      <c r="R11" s="15">
-        <v>99</v>
+        <v>217</v>
+      </c>
+      <c r="O11" s="6">
+        <v>84</v>
+      </c>
+      <c r="P11" s="16">
+        <v>51</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>56</v>
+      </c>
+      <c r="R11" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2047,55 +2017,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="L12" s="4">
-        <v>-18.2</v>
+        <v>-36.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O12" s="11">
-        <v>98</v>
-      </c>
-      <c r="P12" s="22">
-        <v>93</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>94</v>
-      </c>
-      <c r="R12" s="10">
+        <v>217</v>
+      </c>
+      <c r="O12" s="6">
+        <v>77</v>
+      </c>
+      <c r="P12" s="11">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="18">
         <v>45</v>
+      </c>
+      <c r="R12" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2103,55 +2073,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L13" s="4">
-        <v>-31.3</v>
+        <v>-40.8</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O13" s="11">
-        <v>100</v>
-      </c>
-      <c r="P13" s="17">
-        <v>89</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>98</v>
-      </c>
-      <c r="R13" s="23">
-        <v>39</v>
+        <v>217</v>
+      </c>
+      <c r="O13" s="6">
+        <v>69</v>
+      </c>
+      <c r="P13" s="15">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>18</v>
+      </c>
+      <c r="R13" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2159,55 +2129,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="L14" s="4">
-        <v>-39.7</v>
+        <v>-20.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O14" s="11">
-        <v>99</v>
-      </c>
-      <c r="P14" s="13">
-        <v>80</v>
-      </c>
-      <c r="Q14" s="22">
-        <v>97</v>
-      </c>
-      <c r="R14" s="24">
-        <v>53</v>
+        <v>218</v>
+      </c>
+      <c r="O14" s="20">
+        <v>8</v>
+      </c>
+      <c r="P14" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>0</v>
+      </c>
+      <c r="R14" s="21">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2215,55 +2185,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L15" s="4">
-        <v>-40.5</v>
+        <v>-32.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O15" s="11">
-        <v>100</v>
-      </c>
-      <c r="P15" s="21">
-        <v>66</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>95</v>
-      </c>
-      <c r="R15" s="15">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O15" s="20">
+        <v>8</v>
+      </c>
+      <c r="P15" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>0</v>
+      </c>
+      <c r="R15" s="17">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2271,54 +2241,54 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="L16" s="4">
-        <v>-26</v>
+        <v>-39.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O16" s="11">
-        <v>75</v>
-      </c>
-      <c r="P16" s="25">
-        <v>52</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>74</v>
-      </c>
-      <c r="R16" s="7">
+        <v>217</v>
+      </c>
+      <c r="O16" s="20">
+        <v>5</v>
+      </c>
+      <c r="P16" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2327,55 +2297,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="L17" s="4">
-        <v>-36.7</v>
+        <v>-14</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O17" s="11">
-        <v>66</v>
-      </c>
-      <c r="P17" s="24">
-        <v>53</v>
-      </c>
-      <c r="Q17" s="21">
-        <v>66</v>
-      </c>
-      <c r="R17" s="7">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="O17" s="6">
+        <v>58</v>
+      </c>
+      <c r="P17" s="18">
+        <v>47</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>23</v>
+      </c>
+      <c r="R17" s="17">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2383,55 +2353,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="L18" s="4">
-        <v>-40.8</v>
+        <v>-27.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O18" s="11">
-        <v>86</v>
-      </c>
-      <c r="P18" s="24">
-        <v>55</v>
-      </c>
-      <c r="Q18" s="21">
-        <v>67</v>
-      </c>
-      <c r="R18" s="7">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O18" s="6">
+        <v>41</v>
+      </c>
+      <c r="P18" s="23">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>41</v>
+      </c>
+      <c r="R18" s="23">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2439,55 +2409,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>220</v>
+        <v>84</v>
       </c>
       <c r="L19" s="4">
-        <v>-20.2</v>
+        <v>-37.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O19" s="9">
-        <v>42</v>
+        <v>217</v>
+      </c>
+      <c r="O19" s="6">
+        <v>51</v>
       </c>
       <c r="P19" s="23">
-        <v>39</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>51</v>
       </c>
       <c r="R19" s="7">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2495,55 +2465,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="L20" s="4">
-        <v>-32.6</v>
+        <v>-7.6</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O20" s="9">
-        <v>37</v>
-      </c>
-      <c r="P20" s="20">
+        <v>218</v>
+      </c>
+      <c r="O20" s="25">
+        <v>33</v>
+      </c>
+      <c r="P20" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="26">
         <v>30</v>
       </c>
-      <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>1</v>
+      <c r="R20" s="27">
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2551,55 +2521,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="L21" s="4">
-        <v>-39.7</v>
+        <v>-22</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O21" s="6">
-        <v>18</v>
-      </c>
-      <c r="P21" s="26">
-        <v>12</v>
-      </c>
-      <c r="Q21" s="7">
+        <v>218</v>
+      </c>
+      <c r="O21" s="20">
+        <v>3</v>
+      </c>
+      <c r="P21" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="17">
         <v>0</v>
       </c>
-      <c r="R21" s="7">
-        <v>1</v>
+      <c r="R21" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2607,54 +2577,54 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-33.5</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-14</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O22" s="6">
-        <v>7</v>
-      </c>
-      <c r="P22" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q22" s="7">
+        <v>217</v>
+      </c>
+      <c r="O22" s="25">
+        <v>32</v>
+      </c>
+      <c r="P22" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="17">
         <v>0</v>
       </c>
-      <c r="R22" s="7">
+      <c r="R22" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2663,55 +2633,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>222</v>
+        <v>88</v>
       </c>
       <c r="L23" s="4">
-        <v>-27.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O23" s="6">
-        <v>3</v>
-      </c>
-      <c r="P23" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="7">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="O23" s="25">
+        <v>41</v>
+      </c>
+      <c r="P23" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="21">
+        <v>5</v>
+      </c>
+      <c r="R23" s="21">
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2719,54 +2689,54 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="L24" s="4">
-        <v>-37.3</v>
+        <v>-16</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="O24" s="6">
-        <v>1</v>
-      </c>
-      <c r="P24" s="7">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="P24" s="28">
+        <v>71</v>
       </c>
       <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7">
+        <v>13</v>
+      </c>
+      <c r="R24" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2775,55 +2745,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="L25" s="4">
-        <v>-7.6</v>
+        <v>-29</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O25" s="9">
+        <v>217</v>
+      </c>
+      <c r="O25" s="6">
+        <v>61</v>
+      </c>
+      <c r="P25" s="18">
+        <v>46</v>
+      </c>
+      <c r="Q25" s="22">
         <v>24</v>
       </c>
-      <c r="P25" s="27">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7">
-        <v>0</v>
+      <c r="R25" s="22">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2831,226 +2801,114 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-37.5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-22</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="O26" s="6">
-        <v>10</v>
-      </c>
-      <c r="P26" s="26">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="P26" s="27">
+        <v>34</v>
       </c>
       <c r="Q26" s="7">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="2">
-        <v>27</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-33.5</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O27" s="6">
-        <v>3</v>
-      </c>
-      <c r="P27" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="7">
-        <v>1</v>
-      </c>
-      <c r="R27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="2">
-        <v>11</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L28" s="4">
-        <v>-39.4</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="O28" s="6">
-        <v>3</v>
-      </c>
-      <c r="P28" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q28" s="7">
-        <v>1</v>
-      </c>
-      <c r="R28" s="7">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="19">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A28">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B28">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C28">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D28">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E28">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F28">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G28">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H28">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I28">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J28">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K28">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L28">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -3069,12 +2927,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M28">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N28">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3091,22 +2949,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O28">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P28">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q28">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R28">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="220">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260314--01</t>
-  </si>
-  <si>
-    <t>20260314--02</t>
-  </si>
-  <si>
-    <t>20260314--03</t>
-  </si>
-  <si>
-    <t>20260314--04</t>
-  </si>
-  <si>
     <t>20260315--01</t>
   </si>
   <si>
@@ -145,61 +133,79 @@
     <t>20260320--03</t>
   </si>
   <si>
-    <t>03:21</t>
-  </si>
-  <si>
-    <t>03:35</t>
+    <t>20260321--01</t>
+  </si>
+  <si>
+    <t>20260321--02</t>
+  </si>
+  <si>
+    <t>20260321--03</t>
+  </si>
+  <si>
+    <t>04:12</t>
+  </si>
+  <si>
+    <t>02:21</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>06:15</t>
   </si>
   <si>
     <t>06:11</t>
   </si>
   <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>04:12</t>
-  </si>
-  <si>
-    <t>02:21</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:33</t>
+    <t>03:34</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>04:23</t>
   </si>
   <si>
     <t>00:00</t>
@@ -217,387 +223,375 @@
     <t>03:39</t>
   </si>
   <si>
-    <t>01:08:37</t>
-  </si>
-  <si>
-    <t>19:36:46</t>
-  </si>
-  <si>
-    <t>21:13:22</t>
-  </si>
-  <si>
-    <t>22:50:47</t>
-  </si>
-  <si>
-    <t>00:28:34</t>
-  </si>
-  <si>
-    <t>18:57:02</t>
-  </si>
-  <si>
-    <t>20:33:25</t>
-  </si>
-  <si>
-    <t>22:10:46</t>
-  </si>
-  <si>
-    <t>23:48:29</t>
-  </si>
-  <si>
-    <t>19:53:26</t>
-  </si>
-  <si>
-    <t>21:30:42</t>
-  </si>
-  <si>
-    <t>23:08:21</t>
-  </si>
-  <si>
-    <t>19:13:25</t>
-  </si>
-  <si>
-    <t>20:50:34</t>
-  </si>
-  <si>
-    <t>22:28:10</t>
-  </si>
-  <si>
-    <t>18:33:21</t>
-  </si>
-  <si>
-    <t>20:10:24</t>
-  </si>
-  <si>
-    <t>21:47:57</t>
-  </si>
-  <si>
-    <t>17:53:16</t>
-  </si>
-  <si>
-    <t>19:30:10</t>
-  </si>
-  <si>
-    <t>21:07:40</t>
-  </si>
-  <si>
-    <t>22:45:36</t>
-  </si>
-  <si>
-    <t>18:49:54</t>
-  </si>
-  <si>
-    <t>20:27:20</t>
-  </si>
-  <si>
-    <t>22:05:09</t>
-  </si>
-  <si>
-    <t>01:11:40</t>
-  </si>
-  <si>
-    <t>19:39:44</t>
-  </si>
-  <si>
-    <t>21:15:40</t>
-  </si>
-  <si>
-    <t>22:53:04</t>
-  </si>
-  <si>
-    <t>00:31:22</t>
-  </si>
-  <si>
-    <t>19:00:26</t>
-  </si>
-  <si>
-    <t>20:35:45</t>
-  </si>
-  <si>
-    <t>22:13:02</t>
-  </si>
-  <si>
-    <t>23:51:07</t>
-  </si>
-  <si>
-    <t>19:55:48</t>
-  </si>
-  <si>
-    <t>21:32:57</t>
-  </si>
-  <si>
-    <t>23:10:52</t>
-  </si>
-  <si>
-    <t>19:15:50</t>
-  </si>
-  <si>
-    <t>20:52:50</t>
-  </si>
-  <si>
-    <t>22:30:36</t>
-  </si>
-  <si>
-    <t>18:35:52</t>
-  </si>
-  <si>
-    <t>20:12:39</t>
-  </si>
-  <si>
-    <t>21:50:19</t>
-  </si>
-  <si>
-    <t>17:55:53</t>
-  </si>
-  <si>
-    <t>19:32:26</t>
-  </si>
-  <si>
-    <t>21:10:00</t>
-  </si>
-  <si>
-    <t>22:49:02</t>
-  </si>
-  <si>
-    <t>18:52:11</t>
-  </si>
-  <si>
-    <t>20:29:38</t>
-  </si>
-  <si>
-    <t>22:08:09</t>
-  </si>
-  <si>
-    <t>01:13:21</t>
-  </si>
-  <si>
-    <t>19:41:31</t>
-  </si>
-  <si>
-    <t>21:18:45</t>
-  </si>
-  <si>
-    <t>22:56:12</t>
-  </si>
-  <si>
-    <t>00:33:28</t>
-  </si>
-  <si>
-    <t>19:01:36</t>
-  </si>
-  <si>
-    <t>20:38:46</t>
-  </si>
-  <si>
-    <t>22:16:12</t>
-  </si>
-  <si>
-    <t>23:53:31</t>
-  </si>
-  <si>
-    <t>19:58:44</t>
-  </si>
-  <si>
-    <t>21:36:09</t>
-  </si>
-  <si>
-    <t>23:13:30</t>
-  </si>
-  <si>
-    <t>19:18:38</t>
-  </si>
-  <si>
-    <t>20:56:01</t>
-  </si>
-  <si>
-    <t>22:33:24</t>
-  </si>
-  <si>
-    <t>18:38:29</t>
-  </si>
-  <si>
-    <t>20:15:50</t>
-  </si>
-  <si>
-    <t>21:53:14</t>
-  </si>
-  <si>
-    <t>17:58:18</t>
-  </si>
-  <si>
-    <t>19:35:36</t>
-  </si>
-  <si>
-    <t>21:13:01</t>
-  </si>
-  <si>
-    <t>22:50:10</t>
-  </si>
-  <si>
-    <t>18:55:18</t>
-  </si>
-  <si>
-    <t>20:32:43</t>
-  </si>
-  <si>
-    <t>22:09:56</t>
-  </si>
-  <si>
-    <t>01:15:01</t>
-  </si>
-  <si>
-    <t>19:43:19</t>
-  </si>
-  <si>
-    <t>21:21:51</t>
-  </si>
-  <si>
-    <t>22:59:19</t>
-  </si>
-  <si>
-    <t>00:35:34</t>
-  </si>
-  <si>
-    <t>19:02:47</t>
-  </si>
-  <si>
-    <t>20:41:47</t>
-  </si>
-  <si>
-    <t>22:19:22</t>
-  </si>
-  <si>
-    <t>23:55:55</t>
-  </si>
-  <si>
-    <t>20:01:40</t>
-  </si>
-  <si>
-    <t>21:39:20</t>
-  </si>
-  <si>
-    <t>23:16:07</t>
-  </si>
-  <si>
-    <t>19:21:27</t>
-  </si>
-  <si>
-    <t>20:59:13</t>
-  </si>
-  <si>
-    <t>22:36:12</t>
-  </si>
-  <si>
-    <t>18:41:08</t>
-  </si>
-  <si>
-    <t>20:19:02</t>
-  </si>
-  <si>
-    <t>21:56:10</t>
-  </si>
-  <si>
-    <t>18:00:43</t>
-  </si>
-  <si>
-    <t>19:38:46</t>
-  </si>
-  <si>
-    <t>21:16:02</t>
-  </si>
-  <si>
-    <t>22:51:17</t>
-  </si>
-  <si>
-    <t>18:58:26</t>
-  </si>
-  <si>
-    <t>20:35:49</t>
-  </si>
-  <si>
-    <t>22:11:42</t>
-  </si>
-  <si>
-    <t>01:18:04</t>
-  </si>
-  <si>
-    <t>19:46:18</t>
-  </si>
-  <si>
-    <t>21:24:09</t>
-  </si>
-  <si>
-    <t>23:01:37</t>
-  </si>
-  <si>
-    <t>00:38:21</t>
-  </si>
-  <si>
-    <t>19:06:11</t>
-  </si>
-  <si>
-    <t>20:44:08</t>
-  </si>
-  <si>
-    <t>22:21:38</t>
-  </si>
-  <si>
-    <t>23:58:32</t>
-  </si>
-  <si>
-    <t>20:04:02</t>
-  </si>
-  <si>
-    <t>21:41:35</t>
-  </si>
-  <si>
-    <t>23:18:37</t>
-  </si>
-  <si>
-    <t>19:23:53</t>
-  </si>
-  <si>
-    <t>21:01:28</t>
-  </si>
-  <si>
-    <t>22:38:37</t>
-  </si>
-  <si>
-    <t>18:43:39</t>
-  </si>
-  <si>
-    <t>20:21:17</t>
-  </si>
-  <si>
-    <t>21:58:32</t>
-  </si>
-  <si>
-    <t>18:03:21</t>
-  </si>
-  <si>
-    <t>19:41:02</t>
-  </si>
-  <si>
-    <t>21:18:22</t>
-  </si>
-  <si>
-    <t>22:54:43</t>
-  </si>
-  <si>
-    <t>19:00:43</t>
-  </si>
-  <si>
-    <t>20:38:07</t>
-  </si>
-  <si>
-    <t>22:14:41</t>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>01:34</t>
+  </si>
+  <si>
+    <t>00:28:33</t>
+  </si>
+  <si>
+    <t>18:57:01</t>
+  </si>
+  <si>
+    <t>20:33:24</t>
+  </si>
+  <si>
+    <t>22:10:44</t>
+  </si>
+  <si>
+    <t>23:48:27</t>
+  </si>
+  <si>
+    <t>19:53:22</t>
+  </si>
+  <si>
+    <t>21:30:38</t>
+  </si>
+  <si>
+    <t>23:08:17</t>
+  </si>
+  <si>
+    <t>19:13:19</t>
+  </si>
+  <si>
+    <t>20:50:28</t>
+  </si>
+  <si>
+    <t>22:28:03</t>
+  </si>
+  <si>
+    <t>18:33:12</t>
+  </si>
+  <si>
+    <t>20:10:14</t>
+  </si>
+  <si>
+    <t>21:47:46</t>
+  </si>
+  <si>
+    <t>17:53:03</t>
+  </si>
+  <si>
+    <t>19:29:56</t>
+  </si>
+  <si>
+    <t>21:07:26</t>
+  </si>
+  <si>
+    <t>22:45:21</t>
+  </si>
+  <si>
+    <t>18:49:35</t>
+  </si>
+  <si>
+    <t>20:27:01</t>
+  </si>
+  <si>
+    <t>22:04:50</t>
+  </si>
+  <si>
+    <t>18:09:10</t>
+  </si>
+  <si>
+    <t>19:46:32</t>
+  </si>
+  <si>
+    <t>21:24:16</t>
+  </si>
+  <si>
+    <t>00:31:21</t>
+  </si>
+  <si>
+    <t>19:00:24</t>
+  </si>
+  <si>
+    <t>20:35:43</t>
+  </si>
+  <si>
+    <t>22:13:00</t>
+  </si>
+  <si>
+    <t>23:51:05</t>
+  </si>
+  <si>
+    <t>19:55:45</t>
+  </si>
+  <si>
+    <t>21:32:54</t>
+  </si>
+  <si>
+    <t>23:10:48</t>
+  </si>
+  <si>
+    <t>19:15:44</t>
+  </si>
+  <si>
+    <t>20:52:43</t>
+  </si>
+  <si>
+    <t>22:30:30</t>
+  </si>
+  <si>
+    <t>18:35:42</t>
+  </si>
+  <si>
+    <t>20:12:29</t>
+  </si>
+  <si>
+    <t>21:50:09</t>
+  </si>
+  <si>
+    <t>17:55:40</t>
+  </si>
+  <si>
+    <t>19:32:12</t>
+  </si>
+  <si>
+    <t>21:09:46</t>
+  </si>
+  <si>
+    <t>22:48:47</t>
+  </si>
+  <si>
+    <t>18:51:52</t>
+  </si>
+  <si>
+    <t>20:29:19</t>
+  </si>
+  <si>
+    <t>22:07:49</t>
+  </si>
+  <si>
+    <t>18:11:29</t>
+  </si>
+  <si>
+    <t>19:48:49</t>
+  </si>
+  <si>
+    <t>21:27:01</t>
+  </si>
+  <si>
+    <t>00:33:27</t>
+  </si>
+  <si>
+    <t>19:01:34</t>
+  </si>
+  <si>
+    <t>20:38:44</t>
+  </si>
+  <si>
+    <t>22:16:10</t>
+  </si>
+  <si>
+    <t>23:53:29</t>
+  </si>
+  <si>
+    <t>19:58:40</t>
+  </si>
+  <si>
+    <t>21:36:05</t>
+  </si>
+  <si>
+    <t>23:13:26</t>
+  </si>
+  <si>
+    <t>19:18:32</t>
+  </si>
+  <si>
+    <t>20:55:55</t>
+  </si>
+  <si>
+    <t>22:33:17</t>
+  </si>
+  <si>
+    <t>18:38:20</t>
+  </si>
+  <si>
+    <t>20:15:40</t>
+  </si>
+  <si>
+    <t>21:53:04</t>
+  </si>
+  <si>
+    <t>17:58:04</t>
+  </si>
+  <si>
+    <t>19:35:22</t>
+  </si>
+  <si>
+    <t>21:12:46</t>
+  </si>
+  <si>
+    <t>22:49:55</t>
+  </si>
+  <si>
+    <t>18:55:00</t>
+  </si>
+  <si>
+    <t>20:32:24</t>
+  </si>
+  <si>
+    <t>22:09:36</t>
+  </si>
+  <si>
+    <t>18:14:33</t>
+  </si>
+  <si>
+    <t>19:51:57</t>
+  </si>
+  <si>
+    <t>21:29:12</t>
+  </si>
+  <si>
+    <t>00:35:33</t>
+  </si>
+  <si>
+    <t>19:02:45</t>
+  </si>
+  <si>
+    <t>20:41:46</t>
+  </si>
+  <si>
+    <t>22:19:20</t>
+  </si>
+  <si>
+    <t>23:55:53</t>
+  </si>
+  <si>
+    <t>20:01:36</t>
+  </si>
+  <si>
+    <t>21:39:16</t>
+  </si>
+  <si>
+    <t>23:16:03</t>
+  </si>
+  <si>
+    <t>19:21:20</t>
+  </si>
+  <si>
+    <t>20:59:06</t>
+  </si>
+  <si>
+    <t>22:36:05</t>
+  </si>
+  <si>
+    <t>18:40:58</t>
+  </si>
+  <si>
+    <t>20:18:52</t>
+  </si>
+  <si>
+    <t>21:55:59</t>
+  </si>
+  <si>
+    <t>18:00:29</t>
+  </si>
+  <si>
+    <t>19:38:32</t>
+  </si>
+  <si>
+    <t>21:15:48</t>
+  </si>
+  <si>
+    <t>22:51:03</t>
+  </si>
+  <si>
+    <t>18:58:07</t>
+  </si>
+  <si>
+    <t>20:35:30</t>
+  </si>
+  <si>
+    <t>22:11:23</t>
+  </si>
+  <si>
+    <t>18:17:37</t>
+  </si>
+  <si>
+    <t>19:55:06</t>
+  </si>
+  <si>
+    <t>21:31:24</t>
+  </si>
+  <si>
+    <t>00:38:20</t>
+  </si>
+  <si>
+    <t>19:06:09</t>
+  </si>
+  <si>
+    <t>20:44:06</t>
+  </si>
+  <si>
+    <t>22:21:36</t>
+  </si>
+  <si>
+    <t>23:58:30</t>
+  </si>
+  <si>
+    <t>20:03:58</t>
+  </si>
+  <si>
+    <t>21:41:31</t>
+  </si>
+  <si>
+    <t>23:18:33</t>
+  </si>
+  <si>
+    <t>19:23:46</t>
+  </si>
+  <si>
+    <t>21:01:22</t>
+  </si>
+  <si>
+    <t>22:38:30</t>
+  </si>
+  <si>
+    <t>18:43:29</t>
+  </si>
+  <si>
+    <t>20:21:07</t>
+  </si>
+  <si>
+    <t>21:58:22</t>
+  </si>
+  <si>
+    <t>18:03:07</t>
+  </si>
+  <si>
+    <t>19:40:48</t>
+  </si>
+  <si>
+    <t>21:18:07</t>
+  </si>
+  <si>
+    <t>22:54:29</t>
+  </si>
+  <si>
+    <t>19:00:25</t>
+  </si>
+  <si>
+    <t>20:37:48</t>
+  </si>
+  <si>
+    <t>22:14:22</t>
+  </si>
+  <si>
+    <t>18:19:56</t>
+  </si>
+  <si>
+    <t>19:57:22</t>
+  </si>
+  <si>
+    <t>21:34:08</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>-1°</t>
-  </si>
-  <si>
     <t>6°</t>
   </si>
   <si>
@@ -616,43 +610,52 @@
     <t>23°</t>
   </si>
   <si>
-    <t>29°</t>
+    <t>28°</t>
   </si>
   <si>
     <t>8°</t>
   </si>
   <si>
-    <t>19:36:33</t>
-  </si>
-  <si>
-    <t>18:59:05</t>
-  </si>
-  <si>
-    <t>19:54:54</t>
-  </si>
-  <si>
-    <t>19:17:01</t>
-  </si>
-  <si>
-    <t>18:38:58</t>
-  </si>
-  <si>
-    <t>20:12:25</t>
-  </si>
-  <si>
-    <t>18:00:45</t>
-  </si>
-  <si>
-    <t>19:34:12</t>
-  </si>
-  <si>
-    <t>21:07:38</t>
-  </si>
-  <si>
-    <t>18:55:50</t>
-  </si>
-  <si>
-    <t>20:29:16</t>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>18:59:04</t>
+  </si>
+  <si>
+    <t>19:54:50</t>
+  </si>
+  <si>
+    <t>19:16:55</t>
+  </si>
+  <si>
+    <t>18:38:48</t>
+  </si>
+  <si>
+    <t>20:12:16</t>
+  </si>
+  <si>
+    <t>18:00:31</t>
+  </si>
+  <si>
+    <t>19:33:58</t>
+  </si>
+  <si>
+    <t>21:07:25</t>
+  </si>
+  <si>
+    <t>18:55:31</t>
+  </si>
+  <si>
+    <t>20:28:57</t>
+  </si>
+  <si>
+    <t>18:16:57</t>
+  </si>
+  <si>
+    <t>19:50:23</t>
   </si>
   <si>
     <t>B</t>
@@ -664,10 +667,10 @@
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>2</t>
@@ -704,7 +707,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -725,7 +728,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,43 +782,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,7 +794,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,55 +842,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,7 +889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -973,9 +970,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1379,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1457,55 +1451,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>167</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-35.8</v>
+        <v>-38.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="P2" s="7">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="8">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="R2" s="9">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1513,55 +1507,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>168</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>202</v>
       </c>
       <c r="L3" s="4">
-        <v>-24.2</v>
+        <v>-18.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O3" s="6">
         <v>98</v>
       </c>
       <c r="P3" s="10">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>85</v>
-      </c>
-      <c r="R3" s="9">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>90</v>
+      </c>
+      <c r="R3" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1569,55 +1563,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>169</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-35.9</v>
+        <v>-31.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O4" s="6">
-        <v>99</v>
-      </c>
-      <c r="P4" s="9">
-        <v>79</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>79</v>
-      </c>
-      <c r="R4" s="8">
-        <v>85</v>
+        <v>98</v>
+      </c>
+      <c r="P4" s="7">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>94</v>
+      </c>
+      <c r="R4" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1625,55 +1619,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>170</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-41.5</v>
+        <v>-39.7</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O5" s="6">
-        <v>99</v>
-      </c>
-      <c r="P5" s="8">
-        <v>86</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>54</v>
-      </c>
-      <c r="R5" s="12">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="P5" s="14">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>84</v>
+      </c>
+      <c r="R5" s="16">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1681,40 +1675,40 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>171</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L6" s="4">
-        <v>-38.7</v>
+        <v>-40.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>217</v>
@@ -1722,14 +1716,14 @@
       <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="12">
-        <v>96</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>77</v>
-      </c>
-      <c r="R6" s="14">
-        <v>100</v>
+      <c r="P6" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>92</v>
+      </c>
+      <c r="R6" s="9">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1737,55 +1731,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>203</v>
       </c>
       <c r="L7" s="4">
-        <v>-18.2</v>
+        <v>-25.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="15">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>100</v>
-      </c>
-      <c r="R7" s="10">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="P7" s="17">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>40</v>
+      </c>
+      <c r="R7" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1793,55 +1787,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>173</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-31.3</v>
+        <v>-36.7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O8" s="6">
-        <v>99</v>
-      </c>
-      <c r="P8" s="15">
-        <v>61</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>94</v>
-      </c>
-      <c r="R8" s="8">
         <v>85</v>
+      </c>
+      <c r="P8" s="16">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>34</v>
+      </c>
+      <c r="R8" s="17">
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1849,55 +1843,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>174</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L9" s="4">
-        <v>-39.7</v>
+        <v>-40.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="8">
-        <v>84</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>87</v>
-      </c>
-      <c r="R9" s="9">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="P9" s="7">
+        <v>71</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>8</v>
+      </c>
+      <c r="R9" s="17">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1905,55 +1899,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>175</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="L10" s="4">
-        <v>-40.5</v>
+        <v>-20.2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O10" s="6">
-        <v>98</v>
-      </c>
-      <c r="P10" s="9">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>79</v>
-      </c>
-      <c r="R10" s="9">
-        <v>78</v>
+        <v>219</v>
+      </c>
+      <c r="O10" s="21">
+        <v>12</v>
+      </c>
+      <c r="P10" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>2</v>
+      </c>
+      <c r="R10" s="20">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1961,55 +1955,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>176</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="L11" s="4">
-        <v>-26</v>
+        <v>-32.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="O11" s="6">
-        <v>84</v>
-      </c>
-      <c r="P11" s="16">
-        <v>51</v>
+      <c r="O11" s="21">
+        <v>17</v>
+      </c>
+      <c r="P11" s="11">
+        <v>3</v>
       </c>
       <c r="Q11" s="11">
-        <v>56</v>
-      </c>
-      <c r="R11" s="17">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="R11" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2017,55 +2011,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>177</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-36.7</v>
+        <v>-39.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="O12" s="6">
-        <v>77</v>
-      </c>
-      <c r="P12" s="11">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>45</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
+      <c r="O12" s="21">
+        <v>9</v>
+      </c>
+      <c r="P12" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2076,52 +2070,52 @@
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>178</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="L13" s="4">
-        <v>-40.8</v>
+        <v>-14</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O13" s="6">
-        <v>69</v>
-      </c>
-      <c r="P13" s="15">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="19">
-        <v>18</v>
-      </c>
-      <c r="R13" s="17">
-        <v>2</v>
+        <v>219</v>
+      </c>
+      <c r="O13" s="22">
+        <v>26</v>
+      </c>
+      <c r="P13" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>7</v>
+      </c>
+      <c r="R13" s="23">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2129,25 +2123,25 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>179</v>
@@ -2156,28 +2150,28 @@
         <v>195</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L14" s="4">
-        <v>-20.2</v>
+        <v>-27.5</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>214</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O14" s="20">
-        <v>8</v>
-      </c>
-      <c r="P14" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="17">
+        <v>217</v>
+      </c>
+      <c r="O14" s="6">
+        <v>69</v>
+      </c>
+      <c r="P14" s="19">
         <v>0</v>
       </c>
-      <c r="R14" s="21">
-        <v>3</v>
+      <c r="Q14" s="14">
+        <v>64</v>
+      </c>
+      <c r="R14" s="7">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2185,55 +2179,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>180</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L15" s="4">
-        <v>-32.6</v>
+        <v>-37.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="O15" s="20">
-        <v>8</v>
-      </c>
-      <c r="P15" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="17">
+      <c r="O15" s="6">
+        <v>64</v>
+      </c>
+      <c r="P15" s="19">
         <v>0</v>
       </c>
-      <c r="R15" s="17">
-        <v>1</v>
+      <c r="Q15" s="14">
+        <v>64</v>
+      </c>
+      <c r="R15" s="14">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2241,55 +2235,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>181</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="L16" s="4">
-        <v>-39.7</v>
+        <v>-7.6</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O16" s="20">
-        <v>5</v>
-      </c>
-      <c r="P16" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="17">
+        <v>219</v>
+      </c>
+      <c r="O16" s="6">
+        <v>56</v>
+      </c>
+      <c r="P16" s="19">
         <v>0</v>
       </c>
-      <c r="R16" s="17">
+      <c r="Q16" s="19">
         <v>0</v>
+      </c>
+      <c r="R16" s="24">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2297,55 +2291,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>182</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L17" s="4">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O17" s="6">
-        <v>58</v>
-      </c>
-      <c r="P17" s="18">
-        <v>47</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>23</v>
+        <v>53</v>
+      </c>
+      <c r="P17" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="19">
+        <v>0</v>
       </c>
       <c r="R17" s="17">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2353,55 +2347,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>183</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L18" s="4">
-        <v>-27.6</v>
+        <v>-33.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O18" s="6">
-        <v>41</v>
-      </c>
-      <c r="P18" s="23">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>41</v>
-      </c>
-      <c r="R18" s="23">
-        <v>11</v>
+        <v>96</v>
+      </c>
+      <c r="P18" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>0</v>
+      </c>
+      <c r="R18" s="12">
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2409,55 +2403,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>184</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L19" s="4">
-        <v>-37.3</v>
+        <v>-39.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O19" s="6">
-        <v>51</v>
-      </c>
-      <c r="P19" s="23">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>51</v>
-      </c>
-      <c r="R19" s="7">
-        <v>16</v>
+        <v>96</v>
+      </c>
+      <c r="P19" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>12</v>
+      </c>
+      <c r="R19" s="9">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2465,25 +2459,25 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>185</v>
@@ -2492,28 +2486,28 @@
         <v>198</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" s="4">
-        <v>-7.6</v>
+        <v>-15.9</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>215</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O20" s="25">
-        <v>33</v>
-      </c>
-      <c r="P20" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="26">
-        <v>30</v>
-      </c>
-      <c r="R20" s="27">
-        <v>33</v>
+        <v>219</v>
+      </c>
+      <c r="O20" s="6">
+        <v>100</v>
+      </c>
+      <c r="P20" s="25">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>93</v>
+      </c>
+      <c r="R20" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2521,25 +2515,25 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>186</v>
@@ -2548,27 +2542,27 @@
         <v>199</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L21" s="4">
-        <v>-22</v>
+        <v>-28.9</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>214</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O21" s="20">
-        <v>3</v>
-      </c>
-      <c r="P21" s="21">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>0</v>
-      </c>
-      <c r="R21" s="17">
+        <v>217</v>
+      </c>
+      <c r="O21" s="6">
+        <v>91</v>
+      </c>
+      <c r="P21" s="24">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>76</v>
+      </c>
+      <c r="R21" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2577,55 +2571,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>187</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>210</v>
+        <v>91</v>
       </c>
       <c r="L22" s="4">
-        <v>-33.5</v>
+        <v>-37.5</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O22" s="25">
-        <v>32</v>
+        <v>218</v>
+      </c>
+      <c r="O22" s="6">
+        <v>93</v>
       </c>
       <c r="P22" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="17">
-        <v>0</v>
-      </c>
-      <c r="R22" s="17">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>67</v>
+      </c>
+      <c r="R22" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2633,55 +2627,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>188</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="L23" s="4">
-        <v>-39.4</v>
+        <v>-9.6</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O23" s="25">
-        <v>41</v>
-      </c>
-      <c r="P23" s="17">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="21">
-        <v>5</v>
-      </c>
-      <c r="R23" s="21">
-        <v>6</v>
+        <v>219</v>
+      </c>
+      <c r="O23" s="6">
+        <v>78</v>
+      </c>
+      <c r="P23" s="25">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>36</v>
+      </c>
+      <c r="R23" s="10">
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2692,52 +2686,52 @@
         <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>189</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L24" s="4">
-        <v>-16</v>
+        <v>-23.7</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" s="6">
-        <v>74</v>
-      </c>
-      <c r="P24" s="28">
-        <v>71</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>13</v>
-      </c>
-      <c r="R24" s="17">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="P24" s="13">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="27">
+        <v>32</v>
+      </c>
+      <c r="R24" s="10">
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2745,170 +2739,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>190</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="L25" s="4">
-        <v>-29</v>
+        <v>-34.4</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O25" s="6">
-        <v>61</v>
-      </c>
-      <c r="P25" s="18">
-        <v>46</v>
-      </c>
-      <c r="Q25" s="22">
-        <v>24</v>
-      </c>
-      <c r="R25" s="22">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>13</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-37.5</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O26" s="6">
-        <v>45</v>
-      </c>
-      <c r="P26" s="27">
-        <v>34</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>16</v>
-      </c>
-      <c r="R26" s="19">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="P25" s="20">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="18">
+        <v>39</v>
+      </c>
+      <c r="R25" s="15">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2927,12 +2865,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2949,22 +2887,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
   <si>
     <t>Datum</t>
   </si>
@@ -70,21 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260315--01</t>
-  </si>
-  <si>
-    <t>20260315--02</t>
-  </si>
-  <si>
-    <t>20260315--03</t>
-  </si>
-  <si>
-    <t>20260315--04</t>
-  </si>
-  <si>
-    <t>20260315--05</t>
-  </si>
-  <si>
     <t>20260316--01</t>
   </si>
   <si>
@@ -142,48 +127,42 @@
     <t>20260321--03</t>
   </si>
   <si>
-    <t>04:12</t>
-  </si>
-  <si>
-    <t>02:21</t>
-  </si>
-  <si>
-    <t>06:03</t>
+    <t>20260322--01</t>
+  </si>
+  <si>
+    <t>20260322--02</t>
+  </si>
+  <si>
+    <t>05:51</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:49</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>04:48</t>
-  </si>
-  <si>
-    <t>05:51</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:49</t>
-  </si>
-  <si>
     <t>06:02</t>
   </si>
   <si>
@@ -208,6 +187,9 @@
     <t>04:23</t>
   </si>
   <si>
+    <t>04:57</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -229,19 +211,7 @@
     <t>01:34</t>
   </si>
   <si>
-    <t>00:28:33</t>
-  </si>
-  <si>
-    <t>18:57:01</t>
-  </si>
-  <si>
-    <t>20:33:24</t>
-  </si>
-  <si>
-    <t>22:10:44</t>
-  </si>
-  <si>
-    <t>23:48:27</t>
+    <t>03:25</t>
   </si>
   <si>
     <t>19:53:22</t>
@@ -301,19 +271,10 @@
     <t>21:24:16</t>
   </si>
   <si>
-    <t>00:31:21</t>
-  </si>
-  <si>
-    <t>19:00:24</t>
-  </si>
-  <si>
-    <t>20:35:43</t>
-  </si>
-  <si>
-    <t>22:13:00</t>
-  </si>
-  <si>
-    <t>23:51:05</t>
+    <t>19:06:00</t>
+  </si>
+  <si>
+    <t>20:43:39</t>
   </si>
   <si>
     <t>19:55:45</t>
@@ -373,19 +334,10 @@
     <t>21:27:01</t>
   </si>
   <si>
-    <t>00:33:27</t>
-  </si>
-  <si>
-    <t>19:01:34</t>
-  </si>
-  <si>
-    <t>20:38:44</t>
-  </si>
-  <si>
-    <t>22:16:10</t>
-  </si>
-  <si>
-    <t>23:53:29</t>
+    <t>19:08:16</t>
+  </si>
+  <si>
+    <t>20:46:15</t>
   </si>
   <si>
     <t>19:58:40</t>
@@ -445,19 +397,10 @@
     <t>21:29:12</t>
   </si>
   <si>
-    <t>00:35:33</t>
-  </si>
-  <si>
-    <t>19:02:45</t>
-  </si>
-  <si>
-    <t>20:41:46</t>
-  </si>
-  <si>
-    <t>22:19:20</t>
-  </si>
-  <si>
-    <t>23:55:53</t>
+    <t>19:11:26</t>
+  </si>
+  <si>
+    <t>20:48:44</t>
   </si>
   <si>
     <t>20:01:36</t>
@@ -517,19 +460,10 @@
     <t>21:31:24</t>
   </si>
   <si>
-    <t>00:38:20</t>
-  </si>
-  <si>
-    <t>19:06:09</t>
-  </si>
-  <si>
-    <t>20:44:06</t>
-  </si>
-  <si>
-    <t>22:21:36</t>
-  </si>
-  <si>
-    <t>23:58:30</t>
+    <t>19:14:36</t>
+  </si>
+  <si>
+    <t>20:51:12</t>
   </si>
   <si>
     <t>20:03:58</t>
@@ -589,12 +523,18 @@
     <t>21:34:08</t>
   </si>
   <si>
+    <t>19:16:52</t>
+  </si>
+  <si>
+    <t>20:53:47</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
     <t>0°</t>
   </si>
   <si>
-    <t>6°</t>
-  </si>
-  <si>
     <t>16°</t>
   </si>
   <si>
@@ -622,7 +562,10 @@
     <t>21°</t>
   </si>
   <si>
-    <t>18:59:04</t>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>5°</t>
   </si>
   <si>
     <t>19:54:50</t>
@@ -658,6 +601,12 @@
     <t>19:50:23</t>
   </si>
   <si>
+    <t>19:11:41</t>
+  </si>
+  <si>
+    <t>20:45:06</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -670,10 +619,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -707,7 +656,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -728,7 +677,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,13 +707,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,37 +731,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +749,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,43 +767,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,18 +883,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1373,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1451,55 +1364,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="L2" s="4">
-        <v>-38.7</v>
+        <v>-25.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="O2" s="6">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="P2" s="7">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="8">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="R2" s="9">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1507,55 +1420,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.2</v>
+        <v>-36.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="O3" s="6">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="P3" s="10">
-        <v>79</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>90</v>
-      </c>
-      <c r="R3" s="11">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>34</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1563,55 +1476,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4">
-        <v>-31.3</v>
+        <v>-40.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="O4" s="6">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="P4" s="7">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="Q4" s="12">
-        <v>94</v>
-      </c>
-      <c r="R4" s="13">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1619,55 +1532,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.7</v>
+        <v>-20.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O5" s="6">
-        <v>98</v>
-      </c>
-      <c r="P5" s="14">
-        <v>64</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>84</v>
-      </c>
-      <c r="R5" s="16">
-        <v>56</v>
+        <v>201</v>
+      </c>
+      <c r="O5" s="13">
+        <v>1</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1675,55 +1588,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L6" s="4">
-        <v>-40.5</v>
+        <v>-32.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O6" s="6">
-        <v>100</v>
-      </c>
-      <c r="P6" s="15">
-        <v>85</v>
+        <v>200</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
       </c>
       <c r="Q6" s="9">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R6" s="9">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1731,54 +1644,54 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="L7" s="4">
-        <v>-25.9</v>
+        <v>-39.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O7" s="6">
-        <v>65</v>
-      </c>
-      <c r="P7" s="17">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>40</v>
-      </c>
-      <c r="R7" s="19">
+        <v>200</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1787,55 +1700,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="L8" s="4">
-        <v>-36.7</v>
+        <v>-14</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O8" s="6">
-        <v>85</v>
-      </c>
-      <c r="P8" s="16">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>34</v>
-      </c>
-      <c r="R8" s="17">
-        <v>52</v>
+        <v>201</v>
+      </c>
+      <c r="O8" s="13">
+        <v>1</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1843,55 +1756,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="L9" s="4">
-        <v>-40.8</v>
+        <v>-27.5</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O9" s="6">
-        <v>85</v>
-      </c>
-      <c r="P9" s="7">
-        <v>71</v>
-      </c>
-      <c r="Q9" s="20">
-        <v>8</v>
-      </c>
-      <c r="R9" s="17">
-        <v>50</v>
+        <v>200</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1899,55 +1812,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="L10" s="4">
-        <v>-20.2</v>
+        <v>-37.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O10" s="21">
-        <v>12</v>
-      </c>
-      <c r="P10" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>2</v>
-      </c>
-      <c r="R10" s="20">
-        <v>12</v>
+        <v>200</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1955,55 +1868,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="L11" s="4">
-        <v>-32.6</v>
+        <v>-7.6</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O11" s="21">
-        <v>17</v>
-      </c>
-      <c r="P11" s="11">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>3</v>
-      </c>
-      <c r="R11" s="13">
-        <v>17</v>
+        <v>201</v>
+      </c>
+      <c r="O11" s="6">
+        <v>66</v>
+      </c>
+      <c r="P11" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>66</v>
+      </c>
+      <c r="R11" s="7">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2011,55 +1924,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="L12" s="4">
-        <v>-39.7</v>
+        <v>-22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O12" s="21">
-        <v>9</v>
-      </c>
-      <c r="P12" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>1</v>
-      </c>
-      <c r="R12" s="11">
+        <v>201</v>
+      </c>
+      <c r="O12" s="6">
+        <v>84</v>
+      </c>
+      <c r="P12" s="15">
         <v>4</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>74</v>
+      </c>
+      <c r="R12" s="14">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2067,55 +1980,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="L13" s="4">
-        <v>-14</v>
+        <v>-33.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" s="22">
-        <v>26</v>
-      </c>
-      <c r="P13" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>7</v>
-      </c>
-      <c r="R13" s="23">
-        <v>25</v>
+        <v>200</v>
+      </c>
+      <c r="O13" s="6">
+        <v>49</v>
+      </c>
+      <c r="P13" s="17">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>39</v>
+      </c>
+      <c r="R13" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2123,55 +2036,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4">
-        <v>-27.5</v>
+        <v>-39.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="O14" s="6">
-        <v>69</v>
-      </c>
-      <c r="P14" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>64</v>
-      </c>
-      <c r="R14" s="7">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="P14" s="17">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>33</v>
+      </c>
+      <c r="R14" s="17">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2179,55 +2092,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="L15" s="4">
-        <v>-37.3</v>
+        <v>-15.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="O15" s="6">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P15" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>64</v>
-      </c>
-      <c r="R15" s="14">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>71</v>
+      </c>
+      <c r="R15" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2235,55 +2148,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="L16" s="4">
-        <v>-7.6</v>
+        <v>-28.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="O16" s="6">
-        <v>56</v>
-      </c>
-      <c r="P16" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>0</v>
-      </c>
-      <c r="R16" s="24">
-        <v>46</v>
+        <v>89</v>
+      </c>
+      <c r="P16" s="8">
+        <v>83</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>86</v>
+      </c>
+      <c r="R16" s="15">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2291,55 +2204,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-37.5</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-22</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="N17" s="1" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="O17" s="6">
-        <v>53</v>
-      </c>
-      <c r="P17" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="19">
-        <v>0</v>
-      </c>
-      <c r="R17" s="17">
-        <v>51</v>
+        <v>91</v>
+      </c>
+      <c r="P17" s="8">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>54</v>
+      </c>
+      <c r="R17" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2347,55 +2260,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L18" s="4">
-        <v>-33.5</v>
+        <v>-9.6</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O18" s="6">
-        <v>96</v>
-      </c>
-      <c r="P18" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>0</v>
-      </c>
-      <c r="R18" s="12">
-        <v>94</v>
+        <v>201</v>
+      </c>
+      <c r="O18" s="20">
+        <v>43</v>
+      </c>
+      <c r="P18" s="18">
+        <v>39</v>
+      </c>
+      <c r="Q18" s="21">
+        <v>10</v>
+      </c>
+      <c r="R18" s="15">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2403,55 +2316,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="L19" s="4">
-        <v>-39.4</v>
+        <v>-23.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="O19" s="6">
-        <v>96</v>
-      </c>
-      <c r="P19" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="20">
-        <v>12</v>
-      </c>
-      <c r="R19" s="9">
-        <v>91</v>
+        <v>47</v>
+      </c>
+      <c r="P19" s="22">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>7</v>
+      </c>
+      <c r="R19" s="21">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2459,55 +2372,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="L20" s="4">
-        <v>-15.9</v>
+        <v>-34.4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="O20" s="6">
-        <v>100</v>
-      </c>
-      <c r="P20" s="25">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="12">
-        <v>93</v>
-      </c>
-      <c r="R20" s="19">
+        <v>50</v>
+      </c>
+      <c r="P20" s="22">
+        <v>44</v>
+      </c>
+      <c r="Q20" s="9">
         <v>0</v>
+      </c>
+      <c r="R20" s="17">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2515,55 +2428,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="L21" s="4">
-        <v>-28.9</v>
+        <v>-17.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="O21" s="6">
-        <v>91</v>
-      </c>
-      <c r="P21" s="24">
-        <v>43</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>76</v>
-      </c>
-      <c r="R21" s="19">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="P21" s="11">
+        <v>37</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>50</v>
+      </c>
+      <c r="R21" s="21">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2571,282 +2484,114 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="L22" s="4">
-        <v>-37.5</v>
+        <v>-30.1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="O22" s="6">
-        <v>93</v>
-      </c>
-      <c r="P22" s="17">
-        <v>51</v>
-      </c>
-      <c r="Q22" s="14">
-        <v>67</v>
-      </c>
-      <c r="R22" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="2">
-        <v>28</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-9.6</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O23" s="6">
-        <v>78</v>
-      </c>
-      <c r="P23" s="25">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>36</v>
-      </c>
-      <c r="R23" s="10">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" s="18">
         <v>40</v>
       </c>
-      <c r="B24" s="2">
-        <v>30</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-23.7</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O24" s="6">
-        <v>78</v>
-      </c>
-      <c r="P24" s="13">
-        <v>16</v>
-      </c>
-      <c r="Q24" s="27">
-        <v>32</v>
-      </c>
-      <c r="R24" s="10">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2">
-        <v>16</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-34.4</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="6">
-        <v>86</v>
-      </c>
-      <c r="P25" s="20">
-        <v>12</v>
-      </c>
-      <c r="Q25" s="18">
-        <v>39</v>
-      </c>
-      <c r="R25" s="15">
-        <v>86</v>
+      <c r="Q22" s="23">
+        <v>50</v>
+      </c>
+      <c r="R22" s="15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A22">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B22">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D22">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E22">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F22">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G22">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I22">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J22">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2865,12 +2610,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M22">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2887,22 +2632,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="200">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260316--01</t>
-  </si>
-  <si>
-    <t>20260316--02</t>
-  </si>
-  <si>
-    <t>20260316--03</t>
-  </si>
-  <si>
     <t>20260317--01</t>
   </si>
   <si>
@@ -133,73 +124,79 @@
     <t>20260322--02</t>
   </si>
   <si>
-    <t>05:51</t>
+    <t>20260323--01</t>
+  </si>
+  <si>
+    <t>20260323--02</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:34</t>
+  </si>
+  <si>
+    <t>05:16</t>
   </si>
   <si>
     <t>06:22</t>
   </si>
   <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
     <t>05:50</t>
   </si>
   <si>
     <t>04:49</t>
   </si>
   <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:22</t>
+  </si>
+  <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>02:16</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:34</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>04:23</t>
-  </si>
-  <si>
-    <t>04:57</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>01:11</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:11</t>
-  </si>
-  <si>
     <t>03:06</t>
   </si>
   <si>
-    <t>01:46</t>
+    <t>01:45</t>
   </si>
   <si>
     <t>03:39</t>
@@ -208,336 +205,324 @@
     <t>05:28</t>
   </si>
   <si>
-    <t>01:34</t>
-  </si>
-  <si>
-    <t>03:25</t>
-  </si>
-  <si>
-    <t>19:53:22</t>
-  </si>
-  <si>
-    <t>21:30:38</t>
-  </si>
-  <si>
-    <t>23:08:17</t>
-  </si>
-  <si>
-    <t>19:13:19</t>
-  </si>
-  <si>
-    <t>20:50:28</t>
-  </si>
-  <si>
-    <t>22:28:03</t>
-  </si>
-  <si>
-    <t>18:33:12</t>
-  </si>
-  <si>
-    <t>20:10:14</t>
-  </si>
-  <si>
-    <t>21:47:46</t>
-  </si>
-  <si>
-    <t>17:53:03</t>
-  </si>
-  <si>
-    <t>19:29:56</t>
-  </si>
-  <si>
-    <t>21:07:26</t>
-  </si>
-  <si>
-    <t>22:45:21</t>
-  </si>
-  <si>
-    <t>18:49:35</t>
-  </si>
-  <si>
-    <t>20:27:01</t>
-  </si>
-  <si>
-    <t>22:04:50</t>
-  </si>
-  <si>
-    <t>18:09:10</t>
-  </si>
-  <si>
-    <t>19:46:32</t>
-  </si>
-  <si>
-    <t>21:24:16</t>
-  </si>
-  <si>
-    <t>19:06:00</t>
-  </si>
-  <si>
-    <t>20:43:39</t>
-  </si>
-  <si>
-    <t>19:55:45</t>
-  </si>
-  <si>
-    <t>21:32:54</t>
-  </si>
-  <si>
-    <t>23:10:48</t>
-  </si>
-  <si>
-    <t>19:15:44</t>
-  </si>
-  <si>
-    <t>20:52:43</t>
-  </si>
-  <si>
-    <t>22:30:30</t>
-  </si>
-  <si>
-    <t>18:35:42</t>
-  </si>
-  <si>
-    <t>20:12:29</t>
-  </si>
-  <si>
-    <t>21:50:09</t>
-  </si>
-  <si>
-    <t>17:55:40</t>
-  </si>
-  <si>
-    <t>19:32:12</t>
-  </si>
-  <si>
-    <t>21:09:46</t>
-  </si>
-  <si>
-    <t>22:48:47</t>
-  </si>
-  <si>
-    <t>18:51:52</t>
-  </si>
-  <si>
-    <t>20:29:19</t>
-  </si>
-  <si>
-    <t>22:07:49</t>
-  </si>
-  <si>
-    <t>18:11:29</t>
-  </si>
-  <si>
-    <t>19:48:49</t>
-  </si>
-  <si>
-    <t>21:27:01</t>
-  </si>
-  <si>
-    <t>19:08:16</t>
-  </si>
-  <si>
-    <t>20:46:15</t>
-  </si>
-  <si>
-    <t>19:58:40</t>
-  </si>
-  <si>
-    <t>21:36:05</t>
-  </si>
-  <si>
-    <t>23:13:26</t>
-  </si>
-  <si>
-    <t>19:18:32</t>
-  </si>
-  <si>
-    <t>20:55:55</t>
-  </si>
-  <si>
-    <t>22:33:17</t>
-  </si>
-  <si>
-    <t>18:38:20</t>
-  </si>
-  <si>
-    <t>20:15:40</t>
-  </si>
-  <si>
-    <t>21:53:04</t>
-  </si>
-  <si>
-    <t>17:58:04</t>
-  </si>
-  <si>
-    <t>19:35:22</t>
-  </si>
-  <si>
-    <t>21:12:46</t>
-  </si>
-  <si>
-    <t>22:49:55</t>
-  </si>
-  <si>
-    <t>18:55:00</t>
-  </si>
-  <si>
-    <t>20:32:24</t>
-  </si>
-  <si>
-    <t>22:09:36</t>
-  </si>
-  <si>
-    <t>18:14:33</t>
-  </si>
-  <si>
-    <t>19:51:57</t>
-  </si>
-  <si>
-    <t>21:29:12</t>
-  </si>
-  <si>
-    <t>19:11:26</t>
-  </si>
-  <si>
-    <t>20:48:44</t>
-  </si>
-  <si>
-    <t>20:01:36</t>
-  </si>
-  <si>
-    <t>21:39:16</t>
-  </si>
-  <si>
-    <t>23:16:03</t>
-  </si>
-  <si>
-    <t>19:21:20</t>
-  </si>
-  <si>
-    <t>20:59:06</t>
-  </si>
-  <si>
-    <t>22:36:05</t>
-  </si>
-  <si>
-    <t>18:40:58</t>
-  </si>
-  <si>
-    <t>20:18:52</t>
-  </si>
-  <si>
-    <t>21:55:59</t>
-  </si>
-  <si>
-    <t>18:00:29</t>
-  </si>
-  <si>
-    <t>19:38:32</t>
-  </si>
-  <si>
-    <t>21:15:48</t>
-  </si>
-  <si>
-    <t>22:51:03</t>
-  </si>
-  <si>
-    <t>18:58:07</t>
-  </si>
-  <si>
-    <t>20:35:30</t>
-  </si>
-  <si>
-    <t>22:11:23</t>
-  </si>
-  <si>
-    <t>18:17:37</t>
-  </si>
-  <si>
-    <t>19:55:06</t>
-  </si>
-  <si>
-    <t>21:31:24</t>
-  </si>
-  <si>
-    <t>19:14:36</t>
-  </si>
-  <si>
-    <t>20:51:12</t>
-  </si>
-  <si>
-    <t>20:03:58</t>
-  </si>
-  <si>
-    <t>21:41:31</t>
-  </si>
-  <si>
-    <t>23:18:33</t>
-  </si>
-  <si>
-    <t>19:23:46</t>
-  </si>
-  <si>
-    <t>21:01:22</t>
-  </si>
-  <si>
-    <t>22:38:30</t>
-  </si>
-  <si>
-    <t>18:43:29</t>
-  </si>
-  <si>
-    <t>20:21:07</t>
-  </si>
-  <si>
-    <t>21:58:22</t>
-  </si>
-  <si>
-    <t>18:03:07</t>
-  </si>
-  <si>
-    <t>19:40:48</t>
-  </si>
-  <si>
-    <t>21:18:07</t>
-  </si>
-  <si>
-    <t>22:54:29</t>
-  </si>
-  <si>
-    <t>19:00:25</t>
-  </si>
-  <si>
-    <t>20:37:48</t>
-  </si>
-  <si>
-    <t>22:14:22</t>
-  </si>
-  <si>
-    <t>18:19:56</t>
-  </si>
-  <si>
-    <t>19:57:22</t>
-  </si>
-  <si>
-    <t>21:34:08</t>
-  </si>
-  <si>
-    <t>19:16:52</t>
-  </si>
-  <si>
-    <t>20:53:47</t>
-  </si>
-  <si>
-    <t>6°</t>
+    <t>01:33</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>05:14</t>
+  </si>
+  <si>
+    <t>00:49</t>
+  </si>
+  <si>
+    <t>19:13:21</t>
+  </si>
+  <si>
+    <t>20:50:31</t>
+  </si>
+  <si>
+    <t>22:28:07</t>
+  </si>
+  <si>
+    <t>18:33:17</t>
+  </si>
+  <si>
+    <t>20:10:19</t>
+  </si>
+  <si>
+    <t>21:47:52</t>
+  </si>
+  <si>
+    <t>17:53:11</t>
+  </si>
+  <si>
+    <t>19:30:04</t>
+  </si>
+  <si>
+    <t>21:07:34</t>
+  </si>
+  <si>
+    <t>22:45:30</t>
+  </si>
+  <si>
+    <t>18:49:47</t>
+  </si>
+  <si>
+    <t>20:27:13</t>
+  </si>
+  <si>
+    <t>22:05:03</t>
+  </si>
+  <si>
+    <t>18:09:27</t>
+  </si>
+  <si>
+    <t>19:46:49</t>
+  </si>
+  <si>
+    <t>21:24:34</t>
+  </si>
+  <si>
+    <t>19:06:22</t>
+  </si>
+  <si>
+    <t>20:44:02</t>
+  </si>
+  <si>
+    <t>18:25:51</t>
+  </si>
+  <si>
+    <t>20:03:28</t>
+  </si>
+  <si>
+    <t>19:15:47</t>
+  </si>
+  <si>
+    <t>20:52:46</t>
+  </si>
+  <si>
+    <t>22:30:33</t>
+  </si>
+  <si>
+    <t>18:35:47</t>
+  </si>
+  <si>
+    <t>20:12:35</t>
+  </si>
+  <si>
+    <t>21:50:15</t>
+  </si>
+  <si>
+    <t>17:55:48</t>
+  </si>
+  <si>
+    <t>19:32:21</t>
+  </si>
+  <si>
+    <t>21:09:54</t>
+  </si>
+  <si>
+    <t>22:48:56</t>
+  </si>
+  <si>
+    <t>18:52:04</t>
+  </si>
+  <si>
+    <t>20:29:32</t>
+  </si>
+  <si>
+    <t>22:08:02</t>
+  </si>
+  <si>
+    <t>18:11:45</t>
+  </si>
+  <si>
+    <t>19:49:06</t>
+  </si>
+  <si>
+    <t>21:27:18</t>
+  </si>
+  <si>
+    <t>19:08:38</t>
+  </si>
+  <si>
+    <t>20:46:38</t>
+  </si>
+  <si>
+    <t>18:28:07</t>
+  </si>
+  <si>
+    <t>20:05:57</t>
+  </si>
+  <si>
+    <t>19:18:35</t>
+  </si>
+  <si>
+    <t>20:55:58</t>
+  </si>
+  <si>
+    <t>22:33:20</t>
+  </si>
+  <si>
+    <t>18:38:25</t>
+  </si>
+  <si>
+    <t>20:15:46</t>
+  </si>
+  <si>
+    <t>21:53:10</t>
+  </si>
+  <si>
+    <t>17:58:13</t>
+  </si>
+  <si>
+    <t>19:35:30</t>
+  </si>
+  <si>
+    <t>21:12:55</t>
+  </si>
+  <si>
+    <t>22:50:04</t>
+  </si>
+  <si>
+    <t>18:55:12</t>
+  </si>
+  <si>
+    <t>20:32:37</t>
+  </si>
+  <si>
+    <t>22:09:49</t>
+  </si>
+  <si>
+    <t>18:14:50</t>
+  </si>
+  <si>
+    <t>19:52:14</t>
+  </si>
+  <si>
+    <t>21:29:29</t>
+  </si>
+  <si>
+    <t>19:11:48</t>
+  </si>
+  <si>
+    <t>20:49:06</t>
+  </si>
+  <si>
+    <t>18:31:18</t>
+  </si>
+  <si>
+    <t>20:08:38</t>
+  </si>
+  <si>
+    <t>19:21:23</t>
+  </si>
+  <si>
+    <t>20:59:09</t>
+  </si>
+  <si>
+    <t>22:36:07</t>
+  </si>
+  <si>
+    <t>18:41:03</t>
+  </si>
+  <si>
+    <t>20:18:57</t>
+  </si>
+  <si>
+    <t>21:56:05</t>
+  </si>
+  <si>
+    <t>18:00:37</t>
+  </si>
+  <si>
+    <t>19:38:40</t>
+  </si>
+  <si>
+    <t>21:15:56</t>
+  </si>
+  <si>
+    <t>22:51:11</t>
+  </si>
+  <si>
+    <t>18:58:19</t>
+  </si>
+  <si>
+    <t>20:35:42</t>
+  </si>
+  <si>
+    <t>22:11:35</t>
+  </si>
+  <si>
+    <t>18:17:54</t>
+  </si>
+  <si>
+    <t>19:55:22</t>
+  </si>
+  <si>
+    <t>21:31:40</t>
+  </si>
+  <si>
+    <t>19:14:58</t>
+  </si>
+  <si>
+    <t>20:51:34</t>
+  </si>
+  <si>
+    <t>18:34:29</t>
+  </si>
+  <si>
+    <t>20:11:19</t>
+  </si>
+  <si>
+    <t>19:23:49</t>
+  </si>
+  <si>
+    <t>21:01:24</t>
+  </si>
+  <si>
+    <t>22:38:33</t>
+  </si>
+  <si>
+    <t>18:43:34</t>
+  </si>
+  <si>
+    <t>20:21:12</t>
+  </si>
+  <si>
+    <t>21:58:27</t>
+  </si>
+  <si>
+    <t>18:03:15</t>
+  </si>
+  <si>
+    <t>19:40:56</t>
+  </si>
+  <si>
+    <t>21:18:16</t>
+  </si>
+  <si>
+    <t>22:54:37</t>
+  </si>
+  <si>
+    <t>19:00:36</t>
+  </si>
+  <si>
+    <t>20:38:00</t>
+  </si>
+  <si>
+    <t>22:14:34</t>
+  </si>
+  <si>
+    <t>18:20:13</t>
+  </si>
+  <si>
+    <t>19:57:39</t>
+  </si>
+  <si>
+    <t>21:34:24</t>
+  </si>
+  <si>
+    <t>19:17:14</t>
+  </si>
+  <si>
+    <t>20:54:09</t>
+  </si>
+  <si>
+    <t>18:36:45</t>
+  </si>
+  <si>
+    <t>20:13:47</t>
+  </si>
+  <si>
+    <t>16°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
     <t>19°</t>
   </si>
   <si>
@@ -550,7 +535,7 @@
     <t>23°</t>
   </si>
   <si>
-    <t>28°</t>
+    <t>29°</t>
   </si>
   <si>
     <t>8°</t>
@@ -568,58 +553,64 @@
     <t>5°</t>
   </si>
   <si>
-    <t>19:54:50</t>
-  </si>
-  <si>
-    <t>19:16:55</t>
-  </si>
-  <si>
-    <t>18:38:48</t>
-  </si>
-  <si>
-    <t>20:12:16</t>
-  </si>
-  <si>
-    <t>18:00:31</t>
-  </si>
-  <si>
-    <t>19:33:58</t>
-  </si>
-  <si>
-    <t>21:07:25</t>
-  </si>
-  <si>
-    <t>18:55:31</t>
-  </si>
-  <si>
-    <t>20:28:57</t>
-  </si>
-  <si>
-    <t>18:16:57</t>
-  </si>
-  <si>
-    <t>19:50:23</t>
-  </si>
-  <si>
-    <t>19:11:41</t>
-  </si>
-  <si>
-    <t>20:45:06</t>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>19:16:58</t>
+  </si>
+  <si>
+    <t>18:38:53</t>
+  </si>
+  <si>
+    <t>20:12:21</t>
+  </si>
+  <si>
+    <t>18:00:39</t>
+  </si>
+  <si>
+    <t>19:34:06</t>
+  </si>
+  <si>
+    <t>21:07:33</t>
+  </si>
+  <si>
+    <t>18:55:43</t>
+  </si>
+  <si>
+    <t>20:29:09</t>
+  </si>
+  <si>
+    <t>18:17:13</t>
+  </si>
+  <si>
+    <t>19:50:39</t>
+  </si>
+  <si>
+    <t>19:12:02</t>
+  </si>
+  <si>
+    <t>20:45:28</t>
+  </si>
+  <si>
+    <t>18:33:21</t>
+  </si>
+  <si>
+    <t>20:06:46</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -656,7 +647,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,19 +662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +674,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -713,7 +710,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,49 +746,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -883,6 +886,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1364,54 +1373,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L2" s="4">
-        <v>-25.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="O2" s="6">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="P2" s="7">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>87</v>
-      </c>
-      <c r="R2" s="9">
+        <v>39</v>
+      </c>
+      <c r="R2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1423,51 +1432,51 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L3" s="4">
-        <v>-36.7</v>
+        <v>-32.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="6">
-        <v>77</v>
-      </c>
-      <c r="P3" s="10">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>34</v>
-      </c>
-      <c r="R3" s="9">
+        <v>198</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1476,54 +1485,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L4" s="4">
-        <v>-40.8</v>
+        <v>-39.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O4" s="6">
-        <v>71</v>
+        <v>198</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
       </c>
       <c r="P4" s="7">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>16</v>
-      </c>
-      <c r="R4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1532,55 +1541,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L5" s="4">
-        <v>-20.2</v>
+        <v>-14</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O5" s="13">
-        <v>1</v>
-      </c>
-      <c r="P5" s="9">
+        <v>197</v>
+      </c>
+      <c r="O5" s="10">
+        <v>57</v>
+      </c>
+      <c r="P5" s="11">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
+      <c r="R5" s="12">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1591,52 +1600,52 @@
         <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="L6" s="4">
-        <v>-32.6</v>
+        <v>-27.6</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-      <c r="R6" s="9">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O6" s="10">
+        <v>62</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>16</v>
+      </c>
+      <c r="R6" s="14">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1644,55 +1653,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L7" s="4">
-        <v>-39.7</v>
+        <v>-37.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O7" s="13">
+        <v>198</v>
+      </c>
+      <c r="O7" s="10">
+        <v>55</v>
+      </c>
+      <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
-        <v>0</v>
+      <c r="Q7" s="8">
+        <v>40</v>
+      </c>
+      <c r="R7" s="15">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1700,55 +1709,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L8" s="4">
-        <v>-14</v>
+        <v>-7.6</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O8" s="13">
-        <v>1</v>
-      </c>
-      <c r="P8" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-      <c r="R8" s="9">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="O8" s="6">
+        <v>34</v>
+      </c>
+      <c r="P8" s="16">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>34</v>
+      </c>
+      <c r="R8" s="12">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1756,55 +1765,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L9" s="4">
-        <v>-27.5</v>
+        <v>-22</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-      <c r="R9" s="9">
-        <v>0</v>
+      <c r="O9" s="10">
+        <v>100</v>
+      </c>
+      <c r="P9" s="17">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>31</v>
+      </c>
+      <c r="R9" s="18">
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1812,7 +1821,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
@@ -1821,46 +1830,46 @@
         <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="L10" s="4">
-        <v>-37.3</v>
+        <v>-33.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-      <c r="R10" s="9">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="O10" s="10">
+        <v>95</v>
+      </c>
+      <c r="P10" s="16">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>64</v>
+      </c>
+      <c r="R10" s="20">
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1868,55 +1877,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="L11" s="4">
-        <v>-7.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O11" s="6">
-        <v>66</v>
-      </c>
-      <c r="P11" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>66</v>
-      </c>
-      <c r="R11" s="7">
-        <v>62</v>
+      <c r="O11" s="10">
+        <v>65</v>
+      </c>
+      <c r="P11" s="16">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="21">
+        <v>55</v>
+      </c>
+      <c r="R11" s="16">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1924,7 +1933,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
@@ -1933,46 +1942,46 @@
         <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L12" s="4">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O12" s="6">
-        <v>84</v>
-      </c>
-      <c r="P12" s="15">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>74</v>
-      </c>
-      <c r="R12" s="14">
-        <v>67</v>
+        <v>197</v>
+      </c>
+      <c r="O12" s="10">
+        <v>60</v>
+      </c>
+      <c r="P12" s="22">
+        <v>60</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>38</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1980,7 +1989,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>49</v>
@@ -1989,46 +1998,46 @@
         <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L13" s="4">
-        <v>-33.5</v>
+        <v>-29</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O13" s="6">
-        <v>49</v>
-      </c>
-      <c r="P13" s="17">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>39</v>
-      </c>
-      <c r="R13" s="15">
-        <v>5</v>
+        <v>198</v>
+      </c>
+      <c r="O13" s="10">
+        <v>85</v>
+      </c>
+      <c r="P13" s="23">
+        <v>82</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>14</v>
+      </c>
+      <c r="R13" s="24">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2036,7 +2045,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>50</v>
@@ -2045,46 +2054,46 @@
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4">
-        <v>-39.4</v>
+        <v>-37.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O14" s="6">
-        <v>55</v>
-      </c>
-      <c r="P14" s="17">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>33</v>
-      </c>
-      <c r="R14" s="17">
-        <v>19</v>
+        <v>199</v>
+      </c>
+      <c r="O14" s="10">
+        <v>77</v>
+      </c>
+      <c r="P14" s="20">
+        <v>77</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2092,7 +2101,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>51</v>
@@ -2101,46 +2110,46 @@
         <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L15" s="4">
-        <v>-15.9</v>
+        <v>-9.6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O15" s="6">
-        <v>71</v>
-      </c>
-      <c r="P15" s="19">
-        <v>68</v>
-      </c>
-      <c r="Q15" s="19">
-        <v>71</v>
-      </c>
-      <c r="R15" s="9">
-        <v>2</v>
+        <v>197</v>
+      </c>
+      <c r="O15" s="10">
+        <v>74</v>
+      </c>
+      <c r="P15" s="13">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>8</v>
+      </c>
+      <c r="R15" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2148,55 +2157,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L16" s="4">
-        <v>-28.9</v>
+        <v>-23.7</v>
       </c>
       <c r="M16" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O16" s="6">
-        <v>89</v>
-      </c>
-      <c r="P16" s="8">
-        <v>83</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>86</v>
-      </c>
-      <c r="R16" s="15">
-        <v>3</v>
+      <c r="O16" s="10">
+        <v>62</v>
+      </c>
+      <c r="P16" s="13">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>14</v>
+      </c>
+      <c r="R16" s="25">
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2204,7 +2213,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>53</v>
@@ -2213,46 +2222,46 @@
         <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L17" s="4">
-        <v>-37.5</v>
+        <v>-34.4</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O17" s="6">
-        <v>91</v>
-      </c>
-      <c r="P17" s="8">
-        <v>84</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>54</v>
-      </c>
-      <c r="R17" s="9">
-        <v>2</v>
+        <v>198</v>
+      </c>
+      <c r="O17" s="10">
+        <v>64</v>
+      </c>
+      <c r="P17" s="24">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>43</v>
+      </c>
+      <c r="R17" s="8">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2260,55 +2269,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L18" s="4">
-        <v>-9.6</v>
+        <v>-17.8</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="20">
-        <v>43</v>
-      </c>
-      <c r="P18" s="18">
-        <v>39</v>
-      </c>
-      <c r="Q18" s="21">
-        <v>10</v>
-      </c>
-      <c r="R18" s="15">
-        <v>7</v>
+        <v>197</v>
+      </c>
+      <c r="O18" s="6">
+        <v>41</v>
+      </c>
+      <c r="P18" s="16">
+        <v>22</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>31</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2316,55 +2325,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>104</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L19" s="4">
-        <v>-23.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="O19" s="6">
-        <v>47</v>
-      </c>
-      <c r="P19" s="22">
-        <v>43</v>
-      </c>
-      <c r="Q19" s="15">
-        <v>7</v>
-      </c>
-      <c r="R19" s="21">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="P19" s="13">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>18</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2372,55 +2381,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L20" s="4">
-        <v>-34.4</v>
+        <v>-11.6</v>
       </c>
       <c r="M20" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" s="6">
-        <v>50</v>
-      </c>
-      <c r="P20" s="22">
-        <v>44</v>
-      </c>
-      <c r="Q20" s="9">
-        <v>0</v>
-      </c>
-      <c r="R20" s="17">
-        <v>20</v>
+      <c r="O20" s="10">
+        <v>66</v>
+      </c>
+      <c r="P20" s="25">
+        <v>49</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>46</v>
+      </c>
+      <c r="R20" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2428,170 +2437,114 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L21" s="4">
-        <v>-17.8</v>
+        <v>-25.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O21" s="6">
-        <v>54</v>
-      </c>
-      <c r="P21" s="11">
-        <v>37</v>
-      </c>
-      <c r="Q21" s="23">
-        <v>50</v>
-      </c>
-      <c r="R21" s="21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="2">
-        <v>18</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L22" s="4">
-        <v>-30.1</v>
-      </c>
-      <c r="M22" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O22" s="6">
-        <v>66</v>
-      </c>
-      <c r="P22" s="18">
-        <v>40</v>
-      </c>
-      <c r="Q22" s="23">
-        <v>50</v>
-      </c>
-      <c r="R22" s="15">
-        <v>5</v>
+      <c r="O21" s="10">
+        <v>39</v>
+      </c>
+      <c r="P21" s="12">
+        <v>35</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>39</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A22">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C22">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D22">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F22">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G22">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2610,12 +2563,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2632,22 +2585,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P22">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="185">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260317--01</t>
-  </si>
-  <si>
-    <t>20260317--02</t>
-  </si>
-  <si>
-    <t>20260317--03</t>
-  </si>
-  <si>
     <t>20260318--01</t>
   </si>
   <si>
@@ -130,405 +121,369 @@
     <t>20260323--02</t>
   </si>
   <si>
-    <t>05:36</t>
+    <t>20260324--01</t>
+  </si>
+  <si>
+    <t>05:16</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:02</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:22</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>06:23</t>
   </si>
   <si>
-    <t>05:34</t>
-  </si>
-  <si>
-    <t>05:16</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:49</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>06:09</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:22</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>05:22</t>
-  </si>
-  <si>
-    <t>01:11</t>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>03:06</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:06</t>
-  </si>
-  <si>
     <t>01:45</t>
   </si>
   <si>
-    <t>03:39</t>
-  </si>
-  <si>
-    <t>05:28</t>
-  </si>
-  <si>
-    <t>01:33</t>
-  </si>
-  <si>
-    <t>03:24</t>
-  </si>
-  <si>
-    <t>05:14</t>
-  </si>
-  <si>
-    <t>00:49</t>
-  </si>
-  <si>
-    <t>19:13:21</t>
-  </si>
-  <si>
-    <t>20:50:31</t>
-  </si>
-  <si>
-    <t>22:28:07</t>
-  </si>
-  <si>
-    <t>18:33:17</t>
-  </si>
-  <si>
-    <t>20:10:19</t>
-  </si>
-  <si>
-    <t>21:47:52</t>
-  </si>
-  <si>
-    <t>17:53:11</t>
-  </si>
-  <si>
-    <t>19:30:04</t>
-  </si>
-  <si>
-    <t>21:07:34</t>
-  </si>
-  <si>
-    <t>22:45:30</t>
-  </si>
-  <si>
-    <t>18:49:47</t>
-  </si>
-  <si>
-    <t>20:27:13</t>
-  </si>
-  <si>
-    <t>22:05:03</t>
-  </si>
-  <si>
-    <t>18:09:27</t>
-  </si>
-  <si>
-    <t>19:46:49</t>
-  </si>
-  <si>
-    <t>21:24:34</t>
-  </si>
-  <si>
-    <t>19:06:22</t>
-  </si>
-  <si>
-    <t>20:44:02</t>
-  </si>
-  <si>
-    <t>18:25:51</t>
-  </si>
-  <si>
-    <t>20:03:28</t>
-  </si>
-  <si>
-    <t>19:15:47</t>
-  </si>
-  <si>
-    <t>20:52:46</t>
-  </si>
-  <si>
-    <t>22:30:33</t>
-  </si>
-  <si>
-    <t>18:35:47</t>
-  </si>
-  <si>
-    <t>20:12:35</t>
-  </si>
-  <si>
-    <t>21:50:15</t>
-  </si>
-  <si>
-    <t>17:55:48</t>
-  </si>
-  <si>
-    <t>19:32:21</t>
-  </si>
-  <si>
-    <t>21:09:54</t>
-  </si>
-  <si>
-    <t>22:48:56</t>
-  </si>
-  <si>
-    <t>18:52:04</t>
-  </si>
-  <si>
-    <t>20:29:32</t>
-  </si>
-  <si>
-    <t>22:08:02</t>
-  </si>
-  <si>
-    <t>18:11:45</t>
-  </si>
-  <si>
-    <t>19:49:06</t>
-  </si>
-  <si>
-    <t>21:27:18</t>
-  </si>
-  <si>
-    <t>19:08:38</t>
-  </si>
-  <si>
-    <t>20:46:38</t>
-  </si>
-  <si>
-    <t>18:28:07</t>
-  </si>
-  <si>
-    <t>20:05:57</t>
-  </si>
-  <si>
-    <t>19:18:35</t>
-  </si>
-  <si>
-    <t>20:55:58</t>
-  </si>
-  <si>
-    <t>22:33:20</t>
-  </si>
-  <si>
-    <t>18:38:25</t>
-  </si>
-  <si>
-    <t>20:15:46</t>
-  </si>
-  <si>
-    <t>21:53:10</t>
-  </si>
-  <si>
-    <t>17:58:13</t>
-  </si>
-  <si>
-    <t>19:35:30</t>
-  </si>
-  <si>
-    <t>21:12:55</t>
-  </si>
-  <si>
-    <t>22:50:04</t>
-  </si>
-  <si>
-    <t>18:55:12</t>
-  </si>
-  <si>
-    <t>20:32:37</t>
-  </si>
-  <si>
-    <t>22:09:49</t>
-  </si>
-  <si>
-    <t>18:14:50</t>
-  </si>
-  <si>
-    <t>19:52:14</t>
-  </si>
-  <si>
-    <t>21:29:29</t>
-  </si>
-  <si>
-    <t>19:11:48</t>
-  </si>
-  <si>
-    <t>20:49:06</t>
-  </si>
-  <si>
-    <t>18:31:18</t>
-  </si>
-  <si>
-    <t>20:08:38</t>
-  </si>
-  <si>
-    <t>19:21:23</t>
-  </si>
-  <si>
-    <t>20:59:09</t>
-  </si>
-  <si>
-    <t>22:36:07</t>
-  </si>
-  <si>
-    <t>18:41:03</t>
-  </si>
-  <si>
-    <t>20:18:57</t>
-  </si>
-  <si>
-    <t>21:56:05</t>
-  </si>
-  <si>
-    <t>18:00:37</t>
-  </si>
-  <si>
-    <t>19:38:40</t>
-  </si>
-  <si>
-    <t>21:15:56</t>
-  </si>
-  <si>
-    <t>22:51:11</t>
-  </si>
-  <si>
-    <t>18:58:19</t>
-  </si>
-  <si>
-    <t>20:35:42</t>
-  </si>
-  <si>
-    <t>22:11:35</t>
-  </si>
-  <si>
-    <t>18:17:54</t>
-  </si>
-  <si>
-    <t>19:55:22</t>
-  </si>
-  <si>
-    <t>21:31:40</t>
-  </si>
-  <si>
-    <t>19:14:58</t>
-  </si>
-  <si>
-    <t>20:51:34</t>
-  </si>
-  <si>
-    <t>18:34:29</t>
-  </si>
-  <si>
-    <t>20:11:19</t>
-  </si>
-  <si>
-    <t>19:23:49</t>
-  </si>
-  <si>
-    <t>21:01:24</t>
-  </si>
-  <si>
-    <t>22:38:33</t>
-  </si>
-  <si>
-    <t>18:43:34</t>
-  </si>
-  <si>
-    <t>20:21:12</t>
-  </si>
-  <si>
-    <t>21:58:27</t>
-  </si>
-  <si>
-    <t>18:03:15</t>
-  </si>
-  <si>
-    <t>19:40:56</t>
-  </si>
-  <si>
-    <t>21:18:16</t>
-  </si>
-  <si>
-    <t>22:54:37</t>
-  </si>
-  <si>
-    <t>19:00:36</t>
-  </si>
-  <si>
-    <t>20:38:00</t>
-  </si>
-  <si>
-    <t>22:14:34</t>
-  </si>
-  <si>
-    <t>18:20:13</t>
-  </si>
-  <si>
-    <t>19:57:39</t>
-  </si>
-  <si>
-    <t>21:34:24</t>
-  </si>
-  <si>
-    <t>19:17:14</t>
-  </si>
-  <si>
-    <t>20:54:09</t>
-  </si>
-  <si>
-    <t>18:36:45</t>
-  </si>
-  <si>
-    <t>20:13:47</t>
-  </si>
-  <si>
-    <t>16°</t>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>01:32</t>
+  </si>
+  <si>
+    <t>03:23</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>00:48</t>
+  </si>
+  <si>
+    <t>02:43</t>
+  </si>
+  <si>
+    <t>18:33:19</t>
+  </si>
+  <si>
+    <t>20:10:21</t>
+  </si>
+  <si>
+    <t>21:47:54</t>
+  </si>
+  <si>
+    <t>17:53:14</t>
+  </si>
+  <si>
+    <t>19:30:08</t>
+  </si>
+  <si>
+    <t>21:07:38</t>
+  </si>
+  <si>
+    <t>22:45:34</t>
+  </si>
+  <si>
+    <t>18:49:53</t>
+  </si>
+  <si>
+    <t>20:27:19</t>
+  </si>
+  <si>
+    <t>22:05:09</t>
+  </si>
+  <si>
+    <t>18:09:35</t>
+  </si>
+  <si>
+    <t>19:46:58</t>
+  </si>
+  <si>
+    <t>21:24:42</t>
+  </si>
+  <si>
+    <t>19:06:34</t>
+  </si>
+  <si>
+    <t>20:44:14</t>
+  </si>
+  <si>
+    <t>18:26:07</t>
+  </si>
+  <si>
+    <t>20:03:44</t>
+  </si>
+  <si>
+    <t>19:23:11</t>
+  </si>
+  <si>
+    <t>18:35:49</t>
+  </si>
+  <si>
+    <t>20:12:37</t>
+  </si>
+  <si>
+    <t>21:50:17</t>
+  </si>
+  <si>
+    <t>17:55:51</t>
+  </si>
+  <si>
+    <t>19:32:24</t>
+  </si>
+  <si>
+    <t>21:09:58</t>
+  </si>
+  <si>
+    <t>22:49:00</t>
+  </si>
+  <si>
+    <t>18:52:10</t>
+  </si>
+  <si>
+    <t>20:29:38</t>
+  </si>
+  <si>
+    <t>22:08:08</t>
+  </si>
+  <si>
+    <t>18:11:54</t>
+  </si>
+  <si>
+    <t>19:49:15</t>
+  </si>
+  <si>
+    <t>21:27:27</t>
+  </si>
+  <si>
+    <t>19:08:50</t>
+  </si>
+  <si>
+    <t>20:46:50</t>
+  </si>
+  <si>
+    <t>18:28:22</t>
+  </si>
+  <si>
+    <t>20:06:13</t>
+  </si>
+  <si>
+    <t>19:25:36</t>
+  </si>
+  <si>
+    <t>18:38:27</t>
+  </si>
+  <si>
+    <t>20:15:48</t>
+  </si>
+  <si>
+    <t>21:53:12</t>
+  </si>
+  <si>
+    <t>17:58:16</t>
+  </si>
+  <si>
+    <t>19:35:34</t>
+  </si>
+  <si>
+    <t>21:12:59</t>
+  </si>
+  <si>
+    <t>22:50:08</t>
+  </si>
+  <si>
+    <t>18:55:17</t>
+  </si>
+  <si>
+    <t>20:32:42</t>
+  </si>
+  <si>
+    <t>22:09:55</t>
+  </si>
+  <si>
+    <t>18:14:58</t>
+  </si>
+  <si>
+    <t>19:52:23</t>
+  </si>
+  <si>
+    <t>21:29:38</t>
+  </si>
+  <si>
+    <t>19:12:00</t>
+  </si>
+  <si>
+    <t>20:49:18</t>
+  </si>
+  <si>
+    <t>18:31:33</t>
+  </si>
+  <si>
+    <t>20:08:54</t>
+  </si>
+  <si>
+    <t>19:28:26</t>
+  </si>
+  <si>
+    <t>18:41:05</t>
+  </si>
+  <si>
+    <t>20:18:59</t>
+  </si>
+  <si>
+    <t>21:56:07</t>
+  </si>
+  <si>
+    <t>18:00:41</t>
+  </si>
+  <si>
+    <t>19:38:44</t>
+  </si>
+  <si>
+    <t>21:16:00</t>
+  </si>
+  <si>
+    <t>22:51:15</t>
+  </si>
+  <si>
+    <t>18:58:25</t>
+  </si>
+  <si>
+    <t>20:35:48</t>
+  </si>
+  <si>
+    <t>22:11:41</t>
+  </si>
+  <si>
+    <t>18:18:02</t>
+  </si>
+  <si>
+    <t>19:55:31</t>
+  </si>
+  <si>
+    <t>21:31:49</t>
+  </si>
+  <si>
+    <t>19:15:10</t>
+  </si>
+  <si>
+    <t>20:51:45</t>
+  </si>
+  <si>
+    <t>18:34:45</t>
+  </si>
+  <si>
+    <t>20:11:34</t>
+  </si>
+  <si>
+    <t>19:31:16</t>
+  </si>
+  <si>
+    <t>18:43:36</t>
+  </si>
+  <si>
+    <t>20:21:14</t>
+  </si>
+  <si>
+    <t>21:58:29</t>
+  </si>
+  <si>
+    <t>18:03:18</t>
+  </si>
+  <si>
+    <t>19:41:00</t>
+  </si>
+  <si>
+    <t>21:18:19</t>
+  </si>
+  <si>
+    <t>22:54:41</t>
+  </si>
+  <si>
+    <t>19:00:42</t>
+  </si>
+  <si>
+    <t>20:38:06</t>
+  </si>
+  <si>
+    <t>22:14:40</t>
+  </si>
+  <si>
+    <t>18:20:21</t>
+  </si>
+  <si>
+    <t>19:57:48</t>
+  </si>
+  <si>
+    <t>21:34:33</t>
+  </si>
+  <si>
+    <t>19:17:26</t>
+  </si>
+  <si>
+    <t>20:54:21</t>
+  </si>
+  <si>
+    <t>18:37:00</t>
+  </si>
+  <si>
+    <t>20:14:03</t>
+  </si>
+  <si>
+    <t>19:33:40</t>
+  </si>
+  <si>
+    <t>19°</t>
+  </si>
+  <si>
+    <t>9°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -556,46 +511,46 @@
     <t>18°</t>
   </si>
   <si>
-    <t>19:16:58</t>
-  </si>
-  <si>
-    <t>18:38:53</t>
-  </si>
-  <si>
-    <t>20:12:21</t>
-  </si>
-  <si>
-    <t>18:00:39</t>
-  </si>
-  <si>
-    <t>19:34:06</t>
-  </si>
-  <si>
-    <t>21:07:33</t>
-  </si>
-  <si>
-    <t>18:55:43</t>
-  </si>
-  <si>
-    <t>20:29:09</t>
-  </si>
-  <si>
-    <t>18:17:13</t>
-  </si>
-  <si>
-    <t>19:50:39</t>
-  </si>
-  <si>
-    <t>19:12:02</t>
-  </si>
-  <si>
-    <t>20:45:28</t>
-  </si>
-  <si>
-    <t>18:33:21</t>
-  </si>
-  <si>
-    <t>20:06:46</t>
+    <t>18:38:55</t>
+  </si>
+  <si>
+    <t>20:12:23</t>
+  </si>
+  <si>
+    <t>18:00:43</t>
+  </si>
+  <si>
+    <t>19:34:09</t>
+  </si>
+  <si>
+    <t>21:07:36</t>
+  </si>
+  <si>
+    <t>18:55:48</t>
+  </si>
+  <si>
+    <t>20:29:15</t>
+  </si>
+  <si>
+    <t>18:17:21</t>
+  </si>
+  <si>
+    <t>19:50:47</t>
+  </si>
+  <si>
+    <t>19:12:13</t>
+  </si>
+  <si>
+    <t>20:45:39</t>
+  </si>
+  <si>
+    <t>18:33:35</t>
+  </si>
+  <si>
+    <t>20:07:01</t>
+  </si>
+  <si>
+    <t>19:28:19</t>
   </si>
   <si>
     <t>A+B</t>
@@ -647,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -662,7 +617,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,13 +629,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +659,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,13 +683,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +695,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,49 +713,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -817,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,9 +838,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1295,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1373,55 +1319,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L2" s="4">
-        <v>-20.2</v>
+        <v>-14</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="O2" s="6">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="Q2" s="8">
-        <v>39</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1432,52 +1378,52 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="L3" s="4">
-        <v>-32.6</v>
+        <v>-27.6</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="P3" s="10">
+        <v>10</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R3" s="11">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1485,55 +1431,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L4" s="4">
-        <v>-39.7</v>
+        <v>-37.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
+        <v>183</v>
+      </c>
+      <c r="O4" s="12">
+        <v>92</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="Q4" s="10">
+        <v>9</v>
+      </c>
+      <c r="R4" s="13">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1541,55 +1487,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-7.6</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O5" s="9">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-14</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O5" s="10">
-        <v>57</v>
-      </c>
-      <c r="P5" s="11">
-        <v>11</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>37</v>
+      <c r="P5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>3</v>
+      </c>
+      <c r="R5" s="14">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1597,55 +1543,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-22</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="4">
-        <v>-27.6</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O6" s="10">
-        <v>62</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>16</v>
-      </c>
-      <c r="R6" s="14">
-        <v>45</v>
+      <c r="O6" s="12">
+        <v>52</v>
+      </c>
+      <c r="P6" s="14">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>14</v>
+      </c>
+      <c r="R6" s="16">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1653,55 +1599,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="L7" s="4">
-        <v>-37.3</v>
+        <v>-33.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O7" s="10">
-        <v>55</v>
-      </c>
-      <c r="P7" s="7">
+        <v>183</v>
+      </c>
+      <c r="O7" s="6">
+        <v>8</v>
+      </c>
+      <c r="P7" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
-        <v>40</v>
-      </c>
-      <c r="R7" s="15">
-        <v>29</v>
+      <c r="R7" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1709,55 +1655,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="L8" s="4">
-        <v>-7.6</v>
+        <v>-39.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O8" s="6">
-        <v>34</v>
-      </c>
-      <c r="P8" s="16">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>34</v>
-      </c>
-      <c r="R8" s="12">
-        <v>34</v>
+        <v>184</v>
+      </c>
+      <c r="O8" s="9">
+        <v>24</v>
+      </c>
+      <c r="P8" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>17</v>
+      </c>
+      <c r="R8" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1765,55 +1711,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-16</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O9" s="12">
+        <v>84</v>
+      </c>
+      <c r="P9" s="17">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="18">
         <v>31</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-22</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O9" s="10">
-        <v>100</v>
-      </c>
-      <c r="P9" s="17">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>31</v>
-      </c>
-      <c r="R9" s="18">
-        <v>99</v>
+      <c r="R9" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1821,55 +1767,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-29</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O10" s="12">
         <v>95</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-33.5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O10" s="10">
+      <c r="P10" s="19">
         <v>95</v>
       </c>
-      <c r="P10" s="16">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>64</v>
-      </c>
-      <c r="R10" s="20">
-        <v>76</v>
+      <c r="Q10" s="15">
+        <v>16</v>
+      </c>
+      <c r="R10" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1877,55 +1823,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-37.5</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="O11" s="12">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-39.4</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O11" s="10">
-        <v>65</v>
-      </c>
-      <c r="P11" s="16">
-        <v>19</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>55</v>
-      </c>
-      <c r="R11" s="16">
-        <v>20</v>
+      <c r="P11" s="19">
+        <v>96</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>12</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1933,52 +1879,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="L12" s="4">
-        <v>-16</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O12" s="10">
-        <v>60</v>
-      </c>
-      <c r="P12" s="22">
-        <v>60</v>
+        <v>182</v>
+      </c>
+      <c r="O12" s="12">
+        <v>75</v>
+      </c>
+      <c r="P12" s="17">
+        <v>67</v>
       </c>
       <c r="Q12" s="8">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="R12" s="7">
         <v>0</v>
@@ -1989,55 +1935,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="L13" s="4">
-        <v>-29</v>
+        <v>-23.7</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O13" s="10">
-        <v>85</v>
-      </c>
-      <c r="P13" s="23">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>14</v>
-      </c>
-      <c r="R13" s="24">
-        <v>4</v>
+        <v>182</v>
+      </c>
+      <c r="O13" s="12">
+        <v>69</v>
+      </c>
+      <c r="P13" s="17">
+        <v>63</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>28</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2045,52 +1991,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L14" s="4">
-        <v>-37.5</v>
+        <v>-34.4</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="O14" s="10">
-        <v>77</v>
+        <v>183</v>
+      </c>
+      <c r="O14" s="12">
+        <v>64</v>
       </c>
       <c r="P14" s="20">
-        <v>77</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="Q14" s="21">
+        <v>25</v>
       </c>
       <c r="R14" s="7">
         <v>0</v>
@@ -2101,55 +2047,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L15" s="4">
-        <v>-9.6</v>
+        <v>-17.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O15" s="10">
-        <v>74</v>
-      </c>
-      <c r="P15" s="13">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>8</v>
-      </c>
-      <c r="R15" s="12">
-        <v>35</v>
+        <v>182</v>
+      </c>
+      <c r="O15" s="12">
+        <v>87</v>
+      </c>
+      <c r="P15" s="11">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>2</v>
+      </c>
+      <c r="R15" s="22">
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2157,55 +2103,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L16" s="4">
-        <v>-23.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O16" s="10">
-        <v>62</v>
-      </c>
-      <c r="P16" s="13">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>14</v>
-      </c>
-      <c r="R16" s="25">
-        <v>52</v>
+        <v>183</v>
+      </c>
+      <c r="O16" s="12">
+        <v>74</v>
+      </c>
+      <c r="P16" s="18">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>3</v>
+      </c>
+      <c r="R16" s="23">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2213,55 +2159,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="L17" s="4">
-        <v>-34.4</v>
+        <v>-11.7</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O17" s="10">
-        <v>64</v>
-      </c>
-      <c r="P17" s="24">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="14">
-        <v>43</v>
-      </c>
-      <c r="R17" s="8">
-        <v>42</v>
+        <v>182</v>
+      </c>
+      <c r="O17" s="12">
+        <v>100</v>
+      </c>
+      <c r="P17" s="16">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="19">
+        <v>93</v>
+      </c>
+      <c r="R17" s="24">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2269,55 +2215,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="L18" s="4">
-        <v>-17.8</v>
+        <v>-25.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O18" s="6">
-        <v>41</v>
+        <v>182</v>
+      </c>
+      <c r="O18" s="12">
+        <v>100</v>
       </c>
       <c r="P18" s="16">
-        <v>22</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>31</v>
-      </c>
-      <c r="R18" s="7">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Q18" s="24">
+        <v>98</v>
+      </c>
+      <c r="R18" s="24">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2325,226 +2271,114 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="L19" s="4">
-        <v>-30.2</v>
+        <v>-19.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="O19" s="6">
-        <v>25</v>
+        <v>182</v>
+      </c>
+      <c r="O19" s="12">
+        <v>85</v>
       </c>
       <c r="P19" s="13">
-        <v>16</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>18</v>
-      </c>
-      <c r="R19" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="2">
-        <v>32</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-11.6</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O20" s="10">
-        <v>66</v>
-      </c>
-      <c r="P20" s="25">
-        <v>49</v>
-      </c>
-      <c r="Q20" s="14">
-        <v>46</v>
-      </c>
-      <c r="R20" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="2">
-        <v>20</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-25.2</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O21" s="10">
-        <v>39</v>
-      </c>
-      <c r="P21" s="12">
-        <v>35</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>39</v>
-      </c>
-      <c r="R21" s="7">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>71</v>
+      </c>
+      <c r="R19" s="8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A19">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B19">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C19">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D19">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F19">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J19">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K19">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2563,12 +2397,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M19">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N19">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2585,22 +2419,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O19">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P19">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q19">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R19">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260318--01</t>
-  </si>
-  <si>
-    <t>20260318--02</t>
-  </si>
-  <si>
-    <t>20260318--03</t>
-  </si>
-  <si>
     <t>20260319--01</t>
   </si>
   <si>
@@ -124,67 +115,61 @@
     <t>20260324--01</t>
   </si>
   <si>
-    <t>05:16</t>
+    <t>20260325--01</t>
+  </si>
+  <si>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>02:14</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>03:33</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>04:55</t>
   </si>
   <si>
     <t>06:22</t>
   </si>
   <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:02</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:22</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>03:06</t>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>01:45</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>03:38</t>
+    <t>03:39</t>
   </si>
   <si>
     <t>05:27</t>
@@ -196,370 +181,334 @@
     <t>03:23</t>
   </si>
   <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>00:48</t>
+    <t>05:12</t>
+  </si>
+  <si>
+    <t>00:47</t>
   </si>
   <si>
     <t>02:43</t>
   </si>
   <si>
-    <t>18:33:19</t>
-  </si>
-  <si>
-    <t>20:10:21</t>
-  </si>
-  <si>
-    <t>21:47:54</t>
-  </si>
-  <si>
-    <t>17:53:14</t>
-  </si>
-  <si>
-    <t>19:30:08</t>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>17:53:16</t>
+  </si>
+  <si>
+    <t>19:30:10</t>
+  </si>
+  <si>
+    <t>21:07:40</t>
+  </si>
+  <si>
+    <t>22:45:35</t>
+  </si>
+  <si>
+    <t>18:49:55</t>
+  </si>
+  <si>
+    <t>20:27:22</t>
+  </si>
+  <si>
+    <t>22:05:12</t>
+  </si>
+  <si>
+    <t>18:09:39</t>
+  </si>
+  <si>
+    <t>19:47:02</t>
+  </si>
+  <si>
+    <t>21:24:47</t>
+  </si>
+  <si>
+    <t>19:06:40</t>
+  </si>
+  <si>
+    <t>20:44:20</t>
+  </si>
+  <si>
+    <t>18:26:15</t>
+  </si>
+  <si>
+    <t>20:03:52</t>
+  </si>
+  <si>
+    <t>19:23:22</t>
+  </si>
+  <si>
+    <t>18:42:49</t>
+  </si>
+  <si>
+    <t>17:55:53</t>
+  </si>
+  <si>
+    <t>19:32:26</t>
+  </si>
+  <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
+    <t>22:49:02</t>
+  </si>
+  <si>
+    <t>18:52:12</t>
+  </si>
+  <si>
+    <t>20:29:40</t>
+  </si>
+  <si>
+    <t>22:08:11</t>
+  </si>
+  <si>
+    <t>18:11:58</t>
+  </si>
+  <si>
+    <t>19:49:19</t>
+  </si>
+  <si>
+    <t>21:27:32</t>
+  </si>
+  <si>
+    <t>19:08:56</t>
+  </si>
+  <si>
+    <t>20:46:56</t>
+  </si>
+  <si>
+    <t>18:28:31</t>
+  </si>
+  <si>
+    <t>20:06:22</t>
+  </si>
+  <si>
+    <t>19:25:47</t>
+  </si>
+  <si>
+    <t>18:45:11</t>
+  </si>
+  <si>
+    <t>17:58:18</t>
+  </si>
+  <si>
+    <t>19:35:36</t>
+  </si>
+  <si>
+    <t>21:13:01</t>
+  </si>
+  <si>
+    <t>22:50:09</t>
+  </si>
+  <si>
+    <t>18:55:20</t>
+  </si>
+  <si>
+    <t>20:32:46</t>
+  </si>
+  <si>
+    <t>22:09:58</t>
+  </si>
+  <si>
+    <t>18:15:02</t>
+  </si>
+  <si>
+    <t>19:52:27</t>
+  </si>
+  <si>
+    <t>21:29:42</t>
+  </si>
+  <si>
+    <t>19:12:06</t>
+  </si>
+  <si>
+    <t>20:49:24</t>
+  </si>
+  <si>
+    <t>18:31:42</t>
+  </si>
+  <si>
+    <t>20:09:02</t>
+  </si>
+  <si>
+    <t>19:28:37</t>
+  </si>
+  <si>
+    <t>18:48:08</t>
+  </si>
+  <si>
+    <t>18:00:42</t>
+  </si>
+  <si>
+    <t>19:38:45</t>
+  </si>
+  <si>
+    <t>21:16:01</t>
+  </si>
+  <si>
+    <t>22:51:16</t>
+  </si>
+  <si>
+    <t>18:58:28</t>
+  </si>
+  <si>
+    <t>20:35:50</t>
+  </si>
+  <si>
+    <t>22:11:44</t>
+  </si>
+  <si>
+    <t>18:18:06</t>
+  </si>
+  <si>
+    <t>19:55:35</t>
+  </si>
+  <si>
+    <t>21:31:53</t>
+  </si>
+  <si>
+    <t>19:15:16</t>
+  </si>
+  <si>
+    <t>20:51:51</t>
+  </si>
+  <si>
+    <t>18:34:53</t>
+  </si>
+  <si>
+    <t>20:11:42</t>
+  </si>
+  <si>
+    <t>19:31:26</t>
+  </si>
+  <si>
+    <t>18:51:05</t>
+  </si>
+  <si>
+    <t>18:03:20</t>
+  </si>
+  <si>
+    <t>19:41:01</t>
+  </si>
+  <si>
+    <t>21:18:21</t>
+  </si>
+  <si>
+    <t>22:54:42</t>
+  </si>
+  <si>
+    <t>19:00:45</t>
+  </si>
+  <si>
+    <t>20:38:08</t>
+  </si>
+  <si>
+    <t>22:14:42</t>
+  </si>
+  <si>
+    <t>18:20:25</t>
+  </si>
+  <si>
+    <t>19:57:52</t>
+  </si>
+  <si>
+    <t>21:34:37</t>
+  </si>
+  <si>
+    <t>19:17:32</t>
+  </si>
+  <si>
+    <t>20:54:27</t>
+  </si>
+  <si>
+    <t>18:37:08</t>
+  </si>
+  <si>
+    <t>20:14:11</t>
+  </si>
+  <si>
+    <t>19:33:51</t>
+  </si>
+  <si>
+    <t>18:53:26</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>18:00:44</t>
+  </si>
+  <si>
+    <t>19:34:11</t>
   </si>
   <si>
     <t>21:07:38</t>
   </si>
   <si>
-    <t>22:45:34</t>
-  </si>
-  <si>
-    <t>18:49:53</t>
-  </si>
-  <si>
-    <t>20:27:19</t>
-  </si>
-  <si>
-    <t>22:05:09</t>
-  </si>
-  <si>
-    <t>18:09:35</t>
-  </si>
-  <si>
-    <t>19:46:58</t>
-  </si>
-  <si>
-    <t>21:24:42</t>
-  </si>
-  <si>
-    <t>19:06:34</t>
-  </si>
-  <si>
-    <t>20:44:14</t>
-  </si>
-  <si>
-    <t>18:26:07</t>
-  </si>
-  <si>
-    <t>20:03:44</t>
-  </si>
-  <si>
-    <t>19:23:11</t>
-  </si>
-  <si>
-    <t>18:35:49</t>
-  </si>
-  <si>
-    <t>20:12:37</t>
-  </si>
-  <si>
-    <t>21:50:17</t>
-  </si>
-  <si>
-    <t>17:55:51</t>
-  </si>
-  <si>
-    <t>19:32:24</t>
-  </si>
-  <si>
-    <t>21:09:58</t>
-  </si>
-  <si>
-    <t>22:49:00</t>
-  </si>
-  <si>
-    <t>18:52:10</t>
-  </si>
-  <si>
-    <t>20:29:38</t>
-  </si>
-  <si>
-    <t>22:08:08</t>
-  </si>
-  <si>
-    <t>18:11:54</t>
-  </si>
-  <si>
-    <t>19:49:15</t>
-  </si>
-  <si>
-    <t>21:27:27</t>
-  </si>
-  <si>
-    <t>19:08:50</t>
-  </si>
-  <si>
-    <t>20:46:50</t>
-  </si>
-  <si>
-    <t>18:28:22</t>
-  </si>
-  <si>
-    <t>20:06:13</t>
-  </si>
-  <si>
-    <t>19:25:36</t>
-  </si>
-  <si>
-    <t>18:38:27</t>
-  </si>
-  <si>
-    <t>20:15:48</t>
-  </si>
-  <si>
-    <t>21:53:12</t>
-  </si>
-  <si>
-    <t>17:58:16</t>
-  </si>
-  <si>
-    <t>19:35:34</t>
-  </si>
-  <si>
-    <t>21:12:59</t>
-  </si>
-  <si>
-    <t>22:50:08</t>
-  </si>
-  <si>
-    <t>18:55:17</t>
-  </si>
-  <si>
-    <t>20:32:42</t>
-  </si>
-  <si>
-    <t>22:09:55</t>
-  </si>
-  <si>
-    <t>18:14:58</t>
-  </si>
-  <si>
-    <t>19:52:23</t>
-  </si>
-  <si>
-    <t>21:29:38</t>
-  </si>
-  <si>
-    <t>19:12:00</t>
-  </si>
-  <si>
-    <t>20:49:18</t>
-  </si>
-  <si>
-    <t>18:31:33</t>
-  </si>
-  <si>
-    <t>20:08:54</t>
-  </si>
-  <si>
-    <t>19:28:26</t>
-  </si>
-  <si>
-    <t>18:41:05</t>
-  </si>
-  <si>
-    <t>20:18:59</t>
-  </si>
-  <si>
-    <t>21:56:07</t>
-  </si>
-  <si>
-    <t>18:00:41</t>
-  </si>
-  <si>
-    <t>19:38:44</t>
-  </si>
-  <si>
-    <t>21:16:00</t>
-  </si>
-  <si>
-    <t>22:51:15</t>
-  </si>
-  <si>
-    <t>18:58:25</t>
-  </si>
-  <si>
-    <t>20:35:48</t>
-  </si>
-  <si>
-    <t>22:11:41</t>
-  </si>
-  <si>
-    <t>18:18:02</t>
-  </si>
-  <si>
-    <t>19:55:31</t>
-  </si>
-  <si>
-    <t>21:31:49</t>
-  </si>
-  <si>
-    <t>19:15:10</t>
-  </si>
-  <si>
-    <t>20:51:45</t>
-  </si>
-  <si>
-    <t>18:34:45</t>
-  </si>
-  <si>
-    <t>20:11:34</t>
-  </si>
-  <si>
-    <t>19:31:16</t>
-  </si>
-  <si>
-    <t>18:43:36</t>
-  </si>
-  <si>
-    <t>20:21:14</t>
-  </si>
-  <si>
-    <t>21:58:29</t>
-  </si>
-  <si>
-    <t>18:03:18</t>
-  </si>
-  <si>
-    <t>19:41:00</t>
-  </si>
-  <si>
-    <t>21:18:19</t>
-  </si>
-  <si>
-    <t>22:54:41</t>
-  </si>
-  <si>
-    <t>19:00:42</t>
-  </si>
-  <si>
-    <t>20:38:06</t>
-  </si>
-  <si>
-    <t>22:14:40</t>
-  </si>
-  <si>
-    <t>18:20:21</t>
-  </si>
-  <si>
-    <t>19:57:48</t>
-  </si>
-  <si>
-    <t>21:34:33</t>
-  </si>
-  <si>
-    <t>19:17:26</t>
-  </si>
-  <si>
-    <t>20:54:21</t>
-  </si>
-  <si>
-    <t>18:37:00</t>
-  </si>
-  <si>
-    <t>20:14:03</t>
-  </si>
-  <si>
-    <t>19:33:40</t>
-  </si>
-  <si>
-    <t>19°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>18:38:55</t>
-  </si>
-  <si>
-    <t>20:12:23</t>
-  </si>
-  <si>
-    <t>18:00:43</t>
-  </si>
-  <si>
-    <t>19:34:09</t>
-  </si>
-  <si>
-    <t>21:07:36</t>
-  </si>
-  <si>
-    <t>18:55:48</t>
-  </si>
-  <si>
-    <t>20:29:15</t>
-  </si>
-  <si>
-    <t>18:17:21</t>
-  </si>
-  <si>
-    <t>19:50:47</t>
-  </si>
-  <si>
-    <t>19:12:13</t>
-  </si>
-  <si>
-    <t>20:45:39</t>
-  </si>
-  <si>
-    <t>18:33:35</t>
-  </si>
-  <si>
-    <t>20:07:01</t>
-  </si>
-  <si>
-    <t>19:28:19</t>
+    <t>18:55:51</t>
+  </si>
+  <si>
+    <t>20:29:17</t>
+  </si>
+  <si>
+    <t>18:17:25</t>
+  </si>
+  <si>
+    <t>19:50:51</t>
+  </si>
+  <si>
+    <t>19:12:19</t>
+  </si>
+  <si>
+    <t>20:45:45</t>
+  </si>
+  <si>
+    <t>18:33:43</t>
+  </si>
+  <si>
+    <t>20:07:09</t>
+  </si>
+  <si>
+    <t>19:28:30</t>
+  </si>
+  <si>
+    <t>18:49:48</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>2</t>
@@ -602,7 +551,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,7 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,7 +590,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,55 +644,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,25 +656,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -829,15 +760,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1241,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1319,54 +1241,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-7.6</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L2" s="4">
-        <v>-14</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="O2" s="6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="7">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="9">
         <v>3</v>
       </c>
     </row>
@@ -1375,55 +1297,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="L3" s="4">
-        <v>-27.6</v>
+        <v>-22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O3" s="9">
-        <v>44</v>
+        <v>165</v>
+      </c>
+      <c r="O3" s="6">
+        <v>24</v>
       </c>
       <c r="P3" s="10">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-      <c r="R3" s="11">
-        <v>44</v>
+        <v>24</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1431,55 +1353,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-33.5</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="6">
         <v>38</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-37.3</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O4" s="12">
-        <v>92</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>9</v>
-      </c>
-      <c r="R4" s="13">
-        <v>61</v>
+      <c r="P4" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>1</v>
+      </c>
+      <c r="R4" s="7">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1487,55 +1409,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-39.4</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L5" s="4">
-        <v>-7.6</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O5" s="9">
-        <v>20</v>
-      </c>
-      <c r="P5" s="7">
+      <c r="O5" s="6">
+        <v>48</v>
+      </c>
+      <c r="P5" s="8">
         <v>1</v>
       </c>
-      <c r="Q5" s="8">
-        <v>3</v>
-      </c>
-      <c r="R5" s="14">
-        <v>20</v>
+      <c r="Q5" s="11">
+        <v>13</v>
+      </c>
+      <c r="R5" s="12">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1543,55 +1465,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="L6" s="4">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O6" s="12">
-        <v>52</v>
+        <v>165</v>
+      </c>
+      <c r="O6" s="13">
+        <v>83</v>
       </c>
       <c r="P6" s="14">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>14</v>
-      </c>
-      <c r="R6" s="16">
-        <v>36</v>
+        <v>77</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1599,55 +1521,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="L7" s="4">
-        <v>-33.5</v>
+        <v>-29</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O7" s="6">
-        <v>8</v>
-      </c>
-      <c r="P7" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="7">
+        <v>166</v>
+      </c>
+      <c r="O7" s="13">
+        <v>72</v>
+      </c>
+      <c r="P7" s="15">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>7</v>
+      </c>
+      <c r="R7" s="8">
         <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1655,55 +1577,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L8" s="4">
-        <v>-39.4</v>
+        <v>-37.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O8" s="9">
-        <v>24</v>
-      </c>
-      <c r="P8" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>17</v>
+        <v>167</v>
+      </c>
+      <c r="O8" s="6">
+        <v>38</v>
+      </c>
+      <c r="P8" s="16">
+        <v>38</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
       </c>
       <c r="R8" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1711,55 +1633,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L9" s="4">
-        <v>-16</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O9" s="12">
-        <v>84</v>
-      </c>
-      <c r="P9" s="17">
-        <v>64</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>31</v>
+        <v>165</v>
+      </c>
+      <c r="O9" s="6">
+        <v>17</v>
+      </c>
+      <c r="P9" s="11">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1767,55 +1689,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="L10" s="4">
-        <v>-29</v>
+        <v>-23.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O10" s="12">
-        <v>95</v>
-      </c>
-      <c r="P10" s="19">
-        <v>95</v>
-      </c>
-      <c r="Q10" s="15">
-        <v>16</v>
-      </c>
-      <c r="R10" s="7">
-        <v>2</v>
+        <v>165</v>
+      </c>
+      <c r="O10" s="6">
+        <v>20</v>
+      </c>
+      <c r="P10" s="11">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>1</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1823,54 +1745,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L11" s="4">
-        <v>-37.5</v>
+        <v>-34.4</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="O11" s="12">
-        <v>96</v>
-      </c>
-      <c r="P11" s="19">
-        <v>96</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>12</v>
-      </c>
-      <c r="R11" s="7">
+        <v>166</v>
+      </c>
+      <c r="O11" s="17">
+        <v>7</v>
+      </c>
+      <c r="P11" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>3</v>
+      </c>
+      <c r="R11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1879,54 +1801,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="L12" s="4">
-        <v>-9.699999999999999</v>
+        <v>-17.9</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O12" s="12">
-        <v>75</v>
-      </c>
-      <c r="P12" s="17">
-        <v>67</v>
+        <v>165</v>
+      </c>
+      <c r="O12" s="6">
+        <v>22</v>
+      </c>
+      <c r="P12" s="11">
+        <v>17</v>
       </c>
       <c r="Q12" s="8">
-        <v>3</v>
-      </c>
-      <c r="R12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1935,54 +1857,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="L13" s="4">
-        <v>-23.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O13" s="12">
-        <v>69</v>
-      </c>
-      <c r="P13" s="17">
-        <v>63</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>28</v>
-      </c>
-      <c r="R13" s="7">
+        <v>166</v>
+      </c>
+      <c r="O13" s="6">
+        <v>41</v>
+      </c>
+      <c r="P13" s="10">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1991,55 +1913,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="L14" s="4">
-        <v>-34.4</v>
+        <v>-11.7</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O14" s="12">
-        <v>64</v>
-      </c>
-      <c r="P14" s="20">
-        <v>56</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>25</v>
-      </c>
-      <c r="R14" s="7">
+        <v>165</v>
+      </c>
+      <c r="O14" s="17">
+        <v>17</v>
+      </c>
+      <c r="P14" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="8">
         <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2047,55 +1969,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="L15" s="4">
-        <v>-17.9</v>
+        <v>-25.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O15" s="12">
-        <v>87</v>
-      </c>
-      <c r="P15" s="11">
-        <v>43</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>2</v>
-      </c>
-      <c r="R15" s="22">
-        <v>75</v>
+        <v>165</v>
+      </c>
+      <c r="O15" s="6">
+        <v>39</v>
+      </c>
+      <c r="P15" s="10">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="18">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2103,55 +2025,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-30.2</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="O16" s="12">
-        <v>74</v>
-      </c>
-      <c r="P16" s="18">
-        <v>31</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>3</v>
-      </c>
-      <c r="R16" s="23">
-        <v>69</v>
+        <v>165</v>
+      </c>
+      <c r="O16" s="13">
+        <v>100</v>
+      </c>
+      <c r="P16" s="14">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="19">
+        <v>92</v>
+      </c>
+      <c r="R16" s="20">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2159,226 +2081,114 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O17" s="13">
         <v>96</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O17" s="12">
-        <v>100</v>
-      </c>
-      <c r="P17" s="16">
-        <v>34</v>
+      <c r="P17" s="12">
+        <v>51</v>
       </c>
       <c r="Q17" s="19">
-        <v>93</v>
-      </c>
-      <c r="R17" s="24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
-        <v>20</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-25.2</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O18" s="12">
-        <v>100</v>
-      </c>
-      <c r="P18" s="16">
-        <v>33</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>98</v>
-      </c>
-      <c r="R18" s="24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O19" s="12">
-        <v>85</v>
-      </c>
-      <c r="P19" s="13">
-        <v>60</v>
-      </c>
-      <c r="Q19" s="23">
-        <v>71</v>
-      </c>
-      <c r="R19" s="8">
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="R17" s="21">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
+  <conditionalFormatting sqref="A2:A17">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B19">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C19">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2397,12 +2207,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2419,22 +2229,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P19">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q19">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="155">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260319--01</t>
-  </si>
-  <si>
-    <t>20260319--02</t>
-  </si>
-  <si>
-    <t>20260319--03</t>
-  </si>
-  <si>
-    <t>20260319--04</t>
-  </si>
-  <si>
     <t>20260320--01</t>
   </si>
   <si>
@@ -118,43 +106,40 @@
     <t>20260325--01</t>
   </si>
   <si>
-    <t>04:49</t>
-  </si>
-  <si>
-    <t>06:19</t>
-  </si>
-  <si>
-    <t>06:01</t>
-  </si>
-  <si>
-    <t>02:14</t>
+    <t>20260326--01</t>
+  </si>
+  <si>
+    <t>20260326--02</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>06:09</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>03:33</t>
-  </si>
-  <si>
-    <t>06:08</t>
-  </si>
-  <si>
     <t>04:21</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>05:20</t>
+    <t>04:56</t>
+  </si>
+  <si>
+    <t>06:23</t>
+  </si>
+  <si>
+    <t>05:21</t>
   </si>
   <si>
     <t>05:39</t>
@@ -163,28 +148,31 @@
     <t>05:54</t>
   </si>
   <si>
-    <t>01:45</t>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>02:48</t>
+  </si>
+  <si>
+    <t>03:38</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:39</t>
-  </si>
-  <si>
     <t>05:27</t>
   </si>
   <si>
-    <t>01:32</t>
-  </si>
-  <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>05:12</t>
-  </si>
-  <si>
-    <t>00:47</t>
+    <t>01:31</t>
+  </si>
+  <si>
+    <t>03:24</t>
+  </si>
+  <si>
+    <t>05:13</t>
+  </si>
+  <si>
+    <t>00:48</t>
   </si>
   <si>
     <t>02:43</t>
@@ -193,64 +181,49 @@
     <t>04:37</t>
   </si>
   <si>
-    <t>17:53:16</t>
-  </si>
-  <si>
-    <t>19:30:10</t>
-  </si>
-  <si>
-    <t>21:07:40</t>
-  </si>
-  <si>
-    <t>22:45:35</t>
+    <t>01:09</t>
   </si>
   <si>
     <t>18:49:55</t>
   </si>
   <si>
-    <t>20:27:22</t>
-  </si>
-  <si>
-    <t>22:05:12</t>
-  </si>
-  <si>
-    <t>18:09:39</t>
-  </si>
-  <si>
-    <t>19:47:02</t>
-  </si>
-  <si>
-    <t>21:24:47</t>
-  </si>
-  <si>
-    <t>19:06:40</t>
-  </si>
-  <si>
-    <t>20:44:20</t>
-  </si>
-  <si>
-    <t>18:26:15</t>
-  </si>
-  <si>
-    <t>20:03:52</t>
-  </si>
-  <si>
-    <t>19:23:22</t>
-  </si>
-  <si>
-    <t>18:42:49</t>
-  </si>
-  <si>
-    <t>17:55:53</t>
-  </si>
-  <si>
-    <t>19:32:26</t>
-  </si>
-  <si>
-    <t>21:10:00</t>
-  </si>
-  <si>
-    <t>22:49:02</t>
+    <t>20:27:21</t>
+  </si>
+  <si>
+    <t>22:05:11</t>
+  </si>
+  <si>
+    <t>18:09:38</t>
+  </si>
+  <si>
+    <t>19:47:01</t>
+  </si>
+  <si>
+    <t>21:24:45</t>
+  </si>
+  <si>
+    <t>19:06:37</t>
+  </si>
+  <si>
+    <t>20:44:18</t>
+  </si>
+  <si>
+    <t>18:26:11</t>
+  </si>
+  <si>
+    <t>20:03:48</t>
+  </si>
+  <si>
+    <t>19:23:15</t>
+  </si>
+  <si>
+    <t>18:42:41</t>
+  </si>
+  <si>
+    <t>18:02:04</t>
+  </si>
+  <si>
+    <t>19:39:56</t>
   </si>
   <si>
     <t>18:52:12</t>
@@ -262,255 +235,240 @@
     <t>22:08:11</t>
   </si>
   <si>
-    <t>18:11:58</t>
-  </si>
-  <si>
-    <t>19:49:19</t>
-  </si>
-  <si>
-    <t>21:27:32</t>
-  </si>
-  <si>
-    <t>19:08:56</t>
-  </si>
-  <si>
-    <t>20:46:56</t>
-  </si>
-  <si>
-    <t>18:28:31</t>
-  </si>
-  <si>
-    <t>20:06:22</t>
-  </si>
-  <si>
-    <t>19:25:47</t>
-  </si>
-  <si>
-    <t>18:45:11</t>
-  </si>
-  <si>
-    <t>17:58:18</t>
-  </si>
-  <si>
-    <t>19:35:36</t>
-  </si>
-  <si>
-    <t>21:13:01</t>
-  </si>
-  <si>
-    <t>22:50:09</t>
-  </si>
-  <si>
-    <t>18:55:20</t>
-  </si>
-  <si>
-    <t>20:32:46</t>
-  </si>
-  <si>
-    <t>22:09:58</t>
-  </si>
-  <si>
-    <t>18:15:02</t>
-  </si>
-  <si>
-    <t>19:52:27</t>
-  </si>
-  <si>
-    <t>21:29:42</t>
-  </si>
-  <si>
-    <t>19:12:06</t>
-  </si>
-  <si>
-    <t>20:49:24</t>
-  </si>
-  <si>
-    <t>18:31:42</t>
-  </si>
-  <si>
-    <t>20:09:02</t>
-  </si>
-  <si>
-    <t>19:28:37</t>
-  </si>
-  <si>
-    <t>18:48:08</t>
-  </si>
-  <si>
-    <t>18:00:42</t>
-  </si>
-  <si>
-    <t>19:38:45</t>
-  </si>
-  <si>
-    <t>21:16:01</t>
-  </si>
-  <si>
-    <t>22:51:16</t>
-  </si>
-  <si>
-    <t>18:58:28</t>
+    <t>18:11:56</t>
+  </si>
+  <si>
+    <t>19:49:18</t>
+  </si>
+  <si>
+    <t>21:27:30</t>
+  </si>
+  <si>
+    <t>19:08:53</t>
+  </si>
+  <si>
+    <t>20:46:53</t>
+  </si>
+  <si>
+    <t>18:28:26</t>
+  </si>
+  <si>
+    <t>20:06:17</t>
+  </si>
+  <si>
+    <t>19:25:41</t>
+  </si>
+  <si>
+    <t>18:45:03</t>
+  </si>
+  <si>
+    <t>18:04:23</t>
+  </si>
+  <si>
+    <t>19:43:10</t>
+  </si>
+  <si>
+    <t>18:55:19</t>
+  </si>
+  <si>
+    <t>20:32:45</t>
+  </si>
+  <si>
+    <t>22:09:57</t>
+  </si>
+  <si>
+    <t>18:15:01</t>
+  </si>
+  <si>
+    <t>19:52:25</t>
+  </si>
+  <si>
+    <t>21:29:41</t>
+  </si>
+  <si>
+    <t>19:12:03</t>
+  </si>
+  <si>
+    <t>20:49:21</t>
+  </si>
+  <si>
+    <t>18:31:37</t>
+  </si>
+  <si>
+    <t>20:08:58</t>
+  </si>
+  <si>
+    <t>19:28:31</t>
+  </si>
+  <si>
+    <t>18:48:00</t>
+  </si>
+  <si>
+    <t>18:07:25</t>
+  </si>
+  <si>
+    <t>19:44:34</t>
+  </si>
+  <si>
+    <t>18:58:27</t>
   </si>
   <si>
     <t>20:35:50</t>
   </si>
   <si>
-    <t>22:11:44</t>
-  </si>
-  <si>
-    <t>18:18:06</t>
-  </si>
-  <si>
-    <t>19:55:35</t>
-  </si>
-  <si>
-    <t>21:31:53</t>
-  </si>
-  <si>
-    <t>19:15:16</t>
-  </si>
-  <si>
-    <t>20:51:51</t>
-  </si>
-  <si>
-    <t>18:34:53</t>
-  </si>
-  <si>
-    <t>20:11:42</t>
-  </si>
-  <si>
-    <t>19:31:26</t>
-  </si>
-  <si>
-    <t>18:51:05</t>
-  </si>
-  <si>
-    <t>18:03:20</t>
-  </si>
-  <si>
-    <t>19:41:01</t>
-  </si>
-  <si>
-    <t>21:18:21</t>
-  </si>
-  <si>
-    <t>22:54:42</t>
-  </si>
-  <si>
-    <t>19:00:45</t>
-  </si>
-  <si>
-    <t>20:38:08</t>
+    <t>22:11:43</t>
+  </si>
+  <si>
+    <t>18:18:05</t>
+  </si>
+  <si>
+    <t>19:55:34</t>
+  </si>
+  <si>
+    <t>21:31:51</t>
+  </si>
+  <si>
+    <t>19:15:13</t>
+  </si>
+  <si>
+    <t>20:51:49</t>
+  </si>
+  <si>
+    <t>18:34:49</t>
+  </si>
+  <si>
+    <t>20:11:38</t>
+  </si>
+  <si>
+    <t>19:31:20</t>
+  </si>
+  <si>
+    <t>18:50:57</t>
+  </si>
+  <si>
+    <t>18:10:28</t>
+  </si>
+  <si>
+    <t>19:45:58</t>
+  </si>
+  <si>
+    <t>19:00:44</t>
+  </si>
+  <si>
+    <t>20:38:07</t>
   </si>
   <si>
     <t>22:14:42</t>
   </si>
   <si>
-    <t>18:20:25</t>
-  </si>
-  <si>
-    <t>19:57:52</t>
-  </si>
-  <si>
-    <t>21:34:37</t>
-  </si>
-  <si>
-    <t>19:17:32</t>
-  </si>
-  <si>
-    <t>20:54:27</t>
-  </si>
-  <si>
-    <t>18:37:08</t>
-  </si>
-  <si>
-    <t>20:14:11</t>
-  </si>
-  <si>
-    <t>19:33:51</t>
-  </si>
-  <si>
-    <t>18:53:26</t>
-  </si>
-  <si>
-    <t>10°</t>
+    <t>18:20:24</t>
+  </si>
+  <si>
+    <t>19:57:50</t>
+  </si>
+  <si>
+    <t>21:34:36</t>
+  </si>
+  <si>
+    <t>19:17:29</t>
+  </si>
+  <si>
+    <t>20:54:24</t>
+  </si>
+  <si>
+    <t>18:37:04</t>
+  </si>
+  <si>
+    <t>20:14:07</t>
+  </si>
+  <si>
+    <t>19:33:45</t>
+  </si>
+  <si>
+    <t>18:53:18</t>
+  </si>
+  <si>
+    <t>18:12:47</t>
+  </si>
+  <si>
+    <t>19:49:11</t>
+  </si>
+  <si>
+    <t>29°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18°</t>
   </si>
   <si>
     <t>23°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>29°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>18:00:44</t>
-  </si>
-  <si>
-    <t>19:34:11</t>
-  </si>
-  <si>
-    <t>21:07:38</t>
-  </si>
-  <si>
-    <t>18:55:51</t>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>18:55:50</t>
   </si>
   <si>
     <t>20:29:17</t>
   </si>
   <si>
-    <t>18:17:25</t>
-  </si>
-  <si>
-    <t>19:50:51</t>
-  </si>
-  <si>
-    <t>19:12:19</t>
-  </si>
-  <si>
-    <t>20:45:45</t>
-  </si>
-  <si>
-    <t>18:33:43</t>
-  </si>
-  <si>
-    <t>20:07:09</t>
-  </si>
-  <si>
-    <t>19:28:30</t>
-  </si>
-  <si>
-    <t>18:49:48</t>
+    <t>18:17:23</t>
+  </si>
+  <si>
+    <t>19:50:49</t>
+  </si>
+  <si>
+    <t>19:12:17</t>
+  </si>
+  <si>
+    <t>20:45:42</t>
+  </si>
+  <si>
+    <t>18:33:39</t>
+  </si>
+  <si>
+    <t>20:07:05</t>
+  </si>
+  <si>
+    <t>19:28:24</t>
+  </si>
+  <si>
+    <t>18:49:40</t>
+  </si>
+  <si>
+    <t>18:10:54</t>
+  </si>
+  <si>
+    <t>19:44:19</t>
+  </si>
+  <si>
+    <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -518,6 +476,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -551,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,13 +527,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +551,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,61 +629,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -760,6 +733,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1163,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1241,49 +1220,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L2" s="4">
-        <v>-7.6</v>
+        <v>-16</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O2" s="6">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="P2" s="7">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -1297,55 +1276,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="L3" s="4">
-        <v>-22</v>
+        <v>-29</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="O3" s="6">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P3" s="10">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="9">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>3</v>
+      </c>
+      <c r="R3" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1353,55 +1332,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="L4" s="4">
-        <v>-33.5</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="O4" s="6">
-        <v>38</v>
-      </c>
-      <c r="P4" s="9">
-        <v>4</v>
+        <v>48</v>
+      </c>
+      <c r="P4" s="7">
+        <v>44</v>
       </c>
       <c r="Q4" s="8">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1409,55 +1388,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="L5" s="4">
-        <v>-39.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O5" s="6">
-        <v>48</v>
-      </c>
-      <c r="P5" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>13</v>
-      </c>
-      <c r="R5" s="12">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="P5" s="10">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1468,46 +1447,46 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="L6" s="4">
-        <v>-16</v>
+        <v>-23.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O6" s="13">
-        <v>83</v>
-      </c>
-      <c r="P6" s="14">
-        <v>77</v>
+        <v>151</v>
+      </c>
+      <c r="O6" s="11">
+        <v>25</v>
+      </c>
+      <c r="P6" s="12">
+        <v>25</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
@@ -1521,52 +1500,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="L7" s="4">
-        <v>-29</v>
+        <v>-34.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O7" s="13">
-        <v>72</v>
-      </c>
-      <c r="P7" s="15">
-        <v>63</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>7</v>
+        <v>152</v>
+      </c>
+      <c r="O7" s="6">
+        <v>54</v>
+      </c>
+      <c r="P7" s="13">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
       </c>
       <c r="R7" s="8">
         <v>0</v>
@@ -1577,55 +1556,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="L8" s="4">
-        <v>-37.5</v>
+        <v>-17.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O8" s="6">
-        <v>38</v>
-      </c>
-      <c r="P8" s="16">
-        <v>38</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="14">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>76</v>
+      </c>
+      <c r="R8" s="16">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1633,55 +1612,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="L9" s="4">
-        <v>-9.699999999999999</v>
+        <v>-30.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="O9" s="6">
-        <v>17</v>
-      </c>
-      <c r="P9" s="11">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="P9" s="9">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>62</v>
+      </c>
+      <c r="R9" s="18">
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1689,55 +1668,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.7</v>
+        <v>-11.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O10" s="6">
-        <v>20</v>
-      </c>
-      <c r="P10" s="11">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="P10" s="19">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>18</v>
+      </c>
+      <c r="R10" s="13">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1745,55 +1724,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="L11" s="4">
-        <v>-34.4</v>
+        <v>-25.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O11" s="17">
-        <v>7</v>
-      </c>
-      <c r="P11" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>3</v>
-      </c>
-      <c r="R11" s="8">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="O11" s="6">
+        <v>82</v>
+      </c>
+      <c r="P11" s="21">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>11</v>
+      </c>
+      <c r="R11" s="14">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1801,55 +1780,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L12" s="4">
-        <v>-17.9</v>
+        <v>-19.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O12" s="6">
-        <v>22</v>
-      </c>
-      <c r="P12" s="11">
-        <v>17</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="P12" s="20">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>47</v>
+      </c>
+      <c r="R12" s="10">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1857,55 +1836,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L13" s="4">
-        <v>-30.2</v>
+        <v>-13.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="O13" s="6">
-        <v>41</v>
-      </c>
-      <c r="P13" s="10">
-        <v>27</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P13" s="22">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>73</v>
+      </c>
+      <c r="R13" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1913,55 +1892,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="L14" s="4">
-        <v>-11.7</v>
+        <v>-7.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O14" s="17">
-        <v>17</v>
-      </c>
-      <c r="P14" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
-        <v>14</v>
+        <v>154</v>
+      </c>
+      <c r="O14" s="6">
+        <v>100</v>
+      </c>
+      <c r="P14" s="17">
+        <v>58</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>100</v>
+      </c>
+      <c r="R14" s="22">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1969,226 +1948,114 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="L15" s="4">
-        <v>-25.2</v>
+        <v>-21.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O15" s="6">
-        <v>39</v>
-      </c>
-      <c r="P15" s="10">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>0</v>
-      </c>
-      <c r="R15" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-19.6</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O16" s="13">
         <v>100</v>
       </c>
-      <c r="P16" s="14">
-        <v>76</v>
-      </c>
-      <c r="Q16" s="19">
-        <v>92</v>
-      </c>
-      <c r="R16" s="20">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2">
-        <v>25</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-13.6</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="O17" s="13">
-        <v>96</v>
-      </c>
-      <c r="P17" s="12">
-        <v>51</v>
-      </c>
-      <c r="Q17" s="19">
-        <v>88</v>
-      </c>
-      <c r="R17" s="21">
-        <v>82</v>
+      <c r="P15" s="23">
+        <v>66</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>100</v>
+      </c>
+      <c r="R15" s="7">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A17">
+  <conditionalFormatting sqref="A2:A15">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B15">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C15">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D17">
+  <conditionalFormatting sqref="D2:D15">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I15">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J17">
+  <conditionalFormatting sqref="J2:J15">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K17">
+  <conditionalFormatting sqref="K2:K15">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
+  <conditionalFormatting sqref="L2:L15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2207,12 +2074,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M15">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N17">
+  <conditionalFormatting sqref="N2:N15">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2229,22 +2096,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O17">
+  <conditionalFormatting sqref="O2:O15">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
+  <conditionalFormatting sqref="P2:P15">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q17">
+  <conditionalFormatting sqref="Q2:Q15">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R17">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="140">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260320--01</t>
-  </si>
-  <si>
-    <t>20260320--02</t>
-  </si>
-  <si>
-    <t>20260320--03</t>
-  </si>
-  <si>
     <t>20260321--01</t>
   </si>
   <si>
@@ -112,67 +103,61 @@
     <t>20260326--02</t>
   </si>
   <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>20260327--01</t>
+  </si>
+  <si>
+    <t>06:08</t>
   </si>
   <si>
     <t>06:16</t>
   </si>
   <si>
-    <t>04:21</t>
+    <t>04:20</t>
   </si>
   <si>
     <t>06:20</t>
   </si>
   <si>
-    <t>04:56</t>
-  </si>
-  <si>
-    <t>06:23</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>05:39</t>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>06:22</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:40</t>
   </si>
   <si>
     <t>05:54</t>
   </si>
   <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>02:48</t>
-  </si>
-  <si>
-    <t>03:38</t>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>02:47</t>
+  </si>
+  <si>
+    <t>03:53</t>
+  </si>
+  <si>
+    <t>05:27</t>
+  </si>
+  <si>
+    <t>01:32</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>01:31</t>
-  </si>
-  <si>
-    <t>03:24</t>
+    <t>03:23</t>
   </si>
   <si>
     <t>05:13</t>
   </si>
   <si>
-    <t>00:48</t>
+    <t>00:47</t>
   </si>
   <si>
     <t>02:43</t>
@@ -184,121 +169,103 @@
     <t>01:09</t>
   </si>
   <si>
-    <t>18:49:55</t>
-  </si>
-  <si>
-    <t>20:27:21</t>
-  </si>
-  <si>
-    <t>22:05:11</t>
-  </si>
-  <si>
-    <t>18:09:38</t>
-  </si>
-  <si>
-    <t>19:47:01</t>
-  </si>
-  <si>
-    <t>21:24:45</t>
-  </si>
-  <si>
-    <t>19:06:37</t>
-  </si>
-  <si>
-    <t>20:44:18</t>
-  </si>
-  <si>
-    <t>18:26:11</t>
-  </si>
-  <si>
-    <t>20:03:48</t>
-  </si>
-  <si>
-    <t>19:23:15</t>
+    <t>03:29</t>
+  </si>
+  <si>
+    <t>18:09:40</t>
+  </si>
+  <si>
+    <t>19:47:03</t>
+  </si>
+  <si>
+    <t>21:24:48</t>
+  </si>
+  <si>
+    <t>19:06:40</t>
+  </si>
+  <si>
+    <t>20:44:20</t>
+  </si>
+  <si>
+    <t>18:26:13</t>
+  </si>
+  <si>
+    <t>20:03:50</t>
+  </si>
+  <si>
+    <t>19:23:17</t>
   </si>
   <si>
     <t>18:42:41</t>
   </si>
   <si>
-    <t>18:02:04</t>
-  </si>
-  <si>
-    <t>19:39:56</t>
-  </si>
-  <si>
-    <t>18:52:12</t>
-  </si>
-  <si>
-    <t>20:29:40</t>
-  </si>
-  <si>
-    <t>22:08:11</t>
-  </si>
-  <si>
-    <t>18:11:56</t>
-  </si>
-  <si>
-    <t>19:49:18</t>
-  </si>
-  <si>
-    <t>21:27:30</t>
-  </si>
-  <si>
-    <t>19:08:53</t>
-  </si>
-  <si>
-    <t>20:46:53</t>
-  </si>
-  <si>
-    <t>18:28:26</t>
-  </si>
-  <si>
-    <t>20:06:17</t>
-  </si>
-  <si>
-    <t>19:25:41</t>
+    <t>18:02:03</t>
+  </si>
+  <si>
+    <t>19:39:54</t>
+  </si>
+  <si>
+    <t>18:59:06</t>
+  </si>
+  <si>
+    <t>18:11:59</t>
+  </si>
+  <si>
+    <t>19:49:20</t>
+  </si>
+  <si>
+    <t>21:27:33</t>
+  </si>
+  <si>
+    <t>19:08:56</t>
+  </si>
+  <si>
+    <t>20:46:56</t>
+  </si>
+  <si>
+    <t>18:28:29</t>
+  </si>
+  <si>
+    <t>20:06:20</t>
+  </si>
+  <si>
+    <t>19:25:42</t>
   </si>
   <si>
     <t>18:45:03</t>
   </si>
   <si>
-    <t>18:04:23</t>
-  </si>
-  <si>
-    <t>19:43:10</t>
-  </si>
-  <si>
-    <t>18:55:19</t>
-  </si>
-  <si>
-    <t>20:32:45</t>
-  </si>
-  <si>
-    <t>22:09:57</t>
-  </si>
-  <si>
-    <t>18:15:01</t>
-  </si>
-  <si>
-    <t>19:52:25</t>
-  </si>
-  <si>
-    <t>21:29:41</t>
-  </si>
-  <si>
-    <t>19:12:03</t>
-  </si>
-  <si>
-    <t>20:49:21</t>
-  </si>
-  <si>
-    <t>18:31:37</t>
-  </si>
-  <si>
-    <t>20:08:58</t>
-  </si>
-  <si>
-    <t>19:28:31</t>
+    <t>18:04:22</t>
+  </si>
+  <si>
+    <t>19:43:09</t>
+  </si>
+  <si>
+    <t>19:02:00</t>
+  </si>
+  <si>
+    <t>18:15:03</t>
+  </si>
+  <si>
+    <t>19:52:28</t>
+  </si>
+  <si>
+    <t>21:29:43</t>
+  </si>
+  <si>
+    <t>19:12:06</t>
+  </si>
+  <si>
+    <t>20:49:24</t>
+  </si>
+  <si>
+    <t>18:31:40</t>
+  </si>
+  <si>
+    <t>20:09:00</t>
+  </si>
+  <si>
+    <t>19:28:32</t>
   </si>
   <si>
     <t>18:48:00</t>
@@ -307,157 +274,145 @@
     <t>18:07:25</t>
   </si>
   <si>
-    <t>19:44:34</t>
-  </si>
-  <si>
-    <t>18:58:27</t>
-  </si>
-  <si>
-    <t>20:35:50</t>
-  </si>
-  <si>
-    <t>22:11:43</t>
-  </si>
-  <si>
-    <t>18:18:05</t>
-  </si>
-  <si>
-    <t>19:55:34</t>
-  </si>
-  <si>
-    <t>21:31:51</t>
-  </si>
-  <si>
-    <t>19:15:13</t>
-  </si>
-  <si>
-    <t>20:51:49</t>
-  </si>
-  <si>
-    <t>18:34:49</t>
-  </si>
-  <si>
-    <t>20:11:38</t>
-  </si>
-  <si>
-    <t>19:31:20</t>
+    <t>19:44:33</t>
+  </si>
+  <si>
+    <t>19:03:56</t>
+  </si>
+  <si>
+    <t>18:18:07</t>
+  </si>
+  <si>
+    <t>19:55:36</t>
+  </si>
+  <si>
+    <t>21:31:53</t>
+  </si>
+  <si>
+    <t>19:15:16</t>
+  </si>
+  <si>
+    <t>20:51:51</t>
+  </si>
+  <si>
+    <t>18:34:51</t>
+  </si>
+  <si>
+    <t>20:11:40</t>
+  </si>
+  <si>
+    <t>19:31:22</t>
   </si>
   <si>
     <t>18:50:57</t>
   </si>
   <si>
-    <t>18:10:28</t>
-  </si>
-  <si>
-    <t>19:45:58</t>
-  </si>
-  <si>
-    <t>19:00:44</t>
-  </si>
-  <si>
-    <t>20:38:07</t>
-  </si>
-  <si>
-    <t>22:14:42</t>
-  </si>
-  <si>
-    <t>18:20:24</t>
-  </si>
-  <si>
-    <t>19:57:50</t>
-  </si>
-  <si>
-    <t>21:34:36</t>
-  </si>
-  <si>
-    <t>19:17:29</t>
-  </si>
-  <si>
-    <t>20:54:24</t>
-  </si>
-  <si>
-    <t>18:37:04</t>
-  </si>
-  <si>
-    <t>20:14:07</t>
-  </si>
-  <si>
-    <t>19:33:45</t>
+    <t>18:10:26</t>
+  </si>
+  <si>
+    <t>19:45:56</t>
+  </si>
+  <si>
+    <t>19:05:53</t>
+  </si>
+  <si>
+    <t>18:20:26</t>
+  </si>
+  <si>
+    <t>19:57:52</t>
+  </si>
+  <si>
+    <t>21:34:38</t>
+  </si>
+  <si>
+    <t>19:17:32</t>
+  </si>
+  <si>
+    <t>20:54:26</t>
+  </si>
+  <si>
+    <t>18:37:06</t>
+  </si>
+  <si>
+    <t>20:14:09</t>
+  </si>
+  <si>
+    <t>19:33:46</t>
   </si>
   <si>
     <t>18:53:18</t>
   </si>
   <si>
-    <t>18:12:47</t>
-  </si>
-  <si>
-    <t>19:49:11</t>
-  </si>
-  <si>
-    <t>29°</t>
+    <t>18:12:45</t>
+  </si>
+  <si>
+    <t>19:49:10</t>
+  </si>
+  <si>
+    <t>19:08:45</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>23°</t>
   </si>
   <si>
     <t>8°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
     <t>12°</t>
   </si>
   <si>
-    <t>18:55:50</t>
-  </si>
-  <si>
-    <t>20:29:17</t>
-  </si>
-  <si>
-    <t>18:17:23</t>
-  </si>
-  <si>
-    <t>19:50:49</t>
-  </si>
-  <si>
-    <t>19:12:17</t>
-  </si>
-  <si>
-    <t>20:45:42</t>
-  </si>
-  <si>
-    <t>18:33:39</t>
-  </si>
-  <si>
-    <t>20:07:05</t>
-  </si>
-  <si>
-    <t>19:28:24</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>18:17:26</t>
+  </si>
+  <si>
+    <t>19:50:52</t>
+  </si>
+  <si>
+    <t>19:12:19</t>
+  </si>
+  <si>
+    <t>20:45:45</t>
+  </si>
+  <si>
+    <t>18:33:42</t>
+  </si>
+  <si>
+    <t>20:07:07</t>
+  </si>
+  <si>
+    <t>19:28:25</t>
   </si>
   <si>
     <t>18:49:40</t>
   </si>
   <si>
-    <t>18:10:54</t>
-  </si>
-  <si>
-    <t>19:44:19</t>
+    <t>18:10:53</t>
+  </si>
+  <si>
+    <t>19:44:18</t>
+  </si>
+  <si>
+    <t>19:05:29</t>
   </si>
   <si>
     <t>A+B</t>
@@ -475,10 +430,10 @@
     <t>3</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -512,7 +467,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,7 +482,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,97 +566,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -733,12 +676,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1142,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1220,55 +1157,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L2" s="4">
-        <v>-16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="O2" s="6">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="P2" s="7">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>3</v>
+      <c r="R2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1276,55 +1213,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="L3" s="4">
-        <v>-29</v>
+        <v>-23.7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O3" s="6">
+        <v>136</v>
+      </c>
+      <c r="O3" s="9">
+        <v>55</v>
+      </c>
+      <c r="P3" s="10">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="7">
         <v>38</v>
       </c>
-      <c r="P3" s="10">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>3</v>
-      </c>
       <c r="R3" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1332,52 +1269,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L4" s="4">
-        <v>-37.5</v>
+        <v>-34.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="O4" s="6">
-        <v>48</v>
-      </c>
-      <c r="P4" s="7">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="P4" s="11">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>9</v>
       </c>
       <c r="R4" s="8">
         <v>0</v>
@@ -1388,55 +1325,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="L5" s="4">
-        <v>-9.699999999999999</v>
+        <v>-17.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O5" s="6">
-        <v>49</v>
-      </c>
-      <c r="P5" s="10">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="O5" s="13">
+        <v>11</v>
+      </c>
+      <c r="P5" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>9</v>
+      </c>
+      <c r="R5" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1444,55 +1381,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="L6" s="4">
-        <v>-23.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O6" s="11">
+        <v>137</v>
+      </c>
+      <c r="O6" s="6">
         <v>25</v>
       </c>
-      <c r="P6" s="12">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
+      <c r="P6" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>17</v>
+      </c>
+      <c r="R6" s="14">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1500,55 +1437,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="L7" s="4">
-        <v>-34.4</v>
+        <v>-11.7</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="O7" s="6">
-        <v>54</v>
-      </c>
-      <c r="P7" s="13">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="P7" s="16">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>14</v>
+      </c>
+      <c r="R7" s="12">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1556,55 +1493,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="L8" s="4">
-        <v>-17.9</v>
+        <v>-25.2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="14">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>76</v>
-      </c>
-      <c r="R8" s="16">
-        <v>99</v>
+        <v>29</v>
+      </c>
+      <c r="P8" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>2</v>
+      </c>
+      <c r="R8" s="11">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1612,55 +1549,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="L9" s="4">
-        <v>-30.2</v>
+        <v>-19.6</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O9" s="6">
-        <v>83</v>
-      </c>
-      <c r="P9" s="9">
-        <v>7</v>
+        <v>136</v>
+      </c>
+      <c r="O9" s="9">
+        <v>49</v>
+      </c>
+      <c r="P9" s="11">
+        <v>30</v>
       </c>
       <c r="Q9" s="17">
-        <v>62</v>
-      </c>
-      <c r="R9" s="18">
-        <v>83</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="11">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1668,55 +1605,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-13.6</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-11.7</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O10" s="6">
-        <v>48</v>
-      </c>
-      <c r="P10" s="19">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>18</v>
-      </c>
-      <c r="R10" s="13">
-        <v>48</v>
+        <v>136</v>
+      </c>
+      <c r="O10" s="9">
+        <v>54</v>
+      </c>
+      <c r="P10" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>20</v>
+      </c>
+      <c r="R10" s="10">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1724,55 +1661,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L11" s="4">
-        <v>-25.2</v>
+        <v>-7.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O11" s="6">
-        <v>82</v>
-      </c>
-      <c r="P11" s="21">
-        <v>55</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>11</v>
+        <v>138</v>
+      </c>
+      <c r="O11" s="9">
+        <v>95</v>
+      </c>
+      <c r="P11" s="10">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>89</v>
       </c>
       <c r="R11" s="14">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1780,54 +1717,54 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L12" s="4">
-        <v>-19.6</v>
+        <v>-21.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O12" s="6">
-        <v>82</v>
-      </c>
-      <c r="P12" s="20">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>47</v>
-      </c>
-      <c r="R12" s="10">
+        <v>139</v>
+      </c>
+      <c r="O12" s="9">
+        <v>96</v>
+      </c>
+      <c r="P12" s="10">
+        <v>57</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>89</v>
+      </c>
+      <c r="R12" s="17">
         <v>36</v>
       </c>
     </row>
@@ -1836,226 +1773,114 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-13.6</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="N13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="22">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>73</v>
-      </c>
-      <c r="R13" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2">
-        <v>27</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-7.2</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O14" s="6">
-        <v>100</v>
-      </c>
-      <c r="P14" s="17">
-        <v>58</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>100</v>
-      </c>
-      <c r="R14" s="22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2">
-        <v>12</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-21.2</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="O15" s="6">
-        <v>100</v>
-      </c>
-      <c r="P15" s="23">
+        <v>139</v>
+      </c>
+      <c r="O13" s="9">
+        <v>76</v>
+      </c>
+      <c r="P13" s="19">
+        <v>47</v>
+      </c>
+      <c r="Q13" s="20">
         <v>66</v>
       </c>
-      <c r="Q15" s="16">
-        <v>100</v>
-      </c>
-      <c r="R15" s="7">
-        <v>43</v>
+      <c r="R13" s="21">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A15">
+  <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C15">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F15">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
+  <conditionalFormatting sqref="I2:I13">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K15">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2074,12 +1899,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2096,22 +1921,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O15">
+  <conditionalFormatting sqref="O2:O13">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P15">
+  <conditionalFormatting sqref="P2:P13">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q15">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="120">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260321--01</t>
-  </si>
-  <si>
-    <t>20260321--02</t>
-  </si>
-  <si>
-    <t>20260321--03</t>
-  </si>
-  <si>
     <t>20260322--01</t>
   </si>
   <si>
@@ -106,13 +97,7 @@
     <t>20260327--01</t>
   </si>
   <si>
-    <t>06:08</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:20</t>
+    <t>20260328--01</t>
   </si>
   <si>
     <t>06:20</t>
@@ -127,33 +112,30 @@
     <t>05:20</t>
   </si>
   <si>
-    <t>05:40</t>
+    <t>05:39</t>
   </si>
   <si>
     <t>05:54</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>03:53</t>
-  </si>
-  <si>
-    <t>05:27</t>
-  </si>
-  <si>
-    <t>01:32</t>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>02:49</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>04:37</t>
+  </si>
+  <si>
+    <t>03:23</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:23</t>
-  </si>
-  <si>
     <t>05:13</t>
   </si>
   <si>
@@ -163,213 +145,174 @@
     <t>02:43</t>
   </si>
   <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>01:09</t>
-  </si>
-  <si>
-    <t>03:29</t>
-  </si>
-  <si>
-    <t>18:09:40</t>
-  </si>
-  <si>
-    <t>19:47:03</t>
-  </si>
-  <si>
-    <t>21:24:48</t>
-  </si>
-  <si>
-    <t>19:06:40</t>
-  </si>
-  <si>
-    <t>20:44:20</t>
-  </si>
-  <si>
-    <t>18:26:13</t>
-  </si>
-  <si>
-    <t>20:03:50</t>
-  </si>
-  <si>
-    <t>19:23:17</t>
-  </si>
-  <si>
-    <t>18:42:41</t>
-  </si>
-  <si>
-    <t>18:02:03</t>
-  </si>
-  <si>
-    <t>19:39:54</t>
-  </si>
-  <si>
-    <t>18:59:06</t>
-  </si>
-  <si>
-    <t>18:11:59</t>
-  </si>
-  <si>
-    <t>19:49:20</t>
-  </si>
-  <si>
-    <t>21:27:33</t>
-  </si>
-  <si>
-    <t>19:08:56</t>
-  </si>
-  <si>
-    <t>20:46:56</t>
-  </si>
-  <si>
-    <t>18:28:29</t>
-  </si>
-  <si>
-    <t>20:06:20</t>
-  </si>
-  <si>
-    <t>19:25:42</t>
-  </si>
-  <si>
-    <t>18:45:03</t>
-  </si>
-  <si>
-    <t>18:04:22</t>
-  </si>
-  <si>
-    <t>19:43:09</t>
-  </si>
-  <si>
-    <t>19:02:00</t>
-  </si>
-  <si>
-    <t>18:15:03</t>
-  </si>
-  <si>
-    <t>19:52:28</t>
-  </si>
-  <si>
-    <t>21:29:43</t>
-  </si>
-  <si>
-    <t>19:12:06</t>
-  </si>
-  <si>
-    <t>20:49:24</t>
-  </si>
-  <si>
-    <t>18:31:40</t>
-  </si>
-  <si>
-    <t>20:09:00</t>
-  </si>
-  <si>
-    <t>19:28:32</t>
-  </si>
-  <si>
-    <t>18:48:00</t>
-  </si>
-  <si>
-    <t>18:07:25</t>
-  </si>
-  <si>
-    <t>19:44:33</t>
-  </si>
-  <si>
-    <t>19:03:56</t>
-  </si>
-  <si>
-    <t>18:18:07</t>
-  </si>
-  <si>
-    <t>19:55:36</t>
-  </si>
-  <si>
-    <t>21:31:53</t>
-  </si>
-  <si>
-    <t>19:15:16</t>
-  </si>
-  <si>
-    <t>20:51:51</t>
-  </si>
-  <si>
-    <t>18:34:51</t>
-  </si>
-  <si>
-    <t>20:11:40</t>
-  </si>
-  <si>
-    <t>19:31:22</t>
-  </si>
-  <si>
-    <t>18:50:57</t>
-  </si>
-  <si>
-    <t>18:10:26</t>
-  </si>
-  <si>
-    <t>19:45:56</t>
-  </si>
-  <si>
-    <t>19:05:53</t>
-  </si>
-  <si>
-    <t>18:20:26</t>
-  </si>
-  <si>
-    <t>19:57:52</t>
-  </si>
-  <si>
-    <t>21:34:38</t>
-  </si>
-  <si>
-    <t>19:17:32</t>
-  </si>
-  <si>
-    <t>20:54:26</t>
-  </si>
-  <si>
-    <t>18:37:06</t>
-  </si>
-  <si>
-    <t>20:14:09</t>
-  </si>
-  <si>
-    <t>19:33:46</t>
-  </si>
-  <si>
-    <t>18:53:18</t>
-  </si>
-  <si>
-    <t>18:12:45</t>
-  </si>
-  <si>
-    <t>19:49:10</t>
-  </si>
-  <si>
-    <t>19:08:45</t>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>03:32</t>
+  </si>
+  <si>
+    <t>19:06:37</t>
+  </si>
+  <si>
+    <t>20:44:17</t>
+  </si>
+  <si>
+    <t>18:26:07</t>
+  </si>
+  <si>
+    <t>20:03:44</t>
+  </si>
+  <si>
+    <t>19:23:07</t>
+  </si>
+  <si>
+    <t>18:42:26</t>
+  </si>
+  <si>
+    <t>18:01:41</t>
+  </si>
+  <si>
+    <t>19:39:32</t>
+  </si>
+  <si>
+    <t>18:58:37</t>
+  </si>
+  <si>
+    <t>18:17:38</t>
+  </si>
+  <si>
+    <t>19:08:53</t>
+  </si>
+  <si>
+    <t>20:46:53</t>
+  </si>
+  <si>
+    <t>18:28:23</t>
+  </si>
+  <si>
+    <t>20:06:14</t>
+  </si>
+  <si>
+    <t>19:25:32</t>
+  </si>
+  <si>
+    <t>18:44:48</t>
+  </si>
+  <si>
+    <t>18:04:00</t>
+  </si>
+  <si>
+    <t>19:42:46</t>
+  </si>
+  <si>
+    <t>19:01:29</t>
+  </si>
+  <si>
+    <t>18:20:19</t>
+  </si>
+  <si>
+    <t>19:12:03</t>
+  </si>
+  <si>
+    <t>20:49:21</t>
+  </si>
+  <si>
+    <t>18:31:34</t>
+  </si>
+  <si>
+    <t>20:08:54</t>
+  </si>
+  <si>
+    <t>19:28:22</t>
+  </si>
+  <si>
+    <t>18:47:45</t>
+  </si>
+  <si>
+    <t>18:07:03</t>
+  </si>
+  <si>
+    <t>19:44:11</t>
+  </si>
+  <si>
+    <t>19:03:27</t>
+  </si>
+  <si>
+    <t>18:22:38</t>
+  </si>
+  <si>
+    <t>19:15:13</t>
+  </si>
+  <si>
+    <t>20:51:48</t>
+  </si>
+  <si>
+    <t>18:34:45</t>
+  </si>
+  <si>
+    <t>20:11:34</t>
+  </si>
+  <si>
+    <t>19:31:11</t>
+  </si>
+  <si>
+    <t>18:50:42</t>
+  </si>
+  <si>
+    <t>18:10:05</t>
+  </si>
+  <si>
+    <t>19:45:35</t>
+  </si>
+  <si>
+    <t>19:05:24</t>
+  </si>
+  <si>
+    <t>18:24:56</t>
+  </si>
+  <si>
+    <t>19:17:29</t>
+  </si>
+  <si>
+    <t>20:54:23</t>
+  </si>
+  <si>
+    <t>18:37:00</t>
+  </si>
+  <si>
+    <t>20:14:03</t>
+  </si>
+  <si>
+    <t>19:33:36</t>
+  </si>
+  <si>
+    <t>18:53:03</t>
+  </si>
+  <si>
+    <t>18:12:24</t>
+  </si>
+  <si>
+    <t>19:48:48</t>
+  </si>
+  <si>
+    <t>19:08:16</t>
+  </si>
+  <si>
+    <t>18:27:36</t>
+  </si>
+  <si>
+    <t>31°</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>18°</t>
   </si>
   <si>
     <t>14°</t>
   </si>
   <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>31°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
     <t>23°</t>
   </si>
   <si>
@@ -382,37 +325,34 @@
     <t>11°</t>
   </si>
   <si>
-    <t>18:17:26</t>
-  </si>
-  <si>
-    <t>19:50:52</t>
-  </si>
-  <si>
-    <t>19:12:19</t>
-  </si>
-  <si>
-    <t>20:45:45</t>
-  </si>
-  <si>
-    <t>18:33:42</t>
-  </si>
-  <si>
-    <t>20:07:07</t>
-  </si>
-  <si>
-    <t>19:28:25</t>
-  </si>
-  <si>
-    <t>18:49:40</t>
-  </si>
-  <si>
-    <t>18:10:53</t>
-  </si>
-  <si>
-    <t>19:44:18</t>
-  </si>
-  <si>
-    <t>19:05:29</t>
+    <t>19:12:16</t>
+  </si>
+  <si>
+    <t>20:45:42</t>
+  </si>
+  <si>
+    <t>18:33:36</t>
+  </si>
+  <si>
+    <t>20:07:01</t>
+  </si>
+  <si>
+    <t>19:28:15</t>
+  </si>
+  <si>
+    <t>18:49:25</t>
+  </si>
+  <si>
+    <t>18:10:32</t>
+  </si>
+  <si>
+    <t>19:43:57</t>
+  </si>
+  <si>
+    <t>19:05:01</t>
+  </si>
+  <si>
+    <t>18:26:04</t>
   </si>
   <si>
     <t>A+B</t>
@@ -467,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,7 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +440,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,67 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -676,6 +622,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1157,52 +1106,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.699999999999999</v>
+        <v>-17.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O2" s="6">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="P2" s="7">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>36</v>
       </c>
       <c r="R2" s="8">
         <v>0</v>
@@ -1213,52 +1162,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.7</v>
+        <v>-30.2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="9">
-        <v>55</v>
-      </c>
-      <c r="P3" s="10">
-        <v>54</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>38</v>
+        <v>117</v>
+      </c>
+      <c r="O3" s="6">
+        <v>44</v>
+      </c>
+      <c r="P3" s="9">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>44</v>
       </c>
       <c r="R3" s="8">
         <v>0</v>
@@ -1269,55 +1218,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="L4" s="4">
-        <v>-34.4</v>
+        <v>-11.7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="O4" s="6">
-        <v>38</v>
-      </c>
-      <c r="P4" s="11">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>9</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="P4" s="10">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>8</v>
+      </c>
+      <c r="R4" s="10">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1325,55 +1274,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-25.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O5" s="6">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-17.9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="13">
-        <v>11</v>
-      </c>
-      <c r="P5" s="8">
-        <v>1</v>
+      <c r="P5" s="11">
+        <v>23</v>
       </c>
       <c r="Q5" s="12">
-        <v>9</v>
-      </c>
-      <c r="R5" s="14">
         <v>5</v>
+      </c>
+      <c r="R5" s="13">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1381,55 +1330,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-19.6</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-30.2</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O6" s="6">
-        <v>25</v>
+      <c r="O6" s="14">
+        <v>100</v>
       </c>
       <c r="P6" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="15">
-        <v>17</v>
-      </c>
-      <c r="R6" s="14">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="R6" s="16">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1437,55 +1386,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L7" s="4">
-        <v>-11.7</v>
+        <v>-13.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O7" s="6">
-        <v>35</v>
-      </c>
-      <c r="P7" s="16">
-        <v>21</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>14</v>
-      </c>
-      <c r="R7" s="12">
-        <v>8</v>
+        <v>116</v>
+      </c>
+      <c r="O7" s="14">
+        <v>36</v>
+      </c>
+      <c r="P7" s="7">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>28</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1493,55 +1442,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="L8" s="4">
-        <v>-25.2</v>
+        <v>-7.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O8" s="6">
-        <v>29</v>
-      </c>
-      <c r="P8" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>2</v>
-      </c>
-      <c r="R8" s="11">
-        <v>29</v>
+        <v>118</v>
+      </c>
+      <c r="O8" s="14">
+        <v>62</v>
+      </c>
+      <c r="P8" s="18">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>31</v>
+      </c>
+      <c r="R8" s="19">
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1549,55 +1498,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="L9" s="4">
-        <v>-19.6</v>
+        <v>-21.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O9" s="9">
-        <v>49</v>
+        <v>119</v>
+      </c>
+      <c r="O9" s="14">
+        <v>60</v>
       </c>
       <c r="P9" s="11">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="17">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>14</v>
+      </c>
+      <c r="R9" s="7">
         <v>35</v>
-      </c>
-      <c r="R9" s="11">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1605,55 +1554,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L10" s="4">
-        <v>-13.6</v>
+        <v>-15.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O10" s="9">
-        <v>54</v>
-      </c>
-      <c r="P10" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>20</v>
-      </c>
-      <c r="R10" s="10">
-        <v>54</v>
+        <v>119</v>
+      </c>
+      <c r="O10" s="14">
+        <v>98</v>
+      </c>
+      <c r="P10" s="20">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>88</v>
+      </c>
+      <c r="R10" s="9">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1661,226 +1610,114 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="L11" s="4">
-        <v>-7.2</v>
+        <v>-9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O11" s="9">
-        <v>95</v>
-      </c>
-      <c r="P11" s="10">
-        <v>54</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>89</v>
-      </c>
-      <c r="R11" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-21.2</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" s="9">
-        <v>96</v>
-      </c>
-      <c r="P12" s="10">
-        <v>57</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>89</v>
-      </c>
-      <c r="R12" s="17">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" s="9">
-        <v>76</v>
-      </c>
-      <c r="P13" s="19">
+        <v>116</v>
+      </c>
+      <c r="O11" s="14">
+        <v>52</v>
+      </c>
+      <c r="P11" s="9">
         <v>47</v>
       </c>
-      <c r="Q13" s="20">
-        <v>66</v>
-      </c>
-      <c r="R13" s="21">
-        <v>76</v>
+      <c r="Q11" s="22">
+        <v>52</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D13">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J13">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K13">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L13">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1899,12 +1736,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M13">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N13">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1921,22 +1758,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O13">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P13">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q13">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260322--01</t>
-  </si>
-  <si>
-    <t>20260322--02</t>
-  </si>
-  <si>
     <t>20260323--01</t>
   </si>
   <si>
@@ -100,12 +94,6 @@
     <t>20260328--01</t>
   </si>
   <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
     <t>06:22</t>
   </si>
   <si>
@@ -130,12 +118,6 @@
     <t>04:37</t>
   </si>
   <si>
-    <t>03:23</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
     <t>05:13</t>
   </si>
   <si>
@@ -151,12 +133,6 @@
     <t>03:32</t>
   </si>
   <si>
-    <t>19:06:37</t>
-  </si>
-  <si>
-    <t>20:44:17</t>
-  </si>
-  <si>
     <t>18:26:07</t>
   </si>
   <si>
@@ -181,12 +157,6 @@
     <t>18:17:38</t>
   </si>
   <si>
-    <t>19:08:53</t>
-  </si>
-  <si>
-    <t>20:46:53</t>
-  </si>
-  <si>
     <t>18:28:23</t>
   </si>
   <si>
@@ -211,12 +181,6 @@
     <t>18:20:19</t>
   </si>
   <si>
-    <t>19:12:03</t>
-  </si>
-  <si>
-    <t>20:49:21</t>
-  </si>
-  <si>
     <t>18:31:34</t>
   </si>
   <si>
@@ -241,12 +205,6 @@
     <t>18:22:38</t>
   </si>
   <si>
-    <t>19:15:13</t>
-  </si>
-  <si>
-    <t>20:51:48</t>
-  </si>
-  <si>
     <t>18:34:45</t>
   </si>
   <si>
@@ -271,12 +229,6 @@
     <t>18:24:56</t>
   </si>
   <si>
-    <t>19:17:29</t>
-  </si>
-  <si>
-    <t>20:54:23</t>
-  </si>
-  <si>
     <t>18:37:00</t>
   </si>
   <si>
@@ -301,36 +253,27 @@
     <t>18:27:36</t>
   </si>
   <si>
-    <t>31°</t>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>12°</t>
+  </si>
+  <si>
+    <t>11°</t>
   </si>
   <si>
     <t>5°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>19:12:16</t>
-  </si>
-  <si>
-    <t>20:45:42</t>
-  </si>
-  <si>
     <t>18:33:36</t>
   </si>
   <si>
@@ -358,16 +301,10 @@
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>1</t>
@@ -407,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +389,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,61 +419,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,15 +535,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1109,49 +1019,49 @@
         <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="L2" s="4">
-        <v>-17.9</v>
+        <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="O2" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P2" s="7">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
       </c>
       <c r="R2" s="8">
         <v>0</v>
@@ -1162,55 +1072,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-25.2</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-30.2</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="6">
-        <v>44</v>
-      </c>
-      <c r="P3" s="9">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>44</v>
+      <c r="O3" s="9">
+        <v>12</v>
+      </c>
+      <c r="P3" s="10">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1218,55 +1128,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="L4" s="4">
-        <v>-11.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O4" s="6">
-        <v>20</v>
-      </c>
-      <c r="P4" s="10">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>8</v>
-      </c>
-      <c r="R4" s="10">
-        <v>8</v>
+        <v>96</v>
+      </c>
+      <c r="O4" s="11">
+        <v>83</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>83</v>
+      </c>
+      <c r="R4" s="13">
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1274,55 +1184,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="L5" s="4">
-        <v>-25.2</v>
+        <v>-13.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O5" s="6">
-        <v>33</v>
-      </c>
-      <c r="P5" s="11">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>5</v>
-      </c>
-      <c r="R5" s="13">
-        <v>16</v>
+        <v>96</v>
+      </c>
+      <c r="O5" s="11">
+        <v>54</v>
+      </c>
+      <c r="P5" s="14">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>6</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1330,55 +1240,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="H6" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="L6" s="4">
-        <v>-19.6</v>
+        <v>-7.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O6" s="14">
-        <v>100</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>81</v>
-      </c>
-      <c r="R6" s="16">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="O6" s="11">
+        <v>56</v>
+      </c>
+      <c r="P6" s="16">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>47</v>
+      </c>
+      <c r="R6" s="17">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1386,55 +1296,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="L7" s="4">
-        <v>-13.5</v>
+        <v>-21.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O7" s="14">
-        <v>36</v>
+        <v>98</v>
+      </c>
+      <c r="O7" s="11">
+        <v>69</v>
       </c>
       <c r="P7" s="7">
-        <v>36</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>28</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>48</v>
+      </c>
+      <c r="R7" s="18">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1442,55 +1352,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="L8" s="4">
-        <v>-7.1</v>
+        <v>-15.3</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="14">
-        <v>62</v>
-      </c>
-      <c r="P8" s="18">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>31</v>
-      </c>
-      <c r="R8" s="19">
-        <v>62</v>
+        <v>98</v>
+      </c>
+      <c r="O8" s="11">
+        <v>95</v>
+      </c>
+      <c r="P8" s="12">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>9</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1498,226 +1408,114 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="L9" s="4">
-        <v>-21.2</v>
+        <v>-9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O9" s="14">
-        <v>60</v>
-      </c>
-      <c r="P9" s="11">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>14</v>
-      </c>
-      <c r="R9" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="2">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="11">
+        <v>80</v>
+      </c>
+      <c r="P9" s="10">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="19">
         <v>73</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O10" s="14">
-        <v>98</v>
-      </c>
-      <c r="P10" s="20">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>88</v>
-      </c>
-      <c r="R10" s="9">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="2">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O11" s="14">
-        <v>52</v>
-      </c>
-      <c r="P11" s="9">
-        <v>47</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>52</v>
-      </c>
-      <c r="R11" s="8">
+      <c r="R9" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A9">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B9">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1736,12 +1534,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1758,22 +1556,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O9">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P9">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260323--01</t>
-  </si>
-  <si>
-    <t>20260323--02</t>
-  </si>
-  <si>
     <t>20260324--01</t>
   </si>
   <si>
@@ -94,16 +88,10 @@
     <t>20260328--01</t>
   </si>
   <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
     <t>05:39</t>
   </si>
   <si>
-    <t>05:54</t>
+    <t>05:53</t>
   </si>
   <si>
     <t>06:05</t>
@@ -118,150 +106,111 @@
     <t>04:37</t>
   </si>
   <si>
-    <t>05:13</t>
-  </si>
-  <si>
-    <t>00:47</t>
-  </si>
-  <si>
     <t>02:43</t>
   </si>
   <si>
-    <t>01:11</t>
+    <t>01:10</t>
   </si>
   <si>
     <t>03:32</t>
   </si>
   <si>
-    <t>18:26:07</t>
-  </si>
-  <si>
-    <t>20:03:44</t>
-  </si>
-  <si>
-    <t>19:23:07</t>
-  </si>
-  <si>
-    <t>18:42:26</t>
-  </si>
-  <si>
-    <t>18:01:41</t>
-  </si>
-  <si>
-    <t>19:39:32</t>
-  </si>
-  <si>
-    <t>18:58:37</t>
-  </si>
-  <si>
-    <t>18:17:38</t>
-  </si>
-  <si>
-    <t>18:28:23</t>
-  </si>
-  <si>
-    <t>20:06:14</t>
-  </si>
-  <si>
-    <t>19:25:32</t>
-  </si>
-  <si>
-    <t>18:44:48</t>
-  </si>
-  <si>
-    <t>18:04:00</t>
-  </si>
-  <si>
-    <t>19:42:46</t>
-  </si>
-  <si>
-    <t>19:01:29</t>
-  </si>
-  <si>
-    <t>18:20:19</t>
-  </si>
-  <si>
-    <t>18:31:34</t>
-  </si>
-  <si>
-    <t>20:08:54</t>
-  </si>
-  <si>
-    <t>19:28:22</t>
-  </si>
-  <si>
-    <t>18:47:45</t>
-  </si>
-  <si>
-    <t>18:07:03</t>
-  </si>
-  <si>
-    <t>19:44:11</t>
-  </si>
-  <si>
-    <t>19:03:27</t>
-  </si>
-  <si>
-    <t>18:22:38</t>
-  </si>
-  <si>
-    <t>18:34:45</t>
-  </si>
-  <si>
-    <t>20:11:34</t>
-  </si>
-  <si>
-    <t>19:31:11</t>
-  </si>
-  <si>
-    <t>18:50:42</t>
-  </si>
-  <si>
-    <t>18:10:05</t>
-  </si>
-  <si>
-    <t>19:45:35</t>
-  </si>
-  <si>
-    <t>19:05:24</t>
-  </si>
-  <si>
-    <t>18:24:56</t>
-  </si>
-  <si>
-    <t>18:37:00</t>
-  </si>
-  <si>
-    <t>20:14:03</t>
-  </si>
-  <si>
-    <t>19:33:36</t>
-  </si>
-  <si>
-    <t>18:53:03</t>
-  </si>
-  <si>
-    <t>18:12:24</t>
-  </si>
-  <si>
-    <t>19:48:48</t>
-  </si>
-  <si>
-    <t>19:08:16</t>
-  </si>
-  <si>
-    <t>18:27:36</t>
+    <t>19:23:06</t>
+  </si>
+  <si>
+    <t>18:42:23</t>
+  </si>
+  <si>
+    <t>18:01:36</t>
+  </si>
+  <si>
+    <t>19:39:27</t>
+  </si>
+  <si>
+    <t>18:58:29</t>
+  </si>
+  <si>
+    <t>18:17:27</t>
+  </si>
+  <si>
+    <t>19:25:31</t>
+  </si>
+  <si>
+    <t>18:44:45</t>
+  </si>
+  <si>
+    <t>18:03:55</t>
+  </si>
+  <si>
+    <t>19:42:41</t>
+  </si>
+  <si>
+    <t>19:01:21</t>
+  </si>
+  <si>
+    <t>18:20:08</t>
+  </si>
+  <si>
+    <t>19:28:20</t>
+  </si>
+  <si>
+    <t>18:47:42</t>
+  </si>
+  <si>
+    <t>18:06:58</t>
+  </si>
+  <si>
+    <t>19:44:05</t>
+  </si>
+  <si>
+    <t>19:03:19</t>
+  </si>
+  <si>
+    <t>18:22:26</t>
+  </si>
+  <si>
+    <t>19:31:10</t>
+  </si>
+  <si>
+    <t>18:50:38</t>
+  </si>
+  <si>
+    <t>18:10:00</t>
+  </si>
+  <si>
+    <t>19:45:30</t>
+  </si>
+  <si>
+    <t>19:05:16</t>
+  </si>
+  <si>
+    <t>18:24:45</t>
+  </si>
+  <si>
+    <t>19:33:34</t>
+  </si>
+  <si>
+    <t>18:53:00</t>
+  </si>
+  <si>
+    <t>18:12:18</t>
+  </si>
+  <si>
+    <t>19:48:43</t>
+  </si>
+  <si>
+    <t>19:08:08</t>
+  </si>
+  <si>
+    <t>18:27:25</t>
+  </si>
+  <si>
+    <t>23°</t>
   </si>
   <si>
     <t>18°</t>
   </si>
   <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
     <t>8°</t>
   </si>
   <si>
@@ -274,28 +223,22 @@
     <t>5°</t>
   </si>
   <si>
-    <t>18:33:36</t>
-  </si>
-  <si>
-    <t>20:07:01</t>
-  </si>
-  <si>
-    <t>19:28:15</t>
-  </si>
-  <si>
-    <t>18:49:25</t>
-  </si>
-  <si>
-    <t>18:10:32</t>
-  </si>
-  <si>
-    <t>19:43:57</t>
-  </si>
-  <si>
-    <t>19:05:01</t>
-  </si>
-  <si>
-    <t>18:26:04</t>
+    <t>19:28:14</t>
+  </si>
+  <si>
+    <t>18:49:22</t>
+  </si>
+  <si>
+    <t>18:10:27</t>
+  </si>
+  <si>
+    <t>19:43:51</t>
+  </si>
+  <si>
+    <t>19:04:53</t>
+  </si>
+  <si>
+    <t>18:25:53</t>
   </si>
   <si>
     <t>A+B</t>
@@ -344,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,6 +302,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -371,43 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,25 +356,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,9 +469,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -938,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1016,55 +950,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="L2" s="4">
-        <v>-11.7</v>
+        <v>-19.6</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="6">
         <v>96</v>
       </c>
-      <c r="O2" s="6">
-        <v>39</v>
-      </c>
       <c r="P2" s="7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="R2" s="9">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1072,55 +1006,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="L3" s="4">
-        <v>-25.2</v>
+        <v>-13.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" s="9">
-        <v>12</v>
-      </c>
-      <c r="P3" s="10">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>77</v>
+      </c>
+      <c r="O3" s="10">
+        <v>34</v>
+      </c>
+      <c r="P3" s="11">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>16</v>
+      </c>
+      <c r="R3" s="7">
         <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1128,55 +1062,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-19.6</v>
+        <v>-7.1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="11">
-        <v>83</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="O4" s="10">
+        <v>46</v>
+      </c>
+      <c r="P4" s="7">
+        <v>1</v>
       </c>
       <c r="Q4" s="12">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="R4" s="13">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1184,55 +1118,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-21.2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-13.5</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="11">
-        <v>54</v>
-      </c>
-      <c r="P5" s="14">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>6</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
+      <c r="O5" s="10">
+        <v>40</v>
+      </c>
+      <c r="P5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>5</v>
+      </c>
+      <c r="R5" s="15">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1240,55 +1174,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-15.2</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-7.1</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O6" s="11">
-        <v>56</v>
+        <v>79</v>
+      </c>
+      <c r="O6" s="10">
+        <v>25</v>
       </c>
       <c r="P6" s="16">
-        <v>26</v>
-      </c>
-      <c r="Q6" s="17">
-        <v>47</v>
-      </c>
-      <c r="R6" s="17">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1296,226 +1230,114 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-9</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-21.2</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O7" s="11">
-        <v>69</v>
-      </c>
-      <c r="P7" s="7">
-        <v>31</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>48</v>
+        <v>77</v>
+      </c>
+      <c r="O7" s="6">
+        <v>97</v>
+      </c>
+      <c r="P7" s="8">
+        <v>89</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>96</v>
       </c>
       <c r="R7" s="18">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="2">
-        <v>14</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O8" s="11">
-        <v>95</v>
-      </c>
-      <c r="P8" s="12">
-        <v>86</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>9</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="11">
-        <v>80</v>
-      </c>
-      <c r="P9" s="10">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="19">
-        <v>73</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A9">
+  <conditionalFormatting sqref="A2:A7">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1534,12 +1356,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
+  <conditionalFormatting sqref="N2:N7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1556,22 +1378,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O9">
+  <conditionalFormatting sqref="O2:O7">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P9">
+  <conditionalFormatting sqref="P2:P7">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260324--01</t>
-  </si>
-  <si>
     <t>20260325--01</t>
   </si>
   <si>
@@ -88,10 +85,7 @@
     <t>20260328--01</t>
   </si>
   <si>
-    <t>05:39</t>
-  </si>
-  <si>
-    <t>05:53</t>
+    <t>05:54</t>
   </si>
   <si>
     <t>06:05</t>
@@ -100,112 +94,94 @@
     <t>02:49</t>
   </si>
   <si>
-    <t>03:55</t>
+    <t>03:54</t>
   </si>
   <si>
     <t>04:37</t>
   </si>
   <si>
-    <t>02:43</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:32</t>
-  </si>
-  <si>
-    <t>19:23:06</t>
-  </si>
-  <si>
-    <t>18:42:23</t>
-  </si>
-  <si>
-    <t>18:01:36</t>
-  </si>
-  <si>
-    <t>19:39:27</t>
-  </si>
-  <si>
-    <t>18:58:29</t>
-  </si>
-  <si>
-    <t>18:17:27</t>
-  </si>
-  <si>
-    <t>19:25:31</t>
-  </si>
-  <si>
-    <t>18:44:45</t>
-  </si>
-  <si>
-    <t>18:03:55</t>
-  </si>
-  <si>
-    <t>19:42:41</t>
-  </si>
-  <si>
-    <t>19:01:21</t>
-  </si>
-  <si>
-    <t>18:20:08</t>
-  </si>
-  <si>
-    <t>19:28:20</t>
-  </si>
-  <si>
-    <t>18:47:42</t>
-  </si>
-  <si>
-    <t>18:06:58</t>
-  </si>
-  <si>
-    <t>19:44:05</t>
-  </si>
-  <si>
-    <t>19:03:19</t>
-  </si>
-  <si>
-    <t>18:22:26</t>
-  </si>
-  <si>
-    <t>19:31:10</t>
-  </si>
-  <si>
-    <t>18:50:38</t>
-  </si>
-  <si>
-    <t>18:10:00</t>
-  </si>
-  <si>
-    <t>19:45:30</t>
-  </si>
-  <si>
-    <t>19:05:16</t>
-  </si>
-  <si>
-    <t>18:24:45</t>
-  </si>
-  <si>
-    <t>19:33:34</t>
-  </si>
-  <si>
-    <t>18:53:00</t>
-  </si>
-  <si>
-    <t>18:12:18</t>
-  </si>
-  <si>
-    <t>19:48:43</t>
-  </si>
-  <si>
-    <t>19:08:08</t>
-  </si>
-  <si>
-    <t>18:27:25</t>
-  </si>
-  <si>
-    <t>23°</t>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>01:11</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>18:42:28</t>
+  </si>
+  <si>
+    <t>18:01:46</t>
+  </si>
+  <si>
+    <t>19:39:37</t>
+  </si>
+  <si>
+    <t>18:58:45</t>
+  </si>
+  <si>
+    <t>18:17:51</t>
+  </si>
+  <si>
+    <t>18:44:50</t>
+  </si>
+  <si>
+    <t>18:04:05</t>
+  </si>
+  <si>
+    <t>19:42:51</t>
+  </si>
+  <si>
+    <t>19:01:38</t>
+  </si>
+  <si>
+    <t>18:20:32</t>
+  </si>
+  <si>
+    <t>18:47:47</t>
+  </si>
+  <si>
+    <t>18:07:08</t>
+  </si>
+  <si>
+    <t>19:44:16</t>
+  </si>
+  <si>
+    <t>19:03:35</t>
+  </si>
+  <si>
+    <t>18:22:51</t>
+  </si>
+  <si>
+    <t>18:50:44</t>
+  </si>
+  <si>
+    <t>18:10:10</t>
+  </si>
+  <si>
+    <t>19:45:40</t>
+  </si>
+  <si>
+    <t>19:05:32</t>
+  </si>
+  <si>
+    <t>18:25:09</t>
+  </si>
+  <si>
+    <t>18:53:05</t>
+  </si>
+  <si>
+    <t>18:12:29</t>
+  </si>
+  <si>
+    <t>19:48:53</t>
+  </si>
+  <si>
+    <t>19:08:24</t>
+  </si>
+  <si>
+    <t>18:27:49</t>
   </si>
   <si>
     <t>18°</t>
@@ -223,22 +199,19 @@
     <t>5°</t>
   </si>
   <si>
-    <t>19:28:14</t>
-  </si>
-  <si>
-    <t>18:49:22</t>
-  </si>
-  <si>
-    <t>18:10:27</t>
-  </si>
-  <si>
-    <t>19:43:51</t>
-  </si>
-  <si>
-    <t>19:04:53</t>
-  </si>
-  <si>
-    <t>18:25:53</t>
+    <t>18:49:28</t>
+  </si>
+  <si>
+    <t>18:10:37</t>
+  </si>
+  <si>
+    <t>19:44:02</t>
+  </si>
+  <si>
+    <t>19:05:09</t>
+  </si>
+  <si>
+    <t>18:26:16</t>
   </si>
   <si>
     <t>A+B</t>
@@ -287,7 +260,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,19 +281,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,49 +323,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -415,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -463,12 +424,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -872,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -950,55 +905,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L2" s="4">
-        <v>-19.6</v>
+        <v>-13.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="O2" s="6">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P2" s="7">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>65</v>
+      </c>
+      <c r="R2" s="9">
         <v>0</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>89</v>
-      </c>
-      <c r="R2" s="9">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1006,55 +961,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L3" s="4">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O3" s="10">
-        <v>34</v>
-      </c>
-      <c r="P3" s="11">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>16</v>
+        <v>69</v>
+      </c>
+      <c r="O3" s="6">
+        <v>99</v>
+      </c>
+      <c r="P3" s="10">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>98</v>
       </c>
       <c r="R3" s="7">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1062,55 +1017,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-21.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
+      </c>
+      <c r="P4" s="12">
         <v>26</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-7.1</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="10">
-        <v>46</v>
-      </c>
-      <c r="P4" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>17</v>
-      </c>
-      <c r="R4" s="13">
-        <v>45</v>
+      <c r="Q4" s="11">
+        <v>100</v>
+      </c>
+      <c r="R4" s="7">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1118,55 +1073,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-21.2</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="10">
-        <v>40</v>
-      </c>
-      <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>5</v>
-      </c>
-      <c r="R5" s="15">
-        <v>40</v>
+        <v>70</v>
+      </c>
+      <c r="O5" s="13">
+        <v>19</v>
+      </c>
+      <c r="P5" s="14">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1174,170 +1129,114 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-9</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-15.2</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="10">
-        <v>25</v>
-      </c>
-      <c r="P6" s="16">
-        <v>25</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="6">
+        <v>96</v>
+      </c>
+      <c r="P6" s="7">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>51</v>
+      </c>
+      <c r="R6" s="16">
         <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" s="6">
-        <v>97</v>
-      </c>
-      <c r="P7" s="8">
-        <v>89</v>
-      </c>
-      <c r="Q7" s="17">
-        <v>96</v>
-      </c>
-      <c r="R7" s="18">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A7">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1356,12 +1255,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1378,22 +1277,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O7">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P7">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260325--01</t>
-  </si>
-  <si>
     <t>20260326--01</t>
   </si>
   <si>
@@ -85,10 +82,7 @@
     <t>20260328--01</t>
   </si>
   <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:05</t>
+    <t>06:04</t>
   </si>
   <si>
     <t>02:49</t>
@@ -100,46 +94,34 @@
     <t>04:37</t>
   </si>
   <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>01:11</t>
+    <t>01:10</t>
   </si>
   <si>
     <t>03:31</t>
   </si>
   <si>
-    <t>18:42:28</t>
-  </si>
-  <si>
     <t>18:01:46</t>
   </si>
   <si>
-    <t>19:39:37</t>
-  </si>
-  <si>
-    <t>18:58:45</t>
-  </si>
-  <si>
-    <t>18:17:51</t>
-  </si>
-  <si>
-    <t>18:44:50</t>
-  </si>
-  <si>
-    <t>18:04:05</t>
-  </si>
-  <si>
-    <t>19:42:51</t>
-  </si>
-  <si>
-    <t>19:01:38</t>
-  </si>
-  <si>
-    <t>18:20:32</t>
-  </si>
-  <si>
-    <t>18:47:47</t>
+    <t>19:39:38</t>
+  </si>
+  <si>
+    <t>18:58:46</t>
+  </si>
+  <si>
+    <t>18:17:52</t>
+  </si>
+  <si>
+    <t>18:04:06</t>
+  </si>
+  <si>
+    <t>19:42:52</t>
+  </si>
+  <si>
+    <t>19:01:39</t>
+  </si>
+  <si>
+    <t>18:20:33</t>
   </si>
   <si>
     <t>18:07:08</t>
@@ -148,43 +130,34 @@
     <t>19:44:16</t>
   </si>
   <si>
-    <t>19:03:35</t>
+    <t>19:03:36</t>
   </si>
   <si>
     <t>18:22:51</t>
   </si>
   <si>
-    <t>18:50:44</t>
-  </si>
-  <si>
     <t>18:10:10</t>
   </si>
   <si>
-    <t>19:45:40</t>
-  </si>
-  <si>
-    <t>19:05:32</t>
-  </si>
-  <si>
-    <t>18:25:09</t>
-  </si>
-  <si>
-    <t>18:53:05</t>
+    <t>19:45:41</t>
+  </si>
+  <si>
+    <t>19:05:33</t>
+  </si>
+  <si>
+    <t>18:25:10</t>
   </si>
   <si>
     <t>18:12:29</t>
   </si>
   <si>
-    <t>19:48:53</t>
-  </si>
-  <si>
-    <t>19:08:24</t>
-  </si>
-  <si>
-    <t>18:27:49</t>
-  </si>
-  <si>
-    <t>18°</t>
+    <t>19:48:54</t>
+  </si>
+  <si>
+    <t>19:08:25</t>
+  </si>
+  <si>
+    <t>18:27:50</t>
   </si>
   <si>
     <t>8°</t>
@@ -199,34 +172,31 @@
     <t>5°</t>
   </si>
   <si>
-    <t>18:49:28</t>
-  </si>
-  <si>
-    <t>18:10:37</t>
+    <t>18:10:38</t>
   </si>
   <si>
     <t>19:44:02</t>
   </si>
   <si>
-    <t>19:05:09</t>
-  </si>
-  <si>
-    <t>18:26:16</t>
+    <t>19:05:10</t>
+  </si>
+  <si>
+    <t>18:26:17</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>A</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -260,7 +230,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,13 +251,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF6AD26A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,43 +287,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -415,15 +367,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -827,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -905,55 +848,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-7.1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="6">
+        <v>100</v>
+      </c>
+      <c r="P2" s="7">
         <v>41</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-13.5</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O2" s="6">
-        <v>65</v>
-      </c>
-      <c r="P2" s="7">
-        <v>54</v>
-      </c>
       <c r="Q2" s="8">
-        <v>65</v>
-      </c>
-      <c r="R2" s="9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="R2" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -961,55 +904,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-21.2</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-7.1</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="O3" s="6">
-        <v>99</v>
-      </c>
-      <c r="P3" s="10">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>98</v>
-      </c>
-      <c r="R3" s="7">
+        <v>100</v>
+      </c>
+      <c r="P3" s="9">
         <v>55</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>100</v>
+      </c>
+      <c r="R3" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1017,55 +960,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L4" s="4">
-        <v>-21.2</v>
+        <v>-15.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
-      </c>
-      <c r="P4" s="12">
-        <v>26</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>100</v>
-      </c>
-      <c r="R4" s="7">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="O4" s="10">
+        <v>10</v>
+      </c>
+      <c r="P4" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1073,170 +1016,114 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="L5" s="4">
-        <v>-15.3</v>
+        <v>-9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O5" s="13">
-        <v>19</v>
-      </c>
-      <c r="P5" s="14">
-        <v>17</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="O5" s="6">
+        <v>81</v>
+      </c>
+      <c r="P5" s="11">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>45</v>
       </c>
       <c r="R5" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="6">
-        <v>96</v>
-      </c>
-      <c r="P6" s="7">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="15">
-        <v>51</v>
-      </c>
-      <c r="R6" s="16">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A5">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B5">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E5">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F5">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I5">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1255,12 +1142,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1277,22 +1164,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O5">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P5">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -70,52 +70,25 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260326--01</t>
-  </si>
-  <si>
-    <t>20260326--02</t>
-  </si>
-  <si>
     <t>20260327--01</t>
   </si>
   <si>
     <t>20260328--01</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>02:49</t>
-  </si>
-  <si>
     <t>03:54</t>
   </si>
   <si>
     <t>04:37</t>
   </si>
   <si>
-    <t>01:10</t>
-  </si>
-  <si>
     <t>03:31</t>
   </si>
   <si>
-    <t>18:01:46</t>
-  </si>
-  <si>
-    <t>19:39:38</t>
-  </si>
-  <si>
     <t>18:58:46</t>
   </si>
   <si>
-    <t>18:17:52</t>
-  </si>
-  <si>
-    <t>18:04:06</t>
-  </si>
-  <si>
-    <t>19:42:52</t>
+    <t>18:17:53</t>
   </si>
   <si>
     <t>19:01:39</t>
@@ -124,22 +97,10 @@
     <t>18:20:33</t>
   </si>
   <si>
-    <t>18:07:08</t>
-  </si>
-  <si>
-    <t>19:44:16</t>
-  </si>
-  <si>
     <t>19:03:36</t>
   </si>
   <si>
-    <t>18:22:51</t>
-  </si>
-  <si>
-    <t>18:10:10</t>
-  </si>
-  <si>
-    <t>19:45:41</t>
+    <t>18:22:52</t>
   </si>
   <si>
     <t>19:05:33</t>
@@ -148,49 +109,28 @@
     <t>18:25:10</t>
   </si>
   <si>
-    <t>18:12:29</t>
-  </si>
-  <si>
-    <t>19:48:54</t>
-  </si>
-  <si>
     <t>19:08:25</t>
   </si>
   <si>
     <t>18:27:50</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>12°</t>
-  </si>
-  <si>
     <t>11°</t>
   </si>
   <si>
     <t>5°</t>
   </si>
   <si>
-    <t>18:10:38</t>
-  </si>
-  <si>
-    <t>19:44:02</t>
-  </si>
-  <si>
     <t>19:05:10</t>
   </si>
   <si>
-    <t>18:26:17</t>
+    <t>18:26:18</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>A+B</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>4</t>
@@ -230,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,31 +185,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,13 +215,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -364,9 +298,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -770,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -848,55 +779,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="L2" s="4">
-        <v>-7.1</v>
+        <v>-15.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="P2" s="7">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -904,226 +835,114 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="L3" s="4">
-        <v>-21.2</v>
+        <v>-9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="6">
+        <v>40</v>
+      </c>
+      <c r="O3" s="9">
         <v>100</v>
       </c>
-      <c r="P3" s="9">
-        <v>55</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>100</v>
-      </c>
-      <c r="R3" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="P3" s="10">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="11">
         <v>50</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="10">
-        <v>10</v>
-      </c>
-      <c r="P4" s="11">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" s="6">
-        <v>81</v>
-      </c>
-      <c r="P5" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>45</v>
-      </c>
-      <c r="R5" s="9">
-        <v>55</v>
+      <c r="R3" s="12">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C5">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E5">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I5">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1142,12 +961,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1164,22 +983,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O5">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -70,70 +70,34 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260327--01</t>
-  </si>
-  <si>
     <t>20260328--01</t>
   </si>
   <si>
-    <t>03:54</t>
-  </si>
-  <si>
     <t>04:37</t>
   </si>
   <si>
-    <t>03:31</t>
-  </si>
-  <si>
-    <t>18:58:46</t>
-  </si>
-  <si>
-    <t>18:17:53</t>
-  </si>
-  <si>
-    <t>19:01:39</t>
+    <t>18:17:52</t>
   </si>
   <si>
     <t>18:20:33</t>
   </si>
   <si>
-    <t>19:03:36</t>
-  </si>
-  <si>
     <t>18:22:52</t>
   </si>
   <si>
-    <t>19:05:33</t>
-  </si>
-  <si>
     <t>18:25:10</t>
   </si>
   <si>
-    <t>19:08:25</t>
-  </si>
-  <si>
     <t>18:27:50</t>
   </si>
   <si>
-    <t>11°</t>
-  </si>
-  <si>
     <t>5°</t>
   </si>
   <si>
-    <t>19:05:10</t>
-  </si>
-  <si>
-    <t>18:26:18</t>
-  </si>
-  <si>
-    <t>A+B</t>
+    <t>18:26:17</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>2</t>
@@ -170,7 +134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,43 +149,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -289,15 +235,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -701,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -779,170 +716,114 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-9</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-15.3</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="O2" s="6">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="9">
+        <v>93</v>
+      </c>
+      <c r="R2" s="9">
         <v>100</v>
-      </c>
-      <c r="P3" s="10">
-        <v>11</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>50</v>
-      </c>
-      <c r="R3" s="12">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -961,12 +842,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -983,22 +864,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>Datum</t>
   </si>
@@ -68,39 +68,6 @@
   </si>
   <si>
     <t>Vysoká</t>
-  </si>
-  <si>
-    <t>20260328--01</t>
-  </si>
-  <si>
-    <t>04:37</t>
-  </si>
-  <si>
-    <t>18:17:52</t>
-  </si>
-  <si>
-    <t>18:20:33</t>
-  </si>
-  <si>
-    <t>18:22:52</t>
-  </si>
-  <si>
-    <t>18:25:10</t>
-  </si>
-  <si>
-    <t>18:27:50</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>18:26:17</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -110,7 +77,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,15 +93,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,30 +104,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -224,18 +160,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -638,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -711,119 +635,63 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4">
-        <v>-9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="6">
-        <v>100</v>
-      </c>
-      <c r="P2" s="7">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>93</v>
-      </c>
-      <c r="R2" s="9">
-        <v>100</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C1:C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D1:D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E1:E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F1:F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G1:G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H1:H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I1:I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J1:J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K1:K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L1:L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -842,12 +710,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M1:M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N1:N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -864,22 +732,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O1:O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P1:P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q1:Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R1:R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Datum</t>
   </si>
@@ -68,6 +68,39 @@
   </si>
   <si>
     <t>Vysoká</t>
+  </si>
+  <si>
+    <t>20260422--01</t>
+  </si>
+  <si>
+    <t>01:48</t>
+  </si>
+  <si>
+    <t>02:34:29</t>
+  </si>
+  <si>
+    <t>02:38:04</t>
+  </si>
+  <si>
+    <t>02:38:58</t>
+  </si>
+  <si>
+    <t>02:39:52</t>
+  </si>
+  <si>
+    <t>02:43:28</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>02:36:55</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -77,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;°&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,8 +126,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -104,6 +144,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +224,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -635,63 +711,119 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-11.7</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="6">
+        <v>61</v>
+      </c>
+      <c r="P2" s="7">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>52</v>
+      </c>
+      <c r="R2" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A2">
+  <conditionalFormatting sqref="A2">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2">
+  <conditionalFormatting sqref="B2">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2">
+  <conditionalFormatting sqref="C2">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D2">
+  <conditionalFormatting sqref="D2">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2">
+  <conditionalFormatting sqref="E2">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H2">
+  <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I2">
+  <conditionalFormatting sqref="I2">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2">
+  <conditionalFormatting sqref="K2">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L2">
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -710,12 +842,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N2">
+  <conditionalFormatting sqref="N2">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -732,22 +864,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O2">
+  <conditionalFormatting sqref="O2">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P2">
+  <conditionalFormatting sqref="P2">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q2">
+  <conditionalFormatting sqref="Q2">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R2">
+  <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -73,34 +73,70 @@
     <t>20260422--01</t>
   </si>
   <si>
-    <t>01:48</t>
-  </si>
-  <si>
-    <t>02:34:29</t>
-  </si>
-  <si>
-    <t>02:38:04</t>
-  </si>
-  <si>
-    <t>02:38:58</t>
-  </si>
-  <si>
-    <t>02:39:52</t>
-  </si>
-  <si>
-    <t>02:43:28</t>
+    <t>20260424--01</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>02:34:33</t>
+  </si>
+  <si>
+    <t>02:46:24</t>
+  </si>
+  <si>
+    <t>02:38:07</t>
+  </si>
+  <si>
+    <t>02:48:51</t>
+  </si>
+  <si>
+    <t>02:39:02</t>
+  </si>
+  <si>
+    <t>02:51:32</t>
+  </si>
+  <si>
+    <t>02:39:56</t>
+  </si>
+  <si>
+    <t>02:54:13</t>
+  </si>
+  <si>
+    <t>02:43:31</t>
+  </si>
+  <si>
+    <t>02:56:41</t>
   </si>
   <si>
     <t>7°</t>
   </si>
   <si>
-    <t>02:36:55</t>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>02:36:59</t>
+  </si>
+  <si>
+    <t>02:49:07</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
+    <t>A+B</t>
+  </si>
+  <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -149,25 +185,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -719,111 +755,167 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L2" s="4">
         <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="6">
-        <v>61</v>
-      </c>
-      <c r="P2" s="7">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>52</v>
-      </c>
-      <c r="R2" s="9">
-        <v>1</v>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-9.5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="8">
+        <v>42</v>
+      </c>
+      <c r="P3" s="9">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:A3">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="D2:D3">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
+  <conditionalFormatting sqref="E2:E3">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:F3">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G2:G3">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2">
+  <conditionalFormatting sqref="H2:H3">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2">
+  <conditionalFormatting sqref="I2:I3">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="J2:J3">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2">
+  <conditionalFormatting sqref="K2:K3">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -842,12 +934,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -864,22 +956,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2">
+  <conditionalFormatting sqref="O2:O3">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
+  <conditionalFormatting sqref="P2:P3">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
+  <conditionalFormatting sqref="Q2:Q3">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2">
+  <conditionalFormatting sqref="R2:R3">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Datum</t>
   </si>
@@ -76,55 +76,85 @@
     <t>20260424--01</t>
   </si>
   <si>
+    <t>20260425--01</t>
+  </si>
+  <si>
     <t>01:49</t>
   </si>
   <si>
     <t>05:22</t>
   </si>
   <si>
+    <t>04:54</t>
+  </si>
+  <si>
     <t>05:06</t>
   </si>
   <si>
+    <t>03:16</t>
+  </si>
+  <si>
     <t>02:34:33</t>
   </si>
   <si>
     <t>02:46:24</t>
   </si>
   <si>
+    <t>02:04:14</t>
+  </si>
+  <si>
     <t>02:38:07</t>
   </si>
   <si>
     <t>02:48:51</t>
   </si>
   <si>
+    <t>02:06:48</t>
+  </si>
+  <si>
     <t>02:39:02</t>
   </si>
   <si>
     <t>02:51:32</t>
   </si>
   <si>
+    <t>02:09:15</t>
+  </si>
+  <si>
     <t>02:39:56</t>
   </si>
   <si>
     <t>02:54:13</t>
   </si>
   <si>
+    <t>02:11:42</t>
+  </si>
+  <si>
     <t>02:43:31</t>
   </si>
   <si>
     <t>02:56:41</t>
   </si>
   <si>
+    <t>02:14:17</t>
+  </si>
+  <si>
     <t>7°</t>
   </si>
   <si>
     <t>11°</t>
   </si>
   <si>
+    <t>17°</t>
+  </si>
+  <si>
     <t>02:36:59</t>
   </si>
   <si>
     <t>02:49:07</t>
+  </si>
+  <si>
+    <t>02:08:26</t>
   </si>
   <si>
     <t>A</t>
@@ -170,7 +200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,7 +233,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -244,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -271,6 +325,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -674,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -755,49 +821,49 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L2" s="4">
         <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" s="7">
         <v>0</v>
@@ -811,111 +877,167 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L3" s="4">
         <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O3" s="8">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="P3" s="9">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>0</v>
+      <c r="R3" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-14.4</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="11">
+        <v>74</v>
+      </c>
+      <c r="P4" s="12">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>2</v>
+      </c>
+      <c r="R4" s="13">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G3">
+  <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3">
+  <conditionalFormatting sqref="I2:I4">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J3">
+  <conditionalFormatting sqref="J2:J4">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K3">
+  <conditionalFormatting sqref="K2:K4">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -934,12 +1056,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M3">
+  <conditionalFormatting sqref="M2:M4">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N3">
+  <conditionalFormatting sqref="N2:N4">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -956,22 +1078,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O3">
+  <conditionalFormatting sqref="O2:O4">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P3">
+  <conditionalFormatting sqref="P2:P4">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q3">
+  <conditionalFormatting sqref="Q2:Q4">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R3">
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Datum</t>
   </si>
@@ -79,64 +79,112 @@
     <t>20260425--01</t>
   </si>
   <si>
-    <t>01:49</t>
-  </si>
-  <si>
-    <t>05:22</t>
+    <t>20260426--01</t>
+  </si>
+  <si>
+    <t>20260426--02</t>
+  </si>
+  <si>
+    <t>01:47</t>
+  </si>
+  <si>
+    <t>05:21</t>
   </si>
   <si>
     <t>04:54</t>
   </si>
   <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>02:34:33</t>
-  </si>
-  <si>
-    <t>02:46:24</t>
-  </si>
-  <si>
-    <t>02:04:14</t>
-  </si>
-  <si>
-    <t>02:38:07</t>
-  </si>
-  <si>
-    <t>02:48:51</t>
-  </si>
-  <si>
-    <t>02:06:48</t>
-  </si>
-  <si>
-    <t>02:39:02</t>
-  </si>
-  <si>
-    <t>02:51:32</t>
-  </si>
-  <si>
-    <t>02:09:15</t>
-  </si>
-  <si>
-    <t>02:39:56</t>
-  </si>
-  <si>
-    <t>02:54:13</t>
-  </si>
-  <si>
-    <t>02:11:42</t>
-  </si>
-  <si>
-    <t>02:43:31</t>
-  </si>
-  <si>
-    <t>02:56:41</t>
-  </si>
-  <si>
-    <t>02:14:17</t>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>01:21</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>02:34:25</t>
+  </si>
+  <si>
+    <t>02:46:04</t>
+  </si>
+  <si>
+    <t>02:03:46</t>
+  </si>
+  <si>
+    <t>01:21:28</t>
+  </si>
+  <si>
+    <t>02:58:04</t>
+  </si>
+  <si>
+    <t>02:38:00</t>
+  </si>
+  <si>
+    <t>02:48:31</t>
+  </si>
+  <si>
+    <t>02:06:20</t>
+  </si>
+  <si>
+    <t>01:24:13</t>
+  </si>
+  <si>
+    <t>03:00:20</t>
+  </si>
+  <si>
+    <t>02:38:53</t>
+  </si>
+  <si>
+    <t>02:51:11</t>
+  </si>
+  <si>
+    <t>02:08:47</t>
+  </si>
+  <si>
+    <t>01:26:19</t>
+  </si>
+  <si>
+    <t>03:03:25</t>
+  </si>
+  <si>
+    <t>02:39:47</t>
+  </si>
+  <si>
+    <t>02:53:52</t>
+  </si>
+  <si>
+    <t>02:11:14</t>
+  </si>
+  <si>
+    <t>01:28:27</t>
+  </si>
+  <si>
+    <t>03:06:31</t>
+  </si>
+  <si>
+    <t>02:43:23</t>
+  </si>
+  <si>
+    <t>02:56:21</t>
+  </si>
+  <si>
+    <t>02:13:49</t>
+  </si>
+  <si>
+    <t>01:31:12</t>
+  </si>
+  <si>
+    <t>03:08:48</t>
   </si>
   <si>
     <t>7°</t>
@@ -148,13 +196,25 @@
     <t>17°</t>
   </si>
   <si>
-    <t>02:36:59</t>
-  </si>
-  <si>
-    <t>02:49:07</t>
-  </si>
-  <si>
-    <t>02:08:26</t>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>02:36:50</t>
+  </si>
+  <si>
+    <t>02:48:48</t>
+  </si>
+  <si>
+    <t>02:07:59</t>
+  </si>
+  <si>
+    <t>01:27:06</t>
+  </si>
+  <si>
+    <t>03:00:22</t>
   </si>
   <si>
     <t>A</t>
@@ -200,7 +260,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,25 +281,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,13 +299,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -334,9 +388,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -821,51 +872,51 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L2" s="4">
         <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="O2" s="6">
+        <v>5</v>
+      </c>
+      <c r="P2" s="7">
         <v>4</v>
       </c>
-      <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>2</v>
-      </c>
-      <c r="R2" s="7">
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -877,52 +928,52 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="L3" s="4">
         <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="8">
-        <v>19</v>
-      </c>
-      <c r="P3" s="9">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="7">
+        <v>70</v>
+      </c>
+      <c r="O3" s="9">
+        <v>74</v>
+      </c>
+      <c r="P3" s="10">
+        <v>74</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="10">
-        <v>13</v>
+      <c r="R3" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -933,111 +984,223 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="L4" s="4">
         <v>-14.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="9">
         <v>50</v>
       </c>
-      <c r="O4" s="11">
-        <v>74</v>
-      </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" s="7">
-        <v>2</v>
-      </c>
-      <c r="R4" s="13">
-        <v>67</v>
+      <c r="B5" s="2">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-18.6</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" s="9">
+        <v>86</v>
+      </c>
+      <c r="P5" s="12">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="4">
+        <v>-7.3</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="9">
+        <v>86</v>
+      </c>
+      <c r="P6" s="12">
+        <v>86</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A4">
+  <conditionalFormatting sqref="A2:A6">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1056,12 +1219,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1078,22 +1241,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="P2:P6">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
   <si>
     <t>Datum</t>
   </si>
@@ -85,6 +85,12 @@
     <t>20260426--02</t>
   </si>
   <si>
+    <t>20260427--01</t>
+  </si>
+  <si>
+    <t>20260427--02</t>
+  </si>
+  <si>
     <t>01:47</t>
   </si>
   <si>
@@ -94,97 +100,136 @@
     <t>04:54</t>
   </si>
   <si>
-    <t>04:14</t>
+    <t>04:15</t>
   </si>
   <si>
     <t>06:11</t>
   </si>
   <si>
-    <t>05:04</t>
-  </si>
-  <si>
     <t>03:15</t>
   </si>
   <si>
-    <t>01:21</t>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>01:22</t>
   </si>
   <si>
     <t>06:09</t>
   </si>
   <si>
-    <t>02:34:25</t>
-  </si>
-  <si>
-    <t>02:46:04</t>
-  </si>
-  <si>
-    <t>02:03:46</t>
-  </si>
-  <si>
-    <t>01:21:28</t>
-  </si>
-  <si>
-    <t>02:58:04</t>
-  </si>
-  <si>
-    <t>02:38:00</t>
-  </si>
-  <si>
-    <t>02:48:31</t>
-  </si>
-  <si>
-    <t>02:06:20</t>
-  </si>
-  <si>
-    <t>01:24:13</t>
-  </si>
-  <si>
-    <t>03:00:20</t>
-  </si>
-  <si>
-    <t>02:38:53</t>
-  </si>
-  <si>
-    <t>02:51:11</t>
-  </si>
-  <si>
-    <t>02:08:47</t>
-  </si>
-  <si>
-    <t>01:26:19</t>
-  </si>
-  <si>
-    <t>03:03:25</t>
-  </si>
-  <si>
-    <t>02:39:47</t>
-  </si>
-  <si>
-    <t>02:53:52</t>
-  </si>
-  <si>
-    <t>02:11:14</t>
-  </si>
-  <si>
-    <t>01:28:27</t>
-  </si>
-  <si>
-    <t>03:06:31</t>
-  </si>
-  <si>
-    <t>02:43:23</t>
-  </si>
-  <si>
-    <t>02:56:21</t>
-  </si>
-  <si>
-    <t>02:13:49</t>
-  </si>
-  <si>
-    <t>01:31:12</t>
-  </si>
-  <si>
-    <t>03:08:48</t>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>02:34:27</t>
+  </si>
+  <si>
+    <t>02:46:11</t>
+  </si>
+  <si>
+    <t>02:03:56</t>
+  </si>
+  <si>
+    <t>01:21:42</t>
+  </si>
+  <si>
+    <t>02:58:18</t>
+  </si>
+  <si>
+    <t>00:39:28</t>
+  </si>
+  <si>
+    <t>02:15:51</t>
+  </si>
+  <si>
+    <t>02:38:02</t>
+  </si>
+  <si>
+    <t>02:48:38</t>
+  </si>
+  <si>
+    <t>02:06:30</t>
+  </si>
+  <si>
+    <t>01:24:26</t>
+  </si>
+  <si>
+    <t>03:00:34</t>
+  </si>
+  <si>
+    <t>00:42:30</t>
+  </si>
+  <si>
+    <t>02:18:08</t>
+  </si>
+  <si>
+    <t>02:38:55</t>
+  </si>
+  <si>
+    <t>02:51:18</t>
+  </si>
+  <si>
+    <t>02:08:57</t>
+  </si>
+  <si>
+    <t>01:26:33</t>
+  </si>
+  <si>
+    <t>03:03:39</t>
+  </si>
+  <si>
+    <t>00:44:08</t>
+  </si>
+  <si>
+    <t>02:21:10</t>
+  </si>
+  <si>
+    <t>02:39:49</t>
+  </si>
+  <si>
+    <t>02:53:59</t>
+  </si>
+  <si>
+    <t>02:11:24</t>
+  </si>
+  <si>
+    <t>01:28:41</t>
+  </si>
+  <si>
+    <t>03:06:45</t>
+  </si>
+  <si>
+    <t>00:45:45</t>
+  </si>
+  <si>
+    <t>02:24:12</t>
+  </si>
+  <si>
+    <t>02:43:25</t>
+  </si>
+  <si>
+    <t>02:56:28</t>
+  </si>
+  <si>
+    <t>02:13:59</t>
+  </si>
+  <si>
+    <t>01:31:26</t>
+  </si>
+  <si>
+    <t>03:09:02</t>
+  </si>
+  <si>
+    <t>00:48:49</t>
+  </si>
+  <si>
+    <t>02:26:30</t>
   </si>
   <si>
     <t>7°</t>
@@ -196,31 +241,46 @@
     <t>17°</t>
   </si>
   <si>
-    <t>14°</t>
+    <t>15°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>02:36:50</t>
-  </si>
-  <si>
-    <t>02:48:48</t>
-  </si>
-  <si>
-    <t>02:07:59</t>
-  </si>
-  <si>
-    <t>01:27:06</t>
-  </si>
-  <si>
-    <t>03:00:22</t>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>02:36:53</t>
+  </si>
+  <si>
+    <t>02:48:54</t>
+  </si>
+  <si>
+    <t>02:08:09</t>
+  </si>
+  <si>
+    <t>01:27:19</t>
+  </si>
+  <si>
+    <t>03:00:36</t>
+  </si>
+  <si>
+    <t>00:46:26</t>
+  </si>
+  <si>
+    <t>02:19:42</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
     <t>A+B</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>4</t>
@@ -260,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,13 +335,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,13 +365,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -352,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -388,6 +478,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -791,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -872,46 +977,46 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L2" s="4">
         <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="O2" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P2" s="7">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="8">
         <v>0</v>
@@ -928,52 +1033,52 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="L3" s="4">
         <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="O3" s="9">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="P3" s="10">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
+      <c r="R3" s="11">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -984,46 +1089,46 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="L4" s="4">
         <v>-14.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="O4" s="9">
-        <v>50</v>
-      </c>
-      <c r="P4" s="11">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="P4" s="12">
+        <v>38</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
@@ -1040,52 +1145,52 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="L5" s="4">
         <v>-18.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="O5" s="9">
-        <v>86</v>
-      </c>
-      <c r="P5" s="12">
-        <v>84</v>
+        <v>50</v>
+      </c>
+      <c r="P5" s="13">
+        <v>50</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1096,111 +1201,223 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="L6" s="4">
         <v>-7.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="O6" s="9">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="P6" s="12">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
       <c r="R6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-21.8</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" s="9">
+        <v>92</v>
+      </c>
+      <c r="P7" s="14">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="8">
         <v>0</v>
+      </c>
+      <c r="R7" s="15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-12.4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="9">
+        <v>93</v>
+      </c>
+      <c r="P8" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>24</v>
+      </c>
+      <c r="R8" s="17">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
+  <conditionalFormatting sqref="A2:A8">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B8">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D8">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E8">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F8">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H8">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I8">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J8">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K8">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1219,12 +1436,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M8">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
+  <conditionalFormatting sqref="N2:N8">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1241,22 +1458,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O6">
+  <conditionalFormatting sqref="O2:O8">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="P2:P8">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q8">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R8">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
   <si>
     <t>Datum</t>
   </si>
@@ -91,7 +91,13 @@
     <t>20260427--02</t>
   </si>
   <si>
-    <t>01:47</t>
+    <t>20260428--01</t>
+  </si>
+  <si>
+    <t>20260428--02</t>
+  </si>
+  <si>
+    <t>01:48</t>
   </si>
   <si>
     <t>05:21</t>
@@ -100,22 +106,31 @@
     <t>04:54</t>
   </si>
   <si>
-    <t>04:15</t>
+    <t>04:14</t>
   </si>
   <si>
     <t>06:11</t>
   </si>
   <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
     <t>03:15</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>01:22</t>
+    <t>01:20</t>
   </si>
   <si>
     <t>06:09</t>
@@ -124,112 +139,142 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>04:30</t>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>02:47</t>
   </si>
   <si>
     <t>02:34:27</t>
   </si>
   <si>
-    <t>02:46:11</t>
-  </si>
-  <si>
-    <t>02:03:56</t>
-  </si>
-  <si>
-    <t>01:21:42</t>
-  </si>
-  <si>
-    <t>02:58:18</t>
-  </si>
-  <si>
-    <t>00:39:28</t>
-  </si>
-  <si>
-    <t>02:15:51</t>
-  </si>
-  <si>
-    <t>02:38:02</t>
-  </si>
-  <si>
-    <t>02:48:38</t>
-  </si>
-  <si>
-    <t>02:06:30</t>
-  </si>
-  <si>
-    <t>01:24:26</t>
-  </si>
-  <si>
-    <t>03:00:34</t>
-  </si>
-  <si>
-    <t>00:42:30</t>
-  </si>
-  <si>
-    <t>02:18:08</t>
+    <t>02:46:07</t>
+  </si>
+  <si>
+    <t>02:03:50</t>
+  </si>
+  <si>
+    <t>01:21:33</t>
+  </si>
+  <si>
+    <t>02:58:09</t>
+  </si>
+  <si>
+    <t>00:39:15</t>
+  </si>
+  <si>
+    <t>02:15:38</t>
+  </si>
+  <si>
+    <t>23:56:58</t>
+  </si>
+  <si>
+    <t>01:33:05</t>
+  </si>
+  <si>
+    <t>02:38:01</t>
+  </si>
+  <si>
+    <t>02:48:35</t>
+  </si>
+  <si>
+    <t>02:06:24</t>
+  </si>
+  <si>
+    <t>01:24:17</t>
+  </si>
+  <si>
+    <t>03:00:25</t>
+  </si>
+  <si>
+    <t>00:42:18</t>
+  </si>
+  <si>
+    <t>02:17:56</t>
+  </si>
+  <si>
+    <t>00:01:23</t>
+  </si>
+  <si>
+    <t>01:35:25</t>
   </si>
   <si>
     <t>02:38:55</t>
   </si>
   <si>
-    <t>02:51:18</t>
-  </si>
-  <si>
-    <t>02:08:57</t>
-  </si>
-  <si>
-    <t>01:26:33</t>
-  </si>
-  <si>
-    <t>03:03:39</t>
-  </si>
-  <si>
-    <t>00:44:08</t>
-  </si>
-  <si>
-    <t>02:21:10</t>
+    <t>02:51:15</t>
+  </si>
+  <si>
+    <t>02:08:51</t>
+  </si>
+  <si>
+    <t>01:26:24</t>
+  </si>
+  <si>
+    <t>03:03:30</t>
+  </si>
+  <si>
+    <t>00:43:55</t>
+  </si>
+  <si>
+    <t>02:20:57</t>
+  </si>
+  <si>
+    <t>01:38:20</t>
   </si>
   <si>
     <t>02:39:49</t>
   </si>
   <si>
-    <t>02:53:59</t>
-  </si>
-  <si>
-    <t>02:11:24</t>
-  </si>
-  <si>
-    <t>01:28:41</t>
-  </si>
-  <si>
-    <t>03:06:45</t>
-  </si>
-  <si>
-    <t>00:45:45</t>
-  </si>
-  <si>
-    <t>02:24:12</t>
+    <t>02:53:56</t>
+  </si>
+  <si>
+    <t>02:11:18</t>
+  </si>
+  <si>
+    <t>01:28:31</t>
+  </si>
+  <si>
+    <t>03:06:36</t>
+  </si>
+  <si>
+    <t>00:45:32</t>
+  </si>
+  <si>
+    <t>02:23:59</t>
+  </si>
+  <si>
+    <t>00:01:58</t>
+  </si>
+  <si>
+    <t>01:41:17</t>
   </si>
   <si>
     <t>02:43:25</t>
   </si>
   <si>
-    <t>02:56:28</t>
-  </si>
-  <si>
-    <t>02:13:59</t>
-  </si>
-  <si>
-    <t>01:31:26</t>
-  </si>
-  <si>
-    <t>03:09:02</t>
-  </si>
-  <si>
-    <t>00:48:49</t>
-  </si>
-  <si>
-    <t>02:26:30</t>
+    <t>02:56:24</t>
+  </si>
+  <si>
+    <t>02:13:53</t>
+  </si>
+  <si>
+    <t>01:31:17</t>
+  </si>
+  <si>
+    <t>03:08:53</t>
+  </si>
+  <si>
+    <t>00:48:36</t>
+  </si>
+  <si>
+    <t>02:26:17</t>
+  </si>
+  <si>
+    <t>00:05:49</t>
+  </si>
+  <si>
+    <t>01:43:38</t>
   </si>
   <si>
     <t>7°</t>
@@ -241,7 +286,7 @@
     <t>17°</t>
   </si>
   <si>
-    <t>15°</t>
+    <t>14°</t>
   </si>
   <si>
     <t>10°</t>
@@ -253,25 +298,37 @@
     <t>21°</t>
   </si>
   <si>
-    <t>02:36:53</t>
-  </si>
-  <si>
-    <t>02:48:54</t>
-  </si>
-  <si>
-    <t>02:08:09</t>
-  </si>
-  <si>
-    <t>01:27:19</t>
-  </si>
-  <si>
-    <t>03:00:36</t>
-  </si>
-  <si>
-    <t>00:46:26</t>
-  </si>
-  <si>
-    <t>02:19:42</t>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>02:36:52</t>
+  </si>
+  <si>
+    <t>02:48:51</t>
+  </si>
+  <si>
+    <t>02:08:03</t>
+  </si>
+  <si>
+    <t>01:27:11</t>
+  </si>
+  <si>
+    <t>03:00:27</t>
+  </si>
+  <si>
+    <t>00:46:14</t>
+  </si>
+  <si>
+    <t>02:19:30</t>
+  </si>
+  <si>
+    <t>00:05:14</t>
+  </si>
+  <si>
+    <t>01:38:30</t>
   </si>
   <si>
     <t>A</t>
@@ -320,7 +377,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,13 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,13 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,25 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -493,6 +568,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -896,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -977,52 +1061,52 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L2" s="4">
         <v>-11.7</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="O2" s="6">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P2" s="7">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="R2" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1033,52 +1117,52 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L3" s="4">
         <v>-9.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="9">
-        <v>85</v>
-      </c>
-      <c r="P3" s="10">
-        <v>76</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>109</v>
+      </c>
+      <c r="O3" s="10">
+        <v>80</v>
+      </c>
+      <c r="P3" s="11">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="11">
-        <v>43</v>
+      <c r="R3" s="12">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1089,52 +1173,52 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="L4" s="4">
         <v>-14.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O4" s="9">
-        <v>51</v>
-      </c>
-      <c r="P4" s="12">
-        <v>38</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="O4" s="10">
+        <v>53</v>
+      </c>
+      <c r="P4" s="13">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1</v>
+      </c>
+      <c r="R4" s="14">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1145,52 +1229,52 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="L5" s="4">
         <v>-18.6</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O5" s="9">
-        <v>50</v>
-      </c>
-      <c r="P5" s="13">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="8">
+        <v>109</v>
+      </c>
+      <c r="O5" s="15">
+        <v>10</v>
+      </c>
+      <c r="P5" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>1</v>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1201,52 +1285,52 @@
         <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="L6" s="4">
         <v>-7.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" s="9">
-        <v>41</v>
-      </c>
-      <c r="P6" s="12">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="8">
+        <v>109</v>
+      </c>
+      <c r="O6" s="10">
+        <v>49</v>
+      </c>
+      <c r="P6" s="16">
+        <v>49</v>
+      </c>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>1</v>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1257,52 +1341,52 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="L7" s="4">
         <v>-21.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O7" s="9">
-        <v>92</v>
-      </c>
-      <c r="P7" s="14">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="8">
+        <v>108</v>
+      </c>
+      <c r="O7" s="6">
+        <v>35</v>
+      </c>
+      <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="15">
-        <v>71</v>
+      <c r="Q7" s="9">
+        <v>3</v>
+      </c>
+      <c r="R7" s="17">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1313,111 +1397,223 @@
         <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L8" s="4">
         <v>-12.4</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="9">
-        <v>93</v>
-      </c>
-      <c r="P8" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>24</v>
-      </c>
-      <c r="R8" s="17">
-        <v>92</v>
+        <v>109</v>
+      </c>
+      <c r="O8" s="6">
+        <v>47</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>7</v>
+      </c>
+      <c r="R8" s="13">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-24</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O9" s="10">
+        <v>100</v>
+      </c>
+      <c r="P9" s="17">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>63</v>
+      </c>
+      <c r="R9" s="19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L10" s="4">
+        <v>-16.8</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O10" s="10">
+        <v>100</v>
+      </c>
+      <c r="P10" s="12">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>70</v>
+      </c>
+      <c r="R10" s="19">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A8">
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
+  <conditionalFormatting sqref="B2:B10">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E8">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F8">
+  <conditionalFormatting sqref="F2:F10">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G10">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H10">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
+  <conditionalFormatting sqref="I2:I10">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1436,12 +1632,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M8">
+  <conditionalFormatting sqref="M2:M10">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
+  <conditionalFormatting sqref="N2:N10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1458,22 +1654,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O8">
+  <conditionalFormatting sqref="O2:O10">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P8">
+  <conditionalFormatting sqref="P2:P10">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q8">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R10">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260422--01</t>
-  </si>
-  <si>
     <t>20260424--01</t>
   </si>
   <si>
@@ -97,7 +94,10 @@
     <t>20260428--02</t>
   </si>
   <si>
-    <t>01:48</t>
+    <t>20260429--01</t>
+  </si>
+  <si>
+    <t>20260429--02</t>
   </si>
   <si>
     <t>05:21</t>
@@ -106,178 +106,199 @@
     <t>04:54</t>
   </si>
   <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>03:14</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>05:52</t>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>05:37</t>
+  </si>
+  <si>
+    <t>06:17</t>
   </si>
   <si>
     <t>05:05</t>
   </si>
   <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>06:09</t>
+    <t>03:16</t>
+  </si>
+  <si>
+    <t>01:22</t>
+  </si>
+  <si>
+    <t>06:10</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:29</t>
-  </si>
-  <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>02:34:27</t>
-  </si>
-  <si>
-    <t>02:46:07</t>
-  </si>
-  <si>
-    <t>02:03:50</t>
-  </si>
-  <si>
-    <t>01:21:33</t>
-  </si>
-  <si>
-    <t>02:58:09</t>
-  </si>
-  <si>
-    <t>00:39:15</t>
-  </si>
-  <si>
-    <t>02:15:38</t>
-  </si>
-  <si>
-    <t>23:56:58</t>
-  </si>
-  <si>
-    <t>01:33:05</t>
-  </si>
-  <si>
-    <t>02:38:01</t>
-  </si>
-  <si>
-    <t>02:48:35</t>
-  </si>
-  <si>
-    <t>02:06:24</t>
-  </si>
-  <si>
-    <t>01:24:17</t>
-  </si>
-  <si>
-    <t>03:00:25</t>
-  </si>
-  <si>
-    <t>00:42:18</t>
-  </si>
-  <si>
-    <t>02:17:56</t>
-  </si>
-  <si>
-    <t>00:01:23</t>
-  </si>
-  <si>
-    <t>01:35:25</t>
-  </si>
-  <si>
-    <t>02:38:55</t>
-  </si>
-  <si>
-    <t>02:51:15</t>
-  </si>
-  <si>
-    <t>02:08:51</t>
-  </si>
-  <si>
-    <t>01:26:24</t>
-  </si>
-  <si>
-    <t>03:03:30</t>
-  </si>
-  <si>
-    <t>00:43:55</t>
-  </si>
-  <si>
-    <t>02:20:57</t>
-  </si>
-  <si>
-    <t>01:38:20</t>
-  </si>
-  <si>
-    <t>02:39:49</t>
-  </si>
-  <si>
-    <t>02:53:56</t>
-  </si>
-  <si>
-    <t>02:11:18</t>
-  </si>
-  <si>
-    <t>01:28:31</t>
-  </si>
-  <si>
-    <t>03:06:36</t>
-  </si>
-  <si>
-    <t>00:45:32</t>
-  </si>
-  <si>
-    <t>02:23:59</t>
-  </si>
-  <si>
-    <t>00:01:58</t>
-  </si>
-  <si>
-    <t>01:41:17</t>
-  </si>
-  <si>
-    <t>02:43:25</t>
-  </si>
-  <si>
-    <t>02:56:24</t>
-  </si>
-  <si>
-    <t>02:13:53</t>
-  </si>
-  <si>
-    <t>01:31:17</t>
-  </si>
-  <si>
-    <t>03:08:53</t>
-  </si>
-  <si>
-    <t>00:48:36</t>
-  </si>
-  <si>
-    <t>02:26:17</t>
-  </si>
-  <si>
-    <t>00:05:49</t>
-  </si>
-  <si>
-    <t>01:43:38</t>
-  </si>
-  <si>
-    <t>7°</t>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>02:48</t>
+  </si>
+  <si>
+    <t>01:03</t>
+  </si>
+  <si>
+    <t>02:46:11</t>
+  </si>
+  <si>
+    <t>02:03:57</t>
+  </si>
+  <si>
+    <t>01:21:44</t>
+  </si>
+  <si>
+    <t>02:58:20</t>
+  </si>
+  <si>
+    <t>00:39:32</t>
+  </si>
+  <si>
+    <t>02:15:55</t>
+  </si>
+  <si>
+    <t>23:57:21</t>
+  </si>
+  <si>
+    <t>01:33:28</t>
+  </si>
+  <si>
+    <t>00:51:01</t>
+  </si>
+  <si>
+    <t>02:28:03</t>
+  </si>
+  <si>
+    <t>02:48:38</t>
+  </si>
+  <si>
+    <t>02:06:31</t>
+  </si>
+  <si>
+    <t>01:24:28</t>
+  </si>
+  <si>
+    <t>03:00:36</t>
+  </si>
+  <si>
+    <t>00:42:34</t>
+  </si>
+  <si>
+    <t>02:18:12</t>
+  </si>
+  <si>
+    <t>00:01:46</t>
+  </si>
+  <si>
+    <t>01:35:48</t>
+  </si>
+  <si>
+    <t>00:53:24</t>
+  </si>
+  <si>
+    <t>02:30:18</t>
+  </si>
+  <si>
+    <t>02:51:18</t>
+  </si>
+  <si>
+    <t>02:08:57</t>
+  </si>
+  <si>
+    <t>01:26:35</t>
+  </si>
+  <si>
+    <t>03:03:42</t>
+  </si>
+  <si>
+    <t>00:44:12</t>
+  </si>
+  <si>
+    <t>02:21:14</t>
+  </si>
+  <si>
+    <t>01:38:44</t>
+  </si>
+  <si>
+    <t>00:56:13</t>
+  </si>
+  <si>
+    <t>02:33:26</t>
+  </si>
+  <si>
+    <t>02:53:59</t>
+  </si>
+  <si>
+    <t>02:11:25</t>
+  </si>
+  <si>
+    <t>01:28:43</t>
+  </si>
+  <si>
+    <t>03:06:48</t>
+  </si>
+  <si>
+    <t>00:45:49</t>
+  </si>
+  <si>
+    <t>02:24:16</t>
+  </si>
+  <si>
+    <t>00:02:24</t>
+  </si>
+  <si>
+    <t>01:41:41</t>
+  </si>
+  <si>
+    <t>00:59:01</t>
+  </si>
+  <si>
+    <t>02:36:35</t>
+  </si>
+  <si>
+    <t>02:56:28</t>
+  </si>
+  <si>
+    <t>02:14:00</t>
+  </si>
+  <si>
+    <t>01:31:28</t>
+  </si>
+  <si>
+    <t>03:09:05</t>
+  </si>
+  <si>
+    <t>00:48:53</t>
+  </si>
+  <si>
+    <t>02:26:35</t>
+  </si>
+  <si>
+    <t>00:06:13</t>
+  </si>
+  <si>
+    <t>01:44:02</t>
+  </si>
+  <si>
+    <t>01:01:26</t>
+  </si>
+  <si>
+    <t>02:38:50</t>
   </si>
   <si>
     <t>11°</t>
@@ -286,7 +307,7 @@
     <t>17°</t>
   </si>
   <si>
-    <t>14°</t>
+    <t>15°</t>
   </si>
   <si>
     <t>10°</t>
@@ -301,37 +322,40 @@
     <t>2°</t>
   </si>
   <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>02:36:52</t>
-  </si>
-  <si>
-    <t>02:48:51</t>
-  </si>
-  <si>
-    <t>02:08:03</t>
-  </si>
-  <si>
-    <t>01:27:11</t>
-  </si>
-  <si>
-    <t>03:00:27</t>
-  </si>
-  <si>
-    <t>00:46:14</t>
-  </si>
-  <si>
-    <t>02:19:30</t>
-  </si>
-  <si>
-    <t>00:05:14</t>
-  </si>
-  <si>
-    <t>01:38:30</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>02:48:54</t>
+  </si>
+  <si>
+    <t>02:08:09</t>
+  </si>
+  <si>
+    <t>01:27:21</t>
+  </si>
+  <si>
+    <t>03:00:38</t>
+  </si>
+  <si>
+    <t>00:46:30</t>
+  </si>
+  <si>
+    <t>02:19:46</t>
+  </si>
+  <si>
+    <t>00:05:36</t>
+  </si>
+  <si>
+    <t>01:38:53</t>
+  </si>
+  <si>
+    <t>00:57:58</t>
+  </si>
+  <si>
+    <t>02:31:14</t>
   </si>
   <si>
     <t>A+B</t>
@@ -340,10 +364,10 @@
     <t>B</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -377,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +458,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,15 +574,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -980,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1058,55 +1055,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L2" s="4">
-        <v>-11.7</v>
+        <v>-9.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="O2" s="6">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R2" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1114,55 +1111,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L3" s="4">
-        <v>-9.5</v>
+        <v>-14.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O3" s="10">
-        <v>80</v>
-      </c>
-      <c r="P3" s="11">
-        <v>75</v>
-      </c>
-      <c r="Q3" s="7">
+        <v>116</v>
+      </c>
+      <c r="O3" s="6">
+        <v>65</v>
+      </c>
+      <c r="P3" s="10">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="12">
-        <v>25</v>
+      <c r="R3" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1170,55 +1167,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-18.6</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="6">
         <v>80</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-14.4</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O4" s="10">
-        <v>53</v>
-      </c>
-      <c r="P4" s="13">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="7">
+      <c r="P4" s="11">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
         <v>1</v>
-      </c>
-      <c r="R4" s="14">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1226,55 +1223,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L5" s="4">
-        <v>-18.6</v>
+        <v>-7.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" s="15">
-        <v>10</v>
-      </c>
-      <c r="P5" s="8">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="7">
+        <v>116</v>
+      </c>
+      <c r="O5" s="6">
+        <v>76</v>
+      </c>
+      <c r="P5" s="12">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="8">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1282,55 +1279,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="L6" s="4">
-        <v>-7.3</v>
+        <v>-21.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O6" s="10">
-        <v>49</v>
-      </c>
-      <c r="P6" s="16">
-        <v>49</v>
-      </c>
-      <c r="Q6" s="7">
+        <v>117</v>
+      </c>
+      <c r="O6" s="6">
+        <v>70</v>
+      </c>
+      <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>0</v>
+      <c r="Q6" s="13">
+        <v>57</v>
+      </c>
+      <c r="R6" s="14">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1338,55 +1335,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="4">
+        <v>-12.4</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="6">
         <v>74</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-21.8</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7" s="6">
-        <v>35</v>
-      </c>
-      <c r="P7" s="7">
+      <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="Q7" s="9">
-        <v>3</v>
-      </c>
-      <c r="R7" s="17">
-        <v>22</v>
+      <c r="Q7" s="13">
+        <v>55</v>
+      </c>
+      <c r="R7" s="10">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1394,55 +1391,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L8" s="4">
-        <v>-12.4</v>
+        <v>-23.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="O8" s="6">
-        <v>47</v>
-      </c>
-      <c r="P8" s="7">
+        <v>98</v>
+      </c>
+      <c r="P8" s="8">
         <v>0</v>
       </c>
-      <c r="Q8" s="9">
-        <v>7</v>
-      </c>
-      <c r="R8" s="13">
-        <v>29</v>
+      <c r="Q8" s="15">
+        <v>96</v>
+      </c>
+      <c r="R8" s="14">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1450,55 +1447,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L9" s="4">
+        <v>-16.8</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O9" s="6">
+        <v>98</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="15">
         <v>94</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-24</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O9" s="10">
-        <v>100</v>
-      </c>
-      <c r="P9" s="17">
-        <v>19</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>63</v>
-      </c>
-      <c r="R9" s="19">
-        <v>100</v>
+      <c r="R9" s="10">
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1506,114 +1503,170 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L10" s="4">
-        <v>-16.8</v>
+        <v>-20.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O10" s="10">
-        <v>100</v>
-      </c>
-      <c r="P10" s="12">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="20">
-        <v>70</v>
-      </c>
-      <c r="R10" s="19">
-        <v>100</v>
+        <v>116</v>
+      </c>
+      <c r="O10" s="6">
+        <v>92</v>
+      </c>
+      <c r="P10" s="16">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>74</v>
+      </c>
+      <c r="R10" s="7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-10.3</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O11" s="6">
+        <v>93</v>
+      </c>
+      <c r="P11" s="13">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>85</v>
+      </c>
+      <c r="R11" s="16">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A10">
+  <conditionalFormatting sqref="A2:A11">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B10">
+  <conditionalFormatting sqref="B2:B11">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C10">
+  <conditionalFormatting sqref="C2:C11">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F2:F11">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H2:H11">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
+  <conditionalFormatting sqref="J2:J11">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
+  <conditionalFormatting sqref="K2:K11">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
+  <conditionalFormatting sqref="L2:L11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1632,12 +1685,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M10">
+  <conditionalFormatting sqref="M2:M11">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
+  <conditionalFormatting sqref="N2:N11">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1654,22 +1707,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O10">
+  <conditionalFormatting sqref="O2:O11">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
+  <conditionalFormatting sqref="P2:P11">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R11">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
   <si>
     <t>Datum</t>
   </si>
@@ -100,6 +100,15 @@
     <t>20260429--02</t>
   </si>
   <si>
+    <t>20260430--01</t>
+  </si>
+  <si>
+    <t>20260430--02</t>
+  </si>
+  <si>
+    <t>20260430--03</t>
+  </si>
+  <si>
     <t>05:21</t>
   </si>
   <si>
@@ -130,6 +139,15 @@
     <t>06:17</t>
   </si>
   <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:47</t>
+  </si>
+  <si>
     <t>05:05</t>
   </si>
   <si>
@@ -154,6 +172,9 @@
     <t>01:03</t>
   </si>
   <si>
+    <t>03:40</t>
+  </si>
+  <si>
     <t>02:46:11</t>
   </si>
   <si>
@@ -184,6 +205,15 @@
     <t>02:28:03</t>
   </si>
   <si>
+    <t>00:08:33</t>
+  </si>
+  <si>
+    <t>01:45:28</t>
+  </si>
+  <si>
+    <t>23:26:06</t>
+  </si>
+  <si>
     <t>02:48:38</t>
   </si>
   <si>
@@ -214,6 +244,15 @@
     <t>02:30:18</t>
   </si>
   <si>
+    <t>00:11:02</t>
+  </si>
+  <si>
+    <t>01:47:43</t>
+  </si>
+  <si>
+    <t>23:28:41</t>
+  </si>
+  <si>
     <t>02:51:18</t>
   </si>
   <si>
@@ -241,6 +280,15 @@
     <t>02:33:26</t>
   </si>
   <si>
+    <t>00:13:39</t>
+  </si>
+  <si>
+    <t>01:50:50</t>
+  </si>
+  <si>
+    <t>23:31:04</t>
+  </si>
+  <si>
     <t>02:53:59</t>
   </si>
   <si>
@@ -271,6 +319,15 @@
     <t>02:36:35</t>
   </si>
   <si>
+    <t>00:16:17</t>
+  </si>
+  <si>
+    <t>01:53:59</t>
+  </si>
+  <si>
+    <t>23:33:28</t>
+  </si>
+  <si>
     <t>02:56:28</t>
   </si>
   <si>
@@ -301,6 +358,15 @@
     <t>02:38:50</t>
   </si>
   <si>
+    <t>00:18:46</t>
+  </si>
+  <si>
+    <t>01:56:14</t>
+  </si>
+  <si>
+    <t>23:36:04</t>
+  </si>
+  <si>
     <t>11°</t>
   </si>
   <si>
@@ -328,6 +394,15 @@
     <t>16°</t>
   </si>
   <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
     <t>02:48:54</t>
   </si>
   <si>
@@ -358,6 +433,12 @@
     <t>02:31:14</t>
   </si>
   <si>
+    <t>00:17:02</t>
+  </si>
+  <si>
+    <t>01:50:19</t>
+  </si>
+  <si>
     <t>A+B</t>
   </si>
   <si>
@@ -368,6 +449,9 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -401,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,13 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +548,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -574,6 +676,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -977,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1058,52 +1169,52 @@
         <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L2" s="4">
         <v>-9.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="O2" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="9">
-        <v>5</v>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1114,52 +1225,52 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="L3" s="4">
         <v>-14.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O3" s="6">
-        <v>65</v>
+        <v>143</v>
+      </c>
+      <c r="O3" s="9">
+        <v>41</v>
       </c>
       <c r="P3" s="10">
-        <v>65</v>
-      </c>
-      <c r="Q3" s="8">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1170,52 +1281,52 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L4" s="4">
         <v>-18.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O4" s="6">
-        <v>80</v>
+        <v>143</v>
+      </c>
+      <c r="O4" s="9">
+        <v>54</v>
       </c>
       <c r="P4" s="11">
-        <v>80</v>
-      </c>
-      <c r="Q4" s="8">
+        <v>54</v>
+      </c>
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="8">
-        <v>1</v>
+      <c r="R4" s="12">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1226,52 +1337,52 @@
         <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="L5" s="4">
         <v>-7.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O5" s="6">
-        <v>76</v>
-      </c>
-      <c r="P5" s="12">
-        <v>74</v>
-      </c>
-      <c r="Q5" s="8">
+        <v>143</v>
+      </c>
+      <c r="O5" s="9">
+        <v>81</v>
+      </c>
+      <c r="P5" s="13">
+        <v>80</v>
+      </c>
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="9">
-        <v>6</v>
+      <c r="R5" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1282,52 +1393,52 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L6" s="4">
         <v>-21.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="6">
-        <v>70</v>
-      </c>
-      <c r="P6" s="8">
+        <v>144</v>
+      </c>
+      <c r="O6" s="14">
+        <v>44</v>
+      </c>
+      <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
-        <v>57</v>
-      </c>
-      <c r="R6" s="14">
-        <v>70</v>
+      <c r="Q6" s="12">
+        <v>8</v>
+      </c>
+      <c r="R6" s="10">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1338,52 +1449,52 @@
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L7" s="4">
         <v>-12.4</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O7" s="6">
-        <v>74</v>
-      </c>
-      <c r="P7" s="8">
+        <v>143</v>
+      </c>
+      <c r="O7" s="9">
+        <v>52</v>
+      </c>
+      <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="13">
-        <v>55</v>
-      </c>
-      <c r="R7" s="10">
-        <v>67</v>
+      <c r="Q7" s="15">
+        <v>31</v>
+      </c>
+      <c r="R7" s="16">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1394,52 +1505,52 @@
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L8" s="4">
         <v>-23.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="6">
+        <v>144</v>
+      </c>
+      <c r="O8" s="9">
+        <v>99</v>
+      </c>
+      <c r="P8" s="11">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="17">
         <v>98</v>
       </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>96</v>
-      </c>
-      <c r="R8" s="14">
-        <v>69</v>
+      <c r="R8" s="13">
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1450,52 +1561,52 @@
         <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L9" s="4">
         <v>-16.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O9" s="6">
+        <v>143</v>
+      </c>
+      <c r="O9" s="9">
+        <v>99</v>
+      </c>
+      <c r="P9" s="18">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="17">
         <v>98</v>
       </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>94</v>
-      </c>
-      <c r="R9" s="10">
-        <v>64</v>
+      <c r="R9" s="19">
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1506,52 +1617,52 @@
         <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="L10" s="4">
         <v>-20.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="O10" s="6">
-        <v>92</v>
-      </c>
-      <c r="P10" s="16">
-        <v>44</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>74</v>
+        <v>143</v>
+      </c>
+      <c r="O10" s="9">
+        <v>94</v>
+      </c>
+      <c r="P10" s="13">
+        <v>78</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
       </c>
       <c r="R10" s="7">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1562,111 +1673,279 @@
         <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L11" s="4">
         <v>-10.3</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O11" s="9">
+        <v>84</v>
+      </c>
+      <c r="P11" s="19">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>8</v>
+      </c>
+      <c r="R11" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="J12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L12" s="4">
+        <v>-22.7</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O12" s="9">
+        <v>63</v>
+      </c>
+      <c r="P12" s="11">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>10</v>
+      </c>
+      <c r="R12" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="4">
+        <v>-14.9</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="9">
+        <v>62</v>
+      </c>
+      <c r="P13" s="18">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>2</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="O11" s="6">
-        <v>93</v>
-      </c>
-      <c r="P11" s="13">
-        <v>54</v>
-      </c>
-      <c r="Q11" s="17">
-        <v>85</v>
-      </c>
-      <c r="R11" s="16">
-        <v>43</v>
+      <c r="J14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-24</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O14" s="9">
+        <v>49</v>
+      </c>
+      <c r="P14" s="20">
+        <v>49</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>4</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A11">
+  <conditionalFormatting sqref="A2:A14">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B14">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C14">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D11">
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E14">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F14">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="H2:H14">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
+  <conditionalFormatting sqref="I2:I14">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J11">
+  <conditionalFormatting sqref="J2:J14">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K11">
+  <conditionalFormatting sqref="K2:K14">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L11">
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1685,12 +1964,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M11">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N11">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1707,22 +1986,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O11">
+  <conditionalFormatting sqref="O2:O14">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P11">
+  <conditionalFormatting sqref="P2:P14">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q11">
+  <conditionalFormatting sqref="Q2:Q14">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
+  <conditionalFormatting sqref="R2:R14">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="164">
   <si>
     <t>Datum</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260424--01</t>
-  </si>
-  <si>
     <t>20260425--01</t>
   </si>
   <si>
@@ -109,52 +106,64 @@
     <t>20260430--03</t>
   </si>
   <si>
-    <t>05:21</t>
+    <t>20260501--01</t>
+  </si>
+  <si>
+    <t>20260501--02</t>
+  </si>
+  <si>
+    <t>20260501--03</t>
   </si>
   <si>
     <t>04:54</t>
   </si>
   <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>06:12</t>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>03:14</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>00:36</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>06:17</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>06:16</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>04:03</t>
   </si>
   <si>
     <t>03:15</t>
   </si>
   <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>00:38</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>05:37</t>
-  </si>
-  <si>
-    <t>06:17</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:47</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>03:16</t>
-  </si>
-  <si>
-    <t>01:22</t>
+    <t>01:21</t>
   </si>
   <si>
     <t>06:10</t>
@@ -163,280 +172,325 @@
     <t>00:00</t>
   </si>
   <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>02:48</t>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>02:47</t>
   </si>
   <si>
     <t>01:03</t>
   </si>
   <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>02:46:11</t>
-  </si>
-  <si>
-    <t>02:03:57</t>
-  </si>
-  <si>
-    <t>01:21:44</t>
-  </si>
-  <si>
-    <t>02:58:20</t>
-  </si>
-  <si>
-    <t>00:39:32</t>
-  </si>
-  <si>
-    <t>02:15:55</t>
-  </si>
-  <si>
-    <t>23:57:21</t>
-  </si>
-  <si>
-    <t>01:33:28</t>
-  </si>
-  <si>
-    <t>00:51:01</t>
-  </si>
-  <si>
-    <t>02:28:03</t>
-  </si>
-  <si>
-    <t>00:08:33</t>
-  </si>
-  <si>
-    <t>01:45:28</t>
-  </si>
-  <si>
-    <t>23:26:06</t>
-  </si>
-  <si>
-    <t>02:48:38</t>
-  </si>
-  <si>
-    <t>02:06:31</t>
-  </si>
-  <si>
-    <t>01:24:28</t>
-  </si>
-  <si>
-    <t>03:00:36</t>
-  </si>
-  <si>
-    <t>00:42:34</t>
-  </si>
-  <si>
-    <t>02:18:12</t>
-  </si>
-  <si>
-    <t>00:01:46</t>
-  </si>
-  <si>
-    <t>01:35:48</t>
-  </si>
-  <si>
-    <t>00:53:24</t>
-  </si>
-  <si>
-    <t>02:30:18</t>
-  </si>
-  <si>
-    <t>00:11:02</t>
-  </si>
-  <si>
-    <t>01:47:43</t>
-  </si>
-  <si>
-    <t>23:28:41</t>
-  </si>
-  <si>
-    <t>02:51:18</t>
-  </si>
-  <si>
-    <t>02:08:57</t>
-  </si>
-  <si>
-    <t>01:26:35</t>
-  </si>
-  <si>
-    <t>03:03:42</t>
-  </si>
-  <si>
-    <t>00:44:12</t>
-  </si>
-  <si>
-    <t>02:21:14</t>
-  </si>
-  <si>
-    <t>01:38:44</t>
-  </si>
-  <si>
-    <t>00:56:13</t>
-  </si>
-  <si>
-    <t>02:33:26</t>
-  </si>
-  <si>
-    <t>00:13:39</t>
-  </si>
-  <si>
-    <t>01:50:50</t>
-  </si>
-  <si>
-    <t>23:31:04</t>
-  </si>
-  <si>
-    <t>02:53:59</t>
-  </si>
-  <si>
-    <t>02:11:25</t>
-  </si>
-  <si>
-    <t>01:28:43</t>
-  </si>
-  <si>
-    <t>03:06:48</t>
-  </si>
-  <si>
-    <t>00:45:49</t>
-  </si>
-  <si>
-    <t>02:24:16</t>
-  </si>
-  <si>
-    <t>00:02:24</t>
-  </si>
-  <si>
-    <t>01:41:41</t>
-  </si>
-  <si>
-    <t>00:59:01</t>
-  </si>
-  <si>
-    <t>02:36:35</t>
-  </si>
-  <si>
-    <t>00:16:17</t>
-  </si>
-  <si>
-    <t>01:53:59</t>
-  </si>
-  <si>
-    <t>23:33:28</t>
-  </si>
-  <si>
-    <t>02:56:28</t>
-  </si>
-  <si>
-    <t>02:14:00</t>
-  </si>
-  <si>
-    <t>01:31:28</t>
-  </si>
-  <si>
-    <t>03:09:05</t>
-  </si>
-  <si>
-    <t>00:48:53</t>
-  </si>
-  <si>
-    <t>02:26:35</t>
-  </si>
-  <si>
-    <t>00:06:13</t>
-  </si>
-  <si>
-    <t>01:44:02</t>
-  </si>
-  <si>
-    <t>01:01:26</t>
-  </si>
-  <si>
-    <t>02:38:50</t>
-  </si>
-  <si>
-    <t>00:18:46</t>
-  </si>
-  <si>
-    <t>01:56:14</t>
-  </si>
-  <si>
-    <t>23:36:04</t>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>01:54</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>02:03:55</t>
+  </si>
+  <si>
+    <t>01:21:40</t>
+  </si>
+  <si>
+    <t>02:58:17</t>
+  </si>
+  <si>
+    <t>00:39:26</t>
+  </si>
+  <si>
+    <t>02:15:49</t>
+  </si>
+  <si>
+    <t>23:57:13</t>
+  </si>
+  <si>
+    <t>01:33:20</t>
+  </si>
+  <si>
+    <t>00:50:49</t>
+  </si>
+  <si>
+    <t>02:27:51</t>
+  </si>
+  <si>
+    <t>00:08:18</t>
+  </si>
+  <si>
+    <t>01:45:12</t>
+  </si>
+  <si>
+    <t>23:25:47</t>
+  </si>
+  <si>
+    <t>01:02:31</t>
+  </si>
+  <si>
+    <t>02:39:50</t>
+  </si>
+  <si>
+    <t>22:43:15</t>
+  </si>
+  <si>
+    <t>02:06:29</t>
+  </si>
+  <si>
+    <t>01:24:25</t>
+  </si>
+  <si>
+    <t>03:00:33</t>
+  </si>
+  <si>
+    <t>00:42:29</t>
+  </si>
+  <si>
+    <t>02:18:07</t>
+  </si>
+  <si>
+    <t>00:01:38</t>
+  </si>
+  <si>
+    <t>01:35:40</t>
+  </si>
+  <si>
+    <t>00:53:13</t>
+  </si>
+  <si>
+    <t>02:30:06</t>
+  </si>
+  <si>
+    <t>00:10:47</t>
+  </si>
+  <si>
+    <t>01:47:27</t>
+  </si>
+  <si>
+    <t>23:28:22</t>
+  </si>
+  <si>
+    <t>01:04:46</t>
+  </si>
+  <si>
+    <t>02:42:10</t>
+  </si>
+  <si>
+    <t>22:46:02</t>
+  </si>
+  <si>
+    <t>02:08:55</t>
+  </si>
+  <si>
+    <t>01:26:32</t>
+  </si>
+  <si>
+    <t>03:03:38</t>
+  </si>
+  <si>
+    <t>00:44:06</t>
+  </si>
+  <si>
+    <t>02:21:08</t>
+  </si>
+  <si>
+    <t>01:38:36</t>
+  </si>
+  <si>
+    <t>00:56:01</t>
+  </si>
+  <si>
+    <t>02:33:14</t>
+  </si>
+  <si>
+    <t>00:13:24</t>
+  </si>
+  <si>
+    <t>01:50:35</t>
+  </si>
+  <si>
+    <t>23:30:45</t>
+  </si>
+  <si>
+    <t>01:07:52</t>
+  </si>
+  <si>
+    <t>02:45:07</t>
+  </si>
+  <si>
+    <t>22:48:03</t>
+  </si>
+  <si>
+    <t>02:11:23</t>
+  </si>
+  <si>
+    <t>01:28:39</t>
+  </si>
+  <si>
+    <t>03:06:44</t>
+  </si>
+  <si>
+    <t>00:45:43</t>
+  </si>
+  <si>
+    <t>02:24:10</t>
+  </si>
+  <si>
+    <t>00:02:14</t>
+  </si>
+  <si>
+    <t>01:41:32</t>
+  </si>
+  <si>
+    <t>00:58:49</t>
+  </si>
+  <si>
+    <t>02:36:23</t>
+  </si>
+  <si>
+    <t>00:16:02</t>
+  </si>
+  <si>
+    <t>01:53:43</t>
+  </si>
+  <si>
+    <t>23:33:07</t>
+  </si>
+  <si>
+    <t>01:11:00</t>
+  </si>
+  <si>
+    <t>02:48:04</t>
+  </si>
+  <si>
+    <t>22:50:05</t>
+  </si>
+  <si>
+    <t>02:13:58</t>
+  </si>
+  <si>
+    <t>01:31:25</t>
+  </si>
+  <si>
+    <t>03:09:01</t>
+  </si>
+  <si>
+    <t>00:48:47</t>
+  </si>
+  <si>
+    <t>02:26:29</t>
+  </si>
+  <si>
+    <t>00:06:04</t>
+  </si>
+  <si>
+    <t>01:43:53</t>
+  </si>
+  <si>
+    <t>01:01:14</t>
+  </si>
+  <si>
+    <t>02:38:38</t>
+  </si>
+  <si>
+    <t>00:18:31</t>
+  </si>
+  <si>
+    <t>01:55:59</t>
+  </si>
+  <si>
+    <t>23:35:44</t>
+  </si>
+  <si>
+    <t>01:13:15</t>
+  </si>
+  <si>
+    <t>02:50:24</t>
+  </si>
+  <si>
+    <t>22:52:53</t>
+  </si>
+  <si>
+    <t>17°</t>
+  </si>
+  <si>
+    <t>15°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>26°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>7°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>24°</t>
   </si>
   <si>
     <t>11°</t>
   </si>
   <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>15°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>02:48:54</t>
-  </si>
-  <si>
-    <t>02:08:09</t>
-  </si>
-  <si>
-    <t>01:27:21</t>
-  </si>
-  <si>
-    <t>03:00:38</t>
-  </si>
-  <si>
-    <t>00:46:30</t>
-  </si>
-  <si>
-    <t>02:19:46</t>
-  </si>
-  <si>
-    <t>00:05:36</t>
-  </si>
-  <si>
-    <t>01:38:53</t>
-  </si>
-  <si>
-    <t>00:57:58</t>
-  </si>
-  <si>
-    <t>02:31:14</t>
-  </si>
-  <si>
-    <t>00:17:02</t>
-  </si>
-  <si>
-    <t>01:50:19</t>
+    <t>02:08:08</t>
+  </si>
+  <si>
+    <t>01:27:18</t>
+  </si>
+  <si>
+    <t>03:00:34</t>
+  </si>
+  <si>
+    <t>00:46:24</t>
+  </si>
+  <si>
+    <t>02:19:41</t>
+  </si>
+  <si>
+    <t>00:05:28</t>
+  </si>
+  <si>
+    <t>01:38:45</t>
+  </si>
+  <si>
+    <t>00:57:46</t>
+  </si>
+  <si>
+    <t>02:31:03</t>
+  </si>
+  <si>
+    <t>00:16:48</t>
+  </si>
+  <si>
+    <t>01:50:04</t>
+  </si>
+  <si>
+    <t>01:09:06</t>
+  </si>
+  <si>
+    <t>02:42:22</t>
   </si>
   <si>
     <t>A+B</t>
@@ -485,7 +539,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,7 +554,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,67 +572,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,6 +603,60 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -625,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -685,6 +757,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1166,55 +1247,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="L2" s="4">
-        <v>-9.5</v>
+        <v>-14.4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="O2" s="6">
+        <v>87</v>
+      </c>
+      <c r="P2" s="7">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="8">
         <v>0</v>
       </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
-        <v>4</v>
+      <c r="R2" s="9">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1222,55 +1303,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-18.6</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O3" s="6">
+        <v>74</v>
+      </c>
+      <c r="P3" s="7">
         <v>45</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-14.4</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O3" s="9">
-        <v>41</v>
-      </c>
-      <c r="P3" s="10">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="8">
         <v>0</v>
       </c>
-      <c r="R3" s="8">
-        <v>4</v>
+      <c r="R3" s="10">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1278,55 +1359,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="L4" s="4">
-        <v>-18.6</v>
+        <v>-7.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O4" s="9">
-        <v>54</v>
+        <v>161</v>
+      </c>
+      <c r="O4" s="6">
+        <v>79</v>
       </c>
       <c r="P4" s="11">
-        <v>54</v>
-      </c>
-      <c r="Q4" s="7">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="12">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1334,55 +1415,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L5" s="4">
+        <v>-21.8</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" s="6">
+        <v>78</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>70</v>
+      </c>
+      <c r="R5" s="13">
         <v>69</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-7.3</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O5" s="9">
-        <v>81</v>
-      </c>
-      <c r="P5" s="13">
-        <v>80</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1390,55 +1471,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="L6" s="4">
-        <v>-21.8</v>
+        <v>-12.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O6" s="14">
-        <v>44</v>
-      </c>
-      <c r="P6" s="7">
+        <v>161</v>
+      </c>
+      <c r="O6" s="6">
+        <v>58</v>
+      </c>
+      <c r="P6" s="8">
         <v>0</v>
       </c>
-      <c r="Q6" s="12">
-        <v>8</v>
-      </c>
-      <c r="R6" s="10">
-        <v>39</v>
+      <c r="Q6" s="14">
+        <v>52</v>
+      </c>
+      <c r="R6" s="9">
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1446,55 +1527,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="L7" s="4">
-        <v>-12.4</v>
+        <v>-23.9</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O7" s="9">
-        <v>52</v>
-      </c>
-      <c r="P7" s="7">
+        <v>162</v>
+      </c>
+      <c r="O7" s="6">
+        <v>100</v>
+      </c>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
       <c r="Q7" s="15">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="R7" s="16">
-        <v>25</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1502,55 +1583,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L8" s="4">
-        <v>-23.9</v>
+        <v>-16.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="O8" s="9">
-        <v>99</v>
-      </c>
-      <c r="P8" s="11">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="17">
-        <v>98</v>
-      </c>
-      <c r="R8" s="13">
-        <v>81</v>
+        <v>161</v>
+      </c>
+      <c r="O8" s="6">
+        <v>100</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>100</v>
+      </c>
+      <c r="R8" s="16">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1558,55 +1639,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="L9" s="4">
-        <v>-16.8</v>
+        <v>-20.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O9" s="9">
-        <v>99</v>
-      </c>
-      <c r="P9" s="18">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>98</v>
+        <v>161</v>
+      </c>
+      <c r="O9" s="17">
+        <v>31</v>
+      </c>
+      <c r="P9" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>18</v>
       </c>
       <c r="R9" s="19">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1614,55 +1695,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="L10" s="4">
-        <v>-20.3</v>
+        <v>-10.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O10" s="9">
-        <v>94</v>
-      </c>
-      <c r="P10" s="13">
-        <v>78</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="7">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="O10" s="17">
+        <v>33</v>
+      </c>
+      <c r="P10" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>28</v>
+      </c>
+      <c r="R10" s="21">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1670,55 +1751,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="L11" s="4">
-        <v>-10.3</v>
+        <v>-22.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O11" s="9">
-        <v>84</v>
-      </c>
-      <c r="P11" s="19">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>8</v>
-      </c>
-      <c r="R11" s="12">
-        <v>8</v>
+        <v>163</v>
+      </c>
+      <c r="O11" s="6">
+        <v>64</v>
+      </c>
+      <c r="P11" s="7">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>9</v>
+      </c>
+      <c r="R11" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1726,55 +1807,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="L12" s="4">
-        <v>-22.7</v>
+        <v>-15</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O12" s="9">
-        <v>63</v>
-      </c>
-      <c r="P12" s="11">
-        <v>56</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>10</v>
-      </c>
-      <c r="R12" s="7">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="O12" s="6">
+        <v>53</v>
+      </c>
+      <c r="P12" s="21">
+        <v>37</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="19">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1782,54 +1863,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="L13" s="4">
-        <v>-14.9</v>
+        <v>-24</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="9">
-        <v>62</v>
-      </c>
-      <c r="P13" s="18">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="7">
+        <v>163</v>
+      </c>
+      <c r="O13" s="23">
+        <v>5</v>
+      </c>
+      <c r="P13" s="8">
         <v>2</v>
       </c>
-      <c r="R13" s="7">
+      <c r="Q13" s="8">
+        <v>1</v>
+      </c>
+      <c r="R13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1838,114 +1919,226 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-18.8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O14" s="23">
+        <v>9</v>
+      </c>
+      <c r="P14" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>2</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>26</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="I15" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L15" s="4">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O15" s="23">
+        <v>9</v>
+      </c>
+      <c r="P15" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>3</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" s="4">
         <v>-24</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O14" s="9">
-        <v>49</v>
-      </c>
-      <c r="P14" s="20">
-        <v>49</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>4</v>
-      </c>
-      <c r="R14" s="7">
+      <c r="M16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O16" s="23">
+        <v>6</v>
+      </c>
+      <c r="P16" s="19">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A14">
+  <conditionalFormatting sqref="A2:A16">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B14">
+  <conditionalFormatting sqref="B2:B16">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C14">
+  <conditionalFormatting sqref="C2:C16">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D14">
+  <conditionalFormatting sqref="D2:D16">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E14">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
+  <conditionalFormatting sqref="F2:F16">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H16">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
+  <conditionalFormatting sqref="I2:I16">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
+  <conditionalFormatting sqref="J2:J16">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
+  <conditionalFormatting sqref="K2:K16">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
+  <conditionalFormatting sqref="L2:L16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -1964,12 +2157,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="M2:M16">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N14">
+  <conditionalFormatting sqref="N2:N16">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -1986,22 +2179,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O14">
+  <conditionalFormatting sqref="O2:O16">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P14">
+  <conditionalFormatting sqref="P2:P16">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q14">
+  <conditionalFormatting sqref="Q2:Q16">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R16">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="183">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260425--01</t>
-  </si>
-  <si>
-    <t>20260426--01</t>
-  </si>
-  <si>
-    <t>20260426--02</t>
-  </si>
-  <si>
     <t>20260427--01</t>
   </si>
   <si>
@@ -115,13 +106,22 @@
     <t>20260501--03</t>
   </si>
   <si>
-    <t>04:54</t>
-  </si>
-  <si>
-    <t>04:14</t>
-  </si>
-  <si>
-    <t>06:11</t>
+    <t>20260502--01</t>
+  </si>
+  <si>
+    <t>20260502--02</t>
+  </si>
+  <si>
+    <t>20260502--03</t>
+  </si>
+  <si>
+    <t>20260502--04</t>
+  </si>
+  <si>
+    <t>20260503--01</t>
+  </si>
+  <si>
+    <t>20260503--02</t>
   </si>
   <si>
     <t>03:14</t>
@@ -136,7 +136,7 @@
     <t>05:52</t>
   </si>
   <si>
-    <t>05:36</t>
+    <t>05:37</t>
   </si>
   <si>
     <t>06:17</t>
@@ -151,24 +151,33 @@
     <t>04:45</t>
   </si>
   <si>
-    <t>06:14</t>
+    <t>06:13</t>
   </si>
   <si>
     <t>05:54</t>
   </si>
   <si>
-    <t>04:03</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>01:21</t>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>05:59</t>
   </si>
   <si>
     <t>06:10</t>
   </si>
   <si>
+    <t>05:47</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
@@ -184,325 +193,373 @@
     <t>05:20</t>
   </si>
   <si>
-    <t>03:39</t>
-  </si>
-  <si>
-    <t>01:54</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>02:03:55</t>
-  </si>
-  <si>
-    <t>01:21:40</t>
-  </si>
-  <si>
-    <t>02:58:17</t>
-  </si>
-  <si>
-    <t>00:39:26</t>
-  </si>
-  <si>
-    <t>02:15:49</t>
-  </si>
-  <si>
-    <t>23:57:13</t>
-  </si>
-  <si>
-    <t>01:33:20</t>
-  </si>
-  <si>
-    <t>00:50:49</t>
-  </si>
-  <si>
-    <t>02:27:51</t>
-  </si>
-  <si>
-    <t>00:08:18</t>
-  </si>
-  <si>
-    <t>01:45:12</t>
-  </si>
-  <si>
-    <t>23:25:47</t>
-  </si>
-  <si>
-    <t>01:02:31</t>
-  </si>
-  <si>
-    <t>02:39:50</t>
-  </si>
-  <si>
-    <t>22:43:15</t>
-  </si>
-  <si>
-    <t>02:06:29</t>
-  </si>
-  <si>
-    <t>01:24:25</t>
-  </si>
-  <si>
-    <t>03:00:33</t>
-  </si>
-  <si>
-    <t>00:42:29</t>
-  </si>
-  <si>
-    <t>02:18:07</t>
-  </si>
-  <si>
-    <t>00:01:38</t>
-  </si>
-  <si>
-    <t>01:35:40</t>
-  </si>
-  <si>
-    <t>00:53:13</t>
-  </si>
-  <si>
-    <t>02:30:06</t>
-  </si>
-  <si>
-    <t>00:10:47</t>
-  </si>
-  <si>
-    <t>01:47:27</t>
-  </si>
-  <si>
-    <t>23:28:22</t>
-  </si>
-  <si>
-    <t>01:04:46</t>
-  </si>
-  <si>
-    <t>02:42:10</t>
-  </si>
-  <si>
-    <t>22:46:02</t>
-  </si>
-  <si>
-    <t>02:08:55</t>
-  </si>
-  <si>
-    <t>01:26:32</t>
-  </si>
-  <si>
-    <t>03:03:38</t>
-  </si>
-  <si>
-    <t>00:44:06</t>
-  </si>
-  <si>
-    <t>02:21:08</t>
-  </si>
-  <si>
-    <t>01:38:36</t>
-  </si>
-  <si>
-    <t>00:56:01</t>
-  </si>
-  <si>
-    <t>02:33:14</t>
-  </si>
-  <si>
-    <t>00:13:24</t>
-  </si>
-  <si>
-    <t>01:50:35</t>
-  </si>
-  <si>
-    <t>23:30:45</t>
-  </si>
-  <si>
-    <t>01:07:52</t>
-  </si>
-  <si>
-    <t>02:45:07</t>
-  </si>
-  <si>
-    <t>22:48:03</t>
-  </si>
-  <si>
-    <t>02:11:23</t>
-  </si>
-  <si>
-    <t>01:28:39</t>
-  </si>
-  <si>
-    <t>03:06:44</t>
-  </si>
-  <si>
-    <t>00:45:43</t>
-  </si>
-  <si>
-    <t>02:24:10</t>
-  </si>
-  <si>
-    <t>00:02:14</t>
-  </si>
-  <si>
-    <t>01:41:32</t>
-  </si>
-  <si>
-    <t>00:58:49</t>
-  </si>
-  <si>
-    <t>02:36:23</t>
-  </si>
-  <si>
-    <t>00:16:02</t>
-  </si>
-  <si>
-    <t>01:53:43</t>
-  </si>
-  <si>
-    <t>23:33:07</t>
-  </si>
-  <si>
-    <t>01:11:00</t>
-  </si>
-  <si>
-    <t>02:48:04</t>
-  </si>
-  <si>
-    <t>22:50:05</t>
-  </si>
-  <si>
-    <t>02:13:58</t>
-  </si>
-  <si>
-    <t>01:31:25</t>
-  </si>
-  <si>
-    <t>03:09:01</t>
-  </si>
-  <si>
-    <t>00:48:47</t>
-  </si>
-  <si>
-    <t>02:26:29</t>
-  </si>
-  <si>
-    <t>00:06:04</t>
-  </si>
-  <si>
-    <t>01:43:53</t>
-  </si>
-  <si>
-    <t>01:01:14</t>
-  </si>
-  <si>
-    <t>02:38:38</t>
-  </si>
-  <si>
-    <t>00:18:31</t>
-  </si>
-  <si>
-    <t>01:55:59</t>
-  </si>
-  <si>
-    <t>23:35:44</t>
-  </si>
-  <si>
-    <t>01:13:15</t>
-  </si>
-  <si>
-    <t>02:50:24</t>
-  </si>
-  <si>
-    <t>22:52:53</t>
-  </si>
-  <si>
-    <t>17°</t>
-  </si>
-  <si>
-    <t>15°</t>
+    <t>03:38</t>
+  </si>
+  <si>
+    <t>01:53</t>
+  </si>
+  <si>
+    <t>05:41</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>00:39:24</t>
+  </si>
+  <si>
+    <t>02:15:47</t>
+  </si>
+  <si>
+    <t>23:57:09</t>
+  </si>
+  <si>
+    <t>01:33:15</t>
+  </si>
+  <si>
+    <t>00:50:41</t>
+  </si>
+  <si>
+    <t>02:27:42</t>
+  </si>
+  <si>
+    <t>00:08:05</t>
+  </si>
+  <si>
+    <t>01:44:58</t>
+  </si>
+  <si>
+    <t>23:25:28</t>
+  </si>
+  <si>
+    <t>01:02:11</t>
+  </si>
+  <si>
+    <t>02:39:30</t>
+  </si>
+  <si>
+    <t>22:42:49</t>
+  </si>
+  <si>
+    <t>00:19:21</t>
+  </si>
+  <si>
+    <t>01:56:36</t>
+  </si>
+  <si>
+    <t>22:00:10</t>
+  </si>
+  <si>
+    <t>23:36:28</t>
+  </si>
+  <si>
+    <t>01:13:38</t>
+  </si>
+  <si>
+    <t>22:53:32</t>
+  </si>
+  <si>
+    <t>00:42:27</t>
+  </si>
+  <si>
+    <t>02:18:05</t>
+  </si>
+  <si>
+    <t>00:01:33</t>
+  </si>
+  <si>
+    <t>01:35:35</t>
+  </si>
+  <si>
+    <t>00:53:04</t>
+  </si>
+  <si>
+    <t>02:29:57</t>
+  </si>
+  <si>
+    <t>00:10:33</t>
+  </si>
+  <si>
+    <t>01:47:13</t>
+  </si>
+  <si>
+    <t>23:28:03</t>
+  </si>
+  <si>
+    <t>01:04:27</t>
+  </si>
+  <si>
+    <t>02:41:50</t>
+  </si>
+  <si>
+    <t>22:45:37</t>
+  </si>
+  <si>
+    <t>00:21:37</t>
+  </si>
+  <si>
+    <t>01:58:53</t>
+  </si>
+  <si>
+    <t>22:03:20</t>
+  </si>
+  <si>
+    <t>23:38:46</t>
+  </si>
+  <si>
+    <t>01:15:54</t>
+  </si>
+  <si>
+    <t>22:55:53</t>
+  </si>
+  <si>
+    <t>00:44:04</t>
+  </si>
+  <si>
+    <t>02:21:06</t>
+  </si>
+  <si>
+    <t>01:38:31</t>
+  </si>
+  <si>
+    <t>00:55:52</t>
+  </si>
+  <si>
+    <t>02:33:05</t>
+  </si>
+  <si>
+    <t>00:13:10</t>
+  </si>
+  <si>
+    <t>01:50:21</t>
+  </si>
+  <si>
+    <t>23:30:25</t>
+  </si>
+  <si>
+    <t>01:07:33</t>
+  </si>
+  <si>
+    <t>02:44:47</t>
+  </si>
+  <si>
+    <t>22:47:37</t>
+  </si>
+  <si>
+    <t>00:24:41</t>
+  </si>
+  <si>
+    <t>02:01:55</t>
+  </si>
+  <si>
+    <t>22:04:46</t>
+  </si>
+  <si>
+    <t>23:41:45</t>
+  </si>
+  <si>
+    <t>01:18:59</t>
+  </si>
+  <si>
+    <t>22:58:46</t>
+  </si>
+  <si>
+    <t>00:45:41</t>
+  </si>
+  <si>
+    <t>02:24:08</t>
+  </si>
+  <si>
+    <t>00:02:09</t>
+  </si>
+  <si>
+    <t>01:41:27</t>
+  </si>
+  <si>
+    <t>00:58:41</t>
+  </si>
+  <si>
+    <t>02:36:14</t>
+  </si>
+  <si>
+    <t>00:15:48</t>
+  </si>
+  <si>
+    <t>01:53:29</t>
+  </si>
+  <si>
+    <t>23:32:48</t>
+  </si>
+  <si>
+    <t>01:10:40</t>
+  </si>
+  <si>
+    <t>02:47:44</t>
+  </si>
+  <si>
+    <t>22:49:37</t>
+  </si>
+  <si>
+    <t>00:27:45</t>
+  </si>
+  <si>
+    <t>02:04:57</t>
+  </si>
+  <si>
+    <t>22:06:11</t>
+  </si>
+  <si>
+    <t>23:44:45</t>
+  </si>
+  <si>
+    <t>01:22:04</t>
+  </si>
+  <si>
+    <t>23:01:40</t>
+  </si>
+  <si>
+    <t>00:48:45</t>
+  </si>
+  <si>
+    <t>02:26:26</t>
+  </si>
+  <si>
+    <t>00:05:59</t>
+  </si>
+  <si>
+    <t>01:43:48</t>
+  </si>
+  <si>
+    <t>01:01:05</t>
+  </si>
+  <si>
+    <t>02:38:29</t>
+  </si>
+  <si>
+    <t>00:18:17</t>
+  </si>
+  <si>
+    <t>01:55:45</t>
+  </si>
+  <si>
+    <t>23:35:24</t>
+  </si>
+  <si>
+    <t>01:12:55</t>
+  </si>
+  <si>
+    <t>02:50:04</t>
+  </si>
+  <si>
+    <t>22:52:26</t>
+  </si>
+  <si>
+    <t>00:30:02</t>
+  </si>
+  <si>
+    <t>02:07:15</t>
+  </si>
+  <si>
+    <t>22:09:22</t>
+  </si>
+  <si>
+    <t>23:47:04</t>
+  </si>
+  <si>
+    <t>01:24:21</t>
+  </si>
+  <si>
+    <t>23:04:01</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>21°</t>
+  </si>
+  <si>
+    <t>2°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>11°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>21°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>26°</t>
-  </si>
-  <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>02:08:08</t>
-  </si>
-  <si>
-    <t>01:27:18</t>
-  </si>
-  <si>
-    <t>03:00:34</t>
-  </si>
-  <si>
-    <t>00:46:24</t>
-  </si>
-  <si>
-    <t>02:19:41</t>
-  </si>
-  <si>
-    <t>00:05:28</t>
-  </si>
-  <si>
-    <t>01:38:45</t>
-  </si>
-  <si>
-    <t>00:57:46</t>
-  </si>
-  <si>
-    <t>02:31:03</t>
-  </si>
-  <si>
-    <t>00:16:48</t>
-  </si>
-  <si>
-    <t>01:50:04</t>
-  </si>
-  <si>
-    <t>01:09:06</t>
-  </si>
-  <si>
-    <t>02:42:22</t>
+    <t>1°</t>
+  </si>
+  <si>
+    <t>00:46:22</t>
+  </si>
+  <si>
+    <t>02:19:39</t>
+  </si>
+  <si>
+    <t>00:05:24</t>
+  </si>
+  <si>
+    <t>01:38:40</t>
+  </si>
+  <si>
+    <t>00:57:38</t>
+  </si>
+  <si>
+    <t>02:30:54</t>
+  </si>
+  <si>
+    <t>00:16:35</t>
+  </si>
+  <si>
+    <t>01:49:51</t>
+  </si>
+  <si>
+    <t>01:08:47</t>
+  </si>
+  <si>
+    <t>02:42:03</t>
+  </si>
+  <si>
+    <t>02:01:01</t>
+  </si>
+  <si>
+    <t>23:46:48</t>
+  </si>
+  <si>
+    <t>01:20:04</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>3</t>
@@ -539,7 +596,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,13 +617,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF558CC8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,37 +647,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,13 +665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -638,25 +683,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFC4D7EC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,7 +730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,18 +787,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1247,55 +1268,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="L2" s="4">
-        <v>-14.4</v>
+        <v>-21.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="O2" s="6">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="P2" s="7">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R2" s="9">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1303,55 +1324,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="L3" s="4">
-        <v>-18.6</v>
+        <v>-12.4</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O3" s="6">
-        <v>74</v>
+        <v>181</v>
+      </c>
+      <c r="O3" s="10">
+        <v>29</v>
       </c>
       <c r="P3" s="7">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>61</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>25</v>
+      </c>
+      <c r="R3" s="12">
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1359,55 +1380,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="L4" s="4">
-        <v>-7.3</v>
+        <v>-24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="O4" s="6">
-        <v>79</v>
-      </c>
-      <c r="P4" s="11">
-        <v>77</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>13</v>
+        <v>100</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>54</v>
+      </c>
+      <c r="R4" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1415,55 +1436,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="L5" s="4">
-        <v>-21.8</v>
+        <v>-16.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="O5" s="6">
-        <v>78</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>70</v>
-      </c>
-      <c r="R5" s="13">
-        <v>69</v>
+        <v>100</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>42</v>
+      </c>
+      <c r="R5" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1471,55 +1492,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="L6" s="4">
-        <v>-12.4</v>
+        <v>-20.3</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O6" s="6">
-        <v>58</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>52</v>
-      </c>
-      <c r="R6" s="9">
-        <v>24</v>
+        <v>181</v>
+      </c>
+      <c r="O6" s="16">
+        <v>1</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1527,55 +1548,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.9</v>
+        <v>-10.3</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="O7" s="6">
-        <v>100</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>97</v>
-      </c>
-      <c r="R7" s="16">
-        <v>99</v>
+        <v>181</v>
+      </c>
+      <c r="O7" s="16">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1583,55 +1604,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="L8" s="4">
-        <v>-16.8</v>
+        <v>-22.8</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>100</v>
-      </c>
-      <c r="R8" s="16">
-        <v>100</v>
+        <v>182</v>
+      </c>
+      <c r="O8" s="16">
+        <v>3</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1639,55 +1660,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="L9" s="4">
-        <v>-20.3</v>
+        <v>-15</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O9" s="17">
-        <v>31</v>
-      </c>
-      <c r="P9" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>18</v>
-      </c>
-      <c r="R9" s="19">
-        <v>5</v>
+        <v>181</v>
+      </c>
+      <c r="O9" s="16">
+        <v>3</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1695,55 +1716,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="L10" s="4">
-        <v>-10.3</v>
+        <v>-24</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O10" s="17">
-        <v>33</v>
-      </c>
-      <c r="P10" s="8">
+        <v>182</v>
+      </c>
+      <c r="O10" s="16">
         <v>2</v>
       </c>
-      <c r="Q10" s="20">
-        <v>28</v>
-      </c>
-      <c r="R10" s="21">
-        <v>33</v>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1751,55 +1772,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="L11" s="4">
-        <v>-22.8</v>
+        <v>-18.8</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O11" s="6">
-        <v>64</v>
+        <v>181</v>
+      </c>
+      <c r="O11" s="16">
+        <v>1</v>
       </c>
       <c r="P11" s="7">
-        <v>43</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>9</v>
-      </c>
-      <c r="R11" s="8">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1807,55 +1828,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="L12" s="4">
-        <v>-15</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O12" s="6">
-        <v>53</v>
-      </c>
-      <c r="P12" s="21">
-        <v>37</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0</v>
-      </c>
-      <c r="R12" s="19">
-        <v>3</v>
+        <v>181</v>
+      </c>
+      <c r="O12" s="16">
+        <v>1</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1863,54 +1884,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L13" s="4">
         <v>-24</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O13" s="23">
-        <v>5</v>
-      </c>
-      <c r="P13" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>1</v>
-      </c>
-      <c r="R13" s="8">
+        <v>182</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1919,54 +1940,54 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="L14" s="4">
-        <v>-18.8</v>
+        <v>-21.5</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O14" s="23">
-        <v>9</v>
-      </c>
-      <c r="P14" s="19">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>2</v>
-      </c>
-      <c r="R14" s="8">
+        <v>181</v>
+      </c>
+      <c r="O14" s="16">
+        <v>1</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1975,54 +1996,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L15" s="4">
-        <v>-8.300000000000001</v>
+        <v>-13.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="O15" s="23">
-        <v>9</v>
-      </c>
-      <c r="P15" s="19">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="19">
-        <v>3</v>
-      </c>
-      <c r="R15" s="8">
+        <v>181</v>
+      </c>
+      <c r="O15" s="16">
+        <v>1</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2031,114 +2052,282 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="4">
+        <v>-22.6</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O16" s="10">
+        <v>22</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-24</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="I17" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-23.1</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O17" s="10">
+        <v>21</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>30</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-17.2</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="O18" s="16">
+        <v>16</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>25</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O16" s="23">
-        <v>6</v>
-      </c>
-      <c r="P16" s="19">
-        <v>6</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0</v>
+      <c r="K19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-23.5</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="O19" s="6">
+        <v>80</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>65</v>
+      </c>
+      <c r="R19" s="19">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A16">
+  <conditionalFormatting sqref="A2:A19">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B16">
+  <conditionalFormatting sqref="B2:B19">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C16">
+  <conditionalFormatting sqref="C2:C19">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D16">
+  <conditionalFormatting sqref="D2:D19">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E19">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F16">
+  <conditionalFormatting sqref="F2:F19">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G16">
+  <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H16">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I16">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J16">
+  <conditionalFormatting sqref="J2:J19">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K16">
+  <conditionalFormatting sqref="K2:K19">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
+  <conditionalFormatting sqref="L2:L19">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2157,12 +2346,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M19">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N19">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2179,22 +2368,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O16">
+  <conditionalFormatting sqref="O2:O19">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
+  <conditionalFormatting sqref="P2:P19">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
+  <conditionalFormatting sqref="Q2:Q19">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R16">
+  <conditionalFormatting sqref="R2:R19">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="198">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260427--01</t>
-  </si>
-  <si>
-    <t>20260427--02</t>
-  </si>
-  <si>
     <t>20260428--01</t>
   </si>
   <si>
@@ -124,13 +118,19 @@
     <t>20260503--02</t>
   </si>
   <si>
-    <t>03:14</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>00:36</t>
+    <t>20260504--01</t>
+  </si>
+  <si>
+    <t>20260504--02</t>
+  </si>
+  <si>
+    <t>20260504--03</t>
+  </si>
+  <si>
+    <t>20260504--04</t>
+  </si>
+  <si>
+    <t>00:35</t>
   </si>
   <si>
     <t>05:52</t>
@@ -148,7 +148,7 @@
     <t>06:16</t>
   </si>
   <si>
-    <t>04:45</t>
+    <t>04:44</t>
   </si>
   <si>
     <t>06:13</t>
@@ -160,13 +160,13 @@
     <t>04:00</t>
   </si>
   <si>
-    <t>06:08</t>
+    <t>06:07</t>
   </si>
   <si>
     <t>06:04</t>
   </si>
   <si>
-    <t>02:51</t>
+    <t>02:50</t>
   </si>
   <si>
     <t>05:59</t>
@@ -178,12 +178,21 @@
     <t>05:47</t>
   </si>
   <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>04:29</t>
-  </si>
-  <si>
     <t>02:47</t>
   </si>
   <si>
@@ -193,7 +202,7 @@
     <t>05:20</t>
   </si>
   <si>
-    <t>03:38</t>
+    <t>03:39</t>
   </si>
   <si>
     <t>01:53</t>
@@ -208,10 +217,7 @@
     <t>02:00</t>
   </si>
   <si>
-    <t>00:39:24</t>
-  </si>
-  <si>
-    <t>02:15:47</t>
+    <t>03:01</t>
   </si>
   <si>
     <t>23:57:09</t>
@@ -232,40 +238,46 @@
     <t>01:44:58</t>
   </si>
   <si>
-    <t>23:25:28</t>
-  </si>
-  <si>
-    <t>01:02:11</t>
-  </si>
-  <si>
-    <t>02:39:30</t>
-  </si>
-  <si>
-    <t>22:42:49</t>
-  </si>
-  <si>
-    <t>00:19:21</t>
-  </si>
-  <si>
-    <t>01:56:36</t>
-  </si>
-  <si>
-    <t>22:00:10</t>
-  </si>
-  <si>
-    <t>23:36:28</t>
-  </si>
-  <si>
-    <t>01:13:38</t>
-  </si>
-  <si>
-    <t>22:53:32</t>
-  </si>
-  <si>
-    <t>00:42:27</t>
-  </si>
-  <si>
-    <t>02:18:05</t>
+    <t>23:25:27</t>
+  </si>
+  <si>
+    <t>01:02:10</t>
+  </si>
+  <si>
+    <t>02:39:29</t>
+  </si>
+  <si>
+    <t>22:42:48</t>
+  </si>
+  <si>
+    <t>00:19:20</t>
+  </si>
+  <si>
+    <t>01:56:34</t>
+  </si>
+  <si>
+    <t>22:00:08</t>
+  </si>
+  <si>
+    <t>23:36:26</t>
+  </si>
+  <si>
+    <t>01:13:36</t>
+  </si>
+  <si>
+    <t>22:53:29</t>
+  </si>
+  <si>
+    <t>00:30:34</t>
+  </si>
+  <si>
+    <t>02:08:02</t>
+  </si>
+  <si>
+    <t>22:10:30</t>
+  </si>
+  <si>
+    <t>23:47:28</t>
   </si>
   <si>
     <t>00:01:33</t>
@@ -289,37 +301,43 @@
     <t>23:28:03</t>
   </si>
   <si>
-    <t>01:04:27</t>
-  </si>
-  <si>
-    <t>02:41:50</t>
-  </si>
-  <si>
-    <t>22:45:37</t>
-  </si>
-  <si>
-    <t>00:21:37</t>
-  </si>
-  <si>
-    <t>01:58:53</t>
-  </si>
-  <si>
-    <t>22:03:20</t>
-  </si>
-  <si>
-    <t>23:38:46</t>
-  </si>
-  <si>
-    <t>01:15:54</t>
-  </si>
-  <si>
-    <t>22:55:53</t>
-  </si>
-  <si>
-    <t>00:44:04</t>
-  </si>
-  <si>
-    <t>02:21:06</t>
+    <t>01:04:26</t>
+  </si>
+  <si>
+    <t>02:41:49</t>
+  </si>
+  <si>
+    <t>22:45:36</t>
+  </si>
+  <si>
+    <t>00:21:36</t>
+  </si>
+  <si>
+    <t>01:58:52</t>
+  </si>
+  <si>
+    <t>22:03:19</t>
+  </si>
+  <si>
+    <t>23:38:44</t>
+  </si>
+  <si>
+    <t>01:15:52</t>
+  </si>
+  <si>
+    <t>22:55:50</t>
+  </si>
+  <si>
+    <t>00:32:49</t>
+  </si>
+  <si>
+    <t>02:10:34</t>
+  </si>
+  <si>
+    <t>22:12:55</t>
+  </si>
+  <si>
+    <t>23:49:43</t>
   </si>
   <si>
     <t>01:38:31</t>
@@ -334,46 +352,52 @@
     <t>00:13:10</t>
   </si>
   <si>
-    <t>01:50:21</t>
+    <t>01:50:20</t>
   </si>
   <si>
     <t>23:30:25</t>
   </si>
   <si>
-    <t>01:07:33</t>
-  </si>
-  <si>
-    <t>02:44:47</t>
-  </si>
-  <si>
-    <t>22:47:37</t>
-  </si>
-  <si>
-    <t>00:24:41</t>
-  </si>
-  <si>
-    <t>02:01:55</t>
-  </si>
-  <si>
-    <t>22:04:46</t>
-  </si>
-  <si>
-    <t>23:41:45</t>
-  </si>
-  <si>
-    <t>01:18:59</t>
-  </si>
-  <si>
-    <t>22:58:46</t>
-  </si>
-  <si>
-    <t>00:45:41</t>
-  </si>
-  <si>
-    <t>02:24:08</t>
-  </si>
-  <si>
-    <t>00:02:09</t>
+    <t>01:07:32</t>
+  </si>
+  <si>
+    <t>02:44:46</t>
+  </si>
+  <si>
+    <t>22:47:36</t>
+  </si>
+  <si>
+    <t>00:24:39</t>
+  </si>
+  <si>
+    <t>02:01:54</t>
+  </si>
+  <si>
+    <t>22:04:44</t>
+  </si>
+  <si>
+    <t>23:41:43</t>
+  </si>
+  <si>
+    <t>01:18:57</t>
+  </si>
+  <si>
+    <t>22:58:43</t>
+  </si>
+  <si>
+    <t>00:35:56</t>
+  </si>
+  <si>
+    <t>02:13:04</t>
+  </si>
+  <si>
+    <t>22:15:39</t>
+  </si>
+  <si>
+    <t>23:52:50</t>
+  </si>
+  <si>
+    <t>00:02:08</t>
   </si>
   <si>
     <t>01:41:27</t>
@@ -391,40 +415,46 @@
     <t>01:53:29</t>
   </si>
   <si>
-    <t>23:32:48</t>
-  </si>
-  <si>
-    <t>01:10:40</t>
-  </si>
-  <si>
-    <t>02:47:44</t>
-  </si>
-  <si>
-    <t>22:49:37</t>
-  </si>
-  <si>
-    <t>00:27:45</t>
-  </si>
-  <si>
-    <t>02:04:57</t>
-  </si>
-  <si>
-    <t>22:06:11</t>
-  </si>
-  <si>
-    <t>23:44:45</t>
-  </si>
-  <si>
-    <t>01:22:04</t>
-  </si>
-  <si>
-    <t>23:01:40</t>
-  </si>
-  <si>
-    <t>00:48:45</t>
-  </si>
-  <si>
-    <t>02:26:26</t>
+    <t>23:32:47</t>
+  </si>
+  <si>
+    <t>01:10:39</t>
+  </si>
+  <si>
+    <t>02:47:43</t>
+  </si>
+  <si>
+    <t>22:49:36</t>
+  </si>
+  <si>
+    <t>00:27:43</t>
+  </si>
+  <si>
+    <t>02:04:56</t>
+  </si>
+  <si>
+    <t>22:06:09</t>
+  </si>
+  <si>
+    <t>23:44:43</t>
+  </si>
+  <si>
+    <t>01:22:02</t>
+  </si>
+  <si>
+    <t>23:01:37</t>
+  </si>
+  <si>
+    <t>00:39:03</t>
+  </si>
+  <si>
+    <t>02:15:33</t>
+  </si>
+  <si>
+    <t>22:18:24</t>
+  </si>
+  <si>
+    <t>23:55:58</t>
   </si>
   <si>
     <t>00:05:59</t>
@@ -442,7 +472,7 @@
     <t>00:18:17</t>
   </si>
   <si>
-    <t>01:55:45</t>
+    <t>01:55:44</t>
   </si>
   <si>
     <t>23:35:24</t>
@@ -451,34 +481,40 @@
     <t>01:12:55</t>
   </si>
   <si>
-    <t>02:50:04</t>
-  </si>
-  <si>
-    <t>22:52:26</t>
-  </si>
-  <si>
-    <t>00:30:02</t>
-  </si>
-  <si>
-    <t>02:07:15</t>
-  </si>
-  <si>
-    <t>22:09:22</t>
-  </si>
-  <si>
-    <t>23:47:04</t>
-  </si>
-  <si>
-    <t>01:24:21</t>
-  </si>
-  <si>
-    <t>23:04:01</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>21°</t>
+    <t>02:50:03</t>
+  </si>
+  <si>
+    <t>22:52:25</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>02:07:13</t>
+  </si>
+  <si>
+    <t>22:09:20</t>
+  </si>
+  <si>
+    <t>23:47:02</t>
+  </si>
+  <si>
+    <t>01:24:18</t>
+  </si>
+  <si>
+    <t>23:03:58</t>
+  </si>
+  <si>
+    <t>00:41:18</t>
+  </si>
+  <si>
+    <t>02:18:06</t>
+  </si>
+  <si>
+    <t>22:20:50</t>
+  </si>
+  <si>
+    <t>23:58:13</t>
   </si>
   <si>
     <t>2°</t>
@@ -511,10 +547,10 @@
     <t>1°</t>
   </si>
   <si>
-    <t>00:46:22</t>
-  </si>
-  <si>
-    <t>02:19:39</t>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>18°</t>
   </si>
   <si>
     <t>00:05:24</t>
@@ -532,22 +568,31 @@
     <t>00:16:35</t>
   </si>
   <si>
-    <t>01:49:51</t>
-  </si>
-  <si>
-    <t>01:08:47</t>
-  </si>
-  <si>
-    <t>02:42:03</t>
-  </si>
-  <si>
-    <t>02:01:01</t>
-  </si>
-  <si>
-    <t>23:46:48</t>
-  </si>
-  <si>
-    <t>01:20:04</t>
+    <t>01:49:50</t>
+  </si>
+  <si>
+    <t>01:08:46</t>
+  </si>
+  <si>
+    <t>02:42:02</t>
+  </si>
+  <si>
+    <t>00:27:44</t>
+  </si>
+  <si>
+    <t>02:01:00</t>
+  </si>
+  <si>
+    <t>23:46:46</t>
+  </si>
+  <si>
+    <t>01:20:02</t>
+  </si>
+  <si>
+    <t>00:39:15</t>
+  </si>
+  <si>
+    <t>02:12:32</t>
   </si>
   <si>
     <t>B</t>
@@ -596,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,13 +668,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,31 +698,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,13 +722,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,7 +787,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -787,6 +844,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1190,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1268,55 +1331,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.8</v>
+        <v>-24</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O2" s="6">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
       </c>
       <c r="Q2" s="8">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="R2" s="9">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1324,55 +1387,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="L3" s="4">
-        <v>-12.4</v>
+        <v>-16.8</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O3" s="10">
-        <v>29</v>
+        <v>196</v>
+      </c>
+      <c r="O3" s="6">
+        <v>75</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="11">
-        <v>25</v>
-      </c>
-      <c r="R3" s="12">
-        <v>86</v>
+      <c r="Q3" s="10">
+        <v>17</v>
+      </c>
+      <c r="R3" s="11">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1380,55 +1443,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="L4" s="4">
-        <v>-24</v>
+        <v>-20.3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O4" s="6">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="O4" s="12">
+        <v>47</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
       <c r="Q4" s="13">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="R4" s="14">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1436,55 +1499,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="L5" s="4">
-        <v>-16.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O5" s="6">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="O5" s="15">
+        <v>0</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="15">
-        <v>42</v>
-      </c>
-      <c r="R5" s="14">
-        <v>100</v>
+      <c r="Q5" s="7">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1492,46 +1555,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="L6" s="4">
-        <v>-20.3</v>
+        <v>-22.8</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O6" s="16">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="O6" s="15">
+        <v>2</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1540,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1551,43 +1614,43 @@
         <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="L7" s="4">
-        <v>-10.3</v>
+        <v>-15</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O7" s="16">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="O7" s="15">
+        <v>2</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1596,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1604,55 +1667,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>171</v>
+        <v>74</v>
       </c>
       <c r="L8" s="4">
-        <v>-22.8</v>
+        <v>-24</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O8" s="16">
+        <v>197</v>
+      </c>
+      <c r="O8" s="12">
+        <v>26</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="16">
         <v>3</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1660,45 +1723,45 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L9" s="4">
-        <v>-15</v>
+        <v>-18.8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O9" s="16">
+        <v>196</v>
+      </c>
+      <c r="O9" s="15">
         <v>3</v>
       </c>
       <c r="P9" s="7">
@@ -1708,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1716,45 +1779,45 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="L10" s="4">
-        <v>-24</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O10" s="16">
+        <v>196</v>
+      </c>
+      <c r="O10" s="15">
         <v>2</v>
       </c>
       <c r="P10" s="7">
@@ -1772,46 +1835,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="L11" s="4">
-        <v>-18.8</v>
+        <v>-24</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O11" s="16">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="O11" s="15">
+        <v>0</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
@@ -1828,46 +1891,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="L12" s="4">
-        <v>-8.300000000000001</v>
+        <v>-21.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O12" s="16">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="O12" s="15">
+        <v>0</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
@@ -1884,46 +1947,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="L13" s="4">
-        <v>-24</v>
+        <v>-13.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O13" s="16">
-        <v>0</v>
+        <v>196</v>
+      </c>
+      <c r="O13" s="15">
+        <v>1</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
@@ -1940,46 +2003,46 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="L14" s="4">
-        <v>-21.5</v>
+        <v>-22.6</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O14" s="16">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="O14" s="15">
+        <v>16</v>
       </c>
       <c r="P14" s="7">
         <v>0</v>
@@ -1987,8 +2050,8 @@
       <c r="Q14" s="7">
         <v>0</v>
       </c>
-      <c r="R14" s="7">
-        <v>0</v>
+      <c r="R14" s="10">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1996,46 +2059,46 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L15" s="4">
-        <v>-13.1</v>
+        <v>-23.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O15" s="16">
-        <v>1</v>
+        <v>197</v>
+      </c>
+      <c r="O15" s="12">
+        <v>26</v>
       </c>
       <c r="P15" s="7">
         <v>0</v>
@@ -2043,8 +2106,8 @@
       <c r="Q15" s="7">
         <v>0</v>
       </c>
-      <c r="R15" s="7">
-        <v>0</v>
+      <c r="R15" s="17">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2052,46 +2115,46 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="L16" s="4">
-        <v>-22.6</v>
+        <v>-17.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O16" s="10">
-        <v>22</v>
+        <v>196</v>
+      </c>
+      <c r="O16" s="6">
+        <v>57</v>
       </c>
       <c r="P16" s="7">
         <v>0</v>
@@ -2099,8 +2162,8 @@
       <c r="Q16" s="7">
         <v>0</v>
       </c>
-      <c r="R16" s="7">
-        <v>0</v>
+      <c r="R16" s="18">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2108,55 +2171,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="L17" s="4">
-        <v>-23.1</v>
+        <v>-23.5</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O17" s="10">
-        <v>21</v>
-      </c>
-      <c r="P17" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="O17" s="6">
+        <v>100</v>
+      </c>
+      <c r="P17" s="19">
+        <v>32</v>
+      </c>
+      <c r="Q17" s="20">
+        <v>59</v>
+      </c>
+      <c r="R17" s="21">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2164,55 +2227,43 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="L18" s="4">
-        <v>-17.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O18" s="16">
-        <v>16</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>0</v>
-      </c>
-      <c r="R18" s="17">
-        <v>4</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2220,114 +2271,190 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="L19" s="4">
-        <v>-23.5</v>
+        <v>-11.3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="O19" s="6">
-        <v>80</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="18">
-        <v>65</v>
-      </c>
-      <c r="R19" s="19">
-        <v>80</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>22</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-22.4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="2">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-22.2</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A19">
+  <conditionalFormatting sqref="A2:A21">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B19">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C19">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19">
+  <conditionalFormatting sqref="D2:D21">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E19">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F19">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H21">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I21">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K21">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2346,12 +2473,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N21">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2368,22 +2495,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O19">
+  <conditionalFormatting sqref="O2:O21">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P19">
+  <conditionalFormatting sqref="P2:P21">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q19">
+  <conditionalFormatting sqref="Q2:Q21">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R21">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260428--01</t>
-  </si>
-  <si>
-    <t>20260428--02</t>
-  </si>
-  <si>
     <t>20260429--01</t>
   </si>
   <si>
@@ -130,13 +124,16 @@
     <t>20260504--04</t>
   </si>
   <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>05:52</t>
-  </si>
-  <si>
-    <t>05:37</t>
+    <t>20260505--01</t>
+  </si>
+  <si>
+    <t>20260505--02</t>
+  </si>
+  <si>
+    <t>20260505--03</t>
+  </si>
+  <si>
+    <t>05:36</t>
   </si>
   <si>
     <t>06:17</t>
@@ -154,10 +151,10 @@
     <t>06:13</t>
   </si>
   <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>04:00</t>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:01</t>
   </si>
   <si>
     <t>06:07</t>
@@ -166,7 +163,7 @@
     <t>06:04</t>
   </si>
   <si>
-    <t>02:50</t>
+    <t>02:52</t>
   </si>
   <si>
     <t>05:59</t>
@@ -184,24 +181,27 @@
     <t>04:59</t>
   </si>
   <si>
-    <t>05:29</t>
+    <t>05:30</t>
   </si>
   <si>
     <t>06:15</t>
   </si>
   <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:06</t>
+  </si>
+  <si>
+    <t>01:03</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>02:47</t>
-  </si>
-  <si>
-    <t>01:03</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
     <t>03:39</t>
   </si>
   <si>
@@ -211,339 +211,357 @@
     <t>05:41</t>
   </si>
   <si>
-    <t>03:56</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>03:01</t>
-  </si>
-  <si>
-    <t>23:57:09</t>
-  </si>
-  <si>
-    <t>01:33:15</t>
-  </si>
-  <si>
-    <t>00:50:41</t>
-  </si>
-  <si>
-    <t>02:27:42</t>
-  </si>
-  <si>
-    <t>00:08:05</t>
-  </si>
-  <si>
-    <t>01:44:58</t>
-  </si>
-  <si>
-    <t>23:25:27</t>
-  </si>
-  <si>
-    <t>01:02:10</t>
-  </si>
-  <si>
-    <t>02:39:29</t>
-  </si>
-  <si>
-    <t>22:42:48</t>
-  </si>
-  <si>
-    <t>00:19:20</t>
-  </si>
-  <si>
-    <t>01:56:34</t>
-  </si>
-  <si>
-    <t>22:00:08</t>
-  </si>
-  <si>
-    <t>23:36:26</t>
-  </si>
-  <si>
-    <t>01:13:36</t>
-  </si>
-  <si>
-    <t>22:53:29</t>
-  </si>
-  <si>
-    <t>00:30:34</t>
-  </si>
-  <si>
-    <t>02:08:02</t>
-  </si>
-  <si>
-    <t>22:10:30</t>
-  </si>
-  <si>
-    <t>23:47:28</t>
-  </si>
-  <si>
-    <t>00:01:33</t>
-  </si>
-  <si>
-    <t>01:35:35</t>
-  </si>
-  <si>
-    <t>00:53:04</t>
-  </si>
-  <si>
-    <t>02:29:57</t>
-  </si>
-  <si>
-    <t>00:10:33</t>
-  </si>
-  <si>
-    <t>01:47:13</t>
-  </si>
-  <si>
-    <t>23:28:03</t>
-  </si>
-  <si>
-    <t>01:04:26</t>
-  </si>
-  <si>
-    <t>02:41:49</t>
-  </si>
-  <si>
-    <t>22:45:36</t>
-  </si>
-  <si>
-    <t>00:21:36</t>
-  </si>
-  <si>
-    <t>01:58:52</t>
-  </si>
-  <si>
-    <t>22:03:19</t>
-  </si>
-  <si>
-    <t>23:38:44</t>
-  </si>
-  <si>
-    <t>01:15:52</t>
-  </si>
-  <si>
-    <t>22:55:50</t>
-  </si>
-  <si>
-    <t>00:32:49</t>
-  </si>
-  <si>
-    <t>02:10:34</t>
-  </si>
-  <si>
-    <t>22:12:55</t>
-  </si>
-  <si>
-    <t>23:49:43</t>
-  </si>
-  <si>
-    <t>01:38:31</t>
-  </si>
-  <si>
-    <t>00:55:52</t>
-  </si>
-  <si>
-    <t>02:33:05</t>
-  </si>
-  <si>
-    <t>00:13:10</t>
-  </si>
-  <si>
-    <t>01:50:20</t>
-  </si>
-  <si>
-    <t>23:30:25</t>
-  </si>
-  <si>
-    <t>01:07:32</t>
-  </si>
-  <si>
-    <t>02:44:46</t>
-  </si>
-  <si>
-    <t>22:47:36</t>
-  </si>
-  <si>
-    <t>00:24:39</t>
-  </si>
-  <si>
-    <t>02:01:54</t>
-  </si>
-  <si>
-    <t>22:04:44</t>
-  </si>
-  <si>
-    <t>23:41:43</t>
-  </si>
-  <si>
-    <t>01:18:57</t>
-  </si>
-  <si>
-    <t>22:58:43</t>
-  </si>
-  <si>
-    <t>00:35:56</t>
-  </si>
-  <si>
-    <t>02:13:04</t>
-  </si>
-  <si>
-    <t>22:15:39</t>
-  </si>
-  <si>
-    <t>23:52:50</t>
-  </si>
-  <si>
-    <t>00:02:08</t>
-  </si>
-  <si>
-    <t>01:41:27</t>
-  </si>
-  <si>
-    <t>00:58:41</t>
-  </si>
-  <si>
-    <t>02:36:14</t>
-  </si>
-  <si>
-    <t>00:15:48</t>
-  </si>
-  <si>
-    <t>01:53:29</t>
-  </si>
-  <si>
-    <t>23:32:47</t>
-  </si>
-  <si>
-    <t>01:10:39</t>
-  </si>
-  <si>
-    <t>02:47:43</t>
-  </si>
-  <si>
-    <t>22:49:36</t>
-  </si>
-  <si>
-    <t>00:27:43</t>
-  </si>
-  <si>
-    <t>02:04:56</t>
-  </si>
-  <si>
-    <t>22:06:09</t>
-  </si>
-  <si>
-    <t>23:44:43</t>
-  </si>
-  <si>
-    <t>01:22:02</t>
-  </si>
-  <si>
-    <t>23:01:37</t>
-  </si>
-  <si>
-    <t>00:39:03</t>
-  </si>
-  <si>
-    <t>02:15:33</t>
-  </si>
-  <si>
-    <t>22:18:24</t>
-  </si>
-  <si>
-    <t>23:55:58</t>
-  </si>
-  <si>
-    <t>00:05:59</t>
-  </si>
-  <si>
-    <t>01:43:48</t>
-  </si>
-  <si>
-    <t>01:01:05</t>
-  </si>
-  <si>
-    <t>02:38:29</t>
-  </si>
-  <si>
-    <t>00:18:17</t>
-  </si>
-  <si>
-    <t>01:55:44</t>
-  </si>
-  <si>
-    <t>23:35:24</t>
-  </si>
-  <si>
-    <t>01:12:55</t>
-  </si>
-  <si>
-    <t>02:50:03</t>
-  </si>
-  <si>
-    <t>22:52:25</t>
-  </si>
-  <si>
-    <t>00:30:00</t>
-  </si>
-  <si>
-    <t>02:07:13</t>
-  </si>
-  <si>
-    <t>22:09:20</t>
-  </si>
-  <si>
-    <t>23:47:02</t>
-  </si>
-  <si>
-    <t>01:24:18</t>
-  </si>
-  <si>
-    <t>23:03:58</t>
-  </si>
-  <si>
-    <t>00:41:18</t>
-  </si>
-  <si>
-    <t>02:18:06</t>
-  </si>
-  <si>
-    <t>22:20:50</t>
-  </si>
-  <si>
-    <t>23:58:13</t>
-  </si>
-  <si>
-    <t>2°</t>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>02:01</t>
+  </si>
+  <si>
+    <t>03:02</t>
+  </si>
+  <si>
+    <t>00:42</t>
+  </si>
+  <si>
+    <t>00:50:42</t>
+  </si>
+  <si>
+    <t>02:27:43</t>
+  </si>
+  <si>
+    <t>00:08:08</t>
+  </si>
+  <si>
+    <t>01:45:01</t>
+  </si>
+  <si>
+    <t>23:25:33</t>
+  </si>
+  <si>
+    <t>01:02:16</t>
+  </si>
+  <si>
+    <t>02:39:36</t>
+  </si>
+  <si>
+    <t>22:42:57</t>
+  </si>
+  <si>
+    <t>00:19:29</t>
+  </si>
+  <si>
+    <t>01:56:45</t>
+  </si>
+  <si>
+    <t>22:00:22</t>
+  </si>
+  <si>
+    <t>23:36:40</t>
+  </si>
+  <si>
+    <t>01:13:51</t>
+  </si>
+  <si>
+    <t>22:53:49</t>
+  </si>
+  <si>
+    <t>00:30:54</t>
+  </si>
+  <si>
+    <t>02:08:22</t>
+  </si>
+  <si>
+    <t>22:10:57</t>
+  </si>
+  <si>
+    <t>23:47:55</t>
+  </si>
+  <si>
+    <t>01:25:19</t>
+  </si>
+  <si>
+    <t>21:28:03</t>
+  </si>
+  <si>
+    <t>23:04:53</t>
+  </si>
+  <si>
+    <t>00:53:06</t>
+  </si>
+  <si>
+    <t>02:29:58</t>
+  </si>
+  <si>
+    <t>00:10:36</t>
+  </si>
+  <si>
+    <t>01:47:16</t>
+  </si>
+  <si>
+    <t>23:28:09</t>
+  </si>
+  <si>
+    <t>01:04:32</t>
+  </si>
+  <si>
+    <t>02:41:56</t>
+  </si>
+  <si>
+    <t>22:45:45</t>
+  </si>
+  <si>
+    <t>00:21:46</t>
+  </si>
+  <si>
+    <t>01:59:02</t>
+  </si>
+  <si>
+    <t>22:03:32</t>
+  </si>
+  <si>
+    <t>23:38:58</t>
+  </si>
+  <si>
+    <t>01:16:07</t>
+  </si>
+  <si>
+    <t>22:56:10</t>
+  </si>
+  <si>
+    <t>00:33:09</t>
+  </si>
+  <si>
+    <t>02:10:55</t>
+  </si>
+  <si>
+    <t>22:13:21</t>
+  </si>
+  <si>
+    <t>23:50:10</t>
+  </si>
+  <si>
+    <t>01:27:46</t>
+  </si>
+  <si>
+    <t>21:30:33</t>
+  </si>
+  <si>
+    <t>23:07:08</t>
+  </si>
+  <si>
+    <t>00:55:53</t>
+  </si>
+  <si>
+    <t>02:33:06</t>
+  </si>
+  <si>
+    <t>00:13:13</t>
+  </si>
+  <si>
+    <t>01:50:24</t>
+  </si>
+  <si>
+    <t>23:30:31</t>
+  </si>
+  <si>
+    <t>01:07:38</t>
+  </si>
+  <si>
+    <t>02:44:52</t>
+  </si>
+  <si>
+    <t>22:47:45</t>
+  </si>
+  <si>
+    <t>00:24:49</t>
+  </si>
+  <si>
+    <t>02:02:04</t>
+  </si>
+  <si>
+    <t>22:04:58</t>
+  </si>
+  <si>
+    <t>23:41:57</t>
+  </si>
+  <si>
+    <t>01:19:12</t>
+  </si>
+  <si>
+    <t>22:59:03</t>
+  </si>
+  <si>
+    <t>00:36:16</t>
+  </si>
+  <si>
+    <t>02:13:24</t>
+  </si>
+  <si>
+    <t>22:16:06</t>
+  </si>
+  <si>
+    <t>23:53:17</t>
+  </si>
+  <si>
+    <t>01:30:28</t>
+  </si>
+  <si>
+    <t>21:33:06</t>
+  </si>
+  <si>
+    <t>23:10:15</t>
+  </si>
+  <si>
+    <t>00:58:42</t>
+  </si>
+  <si>
+    <t>02:36:15</t>
+  </si>
+  <si>
+    <t>00:15:51</t>
+  </si>
+  <si>
+    <t>01:53:32</t>
+  </si>
+  <si>
+    <t>23:32:53</t>
+  </si>
+  <si>
+    <t>01:10:45</t>
+  </si>
+  <si>
+    <t>02:47:49</t>
+  </si>
+  <si>
+    <t>22:49:46</t>
+  </si>
+  <si>
+    <t>00:27:53</t>
+  </si>
+  <si>
+    <t>02:05:06</t>
+  </si>
+  <si>
+    <t>22:06:24</t>
+  </si>
+  <si>
+    <t>23:44:57</t>
+  </si>
+  <si>
+    <t>01:22:17</t>
+  </si>
+  <si>
+    <t>23:01:57</t>
+  </si>
+  <si>
+    <t>00:39:23</t>
+  </si>
+  <si>
+    <t>02:15:54</t>
+  </si>
+  <si>
+    <t>22:18:51</t>
+  </si>
+  <si>
+    <t>23:56:25</t>
+  </si>
+  <si>
+    <t>01:33:10</t>
+  </si>
+  <si>
+    <t>21:35:39</t>
+  </si>
+  <si>
+    <t>23:13:22</t>
+  </si>
+  <si>
+    <t>01:01:06</t>
+  </si>
+  <si>
+    <t>02:38:30</t>
+  </si>
+  <si>
+    <t>00:18:20</t>
+  </si>
+  <si>
+    <t>01:55:48</t>
+  </si>
+  <si>
+    <t>23:35:30</t>
+  </si>
+  <si>
+    <t>01:13:01</t>
+  </si>
+  <si>
+    <t>02:50:09</t>
+  </si>
+  <si>
+    <t>22:52:35</t>
+  </si>
+  <si>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>02:07:24</t>
+  </si>
+  <si>
+    <t>22:09:35</t>
+  </si>
+  <si>
+    <t>23:47:16</t>
+  </si>
+  <si>
+    <t>01:24:33</t>
+  </si>
+  <si>
+    <t>23:04:18</t>
+  </si>
+  <si>
+    <t>00:41:39</t>
+  </si>
+  <si>
+    <t>02:18:26</t>
+  </si>
+  <si>
+    <t>22:21:16</t>
+  </si>
+  <si>
+    <t>23:58:40</t>
+  </si>
+  <si>
+    <t>01:35:36</t>
+  </si>
+  <si>
+    <t>21:38:10</t>
+  </si>
+  <si>
+    <t>23:15:37</t>
+  </si>
+  <si>
+    <t>16°</t>
+  </si>
+  <si>
+    <t>6°</t>
+  </si>
+  <si>
+    <t>30°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>11°</t>
+  </si>
+  <si>
+    <t>10°</t>
   </si>
   <si>
     <t>25°</t>
   </si>
   <si>
-    <t>16°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>30°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
@@ -553,61 +571,58 @@
     <t>18°</t>
   </si>
   <si>
-    <t>00:05:24</t>
-  </si>
-  <si>
-    <t>01:38:40</t>
-  </si>
-  <si>
-    <t>00:57:38</t>
-  </si>
-  <si>
-    <t>02:30:54</t>
-  </si>
-  <si>
-    <t>00:16:35</t>
-  </si>
-  <si>
-    <t>01:49:50</t>
-  </si>
-  <si>
-    <t>01:08:46</t>
-  </si>
-  <si>
-    <t>02:42:02</t>
-  </si>
-  <si>
-    <t>00:27:44</t>
-  </si>
-  <si>
-    <t>02:01:00</t>
-  </si>
-  <si>
-    <t>23:46:46</t>
-  </si>
-  <si>
-    <t>01:20:02</t>
-  </si>
-  <si>
-    <t>00:39:15</t>
-  </si>
-  <si>
-    <t>02:12:32</t>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>00:57:39</t>
+  </si>
+  <si>
+    <t>02:30:55</t>
+  </si>
+  <si>
+    <t>00:16:37</t>
+  </si>
+  <si>
+    <t>01:49:53</t>
+  </si>
+  <si>
+    <t>01:08:52</t>
+  </si>
+  <si>
+    <t>02:42:08</t>
+  </si>
+  <si>
+    <t>02:01:09</t>
+  </si>
+  <si>
+    <t>23:47:00</t>
+  </si>
+  <si>
+    <t>01:20:16</t>
+  </si>
+  <si>
+    <t>00:39:34</t>
+  </si>
+  <si>
+    <t>02:12:52</t>
+  </si>
+  <si>
+    <t>01:32:28</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -641,7 +656,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,43 +683,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +707,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,19 +761,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -787,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -850,6 +895,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1331,55 +1391,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L2" s="4">
-        <v>-24</v>
+        <v>-20.3</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="O2" s="6">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="8">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="R2" s="9">
-        <v>89</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1387,55 +1447,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L3" s="4">
-        <v>-16.8</v>
+        <v>-10.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O3" s="6">
-        <v>75</v>
+        <v>200</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>17</v>
+      <c r="Q3" s="11">
+        <v>3</v>
       </c>
       <c r="R3" s="11">
-        <v>78</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1443,55 +1503,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L4" s="4">
-        <v>-20.3</v>
+        <v>-22.8</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O4" s="12">
-        <v>47</v>
+        <v>201</v>
+      </c>
+      <c r="O4" s="10">
+        <v>1</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="13">
-        <v>47</v>
-      </c>
-      <c r="R4" s="14">
-        <v>33</v>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1502,43 +1562,43 @@
         <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L5" s="4">
-        <v>-10.3</v>
+        <v>-15</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O5" s="15">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="O5" s="10">
+        <v>3</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1546,8 +1606,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1555,46 +1615,46 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="L6" s="4">
-        <v>-22.8</v>
+        <v>-24</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O6" s="15">
-        <v>2</v>
+        <v>201</v>
+      </c>
+      <c r="O6" s="12">
+        <v>29</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1602,8 +1662,8 @@
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="7">
-        <v>2</v>
+      <c r="R6" s="13">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1611,46 +1671,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="L7" s="4">
-        <v>-15</v>
+        <v>-18.8</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O7" s="15">
-        <v>2</v>
+        <v>200</v>
+      </c>
+      <c r="O7" s="12">
+        <v>33</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1658,8 +1718,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>2</v>
+      <c r="R7" s="14">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1667,46 +1727,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="L8" s="4">
-        <v>-24</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="O8" s="12">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -1714,8 +1774,8 @@
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="16">
-        <v>3</v>
+      <c r="R8" s="9">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1723,46 +1783,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-18.8</v>
+        <v>-24</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O9" s="15">
-        <v>3</v>
+        <v>201</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
@@ -1779,45 +1839,45 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="L10" s="4">
-        <v>-8.300000000000001</v>
+        <v>-21.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O10" s="15">
+        <v>200</v>
+      </c>
+      <c r="O10" s="10">
         <v>2</v>
       </c>
       <c r="P10" s="7">
@@ -1827,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1835,46 +1895,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="L11" s="4">
-        <v>-24</v>
+        <v>-13.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O11" s="15">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="O11" s="10">
+        <v>2</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
@@ -1891,46 +1951,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-21.5</v>
+        <v>-22.6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O12" s="15">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="O12" s="12">
+        <v>38</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
@@ -1938,8 +1998,8 @@
       <c r="Q12" s="7">
         <v>0</v>
       </c>
-      <c r="R12" s="7">
-        <v>0</v>
+      <c r="R12" s="11">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1947,46 +2007,46 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="L13" s="4">
-        <v>-13.1</v>
+        <v>-23.1</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="O13" s="15">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="O13" s="12">
+        <v>31</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
@@ -2003,46 +2063,46 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="L14" s="4">
-        <v>-22.6</v>
+        <v>-17.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O14" s="15">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="O14" s="10">
+        <v>17</v>
       </c>
       <c r="P14" s="7">
         <v>0</v>
@@ -2050,8 +2110,8 @@
       <c r="Q14" s="7">
         <v>0</v>
       </c>
-      <c r="R14" s="10">
-        <v>16</v>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2059,55 +2119,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="L15" s="4">
-        <v>-23.1</v>
+        <v>-23.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O15" s="12">
-        <v>26</v>
-      </c>
-      <c r="P15" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>26</v>
+        <v>201</v>
+      </c>
+      <c r="O15" s="6">
+        <v>70</v>
+      </c>
+      <c r="P15" s="8">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>70</v>
+      </c>
+      <c r="R15" s="16">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2115,55 +2175,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="L16" s="4">
-        <v>-17.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O16" s="6">
-        <v>57</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0</v>
-      </c>
-      <c r="R16" s="18">
-        <v>57</v>
+        <v>92</v>
+      </c>
+      <c r="P16" s="17">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>92</v>
+      </c>
+      <c r="R16" s="19">
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2171,55 +2231,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L17" s="4">
+        <v>-11.3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O17" s="6">
+        <v>97</v>
+      </c>
+      <c r="P17" s="20">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>91</v>
+      </c>
+      <c r="R17" s="21">
         <v>83</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-23.5</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O17" s="6">
-        <v>100</v>
-      </c>
-      <c r="P17" s="19">
-        <v>32</v>
-      </c>
-      <c r="Q17" s="20">
-        <v>59</v>
-      </c>
-      <c r="R17" s="21">
-        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2227,43 +2287,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>177</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="L18" s="4">
-        <v>-20.2</v>
+        <v>-22.4</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
+      </c>
+      <c r="O18" s="6">
+        <v>99</v>
+      </c>
+      <c r="P18" s="22">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>18</v>
+      </c>
+      <c r="R18" s="23">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2271,43 +2343,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-22.2</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O19" s="6">
+        <v>82</v>
+      </c>
+      <c r="P19" s="22">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>17</v>
+      </c>
+      <c r="R19" s="24">
         <v>67</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="L19" s="4">
-        <v>-11.3</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2315,43 +2399,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="L20" s="4">
-        <v>-22.4</v>
+        <v>-15.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
+      </c>
+      <c r="O20" s="6">
+        <v>62</v>
+      </c>
+      <c r="P20" s="25">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>16</v>
+      </c>
+      <c r="R20" s="22">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2359,102 +2455,170 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O21" s="6">
+        <v>92</v>
+      </c>
+      <c r="P21" s="14">
+        <v>34</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>60</v>
+      </c>
+      <c r="R21" s="16">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="2">
         <v>32</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L21" s="4">
-        <v>-22.2</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>197</v>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" s="4">
+        <v>-22.9</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O22" s="6">
+        <v>93</v>
+      </c>
+      <c r="P22" s="16">
+        <v>48</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>64</v>
+      </c>
+      <c r="R22" s="20">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A21">
+  <conditionalFormatting sqref="A2:A22">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B22">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C22">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D21">
+  <conditionalFormatting sqref="D2:D22">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E22">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F22">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G22">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I21">
+  <conditionalFormatting sqref="I2:I22">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
+  <conditionalFormatting sqref="J2:J22">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K21">
+  <conditionalFormatting sqref="K2:K22">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="L2:L22">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2473,12 +2637,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="M2:M22">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="N2:N22">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2495,22 +2659,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="O2:O22">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="P2:P22">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q21">
+  <conditionalFormatting sqref="Q2:Q22">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="206">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260429--01</t>
-  </si>
-  <si>
-    <t>20260429--02</t>
-  </si>
-  <si>
     <t>20260430--01</t>
   </si>
   <si>
@@ -133,10 +127,13 @@
     <t>20260505--03</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
-    <t>06:17</t>
+    <t>20260506--01</t>
+  </si>
+  <si>
+    <t>20260506--02</t>
+  </si>
+  <si>
+    <t>20260506--03</t>
   </si>
   <si>
     <t>05:15</t>
@@ -145,13 +142,13 @@
     <t>06:16</t>
   </si>
   <si>
-    <t>04:44</t>
+    <t>04:45</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>05:53</t>
+    <t>05:54</t>
   </si>
   <si>
     <t>04:01</t>
@@ -166,7 +163,7 @@
     <t>02:52</t>
   </si>
   <si>
-    <t>05:59</t>
+    <t>06:00</t>
   </si>
   <si>
     <t>06:10</t>
@@ -190,19 +187,22 @@
     <t>05:24</t>
   </si>
   <si>
-    <t>05:06</t>
-  </si>
-  <si>
-    <t>01:03</t>
-  </si>
-  <si>
-    <t>05:20</t>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>04:32</t>
+  </si>
+  <si>
+    <t>06:11</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:39</t>
+    <t>03:38</t>
   </si>
   <si>
     <t>01:53</t>
@@ -223,73 +223,70 @@
     <t>00:42</t>
   </si>
   <si>
-    <t>00:50:42</t>
-  </si>
-  <si>
-    <t>02:27:43</t>
-  </si>
-  <si>
     <t>00:08:08</t>
   </si>
   <si>
     <t>01:45:01</t>
   </si>
   <si>
-    <t>23:25:33</t>
-  </si>
-  <si>
-    <t>01:02:16</t>
-  </si>
-  <si>
-    <t>02:39:36</t>
-  </si>
-  <si>
-    <t>22:42:57</t>
-  </si>
-  <si>
-    <t>00:19:29</t>
-  </si>
-  <si>
-    <t>01:56:45</t>
-  </si>
-  <si>
-    <t>22:00:22</t>
-  </si>
-  <si>
-    <t>23:36:40</t>
-  </si>
-  <si>
-    <t>01:13:51</t>
-  </si>
-  <si>
-    <t>22:53:49</t>
-  </si>
-  <si>
-    <t>00:30:54</t>
-  </si>
-  <si>
-    <t>02:08:22</t>
-  </si>
-  <si>
-    <t>22:10:57</t>
-  </si>
-  <si>
-    <t>23:47:55</t>
-  </si>
-  <si>
-    <t>01:25:19</t>
-  </si>
-  <si>
-    <t>21:28:03</t>
-  </si>
-  <si>
-    <t>23:04:53</t>
-  </si>
-  <si>
-    <t>00:53:06</t>
-  </si>
-  <si>
-    <t>02:29:58</t>
+    <t>23:25:34</t>
+  </si>
+  <si>
+    <t>01:02:17</t>
+  </si>
+  <si>
+    <t>02:39:37</t>
+  </si>
+  <si>
+    <t>22:42:59</t>
+  </si>
+  <si>
+    <t>00:19:31</t>
+  </si>
+  <si>
+    <t>01:56:46</t>
+  </si>
+  <si>
+    <t>22:00:25</t>
+  </si>
+  <si>
+    <t>23:36:43</t>
+  </si>
+  <si>
+    <t>01:13:54</t>
+  </si>
+  <si>
+    <t>22:53:54</t>
+  </si>
+  <si>
+    <t>00:30:59</t>
+  </si>
+  <si>
+    <t>02:08:27</t>
+  </si>
+  <si>
+    <t>22:11:04</t>
+  </si>
+  <si>
+    <t>23:48:02</t>
+  </si>
+  <si>
+    <t>01:25:26</t>
+  </si>
+  <si>
+    <t>21:28:12</t>
+  </si>
+  <si>
+    <t>23:05:02</t>
+  </si>
+  <si>
+    <t>00:42:23</t>
+  </si>
+  <si>
+    <t>20:45:21</t>
+  </si>
+  <si>
+    <t>22:22:01</t>
   </si>
   <si>
     <t>00:10:36</t>
@@ -301,58 +298,61 @@
     <t>23:28:09</t>
   </si>
   <si>
-    <t>01:04:32</t>
+    <t>01:04:33</t>
   </si>
   <si>
     <t>02:41:56</t>
   </si>
   <si>
-    <t>22:45:45</t>
-  </si>
-  <si>
-    <t>00:21:46</t>
-  </si>
-  <si>
-    <t>01:59:02</t>
-  </si>
-  <si>
-    <t>22:03:32</t>
-  </si>
-  <si>
-    <t>23:38:58</t>
-  </si>
-  <si>
-    <t>01:16:07</t>
-  </si>
-  <si>
-    <t>22:56:10</t>
-  </si>
-  <si>
-    <t>00:33:09</t>
-  </si>
-  <si>
-    <t>02:10:55</t>
-  </si>
-  <si>
-    <t>22:13:21</t>
-  </si>
-  <si>
-    <t>23:50:10</t>
-  </si>
-  <si>
-    <t>01:27:46</t>
-  </si>
-  <si>
-    <t>21:30:33</t>
-  </si>
-  <si>
-    <t>23:07:08</t>
-  </si>
-  <si>
-    <t>00:55:53</t>
-  </si>
-  <si>
-    <t>02:33:06</t>
+    <t>22:45:47</t>
+  </si>
+  <si>
+    <t>00:21:48</t>
+  </si>
+  <si>
+    <t>01:59:04</t>
+  </si>
+  <si>
+    <t>22:03:35</t>
+  </si>
+  <si>
+    <t>23:39:01</t>
+  </si>
+  <si>
+    <t>01:16:10</t>
+  </si>
+  <si>
+    <t>22:56:15</t>
+  </si>
+  <si>
+    <t>00:33:14</t>
+  </si>
+  <si>
+    <t>02:11:00</t>
+  </si>
+  <si>
+    <t>22:13:28</t>
+  </si>
+  <si>
+    <t>23:50:17</t>
+  </si>
+  <si>
+    <t>01:27:53</t>
+  </si>
+  <si>
+    <t>21:30:43</t>
+  </si>
+  <si>
+    <t>23:07:17</t>
+  </si>
+  <si>
+    <t>00:44:45</t>
+  </si>
+  <si>
+    <t>20:48:00</t>
+  </si>
+  <si>
+    <t>22:24:16</t>
   </si>
   <si>
     <t>00:13:13</t>
@@ -364,58 +364,61 @@
     <t>23:30:31</t>
   </si>
   <si>
-    <t>01:07:38</t>
-  </si>
-  <si>
-    <t>02:44:52</t>
-  </si>
-  <si>
-    <t>22:47:45</t>
-  </si>
-  <si>
-    <t>00:24:49</t>
-  </si>
-  <si>
-    <t>02:02:04</t>
-  </si>
-  <si>
-    <t>22:04:58</t>
-  </si>
-  <si>
-    <t>23:41:57</t>
-  </si>
-  <si>
-    <t>01:19:12</t>
-  </si>
-  <si>
-    <t>22:59:03</t>
-  </si>
-  <si>
-    <t>00:36:16</t>
-  </si>
-  <si>
-    <t>02:13:24</t>
-  </si>
-  <si>
-    <t>22:16:06</t>
-  </si>
-  <si>
-    <t>23:53:17</t>
-  </si>
-  <si>
-    <t>01:30:28</t>
-  </si>
-  <si>
-    <t>21:33:06</t>
-  </si>
-  <si>
-    <t>23:10:15</t>
-  </si>
-  <si>
-    <t>00:58:42</t>
-  </si>
-  <si>
-    <t>02:36:15</t>
+    <t>01:07:39</t>
+  </si>
+  <si>
+    <t>02:44:53</t>
+  </si>
+  <si>
+    <t>22:47:47</t>
+  </si>
+  <si>
+    <t>00:24:51</t>
+  </si>
+  <si>
+    <t>02:02:06</t>
+  </si>
+  <si>
+    <t>22:05:01</t>
+  </si>
+  <si>
+    <t>23:42:01</t>
+  </si>
+  <si>
+    <t>01:19:15</t>
+  </si>
+  <si>
+    <t>22:59:08</t>
+  </si>
+  <si>
+    <t>00:36:21</t>
+  </si>
+  <si>
+    <t>02:13:29</t>
+  </si>
+  <si>
+    <t>22:16:13</t>
+  </si>
+  <si>
+    <t>23:53:24</t>
+  </si>
+  <si>
+    <t>01:30:35</t>
+  </si>
+  <si>
+    <t>21:33:15</t>
+  </si>
+  <si>
+    <t>23:10:24</t>
+  </si>
+  <si>
+    <t>00:47:36</t>
+  </si>
+  <si>
+    <t>20:50:16</t>
+  </si>
+  <si>
+    <t>22:27:21</t>
   </si>
   <si>
     <t>00:15:51</t>
@@ -424,61 +427,64 @@
     <t>01:53:32</t>
   </si>
   <si>
-    <t>23:32:53</t>
-  </si>
-  <si>
-    <t>01:10:45</t>
-  </si>
-  <si>
-    <t>02:47:49</t>
-  </si>
-  <si>
-    <t>22:49:46</t>
-  </si>
-  <si>
-    <t>00:27:53</t>
-  </si>
-  <si>
-    <t>02:05:06</t>
-  </si>
-  <si>
-    <t>22:06:24</t>
-  </si>
-  <si>
-    <t>23:44:57</t>
-  </si>
-  <si>
-    <t>01:22:17</t>
-  </si>
-  <si>
-    <t>23:01:57</t>
-  </si>
-  <si>
-    <t>00:39:23</t>
-  </si>
-  <si>
-    <t>02:15:54</t>
-  </si>
-  <si>
-    <t>22:18:51</t>
-  </si>
-  <si>
-    <t>23:56:25</t>
-  </si>
-  <si>
-    <t>01:33:10</t>
-  </si>
-  <si>
-    <t>21:35:39</t>
-  </si>
-  <si>
-    <t>23:13:22</t>
-  </si>
-  <si>
-    <t>01:01:06</t>
-  </si>
-  <si>
-    <t>02:38:30</t>
+    <t>23:32:54</t>
+  </si>
+  <si>
+    <t>01:10:46</t>
+  </si>
+  <si>
+    <t>02:47:50</t>
+  </si>
+  <si>
+    <t>22:49:48</t>
+  </si>
+  <si>
+    <t>00:27:55</t>
+  </si>
+  <si>
+    <t>02:05:08</t>
+  </si>
+  <si>
+    <t>22:06:27</t>
+  </si>
+  <si>
+    <t>23:45:01</t>
+  </si>
+  <si>
+    <t>01:22:20</t>
+  </si>
+  <si>
+    <t>23:02:02</t>
+  </si>
+  <si>
+    <t>00:39:28</t>
+  </si>
+  <si>
+    <t>02:15:59</t>
+  </si>
+  <si>
+    <t>22:18:58</t>
+  </si>
+  <si>
+    <t>23:56:32</t>
+  </si>
+  <si>
+    <t>01:33:17</t>
+  </si>
+  <si>
+    <t>21:35:48</t>
+  </si>
+  <si>
+    <t>23:13:31</t>
+  </si>
+  <si>
+    <t>00:50:28</t>
+  </si>
+  <si>
+    <t>20:52:32</t>
+  </si>
+  <si>
+    <t>22:30:27</t>
   </si>
   <si>
     <t>00:18:20</t>
@@ -490,55 +496,61 @@
     <t>23:35:30</t>
   </si>
   <si>
-    <t>01:13:01</t>
-  </si>
-  <si>
-    <t>02:50:09</t>
-  </si>
-  <si>
-    <t>22:52:35</t>
-  </si>
-  <si>
-    <t>00:30:10</t>
-  </si>
-  <si>
-    <t>02:07:24</t>
-  </si>
-  <si>
-    <t>22:09:35</t>
-  </si>
-  <si>
-    <t>23:47:16</t>
-  </si>
-  <si>
-    <t>01:24:33</t>
-  </si>
-  <si>
-    <t>23:04:18</t>
-  </si>
-  <si>
-    <t>00:41:39</t>
-  </si>
-  <si>
-    <t>02:18:26</t>
-  </si>
-  <si>
-    <t>22:21:16</t>
-  </si>
-  <si>
-    <t>23:58:40</t>
-  </si>
-  <si>
-    <t>01:35:36</t>
-  </si>
-  <si>
-    <t>21:38:10</t>
-  </si>
-  <si>
-    <t>23:15:37</t>
-  </si>
-  <si>
-    <t>16°</t>
+    <t>01:13:02</t>
+  </si>
+  <si>
+    <t>02:50:10</t>
+  </si>
+  <si>
+    <t>22:52:36</t>
+  </si>
+  <si>
+    <t>00:30:12</t>
+  </si>
+  <si>
+    <t>02:07:26</t>
+  </si>
+  <si>
+    <t>22:09:38</t>
+  </si>
+  <si>
+    <t>23:47:19</t>
+  </si>
+  <si>
+    <t>01:24:37</t>
+  </si>
+  <si>
+    <t>23:04:23</t>
+  </si>
+  <si>
+    <t>00:41:44</t>
+  </si>
+  <si>
+    <t>02:18:31</t>
+  </si>
+  <si>
+    <t>22:21:23</t>
+  </si>
+  <si>
+    <t>23:58:47</t>
+  </si>
+  <si>
+    <t>01:35:43</t>
+  </si>
+  <si>
+    <t>21:38:19</t>
+  </si>
+  <si>
+    <t>23:15:47</t>
+  </si>
+  <si>
+    <t>00:52:50</t>
+  </si>
+  <si>
+    <t>20:55:12</t>
+  </si>
+  <si>
+    <t>22:32:43</t>
   </si>
   <si>
     <t>6°</t>
@@ -574,52 +586,49 @@
     <t>14°</t>
   </si>
   <si>
-    <t>00:57:39</t>
-  </si>
-  <si>
-    <t>02:30:55</t>
-  </si>
-  <si>
-    <t>00:16:37</t>
-  </si>
-  <si>
-    <t>01:49:53</t>
-  </si>
-  <si>
-    <t>01:08:52</t>
-  </si>
-  <si>
-    <t>02:42:08</t>
-  </si>
-  <si>
-    <t>02:01:09</t>
-  </si>
-  <si>
-    <t>23:47:00</t>
-  </si>
-  <si>
-    <t>01:20:16</t>
-  </si>
-  <si>
-    <t>00:39:34</t>
-  </si>
-  <si>
-    <t>02:12:52</t>
-  </si>
-  <si>
-    <t>01:32:28</t>
+    <t>00:16:38</t>
+  </si>
+  <si>
+    <t>01:49:54</t>
+  </si>
+  <si>
+    <t>01:08:53</t>
+  </si>
+  <si>
+    <t>02:42:09</t>
+  </si>
+  <si>
+    <t>02:01:11</t>
+  </si>
+  <si>
+    <t>23:47:03</t>
+  </si>
+  <si>
+    <t>01:20:19</t>
+  </si>
+  <si>
+    <t>00:39:39</t>
+  </si>
+  <si>
+    <t>02:12:57</t>
+  </si>
+  <si>
+    <t>01:32:35</t>
+  </si>
+  <si>
+    <t>00:52:40</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
+    <t>3</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -656,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -671,7 +680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,7 +692,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,19 +728,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,7 +764,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,67 +806,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -832,7 +847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -910,6 +925,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1313,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1391,55 +1409,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L2" s="4">
-        <v>-20.3</v>
+        <v>-22.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="O2" s="6">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>20</v>
-      </c>
-      <c r="R2" s="9">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1450,52 +1468,52 @@
         <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L3" s="4">
-        <v>-10.3</v>
+        <v>-15</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="10">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="11">
-        <v>3</v>
-      </c>
-      <c r="R3" s="11">
-        <v>3</v>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1503,10 +1521,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>61</v>
@@ -1515,34 +1533,34 @@
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-22.8</v>
+        <v>-24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O4" s="10">
-        <v>1</v>
+        <v>203</v>
+      </c>
+      <c r="O4" s="6">
+        <v>3</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1551,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1559,55 +1577,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="L5" s="4">
-        <v>-15</v>
+        <v>-18.8</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O5" s="10">
-        <v>3</v>
+        <v>204</v>
+      </c>
+      <c r="O5" s="6">
+        <v>14</v>
       </c>
       <c r="P5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="11">
-        <v>3</v>
+      <c r="R5" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1615,55 +1633,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="L6" s="4">
-        <v>-24</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O6" s="12">
-        <v>29</v>
+        <v>204</v>
+      </c>
+      <c r="O6" s="6">
+        <v>10</v>
       </c>
       <c r="P6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
-        <v>29</v>
+      <c r="R6" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1671,46 +1689,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="L7" s="4">
-        <v>-18.8</v>
+        <v>-24</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O7" s="12">
-        <v>33</v>
+        <v>203</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1718,8 +1736,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="14">
-        <v>33</v>
+      <c r="R7" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1727,46 +1745,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="L8" s="4">
-        <v>-8.300000000000001</v>
+        <v>-21.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O8" s="12">
-        <v>23</v>
+        <v>204</v>
+      </c>
+      <c r="O8" s="6">
+        <v>2</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -1774,8 +1792,8 @@
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="9">
-        <v>23</v>
+      <c r="R8" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1783,46 +1801,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="L9" s="4">
-        <v>-24</v>
+        <v>-13.1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O9" s="10">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="O9" s="6">
+        <v>2</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
@@ -1831,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1839,10 +1857,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>61</v>
@@ -1851,34 +1869,34 @@
         <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="L10" s="4">
-        <v>-21.5</v>
+        <v>-22.6</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O10" s="10">
-        <v>2</v>
+        <v>205</v>
+      </c>
+      <c r="O10" s="6">
+        <v>14</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
@@ -1886,8 +1904,8 @@
       <c r="Q10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="7">
-        <v>1</v>
+      <c r="R10" s="10">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1895,46 +1913,46 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L11" s="4">
-        <v>-13.1</v>
+        <v>-23.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O11" s="10">
-        <v>2</v>
+        <v>203</v>
+      </c>
+      <c r="O11" s="11">
+        <v>37</v>
       </c>
       <c r="P11" s="7">
         <v>0</v>
@@ -1942,8 +1960,8 @@
       <c r="Q11" s="7">
         <v>0</v>
       </c>
-      <c r="R11" s="7">
-        <v>0</v>
+      <c r="R11" s="12">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1951,46 +1969,46 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="L12" s="4">
-        <v>-22.6</v>
+        <v>-17.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="O12" s="12">
-        <v>38</v>
+        <v>204</v>
+      </c>
+      <c r="O12" s="11">
+        <v>44</v>
       </c>
       <c r="P12" s="7">
         <v>0</v>
@@ -1998,8 +2016,8 @@
       <c r="Q12" s="7">
         <v>0</v>
       </c>
-      <c r="R12" s="11">
-        <v>5</v>
+      <c r="R12" s="13">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2007,10 +2025,10 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>61</v>
@@ -2019,43 +2037,43 @@
         <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="L13" s="4">
-        <v>-23.1</v>
+        <v>-23.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O13" s="12">
-        <v>31</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7">
-        <v>0</v>
+        <v>203</v>
+      </c>
+      <c r="O13" s="14">
+        <v>100</v>
+      </c>
+      <c r="P13" s="15">
+        <v>22</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>91</v>
+      </c>
+      <c r="R13" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2063,55 +2081,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L14" s="4">
-        <v>-17.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O14" s="10">
-        <v>17</v>
-      </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>0</v>
-      </c>
-      <c r="R14" s="7">
-        <v>0</v>
+        <v>203</v>
+      </c>
+      <c r="O14" s="14">
+        <v>89</v>
+      </c>
+      <c r="P14" s="13">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>85</v>
+      </c>
+      <c r="R14" s="12">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2119,55 +2137,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="L15" s="4">
-        <v>-23.5</v>
+        <v>-11.3</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O15" s="6">
-        <v>70</v>
-      </c>
-      <c r="P15" s="8">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>70</v>
-      </c>
-      <c r="R15" s="16">
-        <v>50</v>
+        <v>204</v>
+      </c>
+      <c r="O15" s="14">
+        <v>87</v>
+      </c>
+      <c r="P15" s="19">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>87</v>
+      </c>
+      <c r="R15" s="12">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2175,10 +2193,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>61</v>
@@ -2187,43 +2205,43 @@
         <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-20.2</v>
+        <v>-22.4</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O16" s="6">
-        <v>92</v>
-      </c>
-      <c r="P16" s="17">
-        <v>43</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>92</v>
-      </c>
-      <c r="R16" s="19">
-        <v>80</v>
+        <v>203</v>
+      </c>
+      <c r="O16" s="14">
+        <v>97</v>
+      </c>
+      <c r="P16" s="20">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="21">
+        <v>97</v>
+      </c>
+      <c r="R16" s="18">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2231,55 +2249,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="L17" s="4">
-        <v>-11.3</v>
+        <v>-22.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O17" s="6">
-        <v>97</v>
-      </c>
-      <c r="P17" s="20">
-        <v>57</v>
-      </c>
-      <c r="Q17" s="18">
-        <v>91</v>
-      </c>
-      <c r="R17" s="21">
-        <v>83</v>
+        <v>203</v>
+      </c>
+      <c r="O17" s="14">
+        <v>98</v>
+      </c>
+      <c r="P17" s="22">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>98</v>
+      </c>
+      <c r="R17" s="18">
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2287,55 +2305,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="L18" s="4">
-        <v>-22.4</v>
+        <v>-15.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="6">
-        <v>99</v>
-      </c>
-      <c r="P18" s="22">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>18</v>
-      </c>
-      <c r="R18" s="23">
-        <v>99</v>
+        <v>204</v>
+      </c>
+      <c r="O18" s="14">
+        <v>100</v>
+      </c>
+      <c r="P18" s="23">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="21">
+        <v>95</v>
+      </c>
+      <c r="R18" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2343,10 +2361,10 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>61</v>
@@ -2355,43 +2373,43 @@
         <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>86</v>
       </c>
       <c r="L19" s="4">
-        <v>-22.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O19" s="6">
-        <v>82</v>
-      </c>
-      <c r="P19" s="22">
-        <v>13</v>
-      </c>
-      <c r="Q19" s="22">
-        <v>17</v>
-      </c>
-      <c r="R19" s="24">
-        <v>67</v>
+        <v>203</v>
+      </c>
+      <c r="O19" s="14">
+        <v>87</v>
+      </c>
+      <c r="P19" s="24">
+        <v>50</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>87</v>
+      </c>
+      <c r="R19" s="25">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2399,55 +2417,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-15.5</v>
+        <v>-22.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O20" s="6">
-        <v>62</v>
-      </c>
-      <c r="P20" s="25">
-        <v>10</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>16</v>
-      </c>
-      <c r="R20" s="22">
-        <v>15</v>
+        <v>203</v>
+      </c>
+      <c r="O20" s="14">
+        <v>70</v>
+      </c>
+      <c r="P20" s="12">
+        <v>37</v>
+      </c>
+      <c r="Q20" s="26">
+        <v>70</v>
+      </c>
+      <c r="R20" s="12">
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2455,7 +2473,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>58</v>
@@ -2467,43 +2485,43 @@
         <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="L21" s="4">
-        <v>-20.2</v>
+        <v>-18.8</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O21" s="6">
-        <v>92</v>
-      </c>
-      <c r="P21" s="14">
-        <v>34</v>
+        <v>203</v>
+      </c>
+      <c r="O21" s="14">
+        <v>69</v>
+      </c>
+      <c r="P21" s="25">
+        <v>39</v>
       </c>
       <c r="Q21" s="26">
-        <v>60</v>
-      </c>
-      <c r="R21" s="16">
-        <v>51</v>
+        <v>69</v>
+      </c>
+      <c r="R21" s="22">
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2511,10 +2529,10 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>61</v>
@@ -2523,102 +2541,158 @@
         <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L22" s="4">
-        <v>-22.9</v>
+        <v>-16.8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N22" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O22" s="14">
+        <v>100</v>
+      </c>
+      <c r="P22" s="16">
+        <v>91</v>
+      </c>
+      <c r="Q22" s="18">
+        <v>86</v>
+      </c>
+      <c r="R22" s="16">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2">
+        <v>30</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-22.2</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="O22" s="6">
-        <v>93</v>
-      </c>
-      <c r="P22" s="16">
-        <v>48</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>64</v>
-      </c>
-      <c r="R22" s="20">
-        <v>54</v>
+      <c r="N23" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O23" s="14">
+        <v>100</v>
+      </c>
+      <c r="P23" s="21">
+        <v>97</v>
+      </c>
+      <c r="Q23" s="26">
+        <v>70</v>
+      </c>
+      <c r="R23" s="27">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A22">
+  <conditionalFormatting sqref="A2:A23">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B22">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C22">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D22">
+  <conditionalFormatting sqref="D2:D23">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E22">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F22">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G22">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I23">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J23">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K23">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2637,12 +2711,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N23">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2659,22 +2733,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O22">
+  <conditionalFormatting sqref="O2:O23">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P22">
+  <conditionalFormatting sqref="P2:P23">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q22">
+  <conditionalFormatting sqref="Q2:Q23">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="214">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260430--01</t>
-  </si>
-  <si>
-    <t>20260430--02</t>
-  </si>
-  <si>
-    <t>20260430--03</t>
-  </si>
-  <si>
     <t>20260501--01</t>
   </si>
   <si>
@@ -136,19 +127,25 @@
     <t>20260506--03</t>
   </si>
   <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>06:16</t>
-  </si>
-  <si>
-    <t>04:45</t>
+    <t>20260507--01</t>
+  </si>
+  <si>
+    <t>20260507--02</t>
+  </si>
+  <si>
+    <t>20260507--03</t>
+  </si>
+  <si>
+    <t>20260507--04</t>
+  </si>
+  <si>
+    <t>20260507--05</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>05:54</t>
+    <t>05:53</t>
   </si>
   <si>
     <t>04:01</t>
@@ -163,19 +160,19 @@
     <t>02:52</t>
   </si>
   <si>
-    <t>06:00</t>
+    <t>05:59</t>
   </si>
   <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>05:47</t>
+    <t>05:46</t>
   </si>
   <si>
     <t>06:14</t>
   </si>
   <si>
-    <t>04:59</t>
+    <t>04:58</t>
   </si>
   <si>
     <t>05:30</t>
@@ -190,27 +187,33 @@
     <t>05:05</t>
   </si>
   <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>04:32</t>
-  </si>
-  <si>
-    <t>06:11</t>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>03:41</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>01:53</t>
+  </si>
+  <si>
+    <t>05:41</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:38</t>
-  </si>
-  <si>
-    <t>01:53</t>
-  </si>
-  <si>
-    <t>05:41</t>
-  </si>
-  <si>
     <t>03:57</t>
   </si>
   <si>
@@ -220,354 +223,378 @@
     <t>03:02</t>
   </si>
   <si>
-    <t>00:42</t>
-  </si>
-  <si>
-    <t>00:08:08</t>
-  </si>
-  <si>
-    <t>01:45:01</t>
-  </si>
-  <si>
-    <t>23:25:34</t>
+    <t>00:41</t>
   </si>
   <si>
     <t>01:02:17</t>
   </si>
   <si>
-    <t>02:39:37</t>
-  </si>
-  <si>
-    <t>22:42:59</t>
-  </si>
-  <si>
-    <t>00:19:31</t>
-  </si>
-  <si>
-    <t>01:56:46</t>
-  </si>
-  <si>
-    <t>22:00:25</t>
-  </si>
-  <si>
-    <t>23:36:43</t>
-  </si>
-  <si>
-    <t>01:13:54</t>
-  </si>
-  <si>
-    <t>22:53:54</t>
-  </si>
-  <si>
-    <t>00:30:59</t>
-  </si>
-  <si>
-    <t>02:08:27</t>
-  </si>
-  <si>
-    <t>22:11:04</t>
-  </si>
-  <si>
-    <t>23:48:02</t>
-  </si>
-  <si>
-    <t>01:25:26</t>
-  </si>
-  <si>
-    <t>21:28:12</t>
-  </si>
-  <si>
-    <t>23:05:02</t>
-  </si>
-  <si>
-    <t>00:42:23</t>
-  </si>
-  <si>
-    <t>20:45:21</t>
-  </si>
-  <si>
-    <t>22:22:01</t>
-  </si>
-  <si>
-    <t>00:10:36</t>
-  </si>
-  <si>
-    <t>01:47:16</t>
-  </si>
-  <si>
-    <t>23:28:09</t>
-  </si>
-  <si>
-    <t>01:04:33</t>
+    <t>02:39:36</t>
+  </si>
+  <si>
+    <t>22:42:58</t>
+  </si>
+  <si>
+    <t>00:19:29</t>
+  </si>
+  <si>
+    <t>01:56:45</t>
+  </si>
+  <si>
+    <t>22:00:22</t>
+  </si>
+  <si>
+    <t>23:36:40</t>
+  </si>
+  <si>
+    <t>01:13:51</t>
+  </si>
+  <si>
+    <t>22:53:49</t>
+  </si>
+  <si>
+    <t>00:30:54</t>
+  </si>
+  <si>
+    <t>02:08:22</t>
+  </si>
+  <si>
+    <t>22:10:56</t>
+  </si>
+  <si>
+    <t>23:47:54</t>
+  </si>
+  <si>
+    <t>01:25:18</t>
+  </si>
+  <si>
+    <t>21:28:02</t>
+  </si>
+  <si>
+    <t>23:04:51</t>
+  </si>
+  <si>
+    <t>00:42:12</t>
+  </si>
+  <si>
+    <t>20:45:07</t>
+  </si>
+  <si>
+    <t>22:21:46</t>
+  </si>
+  <si>
+    <t>23:59:03</t>
+  </si>
+  <si>
+    <t>01:36:45</t>
+  </si>
+  <si>
+    <t>20:02:12</t>
+  </si>
+  <si>
+    <t>21:38:38</t>
+  </si>
+  <si>
+    <t>23:15:51</t>
+  </si>
+  <si>
+    <t>01:04:32</t>
   </si>
   <si>
     <t>02:41:56</t>
   </si>
   <si>
-    <t>22:45:47</t>
-  </si>
-  <si>
-    <t>00:21:48</t>
-  </si>
-  <si>
-    <t>01:59:04</t>
-  </si>
-  <si>
-    <t>22:03:35</t>
-  </si>
-  <si>
-    <t>23:39:01</t>
-  </si>
-  <si>
-    <t>01:16:10</t>
-  </si>
-  <si>
-    <t>22:56:15</t>
-  </si>
-  <si>
-    <t>00:33:14</t>
-  </si>
-  <si>
-    <t>02:11:00</t>
-  </si>
-  <si>
-    <t>22:13:28</t>
-  </si>
-  <si>
-    <t>23:50:17</t>
-  </si>
-  <si>
-    <t>01:27:53</t>
-  </si>
-  <si>
-    <t>21:30:43</t>
-  </si>
-  <si>
-    <t>23:07:17</t>
-  </si>
-  <si>
-    <t>00:44:45</t>
-  </si>
-  <si>
-    <t>20:48:00</t>
-  </si>
-  <si>
-    <t>22:24:16</t>
-  </si>
-  <si>
-    <t>00:13:13</t>
-  </si>
-  <si>
-    <t>01:50:24</t>
-  </si>
-  <si>
-    <t>23:30:31</t>
-  </si>
-  <si>
-    <t>01:07:39</t>
-  </si>
-  <si>
-    <t>02:44:53</t>
-  </si>
-  <si>
-    <t>22:47:47</t>
-  </si>
-  <si>
-    <t>00:24:51</t>
-  </si>
-  <si>
-    <t>02:02:06</t>
-  </si>
-  <si>
-    <t>22:05:01</t>
-  </si>
-  <si>
-    <t>23:42:01</t>
-  </si>
-  <si>
-    <t>01:19:15</t>
-  </si>
-  <si>
-    <t>22:59:08</t>
-  </si>
-  <si>
-    <t>00:36:21</t>
-  </si>
-  <si>
-    <t>02:13:29</t>
-  </si>
-  <si>
-    <t>22:16:13</t>
-  </si>
-  <si>
-    <t>23:53:24</t>
-  </si>
-  <si>
-    <t>01:30:35</t>
-  </si>
-  <si>
-    <t>21:33:15</t>
-  </si>
-  <si>
-    <t>23:10:24</t>
-  </si>
-  <si>
-    <t>00:47:36</t>
-  </si>
-  <si>
-    <t>20:50:16</t>
-  </si>
-  <si>
-    <t>22:27:21</t>
-  </si>
-  <si>
-    <t>00:15:51</t>
-  </si>
-  <si>
-    <t>01:53:32</t>
-  </si>
-  <si>
-    <t>23:32:54</t>
-  </si>
-  <si>
-    <t>01:10:46</t>
-  </si>
-  <si>
-    <t>02:47:50</t>
-  </si>
-  <si>
-    <t>22:49:48</t>
-  </si>
-  <si>
-    <t>00:27:55</t>
-  </si>
-  <si>
-    <t>02:05:08</t>
-  </si>
-  <si>
-    <t>22:06:27</t>
-  </si>
-  <si>
-    <t>23:45:01</t>
-  </si>
-  <si>
-    <t>01:22:20</t>
-  </si>
-  <si>
-    <t>23:02:02</t>
-  </si>
-  <si>
-    <t>00:39:28</t>
-  </si>
-  <si>
-    <t>02:15:59</t>
-  </si>
-  <si>
-    <t>22:18:58</t>
-  </si>
-  <si>
-    <t>23:56:32</t>
-  </si>
-  <si>
-    <t>01:33:17</t>
-  </si>
-  <si>
-    <t>21:35:48</t>
-  </si>
-  <si>
-    <t>23:13:31</t>
-  </si>
-  <si>
-    <t>00:50:28</t>
-  </si>
-  <si>
-    <t>20:52:32</t>
-  </si>
-  <si>
-    <t>22:30:27</t>
-  </si>
-  <si>
-    <t>00:18:20</t>
-  </si>
-  <si>
-    <t>01:55:48</t>
-  </si>
-  <si>
-    <t>23:35:30</t>
-  </si>
-  <si>
-    <t>01:13:02</t>
-  </si>
-  <si>
-    <t>02:50:10</t>
-  </si>
-  <si>
-    <t>22:52:36</t>
-  </si>
-  <si>
-    <t>00:30:12</t>
-  </si>
-  <si>
-    <t>02:07:26</t>
-  </si>
-  <si>
-    <t>22:09:38</t>
-  </si>
-  <si>
-    <t>23:47:19</t>
-  </si>
-  <si>
-    <t>01:24:37</t>
-  </si>
-  <si>
-    <t>23:04:23</t>
-  </si>
-  <si>
-    <t>00:41:44</t>
-  </si>
-  <si>
-    <t>02:18:31</t>
-  </si>
-  <si>
-    <t>22:21:23</t>
-  </si>
-  <si>
-    <t>23:58:47</t>
-  </si>
-  <si>
-    <t>01:35:43</t>
-  </si>
-  <si>
-    <t>21:38:19</t>
-  </si>
-  <si>
-    <t>23:15:47</t>
-  </si>
-  <si>
-    <t>00:52:50</t>
-  </si>
-  <si>
-    <t>20:55:12</t>
-  </si>
-  <si>
-    <t>22:32:43</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>30°</t>
+    <t>22:45:45</t>
+  </si>
+  <si>
+    <t>00:21:46</t>
+  </si>
+  <si>
+    <t>01:59:02</t>
+  </si>
+  <si>
+    <t>22:03:32</t>
+  </si>
+  <si>
+    <t>23:38:58</t>
+  </si>
+  <si>
+    <t>01:16:07</t>
+  </si>
+  <si>
+    <t>22:56:10</t>
+  </si>
+  <si>
+    <t>00:33:09</t>
+  </si>
+  <si>
+    <t>02:10:55</t>
+  </si>
+  <si>
+    <t>22:13:20</t>
+  </si>
+  <si>
+    <t>23:50:09</t>
+  </si>
+  <si>
+    <t>01:27:45</t>
+  </si>
+  <si>
+    <t>21:30:32</t>
+  </si>
+  <si>
+    <t>23:07:06</t>
+  </si>
+  <si>
+    <t>00:44:34</t>
+  </si>
+  <si>
+    <t>20:47:46</t>
+  </si>
+  <si>
+    <t>22:24:02</t>
+  </si>
+  <si>
+    <t>00:01:22</t>
+  </si>
+  <si>
+    <t>01:40:06</t>
+  </si>
+  <si>
+    <t>20:05:06</t>
+  </si>
+  <si>
+    <t>21:40:56</t>
+  </si>
+  <si>
+    <t>23:18:08</t>
+  </si>
+  <si>
+    <t>01:07:38</t>
+  </si>
+  <si>
+    <t>02:44:52</t>
+  </si>
+  <si>
+    <t>22:47:45</t>
+  </si>
+  <si>
+    <t>00:24:49</t>
+  </si>
+  <si>
+    <t>02:02:04</t>
+  </si>
+  <si>
+    <t>22:04:58</t>
+  </si>
+  <si>
+    <t>23:41:57</t>
+  </si>
+  <si>
+    <t>01:19:12</t>
+  </si>
+  <si>
+    <t>22:59:02</t>
+  </si>
+  <si>
+    <t>00:36:16</t>
+  </si>
+  <si>
+    <t>02:13:24</t>
+  </si>
+  <si>
+    <t>22:16:05</t>
+  </si>
+  <si>
+    <t>23:53:16</t>
+  </si>
+  <si>
+    <t>01:30:27</t>
+  </si>
+  <si>
+    <t>21:33:04</t>
+  </si>
+  <si>
+    <t>23:10:13</t>
+  </si>
+  <si>
+    <t>00:47:25</t>
+  </si>
+  <si>
+    <t>20:50:01</t>
+  </si>
+  <si>
+    <t>22:27:07</t>
+  </si>
+  <si>
+    <t>00:04:20</t>
+  </si>
+  <si>
+    <t>01:41:17</t>
+  </si>
+  <si>
+    <t>20:06:56</t>
+  </si>
+  <si>
+    <t>21:43:58</t>
+  </si>
+  <si>
+    <t>23:21:11</t>
+  </si>
+  <si>
+    <t>01:10:45</t>
+  </si>
+  <si>
+    <t>02:47:49</t>
+  </si>
+  <si>
+    <t>22:49:46</t>
+  </si>
+  <si>
+    <t>00:27:53</t>
+  </si>
+  <si>
+    <t>02:05:06</t>
+  </si>
+  <si>
+    <t>22:06:24</t>
+  </si>
+  <si>
+    <t>23:44:57</t>
+  </si>
+  <si>
+    <t>01:22:17</t>
+  </si>
+  <si>
+    <t>23:01:56</t>
+  </si>
+  <si>
+    <t>00:39:23</t>
+  </si>
+  <si>
+    <t>02:15:53</t>
+  </si>
+  <si>
+    <t>22:18:50</t>
+  </si>
+  <si>
+    <t>23:56:24</t>
+  </si>
+  <si>
+    <t>01:33:09</t>
+  </si>
+  <si>
+    <t>21:35:37</t>
+  </si>
+  <si>
+    <t>23:13:20</t>
+  </si>
+  <si>
+    <t>00:50:16</t>
+  </si>
+  <si>
+    <t>20:52:17</t>
+  </si>
+  <si>
+    <t>22:30:12</t>
+  </si>
+  <si>
+    <t>00:07:18</t>
+  </si>
+  <si>
+    <t>01:42:29</t>
+  </si>
+  <si>
+    <t>20:08:47</t>
+  </si>
+  <si>
+    <t>21:47:00</t>
+  </si>
+  <si>
+    <t>23:24:13</t>
+  </si>
+  <si>
+    <t>01:13:01</t>
+  </si>
+  <si>
+    <t>02:50:09</t>
+  </si>
+  <si>
+    <t>22:52:35</t>
+  </si>
+  <si>
+    <t>00:30:10</t>
+  </si>
+  <si>
+    <t>02:07:24</t>
+  </si>
+  <si>
+    <t>22:09:34</t>
+  </si>
+  <si>
+    <t>23:47:16</t>
+  </si>
+  <si>
+    <t>01:24:33</t>
+  </si>
+  <si>
+    <t>23:04:18</t>
+  </si>
+  <si>
+    <t>00:41:38</t>
+  </si>
+  <si>
+    <t>02:18:26</t>
+  </si>
+  <si>
+    <t>22:21:15</t>
+  </si>
+  <si>
+    <t>23:58:39</t>
+  </si>
+  <si>
+    <t>01:35:35</t>
+  </si>
+  <si>
+    <t>21:38:08</t>
+  </si>
+  <si>
+    <t>23:15:36</t>
+  </si>
+  <si>
+    <t>00:52:38</t>
+  </si>
+  <si>
+    <t>20:54:57</t>
+  </si>
+  <si>
+    <t>22:32:28</t>
+  </si>
+  <si>
+    <t>00:09:37</t>
+  </si>
+  <si>
+    <t>01:45:49</t>
+  </si>
+  <si>
+    <t>20:11:41</t>
+  </si>
+  <si>
+    <t>21:49:17</t>
+  </si>
+  <si>
+    <t>23:26:30</t>
+  </si>
+  <si>
+    <t>24°</t>
+  </si>
+  <si>
+    <t>11°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>11°</t>
-  </si>
-  <si>
     <t>10°</t>
   </si>
   <si>
@@ -586,49 +613,46 @@
     <t>14°</t>
   </si>
   <si>
-    <t>00:16:38</t>
-  </si>
-  <si>
-    <t>01:49:54</t>
-  </si>
-  <si>
-    <t>01:08:53</t>
-  </si>
-  <si>
-    <t>02:42:09</t>
-  </si>
-  <si>
-    <t>02:01:11</t>
-  </si>
-  <si>
-    <t>23:47:03</t>
-  </si>
-  <si>
-    <t>01:20:19</t>
-  </si>
-  <si>
-    <t>00:39:39</t>
-  </si>
-  <si>
-    <t>02:12:57</t>
-  </si>
-  <si>
-    <t>01:32:35</t>
-  </si>
-  <si>
-    <t>00:52:40</t>
+    <t>01:08:52</t>
+  </si>
+  <si>
+    <t>02:42:08</t>
+  </si>
+  <si>
+    <t>02:01:09</t>
+  </si>
+  <si>
+    <t>23:47:00</t>
+  </si>
+  <si>
+    <t>01:20:16</t>
+  </si>
+  <si>
+    <t>00:39:34</t>
+  </si>
+  <si>
+    <t>02:12:51</t>
+  </si>
+  <si>
+    <t>01:32:28</t>
+  </si>
+  <si>
+    <t>00:52:30</t>
+  </si>
+  <si>
+    <t>20:04:59</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
+    <t>2</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -665,7 +689,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,13 +716,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6697CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,103 +836,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -928,6 +958,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1331,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1409,55 +1442,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="L2" s="4">
-        <v>-22.8</v>
+        <v>-18.8</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="O2" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="7">
         <v>0</v>
       </c>
-      <c r="R2" s="7">
-        <v>0</v>
+      <c r="R2" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1465,55 +1498,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="L3" s="4">
-        <v>-15</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O3" s="6">
-        <v>1</v>
+        <v>211</v>
+      </c>
+      <c r="O3" s="9">
+        <v>21</v>
       </c>
       <c r="P3" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="7">
-        <v>1</v>
+      <c r="R3" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1521,46 +1554,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
         <v>-24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="O4" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1577,55 +1610,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="L5" s="4">
-        <v>-18.8</v>
+        <v>-21.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="O5" s="6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="8">
-        <v>9</v>
+      <c r="R5" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1633,55 +1666,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L6" s="4">
-        <v>-8.300000000000001</v>
+        <v>-13.1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="O6" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="9">
-        <v>6</v>
+      <c r="R6" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1689,46 +1722,46 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-24</v>
+        <v>-22.6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="O7" s="6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
@@ -1736,8 +1769,8 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
-        <v>0</v>
+      <c r="R7" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1745,46 +1778,46 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="O8" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -1792,8 +1825,8 @@
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
-        <v>2</v>
+      <c r="R8" s="10">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1801,46 +1834,46 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="L9" s="4">
-        <v>-13.1</v>
+        <v>-17.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O9" s="6">
-        <v>2</v>
+        <v>211</v>
+      </c>
+      <c r="O9" s="9">
+        <v>41</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
@@ -1848,8 +1881,8 @@
       <c r="Q9" s="7">
         <v>0</v>
       </c>
-      <c r="R9" s="7">
-        <v>2</v>
+      <c r="R9" s="11">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1857,55 +1890,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-22.6</v>
+        <v>-23.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O10" s="6">
-        <v>14</v>
+        <v>212</v>
+      </c>
+      <c r="O10" s="12">
+        <v>100</v>
       </c>
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="7">
-        <v>0</v>
-      </c>
-      <c r="R10" s="10">
-        <v>13</v>
+      <c r="Q10" s="13">
+        <v>100</v>
+      </c>
+      <c r="R10" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1913,55 +1946,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L11" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O11" s="12">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L11" s="4">
-        <v>-23.1</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O11" s="11">
-        <v>37</v>
-      </c>
       <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>90</v>
+      </c>
+      <c r="R11" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1969,55 +2002,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="L12" s="4">
-        <v>-17.2</v>
+        <v>-11.3</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O12" s="11">
-        <v>44</v>
-      </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7">
-        <v>0</v>
+        <v>211</v>
+      </c>
+      <c r="O12" s="12">
+        <v>100</v>
+      </c>
+      <c r="P12" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>100</v>
       </c>
       <c r="R12" s="13">
-        <v>26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2025,54 +2058,54 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-23.5</v>
+        <v>-22.4</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O13" s="14">
+        <v>212</v>
+      </c>
+      <c r="O13" s="12">
         <v>100</v>
       </c>
       <c r="P13" s="15">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>91</v>
-      </c>
-      <c r="R13" s="17">
+        <v>53</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>98</v>
+      </c>
+      <c r="R13" s="13">
         <v>100</v>
       </c>
     </row>
@@ -2081,55 +2114,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-20.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O14" s="14">
-        <v>89</v>
-      </c>
-      <c r="P14" s="13">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>85</v>
-      </c>
-      <c r="R14" s="12">
-        <v>33</v>
+        <v>212</v>
+      </c>
+      <c r="O14" s="12">
+        <v>100</v>
+      </c>
+      <c r="P14" s="16">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>99</v>
+      </c>
+      <c r="R14" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2137,55 +2170,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="L15" s="4">
-        <v>-11.3</v>
+        <v>-15.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O15" s="14">
-        <v>87</v>
-      </c>
-      <c r="P15" s="19">
-        <v>28</v>
-      </c>
-      <c r="Q15" s="18">
-        <v>87</v>
-      </c>
-      <c r="R15" s="12">
-        <v>33</v>
+        <v>211</v>
+      </c>
+      <c r="O15" s="12">
+        <v>100</v>
+      </c>
+      <c r="P15" s="17">
+        <v>70</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>98</v>
+      </c>
+      <c r="R15" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2193,55 +2226,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-22.4</v>
+        <v>-20.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O16" s="14">
-        <v>97</v>
-      </c>
-      <c r="P16" s="20">
-        <v>44</v>
-      </c>
-      <c r="Q16" s="21">
-        <v>97</v>
-      </c>
-      <c r="R16" s="18">
-        <v>83</v>
+        <v>212</v>
+      </c>
+      <c r="O16" s="12">
+        <v>98</v>
+      </c>
+      <c r="P16" s="14">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>2</v>
+      </c>
+      <c r="R16" s="16">
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2252,52 +2285,52 @@
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L17" s="4">
-        <v>-22.2</v>
+        <v>-22.9</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O17" s="14">
-        <v>98</v>
-      </c>
-      <c r="P17" s="22">
-        <v>54</v>
-      </c>
-      <c r="Q17" s="17">
-        <v>98</v>
-      </c>
-      <c r="R17" s="18">
+        <v>212</v>
+      </c>
+      <c r="O17" s="12">
+        <v>96</v>
+      </c>
+      <c r="P17" s="18">
         <v>87</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>2</v>
+      </c>
+      <c r="R17" s="19">
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2305,55 +2338,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" s="4">
+        <v>-18.9</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O18" s="12">
+        <v>95</v>
+      </c>
+      <c r="P18" s="18">
         <v>85</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-15.5</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O18" s="14">
-        <v>100</v>
-      </c>
-      <c r="P18" s="23">
-        <v>73</v>
-      </c>
-      <c r="Q18" s="21">
-        <v>95</v>
-      </c>
-      <c r="R18" s="17">
-        <v>100</v>
+      <c r="Q18" s="7">
+        <v>2</v>
+      </c>
+      <c r="R18" s="20">
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2361,55 +2394,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-20.2</v>
+        <v>-16.7</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O19" s="14">
-        <v>87</v>
-      </c>
-      <c r="P19" s="24">
-        <v>50</v>
-      </c>
-      <c r="Q19" s="18">
-        <v>87</v>
-      </c>
-      <c r="R19" s="25">
-        <v>41</v>
+        <v>212</v>
+      </c>
+      <c r="O19" s="12">
+        <v>100</v>
+      </c>
+      <c r="P19" s="21">
+        <v>94</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>68</v>
+      </c>
+      <c r="R19" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2417,55 +2450,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="4">
+        <v>-22.2</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O20" s="12">
+        <v>100</v>
+      </c>
+      <c r="P20" s="21">
+        <v>96</v>
+      </c>
+      <c r="Q20" s="20">
         <v>61</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="4">
-        <v>-22.9</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O20" s="14">
-        <v>70</v>
-      </c>
-      <c r="P20" s="12">
-        <v>37</v>
-      </c>
-      <c r="Q20" s="26">
-        <v>70</v>
-      </c>
-      <c r="R20" s="12">
-        <v>35</v>
+      <c r="R20" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2473,55 +2506,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>200</v>
+        <v>89</v>
       </c>
       <c r="L21" s="4">
-        <v>-18.8</v>
+        <v>-21.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O21" s="14">
-        <v>69</v>
-      </c>
-      <c r="P21" s="25">
-        <v>39</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>69</v>
-      </c>
-      <c r="R21" s="22">
-        <v>55</v>
+        <v>212</v>
+      </c>
+      <c r="O21" s="12">
+        <v>100</v>
+      </c>
+      <c r="P21" s="22">
+        <v>79</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>77</v>
+      </c>
+      <c r="R21" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2529,55 +2562,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-16.8</v>
+        <v>-14</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O22" s="14">
+        <v>213</v>
+      </c>
+      <c r="O22" s="12">
         <v>100</v>
       </c>
-      <c r="P22" s="16">
-        <v>91</v>
+      <c r="P22" s="23">
+        <v>73</v>
       </c>
       <c r="Q22" s="18">
-        <v>86</v>
-      </c>
-      <c r="R22" s="16">
-        <v>92</v>
+        <v>83</v>
+      </c>
+      <c r="R22" s="13">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2585,114 +2618,226 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
+        <v>14</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-12.3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O23" s="12">
+        <v>48</v>
+      </c>
+      <c r="P23" s="24">
         <v>30</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L23" s="4">
+      <c r="Q23" s="10">
+        <v>8</v>
+      </c>
+      <c r="R23" s="25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" s="4">
+        <v>-20.3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O24" s="12">
+        <v>50</v>
+      </c>
+      <c r="P24" s="26">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>7</v>
+      </c>
+      <c r="R24" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2">
+        <v>29</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="4">
         <v>-22.2</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O23" s="14">
-        <v>100</v>
-      </c>
-      <c r="P23" s="21">
-        <v>97</v>
-      </c>
-      <c r="Q23" s="26">
-        <v>70</v>
-      </c>
-      <c r="R23" s="27">
-        <v>79</v>
+      <c r="M25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O25" s="12">
+        <v>46</v>
+      </c>
+      <c r="P25" s="27">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>4</v>
+      </c>
+      <c r="R25" s="28">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A23">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D23">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H23">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I23">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J23">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K23">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L23">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2711,12 +2856,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M23">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N23">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2733,22 +2878,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O23">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P23">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q23">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="218">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260501--01</t>
-  </si>
-  <si>
-    <t>20260501--02</t>
-  </si>
-  <si>
-    <t>20260501--03</t>
-  </si>
-  <si>
     <t>20260502--01</t>
   </si>
   <si>
@@ -142,79 +133,85 @@
     <t>20260507--05</t>
   </si>
   <si>
+    <t>20260508--01</t>
+  </si>
+  <si>
+    <t>20260508--02</t>
+  </si>
+  <si>
+    <t>20260508--03</t>
+  </si>
+  <si>
+    <t>20260508--04</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>05:53</t>
-  </si>
-  <si>
-    <t>04:01</t>
-  </si>
-  <si>
-    <t>06:07</t>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>02:24</t>
+  </si>
+  <si>
+    <t>03:40</t>
   </si>
   <si>
     <t>06:04</t>
   </si>
   <si>
-    <t>02:52</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>06:14</t>
-  </si>
-  <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>03:41</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>01:53</t>
-  </si>
-  <si>
-    <t>05:41</t>
+    <t>03:46</t>
+  </si>
+  <si>
+    <t>02:12</t>
+  </si>
+  <si>
+    <t>05:54</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:57</t>
+    <t>03:56</t>
   </si>
   <si>
     <t>02:01</t>
@@ -226,85 +223,82 @@
     <t>00:41</t>
   </si>
   <si>
-    <t>01:02:17</t>
-  </si>
-  <si>
-    <t>02:39:36</t>
-  </si>
-  <si>
-    <t>22:42:58</t>
+    <t>00:36</t>
   </si>
   <si>
     <t>00:19:29</t>
   </si>
   <si>
-    <t>01:56:45</t>
+    <t>01:56:44</t>
   </si>
   <si>
     <t>22:00:22</t>
   </si>
   <si>
-    <t>23:36:40</t>
-  </si>
-  <si>
-    <t>01:13:51</t>
-  </si>
-  <si>
-    <t>22:53:49</t>
-  </si>
-  <si>
-    <t>00:30:54</t>
-  </si>
-  <si>
-    <t>02:08:22</t>
-  </si>
-  <si>
-    <t>22:10:56</t>
-  </si>
-  <si>
-    <t>23:47:54</t>
-  </si>
-  <si>
-    <t>01:25:18</t>
-  </si>
-  <si>
-    <t>21:28:02</t>
-  </si>
-  <si>
-    <t>23:04:51</t>
-  </si>
-  <si>
-    <t>00:42:12</t>
-  </si>
-  <si>
-    <t>20:45:07</t>
-  </si>
-  <si>
-    <t>22:21:46</t>
-  </si>
-  <si>
-    <t>23:59:03</t>
-  </si>
-  <si>
-    <t>01:36:45</t>
-  </si>
-  <si>
-    <t>20:02:12</t>
-  </si>
-  <si>
-    <t>21:38:38</t>
-  </si>
-  <si>
-    <t>23:15:51</t>
-  </si>
-  <si>
-    <t>01:04:32</t>
-  </si>
-  <si>
-    <t>02:41:56</t>
-  </si>
-  <si>
-    <t>22:45:45</t>
+    <t>23:36:39</t>
+  </si>
+  <si>
+    <t>01:13:50</t>
+  </si>
+  <si>
+    <t>22:53:47</t>
+  </si>
+  <si>
+    <t>00:30:52</t>
+  </si>
+  <si>
+    <t>02:08:20</t>
+  </si>
+  <si>
+    <t>22:10:52</t>
+  </si>
+  <si>
+    <t>23:47:50</t>
+  </si>
+  <si>
+    <t>01:25:14</t>
+  </si>
+  <si>
+    <t>21:27:56</t>
+  </si>
+  <si>
+    <t>23:04:46</t>
+  </si>
+  <si>
+    <t>00:42:06</t>
+  </si>
+  <si>
+    <t>20:44:59</t>
+  </si>
+  <si>
+    <t>22:21:38</t>
+  </si>
+  <si>
+    <t>23:58:55</t>
+  </si>
+  <si>
+    <t>01:36:37</t>
+  </si>
+  <si>
+    <t>20:02:02</t>
+  </si>
+  <si>
+    <t>21:38:28</t>
+  </si>
+  <si>
+    <t>23:15:40</t>
+  </si>
+  <si>
+    <t>00:53:16</t>
+  </si>
+  <si>
+    <t>19:19:05</t>
+  </si>
+  <si>
+    <t>20:55:15</t>
+  </si>
+  <si>
+    <t>22:32:23</t>
   </si>
   <si>
     <t>00:21:46</t>
@@ -316,67 +310,70 @@
     <t>22:03:32</t>
   </si>
   <si>
-    <t>23:38:58</t>
-  </si>
-  <si>
-    <t>01:16:07</t>
-  </si>
-  <si>
-    <t>22:56:10</t>
-  </si>
-  <si>
-    <t>00:33:09</t>
-  </si>
-  <si>
-    <t>02:10:55</t>
-  </si>
-  <si>
-    <t>22:13:20</t>
-  </si>
-  <si>
-    <t>23:50:09</t>
-  </si>
-  <si>
-    <t>01:27:45</t>
-  </si>
-  <si>
-    <t>21:30:32</t>
-  </si>
-  <si>
-    <t>23:07:06</t>
-  </si>
-  <si>
-    <t>00:44:34</t>
-  </si>
-  <si>
-    <t>20:47:46</t>
-  </si>
-  <si>
-    <t>22:24:02</t>
-  </si>
-  <si>
-    <t>00:01:22</t>
-  </si>
-  <si>
-    <t>01:40:06</t>
-  </si>
-  <si>
-    <t>20:05:06</t>
-  </si>
-  <si>
-    <t>21:40:56</t>
-  </si>
-  <si>
-    <t>23:18:08</t>
-  </si>
-  <si>
-    <t>01:07:38</t>
-  </si>
-  <si>
-    <t>02:44:52</t>
-  </si>
-  <si>
-    <t>22:47:45</t>
+    <t>23:38:57</t>
+  </si>
+  <si>
+    <t>01:16:06</t>
+  </si>
+  <si>
+    <t>22:56:08</t>
+  </si>
+  <si>
+    <t>00:33:07</t>
+  </si>
+  <si>
+    <t>02:10:53</t>
+  </si>
+  <si>
+    <t>22:13:17</t>
+  </si>
+  <si>
+    <t>23:50:05</t>
+  </si>
+  <si>
+    <t>01:27:41</t>
+  </si>
+  <si>
+    <t>21:30:27</t>
+  </si>
+  <si>
+    <t>23:07:01</t>
+  </si>
+  <si>
+    <t>00:44:28</t>
+  </si>
+  <si>
+    <t>20:47:39</t>
+  </si>
+  <si>
+    <t>22:23:54</t>
+  </si>
+  <si>
+    <t>00:01:14</t>
+  </si>
+  <si>
+    <t>01:39:57</t>
+  </si>
+  <si>
+    <t>20:04:56</t>
+  </si>
+  <si>
+    <t>21:40:45</t>
+  </si>
+  <si>
+    <t>23:17:58</t>
+  </si>
+  <si>
+    <t>00:56:08</t>
+  </si>
+  <si>
+    <t>19:22:29</t>
+  </si>
+  <si>
+    <t>20:57:35</t>
+  </si>
+  <si>
+    <t>22:34:39</t>
   </si>
   <si>
     <t>00:24:49</t>
@@ -385,222 +382,234 @@
     <t>02:02:04</t>
   </si>
   <si>
-    <t>22:04:58</t>
-  </si>
-  <si>
-    <t>23:41:57</t>
-  </si>
-  <si>
-    <t>01:19:12</t>
-  </si>
-  <si>
-    <t>22:59:02</t>
-  </si>
-  <si>
-    <t>00:36:16</t>
-  </si>
-  <si>
-    <t>02:13:24</t>
-  </si>
-  <si>
-    <t>22:16:05</t>
-  </si>
-  <si>
-    <t>23:53:16</t>
-  </si>
-  <si>
-    <t>01:30:27</t>
-  </si>
-  <si>
-    <t>21:33:04</t>
-  </si>
-  <si>
-    <t>23:10:13</t>
-  </si>
-  <si>
-    <t>00:47:25</t>
-  </si>
-  <si>
-    <t>20:50:01</t>
-  </si>
-  <si>
-    <t>22:27:07</t>
-  </si>
-  <si>
-    <t>00:04:20</t>
-  </si>
-  <si>
-    <t>01:41:17</t>
-  </si>
-  <si>
-    <t>20:06:56</t>
-  </si>
-  <si>
-    <t>21:43:58</t>
-  </si>
-  <si>
-    <t>23:21:11</t>
-  </si>
-  <si>
-    <t>01:10:45</t>
-  </si>
-  <si>
-    <t>02:47:49</t>
-  </si>
-  <si>
-    <t>22:49:46</t>
+    <t>22:04:57</t>
+  </si>
+  <si>
+    <t>23:41:56</t>
+  </si>
+  <si>
+    <t>01:19:11</t>
+  </si>
+  <si>
+    <t>22:59:00</t>
+  </si>
+  <si>
+    <t>00:36:13</t>
+  </si>
+  <si>
+    <t>02:13:22</t>
+  </si>
+  <si>
+    <t>22:16:01</t>
+  </si>
+  <si>
+    <t>23:53:12</t>
+  </si>
+  <si>
+    <t>01:30:23</t>
+  </si>
+  <si>
+    <t>21:32:59</t>
+  </si>
+  <si>
+    <t>23:10:08</t>
+  </si>
+  <si>
+    <t>00:47:19</t>
+  </si>
+  <si>
+    <t>20:49:54</t>
+  </si>
+  <si>
+    <t>22:26:59</t>
+  </si>
+  <si>
+    <t>00:04:12</t>
+  </si>
+  <si>
+    <t>01:41:10</t>
+  </si>
+  <si>
+    <t>20:06:46</t>
+  </si>
+  <si>
+    <t>21:43:47</t>
+  </si>
+  <si>
+    <t>23:21:00</t>
+  </si>
+  <si>
+    <t>00:58:01</t>
+  </si>
+  <si>
+    <t>19:23:35</t>
+  </si>
+  <si>
+    <t>21:00:32</t>
+  </si>
+  <si>
+    <t>22:37:44</t>
   </si>
   <si>
     <t>00:27:53</t>
   </si>
   <si>
-    <t>02:05:06</t>
-  </si>
-  <si>
-    <t>22:06:24</t>
-  </si>
-  <si>
-    <t>23:44:57</t>
-  </si>
-  <si>
-    <t>01:22:17</t>
-  </si>
-  <si>
-    <t>23:01:56</t>
-  </si>
-  <si>
-    <t>00:39:23</t>
-  </si>
-  <si>
-    <t>02:15:53</t>
-  </si>
-  <si>
-    <t>22:18:50</t>
-  </si>
-  <si>
-    <t>23:56:24</t>
-  </si>
-  <si>
-    <t>01:33:09</t>
-  </si>
-  <si>
-    <t>21:35:37</t>
-  </si>
-  <si>
-    <t>23:13:20</t>
-  </si>
-  <si>
-    <t>00:50:16</t>
-  </si>
-  <si>
-    <t>20:52:17</t>
-  </si>
-  <si>
-    <t>22:30:12</t>
-  </si>
-  <si>
-    <t>00:07:18</t>
-  </si>
-  <si>
-    <t>01:42:29</t>
-  </si>
-  <si>
-    <t>20:08:47</t>
-  </si>
-  <si>
-    <t>21:47:00</t>
-  </si>
-  <si>
-    <t>23:24:13</t>
-  </si>
-  <si>
-    <t>01:13:01</t>
-  </si>
-  <si>
-    <t>02:50:09</t>
-  </si>
-  <si>
-    <t>22:52:35</t>
+    <t>02:05:05</t>
+  </si>
+  <si>
+    <t>22:06:22</t>
+  </si>
+  <si>
+    <t>23:44:56</t>
+  </si>
+  <si>
+    <t>01:22:16</t>
+  </si>
+  <si>
+    <t>23:01:54</t>
+  </si>
+  <si>
+    <t>00:39:20</t>
+  </si>
+  <si>
+    <t>02:15:51</t>
+  </si>
+  <si>
+    <t>22:18:46</t>
+  </si>
+  <si>
+    <t>23:56:20</t>
+  </si>
+  <si>
+    <t>01:33:05</t>
+  </si>
+  <si>
+    <t>21:35:32</t>
+  </si>
+  <si>
+    <t>23:13:14</t>
+  </si>
+  <si>
+    <t>00:50:11</t>
+  </si>
+  <si>
+    <t>20:52:09</t>
+  </si>
+  <si>
+    <t>22:30:04</t>
+  </si>
+  <si>
+    <t>00:07:10</t>
+  </si>
+  <si>
+    <t>01:42:21</t>
+  </si>
+  <si>
+    <t>20:08:36</t>
+  </si>
+  <si>
+    <t>21:46:49</t>
+  </si>
+  <si>
+    <t>23:24:02</t>
+  </si>
+  <si>
+    <t>00:59:54</t>
+  </si>
+  <si>
+    <t>19:24:41</t>
+  </si>
+  <si>
+    <t>21:03:29</t>
+  </si>
+  <si>
+    <t>22:40:49</t>
   </si>
   <si>
     <t>00:30:10</t>
   </si>
   <si>
-    <t>02:07:24</t>
-  </si>
-  <si>
-    <t>22:09:34</t>
-  </si>
-  <si>
-    <t>23:47:16</t>
-  </si>
-  <si>
-    <t>01:24:33</t>
-  </si>
-  <si>
-    <t>23:04:18</t>
-  </si>
-  <si>
-    <t>00:41:38</t>
-  </si>
-  <si>
-    <t>02:18:26</t>
-  </si>
-  <si>
-    <t>22:21:15</t>
-  </si>
-  <si>
-    <t>23:58:39</t>
-  </si>
-  <si>
-    <t>01:35:35</t>
-  </si>
-  <si>
-    <t>21:38:08</t>
-  </si>
-  <si>
-    <t>23:15:36</t>
-  </si>
-  <si>
-    <t>00:52:38</t>
-  </si>
-  <si>
-    <t>20:54:57</t>
-  </si>
-  <si>
-    <t>22:32:28</t>
-  </si>
-  <si>
-    <t>00:09:37</t>
-  </si>
-  <si>
-    <t>01:45:49</t>
-  </si>
-  <si>
-    <t>20:11:41</t>
-  </si>
-  <si>
-    <t>21:49:17</t>
-  </si>
-  <si>
-    <t>23:26:30</t>
-  </si>
-  <si>
-    <t>24°</t>
-  </si>
-  <si>
-    <t>11°</t>
+    <t>02:07:23</t>
+  </si>
+  <si>
+    <t>22:09:33</t>
+  </si>
+  <si>
+    <t>23:47:15</t>
+  </si>
+  <si>
+    <t>01:24:32</t>
+  </si>
+  <si>
+    <t>23:04:15</t>
+  </si>
+  <si>
+    <t>00:41:36</t>
+  </si>
+  <si>
+    <t>02:18:23</t>
+  </si>
+  <si>
+    <t>22:21:11</t>
+  </si>
+  <si>
+    <t>23:58:35</t>
+  </si>
+  <si>
+    <t>01:35:31</t>
+  </si>
+  <si>
+    <t>21:38:03</t>
+  </si>
+  <si>
+    <t>23:15:30</t>
+  </si>
+  <si>
+    <t>00:52:33</t>
+  </si>
+  <si>
+    <t>20:54:49</t>
+  </si>
+  <si>
+    <t>22:32:20</t>
+  </si>
+  <si>
+    <t>00:09:29</t>
+  </si>
+  <si>
+    <t>01:45:41</t>
+  </si>
+  <si>
+    <t>20:11:31</t>
+  </si>
+  <si>
+    <t>21:49:06</t>
+  </si>
+  <si>
+    <t>23:26:19</t>
+  </si>
+  <si>
+    <t>01:02:47</t>
+  </si>
+  <si>
+    <t>19:28:06</t>
+  </si>
+  <si>
+    <t>21:05:48</t>
+  </si>
+  <si>
+    <t>22:43:05</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>25°</t>
   </si>
   <si>
     <t>0°</t>
   </si>
   <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
     <t>1°</t>
   </si>
   <si>
@@ -613,34 +622,34 @@
     <t>14°</t>
   </si>
   <si>
-    <t>01:08:52</t>
-  </si>
-  <si>
-    <t>02:42:08</t>
-  </si>
-  <si>
     <t>02:01:09</t>
   </si>
   <si>
-    <t>23:47:00</t>
-  </si>
-  <si>
-    <t>01:20:16</t>
-  </si>
-  <si>
-    <t>00:39:34</t>
-  </si>
-  <si>
-    <t>02:12:51</t>
-  </si>
-  <si>
-    <t>01:32:28</t>
-  </si>
-  <si>
-    <t>00:52:30</t>
-  </si>
-  <si>
-    <t>20:04:59</t>
+    <t>23:46:59</t>
+  </si>
+  <si>
+    <t>01:20:15</t>
+  </si>
+  <si>
+    <t>00:39:32</t>
+  </si>
+  <si>
+    <t>02:12:49</t>
+  </si>
+  <si>
+    <t>01:32:24</t>
+  </si>
+  <si>
+    <t>00:52:24</t>
+  </si>
+  <si>
+    <t>20:04:49</t>
+  </si>
+  <si>
+    <t>19:24:52</t>
+  </si>
+  <si>
+    <t>20:58:11</t>
   </si>
   <si>
     <t>A+B</t>
@@ -649,13 +658,16 @@
     <t>B</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -689,7 +701,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,7 +734,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99BADE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,97 +830,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +842,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,9 +964,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1442,55 +1445,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="L2" s="4">
-        <v>-18.8</v>
+        <v>-21.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O2" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="7">
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1498,49 +1501,49 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L3" s="4">
-        <v>-8.300000000000001</v>
+        <v>-13.1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O3" s="9">
-        <v>21</v>
+        <v>215</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
       </c>
       <c r="P3" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="7">
         <v>0</v>
@@ -1554,46 +1557,46 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-24</v>
+        <v>-22.6</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="O4" s="9">
+        <v>82</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
@@ -1601,8 +1604,8 @@
       <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="7">
-        <v>0</v>
+      <c r="R4" s="10">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1610,46 +1613,46 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="L5" s="4">
-        <v>-21.5</v>
+        <v>-23.1</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="O5" s="9">
+        <v>64</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
@@ -1657,8 +1660,8 @@
       <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="7">
-        <v>0</v>
+      <c r="R5" s="11">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1666,10 +1669,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>66</v>
@@ -1678,34 +1681,34 @@
         <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L6" s="4">
-        <v>-13.1</v>
+        <v>-17.2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O6" s="6">
-        <v>4</v>
+        <v>215</v>
+      </c>
+      <c r="O6" s="9">
+        <v>68</v>
       </c>
       <c r="P6" s="7">
         <v>0</v>
@@ -1713,8 +1716,8 @@
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
-        <v>4</v>
+      <c r="R6" s="10">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1722,55 +1725,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.6</v>
+        <v>-23.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O7" s="6">
-        <v>6</v>
+        <v>217</v>
+      </c>
+      <c r="O7" s="9">
+        <v>100</v>
       </c>
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>5</v>
+      <c r="Q7" s="10">
+        <v>70</v>
+      </c>
+      <c r="R7" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1778,55 +1781,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O8" s="9">
         <v>100</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-23.1</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O8" s="6">
-        <v>13</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>10</v>
+      <c r="Q8" s="12">
+        <v>100</v>
+      </c>
+      <c r="R8" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1834,10 +1837,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>67</v>
@@ -1846,43 +1849,43 @@
         <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L9" s="4">
-        <v>-17.2</v>
+        <v>-11.3</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O9" s="9">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="7">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <v>41</v>
+      <c r="Q9" s="13">
+        <v>86</v>
+      </c>
+      <c r="R9" s="14">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1890,54 +1893,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-23.5</v>
+        <v>-22.4</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O10" s="12">
+        <v>217</v>
+      </c>
+      <c r="O10" s="9">
         <v>100</v>
       </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>100</v>
-      </c>
-      <c r="R10" s="13">
+      <c r="P10" s="15">
+        <v>22</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>82</v>
+      </c>
+      <c r="R10" s="12">
         <v>100</v>
       </c>
     </row>
@@ -1946,54 +1949,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="L11" s="4">
-        <v>-20.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O11" s="12">
+        <v>217</v>
+      </c>
+      <c r="O11" s="9">
         <v>100</v>
       </c>
-      <c r="P11" s="7">
-        <v>1</v>
+      <c r="P11" s="17">
+        <v>29</v>
       </c>
       <c r="Q11" s="14">
-        <v>90</v>
-      </c>
-      <c r="R11" s="13">
+        <v>43</v>
+      </c>
+      <c r="R11" s="12">
         <v>100</v>
       </c>
     </row>
@@ -2002,10 +2005,10 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>68</v>
@@ -2014,42 +2017,42 @@
         <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L12" s="4">
-        <v>-11.3</v>
+        <v>-15.5</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O12" s="12">
+        <v>215</v>
+      </c>
+      <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>100</v>
-      </c>
-      <c r="R12" s="13">
+      <c r="P12" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>70</v>
+      </c>
+      <c r="R12" s="12">
         <v>100</v>
       </c>
     </row>
@@ -2058,55 +2061,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-22.4</v>
+        <v>-20.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O13" s="12">
+        <v>217</v>
+      </c>
+      <c r="O13" s="9">
         <v>100</v>
       </c>
-      <c r="P13" s="15">
-        <v>53</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>98</v>
-      </c>
-      <c r="R13" s="13">
+      <c r="P13" s="12">
         <v>100</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>58</v>
+      </c>
+      <c r="R13" s="20">
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2114,55 +2117,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-22.2</v>
+        <v>-22.9</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O14" s="12">
-        <v>100</v>
-      </c>
-      <c r="P14" s="16">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="13">
+        <v>217</v>
+      </c>
+      <c r="O14" s="9">
         <v>99</v>
       </c>
-      <c r="R14" s="13">
-        <v>100</v>
+      <c r="P14" s="21">
+        <v>96</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>76</v>
+      </c>
+      <c r="R14" s="12">
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2170,54 +2173,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L15" s="4">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="O15" s="12">
+        <v>217</v>
+      </c>
+      <c r="O15" s="9">
         <v>100</v>
       </c>
-      <c r="P15" s="17">
-        <v>70</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>98</v>
-      </c>
-      <c r="R15" s="13">
+      <c r="P15" s="20">
+        <v>91</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>74</v>
+      </c>
+      <c r="R15" s="12">
         <v>100</v>
       </c>
     </row>
@@ -2226,55 +2229,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L16" s="4">
-        <v>-20.2</v>
+        <v>-16.7</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O16" s="12">
-        <v>98</v>
-      </c>
-      <c r="P16" s="14">
-        <v>89</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>2</v>
-      </c>
-      <c r="R16" s="16">
-        <v>52</v>
+        <v>217</v>
+      </c>
+      <c r="O16" s="9">
+        <v>100</v>
+      </c>
+      <c r="P16" s="21">
+        <v>95</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>99</v>
+      </c>
+      <c r="R16" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2282,55 +2285,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>85</v>
       </c>
       <c r="L17" s="4">
-        <v>-22.9</v>
+        <v>-22.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O17" s="12">
-        <v>96</v>
-      </c>
-      <c r="P17" s="18">
-        <v>87</v>
-      </c>
-      <c r="Q17" s="7">
-        <v>2</v>
-      </c>
-      <c r="R17" s="19">
-        <v>64</v>
+        <v>217</v>
+      </c>
+      <c r="O17" s="9">
+        <v>100</v>
+      </c>
+      <c r="P17" s="12">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>100</v>
+      </c>
+      <c r="R17" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2338,55 +2341,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>207</v>
+        <v>86</v>
       </c>
       <c r="L18" s="4">
-        <v>-18.9</v>
+        <v>-21.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O18" s="12">
-        <v>95</v>
-      </c>
-      <c r="P18" s="18">
-        <v>85</v>
-      </c>
-      <c r="Q18" s="7">
-        <v>2</v>
-      </c>
-      <c r="R18" s="20">
-        <v>61</v>
+        <v>217</v>
+      </c>
+      <c r="O18" s="9">
+        <v>100</v>
+      </c>
+      <c r="P18" s="12">
+        <v>98</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>100</v>
+      </c>
+      <c r="R18" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2394,54 +2397,54 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>87</v>
       </c>
       <c r="L19" s="4">
-        <v>-16.7</v>
+        <v>-14</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O19" s="12">
+        <v>216</v>
+      </c>
+      <c r="O19" s="9">
         <v>100</v>
       </c>
-      <c r="P19" s="21">
-        <v>94</v>
-      </c>
-      <c r="Q19" s="17">
-        <v>68</v>
-      </c>
-      <c r="R19" s="13">
+      <c r="P19" s="12">
+        <v>98</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>99</v>
+      </c>
+      <c r="R19" s="12">
         <v>100</v>
       </c>
     </row>
@@ -2450,55 +2453,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="L20" s="4">
-        <v>-22.2</v>
+        <v>-12.3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O20" s="12">
-        <v>100</v>
-      </c>
-      <c r="P20" s="21">
-        <v>96</v>
-      </c>
-      <c r="Q20" s="20">
-        <v>61</v>
-      </c>
-      <c r="R20" s="13">
-        <v>100</v>
+        <v>216</v>
+      </c>
+      <c r="O20" s="9">
+        <v>67</v>
+      </c>
+      <c r="P20" s="11">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>2</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2506,55 +2509,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>89</v>
       </c>
       <c r="L21" s="4">
-        <v>-21.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O21" s="12">
-        <v>100</v>
-      </c>
-      <c r="P21" s="22">
-        <v>79</v>
-      </c>
-      <c r="Q21" s="23">
-        <v>77</v>
-      </c>
-      <c r="R21" s="13">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O21" s="9">
+        <v>70</v>
+      </c>
+      <c r="P21" s="23">
+        <v>57</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>4</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2562,55 +2565,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>90</v>
       </c>
       <c r="L22" s="4">
-        <v>-14</v>
+        <v>-22.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O22" s="12">
-        <v>100</v>
-      </c>
-      <c r="P22" s="23">
-        <v>73</v>
-      </c>
-      <c r="Q22" s="18">
-        <v>83</v>
-      </c>
-      <c r="R22" s="13">
-        <v>100</v>
+        <v>217</v>
+      </c>
+      <c r="O22" s="9">
+        <v>64</v>
+      </c>
+      <c r="P22" s="18">
+        <v>41</v>
+      </c>
+      <c r="Q22" s="24">
+        <v>9</v>
+      </c>
+      <c r="R22" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2624,49 +2627,49 @@
         <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="L23" s="4">
-        <v>-12.3</v>
+        <v>-17.6</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O23" s="12">
-        <v>48</v>
-      </c>
-      <c r="P23" s="24">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>8</v>
-      </c>
-      <c r="R23" s="25">
-        <v>19</v>
+        <v>216</v>
+      </c>
+      <c r="O23" s="9">
+        <v>56</v>
+      </c>
+      <c r="P23" s="25">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="24">
+        <v>9</v>
+      </c>
+      <c r="R23" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2674,55 +2677,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="L24" s="4">
-        <v>-20.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O24" s="12">
-        <v>50</v>
+        <v>216</v>
+      </c>
+      <c r="O24" s="9">
+        <v>31</v>
       </c>
       <c r="P24" s="26">
-        <v>23</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>7</v>
-      </c>
-      <c r="R24" s="11">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="Q24" s="26">
+        <v>13</v>
+      </c>
+      <c r="R24" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2730,114 +2733,170 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="L25" s="4">
-        <v>-22.2</v>
+        <v>-17.1</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O25" s="12">
-        <v>46</v>
-      </c>
-      <c r="P25" s="27">
-        <v>14</v>
+        <v>215</v>
+      </c>
+      <c r="O25" s="27">
+        <v>7</v>
+      </c>
+      <c r="P25" s="8">
+        <v>4</v>
       </c>
       <c r="Q25" s="8">
-        <v>4</v>
-      </c>
-      <c r="R25" s="28">
-        <v>36</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2">
+        <v>31</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-21.9</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O26" s="6">
+        <v>1</v>
+      </c>
+      <c r="P26" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>1</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A2:A26">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B25">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C25">
+  <conditionalFormatting sqref="C2:C26">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D25">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G25">
+  <conditionalFormatting sqref="G2:G26">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H25">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J25">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K25">
+  <conditionalFormatting sqref="K2:K26">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L25">
+  <conditionalFormatting sqref="L2:L26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2856,12 +2915,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M25">
+  <conditionalFormatting sqref="M2:M26">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N25">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2878,22 +2937,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O25">
+  <conditionalFormatting sqref="O2:O26">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P25">
+  <conditionalFormatting sqref="P2:P26">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q25">
+  <conditionalFormatting sqref="Q2:Q26">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
+  <conditionalFormatting sqref="R2:R26">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="220">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260502--01</t>
-  </si>
-  <si>
-    <t>20260502--02</t>
-  </si>
-  <si>
-    <t>20260502--03</t>
-  </si>
-  <si>
-    <t>20260502--04</t>
-  </si>
-  <si>
     <t>20260503--01</t>
   </si>
   <si>
@@ -145,79 +133,94 @@
     <t>20260508--04</t>
   </si>
   <si>
-    <t>06:07</t>
+    <t>20260509--01</t>
+  </si>
+  <si>
+    <t>20260509--02</t>
+  </si>
+  <si>
+    <t>20260509--03</t>
+  </si>
+  <si>
+    <t>20260509--04</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:46</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>03:40</t>
   </si>
   <si>
     <t>06:03</t>
   </si>
   <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>05:59</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>05:46</t>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>03:46</t>
+  </si>
+  <si>
+    <t>02:12</t>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:40</t>
   </si>
   <si>
     <t>06:13</t>
   </si>
   <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>02:24</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>03:46</t>
-  </si>
-  <si>
-    <t>02:12</t>
-  </si>
-  <si>
-    <t>05:54</t>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>02:01</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:56</t>
-  </si>
-  <si>
-    <t>02:01</t>
-  </si>
-  <si>
-    <t>03:02</t>
+    <t>03:01</t>
   </si>
   <si>
     <t>00:41</t>
@@ -226,16 +229,7 @@
     <t>00:36</t>
   </si>
   <si>
-    <t>00:19:29</t>
-  </si>
-  <si>
-    <t>01:56:44</t>
-  </si>
-  <si>
-    <t>22:00:22</t>
-  </si>
-  <si>
-    <t>23:36:39</t>
+    <t>03:13</t>
   </si>
   <si>
     <t>01:13:50</t>
@@ -250,67 +244,67 @@
     <t>02:08:20</t>
   </si>
   <si>
-    <t>22:10:52</t>
-  </si>
-  <si>
-    <t>23:47:50</t>
-  </si>
-  <si>
-    <t>01:25:14</t>
-  </si>
-  <si>
-    <t>21:27:56</t>
-  </si>
-  <si>
-    <t>23:04:46</t>
-  </si>
-  <si>
-    <t>00:42:06</t>
-  </si>
-  <si>
-    <t>20:44:59</t>
-  </si>
-  <si>
-    <t>22:21:38</t>
-  </si>
-  <si>
-    <t>23:58:55</t>
-  </si>
-  <si>
-    <t>01:36:37</t>
-  </si>
-  <si>
-    <t>20:02:02</t>
-  </si>
-  <si>
-    <t>21:38:28</t>
-  </si>
-  <si>
-    <t>23:15:40</t>
-  </si>
-  <si>
-    <t>00:53:16</t>
-  </si>
-  <si>
-    <t>19:19:05</t>
-  </si>
-  <si>
-    <t>20:55:15</t>
-  </si>
-  <si>
-    <t>22:32:23</t>
-  </si>
-  <si>
-    <t>00:21:46</t>
-  </si>
-  <si>
-    <t>01:59:02</t>
-  </si>
-  <si>
-    <t>22:03:32</t>
-  </si>
-  <si>
-    <t>23:38:57</t>
+    <t>22:10:54</t>
+  </si>
+  <si>
+    <t>23:47:51</t>
+  </si>
+  <si>
+    <t>01:25:16</t>
+  </si>
+  <si>
+    <t>21:27:59</t>
+  </si>
+  <si>
+    <t>23:04:48</t>
+  </si>
+  <si>
+    <t>00:42:09</t>
+  </si>
+  <si>
+    <t>20:45:03</t>
+  </si>
+  <si>
+    <t>22:21:42</t>
+  </si>
+  <si>
+    <t>23:58:59</t>
+  </si>
+  <si>
+    <t>01:36:41</t>
+  </si>
+  <si>
+    <t>20:02:07</t>
+  </si>
+  <si>
+    <t>21:38:34</t>
+  </si>
+  <si>
+    <t>23:15:46</t>
+  </si>
+  <si>
+    <t>00:53:21</t>
+  </si>
+  <si>
+    <t>19:19:12</t>
+  </si>
+  <si>
+    <t>20:55:23</t>
+  </si>
+  <si>
+    <t>22:32:30</t>
+  </si>
+  <si>
+    <t>00:10:00</t>
+  </si>
+  <si>
+    <t>20:12:11</t>
+  </si>
+  <si>
+    <t>21:49:12</t>
+  </si>
+  <si>
+    <t>23:26:37</t>
   </si>
   <si>
     <t>01:16:06</t>
@@ -325,142 +319,142 @@
     <t>02:10:53</t>
   </si>
   <si>
-    <t>22:13:17</t>
-  </si>
-  <si>
-    <t>23:50:05</t>
-  </si>
-  <si>
-    <t>01:27:41</t>
-  </si>
-  <si>
-    <t>21:30:27</t>
-  </si>
-  <si>
-    <t>23:07:01</t>
-  </si>
-  <si>
-    <t>00:44:28</t>
-  </si>
-  <si>
-    <t>20:47:39</t>
-  </si>
-  <si>
-    <t>22:23:54</t>
-  </si>
-  <si>
-    <t>00:01:14</t>
-  </si>
-  <si>
-    <t>01:39:57</t>
-  </si>
-  <si>
-    <t>20:04:56</t>
-  </si>
-  <si>
-    <t>21:40:45</t>
-  </si>
-  <si>
-    <t>23:17:58</t>
-  </si>
-  <si>
-    <t>00:56:08</t>
-  </si>
-  <si>
-    <t>19:22:29</t>
-  </si>
-  <si>
-    <t>20:57:35</t>
-  </si>
-  <si>
-    <t>22:34:39</t>
-  </si>
-  <si>
-    <t>00:24:49</t>
-  </si>
-  <si>
-    <t>02:02:04</t>
-  </si>
-  <si>
-    <t>22:04:57</t>
-  </si>
-  <si>
-    <t>23:41:56</t>
+    <t>22:13:18</t>
+  </si>
+  <si>
+    <t>23:50:06</t>
+  </si>
+  <si>
+    <t>01:27:42</t>
+  </si>
+  <si>
+    <t>21:30:29</t>
+  </si>
+  <si>
+    <t>23:07:03</t>
+  </si>
+  <si>
+    <t>00:44:31</t>
+  </si>
+  <si>
+    <t>20:47:42</t>
+  </si>
+  <si>
+    <t>22:23:58</t>
+  </si>
+  <si>
+    <t>00:01:18</t>
+  </si>
+  <si>
+    <t>01:40:02</t>
+  </si>
+  <si>
+    <t>20:05:01</t>
+  </si>
+  <si>
+    <t>21:40:51</t>
+  </si>
+  <si>
+    <t>23:18:03</t>
+  </si>
+  <si>
+    <t>00:56:14</t>
+  </si>
+  <si>
+    <t>19:22:36</t>
+  </si>
+  <si>
+    <t>20:57:42</t>
+  </si>
+  <si>
+    <t>22:34:46</t>
+  </si>
+  <si>
+    <t>00:12:39</t>
+  </si>
+  <si>
+    <t>20:14:33</t>
+  </si>
+  <si>
+    <t>21:51:27</t>
+  </si>
+  <si>
+    <t>23:29:08</t>
   </si>
   <si>
     <t>01:19:11</t>
   </si>
   <si>
-    <t>22:59:00</t>
-  </si>
-  <si>
-    <t>00:36:13</t>
+    <t>22:59:01</t>
+  </si>
+  <si>
+    <t>00:36:14</t>
   </si>
   <si>
     <t>02:13:22</t>
   </si>
   <si>
-    <t>22:16:01</t>
-  </si>
-  <si>
-    <t>23:53:12</t>
-  </si>
-  <si>
-    <t>01:30:23</t>
-  </si>
-  <si>
-    <t>21:32:59</t>
-  </si>
-  <si>
-    <t>23:10:08</t>
-  </si>
-  <si>
-    <t>00:47:19</t>
-  </si>
-  <si>
-    <t>20:49:54</t>
-  </si>
-  <si>
-    <t>22:26:59</t>
-  </si>
-  <si>
-    <t>00:04:12</t>
-  </si>
-  <si>
-    <t>01:41:10</t>
-  </si>
-  <si>
-    <t>20:06:46</t>
-  </si>
-  <si>
-    <t>21:43:47</t>
-  </si>
-  <si>
-    <t>23:21:00</t>
-  </si>
-  <si>
-    <t>00:58:01</t>
-  </si>
-  <si>
-    <t>19:23:35</t>
-  </si>
-  <si>
-    <t>21:00:32</t>
-  </si>
-  <si>
-    <t>22:37:44</t>
-  </si>
-  <si>
-    <t>00:27:53</t>
-  </si>
-  <si>
-    <t>02:05:05</t>
-  </si>
-  <si>
-    <t>22:06:22</t>
-  </si>
-  <si>
-    <t>23:44:56</t>
+    <t>22:16:02</t>
+  </si>
+  <si>
+    <t>23:53:14</t>
+  </si>
+  <si>
+    <t>01:30:24</t>
+  </si>
+  <si>
+    <t>21:33:01</t>
+  </si>
+  <si>
+    <t>23:10:10</t>
+  </si>
+  <si>
+    <t>00:47:22</t>
+  </si>
+  <si>
+    <t>20:49:57</t>
+  </si>
+  <si>
+    <t>22:27:03</t>
+  </si>
+  <si>
+    <t>00:04:16</t>
+  </si>
+  <si>
+    <t>01:41:13</t>
+  </si>
+  <si>
+    <t>20:06:51</t>
+  </si>
+  <si>
+    <t>21:43:52</t>
+  </si>
+  <si>
+    <t>23:21:05</t>
+  </si>
+  <si>
+    <t>00:58:07</t>
+  </si>
+  <si>
+    <t>19:23:42</t>
+  </si>
+  <si>
+    <t>21:00:39</t>
+  </si>
+  <si>
+    <t>22:37:51</t>
+  </si>
+  <si>
+    <t>00:14:56</t>
+  </si>
+  <si>
+    <t>20:17:23</t>
+  </si>
+  <si>
+    <t>21:54:34</t>
+  </si>
+  <si>
+    <t>23:31:41</t>
   </si>
   <si>
     <t>01:22:16</t>
@@ -469,163 +463,169 @@
     <t>23:01:54</t>
   </si>
   <si>
-    <t>00:39:20</t>
+    <t>00:39:21</t>
   </si>
   <si>
     <t>02:15:51</t>
   </si>
   <si>
-    <t>22:18:46</t>
-  </si>
-  <si>
-    <t>23:56:20</t>
-  </si>
-  <si>
-    <t>01:33:05</t>
-  </si>
-  <si>
-    <t>21:35:32</t>
-  </si>
-  <si>
-    <t>23:13:14</t>
-  </si>
-  <si>
-    <t>00:50:11</t>
-  </si>
-  <si>
-    <t>20:52:09</t>
-  </si>
-  <si>
-    <t>22:30:04</t>
-  </si>
-  <si>
-    <t>00:07:10</t>
-  </si>
-  <si>
-    <t>01:42:21</t>
-  </si>
-  <si>
-    <t>20:08:36</t>
-  </si>
-  <si>
-    <t>21:46:49</t>
-  </si>
-  <si>
-    <t>23:24:02</t>
-  </si>
-  <si>
-    <t>00:59:54</t>
-  </si>
-  <si>
-    <t>19:24:41</t>
-  </si>
-  <si>
-    <t>21:03:29</t>
-  </si>
-  <si>
-    <t>22:40:49</t>
-  </si>
-  <si>
-    <t>00:30:10</t>
-  </si>
-  <si>
-    <t>02:07:23</t>
-  </si>
-  <si>
-    <t>22:09:33</t>
-  </si>
-  <si>
-    <t>23:47:15</t>
+    <t>22:18:47</t>
+  </si>
+  <si>
+    <t>23:56:21</t>
+  </si>
+  <si>
+    <t>01:33:06</t>
+  </si>
+  <si>
+    <t>21:35:34</t>
+  </si>
+  <si>
+    <t>23:13:17</t>
+  </si>
+  <si>
+    <t>00:50:13</t>
+  </si>
+  <si>
+    <t>20:52:13</t>
+  </si>
+  <si>
+    <t>22:30:08</t>
+  </si>
+  <si>
+    <t>00:07:13</t>
+  </si>
+  <si>
+    <t>01:42:25</t>
+  </si>
+  <si>
+    <t>20:08:41</t>
+  </si>
+  <si>
+    <t>21:46:54</t>
+  </si>
+  <si>
+    <t>23:24:08</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>19:24:48</t>
+  </si>
+  <si>
+    <t>21:03:36</t>
+  </si>
+  <si>
+    <t>22:40:57</t>
+  </si>
+  <si>
+    <t>00:17:13</t>
+  </si>
+  <si>
+    <t>20:20:13</t>
+  </si>
+  <si>
+    <t>21:57:40</t>
+  </si>
+  <si>
+    <t>23:34:15</t>
   </si>
   <si>
     <t>01:24:32</t>
   </si>
   <si>
-    <t>23:04:15</t>
+    <t>23:04:16</t>
   </si>
   <si>
     <t>00:41:36</t>
   </si>
   <si>
-    <t>02:18:23</t>
-  </si>
-  <si>
-    <t>22:21:11</t>
-  </si>
-  <si>
-    <t>23:58:35</t>
-  </si>
-  <si>
-    <t>01:35:31</t>
-  </si>
-  <si>
-    <t>21:38:03</t>
-  </si>
-  <si>
-    <t>23:15:30</t>
-  </si>
-  <si>
-    <t>00:52:33</t>
-  </si>
-  <si>
-    <t>20:54:49</t>
-  </si>
-  <si>
-    <t>22:32:20</t>
-  </si>
-  <si>
-    <t>00:09:29</t>
-  </si>
-  <si>
-    <t>01:45:41</t>
-  </si>
-  <si>
-    <t>20:11:31</t>
-  </si>
-  <si>
-    <t>21:49:06</t>
-  </si>
-  <si>
-    <t>23:26:19</t>
-  </si>
-  <si>
-    <t>01:02:47</t>
-  </si>
-  <si>
-    <t>19:28:06</t>
-  </si>
-  <si>
-    <t>21:05:48</t>
-  </si>
-  <si>
-    <t>22:43:05</t>
+    <t>02:18:24</t>
+  </si>
+  <si>
+    <t>22:21:12</t>
+  </si>
+  <si>
+    <t>23:58:36</t>
+  </si>
+  <si>
+    <t>01:35:32</t>
+  </si>
+  <si>
+    <t>21:38:05</t>
+  </si>
+  <si>
+    <t>23:15:32</t>
+  </si>
+  <si>
+    <t>00:52:35</t>
+  </si>
+  <si>
+    <t>20:54:53</t>
+  </si>
+  <si>
+    <t>22:32:24</t>
+  </si>
+  <si>
+    <t>00:09:32</t>
+  </si>
+  <si>
+    <t>01:45:45</t>
+  </si>
+  <si>
+    <t>20:11:36</t>
+  </si>
+  <si>
+    <t>23:26:25</t>
+  </si>
+  <si>
+    <t>01:02:52</t>
+  </si>
+  <si>
+    <t>19:28:13</t>
+  </si>
+  <si>
+    <t>21:05:56</t>
+  </si>
+  <si>
+    <t>22:43:12</t>
+  </si>
+  <si>
+    <t>00:19:52</t>
+  </si>
+  <si>
+    <t>20:22:35</t>
+  </si>
+  <si>
+    <t>21:59:55</t>
+  </si>
+  <si>
+    <t>23:36:45</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>14°</t>
   </si>
   <si>
     <t>10°</t>
   </si>
   <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>02:01:09</t>
-  </si>
-  <si>
-    <t>23:46:59</t>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>8°</t>
   </si>
   <si>
     <t>01:20:15</t>
@@ -634,22 +634,28 @@
     <t>00:39:32</t>
   </si>
   <si>
-    <t>02:12:49</t>
-  </si>
-  <si>
-    <t>01:32:24</t>
-  </si>
-  <si>
-    <t>00:52:24</t>
-  </si>
-  <si>
-    <t>20:04:49</t>
-  </si>
-  <si>
-    <t>19:24:52</t>
-  </si>
-  <si>
-    <t>20:58:11</t>
+    <t>02:12:50</t>
+  </si>
+  <si>
+    <t>01:32:25</t>
+  </si>
+  <si>
+    <t>00:52:26</t>
+  </si>
+  <si>
+    <t>20:04:53</t>
+  </si>
+  <si>
+    <t>19:24:59</t>
+  </si>
+  <si>
+    <t>20:58:18</t>
+  </si>
+  <si>
+    <t>20:17:46</t>
+  </si>
+  <si>
+    <t>21:51:03</t>
   </si>
   <si>
     <t>A+B</t>
@@ -664,10 +670,10 @@
     <t>2</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -701,7 +707,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,7 +722,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +734,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,7 +746,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,19 +806,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,73 +830,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,15 +943,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1445,46 +1424,46 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="L2" s="4">
-        <v>-21.5</v>
+        <v>-17.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O2" s="6">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="P2" s="7">
         <v>0</v>
@@ -1493,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1501,55 +1480,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>202</v>
+        <v>73</v>
       </c>
       <c r="L3" s="4">
-        <v>-13.1</v>
+        <v>-23.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
+        <v>218</v>
+      </c>
+      <c r="O3" s="9">
+        <v>100</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>4</v>
+      <c r="Q3" s="10">
+        <v>94</v>
+      </c>
+      <c r="R3" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1557,55 +1536,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L4" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="O4" s="9">
         <v>97</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-22.6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O4" s="9">
-        <v>82</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="7">
-        <v>0</v>
+      <c r="Q4" s="12">
+        <v>89</v>
       </c>
       <c r="R4" s="10">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1613,55 +1592,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L5" s="4">
-        <v>-23.1</v>
+        <v>-11.3</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O5" s="9">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>64</v>
+      <c r="Q5" s="11">
+        <v>100</v>
+      </c>
+      <c r="R5" s="13">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1669,55 +1648,55 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>204</v>
+        <v>76</v>
       </c>
       <c r="L6" s="4">
-        <v>-17.2</v>
+        <v>-22.4</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O6" s="9">
-        <v>68</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="P6" s="13">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>95</v>
+      </c>
+      <c r="R6" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1725,55 +1704,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L7" s="4">
-        <v>-23.5</v>
+        <v>-22.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O7" s="9">
         <v>100</v>
       </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>70</v>
-      </c>
-      <c r="R7" s="12">
-        <v>100</v>
+      <c r="P7" s="14">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>100</v>
+      </c>
+      <c r="R7" s="11">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1781,40 +1760,40 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L8" s="4">
-        <v>-20.2</v>
+        <v>-15.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>217</v>
@@ -1822,13 +1801,13 @@
       <c r="O8" s="9">
         <v>100</v>
       </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>100</v>
-      </c>
-      <c r="R8" s="12">
+      <c r="P8" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>100</v>
+      </c>
+      <c r="R8" s="11">
         <v>100</v>
       </c>
     </row>
@@ -1846,46 +1825,46 @@
         <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="L9" s="4">
-        <v>-11.3</v>
+        <v>-20.2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O9" s="9">
-        <v>86</v>
-      </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>86</v>
-      </c>
-      <c r="R9" s="14">
-        <v>44</v>
+        <v>100</v>
+      </c>
+      <c r="P9" s="12">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>100</v>
+      </c>
+      <c r="R9" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1893,54 +1872,54 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4">
-        <v>-22.4</v>
+        <v>-22.9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O10" s="9">
         <v>100</v>
       </c>
-      <c r="P10" s="15">
-        <v>22</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>82</v>
-      </c>
-      <c r="R10" s="12">
+      <c r="P10" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>100</v>
+      </c>
+      <c r="R10" s="11">
         <v>100</v>
       </c>
     </row>
@@ -1949,54 +1928,54 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="L11" s="4">
-        <v>-22.2</v>
+        <v>-18.9</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O11" s="9">
         <v>100</v>
       </c>
-      <c r="P11" s="17">
-        <v>29</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>43</v>
-      </c>
-      <c r="R11" s="12">
+      <c r="P11" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>100</v>
+      </c>
+      <c r="R11" s="11">
         <v>100</v>
       </c>
     </row>
@@ -2005,55 +1984,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="L12" s="4">
-        <v>-15.5</v>
+        <v>-16.7</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12" s="18">
-        <v>40</v>
+      <c r="P12" s="11">
+        <v>100</v>
       </c>
       <c r="Q12" s="10">
-        <v>70</v>
-      </c>
-      <c r="R12" s="12">
-        <v>100</v>
+        <v>97</v>
+      </c>
+      <c r="R12" s="8">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2061,55 +2040,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L13" s="4">
-        <v>-20.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O13" s="9">
         <v>100</v>
       </c>
-      <c r="P13" s="12">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="19">
-        <v>58</v>
-      </c>
-      <c r="R13" s="20">
-        <v>90</v>
+      <c r="P13" s="11">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>72</v>
+      </c>
+      <c r="R13" s="10">
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2117,55 +2096,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L14" s="4">
-        <v>-22.9</v>
+        <v>-21.2</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O14" s="9">
-        <v>99</v>
-      </c>
-      <c r="P14" s="21">
+        <v>100</v>
+      </c>
+      <c r="P14" s="10">
         <v>96</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="16">
         <v>76</v>
       </c>
-      <c r="R14" s="12">
-        <v>99</v>
+      <c r="R14" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2173,54 +2152,54 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>208</v>
+        <v>85</v>
       </c>
       <c r="L15" s="4">
-        <v>-18.9</v>
+        <v>-14</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O15" s="9">
         <v>100</v>
       </c>
-      <c r="P15" s="20">
-        <v>91</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>74</v>
-      </c>
-      <c r="R15" s="12">
+      <c r="P15" s="10">
+        <v>95</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>71</v>
+      </c>
+      <c r="R15" s="11">
         <v>100</v>
       </c>
     </row>
@@ -2229,55 +2208,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="L16" s="4">
-        <v>-16.7</v>
+        <v>-12.3</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O16" s="9">
         <v>100</v>
       </c>
-      <c r="P16" s="21">
-        <v>95</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>99</v>
-      </c>
-      <c r="R16" s="12">
-        <v>100</v>
+      <c r="P16" s="10">
+        <v>96</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>80</v>
+      </c>
+      <c r="R16" s="11">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2285,55 +2264,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L17" s="4">
-        <v>-22.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O17" s="9">
         <v>100</v>
       </c>
-      <c r="P17" s="12">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="12">
-        <v>100</v>
-      </c>
-      <c r="R17" s="12">
-        <v>100</v>
+      <c r="P17" s="10">
+        <v>93</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>75</v>
+      </c>
+      <c r="R17" s="10">
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2341,55 +2320,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>-21.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O18" s="9">
-        <v>100</v>
-      </c>
-      <c r="P18" s="12">
         <v>98</v>
       </c>
-      <c r="Q18" s="12">
-        <v>100</v>
-      </c>
-      <c r="R18" s="12">
-        <v>100</v>
+      <c r="P18" s="18">
+        <v>87</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>67</v>
+      </c>
+      <c r="R18" s="17">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2397,55 +2376,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L19" s="4">
-        <v>-14</v>
+        <v>-17.6</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O19" s="9">
-        <v>100</v>
-      </c>
-      <c r="P19" s="12">
-        <v>98</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>99</v>
-      </c>
-      <c r="R19" s="12">
-        <v>100</v>
+        <v>97</v>
+      </c>
+      <c r="P19" s="18">
+        <v>85</v>
+      </c>
+      <c r="Q19" s="19">
+        <v>64</v>
+      </c>
+      <c r="R19" s="8">
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2453,52 +2432,52 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L20" s="4">
-        <v>-12.3</v>
+        <v>-7.1</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O20" s="9">
-        <v>67</v>
-      </c>
-      <c r="P20" s="11">
-        <v>65</v>
+        <v>46</v>
+      </c>
+      <c r="P20" s="20">
+        <v>45</v>
       </c>
       <c r="Q20" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" s="7">
         <v>0</v>
@@ -2509,52 +2488,52 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="L21" s="4">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>217</v>
       </c>
       <c r="O21" s="9">
-        <v>70</v>
-      </c>
-      <c r="P21" s="23">
-        <v>57</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="P21" s="15">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>1</v>
       </c>
       <c r="R21" s="7">
         <v>0</v>
@@ -2565,52 +2544,52 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L22" s="4">
-        <v>-22.2</v>
+        <v>-21.9</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O22" s="9">
-        <v>64</v>
-      </c>
-      <c r="P22" s="18">
-        <v>41</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>9</v>
+        <v>54</v>
+      </c>
+      <c r="P22" s="21">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>3</v>
       </c>
       <c r="R22" s="7">
         <v>0</v>
@@ -2621,55 +2600,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L23" s="4">
-        <v>-17.6</v>
+        <v>-20.1</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O23" s="9">
-        <v>56</v>
-      </c>
-      <c r="P23" s="25">
-        <v>33</v>
-      </c>
-      <c r="Q23" s="24">
+        <v>60</v>
+      </c>
+      <c r="P23" s="23">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>2</v>
+      </c>
+      <c r="R23" s="13">
         <v>9</v>
-      </c>
-      <c r="R23" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2677,55 +2656,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L24" s="4">
-        <v>-7.1</v>
+        <v>-13</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>214</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O24" s="9">
-        <v>31</v>
-      </c>
-      <c r="P24" s="26">
-        <v>15</v>
-      </c>
-      <c r="Q24" s="26">
-        <v>13</v>
-      </c>
-      <c r="R24" s="7">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="P24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>44</v>
+      </c>
+      <c r="R24" s="15">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2733,55 +2712,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L25" s="4">
-        <v>-17.1</v>
+        <v>-20.2</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="O25" s="27">
-        <v>7</v>
-      </c>
-      <c r="P25" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>7</v>
-      </c>
-      <c r="R25" s="7">
+        <v>218</v>
+      </c>
+      <c r="O25" s="6">
+        <v>44</v>
+      </c>
+      <c r="P25" s="7">
         <v>0</v>
+      </c>
+      <c r="Q25" s="24">
+        <v>31</v>
+      </c>
+      <c r="R25" s="14">
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2789,55 +2768,55 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>197</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L26" s="4">
-        <v>-21.9</v>
+        <v>-21.5</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O26" s="6">
-        <v>1</v>
-      </c>
-      <c r="P26" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="7">
-        <v>1</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P26" s="22">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="14">
+        <v>13</v>
+      </c>
+      <c r="R26" s="22">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="227">
   <si>
     <t>Datum</t>
   </si>
@@ -70,12 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260503--01</t>
-  </si>
-  <si>
-    <t>20260503--02</t>
-  </si>
-  <si>
     <t>20260504--01</t>
   </si>
   <si>
@@ -145,52 +139,55 @@
     <t>20260509--04</t>
   </si>
   <si>
+    <t>20260510--01</t>
+  </si>
+  <si>
+    <t>20260510--02</t>
+  </si>
+  <si>
+    <t>20260510--03</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>05:43</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>05:46</t>
-  </si>
-  <si>
-    <t>06:14</t>
-  </si>
-  <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>05:29</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:31</t>
-  </si>
-  <si>
     <t>05:55</t>
   </si>
   <si>
     <t>02:23</t>
   </si>
   <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:03</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>03:46</t>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>03:45</t>
   </si>
   <si>
     <t>02:12</t>
@@ -199,22 +196,19 @@
     <t>05:54</t>
   </si>
   <si>
-    <t>06:11</t>
-  </si>
-  <si>
     <t>04:34</t>
   </si>
   <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>02:01</t>
+    <t>05:08</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:31</t>
   </si>
   <si>
     <t>00:00</t>
@@ -223,7 +217,7 @@
     <t>03:01</t>
   </si>
   <si>
-    <t>00:41</t>
+    <t>00:40</t>
   </si>
   <si>
     <t>00:36</t>
@@ -232,10 +226,7 @@
     <t>03:13</t>
   </si>
   <si>
-    <t>01:13:50</t>
-  </si>
-  <si>
-    <t>22:53:47</t>
+    <t>01:57</t>
   </si>
   <si>
     <t>00:30:52</t>
@@ -247,7 +238,7 @@
     <t>22:10:54</t>
   </si>
   <si>
-    <t>23:47:51</t>
+    <t>23:47:52</t>
   </si>
   <si>
     <t>01:25:16</t>
@@ -256,61 +247,64 @@
     <t>21:27:59</t>
   </si>
   <si>
-    <t>23:04:48</t>
+    <t>23:04:49</t>
   </si>
   <si>
     <t>00:42:09</t>
   </si>
   <si>
-    <t>20:45:03</t>
-  </si>
-  <si>
-    <t>22:21:42</t>
-  </si>
-  <si>
-    <t>23:58:59</t>
-  </si>
-  <si>
-    <t>01:36:41</t>
-  </si>
-  <si>
-    <t>20:02:07</t>
-  </si>
-  <si>
-    <t>21:38:34</t>
-  </si>
-  <si>
-    <t>23:15:46</t>
-  </si>
-  <si>
-    <t>00:53:21</t>
-  </si>
-  <si>
-    <t>19:19:12</t>
-  </si>
-  <si>
-    <t>20:55:23</t>
-  </si>
-  <si>
-    <t>22:32:30</t>
-  </si>
-  <si>
-    <t>00:10:00</t>
-  </si>
-  <si>
-    <t>20:12:11</t>
-  </si>
-  <si>
-    <t>21:49:12</t>
-  </si>
-  <si>
-    <t>23:26:37</t>
-  </si>
-  <si>
-    <t>01:16:06</t>
-  </si>
-  <si>
-    <t>22:56:08</t>
+    <t>20:45:04</t>
+  </si>
+  <si>
+    <t>22:21:43</t>
+  </si>
+  <si>
+    <t>23:59:00</t>
+  </si>
+  <si>
+    <t>01:36:42</t>
+  </si>
+  <si>
+    <t>20:02:09</t>
+  </si>
+  <si>
+    <t>21:38:35</t>
+  </si>
+  <si>
+    <t>23:15:47</t>
+  </si>
+  <si>
+    <t>00:53:23</t>
+  </si>
+  <si>
+    <t>19:19:14</t>
+  </si>
+  <si>
+    <t>20:55:25</t>
+  </si>
+  <si>
+    <t>22:32:32</t>
+  </si>
+  <si>
+    <t>00:10:02</t>
+  </si>
+  <si>
+    <t>20:12:13</t>
+  </si>
+  <si>
+    <t>21:49:14</t>
+  </si>
+  <si>
+    <t>23:26:40</t>
+  </si>
+  <si>
+    <t>19:29:00</t>
+  </si>
+  <si>
+    <t>21:05:54</t>
+  </si>
+  <si>
+    <t>22:43:15</t>
   </si>
   <si>
     <t>00:33:07</t>
@@ -319,73 +313,76 @@
     <t>02:10:53</t>
   </si>
   <si>
-    <t>22:13:18</t>
-  </si>
-  <si>
-    <t>23:50:06</t>
+    <t>22:13:19</t>
+  </si>
+  <si>
+    <t>23:50:07</t>
   </si>
   <si>
     <t>01:27:42</t>
   </si>
   <si>
-    <t>21:30:29</t>
-  </si>
-  <si>
-    <t>23:07:03</t>
+    <t>21:30:30</t>
+  </si>
+  <si>
+    <t>23:07:04</t>
   </si>
   <si>
     <t>00:44:31</t>
   </si>
   <si>
-    <t>20:47:42</t>
-  </si>
-  <si>
-    <t>22:23:58</t>
-  </si>
-  <si>
-    <t>00:01:18</t>
-  </si>
-  <si>
-    <t>01:40:02</t>
-  </si>
-  <si>
-    <t>20:05:01</t>
-  </si>
-  <si>
-    <t>21:40:51</t>
-  </si>
-  <si>
-    <t>23:18:03</t>
-  </si>
-  <si>
-    <t>00:56:14</t>
-  </si>
-  <si>
-    <t>19:22:36</t>
-  </si>
-  <si>
-    <t>20:57:42</t>
-  </si>
-  <si>
-    <t>22:34:46</t>
-  </si>
-  <si>
-    <t>00:12:39</t>
-  </si>
-  <si>
-    <t>20:14:33</t>
-  </si>
-  <si>
-    <t>21:51:27</t>
-  </si>
-  <si>
-    <t>23:29:08</t>
-  </si>
-  <si>
-    <t>01:19:11</t>
-  </si>
-  <si>
-    <t>22:59:01</t>
+    <t>20:47:43</t>
+  </si>
+  <si>
+    <t>22:23:59</t>
+  </si>
+  <si>
+    <t>00:01:19</t>
+  </si>
+  <si>
+    <t>01:40:03</t>
+  </si>
+  <si>
+    <t>20:05:03</t>
+  </si>
+  <si>
+    <t>21:40:52</t>
+  </si>
+  <si>
+    <t>23:18:05</t>
+  </si>
+  <si>
+    <t>00:56:16</t>
+  </si>
+  <si>
+    <t>19:22:38</t>
+  </si>
+  <si>
+    <t>20:57:44</t>
+  </si>
+  <si>
+    <t>22:34:48</t>
+  </si>
+  <si>
+    <t>00:12:41</t>
+  </si>
+  <si>
+    <t>20:14:35</t>
+  </si>
+  <si>
+    <t>21:51:30</t>
+  </si>
+  <si>
+    <t>23:29:10</t>
+  </si>
+  <si>
+    <t>19:31:27</t>
+  </si>
+  <si>
+    <t>21:08:09</t>
+  </si>
+  <si>
+    <t>22:45:40</t>
   </si>
   <si>
     <t>00:36:14</t>
@@ -394,7 +391,7 @@
     <t>02:13:22</t>
   </si>
   <si>
-    <t>22:16:02</t>
+    <t>22:16:03</t>
   </si>
   <si>
     <t>23:53:14</t>
@@ -403,7 +400,7 @@
     <t>01:30:24</t>
   </si>
   <si>
-    <t>21:33:01</t>
+    <t>21:33:02</t>
   </si>
   <si>
     <t>23:10:10</t>
@@ -412,55 +409,58 @@
     <t>00:47:22</t>
   </si>
   <si>
-    <t>20:49:57</t>
-  </si>
-  <si>
-    <t>22:27:03</t>
-  </si>
-  <si>
-    <t>00:04:16</t>
-  </si>
-  <si>
-    <t>01:41:13</t>
-  </si>
-  <si>
-    <t>20:06:51</t>
-  </si>
-  <si>
-    <t>21:43:52</t>
-  </si>
-  <si>
-    <t>23:21:05</t>
-  </si>
-  <si>
-    <t>00:58:07</t>
-  </si>
-  <si>
-    <t>19:23:42</t>
-  </si>
-  <si>
-    <t>21:00:39</t>
-  </si>
-  <si>
-    <t>22:37:51</t>
-  </si>
-  <si>
-    <t>00:14:56</t>
-  </si>
-  <si>
-    <t>20:17:23</t>
-  </si>
-  <si>
-    <t>21:54:34</t>
-  </si>
-  <si>
-    <t>23:31:41</t>
-  </si>
-  <si>
-    <t>01:22:16</t>
-  </si>
-  <si>
-    <t>23:01:54</t>
+    <t>20:49:58</t>
+  </si>
+  <si>
+    <t>22:27:04</t>
+  </si>
+  <si>
+    <t>00:04:17</t>
+  </si>
+  <si>
+    <t>01:41:14</t>
+  </si>
+  <si>
+    <t>20:06:52</t>
+  </si>
+  <si>
+    <t>21:43:54</t>
+  </si>
+  <si>
+    <t>23:21:07</t>
+  </si>
+  <si>
+    <t>00:58:08</t>
+  </si>
+  <si>
+    <t>19:23:44</t>
+  </si>
+  <si>
+    <t>21:00:41</t>
+  </si>
+  <si>
+    <t>22:37:53</t>
+  </si>
+  <si>
+    <t>00:14:58</t>
+  </si>
+  <si>
+    <t>20:17:25</t>
+  </si>
+  <si>
+    <t>21:54:36</t>
+  </si>
+  <si>
+    <t>23:31:44</t>
+  </si>
+  <si>
+    <t>19:34:06</t>
+  </si>
+  <si>
+    <t>21:11:15</t>
+  </si>
+  <si>
+    <t>22:48:25</t>
   </si>
   <si>
     <t>00:39:21</t>
@@ -484,58 +484,61 @@
     <t>23:13:17</t>
   </si>
   <si>
-    <t>00:50:13</t>
-  </si>
-  <si>
-    <t>20:52:13</t>
-  </si>
-  <si>
-    <t>22:30:08</t>
-  </si>
-  <si>
-    <t>00:07:13</t>
-  </si>
-  <si>
-    <t>01:42:25</t>
-  </si>
-  <si>
-    <t>20:08:41</t>
-  </si>
-  <si>
-    <t>21:46:54</t>
-  </si>
-  <si>
-    <t>23:24:08</t>
-  </si>
-  <si>
-    <t>01:00:00</t>
-  </si>
-  <si>
-    <t>19:24:48</t>
-  </si>
-  <si>
-    <t>21:03:36</t>
-  </si>
-  <si>
-    <t>22:40:57</t>
-  </si>
-  <si>
-    <t>00:17:13</t>
-  </si>
-  <si>
-    <t>20:20:13</t>
-  </si>
-  <si>
-    <t>21:57:40</t>
-  </si>
-  <si>
-    <t>23:34:15</t>
-  </si>
-  <si>
-    <t>01:24:32</t>
-  </si>
-  <si>
-    <t>23:04:16</t>
+    <t>00:50:14</t>
+  </si>
+  <si>
+    <t>20:52:14</t>
+  </si>
+  <si>
+    <t>22:30:09</t>
+  </si>
+  <si>
+    <t>00:07:14</t>
+  </si>
+  <si>
+    <t>01:42:26</t>
+  </si>
+  <si>
+    <t>20:08:42</t>
+  </si>
+  <si>
+    <t>21:46:56</t>
+  </si>
+  <si>
+    <t>23:24:09</t>
+  </si>
+  <si>
+    <t>01:00:01</t>
+  </si>
+  <si>
+    <t>19:24:50</t>
+  </si>
+  <si>
+    <t>21:03:38</t>
+  </si>
+  <si>
+    <t>22:40:58</t>
+  </si>
+  <si>
+    <t>00:17:15</t>
+  </si>
+  <si>
+    <t>20:20:15</t>
+  </si>
+  <si>
+    <t>21:57:43</t>
+  </si>
+  <si>
+    <t>23:34:18</t>
+  </si>
+  <si>
+    <t>19:36:47</t>
+  </si>
+  <si>
+    <t>21:14:23</t>
+  </si>
+  <si>
+    <t>22:51:11</t>
   </si>
   <si>
     <t>00:41:36</t>
@@ -544,133 +547,151 @@
     <t>02:18:24</t>
   </si>
   <si>
-    <t>22:21:12</t>
+    <t>22:21:13</t>
   </si>
   <si>
     <t>23:58:36</t>
   </si>
   <si>
-    <t>01:35:32</t>
+    <t>01:35:33</t>
   </si>
   <si>
     <t>21:38:05</t>
   </si>
   <si>
-    <t>23:15:32</t>
-  </si>
-  <si>
-    <t>00:52:35</t>
-  </si>
-  <si>
-    <t>20:54:53</t>
-  </si>
-  <si>
-    <t>22:32:24</t>
-  </si>
-  <si>
-    <t>00:09:32</t>
-  </si>
-  <si>
-    <t>01:45:45</t>
-  </si>
-  <si>
-    <t>20:11:36</t>
-  </si>
-  <si>
-    <t>23:26:25</t>
-  </si>
-  <si>
-    <t>01:02:52</t>
-  </si>
-  <si>
-    <t>19:28:13</t>
-  </si>
-  <si>
-    <t>21:05:56</t>
-  </si>
-  <si>
-    <t>22:43:12</t>
-  </si>
-  <si>
-    <t>00:19:52</t>
-  </si>
-  <si>
-    <t>20:22:35</t>
-  </si>
-  <si>
-    <t>21:59:55</t>
-  </si>
-  <si>
-    <t>23:36:45</t>
+    <t>23:15:33</t>
+  </si>
+  <si>
+    <t>00:52:36</t>
+  </si>
+  <si>
+    <t>20:54:54</t>
+  </si>
+  <si>
+    <t>22:32:25</t>
+  </si>
+  <si>
+    <t>00:09:33</t>
+  </si>
+  <si>
+    <t>01:45:46</t>
+  </si>
+  <si>
+    <t>20:11:37</t>
+  </si>
+  <si>
+    <t>21:49:13</t>
+  </si>
+  <si>
+    <t>23:26:26</t>
+  </si>
+  <si>
+    <t>01:02:54</t>
+  </si>
+  <si>
+    <t>19:28:15</t>
+  </si>
+  <si>
+    <t>21:05:57</t>
+  </si>
+  <si>
+    <t>22:43:14</t>
+  </si>
+  <si>
+    <t>00:19:54</t>
+  </si>
+  <si>
+    <t>20:22:38</t>
+  </si>
+  <si>
+    <t>21:59:58</t>
+  </si>
+  <si>
+    <t>23:36:47</t>
+  </si>
+  <si>
+    <t>19:39:14</t>
+  </si>
+  <si>
+    <t>21:16:38</t>
+  </si>
+  <si>
+    <t>22:53:35</t>
+  </si>
+  <si>
+    <t>9°</t>
+  </si>
+  <si>
+    <t>18°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>8°</t>
   </si>
   <si>
     <t>25°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>01:20:15</t>
-  </si>
-  <si>
     <t>00:39:32</t>
   </si>
   <si>
     <t>02:12:50</t>
   </si>
   <si>
-    <t>01:32:25</t>
-  </si>
-  <si>
-    <t>00:52:26</t>
-  </si>
-  <si>
-    <t>20:04:53</t>
-  </si>
-  <si>
-    <t>19:24:59</t>
-  </si>
-  <si>
-    <t>20:58:18</t>
-  </si>
-  <si>
-    <t>20:17:46</t>
-  </si>
-  <si>
-    <t>21:51:03</t>
+    <t>01:32:26</t>
+  </si>
+  <si>
+    <t>00:52:27</t>
+  </si>
+  <si>
+    <t>20:04:55</t>
+  </si>
+  <si>
+    <t>19:25:01</t>
+  </si>
+  <si>
+    <t>20:58:20</t>
+  </si>
+  <si>
+    <t>20:17:48</t>
+  </si>
+  <si>
+    <t>21:51:05</t>
+  </si>
+  <si>
+    <t>19:36:50</t>
+  </si>
+  <si>
+    <t>21:10:06</t>
+  </si>
+  <si>
+    <t>22:43:21</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>4</t>
@@ -707,7 +728,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,7 +743,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
+        <fgColor rgb="FFF0707F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,13 +755,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0707F"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,37 +773,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +803,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,25 +857,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AD26A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -943,6 +988,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1346,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1424,55 +1481,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="L2" s="4">
-        <v>-17.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="O2" s="6">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>100</v>
       </c>
       <c r="R2" s="8">
-        <v>71</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1480,55 +1537,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="L3" s="4">
-        <v>-23.5</v>
+        <v>-11.3</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O3" s="9">
-        <v>100</v>
+        <v>225</v>
+      </c>
+      <c r="O3" s="6">
+        <v>91</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
       </c>
-      <c r="Q3" s="10">
-        <v>94</v>
-      </c>
-      <c r="R3" s="11">
+      <c r="Q3" s="8">
         <v>100</v>
+      </c>
+      <c r="R3" s="9">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1536,55 +1593,55 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="L4" s="4">
-        <v>-20.2</v>
+        <v>-22.4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O4" s="9">
-        <v>97</v>
+        <v>224</v>
+      </c>
+      <c r="O4" s="6">
+        <v>100</v>
       </c>
       <c r="P4" s="7">
         <v>0</v>
       </c>
-      <c r="Q4" s="12">
-        <v>89</v>
-      </c>
-      <c r="R4" s="10">
-        <v>96</v>
+      <c r="Q4" s="10">
+        <v>95</v>
+      </c>
+      <c r="R4" s="8">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1592,55 +1649,55 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="L5" s="4">
-        <v>-11.3</v>
+        <v>-22.2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O5" s="9">
+        <v>224</v>
+      </c>
+      <c r="O5" s="6">
         <v>100</v>
       </c>
       <c r="P5" s="7">
         <v>0</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="10">
+        <v>93</v>
+      </c>
+      <c r="R5" s="8">
         <v>100</v>
-      </c>
-      <c r="R5" s="13">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1648,7 +1705,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>47</v>
@@ -1657,45 +1714,45 @@
         <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="L6" s="4">
-        <v>-22.4</v>
+        <v>-15.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O6" s="9">
+        <v>225</v>
+      </c>
+      <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="13">
-        <v>11</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>95</v>
-      </c>
-      <c r="R6" s="11">
+      <c r="P6" s="11">
+        <v>51</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>99</v>
+      </c>
+      <c r="R6" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1704,55 +1761,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O7" s="9">
+        <v>224</v>
+      </c>
+      <c r="O7" s="6">
         <v>100</v>
       </c>
-      <c r="P7" s="14">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="11">
+      <c r="P7" s="12">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>91</v>
+      </c>
+      <c r="R7" s="8">
         <v>100</v>
-      </c>
-      <c r="R7" s="11">
-        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1760,54 +1817,54 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="L8" s="4">
-        <v>-15.5</v>
+        <v>-22.9</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O8" s="9">
+        <v>224</v>
+      </c>
+      <c r="O8" s="6">
         <v>100</v>
       </c>
-      <c r="P8" s="15">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="11">
+      <c r="P8" s="14">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="8">
         <v>100</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1816,54 +1873,54 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>104</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="L9" s="4">
-        <v>-20.2</v>
+        <v>-18.9</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O9" s="9">
+        <v>224</v>
+      </c>
+      <c r="O9" s="6">
         <v>100</v>
       </c>
-      <c r="P9" s="12">
-        <v>88</v>
-      </c>
-      <c r="Q9" s="11">
+      <c r="P9" s="15">
+        <v>87</v>
+      </c>
+      <c r="Q9" s="8">
         <v>100</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1872,55 +1929,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L10" s="4">
-        <v>-22.9</v>
+        <v>-16.7</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O10" s="9">
-        <v>100</v>
+        <v>224</v>
+      </c>
+      <c r="O10" s="6">
+        <v>98</v>
       </c>
       <c r="P10" s="11">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>100</v>
-      </c>
-      <c r="R10" s="11">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>29</v>
+      </c>
+      <c r="R10" s="17">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1928,55 +1985,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="L11" s="4">
-        <v>-18.9</v>
+        <v>-22.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O11" s="9">
-        <v>100</v>
-      </c>
-      <c r="P11" s="11">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>100</v>
-      </c>
-      <c r="R11" s="11">
-        <v>100</v>
+        <v>224</v>
+      </c>
+      <c r="O11" s="6">
+        <v>95</v>
+      </c>
+      <c r="P11" s="18">
+        <v>70</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>22</v>
+      </c>
+      <c r="R11" s="20">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1984,55 +2041,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>107</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L12" s="4">
-        <v>-16.7</v>
+        <v>-21.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O12" s="9">
-        <v>100</v>
-      </c>
-      <c r="P12" s="11">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>97</v>
-      </c>
-      <c r="R12" s="8">
-        <v>72</v>
+        <v>224</v>
+      </c>
+      <c r="O12" s="6">
+        <v>98</v>
+      </c>
+      <c r="P12" s="13">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="21">
+        <v>25</v>
+      </c>
+      <c r="R12" s="13">
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2040,55 +2097,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L13" s="4">
-        <v>-22.2</v>
+        <v>-14</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O13" s="9">
+        <v>226</v>
+      </c>
+      <c r="O13" s="6">
         <v>100</v>
       </c>
-      <c r="P13" s="11">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>72</v>
+      <c r="P13" s="13">
+        <v>92</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>80</v>
       </c>
       <c r="R13" s="10">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2096,55 +2153,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="L14" s="4">
-        <v>-21.2</v>
+        <v>-12.3</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O14" s="9">
-        <v>100</v>
-      </c>
-      <c r="P14" s="10">
-        <v>96</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>76</v>
-      </c>
-      <c r="R14" s="11">
-        <v>100</v>
+        <v>226</v>
+      </c>
+      <c r="O14" s="6">
+        <v>73</v>
+      </c>
+      <c r="P14" s="18">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>37</v>
+      </c>
+      <c r="R14" s="19">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2152,55 +2209,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L15" s="4">
-        <v>-14</v>
+        <v>-20.2</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" s="9">
-        <v>100</v>
-      </c>
-      <c r="P15" s="10">
-        <v>95</v>
-      </c>
-      <c r="Q15" s="8">
+        <v>224</v>
+      </c>
+      <c r="O15" s="6">
+        <v>79</v>
+      </c>
+      <c r="P15" s="18">
         <v>71</v>
       </c>
-      <c r="R15" s="11">
-        <v>100</v>
+      <c r="Q15" s="16">
+        <v>29</v>
+      </c>
+      <c r="R15" s="23">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2208,55 +2265,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>209</v>
+        <v>85</v>
       </c>
       <c r="L16" s="4">
-        <v>-12.3</v>
+        <v>-22.2</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O16" s="9">
-        <v>100</v>
-      </c>
-      <c r="P16" s="10">
-        <v>96</v>
-      </c>
-      <c r="Q16" s="17">
-        <v>80</v>
-      </c>
-      <c r="R16" s="11">
-        <v>98</v>
+        <v>224</v>
+      </c>
+      <c r="O16" s="6">
+        <v>72</v>
+      </c>
+      <c r="P16" s="20">
+        <v>62</v>
+      </c>
+      <c r="Q16" s="23">
+        <v>17</v>
+      </c>
+      <c r="R16" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2264,55 +2321,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L17" s="4">
-        <v>-20.2</v>
+        <v>-17.6</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O17" s="9">
-        <v>100</v>
-      </c>
-      <c r="P17" s="10">
-        <v>93</v>
-      </c>
-      <c r="Q17" s="16">
-        <v>75</v>
-      </c>
-      <c r="R17" s="10">
-        <v>97</v>
+        <v>226</v>
+      </c>
+      <c r="O17" s="6">
+        <v>51</v>
+      </c>
+      <c r="P17" s="24">
+        <v>47</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>12</v>
+      </c>
+      <c r="R17" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2320,55 +2377,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="L18" s="4">
-        <v>-22.2</v>
+        <v>-7.1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O18" s="9">
-        <v>98</v>
-      </c>
-      <c r="P18" s="18">
-        <v>87</v>
-      </c>
-      <c r="Q18" s="19">
-        <v>67</v>
-      </c>
-      <c r="R18" s="17">
-        <v>78</v>
+        <v>226</v>
+      </c>
+      <c r="O18" s="26">
+        <v>37</v>
+      </c>
+      <c r="P18" s="22">
+        <v>33</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2376,55 +2433,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>114</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="L19" s="4">
-        <v>-17.6</v>
+        <v>-17.1</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O19" s="9">
-        <v>97</v>
-      </c>
-      <c r="P19" s="18">
-        <v>85</v>
-      </c>
-      <c r="Q19" s="19">
+        <v>225</v>
+      </c>
+      <c r="O19" s="6">
+        <v>71</v>
+      </c>
+      <c r="P19" s="17">
         <v>64</v>
       </c>
-      <c r="R19" s="8">
-        <v>72</v>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2432,55 +2489,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>115</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L20" s="4">
-        <v>-7.1</v>
+        <v>-21.9</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="O20" s="9">
-        <v>46</v>
-      </c>
-      <c r="P20" s="20">
-        <v>45</v>
+        <v>224</v>
+      </c>
+      <c r="O20" s="6">
+        <v>78</v>
+      </c>
+      <c r="P20" s="18">
+        <v>70</v>
       </c>
       <c r="Q20" s="7">
         <v>0</v>
       </c>
       <c r="R20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2488,55 +2545,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="L21" s="4">
-        <v>-17.1</v>
+        <v>-20.1</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O21" s="9">
-        <v>51</v>
-      </c>
-      <c r="P21" s="15">
-        <v>36</v>
+        <v>224</v>
+      </c>
+      <c r="O21" s="6">
+        <v>84</v>
+      </c>
+      <c r="P21" s="9">
+        <v>41</v>
       </c>
       <c r="Q21" s="7">
-        <v>1</v>
-      </c>
-      <c r="R21" s="7">
         <v>0</v>
+      </c>
+      <c r="R21" s="22">
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2544,55 +2601,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>92</v>
+        <v>216</v>
       </c>
       <c r="L22" s="4">
-        <v>-21.9</v>
+        <v>-13</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O22" s="9">
-        <v>54</v>
-      </c>
-      <c r="P22" s="21">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="22">
-        <v>3</v>
-      </c>
-      <c r="R22" s="7">
+        <v>225</v>
+      </c>
+      <c r="O22" s="27">
+        <v>16</v>
+      </c>
+      <c r="P22" s="28">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="7">
         <v>0</v>
+      </c>
+      <c r="R22" s="25">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2600,55 +2657,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>93</v>
+        <v>217</v>
       </c>
       <c r="L23" s="4">
-        <v>-20.1</v>
+        <v>-20.2</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O23" s="9">
-        <v>60</v>
-      </c>
-      <c r="P23" s="23">
-        <v>18</v>
+        <v>224</v>
+      </c>
+      <c r="O23" s="26">
+        <v>21</v>
+      </c>
+      <c r="P23" s="28">
+        <v>5</v>
       </c>
       <c r="Q23" s="7">
-        <v>2</v>
-      </c>
-      <c r="R23" s="13">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="R23" s="25">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2656,55 +2713,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>119</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>212</v>
+        <v>93</v>
       </c>
       <c r="L24" s="4">
-        <v>-13</v>
+        <v>-21.5</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="O24" s="9">
-        <v>53</v>
+        <v>224</v>
+      </c>
+      <c r="O24" s="26">
+        <v>23</v>
       </c>
       <c r="P24" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="7">
         <v>0</v>
       </c>
-      <c r="Q24" s="20">
-        <v>44</v>
-      </c>
-      <c r="R24" s="15">
-        <v>33</v>
+      <c r="R24" s="28">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2712,55 +2769,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="L25" s="4">
-        <v>-20.2</v>
+        <v>-7.9</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O25" s="6">
-        <v>44</v>
+        <v>225</v>
+      </c>
+      <c r="O25" s="27">
+        <v>1</v>
       </c>
       <c r="P25" s="7">
         <v>0</v>
       </c>
-      <c r="Q25" s="24">
-        <v>31</v>
-      </c>
-      <c r="R25" s="14">
-        <v>17</v>
+      <c r="Q25" s="7">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2768,114 +2825,170 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L26" s="4">
+        <v>-17.4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="O26" s="27">
+        <v>3</v>
+      </c>
+      <c r="P26" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2">
+        <v>22</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="L26" s="4">
+      <c r="F27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L27" s="4">
         <v>-21.5</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="O26" s="6">
-        <v>25</v>
-      </c>
-      <c r="P26" s="22">
+      <c r="M27" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="O27" s="27">
         <v>4</v>
       </c>
-      <c r="Q26" s="14">
-        <v>13</v>
-      </c>
-      <c r="R26" s="22">
-        <v>4</v>
+      <c r="P27" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="A2:A27">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C26">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D26">
+  <conditionalFormatting sqref="D2:D27">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F26">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G26">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H26">
+  <conditionalFormatting sqref="H2:H27">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I26">
+  <conditionalFormatting sqref="I2:I27">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J26">
+  <conditionalFormatting sqref="J2:J27">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K26">
+  <conditionalFormatting sqref="K2:K27">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L27">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -2894,12 +3007,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M26">
+  <conditionalFormatting sqref="M2:M27">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N26">
+  <conditionalFormatting sqref="N2:N27">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -2916,22 +3029,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O26">
+  <conditionalFormatting sqref="O2:O27">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P26">
+  <conditionalFormatting sqref="P2:P27">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q26">
+  <conditionalFormatting sqref="Q2:Q27">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R26">
+  <conditionalFormatting sqref="R2:R27">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="215">
   <si>
     <t>Datum</t>
   </si>
@@ -70,18 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260504--01</t>
-  </si>
-  <si>
-    <t>20260504--02</t>
-  </si>
-  <si>
-    <t>20260504--03</t>
-  </si>
-  <si>
-    <t>20260504--04</t>
-  </si>
-  <si>
     <t>20260505--01</t>
   </si>
   <si>
@@ -148,40 +136,37 @@
     <t>20260510--03</t>
   </si>
   <si>
+    <t>20260511--01</t>
+  </si>
+  <si>
+    <t>20260511--02</t>
+  </si>
+  <si>
+    <t>05:24</t>
+  </si>
+  <si>
+    <t>05:04</t>
+  </si>
+  <si>
     <t>06:14</t>
   </si>
   <si>
-    <t>04:58</t>
-  </si>
-  <si>
-    <t>05:28</t>
-  </si>
-  <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:04</t>
-  </si>
-  <si>
-    <t>06:13</t>
-  </si>
-  <si>
-    <t>05:43</t>
-  </si>
-  <si>
-    <t>04:31</t>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:30</t>
   </si>
   <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>05:55</t>
+    <t>05:56</t>
   </si>
   <si>
     <t>02:23</t>
   </si>
   <si>
-    <t>03:39</t>
+    <t>03:40</t>
   </si>
   <si>
     <t>06:04</t>
@@ -190,55 +175,52 @@
     <t>03:45</t>
   </si>
   <si>
-    <t>02:12</t>
+    <t>02:11</t>
   </si>
   <si>
     <t>05:54</t>
   </si>
   <si>
+    <t>06:11</t>
+  </si>
+  <si>
     <t>04:34</t>
   </si>
   <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>05:08</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>05:31</t>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:21</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>00:41</t>
   </si>
   <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>03:01</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
     <t>00:36</t>
   </si>
   <si>
     <t>03:13</t>
   </si>
   <si>
-    <t>01:57</t>
-  </si>
-  <si>
-    <t>00:30:52</t>
-  </si>
-  <si>
-    <t>02:08:20</t>
-  </si>
-  <si>
-    <t>22:10:54</t>
-  </si>
-  <si>
-    <t>23:47:52</t>
+    <t>01:58</t>
+  </si>
+  <si>
+    <t>04:02</t>
   </si>
   <si>
     <t>01:25:16</t>
@@ -247,7 +229,7 @@
     <t>21:27:59</t>
   </si>
   <si>
-    <t>23:04:49</t>
+    <t>23:04:48</t>
   </si>
   <si>
     <t>00:42:09</t>
@@ -259,64 +241,58 @@
     <t>22:21:43</t>
   </si>
   <si>
-    <t>23:59:00</t>
+    <t>23:58:59</t>
   </si>
   <si>
     <t>01:36:42</t>
   </si>
   <si>
-    <t>20:02:09</t>
-  </si>
-  <si>
-    <t>21:38:35</t>
+    <t>20:02:08</t>
+  </si>
+  <si>
+    <t>21:38:34</t>
   </si>
   <si>
     <t>23:15:47</t>
   </si>
   <si>
-    <t>00:53:23</t>
-  </si>
-  <si>
-    <t>19:19:14</t>
-  </si>
-  <si>
-    <t>20:55:25</t>
-  </si>
-  <si>
-    <t>22:32:32</t>
-  </si>
-  <si>
-    <t>00:10:02</t>
-  </si>
-  <si>
-    <t>20:12:13</t>
-  </si>
-  <si>
-    <t>21:49:14</t>
-  </si>
-  <si>
-    <t>23:26:40</t>
-  </si>
-  <si>
-    <t>19:29:00</t>
-  </si>
-  <si>
-    <t>21:05:54</t>
-  </si>
-  <si>
-    <t>22:43:15</t>
-  </si>
-  <si>
-    <t>00:33:07</t>
-  </si>
-  <si>
-    <t>02:10:53</t>
-  </si>
-  <si>
-    <t>22:13:19</t>
-  </si>
-  <si>
-    <t>23:50:07</t>
+    <t>00:53:22</t>
+  </si>
+  <si>
+    <t>19:19:13</t>
+  </si>
+  <si>
+    <t>20:55:24</t>
+  </si>
+  <si>
+    <t>22:32:31</t>
+  </si>
+  <si>
+    <t>00:10:01</t>
+  </si>
+  <si>
+    <t>20:12:12</t>
+  </si>
+  <si>
+    <t>21:49:13</t>
+  </si>
+  <si>
+    <t>23:26:39</t>
+  </si>
+  <si>
+    <t>19:28:59</t>
+  </si>
+  <si>
+    <t>21:05:52</t>
+  </si>
+  <si>
+    <t>22:43:14</t>
+  </si>
+  <si>
+    <t>20:22:29</t>
+  </si>
+  <si>
+    <t>21:59:46</t>
   </si>
   <si>
     <t>01:27:42</t>
@@ -325,7 +301,7 @@
     <t>21:30:30</t>
   </si>
   <si>
-    <t>23:07:04</t>
+    <t>23:07:03</t>
   </si>
   <si>
     <t>00:44:31</t>
@@ -334,73 +310,67 @@
     <t>20:47:43</t>
   </si>
   <si>
-    <t>22:23:59</t>
-  </si>
-  <si>
-    <t>00:01:19</t>
-  </si>
-  <si>
-    <t>01:40:03</t>
-  </si>
-  <si>
-    <t>20:05:03</t>
-  </si>
-  <si>
-    <t>21:40:52</t>
-  </si>
-  <si>
-    <t>23:18:05</t>
-  </si>
-  <si>
-    <t>00:56:16</t>
+    <t>22:23:58</t>
+  </si>
+  <si>
+    <t>00:01:18</t>
+  </si>
+  <si>
+    <t>01:40:02</t>
+  </si>
+  <si>
+    <t>20:05:02</t>
+  </si>
+  <si>
+    <t>21:40:51</t>
+  </si>
+  <si>
+    <t>23:18:04</t>
+  </si>
+  <si>
+    <t>00:56:15</t>
   </si>
   <si>
     <t>19:22:38</t>
   </si>
   <si>
-    <t>20:57:44</t>
-  </si>
-  <si>
-    <t>22:34:48</t>
-  </si>
-  <si>
-    <t>00:12:41</t>
-  </si>
-  <si>
-    <t>20:14:35</t>
-  </si>
-  <si>
-    <t>21:51:30</t>
-  </si>
-  <si>
-    <t>23:29:10</t>
-  </si>
-  <si>
-    <t>19:31:27</t>
-  </si>
-  <si>
-    <t>21:08:09</t>
-  </si>
-  <si>
-    <t>22:45:40</t>
-  </si>
-  <si>
-    <t>00:36:14</t>
-  </si>
-  <si>
-    <t>02:13:22</t>
-  </si>
-  <si>
-    <t>22:16:03</t>
-  </si>
-  <si>
-    <t>23:53:14</t>
+    <t>20:57:43</t>
+  </si>
+  <si>
+    <t>22:34:47</t>
+  </si>
+  <si>
+    <t>00:12:40</t>
+  </si>
+  <si>
+    <t>20:14:34</t>
+  </si>
+  <si>
+    <t>21:51:28</t>
+  </si>
+  <si>
+    <t>23:29:09</t>
+  </si>
+  <si>
+    <t>19:31:25</t>
+  </si>
+  <si>
+    <t>21:08:07</t>
+  </si>
+  <si>
+    <t>22:45:39</t>
+  </si>
+  <si>
+    <t>20:24:44</t>
+  </si>
+  <si>
+    <t>22:02:07</t>
   </si>
   <si>
     <t>01:30:24</t>
   </si>
   <si>
-    <t>21:33:02</t>
+    <t>21:33:01</t>
   </si>
   <si>
     <t>23:10:10</t>
@@ -412,67 +382,61 @@
     <t>20:49:58</t>
   </si>
   <si>
-    <t>22:27:04</t>
-  </si>
-  <si>
-    <t>00:04:17</t>
-  </si>
-  <si>
-    <t>01:41:14</t>
+    <t>22:27:03</t>
+  </si>
+  <si>
+    <t>00:04:16</t>
+  </si>
+  <si>
+    <t>01:41:13</t>
   </si>
   <si>
     <t>20:06:52</t>
   </si>
   <si>
-    <t>21:43:54</t>
-  </si>
-  <si>
-    <t>23:21:07</t>
+    <t>21:43:53</t>
+  </si>
+  <si>
+    <t>23:21:06</t>
   </si>
   <si>
     <t>00:58:08</t>
   </si>
   <si>
-    <t>19:23:44</t>
-  </si>
-  <si>
-    <t>21:00:41</t>
-  </si>
-  <si>
-    <t>22:37:53</t>
-  </si>
-  <si>
-    <t>00:14:58</t>
-  </si>
-  <si>
-    <t>20:17:25</t>
-  </si>
-  <si>
-    <t>21:54:36</t>
-  </si>
-  <si>
-    <t>23:31:44</t>
-  </si>
-  <si>
-    <t>19:34:06</t>
-  </si>
-  <si>
-    <t>21:11:15</t>
-  </si>
-  <si>
-    <t>22:48:25</t>
-  </si>
-  <si>
-    <t>00:39:21</t>
-  </si>
-  <si>
-    <t>02:15:51</t>
-  </si>
-  <si>
-    <t>22:18:47</t>
-  </si>
-  <si>
-    <t>23:56:21</t>
+    <t>19:23:43</t>
+  </si>
+  <si>
+    <t>21:00:40</t>
+  </si>
+  <si>
+    <t>22:37:52</t>
+  </si>
+  <si>
+    <t>00:14:57</t>
+  </si>
+  <si>
+    <t>20:17:24</t>
+  </si>
+  <si>
+    <t>21:54:35</t>
+  </si>
+  <si>
+    <t>23:31:43</t>
+  </si>
+  <si>
+    <t>19:34:05</t>
+  </si>
+  <si>
+    <t>21:11:14</t>
+  </si>
+  <si>
+    <t>22:48:24</t>
+  </si>
+  <si>
+    <t>20:27:50</t>
+  </si>
+  <si>
+    <t>22:05:01</t>
   </si>
   <si>
     <t>01:33:06</t>
@@ -484,91 +448,85 @@
     <t>23:13:17</t>
   </si>
   <si>
-    <t>00:50:14</t>
-  </si>
-  <si>
-    <t>20:52:14</t>
-  </si>
-  <si>
-    <t>22:30:09</t>
+    <t>00:50:13</t>
+  </si>
+  <si>
+    <t>20:52:13</t>
+  </si>
+  <si>
+    <t>22:30:08</t>
   </si>
   <si>
     <t>00:07:14</t>
   </si>
   <si>
-    <t>01:42:26</t>
+    <t>01:42:25</t>
   </si>
   <si>
     <t>20:08:42</t>
   </si>
   <si>
-    <t>21:46:56</t>
-  </si>
-  <si>
-    <t>23:24:09</t>
-  </si>
-  <si>
-    <t>01:00:01</t>
-  </si>
-  <si>
-    <t>19:24:50</t>
-  </si>
-  <si>
-    <t>21:03:38</t>
+    <t>21:46:55</t>
+  </si>
+  <si>
+    <t>23:24:08</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>19:24:49</t>
+  </si>
+  <si>
+    <t>21:03:37</t>
   </si>
   <si>
     <t>22:40:58</t>
   </si>
   <si>
-    <t>00:17:15</t>
-  </si>
-  <si>
-    <t>20:20:15</t>
-  </si>
-  <si>
-    <t>21:57:43</t>
-  </si>
-  <si>
-    <t>23:34:18</t>
-  </si>
-  <si>
-    <t>19:36:47</t>
-  </si>
-  <si>
-    <t>21:14:23</t>
-  </si>
-  <si>
-    <t>22:51:11</t>
-  </si>
-  <si>
-    <t>00:41:36</t>
-  </si>
-  <si>
-    <t>02:18:24</t>
-  </si>
-  <si>
-    <t>22:21:13</t>
-  </si>
-  <si>
-    <t>23:58:36</t>
-  </si>
-  <si>
-    <t>01:35:33</t>
+    <t>00:17:14</t>
+  </si>
+  <si>
+    <t>20:20:14</t>
+  </si>
+  <si>
+    <t>21:57:42</t>
+  </si>
+  <si>
+    <t>23:34:16</t>
+  </si>
+  <si>
+    <t>19:36:46</t>
+  </si>
+  <si>
+    <t>21:14:21</t>
+  </si>
+  <si>
+    <t>22:51:09</t>
+  </si>
+  <si>
+    <t>20:30:56</t>
+  </si>
+  <si>
+    <t>22:07:55</t>
+  </si>
+  <si>
+    <t>01:35:32</t>
   </si>
   <si>
     <t>21:38:05</t>
   </si>
   <si>
-    <t>23:15:33</t>
-  </si>
-  <si>
-    <t>00:52:36</t>
-  </si>
-  <si>
-    <t>20:54:54</t>
-  </si>
-  <si>
-    <t>22:32:25</t>
+    <t>23:15:32</t>
+  </si>
+  <si>
+    <t>00:52:35</t>
+  </si>
+  <si>
+    <t>20:54:53</t>
+  </si>
+  <si>
+    <t>22:32:24</t>
   </si>
   <si>
     <t>00:09:33</t>
@@ -577,121 +535,127 @@
     <t>01:45:46</t>
   </si>
   <si>
-    <t>20:11:37</t>
-  </si>
-  <si>
-    <t>21:49:13</t>
-  </si>
-  <si>
-    <t>23:26:26</t>
-  </si>
-  <si>
-    <t>01:02:54</t>
-  </si>
-  <si>
-    <t>19:28:15</t>
+    <t>20:11:36</t>
+  </si>
+  <si>
+    <t>21:49:12</t>
+  </si>
+  <si>
+    <t>23:26:25</t>
+  </si>
+  <si>
+    <t>01:02:53</t>
+  </si>
+  <si>
+    <t>19:28:14</t>
   </si>
   <si>
     <t>21:05:57</t>
   </si>
   <si>
-    <t>22:43:14</t>
-  </si>
-  <si>
-    <t>00:19:54</t>
-  </si>
-  <si>
-    <t>20:22:38</t>
-  </si>
-  <si>
-    <t>21:59:58</t>
-  </si>
-  <si>
-    <t>23:36:47</t>
-  </si>
-  <si>
-    <t>19:39:14</t>
-  </si>
-  <si>
-    <t>21:16:38</t>
-  </si>
-  <si>
-    <t>22:53:35</t>
+    <t>22:43:13</t>
+  </si>
+  <si>
+    <t>00:19:53</t>
+  </si>
+  <si>
+    <t>20:22:37</t>
+  </si>
+  <si>
+    <t>21:59:57</t>
+  </si>
+  <si>
+    <t>23:36:46</t>
+  </si>
+  <si>
+    <t>19:39:13</t>
+  </si>
+  <si>
+    <t>21:16:36</t>
+  </si>
+  <si>
+    <t>22:53:34</t>
+  </si>
+  <si>
+    <t>20:33:11</t>
+  </si>
+  <si>
+    <t>22:10:15</t>
+  </si>
+  <si>
+    <t>14°</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>10°</t>
+  </si>
+  <si>
+    <t>23°</t>
+  </si>
+  <si>
+    <t>8°</t>
+  </si>
+  <si>
+    <t>25°</t>
+  </si>
+  <si>
+    <t>26°</t>
   </si>
   <si>
     <t>9°</t>
   </si>
   <si>
-    <t>18°</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>14°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
-    <t>23°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>25°</t>
-  </si>
-  <si>
-    <t>00:39:32</t>
-  </si>
-  <si>
-    <t>02:12:50</t>
-  </si>
-  <si>
-    <t>01:32:26</t>
+    <t>01:32:25</t>
   </si>
   <si>
     <t>00:52:27</t>
   </si>
   <si>
-    <t>20:04:55</t>
-  </si>
-  <si>
-    <t>19:25:01</t>
-  </si>
-  <si>
-    <t>20:58:20</t>
-  </si>
-  <si>
-    <t>20:17:48</t>
-  </si>
-  <si>
-    <t>21:51:05</t>
-  </si>
-  <si>
-    <t>19:36:50</t>
-  </si>
-  <si>
-    <t>21:10:06</t>
-  </si>
-  <si>
-    <t>22:43:21</t>
+    <t>20:04:54</t>
+  </si>
+  <si>
+    <t>19:25:00</t>
+  </si>
+  <si>
+    <t>20:58:19</t>
+  </si>
+  <si>
+    <t>20:17:47</t>
+  </si>
+  <si>
+    <t>21:51:04</t>
+  </si>
+  <si>
+    <t>19:36:49</t>
+  </si>
+  <si>
+    <t>21:10:05</t>
+  </si>
+  <si>
+    <t>22:43:20</t>
+  </si>
+  <si>
+    <t>20:28:46</t>
+  </si>
+  <si>
+    <t>22:02:01</t>
+  </si>
+  <si>
+    <t>A+B</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>A+B</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>4</t>
@@ -728,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -755,7 +719,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4E2F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCDCEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2CBE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,37 +797,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,19 +809,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFA2C0E1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,49 +821,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AD26A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -994,12 +946,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1403,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1481,54 +1427,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2" s="4">
+        <v>-15.5</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="L2" s="4">
-        <v>-20.2</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="O2" s="6">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
       </c>
       <c r="Q2" s="8">
-        <v>100</v>
-      </c>
-      <c r="R2" s="8">
+        <v>73</v>
+      </c>
+      <c r="R2" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1540,52 +1486,52 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="4">
+        <v>-20.2</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L3" s="4">
-        <v>-11.3</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="O3" s="6">
-        <v>91</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
         <v>100</v>
       </c>
+      <c r="P3" s="10">
+        <v>64</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>100</v>
+      </c>
       <c r="R3" s="9">
-        <v>39</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1593,54 +1539,54 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4">
-        <v>-22.4</v>
+        <v>-22.9</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>95</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="P4" s="11">
+        <v>83</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>100</v>
+      </c>
+      <c r="R4" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1649,54 +1595,54 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="L5" s="4">
-        <v>-22.2</v>
+        <v>-18.9</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O5" s="6">
         <v>100</v>
       </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>93</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="P5" s="8">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>100</v>
+      </c>
+      <c r="R5" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1705,54 +1651,54 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="L6" s="4">
-        <v>-15.5</v>
+        <v>-16.7</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="11">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>99</v>
-      </c>
-      <c r="R6" s="8">
+      <c r="P6" s="12">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>86</v>
+      </c>
+      <c r="R6" s="9">
         <v>100</v>
       </c>
     </row>
@@ -1761,55 +1707,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L7" s="4">
-        <v>-20.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O7" s="6">
         <v>100</v>
       </c>
-      <c r="P7" s="12">
-        <v>55</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>91</v>
-      </c>
-      <c r="R7" s="8">
-        <v>100</v>
+      <c r="P7" s="11">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>86</v>
+      </c>
+      <c r="R7" s="10">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1817,55 +1763,55 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L8" s="4">
+        <v>-21.2</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O8" s="6">
+        <v>98</v>
+      </c>
+      <c r="P8" s="8">
         <v>77</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-22.9</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O8" s="6">
-        <v>100</v>
-      </c>
-      <c r="P8" s="14">
-        <v>80</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>100</v>
-      </c>
-      <c r="R8" s="8">
-        <v>100</v>
+      <c r="Q8" s="13">
+        <v>91</v>
+      </c>
+      <c r="R8" s="14">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1873,55 +1819,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4">
-        <v>-18.9</v>
+        <v>-14</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="O9" s="6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P9" s="15">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="8">
-        <v>100</v>
-      </c>
-      <c r="R9" s="8">
-        <v>100</v>
+        <v>77</v>
+      </c>
+      <c r="R9" s="14">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1929,55 +1875,55 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="L10" s="4">
-        <v>-16.7</v>
+        <v>-12.3</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="O10" s="6">
-        <v>98</v>
-      </c>
-      <c r="P10" s="11">
-        <v>50</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>29</v>
-      </c>
-      <c r="R10" s="17">
-        <v>63</v>
+        <v>70</v>
+      </c>
+      <c r="P10" s="12">
+        <v>69</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>2</v>
+      </c>
+      <c r="R10" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1985,55 +1931,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L11" s="4">
-        <v>-22.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O11" s="6">
-        <v>95</v>
-      </c>
-      <c r="P11" s="18">
-        <v>70</v>
-      </c>
-      <c r="Q11" s="19">
-        <v>22</v>
-      </c>
-      <c r="R11" s="20">
-        <v>60</v>
+        <v>96</v>
+      </c>
+      <c r="P11" s="12">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="14">
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2041,55 +1987,55 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L12" s="4">
-        <v>-21.2</v>
+        <v>-22.2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O12" s="6">
-        <v>98</v>
-      </c>
-      <c r="P12" s="13">
-        <v>89</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>25</v>
-      </c>
-      <c r="R12" s="13">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="P12" s="10">
+        <v>66</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>19</v>
+      </c>
+      <c r="R12" s="18">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2097,55 +2043,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L13" s="4">
-        <v>-14</v>
+        <v>-17.6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="O13" s="6">
-        <v>100</v>
-      </c>
-      <c r="P13" s="13">
-        <v>92</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>80</v>
-      </c>
-      <c r="R13" s="10">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="P13" s="10">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>21</v>
+      </c>
+      <c r="R13" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2153,55 +2099,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="4">
+        <v>-7.1</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="O14" s="6">
+        <v>68</v>
+      </c>
+      <c r="P14" s="14">
         <v>55</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-12.3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O14" s="6">
-        <v>73</v>
-      </c>
-      <c r="P14" s="18">
-        <v>69</v>
-      </c>
-      <c r="Q14" s="22">
-        <v>37</v>
-      </c>
-      <c r="R14" s="19">
-        <v>21</v>
+      <c r="Q14" s="19">
+        <v>27</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2209,55 +2155,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L15" s="4">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="O15" s="6">
-        <v>79</v>
-      </c>
-      <c r="P15" s="18">
-        <v>71</v>
-      </c>
-      <c r="Q15" s="16">
-        <v>29</v>
-      </c>
-      <c r="R15" s="23">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="P15" s="20">
+        <v>39</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>24</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2265,55 +2211,55 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L16" s="4">
-        <v>-22.2</v>
+        <v>-21.9</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O16" s="6">
-        <v>72</v>
-      </c>
-      <c r="P16" s="20">
-        <v>62</v>
-      </c>
-      <c r="Q16" s="23">
-        <v>17</v>
+        <v>213</v>
+      </c>
+      <c r="O16" s="21">
+        <v>38</v>
+      </c>
+      <c r="P16" s="22">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>21</v>
       </c>
       <c r="R16" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2321,55 +2267,55 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L17" s="4">
-        <v>-17.6</v>
+        <v>-20.1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="O17" s="6">
         <v>51</v>
       </c>
-      <c r="P17" s="24">
-        <v>47</v>
-      </c>
-      <c r="Q17" s="25">
-        <v>12</v>
+      <c r="P17" s="23">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>28</v>
       </c>
       <c r="R17" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2377,55 +2323,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="L18" s="4">
-        <v>-7.1</v>
+        <v>-13</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="O18" s="26">
-        <v>37</v>
-      </c>
-      <c r="P18" s="22">
-        <v>33</v>
-      </c>
-      <c r="Q18" s="7">
+        <v>212</v>
+      </c>
+      <c r="O18" s="6">
+        <v>74</v>
+      </c>
+      <c r="P18" s="7">
         <v>0</v>
       </c>
-      <c r="R18" s="7">
-        <v>0</v>
+      <c r="Q18" s="16">
+        <v>8</v>
+      </c>
+      <c r="R18" s="24">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2433,55 +2379,55 @@
         <v>35</v>
       </c>
       <c r="B19" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="L19" s="4">
-        <v>-17.1</v>
+        <v>-20.2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="O19" s="6">
-        <v>71</v>
-      </c>
-      <c r="P19" s="17">
-        <v>64</v>
-      </c>
-      <c r="Q19" s="7">
+        <v>51</v>
+      </c>
+      <c r="P19" s="7">
         <v>0</v>
       </c>
-      <c r="R19" s="7">
-        <v>0</v>
+      <c r="Q19" s="18">
+        <v>4</v>
+      </c>
+      <c r="R19" s="20">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2489,55 +2435,55 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L20" s="4">
-        <v>-21.9</v>
+        <v>-21.5</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O20" s="6">
-        <v>78</v>
+        <v>213</v>
+      </c>
+      <c r="O20" s="21">
+        <v>22</v>
       </c>
       <c r="P20" s="18">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="7">
-        <v>0</v>
-      </c>
-      <c r="R20" s="7">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R20" s="16">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2545,55 +2491,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
       <c r="L21" s="4">
-        <v>-20.1</v>
+        <v>-7.9</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="O21" s="6">
-        <v>84</v>
-      </c>
-      <c r="P21" s="9">
-        <v>41</v>
-      </c>
-      <c r="Q21" s="7">
-        <v>0</v>
-      </c>
-      <c r="R21" s="22">
-        <v>37</v>
+        <v>97</v>
+      </c>
+      <c r="P21" s="22">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>91</v>
+      </c>
+      <c r="R21" s="20">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2601,55 +2547,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="L22" s="4">
-        <v>-13</v>
+        <v>-17.4</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O22" s="27">
-        <v>16</v>
-      </c>
-      <c r="P22" s="28">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="7">
-        <v>0</v>
-      </c>
-      <c r="R22" s="25">
-        <v>10</v>
+        <v>212</v>
+      </c>
+      <c r="O22" s="6">
+        <v>94</v>
+      </c>
+      <c r="P22" s="25">
+        <v>33</v>
+      </c>
+      <c r="Q22" s="15">
+        <v>94</v>
+      </c>
+      <c r="R22" s="26">
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2657,55 +2603,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L23" s="4">
+        <v>-21.5</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="O23" s="6">
+        <v>92</v>
+      </c>
+      <c r="P23" s="22">
         <v>32</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="Q23" s="13">
         <v>92</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-20.2</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O23" s="26">
-        <v>21</v>
-      </c>
-      <c r="P23" s="28">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>0</v>
-      </c>
-      <c r="R23" s="25">
-        <v>10</v>
+      <c r="R23" s="13">
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2713,55 +2659,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="L24" s="4">
-        <v>-21.5</v>
+        <v>-13.5</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O24" s="26">
-        <v>23</v>
-      </c>
-      <c r="P24" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="7">
-        <v>0</v>
-      </c>
-      <c r="R24" s="28">
-        <v>7</v>
+        <v>212</v>
+      </c>
+      <c r="O24" s="6">
+        <v>91</v>
+      </c>
+      <c r="P24" s="17">
+        <v>22</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>38</v>
+      </c>
+      <c r="R24" s="26">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2769,226 +2715,114 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L25" s="4">
-        <v>-7.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O25" s="27">
-        <v>1</v>
+        <v>213</v>
+      </c>
+      <c r="O25" s="6">
+        <v>72</v>
       </c>
       <c r="P25" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2">
-        <v>32</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-17.4</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="O26" s="27">
-        <v>3</v>
-      </c>
-      <c r="P26" s="7">
         <v>2</v>
       </c>
-      <c r="Q26" s="7">
-        <v>0</v>
-      </c>
-      <c r="R26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" s="1" t="s">
+      <c r="Q25" s="23">
         <v>43</v>
       </c>
-      <c r="B27" s="2">
-        <v>22</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-21.5</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O27" s="27">
-        <v>4</v>
-      </c>
-      <c r="P27" s="28">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="7">
-        <v>0</v>
-      </c>
-      <c r="R27" s="7">
-        <v>1</v>
+      <c r="R25" s="23">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A27">
+  <conditionalFormatting sqref="A2:A25">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B27">
+  <conditionalFormatting sqref="B2:B25">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C25">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D25">
     <cfRule type="expression" dxfId="8" priority="12">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="expression" dxfId="9" priority="13">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G25">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="expression" dxfId="9" priority="16">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I25">
     <cfRule type="expression" dxfId="8" priority="17">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J25">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K25">
     <cfRule type="expression" dxfId="8" priority="19">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>-18</formula>
     </cfRule>
@@ -3007,12 +2841,12 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M25">
     <cfRule type="expression" dxfId="9" priority="21">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N25">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"1"</formula>
     </cfRule>
@@ -3029,22 +2863,22 @@
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O25">
     <cfRule type="expression" dxfId="9" priority="23">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P25">
     <cfRule type="expression" dxfId="9" priority="24">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q25">
     <cfRule type="expression" dxfId="9" priority="25">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="expression" dxfId="9" priority="26">
       <formula>RIGHT($A2,4)="--01"</formula>
     </cfRule>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="216">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260505--01</t>
-  </si>
-  <si>
-    <t>20260505--02</t>
-  </si>
-  <si>
-    <t>20260505--03</t>
-  </si>
-  <si>
     <t>20260506--01</t>
   </si>
   <si>
@@ -142,109 +133,112 @@
     <t>20260511--02</t>
   </si>
   <si>
-    <t>05:24</t>
-  </si>
-  <si>
-    <t>05:04</t>
+    <t>20260512--01</t>
+  </si>
+  <si>
+    <t>20260512--02</t>
+  </si>
+  <si>
+    <t>20260512--03</t>
+  </si>
+  <si>
+    <t>05:42</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>02:11</t>
+  </si>
+  <si>
+    <t>05:53</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:40</t>
   </si>
   <si>
     <t>06:14</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>06:10</t>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>05:48</t>
+  </si>
+  <si>
+    <t>06:08</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>03:04</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>03:13</t>
+  </si>
+  <si>
+    <t>01:57</t>
+  </si>
+  <si>
+    <t>04:02</t>
   </si>
   <si>
     <t>05:56</t>
   </si>
   <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>02:11</t>
-  </si>
-  <si>
-    <t>05:54</t>
-  </si>
-  <si>
-    <t>06:11</t>
-  </si>
-  <si>
-    <t>04:34</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:21</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>05:48</t>
-  </si>
-  <si>
-    <t>00:41</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>00:36</t>
-  </si>
-  <si>
-    <t>03:13</t>
-  </si>
-  <si>
-    <t>01:58</t>
-  </si>
-  <si>
-    <t>04:02</t>
-  </si>
-  <si>
-    <t>01:25:16</t>
-  </si>
-  <si>
-    <t>21:27:59</t>
-  </si>
-  <si>
-    <t>23:04:48</t>
+    <t>01:54</t>
   </si>
   <si>
     <t>00:42:09</t>
   </si>
   <si>
-    <t>20:45:04</t>
-  </si>
-  <si>
-    <t>22:21:43</t>
+    <t>20:45:03</t>
+  </si>
+  <si>
+    <t>22:21:42</t>
   </si>
   <si>
     <t>23:58:59</t>
   </si>
   <si>
-    <t>01:36:42</t>
+    <t>01:36:41</t>
   </si>
   <si>
     <t>20:02:08</t>
@@ -253,7 +247,7 @@
     <t>21:38:34</t>
   </si>
   <si>
-    <t>23:15:47</t>
+    <t>23:15:46</t>
   </si>
   <si>
     <t>00:53:22</t>
@@ -262,7 +256,7 @@
     <t>19:19:13</t>
   </si>
   <si>
-    <t>20:55:24</t>
+    <t>20:55:23</t>
   </si>
   <si>
     <t>22:32:31</t>
@@ -271,37 +265,37 @@
     <t>00:10:01</t>
   </si>
   <si>
-    <t>20:12:12</t>
-  </si>
-  <si>
-    <t>21:49:13</t>
-  </si>
-  <si>
-    <t>23:26:39</t>
-  </si>
-  <si>
-    <t>19:28:59</t>
-  </si>
-  <si>
-    <t>21:05:52</t>
-  </si>
-  <si>
-    <t>22:43:14</t>
-  </si>
-  <si>
-    <t>20:22:29</t>
-  </si>
-  <si>
-    <t>21:59:46</t>
-  </si>
-  <si>
-    <t>01:27:42</t>
-  </si>
-  <si>
-    <t>21:30:30</t>
-  </si>
-  <si>
-    <t>23:07:03</t>
+    <t>20:12:11</t>
+  </si>
+  <si>
+    <t>21:49:12</t>
+  </si>
+  <si>
+    <t>23:26:38</t>
+  </si>
+  <si>
+    <t>19:28:57</t>
+  </si>
+  <si>
+    <t>21:05:51</t>
+  </si>
+  <si>
+    <t>22:43:13</t>
+  </si>
+  <si>
+    <t>20:22:27</t>
+  </si>
+  <si>
+    <t>21:59:45</t>
+  </si>
+  <si>
+    <t>19:39:00</t>
+  </si>
+  <si>
+    <t>21:16:14</t>
+  </si>
+  <si>
+    <t>22:53:52</t>
   </si>
   <si>
     <t>00:44:31</t>
@@ -331,7 +325,7 @@
     <t>00:56:15</t>
   </si>
   <si>
-    <t>19:22:38</t>
+    <t>19:22:37</t>
   </si>
   <si>
     <t>20:57:43</t>
@@ -343,37 +337,37 @@
     <t>00:12:40</t>
   </si>
   <si>
-    <t>20:14:34</t>
-  </si>
-  <si>
-    <t>21:51:28</t>
-  </si>
-  <si>
-    <t>23:29:09</t>
-  </si>
-  <si>
-    <t>19:31:25</t>
-  </si>
-  <si>
-    <t>21:08:07</t>
-  </si>
-  <si>
-    <t>22:45:39</t>
-  </si>
-  <si>
-    <t>20:24:44</t>
-  </si>
-  <si>
-    <t>22:02:07</t>
-  </si>
-  <si>
-    <t>01:30:24</t>
-  </si>
-  <si>
-    <t>21:33:01</t>
-  </si>
-  <si>
-    <t>23:10:10</t>
+    <t>20:14:33</t>
+  </si>
+  <si>
+    <t>21:51:27</t>
+  </si>
+  <si>
+    <t>23:29:08</t>
+  </si>
+  <si>
+    <t>19:31:24</t>
+  </si>
+  <si>
+    <t>21:08:06</t>
+  </si>
+  <si>
+    <t>22:45:37</t>
+  </si>
+  <si>
+    <t>20:24:42</t>
+  </si>
+  <si>
+    <t>22:02:05</t>
+  </si>
+  <si>
+    <t>19:41:16</t>
+  </si>
+  <si>
+    <t>21:18:32</t>
+  </si>
+  <si>
+    <t>22:56:58</t>
   </si>
   <si>
     <t>00:47:22</t>
@@ -391,7 +385,7 @@
     <t>01:41:13</t>
   </si>
   <si>
-    <t>20:06:52</t>
+    <t>20:06:51</t>
   </si>
   <si>
     <t>21:43:53</t>
@@ -400,52 +394,52 @@
     <t>23:21:06</t>
   </si>
   <si>
-    <t>00:58:08</t>
-  </si>
-  <si>
-    <t>19:23:43</t>
-  </si>
-  <si>
-    <t>21:00:40</t>
+    <t>00:58:07</t>
+  </si>
+  <si>
+    <t>19:23:42</t>
+  </si>
+  <si>
+    <t>21:00:39</t>
   </si>
   <si>
     <t>22:37:52</t>
   </si>
   <si>
-    <t>00:14:57</t>
-  </si>
-  <si>
-    <t>20:17:24</t>
-  </si>
-  <si>
-    <t>21:54:35</t>
-  </si>
-  <si>
-    <t>23:31:43</t>
-  </si>
-  <si>
-    <t>19:34:05</t>
-  </si>
-  <si>
-    <t>21:11:14</t>
-  </si>
-  <si>
-    <t>22:48:24</t>
-  </si>
-  <si>
-    <t>20:27:50</t>
-  </si>
-  <si>
-    <t>22:05:01</t>
-  </si>
-  <si>
-    <t>01:33:06</t>
-  </si>
-  <si>
-    <t>21:35:34</t>
-  </si>
-  <si>
-    <t>23:13:17</t>
+    <t>00:14:56</t>
+  </si>
+  <si>
+    <t>20:17:23</t>
+  </si>
+  <si>
+    <t>21:54:34</t>
+  </si>
+  <si>
+    <t>23:31:42</t>
+  </si>
+  <si>
+    <t>19:34:04</t>
+  </si>
+  <si>
+    <t>21:11:13</t>
+  </si>
+  <si>
+    <t>22:48:22</t>
+  </si>
+  <si>
+    <t>20:27:48</t>
+  </si>
+  <si>
+    <t>22:04:59</t>
+  </si>
+  <si>
+    <t>19:44:20</t>
+  </si>
+  <si>
+    <t>21:21:32</t>
+  </si>
+  <si>
+    <t>22:58:30</t>
   </si>
   <si>
     <t>00:50:13</t>
@@ -457,13 +451,13 @@
     <t>22:30:08</t>
   </si>
   <si>
-    <t>00:07:14</t>
+    <t>00:07:13</t>
   </si>
   <si>
     <t>01:42:25</t>
   </si>
   <si>
-    <t>20:08:42</t>
+    <t>20:08:41</t>
   </si>
   <si>
     <t>21:46:55</t>
@@ -475,49 +469,49 @@
     <t>01:00:00</t>
   </si>
   <si>
-    <t>19:24:49</t>
-  </si>
-  <si>
-    <t>21:03:37</t>
-  </si>
-  <si>
-    <t>22:40:58</t>
+    <t>19:24:48</t>
+  </si>
+  <si>
+    <t>21:03:36</t>
+  </si>
+  <si>
+    <t>22:40:57</t>
   </si>
   <si>
     <t>00:17:14</t>
   </si>
   <si>
-    <t>20:20:14</t>
-  </si>
-  <si>
-    <t>21:57:42</t>
-  </si>
-  <si>
-    <t>23:34:16</t>
-  </si>
-  <si>
-    <t>19:36:46</t>
-  </si>
-  <si>
-    <t>21:14:21</t>
-  </si>
-  <si>
-    <t>22:51:09</t>
-  </si>
-  <si>
-    <t>20:30:56</t>
-  </si>
-  <si>
-    <t>22:07:55</t>
-  </si>
-  <si>
-    <t>01:35:32</t>
-  </si>
-  <si>
-    <t>21:38:05</t>
-  </si>
-  <si>
-    <t>23:15:32</t>
+    <t>20:20:13</t>
+  </si>
+  <si>
+    <t>21:57:41</t>
+  </si>
+  <si>
+    <t>23:34:15</t>
+  </si>
+  <si>
+    <t>19:36:44</t>
+  </si>
+  <si>
+    <t>21:14:20</t>
+  </si>
+  <si>
+    <t>22:51:08</t>
+  </si>
+  <si>
+    <t>20:30:54</t>
+  </si>
+  <si>
+    <t>22:07:53</t>
+  </si>
+  <si>
+    <t>19:47:24</t>
+  </si>
+  <si>
+    <t>21:24:31</t>
+  </si>
+  <si>
+    <t>23:00:02</t>
   </si>
   <si>
     <t>00:52:35</t>
@@ -529,69 +523,72 @@
     <t>22:32:24</t>
   </si>
   <si>
-    <t>00:09:33</t>
-  </si>
-  <si>
-    <t>01:45:46</t>
+    <t>00:09:32</t>
+  </si>
+  <si>
+    <t>01:45:45</t>
   </si>
   <si>
     <t>20:11:36</t>
   </si>
   <si>
-    <t>21:49:12</t>
-  </si>
-  <si>
     <t>23:26:25</t>
   </si>
   <si>
-    <t>01:02:53</t>
-  </si>
-  <si>
-    <t>19:28:14</t>
-  </si>
-  <si>
-    <t>21:05:57</t>
-  </si>
-  <si>
-    <t>22:43:13</t>
-  </si>
-  <si>
-    <t>00:19:53</t>
-  </si>
-  <si>
-    <t>20:22:37</t>
-  </si>
-  <si>
-    <t>21:59:57</t>
-  </si>
-  <si>
-    <t>23:36:46</t>
-  </si>
-  <si>
-    <t>19:39:13</t>
-  </si>
-  <si>
-    <t>21:16:36</t>
-  </si>
-  <si>
-    <t>22:53:34</t>
-  </si>
-  <si>
-    <t>20:33:11</t>
-  </si>
-  <si>
-    <t>22:10:15</t>
+    <t>01:02:52</t>
+  </si>
+  <si>
+    <t>19:28:13</t>
+  </si>
+  <si>
+    <t>21:05:56</t>
+  </si>
+  <si>
+    <t>00:19:52</t>
+  </si>
+  <si>
+    <t>20:22:36</t>
+  </si>
+  <si>
+    <t>21:59:56</t>
+  </si>
+  <si>
+    <t>23:36:45</t>
+  </si>
+  <si>
+    <t>19:39:11</t>
+  </si>
+  <si>
+    <t>21:16:35</t>
+  </si>
+  <si>
+    <t>22:53:32</t>
+  </si>
+  <si>
+    <t>20:33:10</t>
+  </si>
+  <si>
+    <t>22:10:13</t>
+  </si>
+  <si>
+    <t>19:49:40</t>
+  </si>
+  <si>
+    <t>21:26:49</t>
+  </si>
+  <si>
+    <t>23:03:07</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>10°</t>
   </si>
   <si>
     <t>14°</t>
   </si>
   <si>
-    <t>0°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>23°</t>
   </si>
   <si>
@@ -607,58 +604,64 @@
     <t>9°</t>
   </si>
   <si>
-    <t>01:32:25</t>
+    <t>11°</t>
   </si>
   <si>
     <t>00:52:27</t>
   </si>
   <si>
-    <t>20:04:54</t>
-  </si>
-  <si>
-    <t>19:25:00</t>
-  </si>
-  <si>
-    <t>20:58:19</t>
-  </si>
-  <si>
-    <t>20:17:47</t>
-  </si>
-  <si>
-    <t>21:51:04</t>
-  </si>
-  <si>
-    <t>19:36:49</t>
-  </si>
-  <si>
-    <t>21:10:05</t>
-  </si>
-  <si>
-    <t>22:43:20</t>
-  </si>
-  <si>
-    <t>20:28:46</t>
-  </si>
-  <si>
-    <t>22:02:01</t>
+    <t>20:04:53</t>
+  </si>
+  <si>
+    <t>19:24:59</t>
+  </si>
+  <si>
+    <t>20:58:18</t>
+  </si>
+  <si>
+    <t>20:17:46</t>
+  </si>
+  <si>
+    <t>21:51:03</t>
+  </si>
+  <si>
+    <t>19:36:48</t>
+  </si>
+  <si>
+    <t>21:10:03</t>
+  </si>
+  <si>
+    <t>22:43:18</t>
+  </si>
+  <si>
+    <t>20:28:44</t>
+  </si>
+  <si>
+    <t>22:01:59</t>
+  </si>
+  <si>
+    <t>19:47:12</t>
+  </si>
+  <si>
+    <t>21:20:26</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <t>A+B</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -713,31 +716,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FFF6F9FC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D7EC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6EEF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,13 +746,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFC4D7EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBD1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90B4DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,7 +824,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
+        <fgColor rgb="FFF0B070"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,49 +836,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
+        <fgColor rgb="FF6E9DD0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90B4DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -946,6 +961,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1427,7 +1448,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>42</v>
@@ -1436,43 +1457,43 @@
         <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>197</v>
       </c>
       <c r="L2" s="4">
-        <v>-15.5</v>
+        <v>-18.9</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O2" s="6">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Q2" s="8">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="R2" s="9">
         <v>100</v>
@@ -1483,37 +1504,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" s="4">
-        <v>-20.2</v>
+        <v>-16.7</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>210</v>
@@ -1522,16 +1543,16 @@
         <v>213</v>
       </c>
       <c r="O3" s="6">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P3" s="10">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>100</v>
-      </c>
-      <c r="R3" s="9">
-        <v>100</v>
+        <v>72</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>88</v>
+      </c>
+      <c r="R3" s="12">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1539,37 +1560,37 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L4" s="4">
-        <v>-22.9</v>
+        <v>-22.2</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>210</v>
@@ -1580,11 +1601,11 @@
       <c r="O4" s="6">
         <v>100</v>
       </c>
-      <c r="P4" s="11">
-        <v>83</v>
+      <c r="P4" s="13">
+        <v>67</v>
       </c>
       <c r="Q4" s="9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R4" s="9">
         <v>100</v>
@@ -1595,37 +1616,37 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
-        <v>-18.9</v>
+        <v>-21.2</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>210</v>
@@ -1636,8 +1657,8 @@
       <c r="O5" s="6">
         <v>100</v>
       </c>
-      <c r="P5" s="8">
-        <v>77</v>
+      <c r="P5" s="10">
+        <v>71</v>
       </c>
       <c r="Q5" s="9">
         <v>100</v>
@@ -1651,52 +1672,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L6" s="4">
-        <v>-16.7</v>
+        <v>-14</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>210</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O6" s="6">
         <v>100</v>
       </c>
-      <c r="P6" s="12">
-        <v>68</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>86</v>
+      <c r="P6" s="14">
+        <v>82</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>99</v>
       </c>
       <c r="R6" s="9">
         <v>100</v>
@@ -1707,55 +1728,55 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="L7" s="4">
-        <v>-22.2</v>
+        <v>-12.3</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>210</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O7" s="6">
         <v>100</v>
       </c>
-      <c r="P7" s="11">
-        <v>87</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>86</v>
-      </c>
-      <c r="R7" s="10">
-        <v>64</v>
+      <c r="P7" s="9">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>52</v>
+      </c>
+      <c r="R7" s="8">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1763,37 +1784,37 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4">
-        <v>-21.2</v>
+        <v>-20.2</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>210</v>
@@ -1802,16 +1823,16 @@
         <v>213</v>
       </c>
       <c r="O8" s="6">
-        <v>98</v>
-      </c>
-      <c r="P8" s="8">
-        <v>77</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>91</v>
-      </c>
-      <c r="R8" s="14">
-        <v>55</v>
+        <v>100</v>
+      </c>
+      <c r="P8" s="9">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>46</v>
+      </c>
+      <c r="R8" s="17">
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1819,55 +1840,55 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>172</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L9" s="4">
-        <v>-14</v>
+        <v>-22.2</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>210</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O9" s="6">
-        <v>98</v>
-      </c>
-      <c r="P9" s="15">
-        <v>95</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>77</v>
-      </c>
-      <c r="R9" s="14">
-        <v>54</v>
+        <v>100</v>
+      </c>
+      <c r="P9" s="9">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>70</v>
+      </c>
+      <c r="R9" s="12">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1878,34 +1899,34 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>173</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="L10" s="4">
-        <v>-12.3</v>
+        <v>-17.6</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>210</v>
@@ -1914,16 +1935,16 @@
         <v>214</v>
       </c>
       <c r="O10" s="6">
-        <v>70</v>
-      </c>
-      <c r="P10" s="12">
-        <v>69</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>2</v>
-      </c>
-      <c r="R10" s="16">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="P10" s="9">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>71</v>
+      </c>
+      <c r="R10" s="17">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1931,55 +1952,55 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>174</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="L11" s="4">
-        <v>-20.2</v>
+        <v>-7.1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O11" s="6">
-        <v>96</v>
-      </c>
-      <c r="P11" s="12">
-        <v>71</v>
-      </c>
-      <c r="Q11" s="7">
+        <v>63</v>
+      </c>
+      <c r="P11" s="18">
+        <v>59</v>
+      </c>
+      <c r="Q11" s="19">
         <v>0</v>
       </c>
-      <c r="R11" s="14">
-        <v>53</v>
+      <c r="R11" s="20">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1987,7 +2008,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>51</v>
@@ -1996,16 +2017,16 @@
         <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>175</v>
@@ -2014,28 +2035,28 @@
         <v>190</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="L12" s="4">
-        <v>-22.2</v>
+        <v>-17.1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O12" s="6">
-        <v>80</v>
-      </c>
-      <c r="P12" s="10">
-        <v>66</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>19</v>
-      </c>
-      <c r="R12" s="18">
-        <v>5</v>
+        <v>74</v>
+      </c>
+      <c r="P12" s="18">
+        <v>58</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>0</v>
+      </c>
+      <c r="R12" s="21">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2043,55 +2064,55 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L13" s="4">
-        <v>-17.6</v>
+        <v>-21.9</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>210</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O13" s="6">
-        <v>85</v>
-      </c>
-      <c r="P13" s="10">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="17">
-        <v>21</v>
-      </c>
-      <c r="R13" s="17">
-        <v>18</v>
+        <v>47</v>
+      </c>
+      <c r="P13" s="16">
+        <v>47</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>0</v>
+      </c>
+      <c r="R13" s="19">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2099,55 +2120,55 @@
         <v>30</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="L14" s="4">
-        <v>-7.1</v>
+        <v>-20.1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O14" s="6">
-        <v>68</v>
-      </c>
-      <c r="P14" s="14">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="P14" s="22">
+        <v>32</v>
       </c>
       <c r="Q14" s="19">
-        <v>27</v>
-      </c>
-      <c r="R14" s="7">
         <v>0</v>
+      </c>
+      <c r="R14" s="23">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2155,55 +2176,55 @@
         <v>31</v>
       </c>
       <c r="B15" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>201</v>
       </c>
       <c r="L15" s="4">
-        <v>-17.1</v>
+        <v>-13</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O15" s="6">
-        <v>48</v>
-      </c>
-      <c r="P15" s="20">
-        <v>39</v>
-      </c>
-      <c r="Q15" s="19">
-        <v>24</v>
-      </c>
-      <c r="R15" s="7">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="P15" s="23">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>20</v>
+      </c>
+      <c r="R15" s="22">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2211,37 +2232,37 @@
         <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="L16" s="4">
-        <v>-21.9</v>
+        <v>-20.2</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>210</v>
@@ -2249,17 +2270,17 @@
       <c r="N16" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O16" s="21">
-        <v>38</v>
-      </c>
-      <c r="P16" s="22">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="17">
+      <c r="O16" s="6">
+        <v>56</v>
+      </c>
+      <c r="P16" s="24">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="23">
         <v>21</v>
       </c>
-      <c r="R16" s="7">
-        <v>0</v>
+      <c r="R16" s="24">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2267,37 +2288,37 @@
         <v>33</v>
       </c>
       <c r="B17" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L17" s="4">
-        <v>-20.1</v>
+        <v>-21.5</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>210</v>
@@ -2305,17 +2326,17 @@
       <c r="N17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O17" s="6">
-        <v>51</v>
-      </c>
-      <c r="P17" s="23">
-        <v>43</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>28</v>
-      </c>
-      <c r="R17" s="7">
+      <c r="O17" s="25">
+        <v>37</v>
+      </c>
+      <c r="P17" s="19">
         <v>0</v>
+      </c>
+      <c r="Q17" s="20">
+        <v>25</v>
+      </c>
+      <c r="R17" s="26">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2323,55 +2344,55 @@
         <v>34</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L18" s="4">
-        <v>-13</v>
+        <v>-7.9</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O18" s="6">
-        <v>74</v>
-      </c>
-      <c r="P18" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="16">
-        <v>8</v>
-      </c>
-      <c r="R18" s="24">
-        <v>60</v>
+        <v>100</v>
+      </c>
+      <c r="P18" s="24">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>14</v>
+      </c>
+      <c r="R18" s="9">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2382,52 +2403,52 @@
         <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>193</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" s="4">
-        <v>-20.2</v>
+        <v>-17.4</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O19" s="6">
-        <v>51</v>
-      </c>
-      <c r="P19" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="18">
-        <v>4</v>
-      </c>
-      <c r="R19" s="20">
-        <v>38</v>
+        <v>82</v>
+      </c>
+      <c r="P19" s="26">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="19">
+        <v>1</v>
+      </c>
+      <c r="R19" s="16">
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2435,34 +2456,34 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="L20" s="4">
         <v>-21.5</v>
@@ -2473,17 +2494,17 @@
       <c r="N20" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O20" s="21">
-        <v>22</v>
-      </c>
-      <c r="P20" s="18">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>2</v>
-      </c>
-      <c r="R20" s="16">
-        <v>11</v>
+      <c r="O20" s="6">
+        <v>74</v>
+      </c>
+      <c r="P20" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>1</v>
+      </c>
+      <c r="R20" s="12">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2491,55 +2512,55 @@
         <v>37</v>
       </c>
       <c r="B21" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L21" s="4">
-        <v>-7.9</v>
+        <v>-13.5</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O21" s="6">
-        <v>97</v>
-      </c>
-      <c r="P21" s="22">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>91</v>
-      </c>
-      <c r="R21" s="20">
-        <v>42</v>
+        <v>82</v>
+      </c>
+      <c r="P21" s="24">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="26">
+        <v>5</v>
+      </c>
+      <c r="R21" s="28">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2547,55 +2568,55 @@
         <v>38</v>
       </c>
       <c r="B22" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L22" s="4">
-        <v>-17.4</v>
+        <v>-20.2</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O22" s="6">
-        <v>94</v>
-      </c>
-      <c r="P22" s="25">
-        <v>33</v>
-      </c>
-      <c r="Q22" s="15">
-        <v>94</v>
-      </c>
-      <c r="R22" s="26">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="P22" s="23">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>13</v>
+      </c>
+      <c r="R22" s="23">
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2603,55 +2624,55 @@
         <v>39</v>
       </c>
       <c r="B23" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L23" s="4">
-        <v>-21.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O23" s="6">
-        <v>92</v>
-      </c>
-      <c r="P23" s="22">
-        <v>32</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>92</v>
-      </c>
-      <c r="R23" s="13">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="P23" s="7">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="28">
+        <v>75</v>
+      </c>
+      <c r="R23" s="28">
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2659,55 +2680,55 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L24" s="4">
-        <v>-13.5</v>
+        <v>-17.7</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O24" s="6">
         <v>91</v>
       </c>
-      <c r="P24" s="17">
-        <v>22</v>
-      </c>
-      <c r="Q24" s="20">
-        <v>38</v>
-      </c>
-      <c r="R24" s="26">
-        <v>82</v>
+      <c r="P24" s="18">
+        <v>61</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>67</v>
+      </c>
+      <c r="R24" s="11">
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2715,55 +2736,55 @@
         <v>41</v>
       </c>
       <c r="B25" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>208</v>
+        <v>93</v>
       </c>
       <c r="L25" s="4">
-        <v>-20.2</v>
+        <v>-21</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>210</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O25" s="6">
-        <v>72</v>
-      </c>
-      <c r="P25" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="23">
-        <v>43</v>
-      </c>
-      <c r="R25" s="23">
-        <v>46</v>
+        <v>95</v>
+      </c>
+      <c r="P25" s="13">
+        <v>64</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>65</v>
+      </c>
+      <c r="R25" s="11">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Prelety.xlsx
+++ b/Prelety.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="217">
   <si>
     <t>Datum</t>
   </si>
@@ -70,15 +70,6 @@
     <t>Vysoká</t>
   </si>
   <si>
-    <t>20260506--01</t>
-  </si>
-  <si>
-    <t>20260506--02</t>
-  </si>
-  <si>
-    <t>20260506--03</t>
-  </si>
-  <si>
     <t>20260507--01</t>
   </si>
   <si>
@@ -142,58 +133,61 @@
     <t>20260512--03</t>
   </si>
   <si>
-    <t>05:42</t>
-  </si>
-  <si>
-    <t>04:30</t>
+    <t>20260513--01</t>
+  </si>
+  <si>
+    <t>20260513--02</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>02:23</t>
+  </si>
+  <si>
+    <t>03:39</t>
+  </si>
+  <si>
+    <t>06:04</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>02:11</t>
+  </si>
+  <si>
+    <t>05:54</t>
   </si>
   <si>
     <t>06:10</t>
   </si>
   <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>02:23</t>
-  </si>
-  <si>
-    <t>03:39</t>
-  </si>
-  <si>
-    <t>06:04</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>02:11</t>
-  </si>
-  <si>
-    <t>05:53</t>
-  </si>
-  <si>
     <t>04:34</t>
   </si>
   <si>
-    <t>05:40</t>
+    <t>05:39</t>
+  </si>
+  <si>
+    <t>06:13</t>
+  </si>
+  <si>
+    <t>05:07</t>
+  </si>
+  <si>
+    <t>05:20</t>
   </si>
   <si>
     <t>06:14</t>
   </si>
   <si>
-    <t>05:07</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>06:12</t>
-  </si>
-  <si>
-    <t>05:48</t>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:11</t>
+  </si>
+  <si>
+    <t>05:47</t>
   </si>
   <si>
     <t>06:08</t>
@@ -205,13 +199,19 @@
     <t>03:04</t>
   </si>
   <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>04:09</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>03:13</t>
+    <t>00:36</t>
+  </si>
+  <si>
+    <t>03:12</t>
   </si>
   <si>
     <t>01:57</t>
@@ -226,34 +226,28 @@
     <t>01:54</t>
   </si>
   <si>
-    <t>00:42:09</t>
-  </si>
-  <si>
-    <t>20:45:03</t>
-  </si>
-  <si>
-    <t>22:21:42</t>
-  </si>
-  <si>
-    <t>23:58:59</t>
+    <t>03:46</t>
+  </si>
+  <si>
+    <t>23:58:58</t>
   </si>
   <si>
     <t>01:36:41</t>
   </si>
   <si>
-    <t>20:02:08</t>
-  </si>
-  <si>
-    <t>21:38:34</t>
+    <t>20:02:07</t>
+  </si>
+  <si>
+    <t>21:38:33</t>
   </si>
   <si>
     <t>23:15:46</t>
   </si>
   <si>
-    <t>00:53:22</t>
-  </si>
-  <si>
-    <t>19:19:13</t>
+    <t>00:53:21</t>
+  </si>
+  <si>
+    <t>19:19:12</t>
   </si>
   <si>
     <t>20:55:23</t>
@@ -268,118 +262,112 @@
     <t>20:12:11</t>
   </si>
   <si>
-    <t>21:49:12</t>
+    <t>21:49:13</t>
   </si>
   <si>
     <t>23:26:38</t>
   </si>
   <si>
-    <t>19:28:57</t>
-  </si>
-  <si>
-    <t>21:05:51</t>
-  </si>
-  <si>
-    <t>22:43:13</t>
-  </si>
-  <si>
-    <t>20:22:27</t>
-  </si>
-  <si>
-    <t>21:59:45</t>
-  </si>
-  <si>
-    <t>19:39:00</t>
-  </si>
-  <si>
-    <t>21:16:14</t>
-  </si>
-  <si>
-    <t>22:53:52</t>
-  </si>
-  <si>
-    <t>00:44:31</t>
-  </si>
-  <si>
-    <t>20:47:43</t>
-  </si>
-  <si>
-    <t>22:23:58</t>
+    <t>19:28:59</t>
+  </si>
+  <si>
+    <t>21:05:52</t>
+  </si>
+  <si>
+    <t>22:43:14</t>
+  </si>
+  <si>
+    <t>20:22:29</t>
+  </si>
+  <si>
+    <t>21:59:47</t>
+  </si>
+  <si>
+    <t>19:39:04</t>
+  </si>
+  <si>
+    <t>21:16:18</t>
+  </si>
+  <si>
+    <t>22:53:56</t>
+  </si>
+  <si>
+    <t>20:32:46</t>
+  </si>
+  <si>
+    <t>22:10:18</t>
   </si>
   <si>
     <t>00:01:18</t>
   </si>
   <si>
-    <t>01:40:02</t>
-  </si>
-  <si>
-    <t>20:05:02</t>
-  </si>
-  <si>
-    <t>21:40:51</t>
-  </si>
-  <si>
-    <t>23:18:04</t>
-  </si>
-  <si>
-    <t>00:56:15</t>
+    <t>01:40:01</t>
+  </si>
+  <si>
+    <t>20:05:01</t>
+  </si>
+  <si>
+    <t>21:40:50</t>
+  </si>
+  <si>
+    <t>23:18:03</t>
+  </si>
+  <si>
+    <t>00:56:14</t>
   </si>
   <si>
     <t>19:22:37</t>
   </si>
   <si>
-    <t>20:57:43</t>
-  </si>
-  <si>
-    <t>22:34:47</t>
-  </si>
-  <si>
-    <t>00:12:40</t>
-  </si>
-  <si>
-    <t>20:14:33</t>
-  </si>
-  <si>
-    <t>21:51:27</t>
-  </si>
-  <si>
-    <t>23:29:08</t>
-  </si>
-  <si>
-    <t>19:31:24</t>
-  </si>
-  <si>
-    <t>21:08:06</t>
-  </si>
-  <si>
-    <t>22:45:37</t>
-  </si>
-  <si>
-    <t>20:24:42</t>
-  </si>
-  <si>
-    <t>22:02:05</t>
-  </si>
-  <si>
-    <t>19:41:16</t>
-  </si>
-  <si>
-    <t>21:18:32</t>
-  </si>
-  <si>
-    <t>22:56:58</t>
-  </si>
-  <si>
-    <t>00:47:22</t>
-  </si>
-  <si>
-    <t>20:49:58</t>
-  </si>
-  <si>
-    <t>22:27:03</t>
-  </si>
-  <si>
-    <t>00:04:16</t>
+    <t>20:57:42</t>
+  </si>
+  <si>
+    <t>22:34:46</t>
+  </si>
+  <si>
+    <t>00:12:39</t>
+  </si>
+  <si>
+    <t>20:14:34</t>
+  </si>
+  <si>
+    <t>21:51:28</t>
+  </si>
+  <si>
+    <t>23:29:09</t>
+  </si>
+  <si>
+    <t>19:31:25</t>
+  </si>
+  <si>
+    <t>21:08:07</t>
+  </si>
+  <si>
+    <t>22:45:39</t>
+  </si>
+  <si>
+    <t>20:24:45</t>
+  </si>
+  <si>
+    <t>22:02:08</t>
+  </si>
+  <si>
+    <t>19:41:20</t>
+  </si>
+  <si>
+    <t>21:18:36</t>
+  </si>
+  <si>
+    <t>22:57:02</t>
+  </si>
+  <si>
+    <t>20:35:03</t>
+  </si>
+  <si>
+    <t>22:13:04</t>
+  </si>
+  <si>
+    <t>00:04:15</t>
   </si>
   <si>
     <t>01:41:13</t>
@@ -388,13 +376,13 @@
     <t>20:06:51</t>
   </si>
   <si>
-    <t>21:43:53</t>
-  </si>
-  <si>
-    <t>23:21:06</t>
-  </si>
-  <si>
-    <t>00:58:07</t>
+    <t>21:43:52</t>
+  </si>
+  <si>
+    <t>23:21:05</t>
+  </si>
+  <si>
+    <t>00:58:06</t>
   </si>
   <si>
     <t>19:23:42</t>
@@ -403,7 +391,7 @@
     <t>21:00:39</t>
   </si>
   <si>
-    <t>22:37:52</t>
+    <t>22:37:51</t>
   </si>
   <si>
     <t>00:14:56</t>
@@ -418,55 +406,52 @@
     <t>23:31:42</t>
   </si>
   <si>
-    <t>19:34:04</t>
-  </si>
-  <si>
-    <t>21:11:13</t>
-  </si>
-  <si>
-    <t>22:48:22</t>
-  </si>
-  <si>
-    <t>20:27:48</t>
-  </si>
-  <si>
-    <t>22:04:59</t>
-  </si>
-  <si>
-    <t>19:44:20</t>
-  </si>
-  <si>
-    <t>21:21:32</t>
-  </si>
-  <si>
-    <t>22:58:30</t>
-  </si>
-  <si>
-    <t>00:50:13</t>
-  </si>
-  <si>
-    <t>20:52:13</t>
-  </si>
-  <si>
-    <t>22:30:08</t>
+    <t>19:34:05</t>
+  </si>
+  <si>
+    <t>21:11:14</t>
+  </si>
+  <si>
+    <t>22:48:24</t>
+  </si>
+  <si>
+    <t>20:27:50</t>
+  </si>
+  <si>
+    <t>22:05:02</t>
+  </si>
+  <si>
+    <t>19:44:24</t>
+  </si>
+  <si>
+    <t>21:21:36</t>
+  </si>
+  <si>
+    <t>22:58:34</t>
+  </si>
+  <si>
+    <t>20:38:06</t>
+  </si>
+  <si>
+    <t>22:15:09</t>
   </si>
   <si>
     <t>00:07:13</t>
   </si>
   <si>
-    <t>01:42:25</t>
-  </si>
-  <si>
-    <t>20:08:41</t>
-  </si>
-  <si>
-    <t>21:46:55</t>
-  </si>
-  <si>
-    <t>23:24:08</t>
-  </si>
-  <si>
-    <t>01:00:00</t>
+    <t>01:42:24</t>
+  </si>
+  <si>
+    <t>20:08:40</t>
+  </si>
+  <si>
+    <t>21:46:54</t>
+  </si>
+  <si>
+    <t>23:24:07</t>
+  </si>
+  <si>
+    <t>00:59:59</t>
   </si>
   <si>
     <t>19:24:48</t>
@@ -475,10 +460,10 @@
     <t>21:03:36</t>
   </si>
   <si>
-    <t>22:40:57</t>
-  </si>
-  <si>
-    <t>00:17:14</t>
+    <t>22:40:56</t>
+  </si>
+  <si>
+    <t>00:17:13</t>
   </si>
   <si>
     <t>20:20:13</t>
@@ -487,52 +472,52 @@
     <t>21:57:41</t>
   </si>
   <si>
-    <t>23:34:15</t>
-  </si>
-  <si>
-    <t>19:36:44</t>
-  </si>
-  <si>
-    <t>21:14:20</t>
-  </si>
-  <si>
-    <t>22:51:08</t>
-  </si>
-  <si>
-    <t>20:30:54</t>
-  </si>
-  <si>
-    <t>22:07:53</t>
-  </si>
-  <si>
-    <t>19:47:24</t>
-  </si>
-  <si>
-    <t>21:24:31</t>
-  </si>
-  <si>
-    <t>23:00:02</t>
-  </si>
-  <si>
-    <t>00:52:35</t>
-  </si>
-  <si>
-    <t>20:54:53</t>
-  </si>
-  <si>
-    <t>22:32:24</t>
+    <t>23:34:16</t>
+  </si>
+  <si>
+    <t>19:36:45</t>
+  </si>
+  <si>
+    <t>21:14:21</t>
+  </si>
+  <si>
+    <t>22:51:09</t>
+  </si>
+  <si>
+    <t>20:30:56</t>
+  </si>
+  <si>
+    <t>22:07:55</t>
+  </si>
+  <si>
+    <t>19:47:28</t>
+  </si>
+  <si>
+    <t>21:24:35</t>
+  </si>
+  <si>
+    <t>23:00:06</t>
+  </si>
+  <si>
+    <t>20:41:10</t>
+  </si>
+  <si>
+    <t>22:17:13</t>
   </si>
   <si>
     <t>00:09:32</t>
   </si>
   <si>
-    <t>01:45:45</t>
-  </si>
-  <si>
-    <t>20:11:36</t>
-  </si>
-  <si>
-    <t>23:26:25</t>
+    <t>01:45:44</t>
+  </si>
+  <si>
+    <t>20:11:35</t>
+  </si>
+  <si>
+    <t>21:49:11</t>
+  </si>
+  <si>
+    <t>23:26:24</t>
   </si>
   <si>
     <t>01:02:52</t>
@@ -541,7 +526,10 @@
     <t>19:28:13</t>
   </si>
   <si>
-    <t>21:05:56</t>
+    <t>21:05:55</t>
+  </si>
+  <si>
+    <t>22:43:12</t>
   </si>
   <si>
     <t>00:19:52</t>
@@ -556,28 +544,34 @@
     <t>23:36:45</t>
   </si>
   <si>
-    <t>19:39:11</t>
-  </si>
-  <si>
-    <t>21:16:35</t>
-  </si>
-  <si>
-    <t>22:53:32</t>
-  </si>
-  <si>
-    <t>20:33:10</t>
-  </si>
-  <si>
-    <t>22:10:13</t>
-  </si>
-  <si>
-    <t>19:49:40</t>
-  </si>
-  <si>
-    <t>21:26:49</t>
-  </si>
-  <si>
-    <t>23:03:07</t>
+    <t>19:39:12</t>
+  </si>
+  <si>
+    <t>21:16:36</t>
+  </si>
+  <si>
+    <t>22:53:33</t>
+  </si>
+  <si>
+    <t>20:33:12</t>
+  </si>
+  <si>
+    <t>22:10:16</t>
+  </si>
+  <si>
+    <t>19:49:44</t>
+  </si>
+  <si>
+    <t>21:26:53</t>
+  </si>
+  <si>
+    <t>23:03:11</t>
+  </si>
+  <si>
+    <t>20:43:26</t>
+  </si>
+  <si>
+    <t>22:19:58</t>
   </si>
   <si>
     <t>0°</t>
@@ -607,13 +601,16 @@
     <t>11°</t>
   </si>
   <si>
-    <t>00:52:27</t>
+    <t>27°</t>
+  </si>
+  <si>
+    <t>6°</t>
   </si>
   <si>
     <t>20:04:53</t>
   </si>
   <si>
-    <t>19:24:59</t>
+    <t>19:24:58</t>
   </si>
   <si>
     <t>20:58:18</t>
@@ -625,25 +622,31 @@
     <t>21:51:03</t>
   </si>
   <si>
-    <t>19:36:48</t>
-  </si>
-  <si>
-    <t>21:10:03</t>
-  </si>
-  <si>
-    <t>22:43:18</t>
-  </si>
-  <si>
-    <t>20:28:44</t>
-  </si>
-  <si>
-    <t>22:01:59</t>
-  </si>
-  <si>
-    <t>19:47:12</t>
-  </si>
-  <si>
-    <t>21:20:26</t>
+    <t>19:36:49</t>
+  </si>
+  <si>
+    <t>21:10:04</t>
+  </si>
+  <si>
+    <t>22:43:20</t>
+  </si>
+  <si>
+    <t>20:28:47</t>
+  </si>
+  <si>
+    <t>22:02:01</t>
+  </si>
+  <si>
+    <t>19:47:16</t>
+  </si>
+  <si>
+    <t>21:20:30</t>
+  </si>
+  <si>
+    <t>20:38:49</t>
+  </si>
+  <si>
+    <t>22:12:02</t>
   </si>
   <si>
     <t>B</t>
@@ -695,7 +698,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,13 +719,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2CBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F9FC"/>
+        <fgColor rgb="FFBBD1E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,19 +731,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCDCEE"/>
+        <fgColor rgb="FFD4E2F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3F9"/>
+        <fgColor rgb="FFDDE8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99BADE"/>
+        <fgColor rgb="FF80A9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAAC5E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,19 +761,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8F4"/>
+        <fgColor rgb="FFCCDCEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAAC5E3"/>
+        <fgColor rgb="FFB2CBE6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2C0E1"/>
+        <fgColor rgb="FF5E92CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF558CC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88AED8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0B070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6E9DD0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6697CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77A3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,67 +821,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBD1E9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF558CC8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80A9D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF90B4DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88AED8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77A3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6697CD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0B070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5E92CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6E9DD0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E2F1"/>
+        <fgColor rgb="FF99BADE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,15 +943,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1370,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
@@ -1448,54 +1424,54 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="L2" s="4">
-        <v>-18.9</v>
+        <v>-21.2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O2" s="6">
         <v>100</v>
       </c>
       <c r="P2" s="7">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="Q2" s="8">
-        <v>97</v>
-      </c>
-      <c r="R2" s="9">
+        <v>100</v>
+      </c>
+      <c r="R2" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1504,55 +1480,55 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>71</v>
+      